--- a/대리점리스트.xlsx
+++ b/대리점리스트.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22140" windowHeight="10155"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12165"/>
   </bookViews>
   <sheets>
     <sheet name="현황" sheetId="8" r:id="rId1"/>

--- a/대리점리스트.xlsx
+++ b/대리점리스트.xlsx
@@ -18,7 +18,7 @@
     <externalReference r:id="rId2"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">현황!$A$1:$E$148</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">현황!$A$1:$E$149</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="319">
   <si>
     <t>순번</t>
     <phoneticPr fontId="6" type="noConversion"/>
@@ -1054,6 +1054,14 @@
   </si>
   <si>
     <t>전재영</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>D00471</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>(주)아주레포츠_특판</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1272,7 +1280,7 @@
       <sheetName val="export"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0">
+      <sheetData sheetId="0" refreshError="1">
         <row r="2">
           <cell r="B2" t="str">
             <v>D00001</v>
@@ -4034,11 +4042,11 @@
           </cell>
         </row>
         <row r="32">
-          <cell r="B32" t="str">
-            <v>D00077</v>
-          </cell>
-          <cell r="C32" t="str">
-            <v>삼성스포츠(동대문)</v>
+          <cell r="B32" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="C32" t="e">
+            <v>#N/A</v>
           </cell>
           <cell r="D32" t="str">
             <v>사용가능</v>
@@ -4046,14 +4054,14 @@
           <cell r="E32" t="str">
             <v>일반사업자</v>
           </cell>
-          <cell r="F32" t="str">
-            <v>5670200021</v>
-          </cell>
-          <cell r="G32" t="str">
-            <v>삼성스포츠(동대문)</v>
-          </cell>
-          <cell r="H32" t="str">
-            <v>김현경</v>
+          <cell r="F32" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="G32" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="H32" t="e">
+            <v>#N/A</v>
           </cell>
           <cell r="I32" t="str">
             <v>도,소매</v>
@@ -4067,29 +4075,64 @@
           <cell r="L32" t="str">
             <v/>
           </cell>
-          <cell r="M32" t="str">
-            <v>02-2252-4765</v>
-          </cell>
-          <cell r="N32" t="str">
-            <v>0222316033</v>
-          </cell>
-          <cell r="O32" t="str">
-            <v>서울특별시 중구</v>
-          </cell>
-          <cell r="P32" t="str">
-            <v>100411</v>
+          <cell r="M32" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="N32" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="O32" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="P32" t="e">
+            <v>#N/A</v>
           </cell>
           <cell r="Q32" t="str">
-            <v>서울특별시 중구 장충단로 229</v>
+            <v xml:space="preserve">_x0001_½¬ÁÀ½Ä³ _x0000_8»½¬ÜÂ _x0000_¨º_x0004_È\¸ _x0000_1_x0000_4_x0000_6_x0000__x000D__x0000__x0000_010-6536-0306_x0012__x0000__x0000_cu1356@hanmail.net_x000E__x0000__x0000_37690004473037_x0006__x0000__x0000_D00080_x0006__x0000__x0001_ÁÀ4»0¼Ü´ü»4Ñ
+_x0000__x0000_4102544630_x0003__x0000__x0001_\Íø»½¬_x000D__x0000__x0001_0¼Ü´ü»4Ñ©ÆÔ,_x0000_ _x0000_¤ÂìÓ Î©ÆÔ_x000C__x0000__x0000_062-371-7460
+_x0000__x0000_0623717461_x0006__x0000__x0000_502859_x0014__x0000__x0001__x0011_­üÈ_x0011_­íÅÜÂ _x0000__x001C_Ál­ _x0000_ÔTÅ´Æ¬¹\¸1_x0000_1_x0000_¼8® _x0000_3_x0000__x000B__x0000__x0001_(_x0000_´Æ¬¹_x0008_Íñ´YÕP­ _x0000_ÄÖ8»)_x0000__x000D__x0000__x0000_010-4608-7460_x0015__x0000__x0000_power-psu@hanmail.net_x0003__x0000__x0001_C_x0000_ñ´	®#_x0000__x0001_2_x0000_3_x0000_F_x0000_W_x0000_ _x0000__x0018_ÂüÈ _x0000_ìÅàÂ _x0000_1_x0000_6_x0000_ _x0000_/_x0000_ _x0000_2_x0000_3_x0000_S_x0000_S_x0000_ _x0000__x0018_ÂüÈ _x0000_ìÅàÂ _x0000_2_x0000_0_x0000_ _x0000_(_x0000__x0018_ÂüÈX_x0000_)_x0000__x000E__x0000__x0000_37690004474637_x0006__x0000__x0000_D00081_x0006__x0000__x0001__x001C_Á_x0000_³8»Æ%±¤Â
+_x0000__x0000_1102115009_x0003__x0000__x0001_$ÇÜÐÄÉ_x0004__x0000__x0001_Ä³Áä¹ÅÅ_x0002__x0000__x0001_XÇX¹_x0008__x0000__x0000_20081029_x000C__x0000__x0000_02-3142-7016
+_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x001C_Á_x0000_³8»l­_x0006__x0000__x0000_120827_x0016__x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x001C_Á_x0000_³8»l­ _x0000_ðÅl×\¸ _x0000_1_x0000_9_x0000_9_x0000_ _x0000_ _x0000_1_x0000_5Î_x000D__x0000__x0000_010-5264-4932_x0012__x0000__x0000_yjjwon@hanmail.net_x000E__x0000__x0000_37690004475237_x0006__x0000__x0000_D00085_x0005__x0000__x0001_1Á_x0015_È_x0008_¸ìÓ Î
+_x0000__x0000_3120525501_x0003__x0000__x0001_1Á0®)¼_x0008__x0000__x0000_20090326_x000C__x0000__x0000_041-556-7884_x0006__x0000__x0000_331961_x0016__x0000__x0001_©Í­Ì¨°Ä³ _x0000_ÌHÅÜÂ _x0000__x001C_Á½l­ _x0000_P´_x0015_È_x0011_É8_x0000_8® _x0000_1_x0000_-_x0000_8_x0000__x000D__x0000__x0000_010-5424-8640_x0015__x0000__x0000_sjreports@hanmail.net_x0008__x0000__x0000_20090325_x000E__x0000__x0000_37690004478137_x0006__x0000__x0000_D00086_x0008__x0000__x0001_üÈÝÂÖ¬À _x0000_ÐÅ¤ÂàÅ
+_x0000__x0000_1318674023_x0003__x0000__x0001_Á_x0004_Ö8Ö_x0008__x0000__x0000_20120330_x000C__x0000__x0000_051-202-3541
+_x0000__x0000_0512013541	_x0000__x0001_½°À_x0011_­íÅÜÂ _x0000__x0015_¬_x001C_Ál­_x0006__x0000__x0000_618814$_x0000__x0001_½°À_x0011_­íÅÜÂ _x0000__x0015_¬_x001C_Ál­ _x0000_+ºÀÉ$ÆXÁÜÂðÒ1_x0000_3_x0000_\¸ _x0000_1_x0000_2_x0000_-_x0000_2_x0000_2_x0000_ _x0000_ _x0000_MÖÄÉL¾)µ _x0000_1_x0000_0_x0000_6_x0000_8Ö_x000D__x0000__x0000_010-4733-3541_x0016__x0000__x0000_coolcomy1982@naver.com_x0008__x0000__x0000_20120409_x000E__x0000__x0000_37690004479837_x0006__x0000__x0000_D00087
+_x0000__x0001_üÈÝÂÖ¬À _x0000_8ÁÄÉ¤ÂìÓ Î
+_x0000__x0000_3298701221_x0003__x0000__x0001__x0015_¼_x001C_Â¼À_x0007__x0000__x0001_Ä³ä¹ _x0000__x000F_¼ _x0000_Áä¹_x0008__x0000__x0000_20070309_x000B__x0000__x0000_02-824-8799	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_Ù³Çl­_x0005__x0000__x0000_06921_x000E__x0000__x0001__x001C_Á¸Æ _x0000_Ù³Çl­ _x0000_Ì¹Å\¸1_x0000_8® _x0000_3_x0000__x0008__x0000__x0001_ÀÉ5Î _x0000_(_x0000_ÁÀÄ³Ù³)_x0000__x000D__x0000__x0000_010-2942-3235_x0019__x0000__x0000_sejinsports2018@naver.com_x0017__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000_ _x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_9_x0000_3_x0000_-_x0000_&gt;_x0000_5_x0000_0_x0000_ _x0000_&lt;Ç\¸ _x0000_pÈ_x0015_È_x000E__x0000__x0000_37690004480837_x001A__x0000__x0001_0_x0000_1_x0000_0_x0000_ _x0000_2_x0000_7_x0000_0_x0000_5_x0000_ _x0000_3_x0000_2_x0000_3_x0000_4_x0000_ _x0000_(_x0000_ä¹¥Ç _x0000_xÆ _x0000_A_x0000_S_x0000_ô²ù²Ç)_x0000__x0006__x0000__x0000_D00089_x0006__x0000__x0001_Á_x0008_Í0¼Ü´ü»4Ñ
+_x0000__x0000_2270299081_x0003__x0000__x0001__x0015_È¬ÇÈÖ_x000C__x0000__x0000_033-638-0024
+_x0000__x0000_0336382400_x0007__x0000__x0001__x0015_¬ÐÆÄ³ _x0000_Á_x0008_ÍÜÂ_x0006__x0000__x0000_217803_x000E__x0000__x0001__x0015_¬ÐÆÄ³ _x0000_Á_x0008_ÍÜÂ _x0000_P­Ù³\¸ _x0000_3_x0000_9_x0000__x000D__x0000__x0000_010-3297-3133_x0019__x0000__x0000_yubgijung1257@hanmail.net_x000E__x0000__x0000_37690004481437_x0006__x0000__x0000_D00090_x000B__x0000__x0001_üÈÝÂÖ¬À _x0000_¤Âä¹lÂ¤ÂìÓ Î
+_x0000__x0000_8558703276_x0006__x0000__x0001_¤Âä¹lÂ¤ÂìÓ Î_x0003__x0000__x0001_$ÇÜ­ø»_x0008__x0000__x0000_20070917_x000B__x0000__x0000_01087511199_x0007__x0000__x0001_½¬0®Ä³ _x0000_HÅ°ÀÜÂ_x0005__x0000__x0000_15497_x0012__x0000__x0001_½¬0® _x0000_HÅ°ÀÜÂ _x0000_ÁÀ]¸l­ _x0000_Ì8»4_x0000_8® _x0000_1_x0000_7_x0000__x001A__x0000__x0001_1_x0000_5Î1_x0000_5_x0000_1_x0000_9_x0000_-_x0000_1_x0000_3_x0000_ _x0000_ _x0000_1_x0000_5Î _x0000_ _x0000_¤Âä¹lÂ¤ÂìÓ Î _x0000_&lt;»X¹&lt;Á0Ñ_x000D__x0000__x0000_010-5471-3330_x0013__x0000__x0000_smash-123@naver.com_x000B__x0000__x0000_01054713330_x000E__x0000__x0000_37690004483737_x0008__x0000__x0001_!Ç1Á_x0010_È&amp;_x0000_1_x0000_0_x0000_0_x0000_%_x0000__x0006__x0000__x0000_D00096_x0005__x0000__x0001_¤ÂìÓ ÎE¼lÐ
+_x0000__x0000_1272092161_x0003__x0000__x0001_@®ÄÉÉÓ_x0004__x0000__x0001_´Ì!Ç©ÆÔ_x0008__x0000__x0000_20070503_x000C__x0000__x0000_031-535-1244
+_x0000__x0000_0315352245_x0007__x0000__x0001_½¬0®Ä³ _x0000_ìÓÌÜÂ_x0006__x0000__x0000_487050_x0018__x0000__x0001_½¬0®Ä³ _x0000_ìÓÌÜÂ _x0000_p­´°tº _x0000_8Öm­\¸ _x0000_1_x0000_6_x0000_9_x0000_6_x0000_._x0000_ _x0000_2_x0000_5Î_x000D__x0000__x0000_010-6354-5471_x0011__x0000__x0000_kjp31@hanmail.net_x000E__x0000__x0000_37690004487237_x0006__x0000__x0000_D00097_x0005__x0000__x0001_¹Â¬¹¤ÂìÓ Î
+_x0000__x0000_2011081473_x0003__x0000__x0001_à¬Ñ¼°Æ_x0008__x0000__x0000_20071221_x000C__x0000__x0000_02-2279-0779
+_x0000__x0000_0222780778_x0005__x0000__x0000_04563_x001E__x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x0011_Él­ _x0000_­ÌÄ¬Ì\¸ _x0000_2_x0000_4_x0000_6_x0000_ _x0000_ _x0000_(_x0000_)¼°ÀÙ³,_x0000_ _x0000_ÉÓTÖÜÂ¥Ç)_x0000__x0016__x0000__x0001_1_x0000_,_x0000_2_x0000_,_x0000_3_x0000_5Î _x0000_ä²-_x0000_1_x0000_0_x0000_2_x0000_(_x0000_)¼°ÀÙ³,_x0000_ÉÓTÖÜÂ¥Ç)_x0000__x000D__x0000__x0000_010-3284-7383_x0019__x0000__x0000_victorysports@hanmail.net_x000E__x0000__x0000_37690004488937_x0006__x0000__x0000_D00101_x0005__x0000__x0001_DÅ°À¤ÂìÓ Î
+_x0000__x0000_3122872982_x0003__x0000__x0001_\Í+È¼¹_x000C__x0000__x0001_Ä³ä¹_x000F_¼ÁÀÔ_x0011_É_x001C_¬ÅÅ,_x0000_Áä¹ÅÅ_x0008__x0000__x0000_20110701_x000C__x0000__x0000_041-532-8381
+_x0000__x0000_0415328382_x0008__x0000__x0001_©Í­Ì¨°Ä³ _x0000_DÅ°ÀÜÂ_x0006__x0000__x0000_336050_x0010__x0000__x0001_©Í­Ì¨°Ä³ _x0000_DÅ°ÀÜÂ _x0000_ÜÂü»\¸ _x0000_2_x0000_5_x0000_1_x0000__x000D__x0000__x0000_010-4946-8385_x0013__x0000__x0000_judocjl@hanmail.net_x000E__x0000__x0000_37690004490537_x0006__x0000__x0000_D00109_x0008__x0000__x0001__x0001_Æ¤ÂìÓ Î(_x0000_¨°ÐÆ)_x0000_
+_x0000__x0000_1095289131_x0003__x0000__x0001_tÇ_x0015_ÈÌ_x0008__x0000__x0000_20071119_x000C__x0000__x0000_063-632-4154
+_x0000__x0000_0636324156_x0005__x0000__x0000_55703_x0015__x0000__x0001__x0004_È|·½Ä³ _x0000_¨°ÐÆÜÂ _x0000_¬Àä¹tº _x0000__x0000_³¬À\¸ _x0000_1_x0000_2_x0000_8_x0000_3_x0000__x0004__x0000__x0001__x0001_Æ¤ÂìÓ Î_x000D__x0000__x0000_010-4594-0634_x0013__x0000__x0000_jclee8734@naver.com_x000E__x0000__x0000_37690004497037_x0006__x0000__x0000_D00110_x0007__x0000__x0001_Æ%±¤Â _x0000_TÖ_x001C_Â_x0010_È
+_x0000__x0000_4080577085_x0003__x0000__x0001__x0004_È+º_x0019_Â_x0008__x0000__x0000_20071102_x000C__x0000__x0000_061-375-6647_x0008__x0000__x0001__x0004_È|·¨°Ä³ _x0000_TÖ_x001C_Âp­_x0006__x0000__x0000_519809_x0014__x0000__x0001__x0004_È|·¨°Ä³ _x0000_TÖ_x001C_Âp­ _x0000__x0011_­U³\¸ _x0000_1_x0000_4_x0000_0_x0000_ _x0000_ _x0000_1_x0000_5Î_x000D__x0000__x0000_010-6632-5893_x0012__x0000__x0000_ms-jon@hanmeil.net_x000E__x0000__x0000_37690004498637_x0006__x0000__x0000_D00111_x000C__x0000__x0001_,Æ¼¹=Õ+ÈiÕ¤ÂìÓ Î(_x0000_©ºìÓ)_x0000_
+_x0000__x0000_4111469486_x0003__x0000__x0001_@®=Ì©Æ_x000C__x0000__x0001_´ÆÙ³©ÆÔ,_x0000_ñ´°Àl­,_x0000_0®P±Ô_x0008__x0000__x0000_20070320_x000C__x0000__x0000_061-242-1032
+_x0000__x0000_0612443032_x0008__x0000__x0001__x0004_È|·¨°Ä³ _x0000_©ºìÓÜÂ_x0005__x0000__x0000_58726_x0010__x0000__x0001__x0004_È¨° _x0000_©ºìÓÜÂ _x0000_(Ì¼_x001D_Á8® _x0000_4_x0000_1_x0000_-_x0000_1_x0000__x0002__x0000__x0001_1_x0000_5Î_x000D__x0000__x0000_010-9243-4285_x0010__x0000__x0000_eyebono@daum.net_x000E__x0000__x0000_37690004499237_x0006__x0000__x0000_D00116_x000F__x0000__x0001_Æ%±¤ÂÈ¹°À_x0000_³¬¹_x0010_È(_x0000_ü»4Ñ¤ÂìÓ Î)_x0000_
+_x0000__x0000_6080288027_x0003__x0000__x0001_ Ç_x0001_Æ_x0019_Â_x0008__x0000__x0001_¤ÂìÓ Î©ÆÔ_x000F_¼XÇX¹_x000C__x0000__x0000_055-222-5431
+_x0000__x0000_0552225432_x0008__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_=ÌÐÆÜÂ_x0006__x0000__x0000_631852_x0018__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_=ÌÐÆÜÂ _x0000_È¹°ÀiÕìÓl­ _x0000_©ÆÈ¹\¸ _x0000_7_x0000_6_x0000_ _x0000_üÈÝÐ_x000D__x0000__x0000_010-3707-6245_x0016__x0000__x0000_dudtjs6245@hanmail.net_x000E__x0000__x0000_37690004504337_x0006__x0000__x0000_D00120_x0006__x0000__x0001_Æ%±¤Â­ÌüÈ_x0010_È
+_x0000__x0000_3170385854_x0003__x0000__x0001_\Í°Æ1Á_x000B__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_XÇX¹,_x0000__x0018_Ât¬_x0008__x0000__x0000_20110729_x000C__x0000__x0000_043-222-3040
+_x0000__x0000_0432245050_x0008__x0000__x0001_©Í­Ì½Ä³ _x0000_­ÌüÈÜÂ_x0006__x0000__x0000_361842_x0012__x0000__x0001_©Í½ _x0000_­ÌüÈÜÂ _x0000_ÁÀù²l­ _x0000_8Öø»\¸ _x0000_2_x0000_0_x0000_6_x0000__x0005__x0000__x0001_1_x0000_5Î _x0000_È!Î_x000D__x0000__x0000_010-5468-3319_x0015__x0000__x0000_wsung3525@hanmail.net_x0008__x0000__x0000_20080429_x000E__x0000__x0000_37690004507237_x0006__x0000__x0000_D00121_x000D__x0000__x0001_Æ%±¤ÂìÓmÕ_x0010_È(_x0000_XÕtÇlÐ¬¹´Å)_x0000_
+_x0000__x0000_5061736246_x0003__x0000__x0001__x0015_È@Ç_x0001_Æ_x0008__x0000__x0000_20090227_x000C__x0000__x0000_054-283-5234
+_x0000__x0000_0542835231_x0008__x0000__x0001_½¬ÁÀ½Ä³ _x0000_ìÓmÕÜÂ_x0006__x0000__x0000_790822_x0012__x0000__x0001_½¬½ _x0000_ìÓmÕÜÂ _x0000_¨°l­ _x0000__x0000_³Ä³Ù³ _x0000_8_x0000_6_x0000_-_x0000_2_x0000__x000D__x0000__x0000_010-4133-7770_x0014__x0000__x0000_minton1125@naver.com_x0008__x0000__x0000_20081105_x000E__x0000__x0000_37690004508937_x0006__x0000__x0000_D00122_x0005__x0000__x0001_°Æ¬¹¤ÂìÓ Î
+_x0000__x0000_4172105493_x0003__x0000__x0001__x0015_¼_x0018_ÂÄÉ_x0008__x0000__x0000_20180101_x000C__x0000__x0000_051-632-2681
+_x0000__x0000_0516322681_x0008__x0000__x0001_½°À_x0011_­íÅÜÂ _x0000_¨°l­_x0006__x0000__x0000_608827_x0011__x0000__x0001_½°À_x0011_­íÅÜÂ </v>
           </cell>
           <cell r="R32" t="str">
             <v/>
           </cell>
-          <cell r="S32" t="str">
-            <v>010-2764-8385</v>
-          </cell>
-          <cell r="T32" t="str">
-            <v>sspt10@naver.com</v>
+          <cell r="S32" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="T32" t="e">
+            <v>#N/A</v>
           </cell>
           <cell r="U32" t="str">
             <v/>
@@ -4106,8 +4149,8 @@
           <cell r="Y32" t="str">
             <v/>
           </cell>
-          <cell r="Z32" t="str">
-            <v>02-2252-4765</v>
+          <cell r="Z32" t="e">
+            <v>#N/A</v>
           </cell>
           <cell r="AA32" t="str">
             <v>N</v>
@@ -4126,11 +4169,11 @@
           </cell>
         </row>
         <row r="33">
-          <cell r="B33" t="str">
-            <v>D00078</v>
-          </cell>
-          <cell r="C33" t="str">
-            <v>삼성스포츠(문경)</v>
+          <cell r="B33" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="C33" t="e">
+            <v>#N/A</v>
           </cell>
           <cell r="D33" t="str">
             <v>사용가능</v>
@@ -4138,14 +4181,14 @@
           <cell r="E33" t="str">
             <v>일반사업자</v>
           </cell>
-          <cell r="F33" t="str">
-            <v>5110499001</v>
-          </cell>
-          <cell r="G33" t="str">
-            <v>삼성스포츠(문경)</v>
-          </cell>
-          <cell r="H33" t="str">
-            <v>김성기</v>
+          <cell r="F33" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="G33" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="H33" t="e">
+            <v>#N/A</v>
           </cell>
           <cell r="I33" t="str">
             <v>소매</v>
@@ -4160,31 +4203,105 @@
             <v/>
           </cell>
           <cell r="M33" t="str">
-            <v>054-554-0306</v>
-          </cell>
-          <cell r="N33" t="str">
-            <v>0545540304</v>
-          </cell>
-          <cell r="O33" t="str">
-            <v>경상북도 문경시</v>
-          </cell>
-          <cell r="P33" t="str">
-            <v>745887</v>
-          </cell>
-          <cell r="Q33" t="str">
-            <v>경상북도 문경시 모전로 146</v>
+            <v>〳ਸ਼_x0000_㔰㔴㐵㌰㐰_x0008_봁솬臀쒽₳㠀붻_xDCAC_ۂ_x0000_㐷㠵㜸_x0010_봁솬臀쒽₳㠀붻_xDCAC_⃂ꠀҺ峈₸㄀㐀㘀ഀ_x0000_㄰ⴰ㔶㘳〭〳ሶ_x0000_畣㌱㘵桀湡慭汩渮瑥_x000E_㌀㘷〹〰㐴㌷㌰ط_x0000_い〰〸_x0006_섁㓀セ_xDCBC_ﲴ㒻૑_x0000_ㄴ㈰㐵㘴〳_x0003_封붻ඬĀ배드민턴용품, 스포츠용품_x000C_　㈶㌭ㄷ㜭㘴ਰ_x0000_㘰㌲ㄷ㐷ㄶ_x0006_㔀㈰㔸ᐹĀ광주광역시 서구 풍암운리로11번길 3_x000B_⠁됀곆ࢹ妴僕₭쐀㣖⦻ഀ_x0000_㄰ⴰ㘴㠰㜭㘴ᔰ_x0000_潰敷⵲獰䁵慨浮楡⹬敮ʹĀC등급#㈁㌀䘀圀 ᠀ﳂ⃈⃂㄀㘀 ⼀ ㈀㌀匀匀 ᠀ﳂ⃈⃂㈀　 ⠀᠀ﳂ壈⤀฀_x0000_㜳㤶〰㐰㜴㘴㜳_x0006_䐀〰㠰رĀ서대문요넥스
+㄀〱ㄲ㔱〰̹Ā윤태진_x0004_쐁貳얹˅Ā의류_x0008_㈀〰ㄸ㈰హ_x0000_㈰㌭㐱ⴲ〷㘱
+ᰁ룁맆쓒_xDCBC_⃂ᰀÁ㢳治ڭ_x0000_㈱㠰㜲_x0016_ᰁ룁맆쓒_xDCBC_⃂ᰀÁ㢳治₭泅峗₸㄀㤀㤀  ㄀㔀෎_x0000_㄰ⴰ㈵㐶㐭㌹ሲ_x0000_橹睪湯桀湡慭汩渮瑥_x000E_㌀㘷〹〰㐴㔷㌲ط_x0000_い〰㔸_x0005_㄁ᗁࣈ⃓૎_x0000_ㄳ〲㈵㔵㄰_x0003_㄁チ⦮ࢼ_x0000_〲㤰㌰㘲_x000C_　ㄴ㔭㘵㜭㠸ش_x0000_㌳㤱ㄶ_x0016_꤁귍꣌쒰₳鰀䣌_xDCC5_⃂ᰀ臁沽₭倀ᖴᇈ㣉㠀₮㄀ⴀ㠀ഀ_x0000_㄰ⴰ㐵㐲㠭㐶ᔰ_x0000_橳敲潰瑲䁳慨浮楡⹬敮ࡴ_x0000_〲㤰㌰㔲_x000E_㌀㘷〹〰㐴㠷㌱ط_x0000_い〰㘸_x0008_ﰁ_xDDC8_賂곖⃀퀀꓅ૅ_x0000_㌱㠱㜶〴㌲_x0003_送Ӂ㣖ࣖ_x0000_〲㈱㌰〳_x000C_　ㄵ㈭㈰㌭㐵਱_x0000_㔰㈱㄰㔳ㄴ	老낽ᇀ_xDCC5_⃂ᔀᲬ況ڭ_x0000_ㄶ㠸㐱$老낽ᇀ_xDCC5_⃂ᔀᲬ況₭蔀삺Ⓣ壆_xDCC1_㇒㌀尀₸㄀㈀ⴀ㈀㈀  䴀쓖䳉⦾₵㄀　㘀㠀ූ_x0000_㄰ⴰ㜴㌳㌭㐵ᘱ_x0000_潣汯潣祭㤱㈸湀癡牥挮浯_x0008_㈀㄰〲〴ู_x0000_㜳㤶〰㐰㜴㠹㜳_x0006_䐀〰㠰਷Ā주식회사 세진스포츠
+㌀㤲㜸㄰㈲̱Ā박순삼_x0007_쐁₹ༀ₼谀ࢹ_x0000_〲㜰㌰㤰_x000B_　ⴲ㈸ⴴ㜸㤹	ᰁ룁맆쓒_xDCBC_⃂_xD900_醳泇֭_x0000_㘰㈹ัĀ서울 동작구 만양로1길 3_x0008_쀁㗉⃎⠀섀쓀_xD9B3_⦳ഀ_x0000_㄰ⴰ㤲㈴㌭㌲ᤵ_x0000_敳楪獮潰瑲㉳㄰䀸慮敶⹲潣᝭Ā25FW 수주여신 193-&gt;50 으로 조정_x000E_㌀㘷〹〰㐴〸㌸ᨷĀ010 2705 3234 (매장 외 AS담당자)_x0006_䐀〰㠰عĀ속초배드민턴
+㈀㜲㈰㤹㠰̱Ā정재훈_x000C_　㌳㘭㠳〭㈰਴_x0000_㌰㘳㠳㐲〰_x0007_ᔁ킬쓆₳贀ࣁ_xDCCD_ۂ_x0000_ㄲ㠷㌰_x000E_ᔁ킬쓆₳贀ࣁ_xDCCD_⃂倀_xD9AD_岳₸㌀㤀ഀ_x0000_㄰ⴰ㈳㜹㌭㌱ᤳ_x0000_畹杢橩湵ㅧ㔲䀷慨浮楡⹬敮๴_x0000_㜳㤶〰㐰㠴㐱㜳_x0006_䐀〰㤰ରĀ주식회사 스매쉬스포츠
+㠀㔵㜸㌰㜲ضĀ스매쉬스포츠_x0003_␁_xDCC7_ࢻ_x0000_〲㜰㤰㜱_x000B_　〱㜸ㄵㄱ㤹_x0007_봁ガ쒮₳䠀냅_xDCC0_ׂ_x0000_㔱㤴ሷĀ경기 안산시 상록구 천문4길 17_x001A_㄁㔀㇎㔀㄀㤀ⴀ㄀㌀  ㄀㔀⃎ ꐀ油꓂⃓⃎㰀墻㲹チෑ_x0000_㄰ⴰ㐵ㄷ㌭㌳ጰ_x0000_浳獡⵨㈱䀳慮敶⹲潣୭_x0000_㄰㔰㜴㌱㌳ะ_x0000_㜳㤶〰㐰㠴㜳㜳_x0008_℁㇇Ⴡ⛈㄀　　─؀_x0000_い〰㘹_x0005_ꐁ⃓䗎沼ૐ_x0000_㈱㈷㤰ㄲㄶ_x0003_䀁쒮짉ӓĀ체육용품_x0008_㈀〰〷〵ళ_x0000_㌰ⴱ㌵ⴵ㈱㐴
+　ㄳ㌵㈵㐲ܵĀ경기도 포천시_x0006_㐀㜸㔰ᠰĀ경기도 포천시 군내면 호국로 1696. 2층_x000D_　〱㘭㔳ⴴ㐵ㄷ_x0011_欀灪ㄳ桀湡慭汩渮瑥_x000E_㌀㘷〹〰㐴㜸㌲ط_x0000_い〰㜹_x0005_뤁곂꒹⃓૎_x0000_〲ㄱ㠰㐱㌷_x0003_톬낼ࣆ_x0000_〲㜰㈱ㄲ_x000C_　ⴲ㈲㤷〭㜷ਹ_x0000_㈰㈲㠷㜰㠷_x0005_　㔴㌶_x001E_ᰁ룁맆쓒_xDCBC_⃂ᄀ泉₭관쓌鲬峌₸㈀㐀㘀  ⠀⤀낼_xD9C0_ⲳ 준哓_xDCD6_ꗂ⧇ᘀĀ1,2,3층 다-102(방산동,평화시장)_x000D_　〱㌭㠲ⴴ㌷㌸_x0019_瘀捩潴祲灳牯獴桀湡慭汩渮瑥_x000E_㌀㘷〹〰㐴㠸㌹ط_x0000_い㄰㄰_x0005_䐁냅꓀⃓૎_x0000_ㄳ㈲㜸㤲㈸_x0003_封藍볈ಹĀ도매및상품중개업,소매업_x0008_㈀㄰〱〷ఱ_x0000_㐰ⴱ㌵ⴲ㌸ㄸ
+　ㄴ㌵㠲㠳࠲Ā충청남도 아산시_x0006_㌀㘳㔰ူĀ충청남도 아산시 시민로 251_x000D_　〱㐭㐹ⴶ㌸㔸_x0013_樀摵捯汪桀湡慭汩渮瑥_x000E_㌀㘷〹〰㐴〹㌵ط_x0000_い㄰㤰_x0008_ā꓆⃓⣎ꠀ킰⧆਀_x0000_〱㔹㠲ㄹㄳ_x0003_琁ᗇ鳈࣌_x0000_〲㜰ㄱ㤱_x000C_　㌶㘭㈳㐭㔱਴_x0000_㘰㘳㈳ㄴ㘵_x0005_㔀㜵㌰_x0015_Ё糈膷쒽₳ꠀ킰_xDCC6_⃂가璹₺_x0000_겳峀₸㄀㈀㠀㌀ЀĀ영스포츠_x000D_　〱㐭㤵ⴴ㘰㐳_x0013_樀汣敥㜸㐳湀癡牥挮浯_x000E_㌀㘷〹〰㐴㜹㌰ط_x0000_い㄰〱_x0007_鐁◆꒱⃂吀᳖Ⴢૈ_x0000_〴〸㜵〷㔸_x0003_Ё藈ᦺࣂ_x0000_〲㜰ㄱ㈰_x000C_　ㄶ㌭㔷㘭㐶࠷Ā전라남도 화순군_x0006_㔀㤱〸ᐹĀ전라남도 화순군 광덕로 140  1층_x000D_　〱㘭㌶ⴲ㠵㌹_x0012_洀⵳潪䁮慨浮楥⹬敮๴_x0000_㜳㤶〰㐰㤴㘸㜳_x0006_䐀〰ㄱఱĀ올림픽종합스포츠(목포)
+㐀ㄱ㐱㤶㠴̶Ā김창용_x000C_됁_xD9C6_꦳裆Ⳕ내泀ⲭ　傮袱ࣔ_x0000_〲㜰㌰〲_x000C_　ㄶ㈭㈴ㄭ㌰ਲ_x0000_㘰㈱㐴〳㈳_x0008_Ё糈ꢷ쒰₳꤀_xDCD3_ׂ_x0000_㠵㈷ံĀ전남 목포시 차범석길 41-1_x0002_㄁㔀෎_x0000_㄰ⴰ㈹㌴㐭㠲ဵ_x0000_祥扥湯䁯慤浵渮瑥_x000E_㌀㘷〹〰㐴㤹㌲ط_x0000_い㄰㘱_x000F_鐁◆꒱죂낹À겳Ⴙ⣈ﰀ㒻ꓑ⃓⧎਀_x0000_〶〸㠲〸㜲_x0003_ ǇᧆࣂĀ스포츠용품및의류_x000C_　㔵㈭㈲㔭㌴਱_x0000_㔰㈵㈲㐵㈳_x0008_봁솬ꣀ쒰₳㴀탌_xDCC6_ۂ_x0000_㌶㠱㈵_x0018_봁솬ꣀ쒰₳㴀탌_xDCC6_⃂저낹槀泓₭꤀죆岹₸㜀㘀 ﰀ_xDDC8_ැ_x0000_㄰ⴰ㜳㜰㘭㐲ᘵ_x0000_畤瑤獪㈶㔴桀湡慭汩渮瑥_x000E_㌀㘷〹〰㔴㐰㌳ط_x0000_い㄰〲_x0006_鐁◆꒱귂ﳌ჈ૈ_x0000_ㄳ〷㠳㠵㐵_x0003_封냍㇆ுĀ스포츠용품,의류,수건_x0008_㈀㄰〱㈷హ_x0000_㐰ⴳ㈲ⴲ〳〴
+　㌴㈲㔴㔰࠰Ā충청북도 청주시_x0006_㌀ㄶ㐸ሲĀ충북 청주시 상당구 호미로 206_x0005_㄁㔀⃎谀⇈෎_x0000_㄰ⴰ㐵㠶㌭ㄳᔹ_x0000_獷湵㍧㈵䀵慨浮楡⹬敮ࡴ_x0000_〲㠰㐰㤲_x000E_㌀㘷〹〰㔴㜰㌲ط_x0000_い㄰ㄲ_x000D_鐁◆꒱淓ვ⣈堀瓕泇곐뒹⧅਀_x0000_〵ㄶ㌷㈶㘴_x0003_ᔁ䃈Ǉࣆ_x0000_〲㤰㈰㜲_x000C_　㐵㈭㌸㔭㌲਴_x0000_㔰㈴㌸㈵ㄳ_x0008_봁솬臀쒽₳淓_xDCD5_ۂ_x0000_㤷㠰㈲_x0012_봁膬₽淓_xDCD5_⃂ꠀ沰₭_x0000_쒳_xD9B3_₳㠀㘀ⴀ㈀ഀ_x0000_㄰ⴰㄴ㌳㜭㜷ᐰ_x0000_業瑮湯ㄱ㔲湀癡牥挮浯_x0008_㈀〰ㄸ〱ี_x0000_㜳㤶〰㐰〵㤸㜳_x0006_䐀〰㈱ԲĀ우리스포츠
+㐀㜱ㄲ㔰㤴̳Ā박수진_x0008_㈀㄰〸〱ఱ_x0000_㔰ⴱ㌶ⴲ㘲ㄸ
+　ㄵ㌶㈲㠶࠱Ā부산광역시 남구_x0006_㘀㠰㈸ᄷĀ부산광역시 남구 자유평화로 49_x000D_　〱㈭㤵ⴴ㘲㈸_x0015_洀硯敩〲〰桀湡慭汩渮瑥_x000E_㌀㘷〹〰㔴㤰㌵ط_x0000_い㄰㌲_x0005_뀁㇆꓁⃓૎_x0000_〲㜷〰㜳㠰_x0003_䀁䒮_xDDC6_ࣂ_x0000_〲㜰〱㤰_x000B_　ⴲ㘴ⴵ㈱㜹	　㐲㔶ㄱ㜹	ᰁ룁맆쓒_xDCBC_⃂ᄀ쒭泉ڭ_x0000_㐱㤳ㄶ_x0010_ᰁ룁맆쓒_xDCBC_⃂ᄀ쒭泉₭氀墭峇₸㘀㘀᐀Ā1층 (구의동 227-6) 우성스포츠_x000D_　〱㌭ㄴⴸ㈱〳_x000F_眀㑳㠱湀癡牥挮浯_x000E_㌀㘷〹〰㔴〱㌵ط_x0000_い㄰㘲_x0005_퀁_xD9C6_뒳⇌곇ી_x0000_〳〶㘳㜳㠴_x0003_ﰁ톻솼ӉĀ운동기구_x0008_㈀〰〵〷వ_x0000_㐰ⴲ㌵ⴱ〴㐰
+　㈴㌵㠲㤸࠹Ā대전광역시 동구_x0005_㌀㘴〳_x000D__x0001_ҳ⃈_xD900_河₭_x0000_ҳ峈₸㜀㘀㔀ഀ_x0000_㄰ⴰ㐵㌵㤭㌵ሶ_x0000_潷獮潰桀湡慭汩渮瑥_x0008_㈀〰〸ㄲิ_x0000_㜳㤶〰㐰ㄵㄱ㜳_x0006_䐀〰㈱࠷Ā원스포츠(제주)
+㘀㘱㤰㈶㔰̱Ā김미경_x000C_　㐶㜭㈵㐭㈴ਲ_x0000_㘰㜴㌲㤲㈹_x000C_ᰁﳈ마쓒邼壇쓎₳ᰀ상_xDCD3_ۂ_x0000_㤶㄰ㄶ_x0013_ᰁﳈ마쓒邼壇쓎₳ᰀﳈ_xDCC8_⃂␀糆岷₸㄀㌀㐀ഀ_x0000_㄰ⴰ㐴㘱㐭ㄴᔲ_x0000_牣湯べ〱䀴慨浮楡⹬敮๴_x0000_㜳㤶〰㐰ㄵ㠲㜳_x0006_䐀〰㌱ԲĀ전주요넥스
+㐀㈰㠰㜸㠸̷Ā이순종_x000C_　㌶㈭㐷㤭㌳਷_x0000_㘰㈳㠷㌹㜳_x0008_Ё糈膷쒽₳Ѐﳈ_xDCC8_ۂ_x0000_㘵〰〸_x0013_Ё糈膷쒽₳Ѐﳈ_xDCC8_⃂䐀냆泀₭膬岽₸㈀　ഀ_x0000_㄰ⴰ㈹㐲㠭㤳ေ_x0000_祪湯硥湀癡牥挮浯_x000E_㌀㘷〹〰㔴㘱㌳ط_x0000_い㄰㘳_x0005_ᰁ糈꓇⃓૎_x0000_〴〴㌵㔳㈴_x000B_ᰁ糈ࣇ¸꓈⃓⣎ᔀ䷈⧇̀Ā김광복	됁_xD9C6_コ沮ྭ뒼_xD9C6_碼ೆ_x0000_㘰ⴳ㌵ⴵㄹ㘴
+　㌶㌵㈳㤰࠳Ā전라북도 정읍시_x0006_㔀〸〸༴Ā전라북도 정읍시 중앙로 83_x000D_　〱㤭㜵ⴹ㠷〰_x0016_猀潰瑲㥳㐱䀶慨浮䥡⹬敮๴_x0000_㜳㤶〰㐰㈵㈰㜳_x0006_䐀〰㌱ଷĀ주식회사 배드민턴마트
+㄀〱ㄸ㌹〲̳Ā정이녀_x000B_ꐁ⃓꧎裆⃔Ѐ郈쇇烀颬ࢷ_x0000_〲㌱㜰㌲_x000C_　ㄳ㤭㐶㌭㌵र_x0000_㈰㠳㤲㔵ܵĀ경기도 고양시_x0005_㄀㔰㐶_x0011_봁ガ₮醬_xDCC5_⃂唀醳泅₭밀ꇀ峁₸㄀㈀܀Ā4층 418호_x000D_　〱㜭㔱ⴲ㔷㠳_x0014_洀湩潴浮牡䁴慮敶⹲潣๭_x0000_㜳㤶〰㐰㈵㤱㜳_x0006_䐀〰㌱सĀ주식회사동우스포츠
+㄀〱ㄸ〸㈴̶Ā송정일_x000B_　ⴲ㠳ⴲ㔳㠹	　㌲㔵㔳㘸	ᰁ룁맆쓒_xDCBC_⃂䀀짇泓ڭ_x0000_㈱㤲㌰_x0018_ᰁ룁맆쓒_xDCBC_⃂䀀짇泓₭᳅峁₸㈀㤀ⴀ㄀ _xD900_낳꓆⃓෎_x0000_㄰ⴰ〲㠱㌭㤵ሸ_x0000_癤灩㈱㌳湀癡牥挮浯_x000B_　〱㐷㔳㔳㠹
+᠁ࣂ₮耀熽㳈峇₸딀່᳑_x0000_㜳㤶〰㐰㈵㔲㜳_x0006_䐀〰㐱ऱĀ중앙스포츠(경주)
+㌀㈲㘶〰㈳̳Ā황영실_x0008_㈀〰ㄸㄲర_x0000_㔰ⴴ㐷ⴱㄵ㜷_x0008_봁솬臀쒽₳봀ﲬ_xDCC8_ۂ_x0000_㠷㤰㌴_x0012_봁솬臀쒽₳봀ﲬ_xDCC8_⃂ࠀㆮ峁₸㈀㤀㐀ⴀ㄀ഀ_x0000_㄰ⴰ㔷㤷㔭㜱ᐷ_x0000_慪灳㌶㐰桀湡慭汩渮瑥_x0008_㈀〰ㄸㄲั_x0000_㜳㤶〰㐰㈵㐵㜳_x0006_䐀〰㐱ԵĀ청룡스포츠
+㘀㔱㜰㘹〳̷Ā조미숙_x0008_㈀㄰㄰〰ఴ_x0000_㔰ⴵㄳⴲ㔹㤵
+　㔵ㄳ㤲㘵࠰Ā경상남도 김해시_x0006_㘀ㄲ㌸ሳĀ경상남도 김해시 장유로 297-5_x000D_　〱㤭ㄵⴳ㔹㤵_x0016_樀獭ㄳ㤲㔵䀹慨浮楡⹬敮ࡴ_x0000_〲〱〱㤱_x000E_㌀㘷〹〰㔴〳㌰ط_x0000_い㄰㠴_x0007__x0001_瓏擇䓅꒾⃓૎_x0000_㈱㈳㠴〱㠶_x0003_ᔁ薼邺ೇ_x0000_㌰ⴱ㔴ⴷ㜸㘰
+　ㄳ㔴㠷〷ܷĀ경기도 안양시_x0006_㐀ㄳ㌸ሷĀ경기도 안양시 동안구 귀인로 89_x000D_　〱㜭㌳ⴸ㌷㔷_x0016_樀浡慪楬〲䀰慨浮楡⹬敮๴_x0000_㜳㤶〰㐰㌵㈲㜳_x0006_䐀〰㐱हĀ코리아오픈(김천)
+㔀〱㄰㜴㈳̴Ā박선영_x0008_㈀〰〷㈴ళ_x0000_㔰ⴴ㌴ⴰ〷㜰
+　㐵㌴㜰〰࠷Ā경상북도 김천시_x0005_㌀㘹㘲_x000E_봁膬₽䀀鲮_xDCCC_⃂ꄀⓁ峁₸㄀㘀㐀ഀ_x0000_㄰ⴰㄴ㔱㘭〳ጶ_x0000_橪〱㔶䀴慨浮楡⹬敮๴_x0000_㜳㤶〰㐰㌵㤳㜳_x0006_䐀〰㔱԰Ā팔구스포츠
+㔀㈰㄰㌵〲̴Ā신상규_x0008_㈀〰〸㌳ఱ_x0000_㔰ⴳ㔹ⴷ㤸㤸
+　㌵㐹㈳㐳࠵Ā대구광역시 동구_x0005_㐀ㄱ㌹_x000F__x0001_河₭_xD900_河₭䐀釅峅ㆸ㄀㠀₮㠀㄀ࠀĀ1층 팔구스포츠_x000D_　〱㠭㔸ⴴ㤸㤸_x0012_㠀猹潰瑲䁳慮敶⹲潣๭_x0000_㜳㤶〰㐰㌵㔴㜳_x0006_䐀〰㔱ԹĀ혜성스포츠
+㄀〳㔰ㄳ㠰̹Ā이의선_x000D_ꐁ⃓꧎裆Ⳕ_x0000_Ҭ᳈裈Ⳕꄀ哇ࣖ_x0000_〲㜰㔰㤲_x000C_　㈳㘭㐵㈭㌱ਲ਼_x0000_㌰㘲㐵ㄲ㈳_x0007_봁ガ쒮₳耀鲽_xDCCC_ۂ_x0000_㈴㠲㤱 봁ガ쒮₳耀鲽_xDCCC_⃂谀곁泀₭봀碬峇ㆸ㈀　蠀㢼₮㈀㠀  ㄀㔀჎⃓㄀砀෎_x0000_㄰ⴰ㔷㠷㜭㐷ᔰ_x0000_獨ㄷ㜶㐷䀱慨浮楡⹬敮๴_x0000_㜳㤶〰㐰㐵㌱㜳_x0006_䐀〰㘱԰Ā호동스포츠
+㄀㐲㤳㤱㐰̷Ā김호동_x0008_㈀㄰〰ㄱళ_x0000_㌰ⴱ㜳ⴵ㌰ㄳ
+　ㄳ㜳〵㌳ܱĀ경기도 오산시_x0006_㐀㜴〸ᨲĀ경기도 오산시 성호대로 25 운산빌딩  1층 4_x000D_　〱㔭㤲ⴵ㈸㠷_x0013_欀摨㤹㈸桀湡慭汩渮瑥_x000E_㌀㘷〹〰㔴㈴㌰ط_x0000_い㄰ㄶ_x0005_䴁㇖铁◆꒱ૂ_x0000_ㄳ〰㐶㔰㠱_x0003_䀁Үᗖࣈ_x0000_〲㤰㘰㘱_x000C_　ㄴ㘭㐳㜭㈳࠷Ā충청남도 홍성군_x0005_㌀㈲㌶_x0012_꤁꣍₰䴀㇖烁₭䴀臖䶽⃇꤀꣍°岳₸㌀㘀ᔀĀ제 1층 제 101호(빌앤더스오피스텔)_x000D_　〱㠭㈶ⴶ㠹㔲_x0010_栀楪㈹䀳慮敶⹲潣๭_x0000_㜳㤶〰㐰㐵㘳㜳_x0006_䐀〰㘱శĀ(주)티제이디스트리뷰션
+㈀ㄱ㜸㈳ㄵ̶Ā송상원_x0006_쐁貳₹쐀ࢹĀ스포츠용품 무역_x0008_㈀㄰〲ㄹ଱_x0000_㈰㔭ㄱ㔭ㄱऴĀ서울특별시 강남구_x0006_㄀㔳㄰ରĀ서울특별시강남구논현동_x000E_ࠁ䂮䳇⦾₵㄀㔀⃎ꀀ꒼룂ꓒꃂ듑ළ_x0000_㄰ⴰ㜸㐸ㄭ㔶ᔱ_x0000_敢瑳硥牴浥䁥慮敶⹲潣m_x0007__x0000__x0001_B_x0000_ñ´	®(_x0000_T_x0000_S_x0000_)_x0000__x0005__x0000__x0000_14049_x0003__x0000__x0001__x0015_¼_x0004_ÖÄÉ_x0008__x0000__x0000_20190917_x0006__x0000__x0000_D00167_x0008__x0000__x0001_üÈÝÂÖ¬À _x0000_ÐÆÐÅÇ
+_x0000__x0000_1268800066_x0003__x0000__x0001_@®DÕ¹Â_x0006__x0000__x0001_Ä³Áä¹ÅÅ _x0000_xÆ_x0007__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_xÆ_x000C__x0000__x0000_02-1644-1662	_x0000__x0001_½°À_x0011_­íÅÜÂ _x0000__x0018_Â_x0001_Æl­_x0006__x0000__x0000_613815_x0013__x0000__x0001_½°À_x0011_­íÅÜÂ _x0000__x0018_Â_x0001_Æl­ _x0000__x0011_­¨°\¸ _x0000_6_x0000_3_x0000_ _x0000_B_x0000_Ù³_x0004__x0000__x0001_4_x0000_5Î|Ç½_x000D__x0000__x0000_010-8882-4137_x0014__x0000__x0000_oneeight@hanmail.net_x0006__x0000__x0000_D00173_x0005__x0000__x0001__x0008_®_x0001_Æ¤ÂìÓ Î
+_x0000__x0000_1052087391_x0003__x0000__x0001_°ÆÀÉÐÆ_x0008__x0000__x0000_20140217_x000D__x0000__x0000_010-6208-8112_x0006__x0000__x0000_121889_x0013__x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_È¹ìÓl­ _x0000_Ù³P­\¸3_x0000_8® _x0000_1_x0000_2_x0000_5_x0000__x0013__x0000__x0000_yonex0901@naver.com_x0008__x0000__x0000_20150122_x000E__x0000__x0000_37690004557937_x0006__x0000__x0000_D00181_x0004__x0000__x0001__x0000_É¤ÂìÓ Î
+_x0000__x0000_1410240836_x0003__x0000__x0001__x0015_¼½¬·_x0008__x0000__x0000_20140825_x000C__x0000__x0000_031-945-2007_x0007__x0000__x0001_½¬0®Ä³ _x0000__x000C_ÓüÈÜÂ_x0006__x0000__x0000_413819$_x0000__x0001_½¬0®Ä³ _x0000__x000C_ÓüÈÜÂ _x0000_DÅ¬¹·\¸ _x0000_5_x0000_5_x0000_ _x0000_-_x0000_8_x0000_1_x0000_ _x0000_(_x0000__x0008_®_x000C_ÍÙ³,_x0000_ _x0000__x000C_ÓüÈ_x0008_®_x000C_ÍXÕ_x0018_ÂÌ¬¹¥Ç)_x0000__x000C__x0000__x0001__x000C_ÓüÈÜÂ _x0000_0¼Ü´ü»4Ñ_x0004_È©Æl­¥Ç_x000D__x0000__x0000_010-9129-1126_x0017__x0000__x0000_leesjun1024@hanmail.net_x000E__x0000__x0000_37690004547137_x0006__x0000__x0000_D00183_x0003__x0000__x0001_T³_x001C_È|Ç
+_x0000__x0000_1171558537_x0003__x0000__x0001_iÖÐÆ Á_x000B__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_XÇX¹,_x0000_¡ÇTÖ_x0008__x0000__x0000_20141027_x000D__x0000__x0000_010-6333-2457	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_ÅÌl­_x0005__x0000__x0000_08078 _x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_ÅÌl­ _x0000_àÂ_x0015_È\¸ _x0000_2_x0000_7_x0000_5_x0000_ _x0000_ _x0000_(_x0000_àÂ_x0015_ÈÙ³,_x0000_ _x0000_àÂ¸Ò¬¹DÅ_x000C_Ó¸Ò)_x0000__x0010__x0000__x0001_ÁÀ_x0000_¬Ù³ _x0000_1_x0000_5Î _x0000_1_x0000_0_x0000_4_x0000_,_x0000_ _x0000_1_x0000_0_x0000_5_x0000_8Ö_x0011__x0000__x0000_thejeil@naver.com_x000D__x0000__x0000_010-9668-2210_x000E__x0000__x0000_37690004550437_x0006__x0000__x0000_D00184_x0005__x0000__x0001_$Æ¨°¤ÂìÓ Î
+_x0000__x0000_1322489384_x0003__x0000__x0001_Å+È¨º_x000D__x0000__x0001_´ÆÙ³0®l­©ÆÔ _x0000_aÅ8Á_x001C_Á¬¹ _x0000_xÆ_x0008__x0000__x0000_20141028
+_x0000__x0000_0315756464
+_x0000__x0000_0315755600_x0008__x0000__x0001_½¬0®Ä³ _x0000_¨°ÅüÈÜÂ_x0006__x0000__x0000_472881_x0016__x0000__x0001_½¬0®Ä³ _x0000_¨°ÅüÈÜÂ _x0000_ÄÉt¬$Æ¨°\¸ _x0000_8_x0000_0_x0000_6_x0000_ _x0000_-_x0000_1_x0000_4_x0000__x000D__x0000__x0000_010-9289-9637_x0012__x0000__x0000_jongmo83@naver.com_x000E__x0000__x0000_37690004552737_x0006__x0000__x0000_D00186_x0005__x0000__x0001_ä¹XÎìÓxÇ¸Ò
+_x0000__x0000_6091853217_x0003__x0000__x0001_iÖ­ÝÂ_x0008__x0000__x0000_20141202_x000C__x0000__x0000_055-298-7330_x0005__x0000__x0000_51378_x0011__x0000__x0001_½¬¨° _x0000_=ÌÐÆÜÂ _x0000_XÇ=Ìl­ _x0000__x0018_¼Ä¬\¸ _x0000_6_x0000_3_x0000__x000D__x0000__x0000_010-3561-0209_x000E__x0000__x0000_o2bbi@nate.com_x0008__x0000__x0000_20141212_x000E__x0000__x0000_37690004554037_x0006__x0000__x0000_D00190_x0005__x0000__x0001_p­°À¤ÂìÓ Î
+_x0000__x0000_4010657765_x0003__x0000__x0001__x0015_¼_x001C_Âl×	_x0000__x0001_¤ÂìÓ ÎXÇX¹,_x0000_ _x0000_©ÆÔ_x0008__x0000__x0000_20150406_x000D__x0000__x0000_010-9977-7141_x0008__x0000__x0001__x0004_È|·½Ä³ _x0000_p­°ÀÜÂ_x0005__x0000__x0000_54102_x000F__x0000__x0001__x0004_È½ _x0000_p­°ÀÜÂ _x0000_¨°_x0018_Â¡Á5_x0000_8® _x0000_4_x0000_2_x0000__x000F__x0000__x0001_1_x0000_0_x0000_1_x0000_8Ö(_x0000__x0018_Â¡ÁÙ³,_x0000_ _x0000_(Ì$Æ¹L¾)_x0000__x0013__x0000__x0000_shp7141@hanmaiL.net_x000E__x0000__x0000_37690004558537_x0006__x0000__x0000_D00192
+_x0000__x0001__x0001_Æ8»¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1222039517_x0005__x0000__x0001__x0001_Æ8»¤ÂìÓ Î_x0003__x0000__x0001_@®_x0001_Æ8»_x0008__x0000__x0000_20150608_x000C__x0000__x0000_032-523-1406_x000C__x0000__x0000_032-517-8009	_x0000__x0001_xÇÌ_x0011_­íÅÜÂ _x0000_½ÉÓl­_x0005__x0000__x0000_21337_x000D__x0000__x0000_010-4320-1406_x0012__x0000__x0000_YM1406@hanmail.net_x0007__x0000__x0001_A_x0000_ñ´	®(_x0000_T_x0000_S_x0000_)_x0000__x0005__x0000__x0000_13042_x0003__x0000__x0001_@®Ù³½¬_x000E__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_+_x0000_3_x0000_0_x0000__x000E__x0000__x0000_37690004561837_x0006__x0000__x0000_D00193_x000B__x0000__x0001_ÑÐ¤Â@Õ¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1320972497_x0006__x0000__x0001_ÑÐ¤Â@Õ¤ÂìÓ Î_x0003__x0000__x0001__x0015_¼_x0004_Ö=Ì_x0006__x0000__x0001_´ÆÙ³_x0004_È8»©ÆÔ_x0008__x0000__x0000_20150610_x000D__x0000__x0000_010-3706-2477_x0007__x0000__x0001_½¬0®Ä³ _x0000_l­¬¹ÜÂ_x0005__x0000__x0000_11907_x000F__x0000__x0001_½¬0® _x0000_l­¬¹ÜÂ _x0000_UÆ_x0019_ÂÌ\¸ _x0000_5_x0000_0_x0000_7_x0000_	_x0000__x0001_3_x0000_5Î _x0000_ÑÐ¤Â@Õ¤ÂìÓ Î_x000F__x0000__x0000_pspin@naver.com_x0005__x0000__x0000_22022_x0003__x0000__x0001_HÅ°ÆÄÉ_x000C__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_7_x0000_._x0000_5_x0000__x000E__x0000__x0000_37690004560137_x0006__x0000__x0000_D00195
+_x0000__x0001_¤ÂìÓ ÎLÑlÐ(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_6172249744_x0005__x0000__x0001_¤ÂìÓ ÎLÑlÐ_x0003__x0000__x0001_tÇÝÐ0®_x0006__x0000__x0001__x001C_ÈpÈÅÅ _x0000_Áä¹_x000C__x0000__x0001_õ¬_x0008_Æ _x0000_¤ÂìÓ Î©ÆÔ,_x0000_ _x0000_¡ÇTÖ_x000B__x0000__x0000_051-7564800_x000C__x0000__x0000_051-756-4801_x0005__x0000__x0000_48222_x0017__x0000__x0001_½°À_x0011_­íÅÜÂ _x0000_Ù³·l­ _x0000_+ÈiÕ´ÆÙ³¥Ç\¸ _x0000_4_x0000_0_x0000_¼8® _x0000_8_x0000_'_x0000__x0001_1_x0000_0_x0000_3_x0000_Ù³ _x0000_1_x0000_0_x0000_5_x0000_8Ö,_x0000_1_x0000_0_x0000_6_x0000_8Ö(_x0000_¬ÀÁÉÙ³,_x0000_½°À _x0000_DÅÜÂDÅÜ´ _x0000_TÏ$Æq¸ _x0000_XÕ²DÌ _x0000_DÅ_x000C_Ó¸Ò)_x0000__x000D__x0000__x0000_010-5578-1988_x0015__x0000__x0000_ltktennis@hanmail.net_x000B__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_8_x0000__x0008__x0000__x0000_20150611_x000E__x0000__x0000_37690004562437_x0006__x0000__x0000_D00196	_x0000__x0001__x0015_¬¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_5041920932_x0004__x0000__x0001__x0015_¬¤ÂìÓ Î_x0003__x0000__x0001__x0015_¬@Çl­_x000D__x0000__x0001_LÑÈ²¤Â©ÆÔ,_x0000_ _x0000_XÇX¹,_x0000_ _x0000_àÂ_x001C_¼_x000C__x0000__x0000_053-314-9090_x0005__x0000__x0000_41433_x000D__x0000__x0000_010-3828-0474_x0013__x0000__x0000_keg0417@hanmail.net_x000D__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_6_x0000_+_x0000_1_x0000_5_x0000__x0008__x0000__x0000_20150612_x000E__x0000__x0000_37690004565337_x0006__x0000__x0000_D00199
+_x0000__x0001_P´¬¹¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1283008985_x0003__x0000__x0001_@®_x0001_Æ Á_x000B__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_¤ÂìÓ ÎXÇX¹_x0008__x0000__x0000_20150703_x000C__x0000__x0000_031-911-4191_x000C__x0000__x0000_031-913-0067_x0006__x0000__x0000_410829_x000F__x0000__x0001_½¬0®Ä³à¬ÅÜÂ _x0000_|Ç°ÀÙ³l­_x0015_È_x001C_¼°ÀÙ³_x000E__x0000__x0001_1_x0000_1_x0000_4_x0000_8_x0000_-_x0000_1_x0000_3_x0000_ _x0000_1_x0000_5Î2_x0000_,_x0000_3_x0000_8Ö_x000D__x0000__x0000_010-4288-3563_x0012__x0000__x0000_usop2n@hanmail.net_x000D__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_6_x0000_+_x0000_2_x0000_3_x0000__x000E__x0000__x0000_37690004568237_x0006__x0000__x0000_D00201_x000E__x0000__x0001_(_x0000_üÈ)_x0000_¤ÂtÎtÇ¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_6278102573_x000B__x0000__x0001_¤ÂtÎtÇ¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000__x0003__x0000__x0001_@®1ÁÐÆ_x0006__x0000__x0001_Áä¹ÅÅ _x0000_Ä³ä¹_x0008__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_ä¹_x0010_È_x000C__x0000__x0000_041-566-1879_x000C__x0000__x0000_041-554-2732_x0005__x0000__x0000_31157"_x0000__x0001_©Í­Ì¨°Ä³ _x0000_ÌHÅÜÂ _x0000__x001C_Á½l­ _x0000_1¼_x001D_Á3_x0000_\¸ _x0000_2_x0000_9_x0000_ _x0000_ _x0000_(_x0000_1¼_x001D_ÁÙ³,_x0000_ _x0000_½¶É¹_x0008_Ã%¼)_x0000__x000D__x0000__x0000_010-4513-1879_x0011__x0000__x0000_kimsw000@nate.com_x000E__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_4_x0000_0_x0000_+_x0000_2_x0000_0_x0000__x0008__x0000__x0000_20150804_x000E__x0000__x0000_37690004570937_x0006__x0000__x0000_D00202_x0008__x0000__x0001_¤ÂìÓå²(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_3052275067_x0003__x0000__x0001_HÅü­¹Â_x000C__x0000__x0000_042-522-9566_x000C__x0000__x0000_042-271-4786_x0006__x0000__x0000_300810_x0017__x0000__x0001__x0000_³_x0004_È_x0011_­íÅÜÂ _x0000__x0011_Él­ _x0000_Ù³_x001C_Á_x0000_³\¸ _x0000_1_x0000_2_x0000_0_x0000_1_x0000_(_x0000_ÜÐÉÓÙ³)_x0000__x0007__x0000__x0001_¤ÂìÓå² _x0000_ÜÐÉÓ_x0010_È_x000B__x0000__x0000_01062224787_x0010__x0000__x0000_spodaq@naver.com_x000D__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_5_x0000_+_x0000_3_x0000_3_x0000__x0008__x0000__x0000_20150805_x000E__x0000__x0000_37690004571537_x0006__x0000__x0000_D00203	_x0000__x0001_ðÅTÏ¬¹DÅ(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_2041477980_x0004__x0000__x0001_ðÅTÏ¬¹DÅ_x0003__x0000__x0001_@®ÁÀ0®_x0006__x0000__x0001_Ä³Áä¹ _x0000_t¬$Á_x000D__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_´Ì!ÇÜÂ_x001C_Á&lt;»$ÁXÎ_x0008__x0000__x0000_20150806_x000C__x0000__x0000_02-3390-4345_x000C__x0000__x0000_02-3390-4344
+_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_Ù³_x0000_³8»l­_x0005__x0000__x0000_02496_x0011__x0000__x0001__x001C_Á¸Æ _x0000_Ù³_x0000_³8»l­ _x0000_Ý¹°Æ\¸1_x0000_2_x0000_8® _x0000_1_x0000_9_x0000__x000B__x0000__x0001_1_x0000_5Î _x0000_XÕtÇÐÆ¤ÂìÓ Î°ÀÅÅ_x000D__x0000__x0000_010-9089-5363_x0017__x0000__x0000_01090895363@hanmail.net_x000B__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_2_x0000_0_x0000__x000E__x0000__x0000_37690004572137_x0006__x0000__x0000_D00205_x0005__x0000__x0001_ÁLÑ¤ÂìÓ Î
+_x0000__x0000_1971301851_x0003__x0000__x0001_@®_x0001_Æ_x0018_Â_x0008__x0000__x0001_Ä³Áä¹ÅÅ _x0000_Ä³ä¹ÅÅ	_x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_4»íÅÅÅ_x000B__x0000__x0000_01063388568_x0008__x0000__x0001_½¬0®Ä³ _x0000_XÇ_x0015_È½ÜÂ_x0005__x0000__x0000_11806!_x0000__x0001_½¬0®Ä³ _x0000_XÇ_x0015_È½ÜÂ _x0000_$Æ©º\¸ _x0000_1_x0000_7_x0000_0_x0000_ _x0000_°Àä´È¹DÇ _x0000_DÅ_x000C_Ó¸Ò _x0000_4_x0000_1_x0000_2_x0000_-_x0000_7_x0000_0_x0000_6_x0000__x000D__x0000__x0000_010-6338-8568_x0011__x0000__x0000_3388568@naver.com_x0005__x0000__x0000_26002_x0003__x0000__x0001__x0015_¬ÜÐ8Ö_x0008__x0000__x0000_20220901_x000E__x0000__x0000_37690004700437_x0006__x0000__x0000_D00209_x0018__x0000__x0001_¤ÂìÓ Î_x000C_Õì·¤Â(_x0000_S_x0000_p_x0000_o_x0000_r_x0000_t_x0000_s_x0000_ _x0000_P_x0000_l_x0000_u_x0000_s_x0000_)_x0000_(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1192167071_x0003__x0000__x0001__x0015_¬ÜÂ¨º_x0006__x0000__x0001_Ä³Áä¹ _x0000_LÇÝÂ_x0008__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_\ÕÝÂ_x000B__x0000__x0000_02-871-5513	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x0000_­EÅl­_x0005__x0000__x0000_08750_x000F__x0000__x0001__x001C_Á¸Æ _x0000__x0000_­EÅl­ _x0000_àÂ¼¹\¸3_x0000_8® _x0000_4_x0000_0_x0000__x0005__x0000__x0001_ÀÉXÕ _x0000_1_x0000_5Î_x000D__x0000__x0000_010-7703-5353_x001A__x0000__x0000_tennisplus0122@esero.go.krX_x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_ _x0000_/_x0000_ _x0000_2_x0000_5_x0000_S_x0000_S_x0000_ _x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_ _x0000_/_x0000_ _x0000_2_x0000_4_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_9_x0000_._x0000_6_x0000_ _x0000_/_x0000_ _x0000_2_x0000_4_x0000_S_x0000_S_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_ _x0000_/_x0000_ _x0000_2_x0000_3_x0000_F_x0000_W_x0000_ _x0000__x0018_ÂüÈ _x0000_ìÅàÂ _x0000_ _x0000_1_x0000_2_x0000_ _x0000_(_x0000_ô²ù²Ç _x0000_Æ­Ì&lt;Ç\¸ _x0000_6_x0000_ _x0000__x0018_¼_x0001_Æ)_x0000__x0008__x0000__x0000_20160114_x000E__x0000__x0000_37690004577337_x0006__x0000__x0000_D00210_x0011__x0000__x0001_(_x0000_üÈ)_x0000_ÐÅtÇ_x001C_ÈtÇxÇ0Ñ´°TÁ °(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1268641398_x000C__x0000__x0000_031-761-8980_x000C__x0000__x0000_031-761-2140_x0005__x0000__x0000_12769_x000D__x0000__x0000_010-4552-3318	_x0000__x0000_1800-6142_x000E__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_4_x0000_0_x0000_+_x0000_2_x0000_5_x0000__x0008__x0000__x0000_20160121_x000E__x0000__x0000_37690004578037_x0006__x0000__x0000_D00256	_x0000__x0001_p¬1Á¤ÂìÓ Î(_x0000_Å°À)_x0000_
+_x0000__x0000_6210808090_x0003__x0000__x0001__x0015_È+È_x0015_¬_x0006__x0000__x0001_Ä³Áä¹ _x0000__x001C_ÈpÈ_x000B__x0000__x0001_ìÕ¤Â0®l­,_x0000_ _x0000_¤ÂìÓ Î©ÆÔ_x0008__x0000__x0000_20160412_x000C__x0000__x0000_055-387-3613_x000C__x0000__x0000_055-387-3615_x0008__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_Å°ÀÜÂ_x0005__x0000__x0000_50621 _x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_Å°ÀÜÂ _x0000__x001C_Á|ÇÙ³\¸ _x0000_2_x0000_5_x0000_ _x0000_ _x0000_(_x0000__x0011_É½Ù³,_x0000_ _x0000_$Ç ÁÝÀ_x0001_Æ´ÅP­äÂ)_x0000__x000D__x0000__x0000_010-2390-2994_x0013__x0000__x0000_dhrhr68@hanmail.netH_x0000__x0001_2_x0000_4_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_3_x0000_5_x0000_ _x0000_/_x0000_2_x0000_4_x0000_S_x0000_S_x0000__x0018_ÂüÈìÅàÂ _x0000_3_x0000_5_x0000_ _x0000_/_x0000_ _x0000_2_x0000_3_x0000_F_x0000_W_x0000_ _x0000__x0018_ÂüÈ _x0000_ìÅàÂ _x0000_3_x0000_5_x0000_ _x0000_/_x0000_ _x0000_2_x0000_3_x0000_S_x0000_S_x0000_ _x0000__x0018_ÂüÈ _x0000_ìÅàÂ _x0000_3_x0000_5_x0000_(_x0000_|·_x0013_Ï+_x0000_È¹D¾¤Â _x0000_9_x0000_4_x0000_3_x0000_,_x0000_2_x0000_5_x0000_0_x0000_)_x0000__x0008__x0000__x0000_20160407_x000E__x0000__x0000_37690004581237_x0006__x0000__x0000_D00267_x0006__x0000__x0001__x001C_ÈtÇD¾¤ÂìÓ Î
+_x0000__x0000_6664100083_x0003__x0000__x0001_Ç_x0015_È\Õ_x000D__x0000__x0001_Ä³ä¹ _x0000__x000F_¼ _x0000_Áä¹ÅÅ,_x0000_ _x0000__x001C_ÁD¾¤Â_x000C__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_ _x0000__x0011_­à¬_x0000_³ÕÅÅ_x0008__x0000__x0000_20160610_x000C__x0000__x0000_062-523-7451_x000C__x0000__x0000_062-523-7455_x0005__x0000__x0000_62023_x000D__x0000__x0001__x0011_­üÈ _x0000__x001C_Ál­ _x0000_´ÆÌ\¸ _x0000_1_x0000_2_x0000_2_x0000__x0005__x0000__x0001_(_x0000__x000D_Ã_x000C_ÍÙ³)_x0000__x000D__x0000__x0000_010-4606-4538_x0015__x0000__x0000_jhrim1226@hanmail.net_x0008__x0000__x0000_20160601_x000E__x0000__x0000_37690004584137_x0006__x0000__x0000_D00280_x0005__x0000__x0001_Ä³ô²¤ÂìÓ Î
+_x0000__x0000_3071042161_x0003__x0000__x0001_$ÇÙ³ÝÂ_x000B__x0000__x0001_Ä³ä¹_x000F_¼ _x0000_Áä¹ÅÅ _x0000_Áä¹ÅÅ_x0010__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_Ç_x0004_Èp¬ _x0000__x0010_Óä¹,_x0000_ _x0000__x0000_³ìÅ_x0008__x0000__x0000_20160825_x000C__x0000__x0000_044-863-8908_x000C__x0000__x0000_044-863-8970_x000F__x0000__x0001_8Á+È¹ÒÄ¼ÇXÎÜÂ _x0000_8Á+È¹ÒÄ¼ÇXÎÜÂ_x0005__x0000__x0000_30102_x001E__x0000__x0001_8Á+È¹ÒÄ¼ÇXÎÜÂ _x0000__x0008_È¬Ç\¸ _x0000_1_x0000_7_x0000_2_x0000_ _x0000_(_x0000_´ÅÄÉÙ³,_x0000_ _x0000_ÜÐ\Õ_x0004_Õ_x0008_¸¤Â&lt;Á0Ñ)_x0000__x0004__x0000__x0001_1_x0000_0_x0000_1_x0000_8Ö_x000D__x0000__x0000_010-7185-8008_x0015__x0000__x0000_dodamsports@naver.com_x000E__x0000__x0000_37690004586437_x0006__x0000__x0000_D00282_x0005__x0000__x0001__x0004_²¬¹¤ÂìÓ Î
+_x0000__x0000_1082124505_x0003__x0000__x0001_@®l×_x0015_È_x0006__x0000__x0001_Áä¹ _x0000_Ä³Áä¹_x000C__x0000__x0001__x0004_ÈÇÁÀp¬·ÅÅ _x0000_0¼Ü´ü»4Ñ _x0000__x000B__x0000__x0000_02-848-6291_x000B__x0000__x0000_02-848-7556
+_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x0001_Æñ´ìÓl­_x0005__x0000__x0000_07375_x000E__x0000__x0001__x001C_Á¸Æ _x0000__x0001_Æñ´ìÓl­ _x0000_Ä³àÂ\¸ _x0000_5_x0000_1_x0000__x000D__x0000__x0001_1_x0000_5Î _x0000_1_x0000_0_x0000_5_x0000_8Ö(_x0000_¡ÁU³L¾)µ)_x0000__x000D__x0000__x0000_010-8393-6291_x0013__x0000__x0000_hee00jung@naver.com_x0008__x0000__x0000_20160905_x000E__x0000__x0000_37690004588737_x0006__x0000__x0000_D00286_x0007__x0000__x0001_Æ%±¤Â _x0000_1Á¨°_x0010_È
+_x0000__x0000_2603001743_x0003__x0000__x0001_MÖ¥Ç8Ö_x0008__x0000__x0001_Ä³ä¹ _x0000__x000F_¼ _x0000_Áä¹ÅÅ_x0008__x0000__x0000_20151218_x000C__x0000__x0000_031-755-7257_x0007__x0000__x0001_½¬0®Ä³ _x0000_1Á¨°ÜÂ_x0005__x0000__x0000_13110_x001E__x0000__x0001_½¬0®Ä³ _x0000_1Á¨°ÜÂ _x0000__x0018_Â_x0015_Èl­ _x0000_1Á¨°_x0000_³\¸ _x0000_1_x0000_2_x0000_6_x0000_7_x0000_ _x0000_-_x0000_1_x0000_ _x0000_(_x0000_ÜÐÉÓÙ³)_x0000__x000D__x0000__x0000_010-7191-7257_x0012__x0000__x0000_nero1016@naver.com_x0002__x0000__x0001_¨°¸Ó_x0008__x0000__x0000_20161109_x000E__x0000__x0000_37690004591037_x0006__x0000__x0000_D00287_x0005__x0000__x0001_¤ÐtÎ¤ÂìÓ Î
+_x0000__x0000_6103752918_x0003__x0000__x0001_@®ÜÐÇ_x0008__x0000__x0000_20161125_x000C__x0000__x0000_052-268-6086_x000C__x0000__x0000_052-272-5908_x0008__x0000__x0001_¸Æ°À_x0011_­íÅÜÂ _x0000_¨°l­_x0005__x0000__x0000_44692_x0016__x0000__x0001_¸Æ°À_x0011_­íÅÜÂ _x0000_¨°l­ _x0000_Ë³ÈÉ\¸ _x0000_1_x0000_2_x0000_4_x0000_ _x0000_ _x0000_(_x0000_ì²Ù³)_x0000__x0003__x0000__x0000_3/2_x000D__x0000__x0000_010-9568-6086_x0014__x0000__x0000_kika5908@hanmail.net_x000E__x0000__x0000_37690004592637_x0006__x0000__x0000_D00292_x0008__x0000__x0001_Æ%±¤Â _x0000_¤ÂìÓÐÆ_x0010_È
+_x0000__x0000_6977800050_x0003__x0000__x0001_\ÕÀ­_x0001_Æ_x0008__x0000__x0000_20170102_x000C__x0000__x0000_051-517-3862_x000C__x0000__x0000_051-583-1023	_x0000__x0001_½°À_x0011_­íÅÜÂ _x0000__x0008_®_x0015_Èl­_x0005__x0000__x0000_46207&amp;_x0000__x0001_½°À_x0011_­íÅÜÂ _x0000__x0008_®_x0015_Èl­ _x0000_´Ì!Çõ¬ÐÆ\¸3_x0000_9_x0000_9_x0000_¼8® _x0000_3_x0000_2_x0000_4_x0000_ _x0000_ _x0000_(_x0000_P´l­Ù³,_x0000_ _x0000_¤ÂìÓÐÆ_x000C_ÓlÐ)_x0000__x0010__x0000__x0001_ÀÉXÕ1_x0000_5Î(_x0000_P´l­Ù³,_x0000_ _x0000_äÂ´°´Ì!Ç_x0000_­)_x0000__x000D__x0000__x0000_010-5505-3862_x0013__x0000__x0000_hgy4285@hanmail.net_x000E__x0000__x0000_37690004595537_x0006__x0000__x0000_D00306_x0007__x0000__x0001_Æ%±¤Â _x0000_ÁÀ4»_x0010_È
+_x0000__x0000_8042300420_x0003__x0000__x0001_@®_x0004_Ö+È_x000D__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_´ÆÙ³©ÆÔ _x0000_¡ÇTÖ_x0008__x0000__x0000_20170119_x000D__x0000__x0000_010-6886-7065_x000C__x0000__x0000_062-374-5410_x0005__x0000__x0000_61970_x0013__x0000__x0001__x0011_­üÈ _x0000__x001C_Ál­ _x0000_ÁÀ4»ü»üÈ\¸3_x0000_2_x0000_¼8® _x0000_3_x0000_-_x0000_5_x0000__x0013__x0000__x0000_sskim-j@hanmail.net_x000E__x0000__x0000_37690004597837_x0006__x0000__x0000_D00308_x0005__x0000__x0001_C_x0000_S_x0000_¤ÂìÓ Î
+_x0000__x0000_2270838785_x0007__x0000__x0001_iÖ_x001C_ÂU³xÆ _x0000_1_x0000_+º_x000C__x0000__x0000_031-385-1222_x000C__x0000__x0000_031-388-3477_x0005__x0000__x0000_13958_x0016__x0000__x0001_½¬0® _x0000_HÅÅÜÂ _x0000_Ì¹HÅl­ _x0000__x0008_Æ Âõ¬ÐÆ\¸5_x0000_2_x0000_¼8® _x0000_2_x0000__x000D__x0000__x0000_010-3176-9037_x0013__x0000__x0000_bill@cssports.co.kr_x000D__x0000__x0000_010-2727-2718_x000F__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_5_x0000_+_x0000_3_x0000_._x0000_5_x0000__x000E__x0000__x0000_37690004598437_x0006__x0000__x0000_D00311
+_x0000__x0001_TÏ¬¹DÅ¤ÂìÓ Î(_x0000_ÜÂe×)_x0000_
+_x0000__x0000_3047001336_x0006__x0000__x0001_TÏ¬¹DÅ¤ÂìÓ Î_x0003__x0000__x0001_\Í_x0001_Æ_x0019_Â_x0012__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000__x0010_Ó	Í&lt;»,_x0000_xÇÄÁ&lt;»,_x0000_0®ÀÐ©ÆÔ_x000D__x0000__x0000_010-2618-5518_x000C__x0000__x0000_031-312-8982_x0007__x0000__x0001_½¬0®Ä³ _x0000_ÜÂe×ÜÂ_x0005__x0000__x0000_14922_x000F__x0000__x0001_½¬0® _x0000_ÜÂe×ÜÂ _x0000_@ÇÄ¬¼_x0001_Æ8® _x0000_2_x0000_7_x0000__x000F__x0000__x0001_3_x0000_0_x0000_3_x0000_8Ö(_x0000_@ÇÕÙ³,_x0000_ _x0000_ÜÂðÒ_x000C_ÓlÐ)_x0000__x0015__x0000__x0000_queenmt5518@naver.com_x000C__x0000__x0000_031-404-6121_x0008__x0000__x0000_20170220_x000E__x0000__x0000_37690004600637_x0006__x0000__x0000_D00312_x000E__x0000__x0001_Æ%±¤Â(_x0000_Y_x0000_O_x0000_N_x0000_E_x0000_X_x0000_)_x0000_ _x0000_t</v>
+          </cell>
+          <cell r="N33" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="O33" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="P33" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="Q33" t="e">
+            <v>#N/A</v>
           </cell>
           <cell r="R33" t="str">
             <v/>
           </cell>
-          <cell r="S33" t="str">
-            <v>010-6536-0306</v>
-          </cell>
-          <cell r="T33" t="str">
-            <v>cu1356@hanmail.net</v>
-          </cell>
-          <cell r="U33" t="str">
-            <v>김성기</v>
+          <cell r="S33" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="T33" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="U33" t="e">
+            <v>#N/A</v>
           </cell>
           <cell r="V33" t="str">
             <v/>
@@ -4199,7 +4316,81 @@
             <v/>
           </cell>
           <cell r="Z33" t="str">
-            <v>054-554-0306</v>
+            <v>〳ਸ਼_x0000_㔰㔴㐵㌰㐰_x0008_봁솬臀쒽₳㠀붻_xDCAC_ۂ_x0000_㐷㠵㜸_x0010_봁솬臀쒽₳㠀붻_xDCAC_⃂ꠀҺ峈₸㄀㐀㘀ഀ_x0000_㄰ⴰ㔶㘳〭〳ሶ_x0000_畣㌱㘵桀湡慭汩渮瑥_x000E_㌀㘷〹〰㐴㌷㌰ط_x0000_い〰〸_x0006_섁㓀セ_xDCBC_ﲴ㒻૑_x0000_ㄴ㈰㐵㘴〳_x0003_封붻ඬĀ배드민턴용품, 스포츠용품_x000C_　㈶㌭ㄷ㜭㘴ਰ_x0000_㘰㌲ㄷ㐷ㄶ_x0006_㔀㈰㔸ᐹĀ광주광역시 서구 풍암운리로11번길 3_x000B_⠁됀곆ࢹ妴僕₭쐀㣖⦻ഀ_x0000_㄰ⴰ㘴㠰㜭㘴ᔰ_x0000_潰敷⵲獰䁵慨浮楡⹬敮ʹĀC등급#㈁㌀䘀圀 ᠀ﳂ⃈⃂㄀㘀 ⼀ ㈀㌀匀匀 ᠀ﳂ⃈⃂㈀　 ⠀᠀ﳂ壈⤀฀_x0000_㜳㤶〰㐰㜴㘴㜳_x0006_䐀〰㠰رĀ서대문요넥스
+㄀〱ㄲ㔱〰̹Ā윤태진_x0004_쐁貳얹˅Ā의류_x0008_㈀〰ㄸ㈰హ_x0000_㈰㌭㐱ⴲ〷㘱
+ᰁ룁맆쓒_xDCBC_⃂ᰀÁ㢳治ڭ_x0000_㈱㠰㜲_x0016_ᰁ룁맆쓒_xDCBC_⃂ᰀÁ㢳治₭泅峗₸㄀㤀㤀  ㄀㔀෎_x0000_㄰ⴰ㈵㐶㐭㌹ሲ_x0000_橹睪湯桀湡慭汩渮瑥_x000E_㌀㘷〹〰㐴㔷㌲ط_x0000_い〰㔸_x0005_㄁ᗁࣈ⃓૎_x0000_ㄳ〲㈵㔵㄰_x0003_㄁チ⦮ࢼ_x0000_〲㤰㌰㘲_x000C_　ㄴ㔭㘵㜭㠸ش_x0000_㌳㤱ㄶ_x0016_꤁귍꣌쒰₳鰀䣌_xDCC5_⃂ᰀ臁沽₭倀ᖴᇈ㣉㠀₮㄀ⴀ㠀ഀ_x0000_㄰ⴰ㐵㐲㠭㐶ᔰ_x0000_橳敲潰瑲䁳慨浮楡⹬敮ࡴ_x0000_〲㤰㌰㔲_x000E_㌀㘷〹〰㐴㠷㌱ط_x0000_い〰㘸_x0008_ﰁ_xDDC8_賂곖⃀퀀꓅ૅ_x0000_㌱㠱㜶〴㌲_x0003_送Ӂ㣖ࣖ_x0000_〲㈱㌰〳_x000C_　ㄵ㈭㈰㌭㐵਱_x0000_㔰㈱㄰㔳ㄴ	老낽ᇀ_xDCC5_⃂ᔀᲬ況ڭ_x0000_ㄶ㠸㐱$老낽ᇀ_xDCC5_⃂ᔀᲬ況₭蔀삺Ⓣ壆_xDCC1_㇒㌀尀₸㄀㈀ⴀ㈀㈀  䴀쓖䳉⦾₵㄀　㘀㠀ූ_x0000_㄰ⴰ㜴㌳㌭㐵ᘱ_x0000_潣汯潣祭㤱㈸湀癡牥挮浯_x0008_㈀㄰〲〴ู_x0000_㜳㤶〰㐰㜴㠹㜳_x0006_䐀〰㠰਷Ā주식회사 세진스포츠
+㌀㤲㜸㄰㈲̱Ā박순삼_x0007_쐁₹ༀ₼谀ࢹ_x0000_〲㜰㌰㤰_x000B_　ⴲ㈸ⴴ㜸㤹	ᰁ룁맆쓒_xDCBC_⃂_xD900_醳泇֭_x0000_㘰㈹ัĀ서울 동작구 만양로1길 3_x0008_쀁㗉⃎⠀섀쓀_xD9B3_⦳ഀ_x0000_㄰ⴰ㤲㈴㌭㌲ᤵ_x0000_敳楪獮潰瑲㉳㄰䀸慮敶⹲潣᝭Ā25FW 수주여신 193-&gt;50 으로 조정_x000E_㌀㘷〹〰㐴〸㌸ᨷĀ010 2705 3234 (매장 외 AS담당자)_x0006_䐀〰㠰عĀ속초배드민턴
+㈀㜲㈰㤹㠰̱Ā정재훈_x000C_　㌳㘭㠳〭㈰਴_x0000_㌰㘳㠳㐲〰_x0007_ᔁ킬쓆₳贀ࣁ_xDCCD_ۂ_x0000_ㄲ㠷㌰_x000E_ᔁ킬쓆₳贀ࣁ_xDCCD_⃂倀_xD9AD_岳₸㌀㤀ഀ_x0000_㄰ⴰ㈳㜹㌭㌱ᤳ_x0000_畹杢橩湵ㅧ㔲䀷慨浮楡⹬敮๴_x0000_㜳㤶〰㐰㠴㐱㜳_x0006_䐀〰㤰ରĀ주식회사 스매쉬스포츠
+㠀㔵㜸㌰㜲ضĀ스매쉬스포츠_x0003_␁_xDCC7_ࢻ_x0000_〲㜰㤰㜱_x000B_　〱㜸ㄵㄱ㤹_x0007_봁ガ쒮₳䠀냅_xDCC0_ׂ_x0000_㔱㤴ሷĀ경기 안산시 상록구 천문4길 17_x001A_㄁㔀㇎㔀㄀㤀ⴀ㄀㌀  ㄀㔀⃎ ꐀ油꓂⃓⃎㰀墻㲹チෑ_x0000_㄰ⴰ㐵ㄷ㌭㌳ጰ_x0000_浳獡⵨㈱䀳慮敶⹲潣୭_x0000_㄰㔰㜴㌱㌳ะ_x0000_㜳㤶〰㐰㠴㜳㜳_x0008_℁㇇Ⴡ⛈㄀　　─؀_x0000_い〰㘹_x0005_ꐁ⃓䗎沼ૐ_x0000_㈱㈷㤰ㄲㄶ_x0003_䀁쒮짉ӓĀ체육용품_x0008_㈀〰〷〵ళ_x0000_㌰ⴱ㌵ⴵ㈱㐴
+　ㄳ㌵㈵㐲ܵĀ경기도 포천시_x0006_㐀㜸㔰ᠰĀ경기도 포천시 군내면 호국로 1696. 2층_x000D_　〱㘭㔳ⴴ㐵ㄷ_x0011_欀灪ㄳ桀湡慭汩渮瑥_x000E_㌀㘷〹〰㐴㜸㌲ط_x0000_い〰㜹_x0005_뤁곂꒹⃓૎_x0000_〲ㄱ㠰㐱㌷_x0003_톬낼ࣆ_x0000_〲㜰㈱ㄲ_x000C_　ⴲ㈲㤷〭㜷ਹ_x0000_㈰㈲㠷㜰㠷_x0005_　㔴㌶_x001E_ᰁ룁맆쓒_xDCBC_⃂ᄀ泉₭관쓌鲬峌₸㈀㐀㘀  ⠀⤀낼_xD9C0_ⲳ 준哓_xDCD6_ꗂ⧇ᘀĀ1,2,3층 다-102(방산동,평화시장)_x000D_　〱㌭㠲ⴴ㌷㌸_x0019_瘀捩潴祲灳牯獴桀湡慭汩渮瑥_x000E_㌀㘷〹〰㐴㠸㌹ط_x0000_い㄰㄰_x0005_䐁냅꓀⃓૎_x0000_ㄳ㈲㜸㤲㈸_x0003_封藍볈ಹĀ도매및상품중개업,소매업_x0008_㈀㄰〱〷ఱ_x0000_㐰ⴱ㌵ⴲ㌸ㄸ
+　ㄴ㌵㠲㠳࠲Ā충청남도 아산시_x0006_㌀㘳㔰ူĀ충청남도 아산시 시민로 251_x000D_　〱㐭㐹ⴶ㌸㔸_x0013_樀摵捯汪桀湡慭汩渮瑥_x000E_㌀㘷〹〰㐴〹㌵ط_x0000_い㄰㤰_x0008_ā꓆⃓⣎ꠀ킰⧆਀_x0000_〱㔹㠲ㄹㄳ_x0003_琁ᗇ鳈࣌_x0000_〲㜰ㄱ㤱_x000C_　㌶㘭㈳㐭㔱਴_x0000_㘰㘳㈳ㄴ㘵_x0005_㔀㜵㌰_x0015_Ё糈膷쒽₳ꠀ킰_xDCC6_⃂가璹₺_x0000_겳峀₸㄀㈀㠀㌀ЀĀ영스포츠_x000D_　〱㐭㤵ⴴ㘰㐳_x0013_樀汣敥㜸㐳湀癡牥挮浯_x000E_㌀㘷〹〰㐴㜹㌰ط_x0000_い㄰〱_x0007_鐁◆꒱⃂吀᳖Ⴢૈ_x0000_〴〸㜵〷㔸_x0003_Ё藈ᦺࣂ_x0000_〲㜰ㄱ㈰_x000C_　ㄶ㌭㔷㘭㐶࠷Ā전라남도 화순군_x0006_㔀㤱〸ᐹĀ전라남도 화순군 광덕로 140  1층_x000D_　〱㘭㌶ⴲ㠵㌹_x0012_洀⵳潪䁮慨浮楥⹬敮๴_x0000_㜳㤶〰㐰㤴㘸㜳_x0006_䐀〰ㄱఱĀ올림픽종합스포츠(목포)
+㐀ㄱ㐱㤶㠴̶Ā김창용_x000C_됁_xD9C6_꦳裆Ⳕ내泀ⲭ　傮袱ࣔ_x0000_〲㜰㌰〲_x000C_　ㄶ㈭㈴ㄭ㌰ਲ_x0000_㘰㈱㐴〳㈳_x0008_Ё糈ꢷ쒰₳꤀_xDCD3_ׂ_x0000_㠵㈷ံĀ전남 목포시 차범석길 41-1_x0002_㄁㔀෎_x0000_㄰ⴰ㈹㌴㐭㠲ဵ_x0000_祥扥湯䁯慤浵渮瑥_x000E_㌀㘷〹〰㐴㤹㌲ط_x0000_い㄰㘱_x000F_鐁◆꒱죂낹À겳Ⴙ⣈ﰀ㒻ꓑ⃓⧎਀_x0000_〶〸㠲〸㜲_x0003_ ǇᧆࣂĀ스포츠용품및의류_x000C_　㔵㈭㈲㔭㌴਱_x0000_㔰㈵㈲㐵㈳_x0008_봁솬ꣀ쒰₳㴀탌_xDCC6_ۂ_x0000_㌶㠱㈵_x0018_봁솬ꣀ쒰₳㴀탌_xDCC6_⃂저낹槀泓₭꤀죆岹₸㜀㘀 ﰀ_xDDC8_ැ_x0000_㄰ⴰ㜳㜰㘭㐲ᘵ_x0000_畤瑤獪㈶㔴桀湡慭汩渮瑥_x000E_㌀㘷〹〰㔴㐰㌳ط_x0000_い㄰〲_x0006_鐁◆꒱귂ﳌ჈ૈ_x0000_ㄳ〷㠳㠵㐵_x0003_封냍㇆ுĀ스포츠용품,의류,수건_x0008_㈀㄰〱㈷హ_x0000_㐰ⴳ㈲ⴲ〳〴
+　㌴㈲㔴㔰࠰Ā충청북도 청주시_x0006_㌀ㄶ㐸ሲĀ충북 청주시 상당구 호미로 206_x0005_㄁㔀⃎谀⇈෎_x0000_㄰ⴰ㐵㠶㌭ㄳᔹ_x0000_獷湵㍧㈵䀵慨浮楡⹬敮ࡴ_x0000_〲㠰㐰㤲_x000E_㌀㘷〹〰㔴㜰㌲ط_x0000_い㄰ㄲ_x000D_鐁◆꒱淓ვ⣈堀瓕泇곐뒹⧅਀_x0000_〵ㄶ㌷㈶㘴_x0003_ᔁ䃈Ǉࣆ_x0000_〲㤰㈰㜲_x000C_　㐵㈭㌸㔭㌲਴_x0000_㔰㈴㌸㈵ㄳ_x0008_봁솬臀쒽₳淓_xDCD5_ۂ_x0000_㤷㠰㈲_x0012_봁膬₽淓_xDCD5_⃂ꠀ沰₭_x0000_쒳_xD9B3_₳㠀㘀ⴀ㈀ഀ_x0000_㄰ⴰㄴ㌳㜭㜷ᐰ_x0000_業瑮湯ㄱ㔲湀癡牥挮浯_x0008_㈀〰ㄸ〱ี_x0000_㜳㤶〰㐰〵㤸㜳_x0006_䐀〰㈱ԲĀ우리스포츠
+㐀㜱ㄲ㔰㤴̳Ā박수진_x0008_㈀㄰〸〱ఱ_x0000_㔰ⴱ㌶ⴲ㘲ㄸ
+　ㄵ㌶㈲㠶࠱Ā부산광역시 남구_x0006_㘀㠰㈸ᄷĀ부산광역시 남구 자유평화로 49_x000D_　〱㈭㤵ⴴ㘲㈸_x0015_洀硯敩〲〰桀湡慭汩渮瑥_x000E_㌀㘷〹〰㔴㤰㌵ط_x0000_い㄰㌲_x0005_뀁㇆꓁⃓૎_x0000_〲㜷〰㜳㠰_x0003_䀁䒮_xDDC6_ࣂ_x0000_〲㜰〱㤰_x000B_　ⴲ㘴ⴵ㈱㜹	　㐲㔶ㄱ㜹	ᰁ룁맆쓒_xDCBC_⃂ᄀ쒭泉ڭ_x0000_㐱㤳ㄶ_x0010_ᰁ룁맆쓒_xDCBC_⃂ᄀ쒭泉₭氀墭峇₸㘀㘀᐀Ā1층 (구의동 227-6) 우성스포츠_x000D_　〱㌭ㄴⴸ㈱〳_x000F_眀㑳㠱湀癡牥挮浯_x000E_㌀㘷〹〰㔴〱㌵ط_x0000_い㄰㘲_x0005_퀁_xD9C6_뒳⇌곇ી_x0000_〳〶㘳㜳㠴_x0003_ﰁ톻솼ӉĀ운동기구_x0008_㈀〰〵〷వ_x0000_㐰ⴲ㌵ⴱ〴㐰
+　㈴㌵㠲㤸࠹Ā대전광역시 동구_x0005_㌀㘴〳_x000D__x0001_ҳ⃈_xD900_河₭_x0000_ҳ峈₸㜀㘀㔀ഀ_x0000_㄰ⴰ㐵㌵㤭㌵ሶ_x0000_潷獮潰桀湡慭汩渮瑥_x0008_㈀〰〸ㄲิ_x0000_㜳㤶〰㐰ㄵㄱ㜳_x0006_䐀〰㈱࠷Ā원스포츠(제주)
+㘀㘱㤰㈶㔰̱Ā김미경_x000C_　㐶㜭㈵㐭㈴ਲ_x0000_㘰㜴㌲㤲㈹_x000C_ᰁﳈ마쓒邼壇쓎₳ᰀ상_xDCD3_ۂ_x0000_㤶㄰ㄶ_x0013_ᰁﳈ마쓒邼壇쓎₳ᰀﳈ_xDCC8_⃂␀糆岷₸㄀㌀㐀ഀ_x0000_㄰ⴰ㐴㘱㐭ㄴᔲ_x0000_牣湯べ〱䀴慨浮楡⹬敮๴_x0000_㜳㤶〰㐰ㄵ㠲㜳_x0006_䐀〰㌱ԲĀ전주요넥스
+㐀㈰㠰㜸㠸̷Ā이순종_x000C_　㌶㈭㐷㤭㌳਷_x0000_㘰㈳㠷㌹㜳_x0008_Ё糈膷쒽₳Ѐﳈ_xDCC8_ۂ_x0000_㘵〰〸_x0013_Ё糈膷쒽₳Ѐﳈ_xDCC8_⃂䐀냆泀₭膬岽₸㈀　ഀ_x0000_㄰ⴰ㈹㐲㠭㤳ေ_x0000_祪湯硥湀癡牥挮浯_x000E_㌀㘷〹〰㔴㘱㌳ط_x0000_い㄰㘳_x0005_ᰁ糈꓇⃓૎_x0000_〴〴㌵㔳㈴_x000B_ᰁ糈ࣇ¸꓈⃓⣎ᔀ䷈⧇̀Ā김광복	됁_xD9C6_コ沮ྭ뒼_xD9C6_碼ೆ_x0000_㘰ⴳ㌵ⴵㄹ㘴
+　㌶㌵㈳㤰࠳Ā전라북도 정읍시_x0006_㔀〸〸༴Ā전라북도 정읍시 중앙로 83_x000D_　〱㤭㜵ⴹ㠷〰_x0016_猀潰瑲㥳㐱䀶慨浮䥡⹬敮๴_x0000_㜳㤶〰㐰㈵㈰㜳_x0006_䐀〰㌱ଷĀ주식회사 배드민턴마트
+㄀〱ㄸ㌹〲̳Ā정이녀_x000B_ꐁ⃓꧎裆⃔Ѐ郈쇇烀颬ࢷ_x0000_〲㌱㜰㌲_x000C_　ㄳ㤭㐶㌭㌵र_x0000_㈰㠳㤲㔵ܵĀ경기도 고양시_x0005_㄀㔰㐶_x0011_봁ガ₮醬_xDCC5_⃂唀醳泅₭밀ꇀ峁₸㄀㈀܀Ā4층 418호_x000D_　〱㜭㔱ⴲ㔷㠳_x0014_洀湩潴浮牡䁴慮敶⹲潣๭_x0000_㜳㤶〰㐰㈵㤱㜳_x0006_䐀〰㌱सĀ주식회사동우스포츠
+㄀〱ㄸ〸㈴̶Ā송정일_x000B_　ⴲ㠳ⴲ㔳㠹	　㌲㔵㔳㘸	ᰁ룁맆쓒_xDCBC_⃂䀀짇泓ڭ_x0000_㈱㤲㌰_x0018_ᰁ룁맆쓒_xDCBC_⃂䀀짇泓₭᳅峁₸㈀㤀ⴀ㄀ _xD900_낳꓆⃓෎_x0000_㄰ⴰ〲㠱㌭㤵ሸ_x0000_癤灩㈱㌳湀癡牥挮浯_x000B_　〱㐷㔳㔳㠹
+᠁ࣂ₮耀熽㳈峇₸딀່᳑_x0000_㜳㤶〰㐰㈵㔲㜳_x0006_䐀〰㐱ऱĀ중앙스포츠(경주)
+㌀㈲㘶〰㈳̳Ā황영실_x0008_㈀〰ㄸㄲర_x0000_㔰ⴴ㐷ⴱㄵ㜷_x0008_봁솬臀쒽₳봀ﲬ_xDCC8_ۂ_x0000_㠷㤰㌴_x0012_봁솬臀쒽₳봀ﲬ_xDCC8_⃂ࠀㆮ峁₸㈀㤀㐀ⴀ㄀ഀ_x0000_㄰ⴰ㔷㤷㔭㜱ᐷ_x0000_慪灳㌶㐰桀湡慭汩渮瑥_x0008_㈀〰ㄸㄲั_x0000_㜳㤶〰㐰㈵㐵㜳_x0006_䐀〰㐱ԵĀ청룡스포츠
+㘀㔱㜰㘹〳̷Ā조미숙_x0008_㈀㄰㄰〰ఴ_x0000_㔰ⴵㄳⴲ㔹㤵
+　㔵ㄳ㤲㘵࠰Ā경상남도 김해시_x0006_㘀ㄲ㌸ሳĀ경상남도 김해시 장유로 297-5_x000D_　〱㤭ㄵⴳ㔹㤵_x0016_樀獭ㄳ㤲㔵䀹慨浮楡⹬敮ࡴ_x0000_〲〱〱㤱_x000E_㌀㘷〹〰㔴〳㌰ط_x0000_い㄰㠴_x0007__x0001_瓏擇䓅꒾⃓૎_x0000_㈱㈳㠴〱㠶_x0003_ᔁ薼邺ೇ_x0000_㌰ⴱ㔴ⴷ㜸㘰
+　ㄳ㔴㠷〷ܷĀ경기도 안양시_x0006_㐀ㄳ㌸ሷĀ경기도 안양시 동안구 귀인로 89_x000D_　〱㜭㌳ⴸ㌷㔷_x0016_樀浡慪楬〲䀰慨浮楡⹬敮๴_x0000_㜳㤶〰㐰㌵㈲㜳_x0006_䐀〰㐱हĀ코리아오픈(김천)
+㔀〱㄰㜴㈳̴Ā박선영_x0008_㈀〰〷㈴ళ_x0000_㔰ⴴ㌴ⴰ〷㜰
+　㐵㌴㜰〰࠷Ā경상북도 김천시_x0005_㌀㘹㘲_x000E_봁膬₽䀀鲮_xDCCC_⃂ꄀⓁ峁₸㄀㘀㐀ഀ_x0000_㄰ⴰㄴ㔱㘭〳ጶ_x0000_橪〱㔶䀴慨浮楡⹬敮๴_x0000_㜳㤶〰㐰㌵㤳㜳_x0006_䐀〰㔱԰Ā팔구스포츠
+㔀㈰㄰㌵〲̴Ā신상규_x0008_㈀〰〸㌳ఱ_x0000_㔰ⴳ㔹ⴷ㤸㤸
+　㌵㐹㈳㐳࠵Ā대구광역시 동구_x0005_㐀ㄱ㌹_x000F__x0001_河₭_xD900_河₭䐀釅峅ㆸ㄀㠀₮㠀㄀ࠀĀ1층 팔구스포츠_x000D_　〱㠭㔸ⴴ㤸㤸_x0012_㠀猹潰瑲䁳慮敶⹲潣๭_x0000_㜳㤶〰㐰㌵㔴㜳_x0006_䐀〰㔱ԹĀ혜성스포츠
+㄀〳㔰ㄳ㠰̹Ā이의선_x000D_ꐁ⃓꧎裆Ⳕ_x0000_Ҭ᳈裈Ⳕꄀ哇ࣖ_x0000_〲㜰㔰㤲_x000C_　㈳㘭㐵㈭㌱ਲ਼_x0000_㌰㘲㐵ㄲ㈳_x0007_봁ガ쒮₳耀鲽_xDCCC_ۂ_x0000_㈴㠲㤱 봁ガ쒮₳耀鲽_xDCCC_⃂谀곁泀₭봀碬峇ㆸ㈀　蠀㢼₮㈀㠀  ㄀㔀჎⃓㄀砀෎_x0000_㄰ⴰ㔷㠷㜭㐷ᔰ_x0000_獨ㄷ㜶㐷䀱慨浮楡⹬敮๴_x0000_㜳㤶〰㐰㐵㌱㜳_x0006_䐀〰㘱԰Ā호동스포츠
+㄀㐲㤳㤱㐰̷Ā김호동_x0008_㈀㄰〰ㄱళ_x0000_㌰ⴱ㜳ⴵ㌰ㄳ
+　ㄳ㜳〵㌳ܱĀ경기도 오산시_x0006_㐀㜴〸ᨲĀ경기도 오산시 성호대로 25 운산빌딩  1층 4_x000D_　〱㔭㤲ⴵ㈸㠷_x0013_欀摨㤹㈸桀湡慭汩渮瑥_x000E_㌀㘷〹〰㔴㈴㌰ط_x0000_い㄰ㄶ_x0005_䴁㇖铁◆꒱ૂ_x0000_ㄳ〰㐶㔰㠱_x0003_䀁Үᗖࣈ_x0000_〲㤰㘰㘱_x000C_　ㄴ㘭㐳㜭㈳࠷Ā충청남도 홍성군_x0005_㌀㈲㌶_x0012_꤁꣍₰䴀㇖烁₭䴀臖䶽⃇꤀꣍°岳₸㌀㘀ᔀĀ제 1층 제 101호(빌앤더스오피스텔)_x000D_　〱㠭㈶ⴶ㠹㔲_x0010_栀楪㈹䀳慮敶⹲潣๭_x0000_㜳㤶〰㐰㐵㘳㜳_x0006_䐀〰㘱శĀ(주)티제이디스트리뷰션
+㈀ㄱ㜸㈳ㄵ̶Ā송상원_x0006_쐁貳₹쐀ࢹĀ스포츠용품 무역_x0008_㈀㄰〲ㄹ଱_x0000_㈰㔭ㄱ㔭ㄱऴĀ서울특별시 강남구_x0006_㄀㔳㄰ରĀ서울특별시강남구논현동_x000E_ࠁ䂮䳇⦾₵㄀㔀⃎ꀀ꒼룂ꓒꃂ듑ළ_x0000_㄰ⴰ㜸㐸ㄭ㔶ᔱ_x0000_敢瑳硥牴浥䁥慮敶⹲潣m_x0007__x0000__x0001_B_x0000_ñ´	®(_x0000_T_x0000_S_x0000_)_x0000__x0005__x0000__x0000_14049_x0003__x0000__x0001__x0015_¼_x0004_ÖÄÉ_x0008__x0000__x0000_20190917_x0006__x0000__x0000_D00167_x0008__x0000__x0001_üÈÝÂÖ¬À _x0000_ÐÆÐÅÇ
+_x0000__x0000_1268800066_x0003__x0000__x0001_@®DÕ¹Â_x0006__x0000__x0001_Ä³Áä¹ÅÅ _x0000_xÆ_x0007__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_xÆ_x000C__x0000__x0000_02-1644-1662	_x0000__x0001_½°À_x0011_­íÅÜÂ _x0000__x0018_Â_x0001_Æl­_x0006__x0000__x0000_613815_x0013__x0000__x0001_½°À_x0011_­íÅÜÂ _x0000__x0018_Â_x0001_Æl­ _x0000__x0011_­¨°\¸ _x0000_6_x0000_3_x0000_ _x0000_B_x0000_Ù³_x0004__x0000__x0001_4_x0000_5Î|Ç½_x000D__x0000__x0000_010-8882-4137_x0014__x0000__x0000_oneeight@hanmail.net_x0006__x0000__x0000_D00173_x0005__x0000__x0001__x0008_®_x0001_Æ¤ÂìÓ Î
+_x0000__x0000_1052087391_x0003__x0000__x0001_°ÆÀÉÐÆ_x0008__x0000__x0000_20140217_x000D__x0000__x0000_010-6208-8112_x0006__x0000__x0000_121889_x0013__x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_È¹ìÓl­ _x0000_Ù³P­\¸3_x0000_8® _x0000_1_x0000_2_x0000_5_x0000__x0013__x0000__x0000_yonex0901@naver.com_x0008__x0000__x0000_20150122_x000E__x0000__x0000_37690004557937_x0006__x0000__x0000_D00181_x0004__x0000__x0001__x0000_É¤ÂìÓ Î
+_x0000__x0000_1410240836_x0003__x0000__x0001__x0015_¼½¬·_x0008__x0000__x0000_20140825_x000C__x0000__x0000_031-945-2007_x0007__x0000__x0001_½¬0®Ä³ _x0000__x000C_ÓüÈÜÂ_x0006__x0000__x0000_413819$_x0000__x0001_½¬0®Ä³ _x0000__x000C_ÓüÈÜÂ _x0000_DÅ¬¹·\¸ _x0000_5_x0000_5_x0000_ _x0000_-_x0000_8_x0000_1_x0000_ _x0000_(_x0000__x0008_®_x000C_ÍÙ³,_x0000_ _x0000__x000C_ÓüÈ_x0008_®_x000C_ÍXÕ_x0018_ÂÌ¬¹¥Ç)_x0000__x000C__x0000__x0001__x000C_ÓüÈÜÂ _x0000_0¼Ü´ü»4Ñ_x0004_È©Æl­¥Ç_x000D__x0000__x0000_010-9129-1126_x0017__x0000__x0000_leesjun1024@hanmail.net_x000E__x0000__x0000_37690004547137_x0006__x0000__x0000_D00183_x0003__x0000__x0001_T³_x001C_È|Ç
+_x0000__x0000_1171558537_x0003__x0000__x0001_iÖÐÆ Á_x000B__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_XÇX¹,_x0000_¡ÇTÖ_x0008__x0000__x0000_20141027_x000D__x0000__x0000_010-6333-2457	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_ÅÌl­_x0005__x0000__x0000_08078 _x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_ÅÌl­ _x0000_àÂ_x0015_È\¸ _x0000_2_x0000_7_x0000_5_x0000_ _x0000_ _x0000_(_x0000_àÂ_x0015_ÈÙ³,_x0000_ _x0000_àÂ¸Ò¬¹DÅ_x000C_Ó¸Ò)_x0000__x0010__x0000__x0001_ÁÀ_x0000_¬Ù³ _x0000_1_x0000_5Î _x0000_1_x0000_0_x0000_4_x0000_,_x0000_ _x0000_1_x0000_0_x0000_5_x0000_8Ö_x0011__x0000__x0000_thejeil@naver.com_x000D__x0000__x0000_010-9668-2210_x000E__x0000__x0000_37690004550437_x0006__x0000__x0000_D00184_x0005__x0000__x0001_$Æ¨°¤ÂìÓ Î
+_x0000__x0000_1322489384_x0003__x0000__x0001_Å+È¨º_x000D__x0000__x0001_´ÆÙ³0®l­©ÆÔ _x0000_aÅ8Á_x001C_Á¬¹ _x0000_xÆ_x0008__x0000__x0000_20141028
+_x0000__x0000_0315756464
+_x0000__x0000_0315755600_x0008__x0000__x0001_½¬0®Ä³ _x0000_¨°ÅüÈÜÂ_x0006__x0000__x0000_472881_x0016__x0000__x0001_½¬0®Ä³ _x0000_¨°ÅüÈÜÂ _x0000_ÄÉt¬$Æ¨°\¸ _x0000_8_x0000_0_x0000_6_x0000_ _x0000_-_x0000_1_x0000_4_x0000__x000D__x0000__x0000_010-9289-9637_x0012__x0000__x0000_jongmo83@naver.com_x000E__x0000__x0000_37690004552737_x0006__x0000__x0000_D00186_x0005__x0000__x0001_ä¹XÎìÓxÇ¸Ò
+_x0000__x0000_6091853217_x0003__x0000__x0001_iÖ­ÝÂ_x0008__x0000__x0000_20141202_x000C__x0000__x0000_055-298-7330_x0005__x0000__x0000_51378_x0011__x0000__x0001_½¬¨° _x0000_=ÌÐÆÜÂ _x0000_XÇ=Ìl­ _x0000__x0018_¼Ä¬\¸ _x0000_6_x0000_3_x0000__x000D__x0000__x0000_010-3561-0209_x000E__x0000__x0000_o2bbi@nate.com_x0008__x0000__x0000_20141212_x000E__x0000__x0000_37690004554037_x0006__x0000__x0000_D00190_x0005__x0000__x0001_p­°À¤ÂìÓ Î
+_x0000__x0000_4010657765_x0003__x0000__x0001__x0015_¼_x001C_Âl×	_x0000__x0001_¤ÂìÓ ÎXÇX¹,_x0000_ _x0000_©ÆÔ_x0008__x0000__x0000_20150406_x000D__x0000__x0000_010-9977-7141_x0008__x0000__x0001__x0004_È|·½Ä³ _x0000_p­°ÀÜÂ_x0005__x0000__x0000_54102_x000F__x0000__x0001__x0004_È½ _x0000_p­°ÀÜÂ _x0000_¨°_x0018_Â¡Á5_x0000_8® _x0000_4_x0000_2_x0000__x000F__x0000__x0001_1_x0000_0_x0000_1_x0000_8Ö(_x0000__x0018_Â¡ÁÙ³,_x0000_ _x0000_(Ì$Æ¹L¾)_x0000__x0013__x0000__x0000_shp7141@hanmaiL.net_x000E__x0000__x0000_37690004558537_x0006__x0000__x0000_D00192
+_x0000__x0001__x0001_Æ8»¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1222039517_x0005__x0000__x0001__x0001_Æ8»¤ÂìÓ Î_x0003__x0000__x0001_@®_x0001_Æ8»_x0008__x0000__x0000_20150608_x000C__x0000__x0000_032-523-1406_x000C__x0000__x0000_032-517-8009	_x0000__x0001_xÇÌ_x0011_­íÅÜÂ _x0000_½ÉÓl­_x0005__x0000__x0000_21337_x000D__x0000__x0000_010-4320-1406_x0012__x0000__x0000_YM1406@hanmail.net_x0007__x0000__x0001_A_x0000_ñ´	®(_x0000_T_x0000_S_x0000_)_x0000__x0005__x0000__x0000_13042_x0003__x0000__x0001_@®Ù³½¬_x000E__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_+_x0000_3_x0000_0_x0000__x000E__x0000__x0000_37690004561837_x0006__x0000__x0000_D00193_x000B__x0000__x0001_ÑÐ¤Â@Õ¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1320972497_x0006__x0000__x0001_ÑÐ¤Â@Õ¤ÂìÓ Î_x0003__x0000__x0001__x0015_¼_x0004_Ö=Ì_x0006__x0000__x0001_´ÆÙ³_x0004_È8»©ÆÔ_x0008__x0000__x0000_20150610_x000D__x0000__x0000_010-3706-2477_x0007__x0000__x0001_½¬0®Ä³ _x0000_l­¬¹ÜÂ_x0005__x0000__x0000_11907_x000F__x0000__x0001_½¬0® _x0000_l­¬¹ÜÂ _x0000_UÆ_x0019_ÂÌ\¸ _x0000_5_x0000_0_x0000_7_x0000_	_x0000__x0001_3_x0000_5Î _x0000_ÑÐ¤Â@Õ¤ÂìÓ Î_x000F__x0000__x0000_pspin@naver.com_x0005__x0000__x0000_22022_x0003__x0000__x0001_HÅ°ÆÄÉ_x000C__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_7_x0000_._x0000_5_x0000__x000E__x0000__x0000_37690004560137_x0006__x0000__x0000_D00195
+_x0000__x0001_¤ÂìÓ ÎLÑlÐ(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_6172249744_x0005__x0000__x0001_¤ÂìÓ ÎLÑlÐ_x0003__x0000__x0001_tÇÝÐ0®_x0006__x0000__x0001__x001C_ÈpÈÅÅ _x0000_Áä¹_x000C__x0000__x0001_õ¬_x0008_Æ _x0000_¤ÂìÓ Î©ÆÔ,_x0000_ _x0000_¡ÇTÖ_x000B__x0000__x0000_051-7564800_x000C__x0000__x0000_051-756-4801_x0005__x0000__x0000_48222_x0017__x0000__x0001_½°À_x0011_­íÅÜÂ _x0000_Ù³·l­ _x0000_+ÈiÕ´ÆÙ³¥Ç\¸ _x0000_4_x0000_0_x0000_¼8® _x0000_8_x0000_'_x0000__x0001_1_x0000_0_x0000_3_x0000_Ù³ _x0000_1_x0000_0_x0000_5_x0000_8Ö,_x0000_1_x0000_0_x0000_6_x0000_8Ö(_x0000_¬ÀÁÉÙ³,_x0000_½°À _x0000_DÅÜÂDÅÜ´ _x0000_TÏ$Æq¸ _x0000_XÕ²DÌ _x0000_DÅ_x000C_Ó¸Ò)_x0000__x000D__x0000__x0000_010-5578-1988_x0015__x0000__x0000_ltktennis@hanmail.net_x000B__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_8_x0000__x0008__x0000__x0000_20150611_x000E__x0000__x0000_37690004562437_x0006__x0000__x0000_D00196	_x0000__x0001__x0015_¬¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_5041920932_x0004__x0000__x0001__x0015_¬¤ÂìÓ Î_x0003__x0000__x0001__x0015_¬@Çl­_x000D__x0000__x0001_LÑÈ²¤Â©ÆÔ,_x0000_ _x0000_XÇX¹,_x0000_ _x0000_àÂ_x001C_¼_x000C__x0000__x0000_053-314-9090_x0005__x0000__x0000_41433_x000D__x0000__x0000_010-3828-0474_x0013__x0000__x0000_keg0417@hanmail.net_x000D__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_6_x0000_+_x0000_1_x0000_5_x0000__x0008__x0000__x0000_20150612_x000E__x0000__x0000_37690004565337_x0006__x0000__x0000_D00199
+_x0000__x0001_P´¬¹¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1283008985_x0003__x0000__x0001_@®_x0001_Æ Á_x000B__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_¤ÂìÓ ÎXÇX¹_x0008__x0000__x0000_20150703_x000C__x0000__x0000_031-911-4191_x000C__x0000__x0000_031-913-0067_x0006__x0000__x0000_410829_x000F__x0000__x0001_½¬0®Ä³à¬ÅÜÂ _x0000_|Ç°ÀÙ³l­_x0015_È_x001C_¼°ÀÙ³_x000E__x0000__x0001_1_x0000_1_x0000_4_x0000_8_x0000_-_x0000_1_x0000_3_x0000_ _x0000_1_x0000_5Î2_x0000_,_x0000_3_x0000_8Ö_x000D__x0000__x0000_010-4288-3563_x0012__x0000__x0000_usop2n@hanmail.net_x000D__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_6_x0000_+_x0000_2_x0000_3_x0000__x000E__x0000__x0000_37690004568237_x0006__x0000__x0000_D00201_x000E__x0000__x0001_(_x0000_üÈ)_x0000_¤ÂtÎtÇ¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_6278102573_x000B__x0000__x0001_¤ÂtÎtÇ¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000__x0003__x0000__x0001_@®1ÁÐÆ_x0006__x0000__x0001_Áä¹ÅÅ _x0000_Ä³ä¹_x0008__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_ä¹_x0010_È_x000C__x0000__x0000_041-566-1879_x000C__x0000__x0000_041-554-2732_x0005__x0000__x0000_31157"_x0000__x0001_©Í­Ì¨°Ä³ _x0000_ÌHÅÜÂ _x0000__x001C_Á½l­ _x0000_1¼_x001D_Á3_x0000_\¸ _x0000_2_x0000_9_x0000_ _x0000_ _x0000_(_x0000_1¼_x001D_ÁÙ³,_x0000_ _x0000_½¶É¹_x0008_Ã%¼)_x0000__x000D__x0000__x0000_010-4513-1879_x0011__x0000__x0000_kimsw000@nate.com_x000E__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_4_x0000_0_x0000_+_x0000_2_x0000_0_x0000__x0008__x0000__x0000_20150804_x000E__x0000__x0000_37690004570937_x0006__x0000__x0000_D00202_x0008__x0000__x0001_¤ÂìÓå²(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_3052275067_x0003__x0000__x0001_HÅü­¹Â_x000C__x0000__x0000_042-522-9566_x000C__x0000__x0000_042-271-4786_x0006__x0000__x0000_300810_x0017__x0000__x0001__x0000_³_x0004_È_x0011_­íÅÜÂ _x0000__x0011_Él­ _x0000_Ù³_x001C_Á_x0000_³\¸ _x0000_1_x0000_2_x0000_0_x0000_1_x0000_(_x0000_ÜÐÉÓÙ³)_x0000__x0007__x0000__x0001_¤ÂìÓå² _x0000_ÜÐÉÓ_x0010_È_x000B__x0000__x0000_01062224787_x0010__x0000__x0000_spodaq@naver.com_x000D__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_5_x0000_+_x0000_3_x0000_3_x0000__x0008__x0000__x0000_20150805_x000E__x0000__x0000_37690004571537_x0006__x0000__x0000_D00203	_x0000__x0001_ðÅTÏ¬¹DÅ(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_2041477980_x0004__x0000__x0001_ðÅTÏ¬¹DÅ_x0003__x0000__x0001_@®ÁÀ0®_x0006__x0000__x0001_Ä³Áä¹ _x0000_t¬$Á_x000D__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_´Ì!ÇÜÂ_x001C_Á&lt;»$ÁXÎ_x0008__x0000__x0000_20150806_x000C__x0000__x0000_02-3390-4345_x000C__x0000__x0000_02-3390-4344
+_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_Ù³_x0000_³8»l­_x0005__x0000__x0000_02496_x0011__x0000__x0001__x001C_Á¸Æ _x0000_Ù³_x0000_³8»l­ _x0000_Ý¹°Æ\¸1_x0000_2_x0000_8® _x0000_1_x0000_9_x0000__x000B__x0000__x0001_1_x0000_5Î _x0000_XÕtÇÐÆ¤ÂìÓ Î°ÀÅÅ_x000D__x0000__x0000_010-9089-5363_x0017__x0000__x0000_01090895363@hanmail.net_x000B__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_2_x0000_0_x0000__x000E__x0000__x0000_37690004572137_x0006__x0000__x0000_D00205_x0005__x0000__x0001_ÁLÑ¤ÂìÓ Î
+_x0000__x0000_1971301851_x0003__x0000__x0001_@®_x0001_Æ_x0018_Â_x0008__x0000__x0001_Ä³Áä¹ÅÅ _x0000_Ä³ä¹ÅÅ	_x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_4»íÅÅÅ_x000B__x0000__x0000_01063388568_x0008__x0000__x0001_½¬0®Ä³ _x0000_XÇ_x0015_È½ÜÂ_x0005__x0000__x0000_11806!_x0000__x0001_½¬0®Ä³ _x0000_XÇ_x0015_È½ÜÂ _x0000_$Æ©º\¸ _x0000_1_x0000_7_x0000_0_x0000_ _x0000_°Àä´È¹DÇ _x0000_DÅ_x000C_Ó¸Ò _x0000_4_x0000_1_x0000_2_x0000_-_x0000_7_x0000_0_x0000_6_x0000__x000D__x0000__x0000_010-6338-8568_x0011__x0000__x0000_3388568@naver.com_x0005__x0000__x0000_26002_x0003__x0000__x0001__x0015_¬ÜÐ8Ö_x0008__x0000__x0000_20220901_x000E__x0000__x0000_37690004700437_x0006__x0000__x0000_D00209_x0018__x0000__x0001_¤ÂìÓ Î_x000C_Õì·¤Â(_x0000_S_x0000_p_x0000_o_x0000_r_x0000_t_x0000_s_x0000_ _x0000_P_x0000_l_x0000_u_x0000_s_x0000_)_x0000_(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1192167071_x0003__x0000__x0001__x0015_¬ÜÂ¨º_x0006__x0000__x0001_Ä³Áä¹ _x0000_LÇÝÂ_x0008__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_\ÕÝÂ_x000B__x0000__x0000_02-871-5513	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x0000_­EÅl­_x0005__x0000__x0000_08750_x000F__x0000__x0001__x001C_Á¸Æ _x0000__x0000_­EÅl­ _x0000_àÂ¼¹\¸3_x0000_8® _x0000_4_x0000_0_x0000__x0005__x0000__x0001_ÀÉXÕ _x0000_1_x0000_5Î_x000D__x0000__x0000_010-7703-5353_x001A__x0000__x0000_tennisplus0122@esero.go.krX_x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_ _x0000_/_x0000_ _x0000_2_x0000_5_x0000_S_x0000_S_x0000_ _x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_ _x0000_/_x0000_ _x0000_2_x0000_4_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_9_x0000_._x0000_6_x0000_ _x0000_/_x0000_ _x0000_2_x0000_4_x0000_S_x0000_S_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_ _x0000_/_x0000_ _x0000_2_x0000_3_x0000_F_x0000_W_x0000_ _x0000__x0018_ÂüÈ _x0000_ìÅàÂ _x0000_ _x0000_1_x0000_2_x0000_ _x0000_(_x0000_ô²ù²Ç _x0000_Æ­Ì&lt;Ç\¸ _x0000_6_x0000_ _x0000__x0018_¼_x0001_Æ)_x0000__x0008__x0000__x0000_20160114_x000E__x0000__x0000_37690004577337_x0006__x0000__x0000_D00210_x0011__x0000__x0001_(_x0000_üÈ)_x0000_ÐÅtÇ_x001C_ÈtÇxÇ0Ñ´°TÁ °(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1268641398_x000C__x0000__x0000_031-761-8980_x000C__x0000__x0000_031-761-2140_x0005__x0000__x0000_12769_x000D__x0000__x0000_010-4552-3318	_x0000__x0000_1800-6142_x000E__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_4_x0000_0_x0000_+_x0000_2_x0000_5_x0000__x0008__x0000__x0000_20160121_x000E__x0000__x0000_37690004578037_x0006__x0000__x0000_D00256	_x0000__x0001_p¬1Á¤ÂìÓ Î(_x0000_Å°À)_x0000_
+_x0000__x0000_6210808090_x0003__x0000__x0001__x0015_È+È_x0015_¬_x0006__x0000__x0001_Ä³Áä¹ _x0000__x001C_ÈpÈ_x000B__x0000__x0001_ìÕ¤Â0®l­,_x0000_ _x0000_¤ÂìÓ Î©ÆÔ_x0008__x0000__x0000_20160412_x000C__x0000__x0000_055-387-3613_x000C__x0000__x0000_055-387-3615_x0008__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_Å°ÀÜÂ_x0005__x0000__x0000_50621 _x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_Å°ÀÜÂ _x0000__x001C_Á|ÇÙ³\¸ _x0000_2_x0000_5_x0000_ _x0000_ _x0000_(_x0000__x0011_É½Ù³,_x0000_ _x0000_$Ç ÁÝÀ_x0001_Æ´ÅP­äÂ)_x0000__x000D__x0000__x0000_010-2390-2994_x0013__x0000__x0000_dhrhr68@hanmail.netH_x0000__x0001_2_x0000_4_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_3_x0000_5_x0000_ _x0000_/_x0000_2_x0000_4_x0000_S_x0000_S_x0000__x0018_ÂüÈìÅàÂ _x0000_3_x0000_5_x0000_ _x0000_/_x0000_ _x0000_2_x0000_3_x0000_F_x0000_W_x0000_ _x0000__x0018_ÂüÈ _x0000_ìÅàÂ _x0000_3_x0000_5_x0000_ _x0000_/_x0000_ _x0000_2_x0000_3_x0000_S_x0000_S_x0000_ _x0000__x0018_ÂüÈ _x0000_ìÅàÂ _x0000_3_x0000_5_x0000_(_x0000_|·_x0013_Ï+_x0000_È¹D¾¤Â _x0000_9_x0000_4_x0000_3_x0000_,_x0000_2_x0000_5_x0000_0_x0000_)_x0000__x0008__x0000__x0000_20160407_x000E__x0000__x0000_37690004581237_x0006__x0000__x0000_D00267_x0006__x0000__x0001__x001C_ÈtÇD¾¤ÂìÓ Î
+_x0000__x0000_6664100083_x0003__x0000__x0001_Ç_x0015_È\Õ_x000D__x0000__x0001_Ä³ä¹ _x0000__x000F_¼ _x0000_Áä¹ÅÅ,_x0000_ _x0000__x001C_ÁD¾¤Â_x000C__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_ _x0000__x0011_­à¬_x0000_³ÕÅÅ_x0008__x0000__x0000_20160610_x000C__x0000__x0000_062-523-7451_x000C__x0000__x0000_062-523-7455_x0005__x0000__x0000_62023_x000D__x0000__x0001__x0011_­üÈ _x0000__x001C_Ál­ _x0000_´ÆÌ\¸ _x0000_1_x0000_2_x0000_2_x0000__x0005__x0000__x0001_(_x0000__x000D_Ã_x000C_ÍÙ³)_x0000__x000D__x0000__x0000_010-4606-4538_x0015__x0000__x0000_jhrim1226@hanmail.net_x0008__x0000__x0000_20160601_x000E__x0000__x0000_37690004584137_x0006__x0000__x0000_D00280_x0005__x0000__x0001_Ä³ô²¤ÂìÓ Î
+_x0000__x0000_3071042161_x0003__x0000__x0001_$ÇÙ³ÝÂ_x000B__x0000__x0001_Ä³ä¹_x000F_¼ _x0000_Áä¹ÅÅ _x0000_Áä¹ÅÅ_x0010__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_Ç_x0004_Èp¬ _x0000__x0010_Óä¹,_x0000_ _x0000__x0000_³ìÅ_x0008__x0000__x0000_20160825_x000C__x0000__x0000_044-863-8908_x000C__x0000__x0000_044-863-8970_x000F__x0000__x0001_8Á+È¹ÒÄ¼ÇXÎÜÂ _x0000_8Á+È¹ÒÄ¼ÇXÎÜÂ_x0005__x0000__x0000_30102_x001E__x0000__x0001_8Á+È¹ÒÄ¼ÇXÎÜÂ _x0000__x0008_È¬Ç\¸ _x0000_1_x0000_7_x0000_2_x0000_ _x0000_(_x0000_´ÅÄÉÙ³,_x0000_ _x0000_ÜÐ\Õ_x0004_Õ_x0008_¸¤Â&lt;Á0Ñ)_x0000__x0004__x0000__x0001_1_x0000_0_x0000_1_x0000_8Ö_x000D__x0000__x0000_010-7185-8008_x0015__x0000__x0000_dodamsports@naver.com_x000E__x0000__x0000_37690004586437_x0006__x0000__x0000_D00282_x0005__x0000__x0001__x0004_²¬¹¤ÂìÓ Î
+_x0000__x0000_1082124505_x0003__x0000__x0001_@®l×_x0015_È_x0006__x0000__x0001_Áä¹ _x0000_Ä³Áä¹_x000C__x0000__x0001__x0004_ÈÇÁÀp¬·ÅÅ _x0000_0¼Ü´ü»4Ñ _x0000__x000B__x0000__x0000_02-848-6291_x000B__x0000__x0000_02-848-7556
+_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x0001_Æñ´ìÓl­_x0005__x0000__x0000_07375_x000E__x0000__x0001__x001C_Á¸Æ _x0000__x0001_Æñ´ìÓl­ _x0000_Ä³àÂ\¸ _x0000_5_x0000_1_x0000__x000D__x0000__x0001_1_x0000_5Î _x0000_1_x0000_0_x0000_5_x0000_8Ö(_x0000_¡ÁU³L¾)µ)_x0000__x000D__x0000__x0000_010-8393-6291_x0013__x0000__x0000_hee00jung@naver.com_x0008__x0000__x0000_20160905_x000E__x0000__x0000_37690004588737_x0006__x0000__x0000_D00286_x0007__x0000__x0001_Æ%±¤Â _x0000_1Á¨°_x0010_È
+_x0000__x0000_2603001743_x0003__x0000__x0001_MÖ¥Ç8Ö_x0008__x0000__x0001_Ä³ä¹ _x0000__x000F_¼ _x0000_Áä¹ÅÅ_x0008__x0000__x0000_20151218_x000C__x0000__x0000_031-755-7257_x0007__x0000__x0001_½¬0®Ä³ _x0000_1Á¨°ÜÂ_x0005__x0000__x0000_13110_x001E__x0000__x0001_½¬0®Ä³ _x0000_1Á¨°ÜÂ _x0000__x0018_Â_x0015_Èl­ _x0000_1Á¨°_x0000_³\¸ _x0000_1_x0000_2_x0000_6_x0000_7_x0000_ _x0000_-_x0000_1_x0000_ _x0000_(_x0000_ÜÐÉÓÙ³)_x0000__x000D__x0000__x0000_010-7191-7257_x0012__x0000__x0000_nero1016@naver.com_x0002__x0000__x0001_¨°¸Ó_x0008__x0000__x0000_20161109_x000E__x0000__x0000_37690004591037_x0006__x0000__x0000_D00287_x0005__x0000__x0001_¤ÐtÎ¤ÂìÓ Î
+_x0000__x0000_6103752918_x0003__x0000__x0001_@®ÜÐÇ_x0008__x0000__x0000_20161125_x000C__x0000__x0000_052-268-6086_x000C__x0000__x0000_052-272-5908_x0008__x0000__x0001_¸Æ°À_x0011_­íÅÜÂ _x0000_¨°l­_x0005__x0000__x0000_44692_x0016__x0000__x0001_¸Æ°À_x0011_­íÅÜÂ _x0000_¨°l­ _x0000_Ë³ÈÉ\¸ _x0000_1_x0000_2_x0000_4_x0000_ _x0000_ _x0000_(_x0000_ì²Ù³)_x0000__x0003__x0000__x0000_3/2_x000D__x0000__x0000_010-9568-6086_x0014__x0000__x0000_kika5908@hanmail.net_x000E__x0000__x0000_37690004592637_x0006__x0000__x0000_D00292_x0008__x0000__x0001_Æ%±¤Â _x0000_¤ÂìÓÐÆ_x0010_È
+_x0000__x0000_6977800050_x0003__x0000__x0001_\ÕÀ­_x0001_Æ_x0008__x0000__x0000_20170102_x000C__x0000__x0000_051-517-3862_x000C__x0000__x0000_051-583-1023	_x0000__x0001_½°À_x0011_­íÅÜÂ _x0000__x0008_®_x0015_Èl­_x0005__x0000__x0000_46207&amp;_x0000__x0001_½°À_x0011_­íÅÜÂ _x0000__x0008_®_x0015_Èl­ _x0000_´Ì!Çõ¬ÐÆ\¸3_x0000_9_x0000_9_x0000_¼8® _x0000_3_x0000_2_x0000_4_x0000_ _x0000_ _x0000_(_x0000_P´l­Ù³,_x0000_ _x0000_¤ÂìÓÐÆ_x000C_ÓlÐ)_x0000__x0010__x0000__x0001_ÀÉXÕ1_x0000_5Î(_x0000_P´l­Ù³,_x0000_ _x0000_äÂ´°´Ì!Ç_x0000_­)_x0000__x000D__x0000__x0000_010-5505-3862_x0013__x0000__x0000_hgy4285@hanmail.net_x000E__x0000__x0000_37690004595537_x0006__x0000__x0000_D00306_x0007__x0000__x0001_Æ%±¤Â _x0000_ÁÀ4»_x0010_È
+_x0000__x0000_8042300420_x0003__x0000__x0001_@®_x0004_Ö+È_x000D__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_´ÆÙ³©ÆÔ _x0000_¡ÇTÖ_x0008__x0000__x0000_20170119_x000D__x0000__x0000_010-6886-7065_x000C__x0000__x0000_062-374-5410_x0005__x0000__x0000_61970_x0013__x0000__x0001__x0011_­üÈ _x0000__x001C_Ál­ _x0000_ÁÀ4»ü»üÈ\¸3_x0000_2_x0000_¼8® _x0000_3_x0000_-_x0000_5_x0000__x0013__x0000__x0000_sskim-j@hanmail.net_x000E__x0000__x0000_37690004597837_x0006__x0000__x0000_D00308_x0005__x0000__x0001_C_x0000_S_x0000_¤ÂìÓ Î
+_x0000__x0000_2270838785_x0007__x0000__x0001_iÖ_x001C_ÂU³xÆ _x0000_1_x0000_+º_x000C__x0000__x0000_031-385-1222_x000C__x0000__x0000_031-388-3477_x0005__x0000__x0000_13958_x0016__x0000__x0001_½¬0® _x0000_HÅÅÜÂ _x0000_Ì¹HÅl­ _x0000__x0008_Æ Âõ¬ÐÆ\¸5_x0000_2_x0000_¼8® _x0000_2_x0000__x000D__x0000__x0000_010-3176-9037_x0013__x0000__x0000_bill@cssports.co.kr_x000D__x0000__x0000_010-2727-2718_x000F__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_5_x0000_+_x0000_3_x0000_._x0000_5_x0000__x000E__x0000__x0000_37690004598437_x0006__x0000__x0000_D00311
+_x0000__x0001_TÏ¬¹DÅ¤ÂìÓ Î(_x0000_ÜÂe×)_x0000_
+_x0000__x0000_3047001336_x0006__x0000__x0001_TÏ¬¹DÅ¤ÂìÓ Î_x0003__x0000__x0001_\Í_x0001_Æ_x0019_Â_x0012__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000__x0010_Ó	Í&lt;»,_x0000_xÇÄÁ&lt;»,_x0000_0®ÀÐ©ÆÔ_x000D__x0000__x0000_010-2618-5518_x000C__x0000__x0000_031-312-8982_x0007__x0000__x0001_½¬0®Ä³ _x0000_ÜÂe×ÜÂ_x0005__x0000__x0000_14922_x000F__x0000__x0001_½¬0® _x0000_ÜÂe×ÜÂ _x0000_@ÇÄ¬¼_x0001_Æ8® _x0000_2_x0000_7_x0000__x000F__x0000__x0001_3_x0000_0_x0000_3_x0000_8Ö(_x0000_@ÇÕÙ³,_x0000_ _x0000_ÜÂðÒ_x000C_ÓlÐ)_x0000__x0015__x0000__x0000_queenmt5518@naver.com_x000C__x0000__x0000_031-404-6121_x0008__x0000__x0000_20170220_x000E__x0000__x0000_37690004600637_x0006__x0000__x0000_D00312_x000E__x0000__x0001_Æ%±¤Â(_x0000_Y_x0000_O_x0000_N_x0000_E_x0000_X_x0000_)_x0000_ _x0000_t</v>
           </cell>
           <cell r="AA33" t="str">
             <v>N</v>
@@ -4219,10 +4410,10 @@
         </row>
         <row r="34">
           <cell r="B34" t="str">
-            <v>D00080</v>
-          </cell>
-          <cell r="C34" t="str">
-            <v>상무배드민턴</v>
+            <v>㔀෎_x0000_㄰ⴰ㈵㐶㐭㌹ሲ_x0000_橹睪湯桀湡慭汩渮瑥_x000E_㌀㘷〹〰㐴㔷㌲ط_x0000_い〰</v>
+          </cell>
+          <cell r="C34" t="e">
+            <v>#N/A</v>
           </cell>
           <cell r="D34" t="str">
             <v>사용가능</v>
@@ -4230,20 +4421,20 @@
           <cell r="E34" t="str">
             <v>일반사업자</v>
           </cell>
-          <cell r="F34" t="str">
-            <v>4102544630</v>
-          </cell>
-          <cell r="G34" t="str">
-            <v>상무배드민턴</v>
-          </cell>
-          <cell r="H34" t="str">
-            <v>최미경</v>
+          <cell r="F34" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="G34" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="H34" t="e">
+            <v>#N/A</v>
           </cell>
           <cell r="I34" t="str">
             <v>도소매</v>
           </cell>
-          <cell r="J34" t="str">
-            <v>배드민턴용품, 스포츠용품</v>
+          <cell r="J34" t="e">
+            <v>#N/A</v>
           </cell>
           <cell r="K34" t="str">
             <v>20080129</v>
@@ -4251,29 +4442,209 @@
           <cell r="L34" t="str">
             <v/>
           </cell>
-          <cell r="M34" t="str">
-            <v>062-371-7460</v>
-          </cell>
-          <cell r="N34" t="str">
-            <v>0623717461</v>
+          <cell r="M34" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="N34" t="e">
+            <v>#N/A</v>
           </cell>
           <cell r="O34" t="str">
             <v>광주광역시 서구</v>
           </cell>
-          <cell r="P34" t="str">
-            <v>502859</v>
+          <cell r="P34" t="e">
+            <v>#N/A</v>
           </cell>
           <cell r="Q34" t="str">
-            <v>광주광역시 서구 풍암운리로11번길 3</v>
-          </cell>
-          <cell r="R34" t="str">
-            <v>(운리초등학교 후문)</v>
-          </cell>
-          <cell r="S34" t="str">
-            <v>010-4608-7460</v>
-          </cell>
-          <cell r="T34" t="str">
-            <v>power-psu@hanmail.net</v>
+            <v>20090325_x000E__x0000__x0000_37690004478137_x0006__x0000__x0000_D00086_x0008__x0000__x0001_üÈÝÂÖ¬À _x0000_ÐÅ¤ÂàÅ
+_x0000__x0000_1318674023_x0003__x0000__x0001_Á_x0004_Ö8Ö_x0008__x0000__x0000_20120330_x000C__x0000__x0000_051-202-3541
+_x0000__x0000_0512013541	_x0000__x0001_½°À_x0011_­íÅÜÂ _x0000__x0015_¬_x001C_Ál­_x0006__x0000__x0000_618814$_x0000__x0001_½°À_x0011_­íÅÜÂ _x0000__x0015_¬_x001C_Ál­ _x0000_+ºÀÉ$ÆXÁÜÂðÒ1_x0000_3_x0000_\¸ _x0000_1_x0000_2_x0000_-_x0000_2_x0000_2_x0000_ _x0000_ _x0000_MÖÄÉL¾)µ _x0000_1_x0000_0_x0000_6_x0000_8Ö_x000D__x0000__x0000_010-4733-3541_x0016__x0000__x0000_coolcomy1982@naver.com_x0008__x0000__x0000_20120409_x000E__x0000__x0000_37690004479837_x0006__x0000__x0000_D00087
+_x0000__x0001_üÈÝÂÖ¬À _x0000_8ÁÄÉ¤ÂìÓ Î
+_x0000__x0000_3298701221_x0003__x0000__x0001__x0015_¼_x001C_Â¼À_x0007__x0000__x0001_Ä³ä¹ _x0000__x000F_¼ _x0000_Áä¹_x0008__x0000__x0000_20070309_x000B__x0000__x0000_02-824-8799	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_Ù³Çl­_x0005__x0000__x0000_06921_x000E__x0000__x0001__x001C_Á¸Æ _x0000_Ù³Çl­ _x0000_Ì¹Å\¸1_x0000_8® _x0000_3_x0000__x0008__x0000__x0001_ÀÉ5Î _x0000_(_x0000_ÁÀÄ³Ù³)_x0000__x000D__x0000__x0000_010-2942-3235_x0019__x0000__x0000_sejinsports2018@naver.com_x0017__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000_ _x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_9_x0000_3_x0000_-_x0000_&gt;_x0000_5_x0000_0_x0000_ _x0000_&lt;Ç\¸ _x0000_pÈ_x0015_È_x000E__x0000__x0000_37690004480837_x001A__x0000__x0001_0_x0000_1_x0000_0_x0000_ _x0000_2_x0000_7_x0000_0_x0000_5_x0000_ _x0000_3_x0000_2_x0000_3_x0000_4_x0000_ _x0000_(_x0000_ä¹¥Ç _x0000_xÆ _x0000_A_x0000_S_x0000_ô²ù²Ç)_x0000__x0006__x0000__x0000_D00089_x0006__x0000__x0001_Á_x0008_Í0¼Ü´ü»4Ñ
+_x0000__x0000_2270299081_x0003__x0000__x0001__x0015_È¬ÇÈÖ_x000C__x0000__x0000_033-638-0024
+_x0000__x0000_0336382400_x0007__x0000__x0001__x0015_¬ÐÆÄ³ _x0000_Á_x0008_ÍÜÂ_x0006__x0000__x0000_217803_x000E__x0000__x0001__x0015_¬ÐÆÄ³ _x0000_Á_x0008_ÍÜÂ _x0000_P­Ù³\¸ _x0000_3_x0000_9_x0000__x000D__x0000__x0000_010-3297-3133_x0019__x0000__x0000_yubgijung1257@hanmail.net_x000E__x0000__x0000_37690004481437_x0006__x0000__x0000_D00090_x000B__x0000__x0001_üÈÝÂÖ¬À _x0000_¤Âä¹lÂ¤ÂìÓ Î
+_x0000__x0000_8558703276_x0006__x0000__x0001_¤Âä¹lÂ¤ÂìÓ Î_x0003__x0000__x0001_$ÇÜ­ø»_x0008__x0000__x0000_20070917_x000B__x0000__x0000_01087511199_x0007__x0000__x0001_½¬0®Ä³ _x0000_HÅ°ÀÜÂ_x0005__x0000__x0000_15497_x0012__x0000__x0001_½¬0® _x0000_HÅ°ÀÜÂ _x0000_ÁÀ]¸l­ _x0000_Ì8»4_x0000_8® _x0000_1_x0000_7_x0000__x001A__x0000__x0001_1_x0000_5Î1_x0000_5_x0000_1_x0000_9_x0000_-_x0000_1_x0000_3_x0000_ _x0000_ _x0000_1_x0000_5Î _x0000_ _x0000_¤Âä¹lÂ¤ÂìÓ Î _x0000_&lt;»X¹&lt;Á0Ñ_x000D__x0000__x0000_010-5471-3330_x0013__x0000__x0000_smash-123@naver.com_x000B__x0000__x0000_01054713330_x000E__x0000__x0000_37690004483737_x0008__x0000__x0001_!Ç1Á_x0010_È&amp;_x0000_1_x0000_0_x0000_0_x0000_%_x0000__x0006__x0000__x0000_D00096_x0005__x0000__x0001_¤ÂìÓ ÎE¼lÐ
+_x0000__x0000_1272092161_x0003__x0000__x0001_@®ÄÉÉÓ_x0004__x0000__x0001_´Ì!Ç©ÆÔ_x0008__x0000__x0000_20070503_x000C__x0000__x0000_031-535-1244
+_x0000__x0000_0315352245_x0007__x0000__x0001_½¬0®Ä³ _x0000_ìÓÌÜÂ_x0006__x0000__x0000_487050_x0018__x0000__x0001_½¬0®Ä³ _x0000_ìÓÌÜÂ _x0000_p­´°tº _x0000_8Öm­\¸ _x0000_1_x0000_6_x0000_9_x0000_6_x0000_._x0000_ _x0000_2_x0000_5Î_x000D__x0000__x0000_010-6354-5471_x0011__x0000__x0000_kjp31@hanmail.net_x000E__x0000__x0000_37690004487237_x0006__x0000__x0000_D00097_x0005__x0000__x0001_¹Â¬¹¤ÂìÓ Î
+_x0000__x0000_2011081473_x0003__x0000__x0001_à¬Ñ¼°Æ_x0008__x0000__x0000_20071221_x000C__x0000__x0000_02-2279-0779
+_x0000__x0000_0222780778_x0005__x0000__x0000_04563_x001E__x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x0011_Él­ _x0000_­ÌÄ¬Ì\¸ _x0000_2_x0000_4_x0000_6_x0000_ _x0000_ _x0000_(_x0000_)¼°ÀÙ³,_x0000_ _x0000_ÉÓTÖÜÂ¥Ç)_x0000__x0016__x0000__x0001_1_x0000_,_x0000_2_x0000_,_x0000_3_x0000_5Î _x0000_ä²-_x0000_1_x0000_0_x0000_2_x0000_(_x0000_)¼°ÀÙ³,_x0000_ÉÓTÖÜÂ¥Ç)_x0000__x000D__x0000__x0000_010-3284-7383_x0019__x0000__x0000_victorysports@hanmail.net_x000E__x0000__x0000_37690004488937_x0006__x0000__x0000_D00101_x0005__x0000__x0001_DÅ°À¤ÂìÓ Î
+_x0000__x0000_3122872982_x0003__x0000__x0001_\Í+È¼¹_x000C__x0000__x0001_Ä³ä¹_x000F_¼ÁÀÔ_x0011_É_x001C_¬ÅÅ,_x0000_Áä¹ÅÅ_x0008__x0000__x0000_20110701_x000C__x0000__x0000_041-532-8381
+_x0000__x0000_0415328382_x0008__x0000__x0001_©Í­Ì¨°Ä³ _x0000_DÅ°ÀÜÂ_x0006__x0000__x0000_336050_x0010__x0000__x0001_©Í­Ì¨°Ä³ _x0000_DÅ°ÀÜÂ _x0000_ÜÂü»\¸ _x0000_2_x0000_5_x0000_1_x0000__x000D__x0000__x0000_010-4946-8385_x0013__x0000__x0000_judocjl@hanmail.net_x000E__x0000__x0000_37690004490537_x0006__x0000__x0000_D00109_x0008__x0000__x0001__x0001_Æ¤ÂìÓ Î(_x0000_¨°ÐÆ)_x0000_
+_x0000__x0000_1095289131_x0003__x0000__x0001_tÇ_x0015_ÈÌ_x0008__x0000__x0000_20071119_x000C__x0000__x0000_063-632-4154
+_x0000__x0000_0636324156_x0005__x0000__x0000_55703_x0015__x0000__x0001__x0004_È|·½Ä³ _x0000_¨°ÐÆÜÂ _x0000_¬Àä¹tº _x0000__x0000_³¬À\¸ _x0000_1_x0000_2_x0000_8_x0000_3_x0000__x0004__x0000__x0001__x0001_Æ¤ÂìÓ Î_x000D__x0000__x0000_010-4594-0634_x0013__x0000__x0000_jclee8734@naver.com_x000E__x0000__x0000_37690004497037_x0006__x0000__x0000_D00110_x0007__x0000__x0001_Æ%±¤Â _x0000_TÖ_x001C_Â_x0010_È
+_x0000__x0000_4080577085_x0003__x0000__x0001__x0004_È+º_x0019_Â_x0008__x0000__x0000_20071102_x000C__x0000__x0000_061-375-6647_x0008__x0000__x0001__x0004_È|·¨°Ä³ _x0000_TÖ_x001C_Âp­_x0006__x0000__x0000_519809_x0014__x0000__x0001__x0004_È|·¨°Ä³ _x0000_TÖ_x001C_Âp­ _x0000__x0011_­U³\¸ _x0000_1_x0000_4_x0000_0_x0000_ _x0000_ _x0000_1_x0000_5Î_x000D__x0000__x0000_010-6632-5893_x0012__x0000__x0000_ms-jon@hanmeil.net_x000E__x0000__x0000_37690004498637_x0006__x0000__x0000_D00111_x000C__x0000__x0001_,Æ¼¹=Õ+ÈiÕ¤ÂìÓ Î(_x0000_©ºìÓ)_x0000_
+_x0000__x0000_4111469486_x0003__x0000__x0001_@®=Ì©Æ_x000C__x0000__x0001_´ÆÙ³©ÆÔ,_x0000_ñ´°Àl­,_x0000_0®P±Ô_x0008__x0000__x0000_20070320_x000C__x0000__x0000_061-242-1032
+_x0000__x0000_0612443032_x0008__x0000__x0001__x0004_È|·¨°Ä³ _x0000_©ºìÓÜÂ_x0005__x0000__x0000_58726_x0010__x0000__x0001__x0004_È¨° _x0000_©ºìÓÜÂ _x0000_(Ì¼_x001D_Á8® _x0000_4_x0000_1_x0000_-_x0000_1_x0000__x0002__x0000__x0001_1_x0000_5Î_x000D__x0000__x0000_010-9243-4285_x0010__x0000__x0000_eyebono@daum.net_x000E__x0000__x0000_37690004499237_x0006__x0000__x0000_D00116_x000F__x0000__x0001_Æ%±¤ÂÈ¹°À_x0000_³¬¹_x0010_È(_x0000_ü»4Ñ¤ÂìÓ Î)_x0000_
+_x0000__x0000_6080288027_x0003__x0000__x0001_ Ç_x0001_Æ_x0019_Â_x0008__x0000__x0001_¤ÂìÓ Î©ÆÔ_x000F_¼XÇX¹_x000C__x0000__x0000_055-222-5431
+_x0000__x0000_0552225432_x0008__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_=ÌÐÆÜÂ_x0006__x0000__x0000_631852_x0018__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_=ÌÐÆÜÂ _x0000_È¹°ÀiÕìÓl­ _x0000_©ÆÈ¹\¸ _x0000_7_x0000_6_x0000_ _x0000_üÈÝÐ_x000D__x0000__x0000_010-3707-6245_x0016__x0000__x0000_dudtjs6245@hanmail.net_x000E__x0000__x0000_37690004504337_x0006__x0000__x0000_D00120_x0006__x0000__x0001_Æ%±¤Â­ÌüÈ_x0010_È
+_x0000__x0000_3170385854_x0003__x0000__x0001_\Í°Æ1Á_x000B__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_XÇX¹,_x0000__x0018_Ât¬_x0008__x0000__x0000_20110729_x000C__x0000__x0000_043-222-3040
+_x0000__x0000_0432245050_x0008__x0000__x0001_©Í­Ì½Ä³ _x0000_­ÌüÈÜÂ_x0006__x0000__x0000_361842_x0012__x0000__x0001_©Í½ _x0000_­ÌüÈÜÂ _x0000_ÁÀù²l­ _x0000_8Öø»\¸ _x0000_2_x0000_0_x0000_6_x0000__x0005__x0000__x0001_1_x0000_5Î _x0000_È!Î_x000D__x0000__x0000_010-5468-3319_x0015__x0000__x0000_wsung3525@hanmail.net_x0008__x0000__x0000_20080429_x000E__x0000__x0000_37690004507237_x0006__x0000__x0000_D00121_x000D__x0000__x0001_Æ%±¤ÂìÓmÕ_x0010_È(_x0000_XÕtÇlÐ¬¹´Å)_x0000_
+_x0000__x0000_5061736246_x0003__x0000__x0001__x0015_È@Ç_x0001_Æ_x0008__x0000__x0000_20090227_x000C__x0000__x0000_054-283-5234
+_x0000__x0000_0542835231_x0008__x0000__x0001_½¬ÁÀ½Ä³ _x0000_ìÓmÕÜÂ_x0006__x0000__x0000_790822_x0012__x0000__x0001_½¬½ _x0000_ìÓmÕÜÂ _x0000_¨°l­ _x0000__x0000_³Ä³Ù³ _x0000_8_x0000_6_x0000_-_x0000_2_x0000__x000D__x0000__x0000_010-4133-7770_x0014__x0000__x0000_minton1125@naver.com_x0008__x0000__x0000_20081105_x000E__x0000__x0000_37690004508937_x0006__x0000__x0000_D00122_x0005__x0000__x0001_°Æ¬¹¤ÂìÓ Î
+_x0000__x0000_4172105493_x0003__x0000__x0001__x0015_¼_x0018_ÂÄÉ_x0008__x0000__x0000_20180101_x000C__x0000__x0000_051-632-2681
+_x0000__x0000_0516322681_x0008__x0000__x0001_½°À_x0011_­íÅÜÂ _x0000_¨°l­_x0006__x0000__x0000_608827_x0011__x0000__x0001_½°À_x0011_­íÅÜÂ _x0000_¨°l­ _x0000_Ç ÇÉÓTÖ\¸ _x0000_4_x0000_9_x0000__x000D__x0000__x0000_010-2594-2682_x0015__x0000__x0000_moxie2000@hanmail.net_x000E__x0000__x0000_37690004509537_x0006__x0000__x0000_D00123_x0005__x0000__x0001_°Æ1Á¤ÂìÓ Î
+_x0000__x0000_2077003708_x0003__x0000__x0001_@®DÆÝÂ_x0008__x0000__x0000_20071009_x000B__x0000__x0000_02-465-1297	_x0000__x0000_024651197	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x0011_­ÄÉl­_x0006__x0000__x0000_143961_x0010__x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x0011_­ÄÉl­ _x0000_l­XÇ\¸ _x0000_6_x0000_6_x0000__x0014__x0000__x0001_1_x0000_5Î _x0000_(_x0000_l­XÇÙ³ _x0000_2_x0000_2_x0000_7_x0000_-_x0000_6_x0000_)_x0000_ _x0000_°Æ1Á¤ÂìÓ Î_x000D__x0000__x0000_010-3418-1230_x000F__x0000__x0000_ws418@naver.com_x000E__x0000__x0000_37690004510537_x0006__x0000__x0000_D00126_x0005__x0000__x0001_ÐÆÙ³´Ì!Ç¬À
+_x0000__x0000_3060363748_x0003__x0000__x0001_ü»Ñ¼ÁÉ_x0004__x0000__x0001_´ÆÙ³0®l­_x0008__x0000__x0000_20050705_x000C__x0000__x0000_042-531-4004
+_x0000__x0000_0425328899_x0008__x0000__x0001__x0000_³_x0004_È_x0011_­íÅÜÂ _x0000_Ù³l­_x0005__x0000__x0000_34630_x000D__x0000__x0001__x0000_³_x0004_È _x0000_Ù³l­ _x0000__x0000_³_x0004_È\¸ _x0000_7_x0000_6_x0000_5_x0000__x000D__x0000__x0000_010-5453-9536_x0012__x0000__x0000_wonspo@hanmail.net_x0008__x0000__x0000_20080214_x000E__x0000__x0000_37690004511137_x0006__x0000__x0000_D00127_x0008__x0000__x0001_ÐÆ¤ÂìÓ Î(_x0000__x001C_ÈüÈ)_x0000_
+_x0000__x0000_6160962051_x0003__x0000__x0001_@®ø»½¬_x000C__x0000__x0000_064-752-4422
+_x0000__x0000_0647232992_x000C__x0000__x0001__x001C_ÈüÈ¹ÒÄ¼ÇXÎÄ³ _x0000__x001C_ÁÀ­ìÓÜÂ_x0006__x0000__x0000_690161_x0013__x0000__x0001__x001C_ÈüÈ¹ÒÄ¼ÇXÎÄ³ _x0000__x001C_ÈüÈÜÂ _x0000_$Æ|·\¸ _x0000_1_x0000_3_x0000_4_x0000__x000D__x0000__x0000_010-4416-4412_x0015__x0000__x0000_crony0104@hanmail.net_x000E__x0000__x0000_37690004512837_x0006__x0000__x0000_D00132_x0005__x0000__x0001__x0004_ÈüÈÆ%±¤Â
+_x0000__x0000_4020887887_x0003__x0000__x0001_tÇ_x001C_Â+È_x000C__x0000__x0000_063-274-9337
+_x0000__x0000_0632789337_x0008__x0000__x0001__x0004_È|·½Ä³ _x0000__x0004_ÈüÈÜÂ_x0006__x0000__x0000_560080_x0013__x0000__x0001__x0004_È|·½Ä³ _x0000__x0004_ÈüÈÜÂ _x0000_DÆ°Àl­ _x0000_õ¬½\¸ _x0000_2_x0000_0_x0000__x000D__x0000__x0000_010-9224-8391_x0010__x0000__x0000_jyonex@naver.com_x000E__x0000__x0000_37690004516337_x0006__x0000__x0000_D00136_x0005__x0000__x0001__x001C_È|Ç¤ÂìÓ Î
+_x0000__x0000_4040533542_x000B__x0000__x0001__x001C_È|Ç_x0008_¸_x0000_È¤ÂìÓ Î(_x0000__x0015_ÈMÇ)_x0000__x0003__x0000__x0001_@®_x0011_­õ¼	_x0000__x0001_´ÆÙ³0®l­_x000F_¼´ÆÙ³õ¼xÆ_x000C__x0000__x0000_063-535-9146
+_x0000__x0000_0635332093_x0008__x0000__x0001__x0004_È|·½Ä³ _x0000__x0015_ÈMÇÜÂ_x0006__x0000__x0000_580804_x000F__x0000__x0001__x0004_È|·½Ä³ _x0000__x0015_ÈMÇÜÂ _x0000__x0011_ÉYÅ\¸ _x0000_8_x0000_3_x0000__x000D__x0000__x0000_010-9579-7800_x0016__x0000__x0000_sports9146@hanmaIl.net_x000E__x0000__x0000_37690004520237_x0006__x0000__x0000_D00137_x000B__x0000__x0001_üÈÝÂÖ¬À _x0000_0¼Ü´ü»4ÑÈ¹¸Ò
+_x0000__x0000_1108193203_x0003__x0000__x0001__x0015_ÈtÇ@±_x000B__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000__x0004_ÈÇÁÀp¬·_x0008__x0000__x0000_20130723_x000C__x0000__x0000_031-964-3530	_x0000__x0000_023829555_x0007__x0000__x0001_½¬0®Ä³ _x0000_à¬ÅÜÂ_x0005__x0000__x0000_10564_x0011__x0000__x0001_½¬0® _x0000_à¬ÅÜÂ _x0000_U³Ål­ _x0000_¼À¡Á\¸ _x0000_1_x0000_2_x0000__x0007__x0000__x0001_4_x0000_5Î _x0000_4_x0000_1_x0000_8_x0000_8Ö_x000D__x0000__x0000_010-7152-7538_x0014__x0000__x0000_mintonmart@naver.com_x000E__x0000__x0000_37690004521937_x0006__x0000__x0000_D00138	_x0000__x0001_üÈÝÂÖ¬ÀÙ³°Æ¤ÂìÓ Î
+_x0000__x0000_1108180426_x0003__x0000__x0001_¡Á_x0015_È|Ç_x000B__x0000__x0000_02-382-3598	_x0000__x0000_023553586	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_@ÇÉÓl­_x0006__x0000__x0000_122903_x0018__x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_@ÇÉÓl­ _x0000_ðÅ_x001C_Á\¸ _x0000_2_x0000_9_x0000_-_x0000_1_x0000_ _x0000_Ù³°Æ¤ÂìÓ Î_x000D__x0000__x0000_010-2018-3598_x0012__x0000__x0000_dvip1233@naver.com_x000B__x0000__x0000_01074353598
+_x0000__x0001__x0018_Â_x0008_® _x0000_½qÈ&lt;Ç\¸ _x0000_µÑ_x001C_È_x000E__x0000__x0000_37690004522537_x0006__x0000__x0000_D00141	_x0000__x0001__x0011_ÉYÅ¤ÂìÓ Î(_x0000_½¬üÈ)_x0000_
+_x0000__x0000_3226600323_x0003__x0000__x0001_iÖ_x0001_ÆäÂ_x0008__x0000__x0000_20081210_x000C__x0000__x0000_054-741-5177_x0008__x0000__x0001_½¬ÁÀ½Ä³ _x0000_½¬üÈÜÂ_x0006__x0000__x0000_780943_x0012__x0000__x0001_½¬ÁÀ½Ä³ _x0000_½¬üÈÜÂ _x0000__x0008_®1Á\¸ _x0000_2_x0000_9_x0000_4_x0000_-_x0000_1_x0000__x000D__x0000__x0000_010-7579-5177_x0014__x0000__x0000_jasp6304@hanmail.net_x0008__x0000__x0000_20081211_x000E__x0000__x0000_37690004525437_x0006__x0000__x0000_D00145_x0005__x0000__x0001_­Ìá¸¤ÂìÓ Î
+_x0000__x0000_6150796307_x0003__x0000__x0001_pÈø»_x0019_Â_x0008__x0000__x0000_20101004_x000C__x0000__x0000_055-312-9559
+_x0000__x0000_0553129560_x0008__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_@®tÕÜÂ_x0006__x0000__x0000_621833_x0012__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_@®tÕÜÂ _x0000_¥Ç Ç\¸ _x0000_2_x0000_9_x0000_7_x0000_-_x0000_5_x0000__x000D__x0000__x0000_010-9513-9559_x0016__x0000__x0000_jms3129559@hanmail.net_x0008__x0000__x0000_20101019_x000E__x0000__x0000_37690004530037_x0006__x0000__x0000_D00148_x0007__x0000__x0001__x0000_ÏtÇdÅD¾¤ÂìÓ Î
+_x0000__x0000_1232481068_x0003__x0000__x0001__x0015_¼+ºÇ_x000C__x0000__x0000_031-457-8706
+_x0000__x0000_0314578707_x0007__x0000__x0001_½¬0®Ä³ _x0000_HÅÅÜÂ_x0006__x0000__x0000_431837_x0012__x0000__x0001_½¬0®Ä³ _x0000_HÅÅÜÂ _x0000_Ù³HÅl­ _x0000_À­xÇ\¸ _x0000_8_x0000_9_x0000__x000D__x0000__x0000_010-7338-7375_x0016__x0000__x0000_jamjali200@hanmail.net_x000E__x0000__x0000_37690004532237_x0006__x0000__x0000_D00149	_x0000__x0001_TÏ¬¹DÅ$Æ_x0008_Õ(_x0000_@®Ì)_x0000_
+_x0000__x0000_5100147324_x0003__x0000__x0001__x0015_¼ Á_x0001_Æ_x0008__x0000__x0000_20070423_x000C__x0000__x0000_054-430-7007
+_x0000__x0000_0544307007_x0008__x0000__x0001_½¬ÁÀ½Ä³ _x0000_@®ÌÜÂ_x0005__x0000__x0000_39626_x000E__x0000__x0001_½¬½ _x0000_@®ÌÜÂ _x0000_¡Á$Á\¸ _x0000_1_x0000_6_x0000_4_x0000__x000D__x0000__x0000_010-4115-6306_x0013__x0000__x0000_jj10654@hanmail.net_x000E__x0000__x0000_37690004533937_x0006__x0000__x0000_D00150_x0005__x0000__x0001__x0014_Ól­¤ÂìÓ Î
+_x0000__x0000_5020153204_x0003__x0000__x0001_àÂÁÀÜ­_x0008__x0000__x0000_20080331_x000C__x0000__x0000_053-957-8989
+_x0000__x0000_0539432345_x0008__x0000__x0001__x0000_³l­_x0011_­íÅÜÂ _x0000_Ù³l­_x0005__x0000__x0000_41193_x000F__x0000__x0001__x0000_³l­ _x0000_Ù³l­ _x0000_DÅÅ\¸1_x0000_1_x0000_8® _x0000_8_x0000_1_x0000__x0008__x0000__x0001_1_x0000_5Î _x0000__x0014_Ól­¤ÂìÓ Î_x000D__x0000__x0000_010-8854-8989_x0012__x0000__x0000_89sports@naver.com_x000E__x0000__x0000_37690004534537_x0006__x0000__x0000_D00159_x0005__x0000__x0001__x001C_Ö1Á¤ÂìÓ Î
+_x0000__x0000_1300531089_x0003__x0000__x0001_tÇXÇ Á_x000D__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000__x0000_¬_x0004_È_x001C_ÈÔ,_x0000_¡ÇTÖ_x0008__x0000__x0000_20070529_x000C__x0000__x0000_032-654-2133
+_x0000__x0000_0326542132_x0007__x0000__x0001_½¬0®Ä³ _x0000_½ÌÜÂ_x0006__x0000__x0000_422819 _x0000__x0001_½¬0®Ä³ _x0000_½ÌÜÂ _x0000_Á¬Àl­ _x0000_½¬xÇ\¸1_x0000_2_x0000_0_x0000_¼8® _x0000_2_x0000_8_x0000_ _x0000_ _x0000_1_x0000_5Î_x0010_ÈìÓ _x0000_1_x0000_xÎ_x000D__x0000__x0000_010-7578-7740_x0015__x0000__x0000_hs7167741@hanmail.net_x000E__x0000__x0000_37690004541337_x0006__x0000__x0000_D00160_x0005__x0000__x0001_8ÖÙ³¤ÂìÓ Î
+_x0000__x0000_1243919047_x0003__x0000__x0001_@®8ÖÙ³_x0008__x0000__x0000_20100113_x000C__x0000__x0000_031-375-0331
+_x0000__x0000_0313750331_x0007__x0000__x0001_½¬0®Ä³ _x0000_$Æ°ÀÜÂ_x0006__x0000__x0000_447802_x001A__x0000__x0001_½¬0®Ä³ _x0000_$Æ°ÀÜÂ _x0000_1Á8Ö_x0000_³\¸ _x0000_2_x0000_5_x0000_ _x0000_´Æ°ÀL¾)µ _x0000_ _x0000_1_x0000_5Î _x0000_4_x0000__x000D__x0000__x0000_010-5295-8278_x0013__x0000__x0000_khd9982@hanmail.net_x000E__x0000__x0000_37690004542037_x0006__x0000__x0000_D00161_x0005__x0000__x0001_MÖ1ÁÆ%±¤Â
+_x0000__x0000_3100640518_x0003__x0000__x0001_@®_x0004_Ö_x0015_È_x0008__x0000__x0000_20090616_x000C__x0000__x0000_041-634-7327_x0008__x0000__x0001_©Í­Ì¨°Ä³ _x0000_MÖ1Áp­_x0005__x0000__x0000_32263_x0012__x0000__x0001_©Í¨° _x0000_MÖ1Áp­ _x0000_MÖ½MÇ _x0000_©Í¨°_x0000_³\¸ _x0000_3_x0000_6_x0000__x0015__x0000__x0001__x001C_È _x0000_1_x0000_5Î _x0000__x001C_È _x0000_1_x0000_0_x0000_1_x0000_8Ö(_x0000_L¾dÅT³¤Â$Æ&lt;Õ¤ÂTÑ)_x0000__x000D__x0000__x0000_010-8626-9825_x0010__x0000__x0000_hji923@naver.com_x000E__x0000__x0000_37690004543637_x0006__x0000__x0000_D00166_x000C__x0000__x0001_(_x0000_üÈ)_x0000_ðÒ_x001C_ÈtÇ_x0014_µ¤Â¸Ò¬¹ð½XÁ
+_x0000__x0000_2118732516_x0003__x0000__x0001_¡ÁÁÀÐÆ_x0006__x0000__x0001_Ä³Áä¹ _x0000_Ä³ä¹_x0008__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_4»íÅ_x0008__x0000__x0000_20120911_x000B__x0000__x0000_02-511-5114	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x0015_¬¨°l­_x0006__x0000__x0000_135010_x000B__x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ_x0015_¬¨°l­|±_x0004_ÖÙ³_x000E__x0000__x0001__x0008_®@ÇL¾)µ _x0000_1_x0000_5Î _x0000_ ¼¤Â¸Ò¤Â Ñ´Å_x000D__x0000__x0000_010-8784-1651_x0015__x0000__x0000_bestextreme@naver.com_x0007__x0000__x0001_B_x0000_ñ´	®(_x0000_T_x0000_S_x0000_)_x0000__x0005__x0000__x0000_14049_x0003__x0000__x0001__x0015_¼_x0004_ÖÄÉ_x0008__x0000__x0000_20190917_x0006__x0000__x0000_D00167_x0008__x0000__x0001_üÈÝÂÖ¬À _x0000_ÐÆÐÅÇ
+_x0000__x0000_1268800066_x0003__x0000__x0001_@®DÕ¹Â_x0006__x0000__x0001_Ä³Áä¹ÅÅ _x0000_xÆ_x0007__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_xÆ_x000C__x0000__x0000_02-1644-1662	_x0000__x0001_½°À_x0011_­íÅÜÂ _x0000__x0018_Â_x0001_Æl­_x0006__x0000__x0000_613815_x0013__x0000__x0001_½°À_x0011_­íÅÜÂ _x0000__x0018_Â_x0001_Æl­ _x0000__x0011_­¨°\¸ _x0000_6_x0000_3_x0000_ _x0000_B_x0000_Ù³_x0004__x0000__x0001_4_x0000_5Î|Ç½_x000D__x0000__x0000_010-8882-4137_x0014__x0000__x0000_oneeight@hanmail.net_x0006__x0000__x0000_D00173_x0005__x0000__x0001__x0008_®_x0001_Æ¤ÂìÓ Î
+_x0000__x0000_1052087391_x0003__x0000__x0001_°ÆÀÉÐÆ_x0008__x0000__x0000_20140217_x000D__x0000__x0000_010-6208-8112_x0006__x0000__x0000_121889_x0013__x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_È¹ìÓl­ _x0000_Ù³P­\¸3_x0000_8® _x0000_1_x0000_2_x0000_5_x0000__x0013__x0000__x0000_yonex0901@naver.com_x0008__x0000__x0000_20150122_x000E__x0000__x0000_37690004557937_x0006__x0000__x0000_D00181_x0004__x0000__x0001__x0000_É¤ÂìÓ Î
+_x0000__x0000_1410240836_x0003__x0000__x0001__x0015_¼½¬·_x0008__x0000__x0000_20140825_x000C__x0000__x0000_031-945-2007_x0007__x0000__x0001_½¬0®Ä³ _x0000__x000C_ÓüÈÜÂ_x0006__x0000__x0000_413819$_x0000__x0001_½¬0®Ä³ _x0000__x000C_ÓüÈÜÂ _x0000_DÅ¬¹·\¸ _x0000_5_x0000_5_x0000_ _x0000_-_x0000_8_x0000_1_x0000_ _x0000_(_x0000__x0008_®_x000C_ÍÙ³,_x0000_ _x0000__x000C_ÓüÈ_x0008_®_x000C_ÍXÕ_x0018_ÂÌ¬¹¥Ç)_x0000__x000C__x0000__x0001__x000C_ÓüÈÜÂ _x0000_0¼Ü´ü»4Ñ_x0004_È©Æl­¥Ç_x000D__x0000__x0000_010-9129-1126_x0017__x0000__x0000_leesjun1024@hanmail.net_x000E__x0000__x0000_37690004547137_x0006__x0000__x0000_D00183_x0003__x0000__x0001_T³_x001C_È|Ç
+_x0000__x0000_1171558537_x0003__x0000__x0001_iÖÐÆ Á_x000B__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_XÇX¹,_x0000_¡ÇTÖ_x0008__x0000__x0000_20141027_x000D__x0000__x0000_010-6333-2457	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_ÅÌl­_x0005__x0000__x0000_08078 _x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_ÅÌl­ _x0000_àÂ_x0015_È\¸ _x0000_2_x0000_7_x0000_5_x0000_ _x0000_ _x0000_(_x0000_àÂ_x0015_ÈÙ³,_x0000_ _x0000_àÂ¸Ò¬¹DÅ_x000C_Ó¸Ò)_x0000__x0010__x0000__x0001_ÁÀ_x0000_¬Ù³ _x0000_1_x0000_5Î _x0000_1_x0000_0_x0000_4_x0000_,_x0000_ _x0000_1_x0000_0_x0000_5_x0000_8Ö_x0011__x0000__x0000_thejeil@naver.com_x000D__x0000__x0000_010-9668-2210_x000E__x0000__x0000_37690004550437_x0006__x0000__x0000_D00184_x0005__x0000__x0001_$Æ¨°¤ÂìÓ Î
+_x0000__x0000_1322489384_x0003__x0000__x0001_Å+È¨º_x000D__x0000__x0001_´ÆÙ³0®l­©ÆÔ _x0000_aÅ8Á_x001C_Á¬¹ _x0000_xÆ_x0008__x0000__x0000_20141028
+_x0000__x0000_0315756464
+_x0000__x0000_0315755600_x0008__x0000__x0001_½¬0®Ä³ _x0000_¨°ÅüÈÜÂ_x0006__x0000__x0000_472881_x0016__x0000__x0001_½¬0®Ä³ _x0000_¨°ÅüÈÜÂ _x0000_ÄÉt¬$Æ¨°\¸ _x0000_8_x0000_0_x0000_6_x0000_ _x0000_-_x0000_1_x0000_4_x0000__x000D__x0000__x0000_010-9289-9637_x0012__x0000__x0000_jongmo83@naver.com_x000E__x0000__x0000_37690004552737_x0006__x0000__x0000_D00186_x0005__x0000__x0001_ä¹XÎìÓxÇ¸Ò
+_x0000__x0000_6091853217_x0003__x0000__x0001_iÖ­ÝÂ_x0008__x0000__x0000_20141202_x000C__x0000__x0000_055-298-7330_x0005__x0000__x0000_51378_x0011__x0000__x0001_½¬¨° _x0000_=ÌÐÆÜÂ _x0000_XÇ=Ìl­ _x0000__x0018_¼Ä¬\¸ _x0000_6_x0000_3_x0000__x000D__x0000__x0000_010-3561-0209_x000E__x0000__x0000_o2bbi@nate.com_x0008__x0000__x0000_20141212_x000E__x0000__x0000_37690004554037_x0006__x0000__x0000_D00190_x0005__x0000__x0001_p­°À¤ÂìÓ Î
+_x0000__x0000_4010657765_x0003__x0000__x0001__x0015_¼_x001C_Âl×	_x0000__x0001_¤ÂìÓ ÎXÇX¹,_x0000_ _x0000_©ÆÔ_x0008__x0000__x0000_20150406_x000D__x0000__x0000_010-9977-7141_x0008__x0000__x0001__x0004_È|·½Ä³ _x0000_p­°ÀÜÂ_x0005__x0000__x0000_54102_x000F__x0000__x0001__x0004_È½ _x0000_p­°ÀÜÂ _x0000_¨°_x0018_Â¡Á5_x0000_8® _x0000_4_x0000_2_x0000__x000F__x0000__x0001_1_x0000_0_x0000_1_x0000_8Ö(_x0000__x0018_Â¡ÁÙ³,_x0000_ _x0000_(Ì$Æ¹L¾)_x0000__x0013__x0000__x0000_shp7141@hanmaiL.net_x000E__x0000__x0000_37690004558537_x0006__x0000__x0000_D00192
+_x0000__x0001__x0001_Æ8»¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1222039517_x0005__x0000__x0001__x0001_Æ8»¤ÂìÓ Î_x0003__x0000__x0001_@®_x0001_Æ8»_x0008__x0000__x0000_20150608_x000C__x0000__x0000_032-523-1406_x000C__x0000__x0000_032-517-8009	_x0000__x0001_xÇÌ_x0011_­íÅÜÂ _x0000_½ÉÓl­_x0005__x0000__x0000_21337_x000D__x0000__x0000_010-4320-1406_x0012__x0000__x0000_YM1406@hanmail.net_x0007__x0000__x0001_A_x0000_ñ´	®(_x0000_T_x0000_S_x0000_)_x0000__x0005__x0000__x0000_13042_x0003__x0000__x0001_@®Ù³½¬_x000E__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_+_x0000_3_x0000_0_x0000__x000E__x0000__x0000_37690004561837_x0006__x0000__x0000_D00193_x000B__x0000__x0001_ÑÐ¤Â@Õ¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1320972497_x0006__x0000__x0001_ÑÐ¤Â@Õ¤ÂìÓ Î_x0003__x0000__x0001__x0015_¼_x0004_Ö=Ì_x0006__x0000__x0001_´ÆÙ³_x0004_È8»©ÆÔ_x0008__x0000__x0000_20150610_x000D__x0000__x0000_010-3706-2477_x0007__x0000__x0001_½¬0®Ä³ _x0000_l­¬¹ÜÂ_x0005__x0000__x0000_11907_x000F__x0000__x0001_½¬0® _x0000_l­¬¹ÜÂ _x0000_UÆ_x0019_ÂÌ\¸ _x0000_5_x0000_0_x0000_7_x0000_	_x0000__x0001_3_x0000_5Î _x0000_ÑÐ¤Â@Õ¤ÂìÓ Î_x000F__x0000__x0000_pspin@naver.com_x0005__x0000__x0000_22022_x0003__x0000__x0001_HÅ°ÆÄÉ_x000C__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_7_x0000_._x0000_5_x0000__x000E__x0000__x0000_37690004560137_x0006__x0000__x0000_D00195
+_x0000__x0001_¤ÂìÓ ÎLÑlÐ(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_6172249744_x0005__x0000__x0001_¤ÂìÓ ÎLÑlÐ_x0003__x0000__x0001_tÇÝÐ0®_x0006__x0000__x0001__x001C_ÈpÈÅÅ _x0000_Áä¹_x000C__x0000__x0001_õ¬_x0008_Æ _x0000_¤ÂìÓ Î©ÆÔ,_x0000_ _x0000_¡ÇTÖ_x000B__x0000__x0000_051-7564800_x000C__x0000__x0000_051-756-4801_x0005__x0000__x0000_48222_x0017__x0000__x0001_½°À_x0011_­íÅÜÂ _x0000_Ù³·l­ _x0000_+ÈiÕ´ÆÙ³¥Ç\¸ _x0000_4_x0000_0_x0000_¼8® _x0000_8_x0000_'_x0000__x0001_1_x0000_0_x0000_3_x0000_Ù³ _x0000_1_x0000_0_x0000_5_x0000_8Ö,_x0000_1_x0000_0_x0000_6_x0000_8Ö(_x0000_¬ÀÁÉÙ³,_x0000_½°À _x0000_DÅÜÂDÅÜ´ _x0000_TÏ$Æq¸ _x0000_XÕ²DÌ _x0000_DÅ_x000C_Ó¸Ò)_x0000__x000D__x0000__x0000_010-5578-1988_x0015__x0000__x0000_ltktennis@hanmail.net_x000B__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_8_x0000__x0008__x0000__x0000_20150611_x000E__x0000__x0000_37690004562437_x0006__x0000__x0000_D00196	_x0000__x0001__x0015_¬¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_5041920932_x0004__x0000__x0001__x0015_¬¤ÂìÓ Î_x0003__x0000__x0001__x0015_¬@Çl­_x000D__x0000__x0001_LÑÈ²¤Â©ÆÔ,_x0000_ _x0000_XÇX¹,_x0000_ _x0000_àÂ_x001C_¼_x000C__x0000__x0000_053-314-9090_x0005__x0000__x0000_41433_x000D__x0000__x0000_010-3828-0474_x0013__x0000__x0000_keg0417@hanmail.net_x000D__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_6_x0000_+_x0000_1_x0000_5_x0000__x0008__x0000__x0000_20150612_x000E__x0000__x0000_37690004565337_x0006__x0000__x0000_D00199
+_x0000__x0001_P´¬¹¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1283008985_x0003__x0000__x0001_@®_x0001_Æ Á_x000B__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_¤ÂìÓ ÎXÇX¹_x0008__x0000__x0000_20150703_x000C__x0000__x0000_031-911-4191_x000C__x0000__x0000_031-913-0067_x0006__x0000__x0000_410829_x000F__x0000__x0001_½¬0®Ä³à¬ÅÜÂ _x0000_|Ç°ÀÙ³l­_x0015_È_x001C_¼°ÀÙ³_x000E__x0000__x0001_1_x0000_1_x0000_4_x0000_8_x0000_-_x0000_1_x0000_3_x0000_ _x0000_1_x0000_5Î2_x0000_,_x0000_3_x0000_8Ö_x000D__x0000__x0000_010-4288-3563_x0012__x0000__x0000_usop2n@hanmail.net_x000D__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_6_x0000_+_x0000_2_x0000_3_x0000__x000E__x0000__x0000_37690004568237_x0006__x0000__x0000_D00201_x000E__x0000__x0001_(_x0000_üÈ)_x0000_¤ÂtÎtÇ¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_6278102573_x000B__x0000__x0001_¤ÂtÎtÇ¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000__x0003__x0000__x0001_@®1ÁÐÆ_x0006__x0000__x0001_Áä¹ÅÅ _x0000_Ä³ä¹_x0008__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_ä¹_x0010_È_x000C__x0000__x0000_041-566-1879_x000C__x0000__x0000_041-554-2732_x0005__x0000__x0000_31157"_x0000__x0001_©Í­Ì¨°Ä³ _x0000_ÌHÅÜÂ _x0000__x001C_Á½l­ _x0000_1¼_x001D_Á3_x0000_\¸ _x0000_2_x0000_9_x0000_ _x0000_ _x0000_(_x0000_1¼_x001D_ÁÙ³,_x0000_ _x0000_½¶É¹_x0008_Ã%¼)_x0000__x000D__x0000__x0000_010-4513-1879_x0011__x0000__x0000_kimsw000@nate.com_x000E__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_4_x0000_0_x0000_+_x0000_2_x0000_0_x0000__x0008__x0000__x0000_20150804_x000E__x0000__x0000_37690004570937_x0006__x0000__x0000_D00202_x0008__x0000__x0001_¤ÂìÓå²(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_3052275067_x0003__x0000__x0001_HÅü­¹Â_x000C__x0000__x0000_042-522-9566_x000C__x0000__x0000_042-271-4786_x0006__x0000__x0000_300810_x0017__x0000__x0001__x0000_³_x0004_È_x0011_­íÅÜÂ _x0000__x0011_Él­ _x0000_Ù³_x001C_Á_x0000_³\¸ _x0000_1_x0000_2_x0000_0_x0000_1_x0000_(_x0000_ÜÐÉÓÙ³)_x0000__x0007__x0000__x0001_¤ÂìÓå² _x0000_ÜÐÉÓ_x0010_È_x000B__x0000__x0000_01062224787_x0010__x0000__x0000_spodaq@naver.com_x000D__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_5_x0000_+_x0000_3_x0000_3_x0000__x0008__x0000__x0000_20150805_x000E__x0000__x0000_37690004571537_x0006__x0000__x0000_D00203	_x0000__x0001_ðÅTÏ¬¹DÅ(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_2041477980_x0004__x0000__x0001_ðÅTÏ¬¹DÅ_x0003__x0000__x0001_@®ÁÀ0®_x0006__x0000__x0001_Ä³Áä¹ _x0000_t¬$Á_x000D__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_´Ì!ÇÜÂ_x001C_Á&lt;»$ÁXÎ_x0008__x0000__x0000_20150806_x000C__x0000__x0000_02-3390-4345_x000C__x0000__x0000_02-3390-4344
+_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_Ù³_x0000_³8»l­_x0005__x0000__x0000_02496_x0011__x0000__x0001__x001C_Á¸Æ _x0000_Ù³_x0000_³8»l­ _x0000_Ý¹°Æ\¸1_x0000_2_x0000_8® _x0000_1_x0000_9_x0000__x000B__x0000__x0001_1_x0000_5Î _x0000_XÕtÇÐÆ¤ÂìÓ Î°ÀÅÅ_x000D__x0000__x0000_010-9089-5363_x0017__x0000__x0000_01090895363@hanmail.net_x000B__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_2_x0000_0_x0000__x000E__x0000__x0000_37690004572137_x0006__x0000__x0000_D00205_x0005__x0000__x0001_ÁLÑ¤ÂìÓ Î
+_x0000__x0000_1971301851_x0003__x0000__x0001_@®_x0001_Æ_x0018_Â_x0008__x0000__x0001_Ä³Áä¹ÅÅ _x0000_Ä³ä¹ÅÅ	_x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_4»íÅÅÅ_x000B__x0000__x0000_01063388568_x0008__x0000__x0001_½¬0®Ä³ _x0000_XÇ_x0015_È½ÜÂ_x0005__x0000__x0000_11806!_x0000__x0001_½¬0®Ä³ _x0000_XÇ_x0015_È½ÜÂ _x0000_$Æ©º\¸ _x0000_1_x0000_7_x0000_0_x0000_ _x0000_°Àä´È¹DÇ _x0000_DÅ_x000C_Ó¸Ò _x0000_4_x0000_1_x0000_2_x0000_-_x0000_7_x0000_0_x0000_6_x0000__x000D__x0000__x0000_010-6338-8568_x0011__x0000__x0000_3388568@naver.com_x0005__x0000__x0000_26002_x0003__x0000__x0001__x0015_¬ÜÐ8Ö_x0008__x0000__x0000_20220901_x000E__x0000__x0000_37690004700437_x0006__x0000__x0000_D00209_x0018__x0000__x0001_¤ÂìÓ Î_x000C_Õì·¤Â(_x0000_S_x0000_p_x0000_o_x0000_r_x0000_t_x0000_s_x0000_ _x0000_P_x0000_l_x0000_u_x0000_s_x0000_)_x0000_(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1192167071_x0003__x0000__x0001__x0015_¬ÜÂ¨º_x0006__x0000__x0001_Ä³Áä¹ _x0000_LÇÝÂ_x0008__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_\ÕÝÂ_x000B__x0000__x0000_02-871-5513	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x0000_­EÅl­_x0005__x0000__x0000_08750_x000F__x0000__x0001__x001C_Á¸Æ _x0000__x0000_­EÅl­ _x0000_àÂ¼¹\¸3_x0000_8® _x0000_4_x0000_0_x0000__x0005__x0000__x0001_ÀÉXÕ _x0000_1_x0000_5Î_x000D__x0000__x0000_010-7703-5353_x001A__x0000__x0000_tennisplus0122@esero.go.krX_x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_ _x0000_/_x0000_ _x0000_2_x0000_5_x0000_S_x0000_S_x0000_ _x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_ _x0000_/_x0000_ _x0000_2_x0000_4_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_9_x0000_._x0000_6_x0000_ _x0000_/_x0000_ _x0000_2_x0000_4_x0000_S_x0000_S_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_ _x0000_/_x0000_ _x0000_2_x0000_3_x0000_F_x0000_W_x0000_ _x0000__x0018_ÂüÈ _x0000_ìÅàÂ _x0000_ _x0000_1_x0000_2_x0000_ _x0000_(_x0000_ô²ù²Ç _x0000_Æ­Ì&lt;Ç\¸ _x0000_6_x0000_ _x0000__x0018_¼_x0001_Æ)_x0000__x0008__x0000__x0000_20160114_x000E__x0000__x0000_37690004577337_x0006__x0000__x0000_D00210_x0011__x0000__x0001_(_x0000_üÈ)_x0000_ÐÅtÇ_x001C_ÈtÇxÇ0Ñ´°TÁ °(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1268641398_x000C__x0000__x0000_031-761-8980_x000C__x0000__x0000_031-761-2140_x0005__x0000__x0000_12769_x000D__x0000__x0000_010-4552-3318	_x0000__x0000_1800-6142_x000E__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_4_x0000_0_x0000_+_x0000_2_x0000_5_x0000__x0008__x0000__x0000_20160121_x000E__x0000__x0000_37690004578037_x0006__x0000__x0000_D00256	_x0000__x0001_p¬1Á¤ÂìÓ Î(_x0000_Å°À)_x0000_
+_x0000__x0000_6210808090_x0003__x0000__x0001__x0015_È+È_x0015_¬_x0006__x0000__x0001_Ä³Áä¹ _x0000__x001C_ÈpÈ_x000B__x0000__x0001_ìÕ¤Â0®l­,_x0000_ _x0000_¤ÂìÓ Î©ÆÔ_x0008__x0000__x0000_20160412_x000C__x0000__x0000_055-387-3613_x000C__x0000__x0000_055-387-3615_x0008__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_Å°ÀÜÂ_x0005__x0000__x0000_50621 _x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_Å°ÀÜÂ _x0000__x001C_Á|ÇÙ³\¸ _x0000_2_x0000_5_x0000_ _x0000_ _x0000_(_x0000__x0011_É½Ù³,_x0000_ _x0000_$Ç ÁÝÀ_x0001_Æ´ÅP­äÂ)_x0000__x000D__x0000__x0000_010-2390-2994_x0013__x0000__x0000_dhrhr68@hanmail.netH_x0000__x0001_2_x0000_4_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_3_x0000_5_x0000_ _x0000_/_x0000_2_x0000_4_x0000_S_x0000_S_x0000__x0018_ÂüÈìÅàÂ _x0000_3_x0000_5_x0000_ _x0000_/_x0000_ _x0000_2_x0000_3_x0000_F_x0000_W_x0000_ _x0000__x0018_ÂüÈ _x0000_ìÅàÂ _x0000_3_x0000_5_x0000_ _x0000_/_x0000_ _x0000_2_x0000_3_x0000_S_x0000_S_x0000_ _x0000__x0018_ÂüÈ _x0000_ìÅàÂ _x0000_3_x0000_5_x0000_(_x0000_|·_x0013_Ï+_x0000_È¹D¾¤Â _x0000_9_x0000_4_x0000_3_x0000_,_x0000_2_x0000_5_x0000_0_x0000_)_x0000__x0008__x0000__x0000_20160407_x000E__x0000__x0000_37690004581237_x0006__x0000__x0000_D00267_x0006__x0000__x0001__x001C_ÈtÇD¾¤ÂìÓ Î
+_x0000__x0000_6664100083_x0003__x0000__x0001_Ç_x0015_È\Õ_x000D__x0000__x0001_Ä³ä¹ _x0000__x000F_¼ _x0000_Áä¹ÅÅ,_x0000_ _x0000__x001C_ÁD¾¤Â_x000C__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_ _x0000__x0011_­à¬_x0000_³ÕÅÅ_x0008__x0000__x0000_20160610_x000C__x0000__x0000_062-523-7451_x000C__x0000__x0000_062-523-7455_x0005__x0000__x0000_62023_x000D__x0000__x0001__x0011_­üÈ _x0000__x001C_Ál­ _x0000_´ÆÌ\¸ _x0000_1_x0000_2_x0000_2_x0000__x0005__x0000__x0001_(_x0000__x000D_Ã_x000C_ÍÙ³)_x0000__x000D__x0000__x0000_010-4606-4538_x0015__x0000__x0000_jhrim1226@hanmail.net_x0008__x0000__x0000_20160601_x000E__x0000__x0000_37690004584137_x0006__x0000__x0000_D00280_x0005__x0000__x0001_Ä³ô²¤ÂìÓ Î
+_x0000__x0000_3071042161_x0003__x0000__x0001_$ÇÙ³ÝÂ_x000B__x0000__x0001_Ä³ä¹_x000F_¼ _x0000_Áä¹ÅÅ _x0000_Áä¹ÅÅ_x0010__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_Ç_x0004_Èp¬ _x0000__x0010_Óä¹,_x0000_ _x0000__x0000_³ìÅ_x0008__x0000__x0000_20160825_x000C__x0000__x0000_044-863-8908_x000C__x0000__x0000_044-863-8970_x000F__x0000__x0001_8Á+È¹ÒÄ¼ÇXÎÜÂ _x0000_8Á+È¹ÒÄ¼ÇXÎÜÂ_x0005__x0000__x0000_30102_x001E__x0000__x0001_8Á+È¹ÒÄ¼ÇXÎÜÂ _x0000__x0008_È¬Ç\¸ _x0000_1_x0000_7_x0000_2_x0000_ _x0000_(_x0000_´ÅÄÉÙ³,_x0000_ _x0000_ÜÐ\Õ_x0004_Õ_x0008_¸¤Â&lt;Á0Ñ)_x0000__x0004__x0000__x0001_1_x0000_0_x0000_1_x0000_8Ö_x000D__x0000__x0000_010-7185-8008_x0015__x0000__x0000_dodamsports@naver.com_x000E__x0000__x0000_37690004586437_x0006__x0000__x0000_D00282_x0005__x0000__x0001__x0004_²¬¹¤ÂìÓ Î
+_x0000__x0000_1082124505_x0003__x0000__x0001_@®l×_x0015_È_x0006__x0000__x0001_Áä¹ _x0000_Ä³Áä¹_x000C__x0000__x0001__x0004_ÈÇÁÀp¬·ÅÅ _x0000_0¼Ü´ü»4Ñ _x0000__x000B__x0000__x0000_02-848-6291_x000B__x0000__x0000_02-848-7556
+_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x0001_Æñ´ìÓl­_x0005__x0000__x0000_07375_x000E__x0000__x0001__x001C_Á¸Æ _x0000__x0001_Æñ´ìÓl­ _x0000_Ä³àÂ\¸ _x0000_5_x0000_1_x0000__x000D__x0000__x0001_1_x0000_5Î _x0000_1_x0000_0_x0000_5_x0000_8Ö(_x0000_¡ÁU³L¾)µ)_x0000__x000D__x0000__x0000_010-8393-6291_x0013__x0000__x0000_hee00jung@naver.com_x0008__x0000__x0000_20160905_x000E__x0000__x0000_37690004588737_x0006__x0000__x0000_D00286_x0007__x0000__x0001_Æ%±¤Â _x0000_1Á¨°_x0010_È
+_x0000__x0000_2603001743_x0003__x0000__x0001_MÖ¥Ç8Ö_x0008__x0000__x0001_Ä³ä¹ _x0000__x000F_¼ _x0000_Áä¹ÅÅ_x0008__x0000__x0000_20151218_x000C__x0000__x0000_031-755-7257_x0007__x0000__x0001_½¬0®Ä³ _x0000_1Á¨°ÜÂ_x0005__x0000__x0000_13110_x001E__x0000__x0001_½¬0®Ä³ _x0000_1Á¨°ÜÂ _x0000__x0018_Â_x0015_Èl­ _x0000_1Á¨°_x0000_³\¸ _x0000_1_x0000_2_x0000_6_x0000_7_x0000_ _x0000_-_x0000_1_x0000_ _x0000_(_x0000_ÜÐÉÓÙ³)_x0000__x000D__x0000__x0000_010-7191-7257_x0012__x0000__x0000_nero1016@naver.com_x0002__x0000__x0001_¨°¸Ó_x0008__x0000__x0000_20161109_x000E__x0000__x0000_37690004591037_x0006__x0000__x0000_D00287_x0005__x0000__x0001_¤ÐtÎ¤ÂìÓ Î
+_x0000__x0000_6103752918_x0003__x0000__x0001_@®ÜÐÇ_x0008__x0000__x0000_20161125_x000C__x0000__x0000_052-268-6086_x000C__x0000__x0000_052-272-5908_x0008__x0000__x0001_¸Æ°À_x0011_­íÅÜÂ _x0000_¨°l­_x0005__x0000__x0000_44692_x0016__x0000__x0001_¸Æ°À_x0011_­íÅÜÂ _x0000_¨°l­ _x0000_Ë³ÈÉ\¸ _x0000_1_x0000_2_x0000_4_x0000_ _x0000_ _x0000_(_x0000_ì²Ù³)_x0000__x0003__x0000__x0000_3/2_x000D__x0000__x0000_010-9568-6086_x0014__x0000__x0000_kika5908@hanmail.net_x000E__x0000__x0000_37690004592637_x0006__x0000__x0000_D00292_x0008__x0000__x0001_Æ%±¤Â _x0000_¤ÂìÓÐÆ_x0010_È
+_x0000__x0000_6977800050_x0003__x0000__x0001_\ÕÀ­_x0001_Æ_x0008__x0000__x0000_20170102_x000C__x0000__x0000_051-517-3862_x000C__x0000__x0000_051-583-1023	_x0000__x0001_½°À_x0011_­íÅÜÂ _x0000__x0008_®_x0015_Èl­_x0005__x0000__x0000_46207&amp;_x0000__x0001_½°À_x0011_­íÅÜÂ _x0000__x0008_®_x0015_Èl­ _x0000_´Ì!Çõ¬ÐÆ\¸3_x0000_9_x0000_9_x0000_¼8® _x0000_3_x0000_2_x0000_4_x0000_ _x0000_ _x0000_(_x0000_P´l­Ù³,_x0000_ _x0000_¤ÂìÓÐÆ_x000C_ÓlÐ)_x0000__x0010__x0000__x0001_ÀÉXÕ1_x0000_5Î(_x0000_P´l­Ù³,_x0000_ _x0000_äÂ´°´Ì!Ç_x0000_­)_x0000__x000D__x0000__x0000_010-5505-3862_x0013__x0000__x0000_hgy4285@hanmail.net_x000E__x0000__x0000_37690004595537_x0006__x0000__x0000_D00306_x0007__x0000__x0001_Æ%±¤Â _x0000_ÁÀ4»_x0010_È
+_x0000__x0000_8042300420_x0003__x0000__x0001_@®_x0004_Ö+È_x000D__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_´ÆÙ³©ÆÔ _x0000_¡ÇTÖ_x0008__x0000__x0000_20170119_x000D__x0000__x0000_010-6886-7065_x000C__x0000__x0000_062-374-5410_x0005__x0000__x0000_61970_x0013__x0000__x0001__x0011_­üÈ _x0000__x001C_Ál­ _x0000_ÁÀ4»ü»üÈ\¸3_x0000_2_x0000_¼8® _x0000_3_x0000_-_x0000_5_x0000__x0013__x0000__x0000_sskim-j@hanmail.net_x000E__x0000__x0000_37690004597837_x0006__x0000__x0000_D00308_x0005__x0000__x0001_C_x0000_S_x0000_¤ÂìÓ Î
+_x0000__x0000_2270838785_x0007__x0000__x0001_iÖ_x001C_ÂU³xÆ _x0000_1_x0000_+º_x000C__x0000__x0000_031-385-1222_x000C__x0000__x0000_031-388-3477_x0005__x0000__x0000_13958_x0016__x0000__x0001_½¬0® _x0000_HÅÅÜÂ _x0000_Ì¹HÅl­ _x0000__x0008_Æ Âõ¬ÐÆ\¸5_x0000_2_x0000_¼8® _x0000_2_x0000__x000D__x0000__x0000_010-3176-9037_x0013__x0000__x0000_bill@cssports.co.kr_x000D__x0000__x0000_010-2727-2718_x000F__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_5_x0000_+_x0000_3_x0000_._x0000_5_x0000__x000E__x0000__x0000_37690004598437_x0006__x0000__x0000_D00311
+_x0000__x0001_TÏ¬¹DÅ¤ÂìÓ Î(_x0000_ÜÂe×)_x0000_
+_x0000__x0000_3047001336_x0006__x0000__x0001_TÏ¬¹DÅ¤ÂìÓ Î_x0003__x0000__x0001_\Í_x0001_Æ_x0019_Â_x0012__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000__x0010_Ó	Í&lt;»,_x0000_xÇÄÁ&lt;»,_x0000_0®ÀÐ©ÆÔ_x000D__x0000__x0000_010-2618-5518_x000C__x0000__x0000_031-312-8982_x0007__x0000__x0001_½¬0®Ä³ _x0000_ÜÂe×ÜÂ_x0005__x0000__x0000_14922_x000F__x0000__x0001_½¬0® _x0000_ÜÂe×ÜÂ _x0000_@ÇÄ¬¼_x0001_Æ8® _x0000_2_x0000_7_x0000__x000F__x0000__x0001_3_x0000_0_x0000_3_x0000_8Ö(_x0000_@ÇÕÙ³,_x0000_ _x0000_ÜÂðÒ_x000C_ÓlÐ)_x0000__x0015__x0000__x0000_queenmt5518@naver.com_x000C__x0000__x0000_031-404-6121_x0008__x0000__x0000_20170220_x000E__x0000__x0000_37690004600637_x0006__x0000__x0000_D00312_x000E__x0000__x0001_Æ%±¤Â(_x0000_Y_x0000_O_x0000_N_x0000_E_x0000_X_x0000_)_x0000_ _x0000_tÇÌ_x0010_È
+_x0000__x0000_1052641553_x0003__x0000__x0001_$Ç ÇÄÉ_x000C__x0000__x0000_031-631-2210_x0007__x0000__x0001_½¬0®Ä³ _x0000_tÇÌÜÂ_x0005__x0000__x0000_17362_x0017__x0000__x0001_½¬0®Ä³ _x0000_tÇÌÜÂ _x0000_`Å(¸_x0015_È\¸ _x0000_1_x0000_4_x0000_2_x0000_ _x0000_ _x0000_(_x0000_=Ì_x0004_ÈÙ³)_x0000__x000D__x0000__x0000_010-3459-1313_x0010__x0000__x0000_jin7601@daum.net_x0003__x0000__x0001_\Í_x0015_¬8Ö_x0008__x0000__x0000_20170221_x000E__x0000__x0000_37690004601237_x0006__x0000__x0000_D00324_x0006__x0000__x0001__x000C_Ó¸Ò_x0008_±¤ÂìÓ Î
+_x0000__x0000_1272471368_x0003__x0000__x0001_@®©Æ`Å_x000C__x0000__x0000_031-398-8953_x000C__x0000__x0000_031-398-8954_x0007__x0000__x0001_½¬0®Ä³ _x0000_p­ìÓÜÂ_x0005__x0000__x0000_15833_x0016__x0000__x0001_½¬0®Ä³ _x0000_p­ìÓÜÂ _x0000_$Æ_x0008_®\¸ _x0000_1_x0000_5_x0000_0_x0000_ _x0000_ _x0000_(_x0000__x0008_®_x0015_ÈÙ³)_x0000_	_x0000__x0001_1_x0000_0_x0000_2_x0000_8Ö(_x0000__x0008_®_x0015_ÈÙ³)_x0000__x000D__x0000__x0000_010-4854-8953_x0010__x0000__x0000_kya5767@nate.com_x0008__x0000__x0000_20170320_x000E__x0000__x0000_37690004603537_x0006__x0000__x0000_D00328_x0006__x0000__x0001_ÄÉüÈ0¼Ü´ü»4Ñ
+_x0000__x0000_6131082729_x0003__x0000__x0001__x0015_È Ìä¬_x000C__x0000__x0000_055-747-2101_x0008__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_ÄÉüÈÜÂ_x0005__x0000__x0000_52806_x0019__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_ÄÉüÈÜÂ _x0000_Á-¼\¸7_x0000_5_x0000_¼8® _x0000_8_x0000_ _x0000_ _x0000_(_x0000_ÁÀÉÓÙ³)_x0000__x000D__x0000__x0000_010-9612-2188_x0011__x0000__x0000_jcg2188@naver.com_x000B__x0000__x0000_01095082188_x0008__x0000__x0000_20170324_x000E__x0000__x0000_37690004604137_x0006__x0000__x0000_D00338
+_x0000__x0001_Æ%±¤Â=ÌÐÆ_x0010_È(_x0000_øÂtÎ)_x0000_
+_x0000__x0000_6092352584_x0003__x0000__x0001_HÅ¬Çü­_x0010__x0000__x0001_¤ÂìÓ Î _x0000_XÇX¹ _x0000__x000F_¼ _x0000_©ÆÔ _x0000_È¹lÐ_x001C_ÈÇ_x0008__x0000__x0000_20170411_x000C__x0000__x0000_055-261-0123_x0005__x0000__x0000_51420_x0019__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_=ÌÐÆÜÂ _x0000_1Á°Àl­ _x0000__x0018_¼ÀÉ\¸ _x0000_8_x0000_ _x0000_ _x0000_(_x0000__x0018_¼ÀÉÙ³)_x0000__x0005__x0000__x0001_(_x0000__x0018_¼ÀÉÙ³)_x0000__x000D__x0000__x0000_010-9796-1346_x0011__x0000__x0000_cwssaka@naver.com
+_x0000__x0000_0552610123_x000E__x0000__x0000_37690004606437_x0006__x0000__x0000_D00382_x0004__x0000__x0001_$Æ¤ÂìÓ Î
+_x0000__x0000_2860500614_x0003__x0000__x0001__x0015_¼Á|·_x000C__x0000__x0001__x0004_ÈÇÁÀp¬·(_x0000_¤ÂìÓ Î©ÆÔ)_x0000__x000C__x0000__x0000_063-231-0360_x0005__x0000__x0000_54947_x0015__x0000__x0001__x0004_È½ _x0000__x0004_ÈüÈÜÂ _x0000_DÆ°Àl­ _x0000__x0004_È|·_x0010_¬_x0001_Æ\¸ _x0000_4_x0000_0_x0000_-_x0000_1_x0000__x000B__x0000__x0000_01076785147_x0014__x0000__x0000_sora1976kr@naver.com_x0003__x0000__x0001__x0015_¼Ñ¼%ÆQ_x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_+_x0000_1_x0000_0_x0000_0_x0000_ _x0000_/_x0000_ _x0000_2_x0000_5_x0000_S_x0000_S_x0000_ _x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_ _x0000_+_x0000_ _x0000_1_x0000_0_x0000_0_x0000_ _x0000_/_x0000_ _x0000_ _x0000_2_x0000_4_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_ _x0000_/_x0000_ _x0000_2_x0000_4_x0000_S_x0000_S_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_ _x0000_/_x0000_ _x0000_2_x0000_3_x0000_F_x0000_W_x0000_ _x0000__x0018_ÂüÈ _x0000_ìÅàÂ _x0000_1_x0000_2_x0000__x0008__x0000__x0000_20170710_x000E__x0000__x0000_37690004610337_x0006__x0000__x0000_D00392_x0007__x0000__x0001_¨Ö1Á+ÈiÕ¤ÂìÓ Î
+_x0000__x0000_7521600607_x0002__x0000__x0001_@®_x0004_½_x0008__x0000__x0000_20170812_x000C__x0000__x0000_064-733-2992_x0005__x0000__x0000_63591_x0013__x0000__x0001__x001C_ÈüÈ¹ÒÄ¼ÇXÎÄ³ _x0000__x001C_ÁÀ­ìÓÜÂ _x0000_Ù³8»\¸ _x0000_3_x0000_0_x0000__x000B__x0000__x0000_01090156265_x0010__x0000__x0000_ddadon@naver.com_x000B__x0000__x0000_01036928845_x0008__x0000__x0000_20170821_x000E__x0000__x0000_37690004611037_x0006__x0000__x0000_D00396_x000E__x0000__x0001_Æ%±¤Â _x0000_Å°À_x0010_È(_x0000_TÖ·¤ÂìÓ Î)_x0000_
+_x0000__x0000_6211383962_x0003__x0000__x0001_\ÍiÖðÅ_x0008__x0000__x0000_20170813_x000C__x0000__x0000_055-382-6688_x000C__x0000__x0000_055-366-6648_x0005__x0000__x0000_50548_x000F__x0000__x0001_½¬¨° _x0000_Å°ÀÜÂ _x0000_ÅÆÁÀ_x0000_³\¸ _x0000_9_x0000_6_x0000_1_x0000__x0007__x0000__x0001_Æ%±¤Â _x0000_Å°À_x0010_È_x000D__x0000__x0000_010-9323-8281_x0016__x0000__x0000_eegmom0808@hanmail.net_x0008__x0000__x0000_20170915_x000E__x0000__x0000_37690004612637_x0006__x0000__x0000_D00408_x0005__x0000__x0001_l­¬¹TÏ¸Ò\¸
+_x0000__x0000_1321920436_x0003__x0000__x0001_àÂ_x0001_Æ8Ö_x0008__x0000__x0000_20060509_x000C__x0000__x0000_031-562-3307_x0005__x0000__x0000_11942_x0012__x0000__x0001_½¬0®Ä³ _x0000_¨°ÅüÈÜÂ _x0000__x0000_¬´Æ\¸2_x0000_8® _x0000_1_x0000_1_x0000_4_x0000__x000D__x0000__x0001_ø»1Á_x0004_Õ|·Ç _x0000_1_x0000_5Î _x0000_1_x0000_0_x0000_3_x0000_8Ö_x000D__x0000__x0000_010-3909-6608_x0015__x0000__x0000_sjs940421@hanmail.net_x000B__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_2_x0000_6_x0000__x0008__x0000__x0000_20171226_x000E__x0000__x0000_37690004615537_x0006__x0000__x0000_D00409_x0007__x0000__x0001_Æ%±¤Â _x0000_¤ÂìÓ Î
+_x0000__x0000_8624500277_x0003__x0000__x0001_tÇU³©Æ_x0008__x0000__x0000_20170905_x000C__x0000__x0000_041-357-1617_x0008__x0000__x0001_©Í­Ì¨°Ä³ _x0000_ù²ÄÉÜÂ_x0005__x0000__x0000_31777_x000E__x0000__x0001_©Í¨° _x0000_ù²ÄÉÜÂ _x0000_P­Ù³8® _x0000_1_x0000_2_x0000_4_x0000__x000D__x0000__x0000_010-3116-9915_x0013__x0000__x0000_ljy161617@naver.com_x0008__x0000__x0000_20171221_x000E__x0000__x0000_37690004616137_x0006__x0000__x0000_D00416_x0005__x0000__x0001__x001C_ÁÄÉ¤ÂìÓ Î
+_x0000__x0000_5920100957_x0003__x0000__x0001_@®ÉÓÜÐ_x000D__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_ _x0000__x0004_ÈÇÁÀp¬·ÅÅ_x0008__x0000__x0000_20180301_x000C__x0000__x0000_031-236-4936_x000C__x0000__x0000_031-216-4936_x0007__x0000__x0001_½¬0®Ä³ _x0000_©ÆxÇÜÂ_x0005__x0000__x0000_16833_x0013__x0000__x0001_½¬0® _x0000_©ÆxÇÜÂ _x0000__x0018_ÂÀÉl­ _x0000_ìÓ@Ç_x0000_³\¸ _x0000_4_x0000_6_x0000_7_x0000__x0016__x0000__x0001__x0018_ÂÀÉxÔt¹ÀÉ$ÆÔÆÜ´È¹lÐÁÀ_x0000_¬ _x0000_1_x0000_0_x0000_3_x0000_Ù³ _x0000_1_x0000_2_x0000_3_x0000_8Ö_x000D__x0000__x0000_010-4679-5630_x0013__x0000__x0000_ren7303@hanmail.net_x000E__x0000__x0000_37690004618437_x0006__x0000__x0000_D00431_x0006__x0000__x0001_¤ÂìÓ Îä¹È²DÅ
+_x0000__x0000_2701201033_x0003__x0000__x0001_8»¹ÂÄÉ_x0008__x0000__x0000_20180615_x000C__x0000__x0000_042-545-8511	_x0000__x0001__x0000_³_x0004_È_x0011_­íÅÜÂ _x0000_ Ç1Ál­_x0005__x0000__x0000_34210_x0016__x0000__x0001__x0000_³_x0004_È _x0000_ Ç1Ál­ _x0000_YÕXÕ_x0011_ÉYÅ\¸1_x0000_2_x0000_8_x0000_¼8® _x0000_2_x0000_3_x0000_-_x0000_8_x0000__x000B__x0000__x0001_1_x0000_0_x0000_2_x0000_8Ö _x0000_¤ÂìÓ Îä¹È²DÅ_x000D__x0000__x0000_010-6683-2114_x0013__x0000__x0000_capmoon39@naver.com_x0008__x0000__x0000_20180427_x000E__x0000__x0000_37690004623037_x0006__x0000__x0000_D00433_x000D__x0000__x0001__x0015_È_x0018_Â¤ÂìÓ Î _x0000_Æ%±¤Â _x0000__x0001_ÆüÈ_x0010_È
+_x0000__x0000_5293300343_x0003__x0000__x0001_@®Ù³ðÅ	_x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_ _x0000_XÇX¹_x0008__x0000__x0000_20170407_x000B__x0000__x0000_01048177736
+_x0000__x0000_0546367233_x0008__x0000__x0001_½¬ÁÀ½Ä³ _x0000__x0001_ÆüÈÜÂ_x0005__x0000__x0000_36138_x0013__x0000__x0001_½¬½ _x0000__x0001_ÆüÈÜÂ _x0000__x0000_³YÕ\¸2_x0000_0_x0000_1_x0000_¼8® _x0000_8_x0000_-_x0000_6_x0000__x0007__x0000__x0001_iÖ_x0008_®L¾)µ _x0000_1_x0000_5Î_x000D__x0000__x0000_010-4817-7736_x0013__x0000__x0000_kdy9249@hanmail.net_x0008__x0000__x0000_20180518_x000E__x0000__x0000_37690004624637_x0006__x0000__x0000_D00471_x000B__x0000__x0001_(_x0000_üÈ)_x0000_DÅüÈ_x0008_¸ìÓ Î__x0000_¹Ò_x0010_Ó_x000B__x0000__x0001_(_x0000_üÈ)_x0000_DÅüÈ_x0008_¸ìÓ Î-_x0000_¹Ò_x0010_Ó_x0008__x0000__x0000_20181026_x000B__x0000__x0000_02-489-1992_x000E__x0000__x0001_½¬0® _x0000__x0011_­üÈÜÂ _x0000_à¬½\¸ _x0000_3_x0000_4_x0000_0_x0000__x000D__x0000__x0000_070-4741-9644_x000E__x0000__x0000_37690004626937_x0006__x0000__x0000_D00490	_x0000__x0001_à¬ÅÜÂ0¼Ü´ü»4Ñ_x0011_ÖÖ
+_x0000__x0000_1288284226_x0003__x0000__x0001_tÇ8ÖÄÉ_x0008__x0000__x0000_20190315_x000B__x0000__x0000_01027161641_x0005__x0000__x0000_10223_x0014__x0000__x0001_½¬0® _x0000_à¬ÅÜÂ _x0000_|Ç°À_x001C_Ál­ _x0000__x0011_ÉYÅ\¸ _x0000_1_x0000_6_x0000_0_x0000_1_x0000__x001D__x0000__x0001_,_x0000_ _x0000_1_x0000_5Î(_x0000__x0000_³TÖÙ³,_x0000_ _x0000_à¬ÅÜÂ+ÈiÕ´ÆÙ³¥Ç _x0000_ÀÉXÕ1_x0000_5Î _x0000_C_x0000_-_x0000_0_x0000_8_x0000_)_x0000__x000D__x0000__x0000_010-2716-1641_x0012__x0000__x0000_76melany@gmail.com_x0005__x0000__x0000_19003_x0003__x0000__x0001_HÅ¬Ç°Æ_x000E__x0000__x0000_37690004628137_x0006__x0000__x0000_D00503_x0005__x0000__x0001_°tÇ¤Âü»4Ñ
+_x0000__x0000_6161951553_x0003__x0000__x0001_à¬ðÅüÈ
+_x0000__x0001_¤ÂìÓ Î©ÆÔ_x000F_¼0®ÀÐ©ÆÔ_x0008__x0000__x0000_20100913_x000C__x0000__x0000_064-712-4524_x000C__x0000__x0000_064-711-4524_x000B__x0000__x0001__x001C_ÈüÈ¹ÒÄ¼ÇXÎÄ³ _x0000__x001C_ÈüÈÜÂ_x0005__x0000__x0000_63087_x0013__x0000__x0001__x001C_ÈüÈ¹ÒÄ¼ÇXÎÄ³ _x0000__x001C_ÈüÈÜÂ _x0000_ÄÉp­8® _x0000_1_x0000_-_x0000_6_x0000__x000D__x0000__x0000_010-3639-7899_x0011__x0000__x0000_ktf1974@naver.com_x0003__x0000__x0001_@®1Át¬_x000B__x0000__x0000_01036397899_x0008__x0000__x0000_20190424_x000E__x0000__x0000_37690004630837_x0006__x0000__x0000_D00504_x0008__x0000__x0001_¤ÂÀÐ¤ÂìÓ Î__x0000_¹Ò_x0010_Ó
+_x0000__x0000_3031310445	_x0000__x0001_¤ÂÀÐ¤ÂìÓ Î(_x0000_©ÍüÈ)_x0000__x0003__x0000__x0001_LÇ_x0011_­l×_x0008__x0000__x0000_20070607_x000C__x0000__x0000_043-855-7688_x000C__x0000__x0000_043-848-3727_x0008__x0000__x0001_©Í­Ì½Ä³ _x0000_©ÍüÈÜÂ_x0005__x0000__x0000_27393_x000E__x0000__x0001_©Í½ _x0000_©ÍüÈÜÂ _x0000__x0015_Ö$Á\¸ _x0000_1_x0000_5_x0000_9_x0000__x0005__x0000__x0001_¤ÂÀÐ¤ÂìÓ Î_x000D__x0000__x0000_010-5303-1397_x0013__x0000__x0000_ekh3083@hanmail.net_x0006__x0000__x0000_D00513	_x0000__x0001__x001C_Á¸ÆÜÂ´Ì!ÇÖ__x0000_¹Ò_x0010_Ó
+_x0000__x0000_6078287556_x0006__x0000__x0001__x001C_Á¸ÆÜÂ´Ì!ÇÖ_x0003__x0000__x0001__x0015_¼ÐÆ_x001C_Â_x0003__x0000__x0001__x001C_ÁD¾¤Â_x0004__x0000__x0001_LÑÈ²¤Â¥Ç_x0008__x0000__x0000_20190614_x0001__x0000__x0000_0	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x0011_É·l­_x0005__x0000__x0000_02119_x000E__x0000__x0001__x001C_Á¸Æ _x0000__x0011_É·l­ _x0000_Ý¹°Æ\¸ _x0000_1_x0000_8_x0000_2_x0000__x0008__x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ´Ì!ÇÖ_x0008__x0000__x0000_20190617_x000E__x0000__x0000_37690004638937_x0006__x0000__x0000_D00515_x0004__x0000__x0001__x0001_Æ4»S_x0000_P_x0000_
+_x0000__x0000_4081497216_x0004__x0000__x0001__x0001_Æ4»s_x0000_p_x0000__x0003__x0000__x0001_@®U³	½_x0007__x0000__x0001_Ä³Áä¹,_x0000_ _x0000__x001C_ÈpÈ_x0011__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_ _x0000_±tÇ0®l­,_x0000_ _x0000_ìÕ¤Â0®l­_x0008__x0000__x0000_20070824_x000D__x0000__x0000_010-3622-7289_x000C__x0000__x0000_062-651-9942_x0008__x0000__x0001__x0011_­üÈ_x0011_­íÅÜÂ _x0000_¨°l­_x0005__x0000__x0000_61655_x000E__x0000__x0001__x0011_­üÈ _x0000_¨°l­ _x0000__x0000_³¨°_x0000_³\¸ _x0000_2_x0000_5_x0000_2_x0000_	_x0000__x0001_1¼´ÆÙ³,_x0000_ _x0000__x0001_Æ4»S_x0000_P_x0000__x0013__x0000__x0000_6519944@hanmail.net_x000D__x0000__x0000_(062)653-4141$_x0000__x0001_2_x0000_4_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_3_x0000_5_x0000_ _x0000_/_x0000_2_x0000_4_x0000_S_x0000_S_x0000__x0018_ÂüÈìÅàÂ _x0000_3_x0000_5_x0000_ _x0000_/_x0000_ _x0000__x0018_Â_x0008_®½qÈ _x0000_2_x0000_ÔÆµÑ_x001C_È_x0008__x0000__x0000_20190531_x000E__x0000__x0000_37690004634337_x0006__x0000__x0000_D00517_x000B__x0000__x0001_O_x0000_K_x0000_ _x0000_¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1293177008_x0003__x0000__x0001_tÇ_x0001_Æ±Æ
+_x0000__x0001_Ä³Áä¹,_x0000_Ä³ä¹,_x0000__x001C_ÁD¾¤Â_x0011__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_l­ä¹_x0000_³Õ,_x0000_t¬&lt;»­ÌÁ©ÆíÅ_x0008__x0000__x0000_20071108_x000C__x0000__x0000_031-708-3066
+_x0000__x0000_0317083067_x0005__x0000__x0000_13504_x0017__x0000__x0001_½¬0® _x0000_1Á¨°ÜÂ _x0000_½ù²l­ _x0000_¥Çø»\¸1_x0000_2_x0000_2_x0000_¼8® _x0000_3_x0000_-_x0000_1_x0000__x0005__x0000__x0001_(_x0000_|ÅÑÐÙ³)_x0000__x000D__x0000__x0000_010-8714-3324_x0014__x0000__x0000_75winwin@hanmail.net_x000B__x0000__x0000_01087143324_x000E__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_5_x0000_+_x0000_2_x0000_2_x0000__x0008__x0000__x0000_20190621_x000E__x0000__x0000_37690004635037_x0006__x0000__x0000_D00519_x0005__x0000__x0001__x0004_Ç_x0008_±¤ÂìÓ Î
+_x0000__x0000_3160449978_x0003__x0000__x0001_\Í_x0004_ÖÄÉ_x0008__x0000__x0000_20140927_x000D__x0000__x0000_010-6482-0228_x000C__x0000__x0000_041-665-1857_x0008__x0000__x0001_©Í­Ì¨°Ä³ _x0000__x001C_Á°ÀÜÂ_x0005__x0000__x0000_31993_x000F__x0000__x0001_©Í¨° _x0000__x001C_Á°ÀÜÂ _x0000_(ÇÀÉ1_x0000_6_x0000_\¸ _x0000_2_x0000_2_x0000__x0008__x0000__x0001_C_x0000_Ù³ _x0000_(_x0000_Ù³8»Ù³)_x0000__x0011__x0000__x0000_chj1981@naver.com_x000D__x0000__x0000_010-9112-9996_x0008__x0000__x0001_6_x0000_ÔÆ _x0000_üÈ8»µÑ_x001C_È/_x0000__x0008__x0000__x0000_20190620_x000E__x0000__x0000_37690004636637_x0006__x0000__x0000_D00524
+_x0000__x0001_üÈÝÂÖ¬À _x0000_©ÆxÇÆ%±¤Â
+_x0000__x0000_7968702997_x0003__x0000__x0001_@®ÄÉ©Æ_x0008__x0000__x0000_20150409_x000D__x0000__x0000_010-8881-0413_x0005__x0000__x0000_16967_x0014__x0000__x0001_½¬0® _x0000_©ÆxÇÜÂ _x0000_0®e×l­ _x0000_àÂ_x0008_¬\¸5_x0000_7_x0000_¼8® _x0000_7_x0000_
+_x0000__x0001_(_x0000_àÂ_x0008_¬Ù³,_x0000_ÐÅ¤Â_x001C_ÈtÇ)_x0000__x0013__x0000__x0000_goodester@naver.com_x0007__x0000__x0001_2_x0000_ÔÆ _x0000__x0018_Â_x0008_®µÑ_x001C_È_x0008__x0000__x0000_20190711_x000E__x0000__x0000_37690004640537_x0006__x0000__x0000_D00526_x0006__x0000__x0001_ìÅ_x0018_Â _x0000_Æ%±¤Â
+_x0000__x0000_6765400493_x0003__x0000__x0001_@® ÁU³_x0008__x0000__x0000_20190701_x000D__x0000__x0000_010-2066-5376_x0008__x0000__x0001__x0004_È|·¨°Ä³ _x0000_ìÅ_x0018_ÂÜÂ_x0005__x0000__x0000_59685_x000D__x0000__x0001__x0004_È¨° _x0000_ìÅ_x0018_ÂÜÂ _x0000_ÈÀ0Ñ\¸ _x0000_2_x0000_5_x0000__x0005__x0000__x0001_(_x0000_àÂ0®Ù³)_x0000__x0014__x0000__x0000_junsoo5376@naver.com_x0003__x0000__x0001_@®_x0000_É_x0018_Â_x0002__x0000__x0001__x0000_¬qÈ_x000E__x0000__x0000_37690004621737_x0006__x0000__x0000_D00527_x000C__x0000__x0001_(_x0000_üÈ)_x0000_tÇÐÅ¤Â¤ÂìÓ Î__x0000_¹Ò_x0010_Ó
+_x0000__x0000_2848100873	_x0000__x0001_(_x0000_üÈ)_x0000_tÇÐÅ¤Â¤ÂìÓ Î_x0003__x0000__x0001__x0015_¼_x0018_Â Ì_x000C__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_ _x0000_µÑàÂ_x0010_Óä¹ÅÅ_x0008__x0000__x0000_20171228_x000C__x0000__x0000_031-763-2002_x000C__x0000__x0000_031-763-0400_x0005__x0000__x0000_12739_x000D__x0000__x0001_½¬0® _x0000__x0011_­üÈÜÂ _x0000_µÑø»\¸ _x0000_9_x0000_2_x0000__x000D__x0000__x0000_010-4085-9292_x0014__x0000__x0000_gysports@hanmail.net_x0008__x0000__x0000_20190725_x000E__x0000__x0000_37690004641137_x0006__x0000__x0000_D00528_x0007__x0000__x0001_2_x0000_0_x0000_8_x0000_0_x0000_Æ%±¤Â
+_x0000__x0000_8131601217_x0003__x0000__x0001_@®ÀÉÐÆ_x000C__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_ _x0000_¤ÂìÓ ÎXÇX¹_x000C__x0000__x0000_061-795-2088_x0008__x0000__x0001__x0004_È|·¨°Ä³ _x0000__x0011_­ÅÜÂ_x0005__x0000__x0000_57767_x0010__x0000__x0001__x0004_È¨° _x0000__x0011_­ÅÜÂ _x0000_ÀÉÙ³8® _x0000_3_x0000_0_x0000_-_x0000_3_x0000_5_x0000__x000D__x0000__x0000_010-9434-2223_x0013__x0000__x0000_3530162@hanmail.net_x0008__x0000__x0000_20190730_x000E__x0000__x0000_37690004643437_x0006__x0000__x0000_D00529	_x0000__x0001_°Æ¬¹¤ÂìÓ Î(_x0000__x0011_­üÈ)_x0000_
+_x0000__x0000_5212100399_x0003__x0000__x0001_$Æ_x0018_ÂÔÆ_x0008__x0000__x0000_20191030_x000C__x0000__x0000_062-434-8963_x0008__x0000__x0001__x0011_­üÈ_x0011_­íÅÜÂ _x0000_½l­_x0005__x0000__x0000_61185_x0018__x0000__x0001__x0011_­üÈ _x0000_½l­ _x0000_¨Ìè²ðÅàÂ\¸ _x0000_2_x0000_9_x0000_¼8® _x0000_1_x0000_5_x0000_ _x0000_ÀÉÁÀ1_x0000_5Î_x000D__x0000__x0001_½l­+ÈiÕ´Ì!Ç_x0000_­ _x0000_´Ì!Ç©ÆÔ_x0010_È_x000D__x0000__x0000_010-4614-9599_x000F__x0000__x0000_19qkqn@daum.net_x000B__x0000__x0000_01046149599_x000D__x0000__x0001_2_x0000_6_x0000_F_x0000_W_x0000_ _x0000_©ÆÔ_x0018_ÂüÈ _x0000_ø»8ÌìÅ_x0008__x0000__x0000_20190802_x000E__x0000__x0000_37690004642837_x0006__x0000__x0000_D00530_x000B__x0000__x0001_àÂàÂ´Ì!Ç¬À _x0000_2_x0000_1_x0000___x0000_¹Ò_x0010_Ó
+_x0000__x0000_1288148960_x000B__x0000__x0001_üÈÝÂÖ¬À _x0000_àÂàÂ´Ì!Ç2_x0000_1_x0000__x0003__x0000__x0001_iÖ¹Â8Ö_x0002__x0000__x0001__x001C_ÈpÈ_x0008__x0000__x0000_20000523
+_x0000__x0000_0319453376
+_x0000__x0000_0319450458_x0005__x0000__x0000_10844_x0013__x0000__x0001_½¬0® _x0000__x000C_ÓüÈÜÂ _x0000_ÔÆq¸tº _x0000_¬_x0014_¼_x0004_Ç8® _x0000_1_x0000_2_x0000_3_x0000__x0006__x0000__x0001_àÂàÂ´Ì!Ç$ÁD¾_x0014__x0000__x0000_sinsin5980@naver.com_x0008__x0000__x0000_20190823_x000E__x0000__x0000_37690004645737_x0006__x0000__x0000_D00534
+_x0000__x0001_2_x0000_0_x0000_1_x0000_9_x0000_ _x0000_TÏ¬¹DÅ$Æ_x0008_Õ
+_x0000__x0000_0000000000	_x0000__x0000_023352551_x0005__x0000__x0000_03964_x000E__x0000__x0001__x001C_Á¸Æ _x0000_È¹ìÓl­ _x0000_ìÓ@Ç\¸ _x0000_1_x0000_2_x0000_0_x0000__x0004__x0000__x0001_U³|ÇL¾)µ_x0008__x0000__x0000_20190918_x0006__x0000__x0000_D00538_x000E__x0000__x0001__x0000_³\Õ¤ÂìÓ Î°ÀÅÅ_x0011_ÖÙ³pÈiÕ__x0000_¹Ò_x0010_Ó
+_x0000__x0000_1168210643_x0003__x0000__x0001_üÈ_x0015_Ö8Ö	_x0000__x0001_´ÆÙ³©Æl­ _x0000__x000F_¼ _x0000_$ÁXÎ_x0008__x0000__x0000_19700319	_x0000__x0000_027867761	_x0000__x0000_027867764_x0005__x0000__x0000_07345_x000E__x0000__x0001__x001C_Á¸Æ _x0000__x0001_Æñ´ìÓl­ _x0000_6_x0000_3_x0000_\¸ _x0000_4_x0000_0_x0000__x0014__x0000__x0001_7_x0000_2_x0000_3_x0000_8Ö _x0000_(_x0000_ìÅXÇÄ³Ù³,_x0000_ _x0000_|·tÇ_x0004_Õ$Æ&lt;Õ¤ÂTÑ)_x0000__x0008__x0000__x0000_20190724_x000E__x0000__x0000_37690004646337_x0006__x0000__x0000_D00539_x000C__x0000__x0001_(_x0000_üÈ)_x0000__x0004_²¬¹ÐÅ¤ÂdÅÀÉ__x0000_¹Ò_x0010_Ó
+_x0000__x0000_2018609461	_x0000__x0001_(_x0000_üÈ)_x0000__x0004_²¬¹ÐÅ¤ÂdÅÀÉ_x0002__x0000__x0001_@®%Æ_x000C__x0000__x0000_031-527-8417_x0005__x0000__x0000_12245_x0015__x0000__x0001_½¬0® _x0000_¨°ÅüÈÜÂ _x0000_½¬_x0015_¬\¸2_x0000_9_x0000_4_x0000_¼8® _x0000_3_x0000_2_x0000_-_x0000_1_x0000__x0008__x0000__x0000_20190626_x000E__x0000__x0000_37690004648637_x0006__x0000__x0000_D00541_x0007__x0000__x0001_íÂtÇ_x0004_¬ÀÉ__x0000_¹Ò_x0010_Ó_x000C__x0000__x0001_¹Ò_x0010_Ó _x0000_p¬· Á _x0000_ÇÜÂ _x0000_ñ´]¸_x000D__x0000__x0000_010-2850-8962_x0003__x0000__x0001_Æ%±¤Â_x0008__x0000__x0000_20191014_x000E__x0000__x0000_37690004647037_x0006__x0000__x0000_D00543	_x0000__x0001_Á¨ºÇè²´Ìõ¼__x0000_¹Ò_x0010_Ó_x0004__x0000__x0001_Ù³¹ÂµÑÁÀ_x0008__x0000__x0000_20191016_x000E__x0000__x0000_37690004674237_x0006__x0000__x0000_D00546_x000B__x0000__x0001_8ÁÄÉ¤ÂìÓ Î)¼ü¬ÄÖ__x0000_¹Ò_x0010_Ó_x0005__x0000__x0000_06964_x000E__x0000__x0001__x001C_Á¸Æ _x0000_Ù³Çl­ _x0000_ÁÀÄ³\¸ _x0000_2_x0000_4_x0000_2_x0000__x0008__x0000__x0000_20191023_x000E__x0000__x0000_37690004649237_x0006__x0000__x0000_D00549	_x0000__x0001_)¼ü¬ÄÖà¬Ç_x0008_Í__x0000_¹Ò_x0010_Ó
+_x0000__x0000_1318303677_x0008__x0000__x0001_xÇÌà¬Ç_x0008_Íñ´YÕP­_x0003__x0000__x0001_@®_x001C_Âl×_x000C__x0000__x0000_032-433-0464	_x0000__x0001_xÇÌ_x0011_­íÅÜÂ _x0000_¨°Ù³l­_x0005__x0000__x0000_21685_x0014__x0000__x0001_xÇÌ _x0000_¨°Ù³l­ _x0000_DÅTÅ_x0000_³\¸1_x0000_5_x0000_0_x0000_3_x0000_¼8® _x0000_4_x0000_8_x0000__x000F__x0000__x0000_gojan@ice.go.kr_x0008__x0000__x0000_20191028_x0006__x0000__x0000_D00550
+_x0000__x0001_TÏ¬¹DÅü»4Ñ¬À·__x0000_¹Ò_x0010_Ó_x0008__x0000__x0000_20191108_x000E__x0000__x0000_37690004650237_x0006__x0000__x0000_D00554	_x0000__x0001_üÈýÅ_x0008_Íñ´YÕP­__x0000_¹Ò_x0010_Ó
+_x0000__x0000_1288302804_x0003__x0000__x0001__x0015_¼	½ Á_x000B__x0000__x0000_0319120031 _x0005__x0000__x0000_10385_x0012__x0000__x0001_½¬0® _x0000_à¬ÅÜÂ _x0000_|Ç°À_x001C_Ál­ _x0000__x0015_¬ Á\¸ _x0000_2_x0000_9_x0000__x0006__x0000__x0001_üÈýÅ_x0008_Íñ´YÕP­_x0008__x0000__x0000_20191118_x0006__x0000__x0000_D00557_x000B__x0000__x0001_üÈÝÂÖ¬À _x0000_tÎxÇÜ´ÉÅtÐÉ
+_x0000__x0000_7318601539_x0003__x0000__x0001_¥Ç¬Ç_x0001_Ö_x0008__x0000__x0000_20191210_x000D__x0000__x0000_010-2600-1460_x0005__x0000__x0000_06065_x000E__x0000__x0001__x001C_Á¸Æ _x0000__x0015_¬¨°l­ _x0000_ Á¹\¸ _x0000_7_x0000_2_x0000_0_x0000__x000E__x0000__x0001_ Ç_x0000_­L¾)µ _x0000_ÀÉXÕ1_x0000_5Î _x0000_ô¼Ü´|·xÇ_x0013__x0000__x0000_paul777@hanmail.net_x0008__x0000__x0000_20200914_x0006__x0000__x0000_D00560	_x0000__x0001_üÈÝÂÖ¬À _x0000__x0014_µÀÉ8ÑÄÉ
+_x0000__x0000_6418600391_x0003__x0000__x0001__x0015_¼¼ Á_x0019__x0000__x0001_ôÎèÔ0Ñ _x0000__x000F_¼ _x0000_üÈÀ¼0®0®,_x0000_ _x0000_´ÆÙ³ _x0000__x000F_¼ _x0000_½¬0®©ÆÔ _x0000_Ä³ä¹ _x0000__x0008__x0000__x0000_20160401_x000B__x0000__x0000_02-707-3326	_x0000__x0000_027038437	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_©Æ°Àl­_x0005__x0000__x0000_04366_x0011__x0000__x0001__x001C_Á¸ÆÜÂ _x0000_Ù³Çl­ _x0000__x0000_³)¼Ù³1_x0000_5_x0000_8® _x0000_3_x0000_0_x0000__x000D__x0000__x0000_010-4722-8308_x0014__x0000__x0000_jin@digitaljin.co.kr_x0005__x0000__x0000_24016_x0003__x0000__x0001_8»=Ì_x0018_Â_x0008__x0000__x0000_20191220_x000E__x0000__x0000_37690004655437_x0017__x0000__x0001_0_x0000_1_x0000_0_x0000_-_x0000_7_x0000_4_x0000_1_x0000_4_x0000_-_x0000_1_x0000_6_x0000_7_x0000_8_x0000_ _x0000_$Ç1ÁÜ­ _x0000_(_x0000_A_x0000_/_x0000_S_x0000_)_x0000__x0006__x0000__x0000_D00563	_x0000__x0001__x0001_ÆÅÅ3_x0000__x0000_Ó0®ÀÐ__x0000_¹Ò_x0010_Ó	_x0000__x0000_023332568_x0008__x0000__x0000_20200101_x0006__x0000__x0000_D00564_x0008__x0000__x0001_ü»4Ñ¤ÂìÓ Î__x0000_¹Ò_x0010_Ó_x0005__x0000__x0001__x001C_¬xÇ¬ÀÅÅÇ
+_x0000__x0000_1013095995_x0005__x0000__x0001_ü»4Ñ¤ÂìÓ Î_x0003__x0000__x0001_à¬_x0015_È%Æ_x0008__x0000__x0000_00000000_x0008__x0000__x0001__x0004_È|·½Ä³ _x0000_à¬=Ìp­_x0005__x0000__x0000_56430_x0012__x0000__x0001__x0004_È½ _x0000_à¬=Ìp­ _x0000_à¬=ÌMÇ _x0000_ÔÆá¬5_x0000_8® _x0000_1_x0000_1_x0000__x0008__x0000__x0000_20200103_x000E__x0000__x0000_37690004654837_x0006__x0000__x0000_D00568_x0007__x0000__x0001_\Õ¤ÂìÓ Î__x0000_¹Ò_x0010_Ó
+_x0000__x0000_3031277167_x0004__x0000__x0001_\Õ¤ÂìÓ Î_x0003__x0000__x0001_iÖ+ÈôÅ_x000D__x0000__x0000_010-5103-6696_x0005__x0000__x0000_27357_x0010__x0000__x0001_©Í½ _x0000_©ÍüÈÜÂ _x0000_Ä¬+º_x0000_³\¸ _x0000_9_x0000_1_x0000_-_x0000_1_x0000__x0005__x0000__x0001_(_x0000_P­_x0004_ÖÙ³)_x0000__x0016__x0000__x0000_archihjy@hometax.go.kr_x0008__x0000__x0000_20200203_x000E__x0000__x0000_37690004658337_x0006__x0000__x0000_D00574_x0006__x0000__x0001_¤Âä¹ñÂ¤ÂìÓ Î
+_x0000__x0000_1238638685_x0003__x0000__x0001_tÇ Ìl×_x0008__x0000__x0001_Ä³Áä¹,_x0000_ _x0000__x001C_ÈpÈÅÅ_x000C__x0000__x0001__x0004_ÈÇÁÀp¬·,_x0000_ _x0000_¤ÂìÓ Î©ÆÔ_x0008__x0000__x0000_20130615
+_x0000__x0000_0314271787_x000B__x0000__x0000_05054271788_x0005__x0000__x0000_15850_x000E__x0000__x0001_½¬0® _x0000_p­ìÓÜÂ _x0000_à¬°À\¸ _x0000_1_x0000_6_x0000_6_x0000__x000F__x0000__x0001_S_x0000_K_x0000_¤¼ðÒÀÆ _x0000_1_x0000_0_x0000_4_x0000_Ù³ _x0000_5_x0000_0_x0000_6_x0000_8Ö_x000D__x0000__x0000_010-3690-1786_x0011__x0000__x0000_4271787@naver.com_x000B__x0000__x0000_07046403943_x0005__x0000__x0000_19022_x0003__x0000__x0001_àÂÙ³ÐÆ_x0008__x0000__x0000_20200220_x000E__x0000__x0000_37690004666837_x0006__x0000__x0000_D00576_x0008__x0000__x0001_1¼È¹¤ÂìÓ Î__x0000_¹Ò_x0010_Ó_x0008__x0000__x0000_20200302_x000E__x0000__x0000_37690004667437_x0006__x0000__x0000_D00578_x0008__x0000__x0001_MÖ1ÁÆ%±¤Â__x0000_¹Ò_x0010_Ó_x0006__x0000__x0001_MÖ1Á _x0000_Æ%±¤Â_x0008__x0000__x0000_20200316_x0005__x0000__x0000_32223_x0016__x0000__x0001_©Í¨° _x0000_MÖ1Áp­ _x0000_MÖ1ÁMÇ _x0000_pÈÅ\¸1_x0000_0_x0000_3_x0000_¼8® _x0000_3_x0000_5_x0000__x000E__x0000__x0000_17-2 17-5 17-6_x000E__x0000__x0000_37690004669737_x0006__x0000__x0000_D00580_x0008__x0000__x0001__x0008_®_x0001_Æ¤ÂìÓ Î__x0000_¹Ò_x0010_Ó_x0005__x0000__x0000_04005_x0010__x0000__x0001__x001C_Á¸Æ _x0000_È¹ìÓl­ _x0000_Ù³P­\¸3_x0000_8® _x0000_1_x0000_2_x0000_5_x0000__x0003__x0000__x0000_205_x0008__x0000__x0000_20200324_x000E__x0000__x0000_37690004671337_x0006__x0000__x0000_D00585_x0008__x0000__x0001_Tº_x0014_µ¬ÀtÇ¸Å__x0000_¹Ò_x0010_Ó
+_x0000__x0000_2102438564_x0005__x0000__x0001_Tº_x0014_µ¬ÀtÇ¸Å_x0003__x0000__x0001__x0015_¼ÌÕÝÂ_x000D__x0000__x0001__x001C_ÁD¾¤Â,_x0000_ _x0000_Ä³ä¹ _x0000__x000F_¼ _x0000_Áä¹ÅÅ_x0010__x0000__x0001_$ÁXÎ_x000F_¼ ÇÀÉô¼_x0018_Â,_x0000_ _x0000_8»l­,_x0000_ _x0000_0®P±Ô_x000B__x0000__x0000_01088813256	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_1ÁÙ³l­_x0005__x0000__x0000_04750_x000F__x0000__x0001__x001C_Á¸Æ _x0000_1ÁÙ³l­ _x0000_à¬°ÀÇ\¸ _x0000_2_x0000_8_x0000_4_x0000__x0018__x0000__x0001_3_x0000_5Î _x0000_3_x0000_0_x0000_1_x0000_8Ö _x0000_6_x0000_1_x0000_äÂ _x0000_(_x0000_Õù²Ù³,_x0000_ _x0000_1ÁÙ³äÀt¹Ý¹)_x0000__x0015__x0000__x0000_eg6753256@hanmail.net_x0008__x0000__x0000_20200525_x000E__x0000__x0000_37690004672037_x0006__x0000__x0000_D00587_x000B__x0000__x0001_üÈÝÂÖ¬À _x0000_°tÇ¤Â(Ó_x0000_¼¬¹
+_x0000__x0000_3658101754_x0003__x0000__x0001__x0015_¼=Ìü»_x000B__x0000__x0001_¤ÂìÓ Î _x0000_©ÆÔ _x0000_Ä³Áä¹ÅÅ_x0008__x0000__x0000_20200407_x000C__x0000__x0000_031-341-8677_x000D__x0000__x0000_031-8068-5999_x0007__x0000__x0001_½¬0®Ä³ _x0000_XÇUÆÜÂ_x0005__x0000__x0000_16011_x000C__x0000__x0001_½¬0® _x0000_XÇUÆÜÂ _x0000_­ÌÄ¬\¸ _x0000_2_x0000__x000D__x0000__x0000_010-7417-4040_x0011__x0000__x0000_cmin401@naver.com_x0008__x0000__x0000_20200602_x000E__x0000__x0000_37690004673637_x0006__x0000__x0000_D00600	_x0000__x0001_Ä³á¬_x0008_Íñ´YÕP­__x0000_¹Ò_x0010_Ó_x0003__x0000__x0001_$Çø»l×_x0003__x0000__x0001_½Ù³°À_x0002__x0000__x0001_Ç_x0000_³	_x0000__x0000_025804577_x0005__x0000__x0000_06205_x0010__x0000__x0001__x001C_Á¸Æ _x0000__x0015_¬¨°l­ _x0000_ Á¹\¸6_x0000_4_x0000_8® _x0000_3_x0000_3_x0000__x0008__x0000__x0001__x001C_Á¸ÆÄ³á¬_x0008_Íñ´YÕP­_x0008__x0000__x0000_20201015_x0006__x0000__x0000_D00602_x000C__x0000__x0001__x001C_Á¸ÆÜÂ0¼Ü´ü»4Ñ_x0011_ÖÖ__x0000_¹Ò_x0010_Ó
+_x0000__x0000_2048204832	_x0000__x0001__x001C_Á¸ÆÜÂ0¼Ü´ü»4Ñ_x0011_ÖÖ_x0003__x0000__x0001__x0015_¼¬ÇXÖ_x000D__x0000__x0000_010-4359-4949_x0004__x0000__x0001_5_x0000_0_x0000_2_x0000_8Ö_x0008__x0000__x0000_20201102_x000E__x0000__x0000_37690004675937_x0006__x0000__x0000_D00605_x000B__x0000__x0001_ÌHÅàÂHÅ_x0008_Íñ´YÕP­__x0000_¹Ò_x0010_Ó
+_x0000__x0000_3128300473_x0003__x0000__x0001_@®_x0015_È`Å_x0008__x0000__x0000_622-7063_x0005__x0000__x0000_31125_x0013__x0000__x0001_©Í¨° _x0000_ÌHÅÜÂ _x0000_Ù³¨°l­ _x0000_ÐÆ1Á2_x0000_5_x0000_8® _x0000_2_x0000_1_x0000__x0008__x0000__x0001_ÌHÅàÂHÅ_x0008_Íñ´YÕP­_x0008__x0000__x0000_20201116_x0006__x0000__x0000_D00608_x000E__x0000__x0001_(_x0000_üÈ)_x0000_ _x0000__x0018_±¼ÐÆ¤ÂìÓ Î(_x0000_T_x0000_S_x0000_)_x0000__x0008__x0000__x0000_20210107_x0005__x0000__x0000_38661_x000E__x0000__x0001_½¬½ _x0000_½¬°ÀÜÂ _x0000_½¬°À\¸ _x0000_2_x0000_4_x0000_3_x0000__x000B__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_2_x0000_4_x0000__x000E__x0000__x0000_37690004676537_x0006__x0000__x0000_D00609	_x0000__x0001__x0008_®_x0001_Æ¤ÂìÓ Î(_x0000_T_x0000_S_x0000_)_x0000_$_x0000__x0001_2_x0000_4_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_4_x0000_0_x0000_ _x0000_/_x0000__x0001_ÆÅÅ¬ÀÐÆ _x0000_Æ­Ì(_x0000_¥Ç0® _x0000_ø»p¬·,_x0000_ _x0000__x0018_Â_x0008_® _x0000_½tÇÕ)_x0000__x000E__x0000__x0000_37690004677137_x0006__x0000__x0000_D00610	_x0000__x0001_XÕD¾¤ÂìÓ Î(_x0000_T_x0000_S_x0000_)_x0000__x0016__x0000__x0000_daegu-daejin@naver.com_x000F__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_4_x0000_0_x0000_+_x0000_5_x0000_0_x0000__x000E__x0000__x0000_37690004678837_x0006__x0000__x0000_D00611	_x0000__x0001_1¼È¹¤ÂìÓ Î(_x0000_T_x0000_S_x0000_)_x0000__x0005__x0000__x0000_04011_x000F__x0000__x0001__x001C_Á¸Æ _x0000_È¹ìÓl­ _x0000_Ù³P­\¸9_x0000_8® _x0000_9_x0000_5_x0000__x0010__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_7_x0000_0_x0000_+_x0000_1_x0000_8_x0000_5_x0000__x000E__x0000__x0000_37690004679437_x0006__x0000__x0000_D00612_x000D__x0000__x0001_¼À1Á¤ÂìÓ Î(_x0000_8»½¬)_x0000_(_x0000_T_x0000_S_x0000_)_x0000__x0005__x0000__x0000_36956_x000E__x0000__x0001_½¬½ _x0000_8»½¬ÜÂ _x0000_¨º_x0004_È\¸ _x0000_1_x0000_4_x0000_6_x0000_V_x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_0_x0000_+_x0000_6_x0000_ _x0000_/_x0000_ _x0000_2_x0000_5_x0000_S_x0000_S_x0000_ _x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_0_x0000_ _x0000_/_x0000_ _x0000_ _x0000_2_x0000_4_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_5_x0000_ _x0000_/_x0000_ _x0000_2_x0000_4_x0000_S_x0000_S_x0000__x0018_ÂüÈìÅàÂ _x0000_5_x0000_ _x0000_/_x0000_ _x0000_2_x0000_3_x0000_F_x0000_W_x0000_ _x0000__x0018_ÂüÈ _x0000_ìÅàÂ _x0000_1_x0000_0_x0000_ _x0000_/_x0000_ _x0000_2_x0000_3_x0000_S_x0000_S_x0000_ _x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_0_x0000__x000E__x0000__x0000_37690004680437_x0006__x0000__x0000_D00614_x0008__x0000__x0001__x0001_ÆÅÅ4_x0000__x0000_ÓÇXÇä¹¥Ç_x000B__x0000__x0000_02-335-2551_x0008__x0000__x0000_20210115_x0006__x0000__x0000_D00616_x0005__x0000__x0001_8Á_x0001_Æ¤ÂìÓ Î
+_x0000__x0000_8055100483_x0005__x0000__x0001_¤ÂìÓ ÎXÇX¹_x0008__x0000__x0000_20210125_x000D__x0000__x0000_070-8808-8799_x0017__x0000__x0000_yonexsejinspo@naver.com_x000E__x0000__x0000_37690004683337_x0006__x0000__x0000_D00620_x000D__x0000__x0001_üÈÝÂÖ¬À _x0000_8ÁÄÉ¤ÂìÓ Î__x0000_è²Å³
+_x0000__x0001_X_x0000_7_x0000_ _x0000_è²Å³¨ºx³ _x0000_TÏÜ´_x0008__x0000__x0000_20210226_x000E__x0000__x0000_37690004684037_x0006__x0000__x0000_D00621_x000E__x0000__x0001_¬À$Á´Ì!Ç_x0000_­(_x0000__x000C_Õ_x0008_¸tÇ(Æ)_x0000___x0000_¹Ò_x0010_Ó
+_x0000__x0000_7820601928_x0004__x0000__x0001__x000C_Õ_x0008_¸tÇ(Æ_x0003__x0000__x0001_\ÍÑ¼ÅÆ_x0008__x0000__x0001_0¼Ü´ü»4ÑtÐý·´Æ_x0001_Æ_x0008__x0000__x0000_20210305_x000D__x0000__x0000_010-4343-5610_x0005__x0000__x0000_31234_x0017__x0000__x0001_©Í¨° _x0000_ÌHÅÜÂ _x0000_Ù³¨°l­ _x0000_©ºÌMÇ _x0000_1Á¨°\¸ _x0000_3_x0000_9_x0000_-_x0000_1_x0000__x0010__x0000__x0000_cbw007@naver.com_x000E__x0000__x0000_37690004685637_x0006__x0000__x0000_D00626_x000B__x0000__x0001__x0018_ÂÐÆ¥ÇHÅà¬ñ´YÕP­__x0000_¹Ò_x0010_Ó
+_x0000__x0000_1358302549_x0006__x0000__x0001_¥ÇHÅà¬ñ´YÕP­_x0003__x0000__x0001_ ÇtÕ·_x0004__x0000__x0001_½Ù³°ÀÅÅ_x0008__x0000__x0000_20210324_x000C__x0000__x0000_031-250-2901_x0007__x0000__x0001_½¬0®Ä³ _x0000__x0018_ÂÐÆÜÂ_x0005__x0000__x0000_16316_x0015__x0000__x0001_½¬0® _x0000__x0018_ÂÐÆÜÂ _x0000_¥ÇHÅl­ _x0000__x0000_³ÉÓ\¸5_x0000_2_x0000_¼8® _x0000_1_x0000_2_x0000__x0013__x0000__x0000_jangan5955@korea.kr_x000E__x0000__x0000_37690004686237_x0006__x0000__x0000_D00628_x0007__x0000__x0001_Æ%±¤Â _x0000__x0018_ÂÐÆ_x0010_È
+_x0000__x0000_4401101673_x0003__x0000__x0001__x0015_¼°_x0004_Ö_x000B__x0000__x0001_¤ÂìÓ Î©Æ _x0000_XÇX¹,_x0000_ _x0000_©ÆÔ_x0008__x0000__x0000_20210407_x000C__x0000__x0000_031-216-4009_x0005__x0000__x0000_16540_x0010__x0000__x0001_½¬0® _x0000__x0018_ÂÐÆÜÂ _x0000__x0001_ÆµÑl­ _x0000_ä¹ÐÆ\¸ _x0000_3_x0000__x000D__x0000__x0000_010-2888-3600_x0011__x0000__x0000_yonexsw@naver.com_x000E__x0000__x0000_37690004687937_x0006__x0000__x0000_D00631_x000C__x0000__x0001__x0011_É·l­0¼Ü´ü»4Ñ_x0011_ÖÖ__x0000_¹Ò_x0010_Ó_x0008__x0000__x0000_20210510_x0006__x0000__x0000_D00632_x0008__x0000__x0001_©ÆÔ¬ÀÅÅ½ _x0000_A_x0000_S_x0000__x0003__x0000__x0001_@® ÌÅÆ_x000B__x0000__x0000_02-335-8077_x0008__x0000__x0000_20210601_x0006__x0000__x0000_D00638_x000D__x0000__x0001_p¬1Á¤ÂìÓ Î(_x0000_HÅÙ³)_x0000_(_x0000_T_x0000_S_x0000_)_x0000__x0008__x0000__x0000_20210622_x000F__x0000__x0001_½¬½ _x0000_HÅÙ³ÜÂ _x0000_½¬½_x0000_³\¸ _x0000_4_x0000_1_x0000_8_x0000__x0018__x0000__x0001_(_x0000_%ÆÙ³,_x0000_ _x0000_LÑÈ¹_x0004_Õ|·Ç)_x0000_Æ%±¤Â _x0000_p¬1Á¤ÂìÓ Î(_x0000_HÅÙ³)_x0000__x0012__x0000__x0000_klcjjh@lycos.co.kr_x000E__x0000__x0000_37690004688537_x0006__x0000__x0000_D00640_x0005__x0000__x0001__x0014_¼x¹¤ÂìÓ Î
+_x0000__x0000_1313599978_x0006__x0000__x0001__x0014_¼x¹ _x0000_¤ÂìÓ Î_x0003__x0000__x0001_tÇ¬Ç_x0001_Æ_x0007__x0000__x0001_Áä¹ÅÅ,_x0000_Ä³ä¹ÅÅ_x0008__x0000__x0000_20210715_x000C__x0000__x0000_032-466-1365_x0005__x0000__x0000_21543_x000E__x0000__x0001_xÇÌ _x0000_¨°Ù³l­ _x0000_1¼¼\¸ _x0000_1_x0000_3_x0000_9_x0000_
+_x0000__x0001_Æ%±¤Â _x0000__x0014_¼x¹ _x0000_¤ÂìÓ Î_x000D__x0000__x0000_010-8872-9764_x0017__x0000__x0000_hangang6528@hanmail.net_x000E__x0000__x0000_37690004689137_x0006__x0000__x0000_D00641_x0004__x0000__x0001_$±¼·Ü´
+_x0000__x0000_1292781688_x0003__x0000__x0001_@®e×-Á_x0013__x0000__x0001__x0004_ÈÇÁÀp¬·ÅÅ,_x0000_ _x0000_¤ÂìÓ Î©ÆÔ,_x0000_ _x0000_ìÕ¤Â©ÆÔ_x0008__x0000__x0000_20210730_x000C__x0000__x0000_031-742-4404_x0005__x0000__x0000_13134_x0013__x0000__x0001_½¬0® _x0000_1Á¨°ÜÂ _x0000__x0018_Â_x0015_Èl­ _x0000_°À1Á_x0000_³\¸ _x0000_5_x0000_8_x0000_5_x0000__x000D__x0000__x0000_010-9034-0945_x0014__x0000__x0000_samulnori4@naver.com_x000E__x0000__x0000_37690004690137_x0006__x0000__x0000_D00643_x000E__x0000__x0001_Æ%±¤Â _x0000_ÐÆüÈ_x0010_È(_x0000_J_x0000_S_x0000_¤ÂìÓ Î)_x0000_
+_x0000__x0000_3181501656_x0003__x0000__x0001_@®¬Ç1Á_x0012__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000__x0004_ÈÇÁÀp¬·(_x0000_¤ÂìÓ Î©ÆÔ)_x0000__x0008__x0000__x0000_20210810_x000C__x0000__x0000_033-764-1409_x0007__x0000__x0001__x0015_¬ÐÆÄ³ _x0000_ÐÆüÈÜÂ_x0005__x0000__x0000_26431_x000F__x0000__x0001__x0015_¬ÐÆ _x0000_ÐÆüÈÜÂ _x0000_ÐÆ|Ç\¸ _x0000_5_x0000_5_x0000_-_x0000_1_x0000__x0006__x0000__x0001_1_x0000_5Î(_x0000_ÐÆÙ³)_x0000__x000D__x0000__x0000_010-9799-0020_x0015__x0000__x0000_yonex_wonju@naver.com_x000E__x0000__x0000_37690004691837_x0006__x0000__x0000_D00649
+_x0000__x0001_(_x0000_üÈ)_x0000_È¹_x000C_ÕTÏ|Ó_x0008_¸tÇXÁ
+_x0000__x0000_1058813322_x0003__x0000__x0001__x0015_¼_x001C_Ö$Ç_x0011__x0000__x0001__x001C_ÈpÈ,_x0000_ _x0000_Ä³Áä¹,_x0000_ _x0000_Ä³ä¹ _x0000__x000F_¼ _x0000_Áä¹ÅÅ	_x0000__x0001_,Á Ç_x0004_Õ°¹¸Ò,_x0000_ _x0000_XÇX¹_x0008__x0000__x0000_20210901_x000D__x0000__x0000_010-4811-6484	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x0008_®Ìl­_x0005__x0000__x0000_08589_x0014__x0000__x0001__x001C_Á¸Æ _x0000__x0008_®Ìl­ _x0000__x0000_¬°À_x0014_µÀÉ8Ñ1_x0000_\¸ _x0000_7_x0000_5_x0000_-_x0000_2_x0000_4_x0000__x000B__x0000__x0001_1_x0000_0_x0000_5Î,_x0000_1_x0000_1_x0000_5Î,_x0000_1_x0000_2_x0000_5Î_x0013__x0000__x0000_account@marpple.com_x0006__x0000__x0000_D00654_x0007__x0000__x0001__x0004_Ö¥Ç_x0010_Óä¹__x0000_©ºìÓ_x0008__x0000__x0000_20211103_x0006__x0000__x0000_D00657_x0008__x0000__x0001_(_x0000_üÈ)_x0000_ìÎÐÌ×´Å\¸
+_x0000__x0000_1448135400
+_x0000__x0001_üÈÝÂÖ¬À _x0000_ìÎÐÌ×´Å\¸_x0003__x0000__x0001_Å_x0000_ÉÜ­_x0016__x0000__x0001__x0015_Èô¼_x001C_ÁD¾¤Â,_x0000_ _x0000_Ä³ä¹ _x0000__x000F_¼ _x0000_Áä¹ÅÅ,_x0000_ _x0000__x0015_Èô¼µÑàÂÅÅ!_x0000__x0001__x0004_ÈÇÁÀp¬·ÅÅ,_x0000_ _x0000__x0015_Èô¼Ì¬¹ÜÂ¤Â\Ñ,_x0000_ _x0000__x0015_Èô¼_x001C_ÁD¾¤ÂÅÅ,_x0000_ _x0000_(Æ|·xÇ_x0015_Èô¼_x001C_Èõ¬ÅÅ_x000D__x0000__x0000_010-4848-6263_x0005__x0000__x0000_13487_x0016__x0000__x0001_½¬0® _x0000_1Á¨°ÜÂ _x0000_½ù²l­ _x0000__x0010_ÓP­\¸2_x0000_2_x0000_8_x0000_¼8® _x0000_1_x0000_5_x0000__x000C__x0000__x0001_3_x0000_Ù³ _x0000_1_x0000_0_x0000_5Î _x0000_1_x0000_0_x0000_0_x0000_1_x0000_8Ö_x0017__x0000__x0000_contact@culturehero.net_x0011__x0000__x0000_YONEX-2021-009852_x0008__x0000__x0000_20211119_x000E__x0000__x0000_37690004694737_x0006__x0000__x0000_D00658_x0007__x0000__x0001_Æ%±¤Â _x0000__x0015_¬¨°_x0010_È
+_x0000__x0000_2440202373_x0003__x0000__x0001_tÇ@ÇüÈ_x0018__x0000__x0001_´ÆÙ³ _x0000__x000F_¼ _x0000_½¬0®©ÆÔ _x0000_Áä¹ÅÅ,_x0000_ _x0000__x0004_ÈÇÁÀp¬· _x0000_Áä¹ÅÅ_x0008__x0000__x0000_20211201_x000C__x0000__x0000_02-6498-9300_x0005__x0000__x0000_06777_x000D__x0000__x0001__x001C_Á¸Æ _x0000__x001C_Á_x0008_Íl­ _x0000_¸Å¨°8® _x0000_4_x0000_5_x0000__x000D__x0000__x0000_010-2416-3327_x0016__x0000__x0000_kidsrun005@hanmail.net_x000E__x0000__x0000_37690004695337_x0006__x0000__x0000_D00664	_x0000__x0001_o¸p³_x000C_¸ÈÐ_x0018_»ø»__x0000_¹Ò_x0010_Ó
+_x0000__x0000_2148779183_x0008__x0000__x0001_o¸p³_x000C_¸ÈÐ _x0000_(_x0000_üÈ)_x0000__x0003__x0000__x0001_@®_x0004_Ö_x0018_Â_x0007__x0000__x0001__x001C_ÁD¾¤Â,_x0000_ _x0000_Áä¹_x0018__x0000__x0001__x0015_Èô¼µÑàÂ0®0®_x000F_¼¥ÇD¾_x000C_¸ÈÐ,_x0000_ _x0000__x0010_Óä¹,_x0000_ _x0000_ ÇÀÉô¼_x0018_Â_x001C_ÁD¾¤Â_x0008__x0000__x0000_20220128_x000D__x0000__x0000_010-3085-5465_x0005__x0000__x0000_14042_x0011__x0000__x0001_½¬0® _x0000_HÅÅÜÂ _x0000_Ù³HÅl­ _x0000__x0004_È_x000C_Ó\¸ _x0000_8_x0000_8_x0000__x0002__x0000__x0001_8_x0000_5Î_x0016__x0000__x0000_ahnhyeokbeom@lotte.net_x0011__x0000__x0000_YONEX-2022-000914_x000E__x0000__x0000_37690004697637_x0017__x0000__x0001_ô²ô¼_x0008_®aÅ _x0000_ø»$Á_x0015_È,_x0000_ _x0000_uÇÔÆ _x0000_1_x0000_0_x0000_0_x0000_%_x0000_ _x0000__x0018_Â_x0008_® _x0000_ÄÉÕ_x0006__x0000__x0000_D00670_x000C__x0000__x0001_(_x0000_üÈ)_x0000_DÅüÈ_x0008_¸ìÓ Î(_x0000_T_x0000_S_x0000_)_x0000__x0008__x0000__x0000_20220317_x0015__x0000__x0000_luckright@hanmail.net_x000E__x0000__x0000_37690004698237_x0006__x0000__x0000_D00672_x000F__x0000__x0001_2_x0000_0_x0000_2_x0000_2_x0000_ _x0000_TÏ¬¹DÅ$Æ_x0008_Õ&amp;_x0000_È¹¤Â0ÑÉ_x0008__x0000__x0000_20220322_x0006__x0000__x0000_D00676_x0007__x0000__x0001__x0004_Ö¥Ç_x0010_Óä¹__x0000__x0000_³_x0004_È_x0008__x0000__x0000_20220509_x0008__x0000__x0001__x0000_³_x0004_È_x0011_­íÅÜÂ _x0000__x0011_Él­_x0006__x0000__x0000_D00677_x000C__x0000__x0001_1Á½l­0¼Ü´ü»4Ñ_x0011_ÖÖ__x0000_¹Ò_x0010_Ó_x0008__x0000__x0000_20220518_x0006__x0000__x0000_D00679_x0007__x0000__x0001__x0004_Ö¥Ç_x0010_Óä¹__x0000_¸Æ°À_x0008__x0000__x0000_20220524_x0006__x0000__x0000_D00680_x0007__x0000__x0001__x0004_Ö¥Ç_x0010_Óä¹__x0000__x001C_Á¸Æ_x0008__x0000__x0000_20220622_x0011__x0000__x0000_YONEX-2022-005692_x0006__x0000__x0000_D00685
+_x0000__x0001_üÈÝÂÖ¬À _x0000_(Æ¬¹¤ÂìÓ Î
+_x0000__x0000_7448101466_x0008__x0000__x0001_üÈÝÂÖ¬À _x0000_ôÎ_x0014_¼xÇ_x0007__x0000__x0001_@®ÁÀ¼,_x0000_8»_x001C_Á_x0004_Ö_x0008__x0000__x0001__x001C_ÁD¾¤ÂÅÅ,_x0000__x001C_ÈpÈÅÅ	_x0000__x0001_¤ÂìÓ ÎXÇX¹,_x0000_0®P±Ô_x0008__x0000__x0000_20220823_x000C__x0000__x0000_052-251-4982_x0008__x0000__x0001_¸Æ°À_x0011_­íÅÜÂ _x0000_½l­_x0005__x0000__x0000_44215_x000D__x0000__x0001_¸Æ°À _x0000_½l­ _x0000_}Å_x0018_Â4_x0000_8® _x0000_2_x0000_0_x0000__x000C__x0000__x0001_(Æ¬¹¤ÂìÓ Î _x0000_0¼Ü´ü»4Ñ&lt;Á0Ñ_x000D__x0000__x0000_010-3857-5279_x0014__x0000__x0000_combine928@gmail.com_x000B__x0000__x0000_01038388951_x000E__x0000__x0000_37690004699937_x0006__x0000__x0000_D00686_x0008__x0000__x0001_üÈÝÂÖ¬À _x0000_4»àÂ¬À
+_x0000__x0000_2118879575_x0003__x0000__x0001_\Õ8»|Ç_x0008__x0000__x0001__x001C_ÁD¾¤Â _x0000_Ä³Áä¹ÅÅ_x0006__x0000__x0001__x0004_ÈÇÁÀp¬·ÅÅ_x0008__x0000__x0000_20120625_x000D__x0000__x0000_010-9500-6432_x0005__x0000__x0000_06017_x0011__x0000__x0001__x001C_Á¸Æ _x0000__x0015_¬¨°l­ _x0000_¸ÅüÈ\¸1_x0000_7_x0000_4_x0000_8® _x0000_3_x0000_0_x0000__x000F__x0000__x0001_àÂ¬ÀÙ³,_x0000_ _x0000_\¸H¾+ºÔ_x0000_­ÀÉXÕ _x0000_1_x0000_5Î_x0015__x0000__x0000_haejun.kim@musinsa.co_x0003__x0000__x0001_@®tÕ_x0000_É_x0006__x0000__x0000_D00689_x000D__x0000__x0001_¨°ÅüÈÜÂ0¼Ü´ü»4Ñ_x0011_ÖÖ__x0000_¹Ò_x0010_Ó_x0005__x0000__x0000_12240_x0011__x0000__x0001_½¬0® _x0000_¨°ÅüÈÜÂ _x0000__x001D_ÁäÂ\¸ _x0000_6_x0000_2_x0000_4_x0000_-_x0000_3_x0000__x0003__x0000__x0001__x0008_®á¬Ù³_x0008__x0000__x0000_20220913_x0006__x0000__x0000_D00690_x000C__x0000__x0001_Æ%±¤Â_x0015_¬Ù³_x0010_È _x0000_M_x0000_Z_x0000_¤ÂìÓ Î
+_x0000__x0000_2270909327_x0003__x0000__x0001__x0004_È_x001C_Ö_x0019_Â_x0008__x0000__x0000_20220916_x000D__x0000__x0000_010-7979-7991	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x0015_¬Ù³l­_x0005__x0000__x0000_05362_x0010__x0000__x0001__x001C_Á¸Æ _x0000__x0015_¬Ù³l­ _x0000_Ì8Ö_x0000_³\¸ _x0000_1_x0000_1_x0000_6_x0000_2_x0000__x0011__x0000__x0001_T´_x000C_ÍÙ³,_x0000_8ÁÅ­ÌÈ¹è¸DÅ_x000C_Ó¸Ò _x0000_1_x0000_0_x0000_9_x0000_8Ö_x0016__x0000__x0000_hyesuk7979@hanmail.net_x000E__x0000__x0000_37690004702737_x0006__x0000__x0000_D00692_x000E__x0000__x0001_2_x0000_0_x0000_2_x0000_2_x0000_ _x0000_LÑÈ²</v>
+          </cell>
+          <cell r="R34" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="S34" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="T34" t="e">
+            <v>#N/A</v>
           </cell>
           <cell r="U34" t="str">
             <v/>
@@ -4290,8 +4661,8 @@
           <cell r="Y34" t="str">
             <v/>
           </cell>
-          <cell r="Z34" t="str">
-            <v>062-371-7460</v>
+          <cell r="Z34" t="e">
+            <v>#N/A</v>
           </cell>
           <cell r="AA34" t="str">
             <v>N</v>
@@ -4299,8 +4670,8 @@
           <cell r="AB34" t="str">
             <v>Y</v>
           </cell>
-          <cell r="AC34" t="str">
-            <v>C등급</v>
+          <cell r="AC34" t="e">
+            <v>#N/A</v>
           </cell>
           <cell r="AD34" t="str">
             <v>23013</v>
@@ -4310,11 +4681,77 @@
           </cell>
         </row>
         <row r="35">
-          <cell r="B35" t="str">
-            <v>D00081</v>
+          <cell r="B35" t="e">
+            <v>#N/A</v>
           </cell>
           <cell r="C35" t="str">
-            <v>서대문요넥스</v>
+            <v>Ì¹Å\¸1_x0000_8® _x0000_3_x0000__x0008__x0000__x0001_ÀÉ5Î _x0000_(_x0000_ÁÀÄ³Ù³)_x0000__x000D__x0000__x0000_010-2942-3235_x0019__x0000__x0000_sejinsports2018@naver.com_x0017__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000_ _x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_9_x0000_3_x0000_-_x0000_&gt;_x0000_5_x0000_0_x0000_ _x0000_&lt;Ç\¸ _x0000_pÈ_x0015_È_x000E__x0000__x0000_37690004480837_x001A__x0000__x0001_0_x0000_1_x0000_0_x0000_ _x0000_2_x0000_7_x0000_0_x0000_5_x0000_ _x0000_3_x0000_2_x0000_3_x0000_4_x0000_ _x0000_(_x0000_ä¹¥Ç _x0000_xÆ _x0000_A_x0000_S_x0000_ô²ù²Ç)_x0000__x0006__x0000__x0000_D00089_x0006__x0000__x0001_Á_x0008_Í0¼Ü´ü»4Ñ
+_x0000__x0000_2270299081_x0003__x0000__x0001__x0015_È¬ÇÈÖ_x000C__x0000__x0000_033-638-0024
+_x0000__x0000_0336382400_x0007__x0000__x0001__x0015_¬ÐÆÄ³ _x0000_Á_x0008_ÍÜÂ_x0006__x0000__x0000_217803_x000E__x0000__x0001__x0015_¬ÐÆÄ³ _x0000_Á_x0008_ÍÜÂ _x0000_P­Ù³\¸ _x0000_3_x0000_9_x0000__x000D__x0000__x0000_010-3297-3133_x0019__x0000__x0000_yubgijung1257@hanmail.net_x000E__x0000__x0000_37690004481437_x0006__x0000__x0000_D00090_x000B__x0000__x0001_üÈÝÂÖ¬À _x0000_¤Âä¹lÂ¤ÂìÓ Î
+_x0000__x0000_8558703276_x0006__x0000__x0001_¤Âä¹lÂ¤ÂìÓ Î_x0003__x0000__x0001_$ÇÜ­ø»_x0008__x0000__x0000_20070917_x000B__x0000__x0000_01087511199_x0007__x0000__x0001_½¬0®Ä³ _x0000_HÅ°ÀÜÂ_x0005__x0000__x0000_15497_x0012__x0000__x0001_½¬0® _x0000_HÅ°ÀÜÂ _x0000_ÁÀ]¸l­ _x0000_Ì8»4_x0000_8® _x0000_1_x0000_7_x0000__x001A__x0000__x0001_1_x0000_5Î1_x0000_5_x0000_1_x0000_9_x0000_-_x0000_1_x0000_3_x0000_ _x0000_ _x0000_1_x0000_5Î _x0000_ _x0000_¤Âä¹lÂ¤ÂìÓ Î _x0000_&lt;»X¹&lt;Á0Ñ_x000D__x0000__x0000_010-5471-3330_x0013__x0000__x0000_smash-123@naver.com_x000B__x0000__x0000_01054713330_x000E__x0000__x0000_37690004483737_x0008__x0000__x0001_!Ç1Á_x0010_È&amp;_x0000_1_x0000_0_x0000_0_x0000_%_x0000__x0006__x0000__x0000_D00096_x0005__x0000__x0001_¤ÂìÓ ÎE¼lÐ
+_x0000__x0000_1272092161_x0003__x0000__x0001_@®ÄÉÉÓ_x0004__x0000__x0001_´Ì!Ç©ÆÔ_x0008__x0000__x0000_20070503_x000C__x0000__x0000_031-535-1244
+_x0000__x0000_0315352245_x0007__x0000__x0001_½¬0®Ä³ _x0000_ìÓÌÜÂ_x0006__x0000__x0000_487050_x0018__x0000__x0001_½¬0®Ä³ _x0000_ìÓÌÜÂ _x0000_p­´°tº _x0000_8Öm­\¸ _x0000_1_x0000_6_x0000_9_x0000_6_x0000_._x0000_ _x0000_2_x0000_5Î_x000D__x0000__x0000_010-6354-5471_x0011__x0000__x0000_kjp31@hanmail.net_x000E__x0000__x0000_37690004487237_x0006__x0000__x0000_D00097_x0005__x0000__x0001_¹Â¬¹¤ÂìÓ Î
+_x0000__x0000_2011081473_x0003__x0000__x0001_à¬Ñ¼°Æ_x0008__x0000__x0000_20071221_x000C__x0000__x0000_02-2279-0779
+_x0000__x0000_0222780778_x0005__x0000__x0000_04563_x001E__x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x0011_Él­ _x0000_­ÌÄ¬Ì\¸ _x0000_2_x0000_4_x0000_6_x0000_ _x0000_ _x0000_(_x0000_)¼°ÀÙ³,_x0000_ _x0000_ÉÓTÖÜÂ¥Ç)_x0000__x0016__x0000__x0001_1_x0000_,_x0000_2_x0000_,_x0000_3_x0000_5Î _x0000_ä²-_x0000_1_x0000_0_x0000_2_x0000_(_x0000_)¼°ÀÙ³,_x0000_ÉÓTÖÜÂ¥Ç)_x0000__x000D__x0000__x0000_010-3284-7383_x0019__x0000__x0000_victorysports@hanmail.net_x000E__x0000__x0000_37690004488937_x0006__x0000__x0000_D00101_x0005__x0000__x0001_DÅ°À¤ÂìÓ Î
+_x0000__x0000_3122872982_x0003__x0000__x0001_\Í+È¼¹_x000C__x0000__x0001_Ä³ä¹_x000F_¼ÁÀÔ_x0011_É_x001C_¬ÅÅ,_x0000_Áä¹ÅÅ_x0008__x0000__x0000_20110701_x000C__x0000__x0000_041-532-8381
+_x0000__x0000_0415328382_x0008__x0000__x0001_©Í­Ì¨°Ä³ _x0000_DÅ°ÀÜÂ_x0006__x0000__x0000_336050_x0010__x0000__x0001_©Í­Ì¨°Ä³ _x0000_DÅ°ÀÜÂ _x0000_ÜÂü»\¸ _x0000_2_x0000_5_x0000_1_x0000__x000D__x0000__x0000_010-4946-8385_x0013__x0000__x0000_judocjl@hanmail.net_x000E__x0000__x0000_37690004490537_x0006__x0000__x0000_D00109_x0008__x0000__x0001__x0001_Æ¤ÂìÓ Î(_x0000_¨°ÐÆ)_x0000_
+_x0000__x0000_1095289131_x0003__x0000__x0001_tÇ_x0015_ÈÌ_x0008__x0000__x0000_20071119_x000C__x0000__x0000_063-632-4154
+_x0000__x0000_0636324156_x0005__x0000__x0000_55703_x0015__x0000__x0001__x0004_È|·½Ä³ _x0000_¨°ÐÆÜÂ _x0000_¬Àä¹tº _x0000__x0000_³¬À\¸ _x0000_1_x0000_2_x0000_8_x0000_3_x0000__x0004__x0000__x0001__x0001_Æ¤ÂìÓ Î_x000D__x0000__x0000_010-4594-0634_x0013__x0000__x0000_jclee8734@naver.com_x000E__x0000__x0000_37690004497037_x0006__x0000__x0000_D00110_x0007__x0000__x0001_Æ%±¤Â _x0000_TÖ_x001C_Â_x0010_È
+_x0000__x0000_4080577085_x0003__x0000__x0001__x0004_È+º_x0019_Â_x0008__x0000__x0000_20071102_x000C__x0000__x0000_061-375-6647_x0008__x0000__x0001__x0004_È|·¨°Ä³ _x0000_TÖ_x001C_Âp­_x0006__x0000__x0000_519809_x0014__x0000__x0001__x0004_È|·¨°Ä³ _x0000_TÖ_x001C_Âp­ _x0000__x0011_­U³\¸ _x0000_1_x0000_4_x0000_0_x0000_ _x0000_ _x0000_1_x0000_5Î_x000D__x0000__x0000_010-6632-5893_x0012__x0000__x0000_ms-jon@hanmeil.net_x000E__x0000__x0000_37690004498637_x0006__x0000__x0000_D00111_x000C__x0000__x0001_,Æ¼¹=Õ+ÈiÕ¤ÂìÓ Î(_x0000_©ºìÓ)_x0000_
+_x0000__x0000_4111469486_x0003__x0000__x0001_@®=Ì©Æ_x000C__x0000__x0001_´ÆÙ³©ÆÔ,_x0000_ñ´°Àl­,_x0000_0®P±Ô_x0008__x0000__x0000_20070320_x000C__x0000__x0000_061-242-1032
+_x0000__x0000_0612443032_x0008__x0000__x0001__x0004_È|·¨°Ä³ _x0000_©ºìÓÜÂ_x0005__x0000__x0000_58726_x0010__x0000__x0001__x0004_È¨° _x0000_©ºìÓÜÂ _x0000_(Ì¼_x001D_Á8® _x0000_4_x0000_1_x0000_-_x0000_1_x0000__x0002__x0000__x0001_1_x0000_5Î_x000D__x0000__x0000_010-9243-4285_x0010__x0000__x0000_eyebono@daum.net_x000E__x0000__x0000_37690004499237_x0006__x0000__x0000_D00116_x000F__x0000__x0001_Æ%±¤ÂÈ¹°À_x0000_³¬¹_x0010_È(_x0000_ü»4Ñ¤ÂìÓ Î)_x0000_
+_x0000__x0000_6080288027_x0003__x0000__x0001_ Ç_x0001_Æ_x0019_Â_x0008__x0000__x0001_¤ÂìÓ Î©ÆÔ_x000F_¼XÇX¹_x000C__x0000__x0000_055-222-5431
+_x0000__x0000_0552225432_x0008__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_=ÌÐÆÜÂ_x0006__x0000__x0000_631852_x0018__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_=ÌÐÆÜÂ _x0000_È¹°ÀiÕìÓl­ _x0000_©ÆÈ¹\¸ _x0000_7_x0000_6_x0000_ _x0000_üÈÝÐ_x000D__x0000__x0000_010-3707-6245_x0016__x0000__x0000_dudtjs6245@hanmail.net_x000E__x0000__x0000_37690004504337_x0006__x0000__x0000_D00120_x0006__x0000__x0001_Æ%±¤Â­ÌüÈ_x0010_È
+_x0000__x0000_3170385854_x0003__x0000__x0001_\Í°Æ1Á_x000B__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_XÇX¹,_x0000__x0018_Ât¬_x0008__x0000__x0000_20110729_x000C__x0000__x0000_043-222-3040
+_x0000__x0000_0432245050_x0008__x0000__x0001_©Í­Ì½Ä³ _x0000_­ÌüÈÜÂ_x0006__x0000__x0000_361842_x0012__x0000__x0001_©Í½ _x0000_­ÌüÈÜÂ _x0000_ÁÀù²l­ _x0000_8Öø»\¸ _x0000_2_x0000_0_x0000_6_x0000__x0005__x0000__x0001_1_x0000_5Î _x0000_È!Î_x000D__x0000__x0000_010-5468-3319_x0015__x0000__x0000_wsung3525@hanmail.net_x0008__x0000__x0000_20080429_x000E__x0000__x0000_37690004507237_x0006__x0000__x0000_D00121_x000D__x0000__x0001_Æ%±¤ÂìÓmÕ_x0010_È(_x0000_XÕtÇlÐ¬¹´Å)_x0000_
+_x0000__x0000_5061736246_x0003__x0000__x0001__x0015_È@Ç_x0001_Æ_x0008__x0000__x0000_20090227_x000C__x0000__x0000_054-283-5234
+_x0000__x0000_0542835231_x0008__x0000__x0001_½¬ÁÀ½Ä³ _x0000_ìÓmÕÜÂ_x0006__x0000__x0000_790822_x0012__x0000__x0001_½¬½ _x0000_ìÓmÕÜÂ _x0000_¨°l­ _x0000__x0000_³Ä³Ù³ _x0000_8_x0000_6_x0000_-_x0000_2_x0000__x000D__x0000__x0000_010-4133-7770_x0014__x0000__x0000_minton1125@naver.com_x0008__x0000__x0000_20081105_x000E__x0000__x0000_37690004508937_x0006__x0000__x0000_D00122_x0005__x0000__x0001_°Æ¬¹¤ÂìÓ Î
+_x0000__x0000_4172105493_x0003__x0000__x0001__x0015_¼_x0018_ÂÄÉ_x0008__x0000__x0000_20180101_x000C__x0000__x0000_051-632-2681
+_x0000__x0000_0516322681_x0008__x0000__x0001_½°À_x0011_­íÅÜÂ _x0000_¨°l­_x0006__x0000__x0000_608827_x0011__x0000__x0001_½°À_x0011_­íÅÜÂ _x0000_¨°l­ _x0000_Ç ÇÉÓTÖ\¸ _x0000_4_x0000_9_x0000__x000D__x0000__x0000_010-2594-2682_x0015__x0000__x0000_moxie2000@hanmail.net_x000E__x0000__x0000_37690004509537_x0006__x0000__x0000_D00123_x0005__x0000__x0001_°Æ1Á¤ÂìÓ Î
+_x0000__x0000_2077003708_x0003__x0000__x0001_@®DÆÝÂ_x0008__x0000__x0000_20071009_x000B__x0000__x0000_02-465-1297	_x0000__x0000_024651197	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x0011_­ÄÉl­_x0006__x0000__x0000_143961_x0010__x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x0011_­ÄÉl­ _x0000_l­XÇ\¸ _x0000_6_x0000_6_x0000__x0014__x0000__x0001_1_x0000_5Î _x0000_(_x0000_l­XÇÙ³ _x0000_2_x0000_2_x0000_7_x0000_-_x0000_6_x0000_)_x0000_ _x0000_°Æ1Á¤ÂìÓ Î_x000D__x0000__x0000_010-3418-1230_x000F__x0000__x0000_ws418@naver.com_x000E__x0000__x0000_37690004510537_x0006__x0000__x0000_D00126_x0005__x0000__x0001_ÐÆÙ³´Ì!Ç¬À
+_x0000__x0000_3060363748_x0003__x0000__x0001_ü»Ñ¼ÁÉ_x0004__x0000__x0001_´ÆÙ³0®l­_x0008__x0000__x0000_20050705_x000C__x0000__x0000_042-531-4004
+_x0000__x0000_0425328899_x0008__x0000__x0001__x0000_³_x0004_È_x0011_­íÅÜÂ _x0000_Ù³l­_x0005__x0000__x0000_34630_x000D__x0000__x0001__x0000_³_x0004_È _x0000_Ù³l­ _x0000__x0000_³_x0004_È\¸ _x0000_7_x0000_6_x0000_5_x0000__x000D__x0000__x0000_010-5453-9536_x0012__x0000__x0000_wonspo@hanmail.net_x0008__x0000__x0000_20080214_x000E__x0000__x0000_37690004511137_x0006__x0000__x0000_D00127_x0008__x0000__x0001_ÐÆ¤ÂìÓ Î(_x0000__x001C_ÈüÈ)_x0000_
+_x0000__x0000_6160962051_x0003__x0000__x0001_@®ø»½¬_x000C__x0000__x0000_064-752-4422
+_x0000__x0000_0647232992_x000C__x0000__x0001__x001C_ÈüÈ¹ÒÄ¼ÇXÎÄ³ _x0000__x001C_ÁÀ­ìÓÜÂ_x0006__x0000__x0000_690161_x0013__x0000__x0001__x001C_ÈüÈ¹ÒÄ¼ÇXÎÄ³ _x0000__x001C_ÈüÈÜÂ _x0000_$Æ|·\¸ _x0000_1_x0000_3_x0000_4_x0000__x000D__x0000__x0000_010-4416-4412_x0015__x0000__x0000_crony0104@hanmail.net_x000E__x0000__x0000_37690004512837_x0006__x0000__x0000_D00132_x0005__x0000__x0001__x0004_ÈüÈÆ%±¤Â
+_x0000__x0000_4020887887_x0003__x0000__x0001_tÇ_x001C_Â+È_x000C__x0000__x0000_063-274-9337
+_x0000__x0000_0632789337_x0008__x0000__x0001__x0004_È|·½Ä³ _x0000__x0004_ÈüÈÜÂ_x0006__x0000__x0000_560080_x0013__x0000__x0001__x0004_È|·½Ä³ _x0000__x0004_ÈüÈÜÂ _x0000_DÆ°Àl­ _x0000_õ¬½\¸ _x0000_2_x0000_0_x0000__x000D__x0000__x0000_010-9224-8391_x0010__x0000__x0000_jyonex@naver.com_x000E__x0000__x0000_37690004516337_x0006__x0000__x0000_D00136_x0005__x0000__x0001__x001C_È|Ç¤ÂìÓ Î
+_x0000__x0000_4040533542_x000B__x0000__x0001__x001C_È|Ç_x0008_¸_x0000_È¤ÂìÓ Î(_x0000__x0015_ÈMÇ)_x0000__x0003__x0000__x0001_@®_x0011_­õ¼	_x0000__x0001_´ÆÙ³0®l­_x000F_¼´ÆÙ³õ¼xÆ_x000C__x0000__x0000_063-535-9146
+_x0000__x0000_0635332093_x0008__x0000__x0001__x0004_È|·½Ä³ _x0000__x0015_ÈMÇÜÂ_x0006__x0000__x0000_580804_x000F__x0000__x0001__x0004_È|·½Ä³ _x0000__x0015_ÈMÇÜÂ _x0000__x0011_ÉYÅ\¸ _x0000_8_x0000_3_x0000__x000D__x0000__x0000_010-9579-7800_x0016__x0000__x0000_sports9146@hanmaIl.net_x000E__x0000__x0000_37690004520237_x0006__x0000__x0000_D00137_x000B__x0000__x0001_üÈÝÂÖ¬À _x0000_0¼Ü´ü»4ÑÈ¹¸Ò
+_x0000__x0000_1108193203_x0003__x0000__x0001__x0015_ÈtÇ@±_x000B__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000__x0004_ÈÇÁÀp¬·_x0008__x0000__x0000_20130723_x000C__x0000__x0000_031-964-3530	_x0000__x0000_023829555_x0007__x0000__x0001_½¬0®Ä³ _x0000_à¬ÅÜÂ_x0005__x0000__x0000_10564_x0011__x0000__x0001_½¬0® _x0000_à¬ÅÜÂ _x0000_U³Ål­ _x0000_¼À¡Á\¸ _x0000_1_x0000_2_x0000__x0007__x0000__x0001_4_x0000_5Î _x0000_4_x0000_1_x0000_8_x0000_8Ö_x000D__x0000__x0000_010-7152-7538_x0014__x0000__x0000_mintonmart@naver.com_x000E__x0000__x0000_37690004521937_x0006__x0000__x0000_D00138	_x0000__x0001_üÈÝÂÖ¬ÀÙ³°Æ¤ÂìÓ Î
+_x0000__x0000_1108180426_x0003__x0000__x0001_¡Á_x0015_È|Ç_x000B__x0000__x0000_02-382-3598	_x0000__x0000_023553586	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_@ÇÉÓl­_x0006__x0000__x0000_122903_x0018__x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_@ÇÉÓl­ _x0000_ðÅ_x001C_Á\¸ _x0000_2_x0000_9_x0000_-_x0000_1_x0000_ _x0000_Ù³°Æ¤ÂìÓ Î_x000D__x0000__x0000_010-2018-3598_x0012__x0000__x0000_dvip1233@naver.com_x000B__x0000__x0000_01074353598
+_x0000__x0001__x0018_Â_x0008_® _x0000_½qÈ&lt;Ç\¸ _x0000_µÑ_x001C_È_x000E__x0000__x0000_37690004522537_x0006__x0000__x0000_D00141	_x0000__x0001__x0011_ÉYÅ¤ÂìÓ Î(_x0000_½¬üÈ)_x0000_
+_x0000__x0000_3226600323_x0003__x0000__x0001_iÖ_x0001_ÆäÂ_x0008__x0000__x0000_20081210_x000C__x0000__x0000_054-741-5177_x0008__x0000__x0001_½¬ÁÀ½Ä³ _x0000_½¬üÈÜÂ_x0006__x0000__x0000_780943_x0012__x0000__x0001_½¬ÁÀ½Ä³ _x0000_½¬üÈÜÂ _x0000__x0008_®1Á\¸ _x0000_2_x0000_9_x0000_4_x0000_-_x0000_1_x0000__x000D__x0000__x0000_010-7579-5177_x0014__x0000__x0000_jasp6304@hanmail.net_x0008__x0000__x0000_20081211_x000E__x0000__x0000_37690004525437_x0006__x0000__x0000_D00145_x0005__x0000__x0001_­Ìá¸¤ÂìÓ Î
+_x0000__x0000_6150796307_x0003__x0000__x0001_pÈø»_x0019_Â_x0008__x0000__x0000_20101004_x000C__x0000__x0000_055-312-9559
+_x0000__x0000_0553129560_x0008__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_@®tÕÜÂ_x0006__x0000__x0000_621833_x0012__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_@®tÕÜÂ _x0000_¥Ç Ç\¸ _x0000_2_x0000_9_x0000_7_x0000_-_x0000_5_x0000__x000D__x0000__x0000_010-9513-9559_x0016__x0000__x0000_jms3129559@hanmail.net_x0008__x0000__x0000_20101019_x000E__x0000__x0000_37690004530037_x0006__x0000__x0000_D00148_x0007__x0000__x0001__x0000_ÏtÇdÅD¾¤ÂìÓ Î
+_x0000__x0000_1232481068_x0003__x0000__x0001__x0015_¼+ºÇ_x000C__x0000__x0000_031-457-8706
+_x0000__x0000_0314578707_x0007__x0000__x0001_½¬0®Ä³ _x0000_HÅÅÜÂ_x0006__x0000__x0000_431837_x0012__x0000__x0001_½¬0®Ä³ _x0000_HÅÅÜÂ _x0000_Ù³HÅl­ _x0000_À­xÇ\¸ _x0000_8_x0000_9_x0000__x000D__x0000__x0000_010-7338-7375_x0016__x0000__x0000_jamjali200@hanmail.net_x000E__x0000__x0000_37690004532237_x0006__x0000__x0000_D00149	_x0000__x0001_TÏ¬¹DÅ$Æ_x0008_Õ(_x0000_@®Ì)_x0000_
+_x0000__x0000_5100147324_x0003__x0000__x0001__x0015_¼ Á_x0001_Æ_x0008__x0000__x0000_20070423_x000C__x0000__x0000_054-430-7007
+_x0000__x0000_0544307007_x0008__x0000__x0001_½¬ÁÀ½Ä³ _x0000_@®ÌÜÂ_x0005__x0000__x0000_39626_x000E__x0000__x0001_½¬½ _x0000_@®ÌÜÂ _x0000_¡Á$Á\¸ _x0000_1_x0000_6_x0000_4_x0000__x000D__x0000__x0000_010-4115-6306_x0013__x0000__x0000_jj10654@hanmail.net_x000E__x0000__x0000_37690004533937_x0006__x0000__x0000_D00150_x0005__x0000__x0001__x0014_Ól­¤ÂìÓ Î
+_x0000__x0000_5020153204_x0003__x0000__x0001_àÂÁÀÜ­_x0008__x0000__x0000_20080331_x000C__x0000__x0000_053-957-8989
+_x0000__x0000_0539432345_x0008__x0000__x0001__x0000_³l­_x0011_­íÅÜÂ _x0000_Ù³l­_x0005__x0000__x0000_41193_x000F__x0000__x0001__x0000_³l­ _x0000_Ù³l­ _x0000_DÅÅ\¸1_x0000_1_x0000_8® _x0000_8_x0000_1_x0000__x0008__x0000__x0001_1_x0000_5Î _x0000__x0014_Ól­¤ÂìÓ Î_x000D__x0000__x0000_010-8854-8989_x0012__x0000__x0000_89sports@naver.com_x000E__x0000__x0000_37690004534537_x0006__x0000__x0000_D00159_x0005__x0000__x0001__x001C_Ö1Á¤ÂìÓ Î
+_x0000__x0000_1300531089_x0003__x0000__x0001_tÇXÇ Á_x000D__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000__x0000_¬_x0004_È_x001C_ÈÔ,_x0000_¡ÇTÖ_x0008__x0000__x0000_20070529_x000C__x0000__x0000_032-654-2133
+_x0000__x0000_0326542132_x0007__x0000__x0001_½¬0®Ä³ _x0000_½ÌÜÂ_x0006__x0000__x0000_422819 _x0000__x0001_½¬0®Ä³ _x0000_½ÌÜÂ _x0000_Á¬Àl­ _x0000_½¬xÇ\¸1_x0000_2_x0000_0_x0000_¼8® _x0000_2_x0000_8_x0000_ _x0000_ _x0000_1_x0000_5Î_x0010_ÈìÓ _x0000_1_x0000_xÎ_x000D__x0000__x0000_010-7578-7740_x0015__x0000__x0000_hs7167741@hanmail.net_x000E__x0000__x0000_37690004541337_x0006__x0000__x0000_D00160_x0005__x0000__x0001_8ÖÙ³¤ÂìÓ Î
+_x0000__x0000_1243919047_x0003__x0000__x0001_@®8ÖÙ³_x0008__x0000__x0000_20100113_x000C__x0000__x0000_031-375-0331
+_x0000__x0000_0313750331_x0007__x0000__x0001_½¬0®Ä³ _x0000_$Æ°ÀÜÂ_x0006__x0000__x0000_447802_x001A__x0000__x0001_½¬0®Ä³ _x0000_$Æ°ÀÜÂ _x0000_1Á8Ö_x0000_³\¸ _x0000_2_x0000_5_x0000_ _x0000_´Æ°ÀL¾)µ _x0000_ _x0000_1_x0000_5Î _x0000_4_x0000__x000D__x0000__x0000_010-5295-8278_x0013__x0000__x0000_khd9982@hanmail.net_x000E__x0000__x0000_37690004542037_x0006__x0000__x0000_D00161_x0005__x0000__x0001_MÖ1ÁÆ%±¤Â
+_x0000__x0000_3100640518_x0003__x0000__x0001_@®_x0004_Ö_x0015_È_x0008__x0000__x0000_20090616_x000C__x0000__x0000_041-634-7327_x0008__x0000__x0001_©Í­Ì¨°Ä³ _x0000_MÖ1Áp­_x0005__x0000__x0000_32263_x0012__x0000__x0001_©Í¨° _x0000_MÖ1Áp­ _x0000_MÖ½MÇ _x0000_©Í¨°_x0000_³\¸ _x0000_3_x0000_6_x0000__x0015__x0000__x0001__x001C_È _x0000_1_x0000_5Î _x0000__x001C_È _x0000_1_x0000_0_x0000_1_x0000_8Ö(_x0000_L¾dÅT³¤Â$Æ&lt;Õ¤ÂTÑ)_x0000__x000D__x0000__x0000_010-8626-9825_x0010__x0000__x0000_hji923@naver.com_x000E__x0000__x0000_37690004543637_x0006__x0000__x0000_D00166_x000C__x0000__x0001_(_x0000_üÈ)_x0000_ðÒ_x001C_ÈtÇ_x0014_µ¤Â¸Ò¬¹ð½XÁ
+_x0000__x0000_2118732516_x0003__x0000__x0001_¡ÁÁÀÐÆ_x0006__x0000__x0001_Ä³Áä¹ _x0000_Ä³ä¹_x0008__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_4»íÅ_x0008__x0000__x0000_20120911_x000B__x0000__x0000_02-511-5114	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x0015_¬¨°l­_x0006__x0000__x0000_135010_x000B__x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ_x0015_¬¨°l­|±_x0004_ÖÙ³_x000E__x0000__x0001__x0008_®@ÇL¾)µ _x0000_1_x0000_5Î _x0000_ ¼¤Â¸Ò¤Â Ñ´Å_x000D__x0000__x0000_010-8784-1651_x0015__x0000__x0000_bestextreme@naver.com_x0007__x0000__x0001_B_x0000_ñ´	®(_x0000_T_x0000_S_x0000_)_x0000__x0005__x0000__x0000_14049_x0003__x0000__x0001__x0015_¼_x0004_ÖÄÉ_x0008__x0000__x0000_20190917_x0006__x0000__x0000_D00167_x0008__x0000__x0001_üÈÝÂÖ¬À _x0000_ÐÆÐÅÇ
+_x0000__x0000_1268800066_x0003__x0000__x0001_@®DÕ¹Â_x0006__x0000__x0001_Ä³Áä¹ÅÅ _x0000_xÆ_x0007__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_xÆ_x000C__x0000__x0000_02-1644-1662	_x0000__x0001_½°À_x0011_­íÅÜÂ _x0000__x0018_Â_x0001_Æl­_x0006__x0000__x0000_613815_x0013__x0000__x0001_½°À_x0011_­íÅÜÂ _x0000__x0018_Â_x0001_Æl­ _x0000__x0011_­¨°\¸ _x0000_6_x0000_3_x0000_ _x0000_B_x0000_Ù³_x0004__x0000__x0001_4_x0000_5Î|Ç½_x000D__x0000__x0000_010-8882-4137_x0014__x0000__x0000_oneeight@hanmail.net_x0006__x0000__x0000_D00173_x0005__x0000__x0001__x0008_®_x0001_Æ¤ÂìÓ Î
+_x0000__x0000_1052087391_x0003__x0000__x0001_°ÆÀÉÐÆ_x0008__x0000__x0000_20140217_x000D__x0000__x0000_010-6208-8112_x0006__x0000__x0000_121889_x0013__x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_È¹ìÓl­ _x0000_Ù³P­\¸3_x0000_8® _x0000_1_x0000_2_x0000_5_x0000__x0013__x0000__x0000_yonex0901@naver.com_x0008__x0000__x0000_20150122_x000E__x0000__x0000_37690004557937_x0006__x0000__x0000_D00181_x0004__x0000__x0001__x0000_É¤ÂìÓ Î
+_x0000__x0000_1410240836_x0003__x0000__x0001__x0015_¼½¬·_x0008__x0000__x0000_20140825_x000C__x0000__x0000_031-945-2007_x0007__x0000__x0001_½¬0®Ä³ _x0000__x000C_ÓüÈÜÂ_x0006__x0000__x0000_413819$_x0000__x0001_½¬0®Ä³ _x0000__x000C_ÓüÈÜÂ _x0000_DÅ¬¹·\¸ _x0000_5_x0000_5_x0000_ _x0000_-_x0000_8_x0000_1_x0000_ _x0000_(_x0000__x0008_®_x000C_ÍÙ³,_x0000_ _x0000__x000C_ÓüÈ_x0008_®_x000C_ÍXÕ_x0018_ÂÌ¬¹¥Ç)_x0000__x000C__x0000__x0001__x000C_ÓüÈÜÂ _x0000_0¼Ü´ü»4Ñ_x0004_È©Æl­¥Ç_x000D__x0000__x0000_010-9129-1126_x0017__x0000__x0000_leesjun1024@hanmail.net_x000E__x0000__x0000_37690004547137_x0006__x0000__x0000_D00183_x0003__x0000__x0001_T³_x001C_È|Ç
+_x0000__x0000_1171558537_x0003__x0000__x0001_iÖÐÆ Á_x000B__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_XÇX¹,_x0000_¡ÇTÖ_x0008__x0000__x0000_20141027_x000D__x0000__x0000_010-6333-2457	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_ÅÌl­_x0005__x0000__x0000_08078 _x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_ÅÌl­ _x0000_àÂ_x0015_È\¸ _x0000_2_x0000_7_x0000_5_x0000_ _x0000_ _x0000_(_x0000_àÂ_x0015_ÈÙ³,_x0000_ _x0000_àÂ¸Ò¬¹DÅ_x000C_Ó¸Ò)_x0000__x0010__x0000__x0001_ÁÀ_x0000_¬Ù³ _x0000_1_x0000_5Î _x0000_1_x0000_0_x0000_4_x0000_,_x0000_ _x0000_1_x0000_0_x0000_5_x0000_8Ö_x0011__x0000__x0000_thejeil@naver.com_x000D__x0000__x0000_010-9668-2210_x000E__x0000__x0000_37690004550437_x0006__x0000__x0000_D00184_x0005__x0000__x0001_$Æ¨°¤ÂìÓ Î
+_x0000__x0000_1322489384_x0003__x0000__x0001_Å+È¨º_x000D__x0000__x0001_´ÆÙ³0®l­©ÆÔ _x0000_aÅ8Á_x001C_Á¬¹ _x0000_xÆ_x0008__x0000__x0000_20141028
+_x0000__x0000_0315756464
+_x0000__x0000_0315755600_x0008__x0000__x0001_½¬0®Ä³ _x0000_¨°ÅüÈÜÂ_x0006__x0000__x0000_472881_x0016__x0000__x0001_½¬0®Ä³ _x0000_¨°ÅüÈÜÂ _x0000_ÄÉt¬$Æ¨°\¸ _x0000_8_x0000_0_x0000_6_x0000_ _x0000_-_x0000_1_x0000_4_x0000__x000D__x0000__x0000_010-9289-9637_x0012__x0000__x0000_jongmo83@naver.com_x000E__x0000__x0000_37690004552737_x0006__x0000__x0000_D00186_x0005__x0000__x0001_ä¹XÎìÓxÇ¸Ò
+_x0000__x0000_6091853217_x0003__x0000__x0001_iÖ­ÝÂ_x0008__x0000__x0000_20141202_x000C__x0000__x0000_055-298-7330_x0005__x0000__x0000_51378_x0011__x0000__x0001_½¬¨° _x0000_=ÌÐÆÜÂ _x0000_XÇ=Ìl­ _x0000__x0018_¼Ä¬\¸ _x0000_6_x0000_3_x0000__x000D__x0000__x0000_010-3561-0209_x000E__x0000__x0000_o2bbi@nate.com_x0008__x0000__x0000_20141212_x000E__x0000__x0000_37690004554037_x0006__x0000__x0000_D00190_x0005__x0000__x0001_p­°À¤ÂìÓ Î
+_x0000__x0000_4010657765_x0003__x0000__x0001__x0015_¼_x001C_Âl×	_x0000__x0001_¤ÂìÓ ÎXÇX¹,_x0000_ _x0000_©ÆÔ_x0008__x0000__x0000_20150406_x000D__x0000__x0000_010-9977-7141_x0008__x0000__x0001__x0004_È|·½Ä³ _x0000_p­°ÀÜÂ_x0005__x0000__x0000_54102_x000F__x0000__x0001__x0004_È½ _x0000_p­°ÀÜÂ _x0000_¨°_x0018_Â¡Á5_x0000_8® _x0000_4_x0000_2_x0000__x000F__x0000__x0001_1_x0000_0_x0000_1_x0000_8Ö(_x0000__x0018_Â¡ÁÙ³,_x0000_ _x0000_(Ì$Æ¹L¾)_x0000__x0013__x0000__x0000_shp7141@hanmaiL.net_x000E__x0000__x0000_37690004558537_x0006__x0000__x0000_D00192
+_x0000__x0001__x0001_Æ8»¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1222039517_x0005__x0000__x0001__x0001_Æ8»¤ÂìÓ Î_x0003__x0000__x0001_@®_x0001_Æ8»_x0008__x0000__x0000_20150608_x000C__x0000__x0000_032-523-1406_x000C__x0000__x0000_032-517-8009	_x0000__x0001_xÇÌ_x0011_­íÅÜÂ _x0000_½ÉÓl­_x0005__x0000__x0000_21337_x000D__x0000__x0000_010-4320-1</v>
           </cell>
           <cell r="D35" t="str">
             <v>사용가능</v>
@@ -4323,49 +4760,275 @@
             <v>일반사업자</v>
           </cell>
           <cell r="F35" t="str">
-            <v>1102115009</v>
+            <v>M1406@hanmail.net_x0007__x0000__x0001_A_x0000_ñ´	®(_x0000_T_x0000_S_x0000_)_x0000__x0005__x0000__x0000_13042_x0003__x0000__x0001_@®Ù³½¬_x000E__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_+_x0000_3_x0000_0_x0000__x000E__x0000__x0000_37690004561837_x0006__x0000__x0000_D00193_x000B__x0000__x0001_ÑÐ¤Â@Õ¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1320972497_x0006__x0000__x0001_ÑÐ¤Â@Õ¤ÂìÓ Î_x0003__x0000__x0001__x0015_¼_x0004_Ö=Ì_x0006__x0000__x0001_´ÆÙ³_x0004_È8»©ÆÔ_x0008__x0000__x0000_20150610_x000D__x0000__x0000_010-3706-2477_x0007__x0000__x0001_½¬0®Ä³ _x0000_l­¬¹ÜÂ_x0005__x0000__x0000_11907_x000F__x0000__x0001_½¬0® _x0000_l­¬¹ÜÂ _x0000_UÆ_x0019_ÂÌ\¸ _x0000_5_x0000_0_x0000_7_x0000_	_x0000__x0001_3_x0000_5Î _x0000_ÑÐ¤Â@Õ¤ÂìÓ Î_x000F__x0000__x0000_pspin@naver.com_x0005__x0000__x0000_22022_x0003__x0000__x0001_HÅ°ÆÄÉ_x000C__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_7_x0000_._x0000_5_x0000__x000E__x0000__x0000_37690004560137_x0006__x0000__x0000_D00195
+_x0000__x0001_¤ÂìÓ ÎLÑlÐ(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_6172249744_x0005__x0000__x0001_¤ÂìÓ ÎLÑlÐ_x0003__x0000__x0001_tÇÝÐ0®_x0006__x0000__x0001__x001C_ÈpÈÅÅ _x0000_Áä¹_x000C__x0000__x0001_õ¬_x0008_Æ _x0000_¤ÂìÓ Î©ÆÔ,_x0000_ _x0000_¡ÇTÖ_x000B__x0000__x0000_051-7564800_x000C__x0000__x0000_051-756-4801_x0005__x0000__x0000_48222_x0017__x0000__x0001_½°À_x0011_­íÅÜÂ _x0000_Ù³·l­ _x0000_+ÈiÕ´ÆÙ³¥Ç\¸ _x0000_4_x0000_0_x0000_¼8® _x0000_8_x0000_'_x0000__x0001_1_x0000_0_x0000_3_x0000_Ù³ _x0000_1_x0000_0_x0000_5_x0000_8Ö,_x0000_1_x0000_0_x0000_6_x0000_8Ö(_x0000_¬ÀÁÉÙ³,_x0000_½°À _x0000_DÅÜÂDÅÜ´ _x0000_TÏ$Æq¸ _x0000_XÕ²DÌ _x0000_DÅ_x000C_Ó¸Ò)_x0000__x000D__x0000__x0000_010-5578-1988_x0015__x0000__x0000_ltktennis@hanmail.net_x000B__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_8_x0000__x0008__x0000__x0000_20150611_x000E__x0000__x0000_37690004562437_x0006__x0000__x0000_D00196	_x0000__x0001__x0015_¬¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_5041920932_x0004__x0000__x0001__x0015_¬¤ÂìÓ Î_x0003__x0000__x0001__x0015_¬@Çl­_x000D__x0000__x0001_LÑÈ²¤Â©ÆÔ,_x0000_ _x0000_XÇX¹,_x0000_ _x0000_àÂ_x001C_¼_x000C__x0000__x0000_053-314-9090_x0005__x0000__x0000_41433_x000D__x0000__x0000_010-3828-0474_x0013__x0000__x0000_keg0417@hanmail.net_x000D__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_6_x0000_+_x0000_1_x0000_5_x0000__x0008__x0000__x0000_20150612_x000E__x0000__x0000_37690004565337_x0006__x0000__x0000_D00199
+_x0000__x0001_P´¬¹¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1283008985_x0003__x0000__x0001_@®_x0001_Æ Á_x000B__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_¤ÂìÓ ÎXÇX¹_x0008__x0000__x0000_20150703_x000C__x0000__x0000_031-911-4191_x000C__x0000__x0000_031-913-0067_x0006__x0000__x0000_410829_x000F__x0000__x0001_½¬0®Ä³à¬ÅÜÂ _x0000_|Ç°ÀÙ³l­_x0015_È_x001C_¼°ÀÙ³_x000E__x0000__x0001_1_x0000_1_x0000_4_x0000_8_x0000_-_x0000_1_x0000_3_x0000_ _x0000_1_x0000_5Î2_x0000_,_x0000_3_x0000_8Ö_x000D__x0000__x0000_010-4288-3563_x0012__x0000__x0000_usop2n@hanmail.net_x000D__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_6_x0000_+_x0000_2_x0000_3_x0000__x000E__x0000__x0000_37690004568237_x0006__x0000__x0000_D00201_x000E__x0000__x0001_(_x0000_üÈ)_x0000_¤ÂtÎtÇ¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_6278102573_x000B__x0000__x0001_¤ÂtÎtÇ¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000__x0003__x0000__x0001_@®1ÁÐÆ_x0006__x0000__x0001_Áä¹ÅÅ _x0000_Ä³ä¹_x0008__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_ä¹_x0010_È_x000C__x0000__x0000_041-566-1879_x000C__x0000__x0000_041-554-2732_x0005__x0000__x0000_31157"_x0000__x0001_©Í­Ì¨°Ä³ _x0000_ÌHÅÜÂ _x0000__x001C_Á½l­ _x0000_1¼_x001D_Á3_x0000_\¸ _x0000_2_x0000_9_x0000_ _x0000_ _x0000_(_x0000_1¼_x001D_ÁÙ³,_x0000_ _x0000_½¶É¹_x0008_Ã%¼)_x0000__x000D__x0000__x0000_010-4513-1879_x0011__x0000__x0000_kimsw000@nate.com_x000E__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_4_x0000_0_x0000_+_x0000_2_x0000_0_x0000__x0008__x0000__x0000_20150804_x000E__x0000__x0000_37690004570937_x0006__x0000__x0000_D00202_x0008__x0000__x0001_¤ÂìÓå²(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_3052275067_x0003__x0000__x0001_HÅü­¹Â_x000C__x0000__x0000_042-522-9566_x000C__x0000__x0000_042-271-4786_x0006__x0000__x0000_300810_x0017__x0000__x0001__x0000_³_x0004_È_x0011_­íÅÜÂ _x0000__x0011_Él­ _x0000_Ù³_x001C_Á_x0000_³\¸ _x0000_1_x0000_2_x0000_0_x0000_1_x0000_(_x0000_ÜÐÉÓÙ³)_x0000__x0007__x0000__x0001_¤ÂìÓå² _x0000_ÜÐÉÓ_x0010_È_x000B__x0000__x0000_01062224787_x0010__x0000__x0000_spodaq@naver.com_x000D__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_5_x0000_+_x0000_3_x0000_3_x0000__x0008__x0000__x0000_20150805_x000E__x0000__x0000_37690004571537_x0006__x0000__x0000_D00203	_x0000__x0001_ðÅTÏ¬¹DÅ(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_2041477980_x0004__x0000__x0001_ðÅTÏ¬¹DÅ_x0003__x0000__x0001_@®ÁÀ0®_x0006__x0000__x0001_Ä³Áä¹ _x0000_t¬$Á_x000D__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_´Ì!ÇÜÂ_x001C_Á&lt;»$ÁXÎ_x0008__x0000__x0000_20150806_x000C__x0000__x0000_02-3390-4345_x000C__x0000__x0000_02-3390-4344
+_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_Ù³_x0000_³8»l­_x0005__x0000__x0000_02496_x0011__x0000__x0001__x001C_Á¸Æ _x0000_Ù³_x0000_³8»l­ _x0000_Ý¹°Æ\¸1_x0000_2_x0000_8® _x0000_1_x0000_9_x0000__x000B__x0000__x0001_1_x0000_5Î _x0000_XÕtÇÐÆ¤ÂìÓ Î°ÀÅÅ_x000D__x0000__x0000_010-9089-5363_x0017__x0000__x0000_01090895363@hanmail.net_x000B__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_2_x0000_0_x0000__x000E__x0000__x0000_37690004572137_x0006__x0000__x0000_D00205_x0005__x0000__x0001_ÁLÑ¤ÂìÓ Î
+_x0000__x0000_1971301851_x0003__x0000__x0001_@®_x0001_Æ_x0018_Â_x0008__x0000__x0001_Ä³Áä¹ÅÅ _x0000_Ä³ä¹ÅÅ	_x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_4»íÅÅÅ_x000B__x0000__x0000_01063388568_x0008__x0000__x0001_½¬0®Ä³ _x0000_XÇ_x0015_È½ÜÂ_x0005__x0000__x0000_11806!_x0000__x0001_½¬0®Ä³ _x0000_XÇ_x0015_È½ÜÂ _x0000_$Æ©º\¸ _x0000_1_x0000_7_x0000_0_x0000_ _x0000_°Àä´È¹DÇ _x0000_DÅ_x000C_Ó¸Ò _x0000_4_x0000_1_x0000_2_x0000_-_x0000_7_x0000_0_x0000_6_x0000__x000D__x0000__x0000_010-6338-8568_x0011__x0000__x0000_3388568@naver.com_x0005__x0000__x0000_26002_x0003__x0000__x0001__x0015_¬ÜÐ8Ö_x0008__x0000__x0000_20220901_x000E__x0000__x0000_37690004700437_x0006__x0000__x0000_D00209_x0018__x0000__x0001_¤ÂìÓ Î_x000C_Õì·¤Â(_x0000_S_x0000_p_x0000_o_x0000_r_x0000_t_x0000_s_x0000_ _x0000_P_x0000_l_x0000_u_x0000_s_x0000_)_x0000_(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1192167071_x0003__x0000__x0001__x0015_¬ÜÂ¨º_x0006__x0000__x0001_Ä³Áä¹ _x0000_LÇÝÂ_x0008__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_\ÕÝÂ_x000B__x0000__x0000_02-871-5513	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x0000_­EÅl­_x0005__x0000__x0000_08750_x000F__x0000__x0001__x001C_Á¸Æ _x0000__x0000_­EÅl­ _x0000_àÂ¼¹\¸3_x0000_8® _x0000_4_x0000_0_x0000__x0005__x0000__x0001_ÀÉXÕ _x0000_1_x0000_5Î_x000D__x0000__x0000_010-7703-5353_x001A__x0000__x0000_tennisplus0122@esero.go.krX_x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_ _x0000_/_x0000_ _x0000_2_x0000_5_x0000_S_x0000_S_x0000_ _x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_ _x0000_/_x0000_ _x0000_2_x0000_4_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_9_x0000_._x0000_6_x0000_ _x0000_/_x0000_ _x0000_2_x0000_4_x0000_S_x0000_S_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_ _x0000_/_x0000_ _x0000_2_x0000_3_x0000_F_x0000_W_x0000_ _x0000__x0018_ÂüÈ _x0000_ìÅàÂ _x0000_ _x0000_1_x0000_2_x0000_ _x0000_(_x0000_ô²ù²Ç _x0000_Æ­Ì&lt;Ç\¸ _x0000_6_x0000_ _x0000__x0018_¼_x0001_Æ)_x0000__x0008__x0000__x0000_20160114_x000E__x0000__x0000_37690004577337_x0006__x0000__x0000_D00210_x0011__x0000__x0001_(_x0000_üÈ)_x0000_ÐÅtÇ_x001C_ÈtÇxÇ0Ñ´°TÁ °(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1268641398_x000C__x0000__x0000_031-761-8980_x000C__x0000__x0000_031-761-2140_x0005__x0000__x0000_12769_x000D__x0000__x0000_010-4552-3318	_x0000__x0000_1800-6142_x000E__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_4_x0000_0_x0000_+_x0000_2_x0000_5_x0000__x0008__x0000__x0000_20160121_x000E__x0000__x0000_37690004578037_x0006__x0000__x0000_D00256	_x0000__x0001_p¬1Á¤ÂìÓ Î(_x0000_Å°À)_x0000_
+_x0000__x0000_6210808090_x0003__x0000__x0001__x0015_È+È_x0015_¬_x0006__x0000__x0001_Ä³Áä¹ _x0000__x001C_ÈpÈ_x000B__x0000__x0001_ìÕ¤Â0®l­,_x0000_ _x0000_¤ÂìÓ Î©ÆÔ_x0008__x0000__x0000_20160412_x000C__x0000__x0000_055-387-3613_x000C__x0000__x0000_055-387-3615_x0008__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_Å°ÀÜÂ_x0005__x0000__x0000_50621 _x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_Å°ÀÜÂ _x0000__x001C_Á|ÇÙ³\¸ _x0000_2_x0000_5_x0000_ _x0000_ _x0000_(_x0000__x0011_É½Ù³,_x0000_ _x0000_$Ç ÁÝÀ_x0001_Æ´ÅP­äÂ)_x0000__x000D__x0000__x0000_010-2390-2994_x0013__x0000__x0000_dhrhr68@hanmail.netH_x0000__x0001_2_x0000_4_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_3_x0000_5_x0000_ _x0000_/_x0000_2_x0000_4_x0000_S_x0000_S_x0000__x0018_ÂüÈìÅàÂ _x0000_3_x0000_5_x0000_ _x0000_/_x0000_ _x0000_2_x0000_3_x0000_F_x0000_W_x0000_ _x0000__x0018_ÂüÈ _x0000_ìÅàÂ _x0000_3_x0000_5_x0000_ _x0000_/_x0000_ _x0000_2_x0000_3_x0000_S_x0000_S_x0000_ _x0000__x0018_ÂüÈ _x0000_ìÅàÂ _x0000_3_x0000_5_x0000_(_x0000_|·_x0013_Ï+_x0000_È¹D¾¤Â _x0000_9_x0000_4_x0000_3_x0000_,_x0000_2_x0000_5_x0000_0_x0000_)_x0000__x0008__x0000__x0000_20160407_x000E__x0000__x0000_37690004581237_x0006__x0000__x0000_D00267_x0006__x0000__x0001__x001C_ÈtÇD¾¤ÂìÓ Î
+_x0000__x0000_6664100083_x0003__x0000__x0001_Ç_x0015_È\Õ_x000D__x0000__x0001_Ä³ä¹ _x0000__x000F_¼ _x0000_Áä¹ÅÅ,_x0000_ _x0000__x001C_ÁD¾¤Â_x000C__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_ _x0000__x0011_­à¬_x0000_³ÕÅÅ_x0008__x0000__x0000_20160610_x000C__x0000__x0000_062-523-7451_x000C__x0000__x0000_062-523-7455_x0005__x0000__x0000_62023_x000D__x0000__x0001__x0011_­üÈ _x0000__x001C_Ál­ _x0000_´ÆÌ\¸ _x0000_1_x0000_2_x0000_2_x0000__x0005__x0000__x0001_(_x0000__x000D_Ã_x000C_ÍÙ³)_x0000__x000D__x0000__x0000_010-4606-4538_x0015__x0000__x0000_jhrim1226@hanmail.net_x0008__x0000__x0000_20160601_x000E__x0000__x0000_37690004584137_x0006__x0000__x0000_D00280_x0005__x0000__x0001_Ä³ô²¤ÂìÓ Î
+_x0000__x0000_3071042161_x0003__x0000__x0001_$ÇÙ³ÝÂ_x000B__x0000__x0001_Ä³ä¹_x000F_¼ _x0000_Áä¹ÅÅ _x0000_Áä¹ÅÅ_x0010__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_Ç_x0004_Èp¬ _x0000__x0010_Óä¹,_x0000_ _x0000__x0000_³ìÅ_x0008__x0000__x0000_20160825_x000C__x0000__x0000_044-863-8908_x000C__x0000__x0000_044-863-8970_x000F__x0000__x0001_8Á+È¹ÒÄ¼ÇXÎÜÂ _x0000_8Á+È¹ÒÄ¼ÇXÎÜÂ_x0005__x0000__x0000_30102_x001E__x0000__x0001_8Á+È¹ÒÄ¼ÇXÎÜÂ _x0000__x0008_È¬Ç\¸ _x0000_1_x0000_7_x0000_2_x0000_ _x0000_(_x0000_´ÅÄÉÙ³,_x0000_ _x0000_ÜÐ\Õ_x0004_Õ_x0008_¸¤Â&lt;Á0Ñ)_x0000__x0004__x0000__x0001_1_x0000_0_x0000_1_x0000_8Ö_x000D__x0000__x0000_010-7185-8008_x0015__x0000__x0000_dodamsports@naver.com_x000E__x0000__x0000_37690004586437_x0006__x0000__x0000_D00282_x0005__x0000__x0001__x0004_²¬¹¤ÂìÓ Î
+_x0000__x0000_1082124505_x0003__x0000__x0001_@®l×_x0015_È_x0006__x0000__x0001_Áä¹ _x0000_Ä³Áä¹_x000C__x0000__x0001__x0004_ÈÇÁÀp¬·ÅÅ _x0000_0¼Ü´ü»4Ñ _x0000__x000B__x0000__x0000_02-848-6291_x000B__x0000__x0000_02-848-7556
+_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x0001_Æñ´ìÓl­_x0005__x0000__x0000_07375_x000E__x0000__x0001__x001C_Á¸Æ _x0000__x0001_Æñ´ìÓl­ _x0000_Ä³àÂ\¸ _x0000_5_x0000_1_x0000__x000D__x0000__x0001_1_x0000_5Î _x0000_1_x0000_0_x0000_5_x0000_8Ö(_x0000_¡ÁU³L¾)µ)_x0000__x000D__x0000__x0000_010-8393-6291_x0013__x0000__x0000_hee00jung@naver.com_x0008__x0000__x0000_20160905_x000E__x0000__x0000_37690004588737_x0006__x0000__x0000_D00286_x0007__x0000__x0001_Æ%±¤Â _x0000_1Á¨°_x0010_È
+_x0000__x0000_2603001743_x0003__x0000__x0001_MÖ¥Ç8Ö_x0008__x0000__x0001_Ä³ä¹ _x0000__x000F_¼ _x0000_Áä¹ÅÅ_x0008__x0000__x0000_20151218_x000C__x0000__x0000_031-755-7257_x0007__x0000__x0001_½¬0®Ä³ _x0000_1Á¨°ÜÂ_x0005__x0000__x0000_13110_x001E__x0000__x0001_½¬0®Ä³ _x0000_1Á¨°ÜÂ _x0000__x0018_Â_x0015_Èl­ _x0000_1Á¨°_x0000_³\¸ _x0000_1_x0000_2_x0000_6_x0000_7_x0000_ _x0000_-_x0000_1_x0000_ _x0000_(_x0000_ÜÐÉÓÙ³)_x0000__x000D__x0000__x0000_010-7191-7257_x0012__x0000__x0000_nero1016@naver.com_x0002__x0000__x0001_¨°¸Ó_x0008__x0000__x0000_20161109_x000E__x0000__x0000_37690004591037_x0006__x0000__x0000_D00287_x0005__x0000__x0001_¤ÐtÎ¤ÂìÓ Î
+_x0000__x0000_6103752918_x0003__x0000__x0001_@®ÜÐÇ_x0008__x0000__x0000_20161125_x000C__x0000__x0000_052-268-6086_x000C__x0000__x0000_052-272-5908_x0008__x0000__x0001_¸Æ°À_x0011_­íÅÜÂ _x0000_¨°l­_x0005__x0000__x0000_44692_x0016__x0000__x0001_¸Æ°À_x0011_­íÅÜÂ _x0000_¨°l­ _x0000_Ë³ÈÉ\¸ _x0000_1_x0000_2_x0000_4_x0000_ _x0000_ _x0000_(_x0000_ì²Ù³)_x0000__x0003__x0000__x0000_3/2_x000D__x0000__x0000_010-9568-6086_x0014__x0000__x0000_kika5908@hanmail.net_x000E__x0000__x0000_37690004592637_x0006__x0000__x0000_D00292_x0008__x0000__x0001_Æ%±¤Â _x0000_¤ÂìÓÐÆ_x0010_È
+_x0000__x0000_6977800050_x0003__x0000__x0001_\ÕÀ­_x0001_Æ_x0008__x0000__x0000_20170102_x000C__x0000__x0000_051-517-3862_x000C__x0000__x0000_051-583-1023	_x0000__x0001_½°À_x0011_­íÅÜÂ _x0000__x0008_®_x0015_Èl­_x0005__x0000__x0000_46207&amp;_x0000__x0001_½°À_x0011_­íÅÜÂ _x0000__x0008_®_x0015_Èl­ _x0000_´Ì!Çõ¬ÐÆ\¸3_x0000_9_x0000_9_x0000_¼8® _x0000_3_x0000_2_x0000_4_x0000_ _x0000_ _x0000_(_x0000_P´l­Ù³,_x0000_ _x0000_¤ÂìÓÐÆ_x000C_ÓlÐ)_x0000__x0010__x0000__x0001_ÀÉXÕ1_x0000_5Î(_x0000_P´l­Ù³,_x0000_ _x0000_äÂ´°´Ì!Ç_x0000_­)_x0000__x000D__x0000__x0000_010-5505-3862_x0013__x0000__x0000_hgy4285@hanmail.net_x000E__x0000__x0000_37690004595537_x0006__x0000__x0000_D00306_x0007__x0000__x0001_Æ%±¤Â _x0000_ÁÀ4»_x0010_È
+_x0000__x0000_8042300420_x0003__x0000__x0001_@®_x0004_Ö+È_x000D__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_´ÆÙ³©ÆÔ _x0000_¡ÇTÖ_x0008__x0000__x0000_20170119_x000D__x0000__x0000_010-6886-7065_x000C__x0000__x0000_062-374-5410_x0005__x0000__x0000_61970_x0013__x0000__x0001__x0011_­üÈ _x0000__x001C_Ál­ _x0000_ÁÀ4»ü»üÈ\¸3_x0000_2_x0000_¼8® _x0000_3_x0000_-_x0000_5_x0000__x0013__x0000__x0000_sskim-j@hanmail.net_x000E__x0000__x0000_37690004597837_x0006__x0000__x0000_D00308_x0005__x0000__x0001_C_x0000_S_x0000_¤ÂìÓ Î
+_x0000__x0000_2270838785_x0007__x0000__x0001_iÖ_x001C_ÂU³xÆ _x0000_1_x0000_+º_x000C__x0000__x0000_031-385-1222_x000C__x0000__x0000_031-388-3477_x0005__x0000__x0000_13958_x0016__x0000__x0001_½¬0® _x0000_HÅÅÜÂ _x0000_Ì¹HÅl­ _x0000__x0008_Æ Âõ¬ÐÆ\¸5_x0000_2_x0000_¼8® _x0000_2_x0000__x000D__x0000__x0000_010-3176-9037_x0013__x0000__x0000_bill@cssports.co.kr_x000D__x0000__x0000_010-2727-2718_x000F__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_5_x0000_+_x0000_3_x0000_._x0000_5_x0000__x000E__x0000__x0000_37690004598437_x0006__x0000__x0000_D00311
+_x0000__x0001_TÏ¬¹DÅ¤ÂìÓ Î(_x0000_ÜÂe×)_x0000_
+_x0000__x0000_3047001336_x0006__x0000__x0001_TÏ¬¹DÅ¤ÂìÓ Î_x0003__x0000__x0001_\Í_x0001_Æ_x0019_Â_x0012__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000__x0010_Ó	Í&lt;»,_x0000_xÇÄÁ&lt;»,_x0000_0®ÀÐ©ÆÔ_x000D__x0000__x0000_010-2618-5518_x000C__x0000__x0000_031-312-8982_x0007__x0000__x0001_½¬0®Ä³ _x0000_ÜÂe×ÜÂ_x0005__x0000__x0000_14922_x000F__x0000__x0001_½¬0® _x0000_ÜÂe×ÜÂ _x0000_@ÇÄ¬¼_x0001_Æ8® _x0000_2_x0000_7_x0000__x000F__x0000__x0001_3_x0000_0_x0000_3_x0000_8Ö(_x0000_@ÇÕÙ³,_x0000_ _x0000_ÜÂðÒ_x000C_ÓlÐ)_x0000__x0015__x0000__x0000_queenmt5518@naver.com_x000C__x0000__x0000_031-404-6121_x0008__x0000__x0000_20170220_x000E__x0000__x0000_37690004600637_x0006__x0000__x0000_D00312_x000E__x0000__x0001_Æ%±¤Â(_x0000_Y_x0000_O_x0000_N_x0000_E_x0000_X_x0000_)_x0000_ _x0000_tÇÌ_x0010_È
+_x0000__x0000_1052641553_x0003__x0000__x0001_$Ç ÇÄÉ_x000C__x0000__x0000_031-631-2210_x0007__x0000__x0001_½¬0®Ä³ _x0000_tÇÌÜÂ_x0005__x0000__x0000_17362_x0017__x0000__x0001_½¬0®Ä³ _x0000_tÇÌÜÂ _x0000_`Å(¸_x0015_È\¸ _x0000_1_x0000_4_x0000_2_x0000_ _x0000_ _x0000_(_x0000_=Ì_x0004_ÈÙ³)_x0000__x000D__x0000__x0000_010-3459-1313_x0010__x0000__x0000_jin7601@daum.net_x0003__x0000__x0001_\Í_x0015_¬8Ö_x0008__x0000__x0000_20170221_x000E__x0000__x0000_37690004601237_x0006__x0000__x0000_D00324_x0006__x0000__x0001__x000C_Ó¸Ò_x0008_±¤ÂìÓ Î
+_x0000__x0000_1272471368_x0003__x0000__x0001_@®©Æ`Å_x000C__x0000__x0000_031-398-8953_x000C__x0000__x0000_031-398-8954_x0007__x0000__x0001_½¬0®Ä³ _x0000_p­ìÓÜÂ_x0005__x0000__x0000_15833_x0016__x0000__x0001_½¬0®Ä³ _x0000_p­ìÓÜÂ _x0000_$Æ_x0008_®\¸ _x0000_1_x0000_5_x0000_0_x0000_ _x0000_ _x0000_(_x0000__x0008_®_x0015_ÈÙ³)_x0000_	_x0000__x0001_1_x0000_0_x0000_2_x0000_8Ö(_x0000__x0008_®_x0015_ÈÙ³)_x0000__x000D__x0000__x0000_010-4854-8953_x0010__x0000__x0000_kya5767@nate.com_x0008__x0000__x0000_20170320_x000E__x0000__x0000_37690004603537_x0006__x0000__x0000_D00328_x0006__x0000__x0001_ÄÉüÈ0¼Ü´ü»4Ñ
+_x0000__x0000_6131082729_x0003__x0000__x0001__x0015_È Ìä¬_x000C__x0000__x0000_055-747-2101_x0008__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_ÄÉüÈÜÂ_x0005__x0000__x0000_52806_x0019__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_ÄÉüÈÜÂ _x0000_Á-¼\¸7_x0000_5_x0000_¼8® _x0000_8_x0000_ _x0000_ _x0000_(_x0000_ÁÀÉÓÙ³)_x0000__x000D__x0000__x0000_010-9612-2188_x0011__x0000__x0000_jcg2188@naver.com_x000B__x0000__x0000_01095082188_x0008__x0000__x0000_20170324_x000E__x0000__x0000_37690004604137_x0006__x0000__x0000_D00338
+_x0000__x0001_Æ%±¤Â=ÌÐÆ_x0010_È(_x0000_øÂtÎ)_x0000_
+_x0000__x0000_6092352584_x0003__x0000__x0001_HÅ¬Çü­_x0010__x0000__x0001_¤ÂìÓ Î _x0000_XÇX¹ _x0000__x000F_¼ _x0000_©ÆÔ _x0000_È¹lÐ_x001C_ÈÇ_x0008__x0000__x0000_20170411_x000C__x0000__x0000_055-261-0123_x0005__x0000__x0000_51420_x0019__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_=ÌÐÆÜÂ _x0000_1Á°Àl­ _x0000__x0018_¼ÀÉ\¸ _x0000_8_x0000_ _x0000_ _x0000_(_x0000__x0018_¼ÀÉÙ³)_x0000__x0005__x0000__x0001_(_x0000__x0018_¼ÀÉÙ³)_x0000__x000D__x0000__x0000_010-9796-1346_x0011__x0000__x0000_cwssaka@naver.com
+_x0000__x0000_0552610123_x000E__x0000__x0000_37690004606437_x0006__x0000__x0000_D00382_x0004__x0000__x0001_$Æ¤ÂìÓ Î
+_x0000__x0000_2860500614_x0003__x0000__x0001__x0015_¼Á|·_x000C__x0000__x0001__x0004_ÈÇÁÀp¬·(_x0000_¤ÂìÓ Î©ÆÔ)_x0000__x000C__x0000__x0000_063-231-0360_x0005__x0000__x0000_54947_x0015__x0000__x0001__x0004_È½ _x0000__x0004_ÈüÈÜÂ _x0000_DÆ°Àl­ _x0000__x0004_È|·_x0010_¬_x0001_Æ\¸ _x0000_4_x0000_0_x0000_-_x0000_1_x0000__x000B__x0000__x0000_01076785147_x0014__x0000__x0000_sora1976kr@naver.com_x0003__x0000__x0001__x0015_¼Ñ¼%ÆQ_x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_+_x0000_1_x0000_0_x0000_0_x0000_ _x0000_/_x0000_ _x0000_2_x0000_5_x0000_S_x0000_S_x0000_ _x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_ _x0000_+_x0000_ _x0000_1_x0000_0_x0000_0_x0000_ _x0000_/_x0000_ _x0000_ _x0000_2_x0000_4_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_ _x0000_/_x0000_ _x0000_2_x0000_4_x0000_S_x0000_S_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_ _x0000_/_x0000_ _x0000_2_x0000_3_x0000_F_x0000_W_x0000_ _x0000__x0018_ÂüÈ _x0000_ìÅàÂ _x0000_1_x0000_2_x0000__x0008__x0000__x0000_20170710_x000E__x0000__x0000_37690004610337_x0006__x0000__x0000_D00392_x0007__x0000__x0001_¨Ö1Á+ÈiÕ¤ÂìÓ Î
+_x0000__x0000_7521600607_x0002__x0000__x0001_@®_x0004_½_x0008__x0000__x0000_20170812_x000C__x0000__x0000_064-733-2992_x0005__x0000__x0000_63591_x0013__x0000__x0001__x001C_ÈüÈ¹ÒÄ¼ÇXÎÄ³ _x0000__x001C_ÁÀ­ìÓÜÂ _x0000_Ù³8»\¸ _x0000_3_x0000_0_x0000__x000B__x0000__x0000_01090156265_x0010__x0000__x0000_ddadon@naver.com_x000B__x0000__x0000_01036928845_x0008__x0000__x0000_20170821_x000E__x0000__x0000_37690004611037_x0006__x0000__x0000_D00396_x000E__x0000__x0001_Æ%±¤Â _x0000_Å°À_x0010_È(_x0000_TÖ·¤ÂìÓ Î)_x0000_
+_x0000__x0000_6211383962_x0003__x0000__x0001_\ÍiÖðÅ_x0008__x0000__x0000_20170813_x000C__x0000__x0000_055-382-6688_x000C__x0000__x0000_055-366-6648_x0005__x0000__x0000_50548_x000F__x0000__x0001_½¬¨° _x0000_Å°ÀÜÂ _x0000_ÅÆÁÀ_x0000_³\¸ _x0000_9_x0000_6_x0000_1_x0000__x0007__x0000__x0001_Æ%±¤Â _x0000_Å°À_x0010_È_x000D__x0000__x0000_010-9323-8281_x0016__x0000__x0000_eegmom0808@hanmail.net_x0008__x0000__x0000_20170915_x000E__x0000__x0000_37690004612637_x0006__x0000__x0000_D00408_x0005__x0000__x0001_l­¬¹TÏ¸Ò\¸
+_x0000__x0000_1321920436_x0003__x0000__x0001_àÂ_x0001_Æ8Ö_x0008__x0000__x0000_20060509_x000C__x0000__x0000_031-562-3307_x0005__x0000__x0000_11942_x0012__x0000__x0001_½¬0®Ä³ _x0000_¨°ÅüÈÜÂ _x0000__x0000_¬´Æ\¸2_x0000_8® _x0000_1_x0000_1_x0000_4_x0000__x000D__x0000__x0001_ø»1Á_x0004_Õ|·Ç _x0000_1_x0000_5Î _x0000_1_x0000_0_x0000_3_x0000_8Ö_x000D__x0000__x0000_010-3909-6608_x0015__x0000__x0000_sjs940421@hanmail.net_x000B__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_2_x0000_6_x0000__x0008__x0000__x0000_20171226_x000E__x0000__x0000_37690004615537_x0006__x0000__x0000_D00409_x0007__x0000__x0001_Æ%±¤Â _x0000_¤ÂìÓ Î
+_x0000__x0000_8624500277_x0003__x0000__x0001_tÇU³©Æ_x0008__x0000__x0000_20170905_x000C__x0000__x0000_041-357-1617_x0008__x0000__x0001_©Í­Ì¨°Ä³ _x0000_ù²ÄÉÜÂ_x0005__x0000__x0000_31777_x000E__x0000__x0001_©Í¨° _x0000_ù²ÄÉÜÂ _x0000_P­Ù³8® _x0000_1_x0000_2_x0000_4_x0000__x000D__x0000__x0000_010-3116-9915_x0013__x0000__x0000_ljy161617@naver.com_x0008__x0000__x0000_20171221_x000E__x0000__x0000_37690004616137_x0006__x0000__x0000_D00416_x0005__x0000__x0001__x001C_ÁÄÉ¤ÂìÓ Î
+_x0000__x0000_5920100957_x0003__x0000__x0001_@®ÉÓÜÐ_x000D__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_ _x0000__x0004_ÈÇÁÀp¬·ÅÅ_x0008__x0000__x0000_20180301_x000C__x0000__x0000_031-236-4936_x000C__x0000__x0000_031-216-4936_x0007__x0000__x0001_½¬0®Ä³ _x0000_©ÆxÇÜÂ_x0005__x0000__x0000_16833_x0013__x0000__x0001_½¬0® _x0000_©ÆxÇÜÂ _x0000__x0018_ÂÀÉl­ _x0000_ìÓ@Ç_x0000_³\¸ _x0000_4_x0000_6_x0000_7_x0000__x0016__x0000__x0001__x0018_ÂÀÉxÔt¹ÀÉ$ÆÔÆÜ´È¹lÐÁÀ_x0000_¬ _x0000_1_x0000_0_x0000_3_x0000_Ù³ _x0000_1_x0000_2_x0000_3_x0000_8Ö_x000D__x0000__x0000_010-4679-5630_x0013__x0000__x0000_ren7303@hanmail.net_x000E__x0000__x0000_37690004618437_x0006__x0000__x0000_D00431_x0006__x0000__x0001_¤ÂìÓ Îä¹È²DÅ
+_x0000__x0000_2701201033_x0003__x0000__x0001_8»¹ÂÄÉ_x0008__x0000__x0000_20180615_x000C__x0000__x0000_042-545-8511	_x0000__x0001__x0000_³_x0004_È_x0011_­íÅÜÂ _x0000_ Ç1Ál­_x0005__x0000__x0000_34210_x0016__x0000__x0001__x0000_³_x0004_È _x0000_ Ç1Ál­ _x0000_YÕXÕ_x0011_ÉYÅ\¸1_x0000_2_x0000_8_x0000_¼8® _x0000_2_x0000_3_x0000_-_x0000_8_x0000__x000B__x0000__x0001_1_x0000_0_x0000_2_x0000_8Ö _x0000_¤ÂìÓ Îä¹È²DÅ_x000D__x0000__x0000_010-6683-2114_x0013__x0000__x0000_capmoon39@naver.com_x0008__x0000__x0000_20180427_x000E__x0000__x0000_37690004623037_x0006__x0000__x0000_D00433_x000D__x0000__x0001__x0015_È_x0018_Â¤ÂìÓ Î _x0000_Æ%±¤Â _x0000__x0001_ÆüÈ_x0010_È
+_x0000__x0000_5293300343_x0003__x0000__x0001_@®Ù³ðÅ	_x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_ _x0000_XÇX¹_x0008__x0000__x0000_20170407_x000B__x0000__x0000_01048177736
+_x0000__x0000_0546367233_x0008__x0000__x0001_½¬ÁÀ½Ä³ _x0000__x0001_ÆüÈÜÂ_x0005__x0000__x0000_36138_x0013__x0000__x0001_½¬½ _x0000__x0001_ÆüÈÜÂ _x0000__x0000_³YÕ\¸2_x0000_0_x0000_1_x0000_¼8® _x0000_8_x0000_-_x0000_6_x0000__x0007__x0000__x0001_iÖ_x0008_®L¾)µ _x0000_1_x0000_5Î_x000D__x0000__x0000_010-4817-7736_x0013__x0000__x0000_kdy9249@hanmail.net_x0008__x0000__x0000_20180518_x000E__x0000__x0000_37690004624637_x0006__x0000__x0000_D00471_x000B__x0000__x0001_(_x0000_üÈ)_x0000_DÅüÈ_x0008_¸ìÓ Î__x0000_¹Ò_x0010_Ó_x000B__x0000__x0001_(_x0000_üÈ)_x0000_DÅüÈ_x0008_¸ìÓ Î-_x0000_¹Ò_x0010_Ó_x0008__x0000__x0000_20181026_x000B__x0000__x0000_02-489-1992_x000E__x0000__x0001_½¬0® _x0000__x0011_­üÈÜÂ _x0000_à¬½\¸ _x0000_3_x0000_4_x0000_0_x0000__x000D__x0000__x0000_070-4741-9644_x000E__x0000__x0000_37690004626937_x0006__x0000__x0000_D00490	_x0000__x0001_à¬ÅÜÂ0¼Ü´ü»4Ñ_x0011_ÖÖ
+_x0000__x0000_1288284226_x0003__x0000__x0001_tÇ8ÖÄÉ_x0008__x0000__x0000_20190315_x000B__x0000__x0000_01027161641_x0005__x0000__x0000_10223_x0014__x0000__x0001_½¬0® _x0000_à¬ÅÜÂ _x0000_|Ç°À_x001C_Ál­ _x0000__x0011_ÉYÅ\¸ _x0000_1_x0000_6_x0000_0_x0000_1_x0000__x001D__x0000__x0001_,_x0000_ _x0000_1_x0000_5Î(_x0000__x0000_³TÖÙ³,_x0000_ _x0000_à¬ÅÜÂ+ÈiÕ´ÆÙ³¥Ç _x0000_ÀÉXÕ1_x0000_5Î _x0000_C_x0000_-_x0000_0_x0000_8_x0000_)_x0000__x000D__x0000__x0000_010-2716-1641_x0012__x0000__x0000_76melany@gmail.com_x0005__x0000__x0000_19003_x0003__x0000__x0001_HÅ¬Ç°Æ_x000E__x0000__x0000_37690004628137_x0006__x0000__x0000_D00503_x0005__x0000__x0001_°tÇ¤Âü»4Ñ
+_x0000__x0000_6161951553_x0003__x0000__x0001_à¬ðÅüÈ
+_x0000__x0001_¤ÂìÓ Î©ÆÔ_x000F_¼0®ÀÐ©ÆÔ_x0008__x0000__x0000_20100913_x000C__x0000__x0000_064-712-4524_x000C__x0000__x0000_064-711-4524_x000B__x0000__x0001__x001C_ÈüÈ¹ÒÄ¼ÇXÎÄ³ _x0000__x001C_ÈüÈÜÂ_x0005__x0000__x0000_63087_x0013__x0000__x0001__x001C_ÈüÈ¹ÒÄ¼ÇXÎÄ³ _x0000__x001C_ÈüÈÜÂ _x0000_ÄÉp­8® _x0000_1_x0000_-_x0000_6_x0000__x000D__x0000__x0000_010-3639-7899_x0011__x0000__x0000_ktf1974@naver.com_x0003__x0000__x0001_@®1Át¬_x000B__x0000__x0000_01036397899_x0008__x0000__x0000_20190424_x000E__x0000__x0000_37690004630837_x0006__x0000__x0000_D00504_x0008__x0000__x0001_¤ÂÀÐ¤ÂìÓ Î__x0000_¹Ò_x0010_Ó
+_x0000__x0000_3031310445	_x0000__x0001_¤ÂÀÐ¤ÂìÓ Î(_x0000_©ÍüÈ)_x0000__x0003__x0000__x0001_LÇ_x0011_­l×_x0008__x0000__x0000_20070607_x000C__x0000__x0000_043-855-7688_x000C__x0000__x0000_043-848-3727_x0008__x0000__x0001_©Í­Ì½Ä³ _x0000_©ÍüÈÜÂ_x0005__x0000__x0000_27393_x000E__x0000__x0001_©Í½ _x0000_©ÍüÈÜÂ _x0000__x0015_Ö$Á\¸ _x0000_1_x0000_5_x0000_9_x0000__x0005__x0000__x0001_¤ÂÀÐ¤ÂìÓ Î_x000D__x0000__x0000_010-5303-1397_x0013__x0000__x0000_ekh3083@hanmail.net_x0006__x0000__x0000_D00513	_x0000__x0001__x001C_Á¸ÆÜÂ´Ì!ÇÖ__x0000_¹Ò_x0010_Ó
+_x0000__x0000_6078287556_x0006__x0000__x0001__x001C_Á¸ÆÜÂ´Ì!ÇÖ_x0003__x0000__x0001__x0015_¼ÐÆ_x001C_Â_x0003__x0000__x0001__x001C_ÁD¾¤Â_x0004__x0000__x0001_LÑÈ²¤Â¥Ç_x0008__x0000__x0000_20190614_x0001__x0000__x0000_0	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x0011_É·l­_x0005__x0000__x0000_02119_x000E__x0000__x0001__x001C_Á¸Æ _x0000__x0011_É·l­ _x0000_Ý¹°Æ\¸ _x0000_1_x0000_8_x0000_2_x0000__x0008__x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ´Ì!ÇÖ_x0008__x0000__x0000_20190617_x000E__x0000__x0000_37690004638937_x0006__x0000__x0000_D00515_x0004__x0000__x0001__x0001_Æ4»S_x0000_P_x0000_
+_x0000__x0000_4081497216_x0004__x0000__x0001__x0001_Æ4»s_x0000_p_x0000__x0003__x0000__x0001_@®U³	½_x0007__x0000__x0001_Ä³Áä¹,_x0000_ _x0000__x001C_ÈpÈ_x0011__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_ _x0000_±tÇ0®l­,_x0000_ _x0000_ìÕ¤Â0®l­_x0008__x0000__x0000_20070824_x000D__x0000__x0000_010-3622-7289_x000C__x0000__x0000_062-651-9942_x0008__x0000__x0001__x0011_­üÈ_x0011_­íÅÜÂ _x0000_¨°l­_x0005__x0000__x0000_61655_x000E__x0000__x0001__x0011_­üÈ _x0000_¨°l­ _x0000__x0000_³¨°_x0000_³\¸ _x0000_2_x0000_5_x0000_2_x0000_	_x0000__x0001_1¼´ÆÙ³,_x0000_ _x0000__x0001_Æ4»S_x0000_P_x0000__x0013__x0000__x0000_6519944@hanmail.net_x000D__x0000__x0000_(062)653-4141$_x0000__x0001_2_x0000_4_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_3_x0000_5_x0000_ _x0000_/_x0000_2_x0000_4_x0000_S_x0000_S_x0000__x0018_ÂüÈìÅàÂ _x0000_3_x0000_5_x0000_ _x0000_/_x0000_ _x0000__x0018_Â_x0008_®½qÈ _x0000_2_x0000_ÔÆµÑ_x001C_È_x0008__x0000__x0000_20190531_x000E__x0000__x0000_37690004634337_x0006__x0000__x0000_D00517_x000B__x0000__x0001_O_x0000_K_x0000_ _x0000_¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1293177008_x0003__x0000__x0001_tÇ_x0001_Æ±Æ
+_x0000__x0001_Ä³Áä¹,_x0000_Ä³ä¹,_x0000__x001C_ÁD¾¤Â_x0011__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_l­ä¹_x0000_³Õ,_x0000_t¬&lt;»­ÌÁ©ÆíÅ_x0008__x0000__x0000_20071108_x000C__x0000__x0000_031-708-3066
+_x0000__x0000_0317083067_x0005__x0000__x0000_13504_x0017__x0000__x0001_½¬0® _x0000_1Á¨°ÜÂ _x0000_½ù²l­ _x0000_¥Çø»\¸1_x0000_2_x0000_2_x0000_¼8® _x0000_3_x0000_-_x0000_1_x0000__x0005__x0000__x0001_(_x0000_|ÅÑÐÙ³)_x0000__x000D__x0000__x0000_010-8714-3324_x0014__x0000__x0000_75winwin@hanmail.net_x000B__x0000__x0000_01087143324_x000E__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_5_x0000_+_x0000_2_x0000_2_x0000__x0008__x0000__x0000_20190621_x000E__x0000__x0000_37690004635037_x0006__x0000__x0000_D00519_x0005__x0000__x0001__x0004_Ç_x0008_±¤ÂìÓ Î
+_x0000__x0000_3160449978_x0003__x0000__x0001_\Í_x0004_ÖÄÉ_x0008__x0000__x0000_20140927_x000D__x0000__x0000_010-6482-0228_x000C__x0000__x0000_041-665-1857_x0008__x0000__x0001_©Í­Ì¨°Ä³ _x0000__x001C_Á°ÀÜÂ_x0005__x0000__x0000_31993_x000F__x0000__x0001_©Í¨° _x0000__x001C_Á°ÀÜÂ _x0000_(ÇÀÉ1_x0000_6_x0000_\¸ _x0000_2_x0000_2_x0000__x0008__x0000__x0001_C_x0000_Ù³ _x0000_(_x0000_Ù³8»Ù³)_x0000__x0011__x0000__x0000_chj1981@naver.com_x000D__x0000__x0000_010-9112-9996_x0008__x0000__x0001_6_x0000_ÔÆ _x0000_üÈ8»µÑ_x001C_È/_x0000__x0008__x0000__x0000_20190620_x000E__x0000__x0000_37690004636637_x0006__x0000__x0000_D00524
+_x0000__x0001_üÈÝÂÖ¬À _x0000_©ÆxÇÆ%±¤Â
+_x0000__x0000_7968702997_x0003__x0000__x0001_@®ÄÉ©Æ_x0008__x0000__x0000_20150409_x000D__x0000__x0000_010-8881-0413_x0005__x0000__x0000_16967_x0014__x0000__x0001_½¬0® _x0000_©ÆxÇÜÂ _x0000_0®e×l­ _x0000_àÂ_x0008_¬\¸5_x0000_7_x0000_¼8® _x0000_7_x0000_
+_x0000__x0001_(_x0000_àÂ_x0008_¬Ù³,_x0000_ÐÅ¤Â_x001C_ÈtÇ)_x0000__x0013__x0000__x0000_goodester@naver.com_x0007__x0000__x0001_2_x0000_ÔÆ _x0000__x0018_Â_x0008_®µÑ_x001C_È_x0008__x0000__x0000_20190711_x000E__x0000__x0000_37690004640537_x0006__x0000__x0000_D00526_x0006__x0000__x0001_ìÅ_x0018_Â _x0000_Æ%±¤Â
+_x0000__x0000_6765400493_x0003__x0000__x0001_@® ÁU³_x0008__x0000__x0000_20190701_x000D__x0000__x0000_010-2066-5376_x0008__x0000__x0001__x0004_È|·¨°Ä³ _x0000_ìÅ_x0018_ÂÜÂ_x0005__x0000__x0000_59685_x000D__x0000__x0001__x0004_È¨° _x0000_ìÅ_x0018_ÂÜÂ _x0000_ÈÀ0Ñ\¸ _x0000_2_x0000_5_x0000__x0005__x0000__x0001_(_x0000_àÂ0®Ù³)_x0000__x0014__x0000__x0000_junsoo5376@naver.com_x0003__x0000__x0001_@®_x0000_É_x0018_Â_x0002__x0000__x0001__x0000_¬qÈ_x000E__x0000__x0000_37690004621737_x0006__x0000__x0000_D00527_x000C__x0000__x0001_(_x0000_üÈ)_x0000_tÇÐÅ¤Â¤ÂìÓ Î__x0000_¹Ò_x0010_Ó
+_x0000__x0000_2848100873	_x0000__x0001_(_x0000_üÈ)_x0000_tÇÐÅ¤Â¤ÂìÓ Î_x0003__x0000__x0001__x0015_¼_x0018_Â Ì_x000C__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_ _x0000_µÑàÂ_x0010_Óä¹ÅÅ_x0008__x0000__x0000_20171228_x000C__x0000__x0000_031-763-2002_x000C__x0000__x0000_031-763-0400_x0005__x0000__x0000_12739_x000D__x0000__x0001_½¬0® _x0000__x0011_­üÈÜÂ _x0000_µÑø»\¸ _x0000_9_x0000_2_x0000__x000D__x0000__x0000_010-4085-9292_x0014__x0000__x0000_gysports@hanmail.net_x0008__x0000__x0000_20190725_x000E__x0000__x0000_37690004641137_x0006__x0000__x0000_D00528_x0007__x0000__x0001_2_x0000_0_x0000_8_x0000_0_x0000_Æ%±¤Â
+_x0000__x0000_8131601217_x0003__x0000__x0001_@®ÀÉÐÆ_x000C__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_ _x0000_¤ÂìÓ ÎXÇX¹_x000C__x0000__x0000_061-795-2088_x0008__x0000__x0001__x0004_È|·¨°Ä³ _x0000__x0011_­ÅÜÂ_x0005__x0000__x0000_57767_x0010__x0000__x0001__x0004_È¨° _x0000__x0011_­ÅÜÂ _x0000_ÀÉÙ³8® _x0000_3_x0000_0_x0000_-_x0000_3_x0000_5_x0000__x000D__x0000__x0000_010-9434-2223_x0013__x0000__x0000_3530162@hanmail.net_x0008__x0000__x0000_20190730_x000E__x0000__x0000_37690004643437_x0006__x0000__x0000_D00529	_x0000__x0001_°Æ¬¹¤ÂìÓ Î(_x0000__x0011_­üÈ)_x0000_
+_x0000__x0000_5212100399_x0003__x0000__x0001_$Æ_x0018_ÂÔÆ_x0008__x0000__x0000_20191030_x000C__x0000__x0000_062-434-8963_x0008__x0000__x0001__x0011_­üÈ_x0011_­íÅÜÂ _x0000_½l­_x0005__x0000__x0000_61185_x0018__x0000__x0001__x0011_­üÈ _x0000_½l­ _x0000_¨Ìè²ðÅàÂ\¸ _x0000_2_x0000_9_x0000_¼8® _x0000_1_x0000_5_x0000_ _x0000_ÀÉÁÀ1_x0000_5Î_x000D__x0000__x0001_½l­+ÈiÕ´Ì!Ç_x0000_­ _x0000_´Ì!Ç©ÆÔ_x0010_È_x000D__x0000__x0000_010-4614-9599_x000F__x0000__x0000_19qkqn@daum.net_x000B__x0000__x0000_01046149599_x000D__x0000__x0001_2_x0000_6_x0000_F_x0000_W_x0000_ _x0000_©ÆÔ_x0018_ÂüÈ _x0000_ø»8ÌìÅ_x0008__x0000__x0000_20190802_x000E__x0000__x0000_37690004642837_x0006__x0000__x0000_D00530_x000B__x0000__x0001_àÂàÂ´Ì!Ç¬À _x0000_2_x0000_1_x0000___x0000_¹Ò_x0010_Ó
+_x0000__x0000_1288148960_x000B__x0000__x0001_üÈÝÂÖ¬À _x0000_àÂàÂ´Ì!Ç2_x0000_1_x0000__x0003__x0000__x0001_iÖ¹Â8Ö_x0002__x0000__x0001__x001C_ÈpÈ_x0008__x0000__x0000_20000523
+_x0000__x0000_0319453376
+_x0000__x0000_0319450458_x0005__x0000__x0000_10844_x0013__x0000__x0001_½¬0® _x0000__x000C_ÓüÈÜÂ _x0000_ÔÆq¸tº _x0000_¬_x0014_¼_x0004_Ç8® _x0000_1_x0000_2_x0000_3_x0000__x0006__x0000__x0001_àÂàÂ´Ì!Ç$ÁD¾_x0014__x0000__x0000_sinsin5980@naver.com_x0008__x0000__x0000_20190823_x000E__x0000__x0000_37690004645737_x0006__x0000__x0000_D00534
+_x0000__x0001_2_x0000_0_x0000_1_x0000_9_x0000_ _x0000_TÏ¬¹DÅ$Æ_x0008_Õ
+_x0000__x0000_0000000000	_x0000__x0000_023352551_x0005__x0000__x0000_03964_x000E__x0000__x0001_</v>
           </cell>
           <cell r="G35" t="str">
-            <v>서대문요넥스</v>
-          </cell>
-          <cell r="H35" t="str">
-            <v>윤태진</v>
-          </cell>
-          <cell r="I35" t="str">
-            <v>도소매업</v>
-          </cell>
-          <cell r="J35" t="str">
-            <v>의류</v>
-          </cell>
-          <cell r="K35" t="str">
-            <v>20081029</v>
+            <v>Ì¹Å\¸1_x0000_8® _x0000_3_x0000__x0008__x0000__x0001_ÀÉ5Î _x0000_(_x0000_ÁÀÄ³Ù³)_x0000__x000D__x0000__x0000_010-2942-3235_x0019__x0000__x0000_sejinsports2018@naver.com_x0017__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000_ _x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_9_x0000_3_x0000_-_x0000_&gt;_x0000_5_x0000_0_x0000_ _x0000_&lt;Ç\¸ _x0000_pÈ_x0015_È_x000E__x0000__x0000_37690004480837_x001A__x0000__x0001_0_x0000_1_x0000_0_x0000_ _x0000_2_x0000_7_x0000_0_x0000_5_x0000_ _x0000_3_x0000_2_x0000_3_x0000_4_x0000_ _x0000_(_x0000_ä¹¥Ç _x0000_xÆ _x0000_A_x0000_S_x0000_ô²ù²Ç)_x0000__x0006__x0000__x0000_D00089_x0006__x0000__x0001_Á_x0008_Í0¼Ü´ü»4Ñ
+_x0000__x0000_2270299081_x0003__x0000__x0001__x0015_È¬ÇÈÖ_x000C__x0000__x0000_033-638-0024
+_x0000__x0000_0336382400_x0007__x0000__x0001__x0015_¬ÐÆÄ³ _x0000_Á_x0008_ÍÜÂ_x0006__x0000__x0000_217803_x000E__x0000__x0001__x0015_¬ÐÆÄ³ _x0000_Á_x0008_ÍÜÂ _x0000_P­Ù³\¸ _x0000_3_x0000_9_x0000__x000D__x0000__x0000_010-3297-3133_x0019__x0000__x0000_yubgijung1257@hanmail.net_x000E__x0000__x0000_37690004481437_x0006__x0000__x0000_D00090_x000B__x0000__x0001_üÈÝÂÖ¬À _x0000_¤Âä¹lÂ¤ÂìÓ Î
+_x0000__x0000_8558703276_x0006__x0000__x0001_¤Âä¹lÂ¤ÂìÓ Î_x0003__x0000__x0001_$ÇÜ­ø»_x0008__x0000__x0000_20070917_x000B__x0000__x0000_01087511199_x0007__x0000__x0001_½¬0®Ä³ _x0000_HÅ°ÀÜÂ_x0005__x0000__x0000_15497_x0012__x0000__x0001_½¬0® _x0000_HÅ°ÀÜÂ _x0000_ÁÀ]¸l­ _x0000_Ì8»4_x0000_8® _x0000_1_x0000_7_x0000__x001A__x0000__x0001_1_x0000_5Î1_x0000_5_x0000_1_x0000_9_x0000_-_x0000_1_x0000_3_x0000_ _x0000_ _x0000_1_x0000_5Î _x0000_ _x0000_¤Âä¹lÂ¤ÂìÓ Î _x0000_&lt;»X¹&lt;Á0Ñ_x000D__x0000__x0000_010-5471-3330_x0013__x0000__x0000_smash-123@naver.com_x000B__x0000__x0000_01054713330_x000E__x0000__x0000_37690004483737_x0008__x0000__x0001_!Ç1Á_x0010_È&amp;_x0000_1_x0000_0_x0000_0_x0000_%_x0000__x0006__x0000__x0000_D00096_x0005__x0000__x0001_¤ÂìÓ ÎE¼lÐ
+_x0000__x0000_1272092161_x0003__x0000__x0001_@®ÄÉÉÓ_x0004__x0000__x0001_´Ì!Ç©ÆÔ_x0008__x0000__x0000_20070503_x000C__x0000__x0000_031-535-1244
+_x0000__x0000_0315352245_x0007__x0000__x0001_½¬0®Ä³ _x0000_ìÓÌÜÂ_x0006__x0000__x0000_487050_x0018__x0000__x0001_½¬0®Ä³ _x0000_ìÓÌÜÂ _x0000_p­´°tº _x0000_8Öm­\¸ _x0000_1_x0000_6_x0000_9_x0000_6_x0000_._x0000_ _x0000_2_x0000_5Î_x000D__x0000__x0000_010-6354-5471_x0011__x0000__x0000_kjp31@hanmail.net_x000E__x0000__x0000_37690004487237_x0006__x0000__x0000_D00097_x0005__x0000__x0001_¹Â¬¹¤ÂìÓ Î
+_x0000__x0000_2011081473_x0003__x0000__x0001_à¬Ñ¼°Æ_x0008__x0000__x0000_20071221_x000C__x0000__x0000_02-2279-0779
+_x0000__x0000_0222780778_x0005__x0000__x0000_04563_x001E__x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x0011_Él­ _x0000_­ÌÄ¬Ì\¸ _x0000_2_x0000_4_x0000_6_x0000_ _x0000_ _x0000_(_x0000_)¼°ÀÙ³,_x0000_ _x0000_ÉÓTÖÜÂ¥Ç)_x0000__x0016__x0000__x0001_1_x0000_,_x0000_2_x0000_,_x0000_3_x0000_5Î _x0000_ä²-_x0000_1_x0000_0_x0000_2_x0000_(_x0000_)¼°ÀÙ³,_x0000_ÉÓTÖÜÂ¥Ç)_x0000__x000D__x0000__x0000_010-3284-7383_x0019__x0000__x0000_victorysports@hanmail.net_x000E__x0000__x0000_37690004488937_x0006__x0000__x0000_D00101_x0005__x0000__x0001_DÅ°À¤ÂìÓ Î
+_x0000__x0000_3122872982_x0003__x0000__x0001_\Í+È¼¹_x000C__x0000__x0001_Ä³ä¹_x000F_¼ÁÀÔ_x0011_É_x001C_¬ÅÅ,_x0000_Áä¹ÅÅ_x0008__x0000__x0000_20110701_x000C__x0000__x0000_041-532-8381
+_x0000__x0000_0415328382_x0008__x0000__x0001_©Í­Ì¨°Ä³ _x0000_DÅ°ÀÜÂ_x0006__x0000__x0000_336050_x0010__x0000__x0001_©Í­Ì¨°Ä³ _x0000_DÅ°ÀÜÂ _x0000_ÜÂü»\¸ _x0000_2_x0000_5_x0000_1_x0000__x000D__x0000__x0000_010-4946-8385_x0013__x0000__x0000_judocjl@hanmail.net_x000E__x0000__x0000_37690004490537_x0006__x0000__x0000_D00109_x0008__x0000__x0001__x0001_Æ¤ÂìÓ Î(_x0000_¨°ÐÆ)_x0000_
+_x0000__x0000_1095289131_x0003__x0000__x0001_tÇ_x0015_ÈÌ_x0008__x0000__x0000_20071119_x000C__x0000__x0000_063-632-4154
+_x0000__x0000_0636324156_x0005__x0000__x0000_55703_x0015__x0000__x0001__x0004_È|·½Ä³ _x0000_¨°ÐÆÜÂ _x0000_¬Àä¹tº _x0000__x0000_³¬À\¸ _x0000_1_x0000_2_x0000_8_x0000_3_x0000__x0004__x0000__x0001__x0001_Æ¤ÂìÓ Î_x000D__x0000__x0000_010-4594-0634_x0013__x0000__x0000_jclee8734@naver.com_x000E__x0000__x0000_37690004497037_x0006__x0000__x0000_D00110_x0007__x0000__x0001_Æ%±¤Â _x0000_TÖ_x001C_Â_x0010_È
+_x0000__x0000_4080577085_x0003__x0000__x0001__x0004_È+º_x0019_Â_x0008__x0000__x0000_20071102_x000C__x0000__x0000_061-375-6647_x0008__x0000__x0001__x0004_È|·¨°Ä³ _x0000_TÖ_x001C_Âp­_x0006__x0000__x0000_519809_x0014__x0000__x0001__x0004_È|·¨°Ä³ _x0000_TÖ_x001C_Âp­ _x0000__x0011_­U³\¸ _x0000_1_x0000_4_x0000_0_x0000_ _x0000_ _x0000_1_x0000_5Î_x000D__x0000__x0000_010-6632-5893_x0012__x0000__x0000_ms-jon@hanmeil.net_x000E__x0000__x0000_37690004498637_x0006__x0000__x0000_D00111_x000C__x0000__x0001_,Æ¼¹=Õ+ÈiÕ¤ÂìÓ Î(_x0000_©ºìÓ)_x0000_
+_x0000__x0000_4111469486_x0003__x0000__x0001_@®=Ì©Æ_x000C__x0000__x0001_´ÆÙ³©ÆÔ,_x0000_ñ´°Àl­,_x0000_0®P±Ô_x0008__x0000__x0000_20070320_x000C__x0000__x0000_061-242-1032
+_x0000__x0000_0612443032_x0008__x0000__x0001__x0004_È|·¨°Ä³ _x0000_©ºìÓÜÂ_x0005__x0000__x0000_58726_x0010__x0000__x0001__x0004_È¨° _x0000_©ºìÓÜÂ _x0000_(Ì¼_x001D_Á8® _x0000_4_x0000_1_x0000_-_x0000_1_x0000__x0002__x0000__x0001_1_x0000_5Î_x000D__x0000__x0000_010-9243-4285_x0010__x0000__x0000_eyebono@daum.net_x000E__x0000__x0000_37690004499237_x0006__x0000__x0000_D00116_x000F__x0000__x0001_Æ%±¤ÂÈ¹°À_x0000_³¬¹_x0010_È(_x0000_ü»4Ñ¤ÂìÓ Î)_x0000_
+_x0000__x0000_6080288027_x0003__x0000__x0001_ Ç_x0001_Æ_x0019_Â_x0008__x0000__x0001_¤ÂìÓ Î©ÆÔ_x000F_¼XÇX¹_x000C__x0000__x0000_055-222-5431
+_x0000__x0000_0552225432_x0008__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_=ÌÐÆÜÂ_x0006__x0000__x0000_631852_x0018__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_=ÌÐÆÜÂ _x0000_È¹°ÀiÕìÓl­ _x0000_©ÆÈ¹\¸ _x0000_7_x0000_6_x0000_ _x0000_üÈÝÐ_x000D__x0000__x0000_010-3707-6245_x0016__x0000__x0000_dudtjs6245@hanmail.net_x000E__x0000__x0000_37690004504337_x0006__x0000__x0000_D00120_x0006__x0000__x0001_Æ%±¤Â­ÌüÈ_x0010_È
+_x0000__x0000_3170385854_x0003__x0000__x0001_\Í°Æ1Á_x000B__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_XÇX¹,_x0000__x0018_Ât¬_x0008__x0000__x0000_20110729_x000C__x0000__x0000_043-222-3040
+_x0000__x0000_0432245050_x0008__x0000__x0001_©Í­Ì½Ä³ _x0000_­ÌüÈÜÂ_x0006__x0000__x0000_361842_x0012__x0000__x0001_©Í½ _x0000_­ÌüÈÜÂ _x0000_ÁÀù²l­ _x0000_8Öø»\¸ _x0000_2_x0000_0_x0000_6_x0000__x0005__x0000__x0001_1_x0000_5Î _x0000_È!Î_x000D__x0000__x0000_010-5468-3319_x0015__x0000__x0000_wsung3525@hanmail.net_x0008__x0000__x0000_20080429_x000E__x0000__x0000_37690004507237_x0006__x0000__x0000_D00121_x000D__x0000__x0001_Æ%±¤ÂìÓmÕ_x0010_È(_x0000_XÕtÇlÐ¬¹´Å)_x0000_
+_x0000__x0000_5061736246_x0003__x0000__x0001__x0015_È@Ç_x0001_Æ_x0008__x0000__x0000_20090227_x000C__x0000__x0000_054-283-5234
+_x0000__x0000_0542835231_x0008__x0000__x0001_½¬ÁÀ½Ä³ _x0000_ìÓmÕÜÂ_x0006__x0000__x0000_790822_x0012__x0000__x0001_½¬½ _x0000_ìÓmÕÜÂ _x0000_¨°l­ _x0000__x0000_³Ä³Ù³ _x0000_8_x0000_6_x0000_-_x0000_2_x0000__x000D__x0000__x0000_010-4133-7770_x0014__x0000__x0000_minton1125@naver.com_x0008__x0000__x0000_20081105_x000E__x0000__x0000_37690004508937_x0006__x0000__x0000_D00122_x0005__x0000__x0001_°Æ¬¹¤ÂìÓ Î
+_x0000__x0000_4172105493_x0003__x0000__x0001__x0015_¼_x0018_ÂÄÉ_x0008__x0000__x0000_20180101_x000C__x0000__x0000_051-632-2681
+_x0000__x0000_0516322681_x0008__x0000__x0001_½°À_x0011_­íÅÜÂ _x0000_¨°l­_x0006__x0000__x0000_608827_x0011__x0000__x0001_½°À_x0011_­íÅÜÂ _x0000_¨°l­ _x0000_Ç ÇÉÓTÖ\¸ _x0000_4_x0000_9_x0000__x000D__x0000__x0000_010-2594-2682_x0015__x0000__x0000_moxie2000@hanmail.net_x000E__x0000__x0000_37690004509537_x0006__x0000__x0000_D00123_x0005__x0000__x0001_°Æ1Á¤ÂìÓ Î
+_x0000__x0000_2077003708_x0003__x0000__x0001_@®DÆÝÂ_x0008__x0000__x0000_20071009_x000B__x0000__x0000_02-465-1297	_x0000__x0000_024651197	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x0011_­ÄÉl­_x0006__x0000__x0000_143961_x0010__x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x0011_­ÄÉl­ _x0000_l­XÇ\¸ _x0000_6_x0000_6_x0000__x0014__x0000__x0001_1_x0000_5Î _x0000_(_x0000_l­XÇÙ³ _x0000_2_x0000_2_x0000_7_x0000_-_x0000_6_x0000_)_x0000_ _x0000_°Æ1Á¤ÂìÓ Î_x000D__x0000__x0000_010-3418-1230_x000F__x0000__x0000_ws418@naver.com_x000E__x0000__x0000_37690004510537_x0006__x0000__x0000_D00126_x0005__x0000__x0001_ÐÆÙ³´Ì!Ç¬À
+_x0000__x0000_3060363748_x0003__x0000__x0001_ü»Ñ¼ÁÉ_x0004__x0000__x0001_´ÆÙ³0®l­_x0008__x0000__x0000_20050705_x000C__x0000__x0000_042-531-4004
+_x0000__x0000_0425328899_x0008__x0000__x0001__x0000_³_x0004_È_x0011_­íÅÜÂ _x0000_Ù³l­_x0005__x0000__x0000_34630_x000D__x0000__x0001__x0000_³_x0004_È _x0000_Ù³l­ _x0000__x0000_³_x0004_È\¸ _x0000_7_x0000_6_x0000_5_x0000__x000D__x0000__x0000_010-5453-9536_x0012__x0000__x0000_wonspo@hanmail.net_x0008__x0000__x0000_20080214_x000E__x0000__x0000_37690004511137_x0006__x0000__x0000_D00127_x0008__x0000__x0001_ÐÆ¤ÂìÓ Î(_x0000__x001C_ÈüÈ)_x0000_
+_x0000__x0000_6160962051_x0003__x0000__x0001_@®ø»½¬_x000C__x0000__x0000_064-752-4422
+_x0000__x0000_0647232992_x000C__x0000__x0001__x001C_ÈüÈ¹ÒÄ¼ÇXÎÄ³ _x0000__x001C_ÁÀ­ìÓÜÂ_x0006__x0000__x0000_690161_x0013__x0000__x0001__x001C_ÈüÈ¹ÒÄ¼ÇXÎÄ³ _x0000__x001C_ÈüÈÜÂ _x0000_$Æ|·\¸ _x0000_1_x0000_3_x0000_4_x0000__x000D__x0000__x0000_010-4416-4412_x0015__x0000__x0000_crony0104@hanmail.net_x000E__x0000__x0000_37690004512837_x0006__x0000__x0000_D00132_x0005__x0000__x0001__x0004_ÈüÈÆ%±¤Â
+_x0000__x0000_4020887887_x0003__x0000__x0001_tÇ_x001C_Â+È_x000C__x0000__x0000_063-274-9337
+_x0000__x0000_0632789337_x0008__x0000__x0001__x0004_È|·½Ä³ _x0000__x0004_ÈüÈÜÂ_x0006__x0000__x0000_560080_x0013__x0000__x0001__x0004_È|·½Ä³ _x0000__x0004_ÈüÈÜÂ _x0000_DÆ°Àl­ _x0000_õ¬½\¸ _x0000_2_x0000_0_x0000__x000D__x0000__x0000_010-9224-8391_x0010__x0000__x0000_jyonex@naver.com_x000E__x0000__x0000_37690004516337_x0006__x0000__x0000_D00136_x0005__x0000__x0001__x001C_È|Ç¤ÂìÓ Î
+_x0000__x0000_4040533542_x000B__x0000__x0001__x001C_È|Ç_x0008_¸_x0000_È¤ÂìÓ Î(_x0000__x0015_ÈMÇ)_x0000__x0003__x0000__x0001_@®_x0011_­õ¼	_x0000__x0001_´ÆÙ³0®l­_x000F_¼´ÆÙ³õ¼xÆ_x000C__x0000__x0000_063-535-9146
+_x0000__x0000_0635332093_x0008__x0000__x0001__x0004_È|·½Ä³ _x0000__x0015_ÈMÇÜÂ_x0006__x0000__x0000_580804_x000F__x0000__x0001__x0004_È|·½Ä³ _x0000__x0015_ÈMÇÜÂ _x0000__x0011_ÉYÅ\¸ _x0000_8_x0000_3_x0000__x000D__x0000__x0000_010-9579-7800_x0016__x0000__x0000_sports9146@hanmaIl.net_x000E__x0000__x0000_37690004520237_x0006__x0000__x0000_D00137_x000B__x0000__x0001_üÈÝÂÖ¬À _x0000_0¼Ü´ü»4ÑÈ¹¸Ò
+_x0000__x0000_1108193203_x0003__x0000__x0001__x0015_ÈtÇ@±_x000B__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000__x0004_ÈÇÁÀp¬·_x0008__x0000__x0000_20130723_x000C__x0000__x0000_031-964-3530	_x0000__x0000_023829555_x0007__x0000__x0001_½¬0®Ä³ _x0000_à¬ÅÜÂ_x0005__x0000__x0000_10564_x0011__x0000__x0001_½¬0® _x0000_à¬ÅÜÂ _x0000_U³Ål­ _x0000_¼À¡Á\¸ _x0000_1_x0000_2_x0000__x0007__x0000__x0001_4_x0000_5Î _x0000_4_x0000_1_x0000_8_x0000_8Ö_x000D__x0000__x0000_010-7152-7538_x0014__x0000__x0000_mintonmart@naver.com_x000E__x0000__x0000_37690004521937_x0006__x0000__x0000_D00138	_x0000__x0001_üÈÝÂÖ¬ÀÙ³°Æ¤ÂìÓ Î
+_x0000__x0000_1108180426_x0003__x0000__x0001_¡Á_x0015_È|Ç_x000B__x0000__x0000_02-382-3598	_x0000__x0000_023553586	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_@ÇÉÓl­_x0006__x0000__x0000_122903_x0018__x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_@ÇÉÓl­ _x0000_ðÅ_x001C_Á\¸ _x0000_2_x0000_9_x0000_-_x0000_1_x0000_ _x0000_Ù³°Æ¤ÂìÓ Î_x000D__x0000__x0000_010-2018-3598_x0012__x0000__x0000_dvip1233@naver.com_x000B__x0000__x0000_01074353598
+_x0000__x0001__x0018_Â_x0008_® _x0000_½qÈ&lt;Ç\¸ _x0000_µÑ_x001C_È_x000E__x0000__x0000_37690004522537_x0006__x0000__x0000_D00141	_x0000__x0001__x0011_ÉYÅ¤ÂìÓ Î(_x0000_½¬üÈ)_x0000_
+_x0000__x0000_3226600323_x0003__x0000__x0001_iÖ_x0001_ÆäÂ_x0008__x0000__x0000_20081210_x000C__x0000__x0000_054-741-5177_x0008__x0000__x0001_½¬ÁÀ½Ä³ _x0000_½¬üÈÜÂ_x0006__x0000__x0000_780943_x0012__x0000__x0001_½¬ÁÀ½Ä³ _x0000_½¬üÈÜÂ _x0000__x0008_®1Á\¸ _x0000_2_x0000_9_x0000_4_x0000_-_x0000_1_x0000__x000D__x0000__x0000_010-7579-5177_x0014__x0000__x0000_jasp6304@hanmail.net_x0008__x0000__x0000_20081211_x000E__x0000__x0000_37690004525437_x0006__x0000__x0000_D00145_x0005__x0000__x0001_­Ìá¸¤ÂìÓ Î
+_x0000__x0000_6150796307_x0003__x0000__x0001_pÈø»_x0019_Â_x0008__x0000__x0000_20101004_x000C__x0000__x0000_055-312-9559
+_x0000__x0000_0553129560_x0008__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_@®tÕÜÂ_x0006__x0000__x0000_621833_x0012__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_@®tÕÜÂ _x0000_¥Ç Ç\¸ _x0000_2_x0000_9_x0000_7_x0000_-_x0000_5_x0000__x000D__x0000__x0000_010-9513-9559_x0016__x0000__x0000_jms3129559@hanmail.net_x0008__x0000__x0000_20101019_x000E__x0000__x0000_37690004530037_x0006__x0000__x0000_D00148_x0007__x0000__x0001__x0000_ÏtÇdÅD¾¤ÂìÓ Î
+_x0000__x0000_1232481068_x0003__x0000__x0001__x0015_¼+ºÇ_x000C__x0000__x0000_031-457-8706
+_x0000__x0000_0314578707_x0007__x0000__x0001_½¬0®Ä³ _x0000_HÅÅÜÂ_x0006__x0000__x0000_431837_x0012__x0000__x0001_½¬0®Ä³ _x0000_HÅÅÜÂ _x0000_Ù³HÅl­ _x0000_À­xÇ\¸ _x0000_8_x0000_9_x0000__x000D__x0000__x0000_010-7338-7375_x0016__x0000__x0000_jamjali200@hanmail.net_x000E__x0000__x0000_37690004532237_x0006__x0000__x0000_D00149	_x0000__x0001_TÏ¬¹DÅ$Æ_x0008_Õ(_x0000_@®Ì)_x0000_
+_x0000__x0000_5100147324_x0003__x0000__x0001__x0015_¼ Á_x0001_Æ_x0008__x0000__x0000_20070423_x000C__x0000__x0000_054-430-7007
+_x0000__x0000_0544307007_x0008__x0000__x0001_½¬ÁÀ½Ä³ _x0000_@®ÌÜÂ_x0005__x0000__x0000_39626_x000E__x0000__x0001_½¬½ _x0000_@®ÌÜÂ _x0000_¡Á$Á\¸ _x0000_1_x0000_6_x0000_4_x0000__x000D__x0000__x0000_010-4115-6306_x0013__x0000__x0000_jj10654@hanmail.net_x000E__x0000__x0000_37690004533937_x0006__x0000__x0000_D00150_x0005__x0000__x0001__x0014_Ól­¤ÂìÓ Î
+_x0000__x0000_5020153204_x0003__x0000__x0001_àÂÁÀÜ­_x0008__x0000__x0000_20080331_x000C__x0000__x0000_053-957-8989
+_x0000__x0000_0539432345_x0008__x0000__x0001__x0000_³l­_x0011_­íÅÜÂ _x0000_Ù³l­_x0005__x0000__x0000_41193_x000F__x0000__x0001__x0000_³l­ _x0000_Ù³l­ _x0000_DÅÅ\¸1_x0000_1_x0000_8® _x0000_8_x0000_1_x0000__x0008__x0000__x0001_1_x0000_5Î _x0000__x0014_Ól­¤ÂìÓ Î_x000D__x0000__x0000_010-8854-8989_x0012__x0000__x0000_89sports@naver.com_x000E__x0000__x0000_37690004534537_x0006__x0000__x0000_D00159_x0005__x0000__x0001__x001C_Ö1Á¤ÂìÓ Î
+_x0000__x0000_1300531089_x0003__x0000__x0001_tÇXÇ Á_x000D__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000__x0000_¬_x0004_È_x001C_ÈÔ,_x0000_¡ÇTÖ_x0008__x0000__x0000_20070529_x000C__x0000__x0000_032-654-2133
+_x0000__x0000_0326542132_x0007__x0000__x0001_½¬0®Ä³ _x0000_½ÌÜÂ_x0006__x0000__x0000_422819 _x0000__x0001_½¬0®Ä³ _x0000_½ÌÜÂ _x0000_Á¬Àl­ _x0000_½¬xÇ\¸1_x0000_2_x0000_0_x0000_¼8® _x0000_2_x0000_8_x0000_ _x0000_ _x0000_1_x0000_5Î_x0010_ÈìÓ _x0000_1_x0000_xÎ_x000D__x0000__x0000_010-7578-7740_x0015__x0000__x0000_hs7167741@hanmail.net_x000E__x0000__x0000_37690004541337_x0006__x0000__x0000_D00160_x0005__x0000__x0001_8ÖÙ³¤ÂìÓ Î
+_x0000__x0000_1243919047_x0003__x0000__x0001_@®8ÖÙ³_x0008__x0000__x0000_20100113_x000C__x0000__x0000_031-375-0331
+_x0000__x0000_0313750331_x0007__x0000__x0001_½¬0®Ä³ _x0000_$Æ°ÀÜÂ_x0006__x0000__x0000_447802_x001A__x0000__x0001_½¬0®Ä³ _x0000_$Æ°ÀÜÂ _x0000_1Á8Ö_x0000_³\¸ _x0000_2_x0000_5_x0000_ _x0000_´Æ°ÀL¾)µ _x0000_ _x0000_1_x0000_5Î _x0000_4_x0000__x000D__x0000__x0000_010-5295-8278_x0013__x0000__x0000_khd9982@hanmail.net_x000E__x0000__x0000_37690004542037_x0006__x0000__x0000_D00161_x0005__x0000__x0001_MÖ1ÁÆ%±¤Â
+_x0000__x0000_3100640518_x0003__x0000__x0001_@®_x0004_Ö_x0015_È_x0008__x0000__x0000_20090616_x000C__x0000__x0000_041-634-7327_x0008__x0000__x0001_©Í­Ì¨°Ä³ _x0000_MÖ1Áp­_x0005__x0000__x0000_32263_x0012__x0000__x0001_©Í¨° _x0000_MÖ1Áp­ _x0000_MÖ½MÇ _x0000_©Í¨°_x0000_³\¸ _x0000_3_x0000_6_x0000__x0015__x0000__x0001__x001C_È _x0000_1_x0000_5Î _x0000__x001C_È _x0000_1_x0000_0_x0000_1_x0000_8Ö(_x0000_L¾dÅT³¤Â$Æ&lt;Õ¤ÂTÑ)_x0000__x000D__x0000__x0000_010-8626-9825_x0010__x0000__x0000_hji923@naver.com_x000E__x0000__x0000_37690004543637_x0006__x0000__x0000_D00166_x000C__x0000__x0001_(_x0000_üÈ)_x0000_ðÒ_x001C_ÈtÇ_x0014_µ¤Â¸Ò¬¹ð½XÁ
+_x0000__x0000_2118732516_x0003__x0000__x0001_¡ÁÁÀÐÆ_x0006__x0000__x0001_Ä³Áä¹ _x0000_Ä³ä¹_x0008__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_4»íÅ_x0008__x0000__x0000_20120911_x000B__x0000__x0000_02-511-5114	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x0015_¬¨°l­_x0006__x0000__x0000_135010_x000B__x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ_x0015_¬¨°l­|±_x0004_ÖÙ³_x000E__x0000__x0001__x0008_®@ÇL¾)µ _x0000_1_x0000_5Î _x0000_ ¼¤Â¸Ò¤Â Ñ´Å_x000D__x0000__x0000_010-8784-1651_x0015__x0000__x0000_bestextreme@naver.com_x0007__x0000__x0001_B_x0000_ñ´	®(_x0000_T_x0000_S_x0000_)_x0000__x0005__x0000__x0000_14049_x0003__x0000__x0001__x0015_¼_x0004_ÖÄÉ_x0008__x0000__x0000_20190917_x0006__x0000__x0000_D00167_x0008__x0000__x0001_üÈÝÂÖ¬À _x0000_ÐÆÐÅÇ
+_x0000__x0000_1268800066_x0003__x0000__x0001_@®DÕ¹Â_x0006__x0000__x0001_Ä³Áä¹ÅÅ _x0000_xÆ_x0007__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_xÆ_x000C__x0000__x0000_02-1644-1662	_x0000__x0001_½°À_x0011_­íÅÜÂ _x0000__x0018_Â_x0001_Æl­_x0006__x0000__x0000_613815_x0013__x0000__x0001_½°À_x0011_­íÅÜÂ _x0000__x0018_Â_x0001_Æl­ _x0000__x0011_­¨°\¸ _x0000_6_x0000_3_x0000_ _x0000_B_x0000_Ù³_x0004__x0000__x0001_4_x0000_5Î|Ç½_x000D__x0000__x0000_010-8882-4137_x0014__x0000__x0000_oneeight@hanmail.net_x0006__x0000__x0000_D00173_x0005__x0000__x0001__x0008_®_x0001_Æ¤ÂìÓ Î
+_x0000__x0000_1052087391_x0003__x0000__x0001_°ÆÀÉÐÆ_x0008__x0000__x0000_20140217_x000D__x0000__x0000_010-6208-8112_x0006__x0000__x0000_121889_x0013__x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_È¹ìÓl­ _x0000_Ù³P­\¸3_x0000_8® _x0000_1_x0000_2_x0000_5_x0000__x0013__x0000__x0000_yonex0901@naver.com_x0008__x0000__x0000_20150122_x000E__x0000__x0000_37690004557937_x0006__x0000__x0000_D00181_x0004__x0000__x0001__x0000_É¤ÂìÓ Î
+_x0000__x0000_1410240836_x0003__x0000__x0001__x0015_¼½¬·_x0008__x0000__x0000_20140825_x000C__x0000__x0000_031-945-2007_x0007__x0000__x0001_½¬0®Ä³ _x0000__x000C_ÓüÈÜÂ_x0006__x0000__x0000_413819$_x0000__x0001_½¬0®Ä³ _x0000__x000C_ÓüÈÜÂ _x0000_DÅ¬¹·\¸ _x0000_5_x0000_5_x0000_ _x0000_-_x0000_8_x0000_1_x0000_ _x0000_(_x0000__x0008_®_x000C_ÍÙ³,_x0000_ _x0000__x000C_ÓüÈ_x0008_®_x000C_ÍXÕ_x0018_ÂÌ¬¹¥Ç)_x0000__x000C__x0000__x0001__x000C_ÓüÈÜÂ _x0000_0¼Ü´ü»4Ñ_x0004_È©Æl­¥Ç_x000D__x0000__x0000_010-9129-1126_x0017__x0000__x0000_leesjun1024@hanmail.net_x000E__x0000__x0000_37690004547137_x0006__x0000__x0000_D00183_x0003__x0000__x0001_T³_x001C_È|Ç
+_x0000__x0000_1171558537_x0003__x0000__x0001_iÖÐÆ Á_x000B__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_XÇX¹,_x0000_¡ÇTÖ_x0008__x0000__x0000_20141027_x000D__x0000__x0000_010-6333-2457	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_ÅÌl­_x0005__x0000__x0000_08078 _x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_ÅÌl­ _x0000_àÂ_x0015_È\¸ _x0000_2_x0000_7_x0000_5_x0000_ _x0000_ _x0000_(_x0000_àÂ_x0015_ÈÙ³,_x0000_ _x0000_àÂ¸Ò¬¹DÅ_x000C_Ó¸Ò)_x0000__x0010__x0000__x0001_ÁÀ_x0000_¬Ù³ _x0000_1_x0000_5Î _x0000_1_x0000_0_x0000_4_x0000_,_x0000_ _x0000_1_x0000_0_x0000_5_x0000_8Ö_x0011__x0000__x0000_thejeil@naver.com_x000D__x0000__x0000_010-9668-2210_x000E__x0000__x0000_37690004550437_x0006__x0000__x0000_D00184_x0005__x0000__x0001_$Æ¨°¤ÂìÓ Î
+_x0000__x0000_1322489384_x0003__x0000__x0001_Å+È¨º_x000D__x0000__x0001_´ÆÙ³0®l­©ÆÔ _x0000_aÅ8Á_x001C_Á¬¹ _x0000_xÆ_x0008__x0000__x0000_20141028
+_x0000__x0000_0315756464
+_x0000__x0000_0315755600_x0008__x0000__x0001_½¬0®Ä³ _x0000_¨°ÅüÈÜÂ_x0006__x0000__x0000_472881_x0016__x0000__x0001_½¬0®Ä³ _x0000_¨°ÅüÈÜÂ _x0000_ÄÉt¬$Æ¨°\¸ _x0000_8_x0000_0_x0000_6_x0000_ _x0000_-_x0000_1_x0000_4_x0000__x000D__x0000__x0000_010-9289-9637_x0012__x0000__x0000_jongmo83@naver.com_x000E__x0000__x0000_37690004552737_x0006__x0000__x0000_D00186_x0005__x0000__x0001_ä¹XÎìÓxÇ¸Ò
+_x0000__x0000_6091853217_x0003__x0000__x0001_iÖ­ÝÂ_x0008__x0000__x0000_20141202_x000C__x0000__x0000_055-298-7330_x0005__x0000__x0000_51378_x0011__x0000__x0001_½¬¨° _x0000_=ÌÐÆÜÂ _x0000_XÇ=Ìl­ _x0000__x0018_¼Ä¬\¸ _x0000_6_x0000_3_x0000__x000D__x0000__x0000_010-3561-0209_x000E__x0000__x0000_o2bbi@nate.com_x0008__x0000__x0000_20141212_x000E__x0000__x0000_37690004554037_x0006__x0000__x0000_D00190_x0005__x0000__x0001_p­°À¤ÂìÓ Î
+_x0000__x0000_4010657765_x0003__x0000__x0001__x0015_¼_x001C_Âl×	_x0000__x0001_¤ÂìÓ ÎXÇX¹,_x0000_ _x0000_©ÆÔ_x0008__x0000__x0000_20150406_x000D__x0000__x0000_010-9977-7141_x0008__x0000__x0001__x0004_È|·½Ä³ _x0000_p­°ÀÜÂ_x0005__x0000__x0000_54102_x000F__x0000__x0001__x0004_È½ _x0000_p­°ÀÜÂ _x0000_¨°_x0018_Â¡Á5_x0000_8® _x0000_4_x0000_2_x0000__x000F__x0000__x0001_1_x0000_0_x0000_1_x0000_8Ö(_x0000__x0018_Â¡ÁÙ³,_x0000_ _x0000_(Ì$Æ¹L¾)_x0000__x0013__x0000__x0000_shp7141@hanmaiL.net_x000E__x0000__x0000_37690004558537_x0006__x0000__x0000_D00192
+_x0000__x0001__x0001_Æ8»¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1222039517_x0005__x0000__x0001__x0001_Æ8»¤ÂìÓ Î_x0003__x0000__x0001_@®_x0001_Æ8»_x0008__x0000__x0000_20150608_x000C__x0000__x0000_032-523-1406_x000C__x0000__x0000_032-517-8009	_x0000__x0001_xÇÌ_x0011_­íÅÜÂ _x0000_½ÉÓl­_x0005__x0000__x0000_21337_x000D__x0000__x0000_010-4320-1</v>
+          </cell>
+          <cell r="H35" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="I35" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="J35" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="K35" t="e">
+            <v>#N/A</v>
           </cell>
           <cell r="L35" t="str">
             <v/>
           </cell>
-          <cell r="M35" t="str">
-            <v>02-3142-7016</v>
+          <cell r="M35" t="e">
+            <v>#N/A</v>
           </cell>
           <cell r="N35" t="str">
             <v/>
           </cell>
-          <cell r="O35" t="str">
-            <v>서울특별시 서대문구</v>
+          <cell r="O35" t="e">
+            <v>#N/A</v>
           </cell>
           <cell r="P35" t="str">
-            <v>120827</v>
-          </cell>
-          <cell r="Q35" t="str">
-            <v>서울특별시 서대문구 연희로 199  1층</v>
+            <v>_x0016__x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x001C_Á_x0000_³8»l­ _x0000_ðÅl×\¸ _x0000_1_x0000_9_x0000_9_x0000_ _x0000_ _x0000_1_x0000_5Î_x000D__x0000__x0000_010-5264-4932_x0012__x0000__x0000_yjjwon@hanmail.net_x000E__x0000__x0000_37690004475237_x0006__x0000__x0000_D00085_x0005__x0000__x0001_1Á_x0015_È_x0008_¸ìÓ Î
+_x0000__x0000_3120525501_x0003__x0000__x0001_1Á0®)¼_x0008__x0000__x0000_20090326_x000C__x0000__x0000_041-556-7884_x0006__x0000__x0000_331961_x0016__x0000__x0001_©Í­Ì¨°Ä³ _x0000_ÌHÅÜÂ _x0000__x001C_Á½l­ _x0000_P´_x0015_È_x0011_É8_x0000_8® _x0000_1_x0000_-_x0000_8_x0000__x000D__x0000__x0000_010-5424-8640_x0015__x0000__x0000_sjreports@hanmail.net_x0008__x0000__x0000_20090325_x000E__x0000__x0000_37690004478137_x0006__x0000__x0000_D00086_x0008__x0000__x0001_üÈÝÂÖ¬À _x0000_ÐÅ¤ÂàÅ
+_x0000__x0000_1318674023_x0003__x0000__x0001_Á_x0004_Ö8Ö_x0008__x0000__x0000_20120330_x000C__x0000__x0000_051-202-3541
+_x0000__x0000_0512013541	_x0000__x0001_½°À_x0011_­íÅÜÂ _x0000__x0015_¬_x001C_Ál­_x0006__x0000__x0000_618814$_x0000__x0001_½°À_x0011_­íÅÜÂ _x0000__x0015_¬_x001C_Ál­ _x0000_+ºÀÉ$ÆXÁÜÂðÒ1_x0000_3_x0000_\¸ _x0000_1_x0000_2_x0000_-_x0000_2_x0000_2_x0000_ _x0000_ _x0000_MÖÄÉL¾)µ _x0000_1_x0000_0_x0000_6_x0000_8Ö_x000D__x0000__x0000_010-4733-3541_x0016__x0000__x0000_coolcomy1982@naver.com_x0008__x0000__x0000_20120409_x000E__x0000__x0000_37690004479837_x0006__x0000__x0000_D00087
+_x0000__x0001_üÈÝÂÖ¬À _x0000_8ÁÄÉ¤ÂìÓ Î
+_x0000__x0000_3298701221_x0003__x0000__x0001__x0015_¼_x001C_Â¼À_x0007__x0000__x0001_Ä³ä¹ _x0000__x000F_¼ _x0000_Áä¹_x0008__x0000__x0000_20070309_x000B__x0000__x0000_02-824-8799	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_Ù³Çl­_x0005__x0000__x0000_06921_x000E__x0000__x0001__x001C_Á¸Æ _x0000_Ù³Çl­ _x0000_Ì¹Å\¸1_x0000_8® _x0000_3_x0000__x0008__x0000__x0001_ÀÉ5Î _x0000_(_x0000_ÁÀÄ³Ù³)_x0000__x000D__x0000__x0000_010-2942-3235_x0019__x0000__x0000_sejinsports2018@naver.com_x0017__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000_ _x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_9_x0000_3_x0000_-_x0000_&gt;_x0000_5_x0000_0_x0000_ _x0000_&lt;Ç\¸ _x0000_pÈ_x0015_È_x000E__x0000__x0000_37690004480837_x001A__x0000__x0001_0_x0000_1_x0000_0_x0000_ _x0000_2_x0000_7_x0000_0_x0000_5_x0000_ _x0000_3_x0000_2_x0000_3_x0000_4_x0000_ _x0000_(_x0000_ä¹¥Ç _x0000_xÆ _x0000_A_x0000_S_x0000_ô²ù²Ç)_x0000__x0006__x0000__x0000_D00089_x0006__x0000__x0001_Á_x0008_Í0¼Ü´ü»4Ñ
+_x0000__x0000_2270299081_x0003__x0000__x0001__x0015_È¬ÇÈÖ_x000C__x0000__x0000_033-638-0024
+_x0000__x0000_0336382400_x0007__x0000__x0001__x0015_¬ÐÆÄ³ _x0000_Á_x0008_ÍÜÂ_x0006__x0000__x0000_217803_x000E__x0000__x0001__x0015_¬ÐÆÄ³ _x0000_Á_x0008_ÍÜÂ _x0000_P­Ù³\¸ _x0000_3_x0000_9_x0000__x000D__x0000__x0000_010-3297-3133_x0019__x0000__x0000_yubgijung1257@hanmail.net_x000E__x0000__x0000_37690004481437_x0006__x0000__x0000_D00090_x000B__x0000__x0001_üÈÝÂÖ¬À _x0000_¤Âä¹lÂ¤ÂìÓ Î
+_x0000__x0000_8558703276_x0006__x0000__x0001_¤Âä¹lÂ¤ÂìÓ Î_x0003__x0000__x0001_$ÇÜ­ø»_x0008__x0000__x0000_20070917_x000B__x0000__x0000_01087511199_x0007__x0000__x0001_½¬0®Ä³ _x0000_HÅ°ÀÜÂ_x0005__x0000__x0000_15497_x0012__x0000__x0001_½¬0® _x0000_HÅ°ÀÜÂ _x0000_ÁÀ]¸l­ _x0000_Ì8»4_x0000_8® _x0000_1_x0000_7_x0000__x001A__x0000__x0001_1_x0000_5Î1_x0000_5_x0000_1_x0000_9_x0000_-_x0000_1_x0000_3_x0000_ _x0000_ _x0000_1_x0000_5Î _x0000_ _x0000_¤Âä¹lÂ¤ÂìÓ Î _x0000_&lt;»X¹&lt;Á0Ñ_x000D__x0000__x0000_010-5471-3330_x0013__x0000__x0000_smash-123@naver.com_x000B__x0000__x0000_01054713330_x000E__x0000__x0000_37690004483737_x0008__x0000__x0001_!Ç1Á_x0010_È&amp;_x0000_1_x0000_0_x0000_0_x0000_%_x0000__x0006__x0000__x0000_D00096_x0005__x0000__x0001_¤ÂìÓ ÎE¼lÐ
+_x0000__x0000_1272092161_x0003__x0000__x0001_@®ÄÉÉÓ_x0004__x0000__x0001_´Ì!Ç©ÆÔ_x0008__x0000__x0000_20070503_x000C__x0000__x0000_031-535-1244
+_x0000__x0000_0315352245_x0007__x0000__x0001_½¬0®Ä³ _x0000_ìÓÌÜÂ_x0006__x0000__x0000_487050_x0018__x0000__x0001_½¬0®Ä³ _x0000_ìÓÌÜÂ _x0000_p­´°tº _x0000_8Öm­\¸ _x0000_1_x0000_6_x0000_9_x0000_6_x0000_._x0000_ _x0000_2_x0000_5Î_x000D__x0000__x0000_010-6354-5471_x0011__x0000__x0000_kjp31@hanmail.net_x000E__x0000__x0000_37690004487237_x0006__x0000__x0000_D00097_x0005__x0000__x0001_¹Â¬¹¤ÂìÓ Î
+_x0000__x0000_2011081473_x0003__x0000__x0001_à¬Ñ¼°Æ_x0008__x0000__x0000_20071221_x000C__x0000__x0000_02-2279-0779
+_x0000__x0000_0222780778_x0005__x0000__x0000_04563_x001E__x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x0011_Él­ _x0000_­ÌÄ¬Ì\¸ _x0000_2_x0000_4_x0000_6_x0000_ _x0000_ _x0000_(_x0000_)¼°ÀÙ³,_x0000_ _x0000_ÉÓTÖÜÂ¥Ç)_x0000__x0016__x0000__x0001_1_x0000_,_x0000_2_x0000_,_x0000_3_x0000_5Î _x0000_ä²-_x0000_1_x0000_0_x0000_2_x0000_(_x0000_)¼°ÀÙ³,_x0000_ÉÓTÖÜÂ¥Ç)_x0000__x000D__x0000__x0000_010-3284-7383_x0019__x0000__x0000_victorysports@hanmail.net_x000E__x0000__x0000_37690004488937_x0006__x0000__x0000_D00101_x0005__x0000__x0001_DÅ°À¤ÂìÓ Î
+_x0000__x0000_3122872982_x0003__x0000__x0001_\Í+È¼¹_x000C__x0000__x0001_Ä³ä¹_x000F_¼ÁÀÔ_x0011_É_x001C_¬ÅÅ,_x0000_Áä¹ÅÅ_x0008__x0000__x0000_20110701_x000C__x0000__x0000_041-532-8381
+_x0000__x0000_0415328382_x0008__x0000__x0001_©Í­Ì¨°Ä³ _x0000_DÅ°ÀÜÂ_x0006__x0000__x0000_336050_x0010__x0000__x0001_©Í­Ì¨°Ä³ _x0000_DÅ°ÀÜÂ _x0000_ÜÂü»\¸ _x0000_2_x0000_5_x0000_1_x0000__x000D__x0000__x0000_010-4946-8385_x0013__x0000__x0000_judocjl@hanmail.net_x000E__x0000__x0000_37690004490537_x0006__x0000__x0000_D00109_x0008__x0000__x0001__x0001_Æ¤ÂìÓ Î(_x0000_¨°ÐÆ)_x0000_
+_x0000__x0000_1095289131_x0003__x0000__x0001_tÇ_x0015_ÈÌ_x0008__x0000__x0000_20071119_x000C__x0000__x0000_063-632-4154
+_x0000__x0000_0636324156_x0005__x0000__x0000_55703_x0015__x0000__x0001__x0004_È|·½Ä³ _x0000_¨°ÐÆÜÂ _x0000_¬Àä¹tº _x0000__x0000_³¬À\¸ _x0000_1_x0000_2_x0000_8_x0000_3_x0000__x0004__x0000__x0001__x0001_Æ¤ÂìÓ Î_x000D__x0000__x0000_010-4594-0634_x0013__x0000__x0000_jclee8734@naver.com_x000E__x0000__x0000_37690004497037_x0006__x0000__x0000_D00110_x0007__x0000__x0001_Æ%±¤Â _x0000_TÖ_x001C_Â_x0010_È
+_x0000__x0000_4080577085_x0003__x0000__x0001__x0004_È+º_x0019_Â_x0008__x0000__x0000_20071102_x000C__x0000__x0000_061-375-6647_x0008__x0000__x0001__x0004_È|·¨°Ä³ _x0000_TÖ_x001C_Âp­_x0006__x0000__x0000_519809_x0014__x0000__x0001__x0004_È|·¨°Ä³ _x0000_TÖ_x001C_Âp­ _x0000__x0011_­U³\¸ _x0000_1_x0000_4_x0000_0_x0000_ _x0000_ _x0000_1_x0000_5Î_x000D__x0000__x0000_010-6632-5893_x0012__x0000__x0000_ms-jon@hanmeil.net_x000E__x0000__x0000_37690004498637_x0006__x0000__x0000_D00111_x000C__x0000__x0001_,Æ¼¹=Õ+ÈiÕ¤ÂìÓ Î(_x0000_©ºìÓ)_x0000_
+_x0000__x0000_4111469486_x0003__x0000__x0001_@®=Ì©Æ_x000C__x0000__x0001_´ÆÙ³©ÆÔ,_x0000_ñ´°Àl­,_x0000_0®P±Ô_x0008__x0000__x0000_20070320_x000C__x0000__x0000_061-242-1032
+_x0000__x0000_0612443032_x0008__x0000__x0001__x0004_È|·¨°Ä³ _x0000_©ºìÓÜÂ_x0005__x0000__x0000_58726_x0010__x0000__x0001__x0004_È¨° _x0000_©ºìÓÜÂ _x0000_(Ì¼_x001D_Á8® _x0000_4_x0000_1_x0000_-_x0000_1_x0000__x0002__x0000__x0001_1_x0000_5Î_x000D__x0000__x0000_010-9243-4285_x0010__x0000__x0000_eyebono@daum.net_x000E__x0000__x0000_37690004499237_x0006__x0000__x0000_D00116_x000F__x0000__x0001_Æ%±¤ÂÈ¹°À_x0000_³¬¹_x0010_È(_x0000_ü»4Ñ¤ÂìÓ Î)_x0000_
+_x0000__x0000_6080288027_x0003__x0000__x0001_ Ç_x0001_Æ_x0019_Â_x0008__x0000__x0001_¤ÂìÓ Î©ÆÔ_x000F_¼XÇX¹_x000C__x0000__x0000_055-222-5431
+_x0000__x0000_0552225432_x0008__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_=ÌÐÆÜÂ_x0006__x0000__x0000_631852_x0018__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_=ÌÐÆÜÂ _x0000_È¹°ÀiÕìÓl­ _x0000_©ÆÈ¹\¸ _x0000_7_x0000_6_x0000_ _x0000_üÈÝÐ_x000D__x0000__x0000_010-3707-6245_x0016__x0000__x0000_dudtjs6245@hanmail.net_x000E__x0000__x0000_37690004504337_x0006__x0000__x0000_D00120_x0006__x0000__x0001_Æ%±¤Â­ÌüÈ_x0010_È
+_x0000__x0000_3170385854_x0003__x0000__x0001_\Í°Æ1Á_x000B__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_XÇX¹,_x0000__x0018_Ât¬_x0008__x0000__x0000_20110729_x000C__x0000__x0000_043-222-3040
+_x0000__x0000_0432245050_x0008__x0000__x0001_©Í­Ì½Ä³ _x0000_­ÌüÈÜÂ_x0006__x0000__x0000_361842_x0012__x0000__x0001_©Í½ _x0000_­ÌüÈÜÂ _x0000_ÁÀù²l­ _x0000_8Öø»\¸ _x0000_2_x0000_0_x0000_6_x0000__x0005__x0000__x0001_1_x0000_5Î _x0000_È!Î_x000D__x0000__x0000_010-5468-3319_x0015__x0000__x0000_wsung3525@hanmail.net_x0008__x0000__x0000_20080429_x000E__x0000__x0000_37690004507237_x0006__x0000__x0000_D00121_x000D__x0000__x0001_Æ%±¤ÂìÓmÕ_x0010_È(_x0000_XÕtÇlÐ¬¹´Å)_x0000_
+_x0000__x0000_5061736246_x0003__x0000__x0001__x0015_È@Ç_x0001_Æ_x0008__x0000__x0000_20090227_x000C__x0000__x0000_054-283-5234
+_x0000__x0000_0542835231_x0008__x0000__x0001_½¬ÁÀ½Ä³ _x0000_ìÓmÕÜÂ_x0006__x0000__x0000_790822_x0012__x0000__x0001_½¬½ _x0000_ìÓmÕÜÂ _x0000_¨°l­ _x0000__x0000_³Ä³Ù³ _x0000_8_x0000_6_x0000_-_x0000_2_x0000__x000D__x0000__x0000_010-4133-7770_x0014__x0000__x0000_minton1125@naver.com_x0008__x0000__x0000_20081105_x000E__x0000__x0000_37690004508937_x0006__x0000__x0000_D00122_x0005__x0000__x0001_°Æ¬¹¤ÂìÓ Î
+_x0000__x0000_4172105493_x0003__x0000__x0001__x0015_¼_x0018_ÂÄÉ_x0008__x0000__x0000_20180101_x000C__x0000__x0000_051-632-2681
+_x0000__x0000_0516322681_x0008__x0000__x0001_½°À_x0011_­íÅÜÂ _x0000_¨°l­_x0006__x0000__x0000_608827_x0011__x0000__x0001_½°À_x0011_­íÅÜÂ _x0000_¨°l­ _x0000_Ç ÇÉÓTÖ\¸ _x0000_4_x0000_9_x0000__x000D__x0000__x0000_010-2594-2682_x0015__x0000__x0000_moxie2000@hanmail.net_x000E__x0000__x0000_37690004509537_x0006__x0000__x0000_D00123_x0005__x0000__x0001_°Æ1Á¤ÂìÓ Î
+_x0000__x0000_2077003708_x0003__x0000__x0001_@®DÆÝÂ_x0008__x0000__x0000_20071009_x000B__x0000__x0000_02-465-1297	_x0000__x0000_024651197	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x0011_­ÄÉl­_x0006__x0000__x0000_143961_x0010__x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x0011_­ÄÉl­ _x0000_l­XÇ\¸ _x0000_6_x0000_6_x0000__x0014__x0000__x0001_1_x0000_5Î _x0000_(_x0000_l­XÇÙ³ _x0000_2_x0000_2_x0000_7_x0000_-_x0000_6_x0000_)_x0000_ _x0000_°Æ1Á¤ÂìÓ Î_x000D__x0000__x0000_010-3418-1230_x000F__x0000__x0000_ws418@naver.com_x000E__x0000__x0000_37690004510537_x0006__x0000__x0000_D00126_x0005__x0000__x0001_ÐÆÙ³´Ì!Ç¬À
+_x0000__x0000_3060363748_x0003__x0000__x0001_ü»Ñ¼ÁÉ_x0004__x0000__x0001_´ÆÙ³0®l­_x0008__x0000__x0000_20050705_x000C__x0000__x0000_042-531-4004
+_x0000__x0000_0425328899_x0008__x0000__x0001__x0000_³_x0004_È_x0011_­íÅÜÂ _x0000_Ù³l­_x0005__x0000__x0000_34630_x000D__x0000__x0001__x0000_³_x0004_È _x0000_Ù³l­ _x0000__x0000_³_x0004_È\¸ _x0000_7_x0000_6_x0000_5_x0000__x000D__x0000__x0000_010-5453-9536_x0012__x0000__x0000_wonspo@hanmail.net_x0008__x0000__x0000_20080214_x000E__x0000__x0000_37690004511137_x0006__x0000__x0000_D00127_x0008__x0000__x0001_ÐÆ¤ÂìÓ Î(_x0000__x001C_ÈüÈ)_x0000_
+_x0000__x0000_6160962051_x0003__x0000__x0001_@®ø»½¬_x000C__x0000__x0000_064-752-4422
+_x0000__x0000_0647232992_x000C__x0000__x0001__x001C_ÈüÈ¹ÒÄ¼ÇXÎÄ³ _x0000__x001C_ÁÀ­ìÓÜÂ_x0006__x0000__x0000_690161_x0013__x0000__x0001__x001C_ÈüÈ¹ÒÄ¼ÇXÎÄ³ _x0000__x001C_ÈüÈÜÂ _x0000_$Æ|·\¸ _x0000_1_x0000_3_x0000_4_x0000__x000D__x0000__x0000_010-4416-4412_x0015__x0000__x0000_crony0104@hanmail.net_x000E__x0000__x0000_37690004512837_x0006__x0000__x0000_D00132_x0005__x0000__x0001__x0004_ÈüÈÆ%±¤Â
+_x0000__x0000_4020887887_x0003__x0000__x0001_tÇ_x001C_Â+È_x000C__x0000__x0000_063-274-9337
+_x0000__x0000_0632789337_x0008__x0000__x0001__x0004_È|·½Ä³ _x0000__x0004_ÈüÈÜÂ_x0006__x0000__x0000_560080_x0013__x0000__x0001__x0004_È|·½Ä³ _x0000__x0004_ÈüÈÜÂ _x0000_DÆ°Àl­ _x0000_õ¬½\¸ _x0000_2_x0000_0_x0000__x000D__x0000__x0000_010-9224-8391_x0010__x0000__x0000_jyonex@naver.com_x000E__x0000__x0000_37690004516337_x0006__x0000__x0000_D00136_x0005__x0000__x0001__x001C_È|Ç¤ÂìÓ Î
+_x0000__x0000_4040533542_x000B__x0000__x0001__x001C_È|Ç_x0008_¸_x0000_È¤ÂìÓ Î(_x0000__x0015_ÈMÇ)_x0000__x0003__x0000__x0001_@®_x0011_­õ¼	_x0000__x0001_´ÆÙ³0®l­_x000F_¼´ÆÙ³õ¼xÆ_x000C__x0000__x0000_063-535-9146
+_x0000__x0000_0635332093_x0008__x0000__x0001__x0004_È|·½Ä³ _x0000__x0015_ÈMÇÜÂ_x0006__x0000__x0000_580804_x000F__x0000__x0001__x0004_È|·½Ä³ _x0000__x0015_ÈMÇÜÂ _x0000__x0011_ÉYÅ\¸ _x0000_8_x0000_3_x0000__x000D__x0000__x0000_010-9579-7800_x0016__x0000__x0000_sports9146@hanmaIl.net_x000E__x0000__x0000_37690004520237_x0006__x0000__x0000_D00137_x000B__x0000__x0001_üÈÝÂÖ¬À _x0000_0¼Ü´ü»4ÑÈ¹¸Ò
+_x0000__x0000_1108193203_x0003__x0000__x0001__x0015_ÈtÇ@±_x000B__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000__x0004_ÈÇÁÀp¬·_x0008__x0000__x0000_20130723_x000C__x0000__x0000_031-964-3530	_x0000__x0000_023829555_x0007__x0000__x0001_½¬0®Ä³ _x0000_à¬ÅÜÂ_x0005__x0000__x0000_10564_x0011__x0000__x0001_½¬0® _x0000_à¬ÅÜÂ _x0000_U³Ål­ _x0000_¼À¡Á\¸ _x0000_1_x0000_2_x0000__x0007__x0000__x0001_4_x0000_5Î _x0000_4_x0000_1_x0000_8_x0000_8Ö_x000D__x0000__x0000_010-7152-7538_x0014__x0000__x0000_mintonmart@naver.com_x000E__x0000__x0000_37690004521937_x0006__x0000__x0000_D00138	_x0000__x0001_üÈÝÂÖ¬ÀÙ³°Æ¤ÂìÓ Î
+_x0000__x0000_1108180426_x0003__x0000__x0001_¡Á_x0015_È|Ç_x000B__x0000__x0000_02-382-3598	_x0000__x0000_023553586	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_@ÇÉÓl­_x0006__x0000__x0000_122903_x0018__x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_@ÇÉÓl­ _x0000_ðÅ_x001C_Á\¸ _x0000_2_x0000_9_x0000_-_x0000_1_x0000_ _x0000_Ù³°Æ¤ÂìÓ Î_x000D__x0000__x0000_010-2018-3598_x0012__x0000__x0000_dvip1233@naver.com_x000B__x0000__x0000_01074353598
+_x0000__x0001__x0018_Â_x0008_® _x0000_½qÈ&lt;Ç\¸ _x0000_µÑ_x001C_È_x000E__x0000__x0000_37690004522537_x0006__x0000__x0000_D00141	_x0000__x0001__x0011_ÉYÅ¤ÂìÓ Î(_x0000_½¬üÈ)_x0000_
+_x0000__x0000_3226600323_x0003__x0000__x0001_iÖ_x0001_ÆäÂ_x0008__x0000__x0000_20081210_x000C__x0000__x0000_054-741-5177_x0008__x0000__x0001_½¬ÁÀ½Ä³ _x0000_½¬üÈÜÂ_x0006__x0000__x0000_780943_x0012__x0000__x0001_½¬ÁÀ½Ä³ _x0000_½¬üÈÜÂ _x0000__x0008_®1Á\¸ _x0000_2_x0000_9_x0000_4_x0000_-_x0000_1_x0000__x000D__x0000__x0000_010-7579-5177_x0014__x0000__x0000_jasp6304@hanmail.net_x0008__x0000__x0000_20081211_x000E__x0000__x0000_37690004525437_x0006__x0000__x0000_D00145_x0005__x0000__x0001_­Ìá¸¤ÂìÓ Î
+_x0000__x0000_6150796307_x0003__x0000__x0001_pÈø»_x0019_Â_x0008__x0000__x0000_20101004_x000C__x0000__x0000_055-312-9559
+_x0000__x0000_0553129560_x0008__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_@®tÕÜÂ_x0006__x0000__x0000_621833_x0012__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_@®tÕÜÂ _x0000_¥Ç Ç\¸ _x0000_2_x0000_9_x0000_7_x0000_-_x0000_5_x0000__x000D__x0000__x0000_010-9513-9559_x0016__x0000__x0000_jms3129559@hanmail.net_x0008__x0000__x0000_20101019_x000E__x0000__x0000_37690004530037_x0006__x0000__x0000_D00148_x0007__x0000__x0001__x0000_ÏtÇdÅD¾¤ÂìÓ Î
+_x0000__x0000_1232481068_x0003__x0000__x0001__x0015_¼+ºÇ_x000C__x0000__x0000_031-457-8706
+_x0000__x0000_0314578707_x0007__x0000__x0001_½¬0®Ä³ _x0000_HÅÅÜÂ_x0006__x0000__x0000_431837_x0012__x0000__x0001_½¬0®Ä³ _x0000_HÅÅÜÂ _x0000_Ù³HÅl­ _x0000_À­xÇ\¸ _x0000_8_x0000_9_x0000__x000D__x0000__x0000_010-7338-7375_x0016__x0000__x0000_jamjali200@hanmail.net_x000E__x0000__x0000_37690004532237_x0006__x0000__x0000_D00149	_x0000__x0001_TÏ¬¹DÅ$Æ_x0008_Õ(_x0000_@®Ì)_x0000_
+_x0000__x0000_5100147324_x0003__x0000__x0001__x0015_¼ Á_x0001_Æ_x0008__x0000__x0000_20070423_x000C__x0000__x0000_054-430-7007
+_x0000__x0000_0544307007_x0008__x0000__x0001_½¬ÁÀ½Ä³ _x0000_@®ÌÜÂ_x0005__x0000__x0000_39626_x000E__x0000__x0001_½¬½ _x0000_@®ÌÜÂ _x0000_¡Á$Á\¸ _x0000_1_x0000_6_x0000_4_x0000__x000D__x0000__x0000_010-4115-6306_x0013__x0000__x0000_jj10654@hanmail.net_x000E__x0000__x0000_37690004533937_x0006__x0000__x0000_D00150_x0005__x0000__x0001__x0014_Ól­¤ÂìÓ Î
+_x0000__x0000_5020153204_x0003__x0000__x0001_àÂÁÀÜ­_x0008__x0000__x0000_20080331_x000C__x0000__x0000_053-957-8989
+_x0000__x0000_0539432345_x0008__x0000__x0001__x0000_³l­_x0011_­íÅÜÂ _x0000_Ù³l­_x0005__x0000__x0000_41193_x000F__x0000__x0001__x0000_³l­ _x0000_Ù³l­ _x0000_DÅÅ\¸1_x0000_1_x0000_8® _x0000_8_x0000_1_x0000__x0008__x0000__x0001_1_x0000_5Î _x0000__x0014_Ól­¤ÂìÓ Î_x000D__x0000__x0000_010-8854-8989_x0012__x0000__x0000_89sports@naver.com_x000E__x0000__x0000_37690004534537_x0006__x0000__x0000_D00159_x0005__x0000__x0001__x001C_Ö1Á¤ÂìÓ Î
+_x0000__x0000_1300531089_x0003__x0000__x0001_tÇXÇ Á_x000D__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000__x0000_¬_x0004_È_x001C_ÈÔ,_x0000_¡ÇTÖ_x0008__x0000__x0000_20070529_x000C__x0000__x0000_032-654-2133
+_x0000__x0000_0326542132_x0007__x0000__x0001_½¬0®Ä³ _x0000_½ÌÜÂ_x0006__x0000__x0000_422819 _x0000__x0001_½¬0®Ä³ _x0000_½ÌÜÂ _x0000_Á¬Àl­ _x0000_½¬xÇ\¸1_x0000_2_x0000_0_x0000_¼8® _x0000_2_x0000_8_x0000_ _x0000_ _x0000_1_x0000_5Î_x0010_ÈìÓ _x0000_1_x0000_xÎ_x000D__x0000__x0000_010-7578-7740_x0015__x0000__x0000_hs7167741@hanmail.net_x000E__x0000__x0000_37690004541337_x0006__x0000__x0000_D00160_x0005__x0000__x0001_8ÖÙ³¤ÂìÓ Î
+_x0000__x0000_1243919047_x0003__x0000__x0001_@®8ÖÙ³_x0008__x0000__x0000_20100113_x000C__x0000__x0000_031-375-0331
+_x0000__x0000_0313750331_x0007__x0000__x0001_½¬0®Ä³ _x0000_$Æ°ÀÜÂ_x0006__x0000__x0000_447802_x001A__x0000__x0001_½¬0®Ä³ _x0000_$Æ°ÀÜÂ _x0000_1Á8Ö_x0000_³\¸ _x0000_2_x0000_5_x0000_ _x0000_´Æ°ÀL¾)µ _x0000_ _x0000_1_x0000_5Î _x0000_4_x0000__x000D__x0000__x0000_010-5295-8278_x0013__x0000__x0000_khd9982@hanmail.net_x000E__x0000__x0000_37690004542037_x0006__x0000__x0000_D00161_x0005__x0000__x0001_MÖ1ÁÆ%±¤Â
+_x0000__x0000_3100640518_x0003__x0000__x0001_@®_x0004_Ö_x0015_È_x0008__x0000__x0000_20090616_x000C__x0000__x0000_041-634-7327_x0008__x0000__x0001_©Í­Ì¨°Ä³ _x0000_MÖ1Áp­_x0005__x0000__x0000_32263_x0012__x0000__x0001_©Í¨° _x0000_MÖ1Áp­ _x0000_MÖ½MÇ _x0000_©Í¨°_x0000_³\¸ _x0000_3_x0000_6_x0000__x0015__x0000__x0001__x001C_È _x0000_1_x0000_5Î _x0000__x001C_È _x0000_1_x0000_0_x0000_1_x0000_8Ö(_x0000_L¾dÅT³¤Â$Æ&lt;Õ¤ÂTÑ)_x0000__x000D__x0000__x0000_010-8626-9825_x0010__x0000__x0000_hji923@naver.com_x000E__x0000__x0000_37690004543637_x0006__x0000__x0000_D00166_x000C__x0000__x0001_(_x0000_üÈ)_x0000_ðÒ_x001C_ÈtÇ_x0014_µ¤Â¸Ò¬¹ð½XÁ
+_x0000__x0000_2118732516_x0003__x0000__x0001_¡ÁÁÀÐÆ_x0006__x0000__x0001_Ä³Áä¹ _x0000_Ä³ä¹_x0008__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_4»íÅ_x0008__x0000__x0000_20120911_x000B__x0000__x0000_02-511-5114	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x0015_¬¨°l­_x0006__x0000__x0000_135010_x000B__x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ_x0015_¬¨°l­|±_x0004_ÖÙ³_x000E__x0000__x0001__x0008_®@ÇL¾)µ _x0000_1_x0000_5Î _x0000_ ¼¤Â¸Ò¤Â Ñ´Å_x000D__x0000__x0000_010-8784-1651_x0015__x0000__x0000_bestextreme@naver.com_x0007__x0000__x0001_B_x0000_ñ´	®(_x0000_T_x0000_S_x0000_)_x0000__x0005__x0000__x0000_14049_x0003__x0000__x0001__x0015_¼_x0004_ÖÄÉ_x0008__x0000__x0000_20190917_x0006__x0000__x0000_D00167_x0008__x0000__x0001_üÈÝÂÖ¬À _x0000_ÐÆÐÅÇ
+_x0000__x0000_1268800066_x0003__x0000__x0001_@®DÕ¹Â_x0006__x0000__x0001_Ä³Áä¹ÅÅ _x0000_xÆ_x0007__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_xÆ_x000C__x0000__x0000_02-1644-1662	_x0000__x0001_½°À_x0011_­íÅÜÂ _x0000__x0018_Â_x0001_Æl­_x0006__x0000__x0000_613815_x0013__x0000__x0001_½°À_x0011_­íÅÜÂ _x0000__x0018_Â_x0001_Æl­ _x0000__x0011_­¨°\¸ _x0000_6_x0000_3_x0000_ _x0000_B_x0000_Ù³_x0004__x0000__x0001_4_x0000_5Î|Ç½_x000D__x0000__x0000_010-8882-4137_x0014__x0000__x0000_oneeight@hanmail.net_x0006__x0000__x0000_D00173_x0005__x0000__x0001__x0008_®_x0001_Æ¤ÂìÓ Î
+_x0000__x0000_1052087391_x0003__x0000__x0001_°ÆÀÉÐÆ_x0008__x0000__x0000_20140217_x000D__x0000__x0000_010-6208-8112_x0006__x0000__x0000_121889_x0013__x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_È¹ìÓl­ _x0000_Ù³P­\¸3_x0000_8® _x0000_1_x0000_2_x0000_5_x0000__x0013__x0000__x0000_yonex0901@naver.com_x0008__x0000__x0000_20150122_x000E__x0000__x0000_37690004557937_x0006__x0000__x0000_D00181_x0004__x0000__x0001__x0000_É¤ÂìÓ Î
+_x0000__x0000_1410240836_x0003__x0000__x0001__x0015_¼½¬·_x0008__x0000__x0000_20140825_x000C__x0000__x0000_031-945-2007_x0007__x0000__x0001_½¬0®Ä³ _x0000__x000C_ÓüÈÜÂ_x0006__x0000__x0000_413819$_x0000__x0001_½¬0®Ä³ _x0000__x000C_ÓüÈÜÂ _x0000_DÅ¬¹·\¸ _x0000_5_x0000_5_x0000_ _x0000_-_x0000_8_x0000_1_x0000_ _x0000_(_x0000__x0008_®_x000C_ÍÙ³,_x0000_ _x0000__x000C_ÓüÈ_x0008_®_x000C_ÍXÕ_x0018_ÂÌ¬¹¥Ç)_x0000__x000C__x0000__x0001__x000C_ÓüÈÜÂ _x0000_0¼Ü´ü»4Ñ_x0004_È©Æl­¥Ç_x000D__x0000__x0000_010-9129-1126_x0017__x0000__x0000_leesjun1024@hanmail.net_x000E__x0000__x0000_37690004547137_x0006__x0000__x0000_D00183_x0003__x0000__x0001_T³_x001C_È|Ç
+_x0000__x0000_1171558537_x0003__x0000__x0001_iÖÐÆ Á_x000B__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_XÇX¹,_x0000_¡ÇTÖ_x0008__x0000__x0000_20141027_x000D__x0000__x0000_010-6333-2457	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_ÅÌl­_x0005__x0000__x0000_08078 _x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_ÅÌl­ _x0000_àÂ_x0015_È\¸ _x0000_2_x0000_7_x0000_5_x0000_ _x0000_ _x0000_(_x0000_àÂ_x0015_ÈÙ³,_x0000_ _x0000_àÂ¸Ò¬¹DÅ_x000C_Ó¸Ò)_x0000__x0010__x0000__x0001_ÁÀ_x0000_¬Ù³ _x0000_1_x0000_5Î _x0000_1_x0000_0_x0000_4_x0000_,_x0000_ _x0000_1_x0000_0_x0000_5_x0000_8Ö_x0011__x0000__x0000_thejeil@naver.com_x000D__x0000__x0000_010-9668-2210_x000E__x0000__x0000_37690004550437_x0006__x0000__x0000_D00184_x0005__x0000__x0001_$Æ¨°¤ÂìÓ Î
+_x0000__x0000_1322489384_x0003__x0000__x0001_Å+È¨º_x000D__x0000__x0001_´ÆÙ³0®l­©ÆÔ _x0000_aÅ8Á_x001C_Á¬¹ _x0000_xÆ_x0008__x0000__x0000_20141028
+_x0000__x0000_0315756464
+_x0000__x0000_0315755600_x0008__x0000__x0001_½¬0®Ä³ _x0000_¨°ÅüÈÜÂ_x0006__x0000__x0000_472881_x0016__x0000__x0001_½¬0®Ä³ _x0000_¨°ÅüÈÜÂ _x0000_ÄÉt¬$Æ¨°\¸ _x0000_8_x0000_0_x0000_6_x0000_ _x0000_-_x0000_1_x0000_4_x0000__x000D__x0000__x0000_010-9289-9637_x0012__x0000__x0000_jongmo83@naver.com_x000E__x0000__x0000_37690004552737_x0006__x0000__x0000_D00186_x0005__x0000__x0001_ä¹XÎìÓxÇ¸Ò
+_x0000__x0000_6091853217_x0003__x0000__x0001_iÖ­ÝÂ_x0008__x0000__x0000_20141202_x000C__x0000__x0000_055-298-7330_x0005__x0000__x0000_51378_x0011__x0000__x0001_½¬¨° _x0000_=ÌÐÆÜÂ _x0000_XÇ=Ìl­ _x0000__x0018_¼Ä¬\¸ _x0000_6_x0000_3_x0000__x000D__x0000__x0000_010-3561-0209_x000E__x0000__x0000_o2bbi@nate.com_x0008__x0000__x0000_20141212_x000E__x0000__x0000_37690004554037_x0006__x0000__x0000_D00190_x0005__x0000__x0001_p­°À¤ÂìÓ Î
+_x0000__x0000_4010657765_x0003__x0000__x0001__x0015_¼_x001C_Âl×	_x0000__x0001_¤ÂìÓ ÎXÇX¹,_x0000_ _x0000_©ÆÔ_x0008__x0000__x0000_20150406_x000D__x0000__x0000_010-9977-7141_x0008__x0000__x0001__x0004_È|·½Ä³ _x0000_p­°ÀÜÂ_x0005__x0000__x0000_54102_x000F__x0000__x0001__x0004_È½ _x0000_p­°ÀÜÂ _x0000_¨°_x0018_Â¡Á5_x0000_8® _x0000_4_x0000_2_x0000__x000F__x0000__x0001_1_x0000_0_x0000_1_x0000_8Ö(_x0000__x0018_Â¡ÁÙ³,_x0000_ _x0000_(Ì$Æ¹L¾)_x0000__x0013__x0000__x0000_shp7141@hanmaiL.net_x000E__x0000__x0000_37690004558537_x0006__x0000__x0000_D00192
+_x0000__x0001__x0001_Æ8»¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1222039517_x0005__x0000__x0001__x0001_Æ8»¤ÂìÓ Î_x0003__x0000__x0001_@®_x0001_Æ8»_x0008__x0000__x0000_20150608_x000C__x0000__x0000_032-523-1406_x000C__x0000__x0000_032-517-8009	_x0000__x0001_xÇÌ_x0011_­íÅÜÂ _x0000_½ÉÓl­_x0005__x0000__x0000_21337_x000D__x0000__x0000_010-4320-1406_x0012__x0000__x0000_YM1406@hanmail.net_x0007__x0000__x0001_A_x0000_ñ´	®(_x0000_T_x0000_S_x0000_)_x0000__x0005__x0000__x0000_13042_x0003__x0000__x0001_@®Ù³½¬_x000E__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_+_x0000_3_x0000_0_x0000__x000E__x0000__x0000_37690004561837_x0006__x0000__x0000_D00193_x000B__x0000__x0001_ÑÐ¤Â@Õ¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1320972497_x0006__x0000__x0001_ÑÐ¤Â@Õ¤ÂìÓ Î_x0003__x0000__x0001__x0015_¼_x0004_Ö=Ì_x0006__x0000__x0001_´ÆÙ³_x0004_È8»©ÆÔ_x0008__x0000__x0000_20150610_x000D__x0000__x0000_010-3706-2477_x0007__x0000__x0001_½¬0®Ä³ _x0000_l­¬¹ÜÂ_x0005__x0000__x0000_11907_x000F__x0000__x0001_½¬0® _x0000_l­¬¹ÜÂ _x0000_UÆ_x0019_ÂÌ\¸ _x0000_5_x0000_0_x0000_7_x0000_	_x0000__x0001_3_x0000_5Î _x0000_ÑÐ¤Â@Õ¤ÂìÓ Î_x000F__x0000__x0000_pspin@naver.com_x0005__x0000__x0000_22022_x0003__x0000__x0001_HÅ°ÆÄÉ_x000C__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_7_x0000_._x0000_5_x0000__x000E__x0000__x0000_37690004560137_x0006__x0000__x0000_D00195
+_x0000__x0001_¤ÂìÓ ÎLÑlÐ(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_6172249744_x0005__x0000__x0001_¤ÂìÓ ÎLÑlÐ_x0003__x0000__x0001_tÇÝÐ0®_x0006__x0000__x0001__x001C_ÈpÈÅÅ _x0000_Áä¹_x000C__x0000__x0001_õ¬_x0008_Æ _x0000_¤ÂìÓ Î©ÆÔ,_x0000_ _x0000_¡ÇTÖ_x000B__x0000__x0000_051-7564800_x000C__x0000__x0000_051-756-4801_x0005__x0000__x0000_48222_x0017__x0000__x0001_½°À_x0011_­íÅÜÂ _x0000_Ù³·l­ _x0000_+ÈiÕ´ÆÙ³¥Ç\¸ _x0000_4_x0000_0_x0000_¼8® _x0000_8_x0000_'_x0000__x0001_1_x0000_0_x0000_3_x0000_Ù³ _x0000_1_x0000_0_x0000_5_x0000_8Ö,_x0000_1_x0000_0_x0000_6_x0000_8Ö(_x0000_¬ÀÁÉÙ³,_x0000_½°À _x0000_DÅÜÂDÅÜ´ _x0000_TÏ$Æq¸ _x0000_XÕ²DÌ _x0000_DÅ_x000C_Ó¸Ò)_x0000__x000D__x0000__x0000_010-5578-1988_x0015__x0000__x0000_ltktennis@hanmail.net_x000B__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_8_x0000__x0008__x0000__x0000_20150611_x000E__x0000__x0000_37690004562437_x0006__x0000__x0000_D00196	_x0000__x0001__x0015_¬¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_5041920932_x0004__x0000__x0001__x0015_¬¤ÂìÓ Î_x0003__x0000__x0001__x0015_¬@Çl­_x000D__x0000__x0001_LÑÈ²¤Â©ÆÔ,_x0000_ _x0000_XÇX¹,_x0000_ _x0000_àÂ_x001C_¼_x000C__x0000__x0000_053-314-9090_x0005__x0000__x0000_41433_x000D__x0000__x0000_010-3828-0474_x0013__x0000__x0000_keg0417@hanmail.net_x000D__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_6_x0000_+_x0000_1_x0000_5_x0000__x0008__x0000__x0000_20150612_x000E__x0000__x0000_37690004565337_x0006__x0000__x0000_D00199
+_x0000__x0001_P´¬¹¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1283008985_x0003__x0000__x0001_@®_x0001_Æ Á_x000B__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_¤ÂìÓ ÎXÇX¹_x0008__x0000__x0000_20150703_x000C__x0000__x0000_031-911-4191_x000C__x0000__x0000_031-913-0067_x0006__x0000__x0000_410829_x000F__x0000__x0001_½¬0®Ä³à¬ÅÜÂ _x0000_|Ç°ÀÙ³l­_x0015_È_x001C_¼°ÀÙ³_x000E__x0000__x0001_1_x0000_1_x0000_4_x0000_8_x0000_-_x0000_1_x0000_3_x0000_ _x0000_1_x0000_5Î2_x0000_,_x0000_3_x0000_8Ö_x000D__x0000__x0000_010-4288-3563_x0012__x0000__x0000_usop2n@hanmail.net_x000D__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_6_x0000_+_x0000_2_x0000_3_x0000__x000E__x0000__x0000_37690004568237_x0006__x0000__x0000_D00201_x000E__x0000__x0001_(_x0000_üÈ)_x0000_¤ÂtÎtÇ¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_6278102573_x000B__x0000__x0001_¤ÂtÎtÇ¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000__x0003__x0000__x0001_@®1ÁÐÆ_x0006__x0000__x0001_Áä¹ÅÅ _x0000_Ä³ä¹_x0008__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_ä¹_x0010_È_x000C__x0000__x0000_041-566-1879_x000C__x0000__x0000_041-554-2732_x0005__x0000__x0000_31157"_x0000__x0001_©Í­Ì¨°Ä³ _x0000_ÌHÅÜÂ _x0000__x001C_Á½l­ _x0000_1¼_x001D_Á3_x0000_\¸ _x0000_2_x0000_9_x0000_ _x0000_ _x0000_(_x0000_1¼_x001D_ÁÙ³,_x0000_ _x0000_½¶É¹_x0008_Ã%¼)_x0000__x000D__x0000__x0000_010-4513-1879_x0011__x0000__x0000_kimsw000@nate.com_x000E__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_4_x0000_0_x0000_+_x0000_2_x0000_0_x0000__x0008__x0000__x0000_20150804_x000E__x0000__x0000_37690004570937_x0006__x0000__x0000_D00202_x0008__x0000__x0001_¤ÂìÓå²(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_3052275067_x0003__x0000__x0001_HÅü­¹Â_x000C__x0000__x0000_042-522-9566_x000C__x0000__x0000_042-271-4786_x0006__x0000__x0000_300810_x0017__x0000__x0001__x0000_³_x0004_È_x0011_­íÅÜÂ _x0000__x0011_Él­ _x0000_Ù³_x001C_Á_x0000_³\¸ _x0000_1_x0000_2_x0000_0_x0000_1_x0000_(_x0000_ÜÐÉÓÙ³)_x0000__x0007__x0000__x0001_¤ÂìÓå² _x0000_ÜÐÉÓ_x0010_È_x000B__x0000__x0000_01062224787_x0010__x0000__x0000_spodaq@naver.com_x000D__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_5_x0000_+_x0000_3_x0000_3_x0000__x0008__x0000__x0000_20150805_x000E__x0000__x0000_37690004571537_x0006__x0000__x0000_D00203	_x0000__x0001_ðÅTÏ¬¹DÅ(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_2041477980_x0004__x0000__x0001_ðÅTÏ¬¹DÅ_x0003__x0000__x0001_@®ÁÀ0®_x0006__x0000__x0001_Ä³Áä¹ _x0000_t¬$Á_x000D__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_´Ì!ÇÜÂ_x001C_Á&lt;»$ÁXÎ_x0008__x0000__x0000_20150806_x000C__x0000__x0000_02-3390-4345_x000C__x0000__x0000_02-3390-4344
+_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_Ù³_x0000_³8»l­_x0005__x0000__x0000_02496_x0011__x0000__x0001__x001C_Á¸Æ _x0000_Ù³_x0000_³8»l­ _x0000_Ý¹°Æ\¸1_x0000_2_x0000_8® _x0000_1_x0000_9_x0000__x000B__x0000__x0001_1_x0000_5Î _x0000_XÕtÇÐÆ¤ÂìÓ Î°ÀÅÅ_x000D__x0000__x0000_010-9089-5363_x0017__x0000__x0000_01090895363@hanmail.net_x000B__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_2_x0000_0_x0000__x000E__x0000__x0000_37690004572137_x0006__x0000__x0000_D00205_x0005__x0000__x0001_ÁLÑ¤ÂìÓ Î
+_x0000__x0000_1971301851_x0003__x0000__x0001_@®_x0001_Æ_x0018_Â_x0008__x0000__x0001_Ä³Áä¹ÅÅ _x0000_Ä³ä¹ÅÅ	_x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_4»íÅÅÅ_x000B__x0000__x0000_01063388568_x0008__x0000__x0001_½¬0®Ä³ _x0000_XÇ_x0015_È½ÜÂ_x0005__x0000__x0000_11806!_x0000__x0001_½¬0®Ä³ _x0000_XÇ_x0015_È½ÜÂ _x0000_$Æ©º\¸ _x0000_1_x0000_7_x0000_0_x0000_ _x0000_°Àä´È¹DÇ _x0000_DÅ_x000C_Ó¸Ò _x0000_4_x0000_1_x0000_2_x0000_-_x0000_7_x0000_0_x0000_6_x0000__x000D__x0000__x0000_010-6338-8568_x0011__x0000__x0000_3388568@naver.com_x0005__x0000__x0000_26002_x0003__x0000__x0001__x0015_¬ÜÐ8Ö_x0008__x0000__x0000_20220901_x000E__x0000__x0000_37690004700437_x0006__x0000__x0000_D00209_x0018__x0000__x0001_¤ÂìÓ Î_x000C_Õì·¤Â(_x0000_S_x0000_p_x0000_o_x0000_r_x0000_t_x0000_s_x0000_ _x0000_P_x0000_l_x0000_u_x0000_s_x0000_)_x0000_(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1192167071_x0003__x0000__x0001__x0015_¬ÜÂ¨º_x0006__x0000__x0001_Ä³Áä¹ _x0000_LÇÝÂ_x0008__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_\ÕÝÂ_x000B__x0000__x0000_02-871-5513	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x0000_­EÅl­_x0005__x0000__x0000_08750_x000F__x0000__x0001__x001C_Á¸Æ _x0000__x0000_­EÅl­ _x0000_àÂ¼¹\¸3_x0000_8® _x0000_4_x0000_0_x0000__x0005__x0000__x0001_ÀÉXÕ _x0000_1_x0000_5Î_x000D__x0000__x0000_010-7703-5353_x001A__x0000__x0000_tennisplus0122@esero.go.krX_x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_ _x0000_/_x0000_ _x0000_2_x0000_5_x0000_S_x0000_S_x0000_ _x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_ _x0000_/_x0000_ _x0000_2_x0000_4_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_9_x0000_._x0000_6_x0000_ _x0000_/_x0000_ _x0000_2_x0000_4_x0000_S_x0000_S_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_ _x0000_/_x0000_ _x0000_2_x0000_3_x0000_F_x0000_W_x0000_ _x0000__x0018_ÂüÈ _x0000_ìÅàÂ _x0000_ _x0000_1_x0000_2_x0000_ _x0000_(_x0000_ô²ù²Ç _x0000_Æ­Ì&lt;Ç\¸ _x0000_6_x0000_ _x0000__x0018_¼_x0001_Æ)_x0000__x0008__x0000__x0000_20160114_x000E__x0000__x0000_37690004577337_x0006__x0000__x0000_D00210_x0011__x0000__x0001_(_x0000_üÈ)_x0000_ÐÅtÇ_x001C_ÈtÇxÇ0Ñ´°TÁ °(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1268641398_x000C__x0000__x0000_031-761-8980_x000C__x0000__x0000_031-761-2140_x0005__x0000__x0000_12769_x000D__x0000__x0000_010-4552-3318	_x0000__x0000_1800-6142_x000E__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_4_x0000_0_x0000_+_x0000_2_x0000_5_x0000__x0008__x0000__x0000_20160121_x000E__x0000__x0000_37690004578037_x0006__x0000__x0000_D00256	_x0000__x0001_p¬1Á¤ÂìÓ Î(_x0000_Å°À)_x0000_
+_x0000__x0000_6210808090_x0003__x0000__x0001__x0015_È+È_x0015_¬_x0006__x0000__x0001_Ä³Áä¹ _x0000__x001C_ÈpÈ_x000B__x0000__x0001_ìÕ¤Â0®l­,_x0000_ _x0000_¤ÂìÓ Î©ÆÔ_x0008__x0000__x0000_20160412_x000C__x0000__x0000_055-387-3613_x000C__x0000__x0000_055-387-3615_x0008__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_Å°ÀÜÂ_x0005__x0000__x0000_50621 _x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_Å°ÀÜÂ _x0000__x001C_Á|ÇÙ³\¸ _x0000_2_x0000_5_x0000_ _x0000_ _x0000_(_x0000__x0011_É½Ù³,_x0000_ _x0000_$Ç ÁÝÀ_x0001_Æ´ÅP­äÂ)_x0000__x000D__x0000__x0000_</v>
+          </cell>
+          <cell r="Q35" t="e">
+            <v>#N/A</v>
           </cell>
           <cell r="R35" t="str">
             <v/>
           </cell>
-          <cell r="S35" t="str">
-            <v>010-5264-4932</v>
-          </cell>
-          <cell r="T35" t="str">
-            <v>yjjwon@hanmail.net</v>
+          <cell r="S35" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="T35" t="e">
+            <v>#N/A</v>
           </cell>
           <cell r="U35" t="str">
             <v/>
@@ -4382,8 +5045,8 @@
           <cell r="Y35" t="str">
             <v/>
           </cell>
-          <cell r="Z35" t="str">
-            <v>02-3142-7016</v>
+          <cell r="Z35" t="e">
+            <v>#N/A</v>
           </cell>
           <cell r="AA35" t="str">
             <v>N</v>
@@ -4402,11 +5065,11 @@
           </cell>
         </row>
         <row r="36">
-          <cell r="B36" t="str">
-            <v>D00085</v>
-          </cell>
-          <cell r="C36" t="str">
-            <v>성정레포츠</v>
+          <cell r="B36" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="C36" t="e">
+            <v>#N/A</v>
           </cell>
           <cell r="D36" t="str">
             <v>사용가능</v>
@@ -4414,14 +5077,14 @@
           <cell r="E36" t="str">
             <v>일반사업자</v>
           </cell>
-          <cell r="F36" t="str">
-            <v>3120525501</v>
-          </cell>
-          <cell r="G36" t="str">
-            <v>성정레포츠</v>
+          <cell r="F36" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="G36" t="e">
+            <v>#N/A</v>
           </cell>
           <cell r="H36" t="str">
-            <v>성기방</v>
+            <v>ÀÜÂ_x0005__x0000__x0000_15497_x0012__x0000__x0001_½¬0® _x0000_HÅ°ÀÜÂ _x0000_ÁÀ]¸</v>
           </cell>
           <cell r="I36" t="str">
             <v>소매업</v>
@@ -4429,14 +5092,14 @@
           <cell r="J36" t="str">
             <v>스포츠용품</v>
           </cell>
-          <cell r="K36" t="str">
-            <v>20090326</v>
+          <cell r="K36" t="e">
+            <v>#N/A</v>
           </cell>
           <cell r="L36" t="str">
             <v/>
           </cell>
-          <cell r="M36" t="str">
-            <v>041-556-7884</v>
+          <cell r="M36" t="e">
+            <v>#N/A</v>
           </cell>
           <cell r="N36" t="str">
             <v/>
@@ -4444,20 +5107,20 @@
           <cell r="O36" t="str">
             <v>충청남도 천안시</v>
           </cell>
-          <cell r="P36" t="str">
-            <v>331961</v>
-          </cell>
-          <cell r="Q36" t="str">
-            <v>충청남도 천안시 서북구 두정중8길 1-8</v>
+          <cell r="P36" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="Q36" t="e">
+            <v>#N/A</v>
           </cell>
           <cell r="R36" t="str">
             <v/>
           </cell>
-          <cell r="S36" t="str">
-            <v>010-5424-8640</v>
-          </cell>
-          <cell r="T36" t="str">
-            <v>sjreports@hanmail.net</v>
+          <cell r="S36" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="T36" t="e">
+            <v>#N/A</v>
           </cell>
           <cell r="U36" t="str">
             <v/>
@@ -4474,8 +5137,8 @@
           <cell r="Y36" t="str">
             <v/>
           </cell>
-          <cell r="Z36" t="str">
-            <v>041-556-7884</v>
+          <cell r="Z36" t="e">
+            <v>#N/A</v>
           </cell>
           <cell r="AA36" t="str">
             <v>N</v>
@@ -4495,10 +5158,73 @@
         </row>
         <row r="37">
           <cell r="B37" t="str">
-            <v>D00086</v>
+            <v>0_x0000_3_x0000_8Ö_x000D__x0000__x0000_010-3909-6608_x0015__x0000__x0000_sjs940421@hanmail.net_x000B__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_2_x0000_6_x0000__x0008__x0000__x0000_20171226_x000E__x0000__x0000_37690004615537_x0006__x0000__x0000_D00409_x0007__x0000__x0001_Æ%±¤Â _x0000_¤ÂìÓ Î
+_x0000__x0000_8624500277_x0003__x0000__x0001_tÇU³©Æ_x0008__x0000__x0000_20170905_x000C__x0000__x0000_041-357-1617_x0008__x0000__x0001_©Í­Ì¨°Ä³ _x0000_ù²ÄÉÜÂ_x0005__x0000__x0000_31777_x000E__x0000__x0001_©Í¨° _x0000_ù²ÄÉÜÂ _x0000_P­Ù³8® _x0000_1_x0000_2_x0000_4_x0000__x000D__x0000__x0000_010-3116-9915_x0013__x0000__x0000_ljy161617@naver.com_x0008__x0000__x0000_20171221_x000E__x0000__x0000_37690004616137_x0006__x0000__x0000_D00416_x0005__x0000__x0001__x001C_ÁÄÉ¤ÂìÓ Î
+_x0000__x0000_5920100957_x0003__x0000__x0001_@®ÉÓÜÐ_x000D__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_ _x0000__x0004_ÈÇÁÀp¬·ÅÅ_x0008__x0000__x0000_20180301_x000C__x0000__x0000_031-236-4936_x000C__x0000__x0000_031-216-4936_x0007__x0000__x0001_½¬0®Ä³ _x0000_©ÆxÇÜÂ_x0005__x0000__x0000_16833_x0013__x0000__x0001_½¬0® _x0000_©ÆxÇÜÂ _x0000__x0018_ÂÀÉl­ _x0000_ìÓ@Ç_x0000_³\¸ _x0000_4_x0000_6_x0000_7_x0000__x0016__x0000__x0001__x0018_ÂÀÉxÔt¹ÀÉ$ÆÔÆÜ´È¹lÐÁÀ_x0000_¬ _x0000_1_x0000_0_x0000_3_x0000_Ù³ _x0000_1_x0000_2_x0000_3_x0000_8Ö_x000D__x0000__x0000_010-4679-5630_x0013__x0000__x0000_ren7303@hanmail.net_x000E__x0000__x0000_37690004618437_x0006__x0000__x0000_D00431_x0006__x0000__x0001_¤ÂìÓ Îä¹È²DÅ
+_x0000__x0000_2701201033_x0003__x0000__x0001_8»¹ÂÄÉ_x0008__x0000__x0000_20180615_x000C__x0000__x0000_042-545-8511	_x0000__x0001__x0000_³_x0004_È_x0011_­íÅÜÂ _x0000_ Ç1Ál­_x0005__x0000__x0000_34210_x0016__x0000__x0001__x0000_³_x0004_È _x0000_ Ç1Ál­ _x0000_YÕXÕ_x0011_ÉYÅ\¸1_x0000_2_x0000_8_x0000_¼8® _x0000_2_x0000_3_x0000_-_x0000_8_x0000__x000B__x0000__x0001_1_x0000_0_x0000_2_x0000_8Ö _x0000_¤ÂìÓ Îä¹È²DÅ_x000D__x0000__x0000_010-6683-2114_x0013__x0000__x0000_capmoon39@naver.com_x0008__x0000__x0000_20180427_x000E__x0000__x0000_37690004623037_x0006__x0000__x0000_D00433_x000D__x0000__x0001__x0015_È_x0018_Â¤ÂìÓ Î _x0000_Æ%±¤Â _x0000__x0001_ÆüÈ_x0010_È
+_x0000__x0000_5293300343_x0003__x0000__x0001_@®Ù³ðÅ	_x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_ _x0000_XÇX¹_x0008__x0000__x0000_20170407_x000B__x0000__x0000_01048177736
+_x0000__x0000_0546367233_x0008__x0000__x0001_½¬ÁÀ½Ä³ _x0000__x0001_ÆüÈÜÂ_x0005__x0000__x0000_36138_x0013__x0000__x0001_½¬½ _x0000__x0001_ÆüÈÜÂ _x0000__x0000_³YÕ\¸2_x0000_0_x0000_1_x0000_¼8® _x0000_8_x0000_-_x0000_6_x0000__x0007__x0000__x0001_iÖ_x0008_®L¾)µ _x0000_1_x0000_5Î_x000D__x0000__x0000_010-4817-7736_x0013__x0000__x0000_kdy9249@hanmail.net_x0008__x0000__x0000_20180518_x000E__x0000__x0000_37690004624637_x0006__x0000__x0000_D00471_x000B__x0000__x0001_(_x0000_üÈ)_x0000_DÅüÈ_x0008_¸ìÓ Î__x0000_¹Ò_x0010_Ó_x000B__x0000__x0001_(_x0000_üÈ)_x0000_DÅüÈ_x0008_¸ìÓ Î-_x0000_¹Ò_x0010_Ó_x0008__x0000__x0000_20181026_x000B__x0000__x0000_02-489-1992_x000E__x0000__x0001_½¬0® _x0000__x0011_­üÈÜÂ _x0000_à¬½\¸ _x0000_3_x0000_4_x0000_0_x0000__x000D__x0000__x0000_070-4741-9644_x000E__x0000__x0000_37690004626937_x0006__x0000__x0000_D00490	_x0000__x0001_à¬ÅÜÂ0¼Ü´ü»4Ñ_x0011_ÖÖ
+_x0000__x0000_1288284226_x0003__x0000__x0001_tÇ8ÖÄÉ_x0008__x0000__x0000_20190315_x000B__x0000__x0000_01027161641_x0005__x0000__x0000_10223_x0014__x0000__x0001_½¬0® _x0000_à¬ÅÜÂ _x0000_|Ç°À_x001C_Ál­ _x0000__x0011_ÉYÅ\¸ _x0000_1_x0000_6_x0000_0_x0000_1_x0000__x001D__x0000__x0001_,_x0000_ _x0000_1_x0000_5Î(_x0000__x0000_³TÖÙ³,_x0000_ _x0000_à¬ÅÜÂ+ÈiÕ´ÆÙ³¥Ç _x0000_ÀÉXÕ1_x0000_5Î _x0000_C_x0000_-_x0000_0_x0000_8_x0000_)_x0000__x000D__x0000__x0000_010-2716-1641_x0012__x0000__x0000_76melany@gmail.com_x0005__x0000__x0000_19003_x0003__x0000__x0001_HÅ¬Ç°Æ_x000E__x0000__x0000_37690004628137_x0006__x0000__x0000_D00503_x0005__x0000__x0001_°tÇ¤Âü»4Ñ
+_x0000__x0000_6161951553_x0003__x0000__x0001_à¬ðÅüÈ
+_x0000__x0001_¤ÂìÓ Î©ÆÔ_x000F_¼0®ÀÐ©ÆÔ_x0008__x0000__x0000_20100913_x000C__x0000__x0000_064-712-4524_x000C__x0000__x0000_064-711-4524_x000B__x0000__x0001__x001C_ÈüÈ¹ÒÄ¼ÇXÎÄ³ _x0000__x001C_ÈüÈÜÂ_x0005__x0000__x0000_63087_x0013__x0000__x0001__x001C_ÈüÈ¹ÒÄ¼ÇXÎÄ³ _x0000__x001C_ÈüÈÜÂ _x0000_ÄÉp­8® _x0000_1_x0000_-_x0000_6_x0000__x000D__x0000__x0000_010-3639-7899_x0011__x0000__x0000_ktf1974@naver.com_x0003__x0000__x0001_@®1Át¬_x000B__x0000__x0000_01036397899_x0008__x0000__x0000_20190424_x000E__x0000__x0000_37690004630837_x0006__x0000__x0000_D00504_x0008__x0000__x0001_¤ÂÀÐ¤ÂìÓ Î__x0000_¹Ò_x0010_Ó
+_x0000__x0000_3031310445	_x0000__x0001_¤ÂÀÐ¤ÂìÓ Î(_x0000_©ÍüÈ)_x0000__x0003__x0000__x0001_LÇ_x0011_­l×_x0008__x0000__x0000_20070607_x000C__x0000__x0000_043-855-7688_x000C__x0000__x0000_043-848-3727_x0008__x0000__x0001_©Í­Ì½Ä³ _x0000_©ÍüÈÜÂ_x0005__x0000__x0000_27393_x000E__x0000__x0001_©Í½ _x0000_©ÍüÈÜÂ _x0000__x0015_Ö$Á\¸ _x0000_1_x0000_5_x0000_9_x0000__x0005__x0000__x0001_¤ÂÀÐ¤ÂìÓ Î_x000D__x0000__x0000_010-5303-1397_x0013__x0000__x0000_ekh3083@hanmail.net_x0006__x0000__x0000_D00513	_x0000__x0001__x001C_Á¸ÆÜÂ´Ì!ÇÖ__x0000_¹Ò_x0010_Ó
+_x0000__x0000_6078287556_x0006__x0000__x0001__x001C_Á¸ÆÜÂ´Ì!ÇÖ_x0003__x0000__x0001__x0015_¼ÐÆ_x001C_Â_x0003__x0000__x0001__x001C_ÁD¾¤Â_x0004__x0000__x0001_LÑÈ²¤Â¥Ç_x0008__x0000__x0000_20190614_x0001__x0000__x0000_0	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x0011_É·l­_x0005__x0000__x0000_02119_x000E__x0000__x0001__x001C_Á¸Æ _x0000__x0011_É·l­ _x0000_Ý¹°Æ\¸ _x0000_1_x0000_8_x0000_2_x0000__x0008__x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ´Ì!ÇÖ_x0008__x0000__x0000_20190617_x000E__x0000__x0000_37690004638937_x0006__x0000__x0000_D00515_x0004__x0000__x0001__x0001_Æ4»S_x0000_P_x0000_
+_x0000__x0000_4081497216_x0004__x0000__x0001__x0001_Æ4»s_x0000_p_x0000__x0003__x0000__x0001_@®U³	½_x0007__x0000__x0001_Ä³Áä¹,_x0000_ _x0000__x001C_ÈpÈ_x0011__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_ _x0000_±tÇ0®l­,_x0000_ _x0000_ìÕ¤Â0®l­_x0008__x0000__x0000_20070824_x000D__x0000__x0000_010-3622-7289_x000C__x0000__x0000_062-651-9942_x0008__x0000__x0001__x0011_­üÈ_x0011_­íÅÜÂ _x0000_¨°l­_x0005__x0000__x0000_61655_x000E__x0000__x0001__x0011_­üÈ _x0000_¨°l­ _x0000__x0000_³¨°_x0000_³\¸ _x0000_2_x0000_5_x0000_2_x0000_	_x0000__x0001_1¼´ÆÙ³,_x0000_ _x0000__x0001_Æ4»S_x0000_P_x0000__x0013__x0000__x0000_6519944@hanmail.net_x000D__x0000__x0000_(062)653-4141$_x0000__x0001_2_x0000_4_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_3_x0000_5_x0000_ _x0000_/_x0000_2_x0000_4_x0000_S_x0000_S_x0000__x0018_ÂüÈìÅàÂ _x0000_3_x0000_5_x0000_ _x0000_/_x0000_ _x0000__x0018_Â_x0008_®½qÈ _x0000_2_x0000_ÔÆµÑ_x001C_È_x0008__x0000__x0000_20190531_x000E__x0000__x0000_37690004634337_x0006__x0000__x0000_D00517_x000B__x0000__x0001_O_x0000_K_x0000_ _x0000_¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1293177008_x0003__x0000__x0001_tÇ_x0001_Æ±Æ
+_x0000__x0001_Ä³Áä¹,_x0000_Ä³ä¹,_x0000__x001C_ÁD¾¤Â_x0011__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_l­ä¹_x0000_³Õ,_x0000_t¬&lt;»­ÌÁ©ÆíÅ_x0008__x0000__x0000_20071108_x000C__x0000__x0000_031-708-3066
+_x0000__x0000_0317083067_x0005__x0000__x0000_13504_x0017__x0000__x0001_½¬0® _x0000_1Á¨°ÜÂ _x0000_½ù²l­ _x0000_¥Çø»\¸1_x0000_2_x0000_2_x0000_¼8® _x0000_3_x0000_-_x0000_1_x0000__x0005__x0000__x0001_(_x0000_|ÅÑÐÙ³)_x0000__x000D__x0000__x0000_010-8714-3324_x0014__x0000__x0000_75winwin@hanmail.net_x000B__x0000__x0000_01087143324_x000E__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_5_x0000_+_x0000_2_x0000_2_x0000__x0008__x0000__x0000_20190621_x000E__x0000__x0000_37690004635037_x0006__x0000__x0000_D00519_x0005__x0000__x0001__x0004_Ç_x0008_±¤ÂìÓ Î
+_x0000__x0000_3160449978_x0003__x0000__x0001_\Í_x0004_ÖÄÉ_x0008__x0000__x0000_20140927_x000D__x0000__x0000_010-6482-0228_x000C__x0000__x0000_041-665-1857_x0008__x0000__x0001_©Í­Ì¨°Ä³ _x0000__x001C_Á°ÀÜÂ_x0005__x0000__x0000_31993_x000F__x0000__x0001_©Í¨° _x0000__x001C_Á°ÀÜÂ _x0000_(ÇÀÉ1_x0000_6_x0000_\¸ _x0000_2_x0000_2_x0000__x0008__x0000__x0001_C_x0000_Ù³ _x0000_(_x0000_Ù³8»Ù³)_x0000__x0011__x0000__x0000_chj1981@naver.com_x000D__x0000__x0000_010-9112-9996_x0008__x0000__x0001_6_x0000_ÔÆ _x0000_üÈ8»µÑ_x001C_È/_x0000__x0008__x0000__x0000_20190620_x000E__x0000__x0000_37690004636637_x0006__x0000__x0000_D00524
+_x0000__x0001_üÈÝÂÖ¬À _x0000_©ÆxÇÆ%±¤Â
+_x0000__x0000_7968702997_x0003__x0000__x0001_@®ÄÉ©Æ_x0008__x0000__x0000_20150409_x000D__x0000__x0000_010-8881-0413_x0005__x0000__x0000_16967_x0014__x0000__x0001_½¬0® _x0000_©ÆxÇÜÂ _x0000_0®e×l­ _x0000_àÂ_x0008_¬\¸5_x0000_7_x0000_¼8® _x0000_7_x0000_
+_x0000__x0001_(_x0000_àÂ_x0008_¬Ù³,_x0000_ÐÅ¤Â_x001C_ÈtÇ)_x0000__x0013__x0000__x0000_goodester@naver.com_x0007__x0000__x0001_2_x0000_ÔÆ _x0000__x0018_Â_x0008_®µÑ_x001C_È_x0008__x0000__x0000_20190711_x000E__x0000__x0000_37690004640537_x0006__x0000__x0000_D00526_x0006__x0000__x0001_ìÅ_x0018_Â _x0000_Æ%±¤Â
+_x0000__x0000_6765400493_x0003__x0000__x0001_@® ÁU³_x0008__x0000__x0000_20190701_x000D__x0000__x0000_010-2066-5376_x0008__x0000__x0001__x0004_È|·¨°Ä³ _x0000_ìÅ_x0018_ÂÜÂ_x0005__x0000__x0000_59685_x000D__x0000__x0001__x0004_È¨° _x0000_ìÅ_x0018_ÂÜÂ _x0000_ÈÀ0Ñ\¸ _x0000_2_x0000_5_x0000__x0005__x0000__x0001_(_x0000_àÂ0®Ù³)_x0000__x0014__x0000__x0000_junsoo5376@naver.com_x0003__x0000__x0001_@®_x0000_É_x0018_Â_x0002__x0000__x0001__x0000_¬qÈ_x000E__x0000__x0000_37690004621737_x0006__x0000__x0000_D00527_x000C__x0000__x0001_(_x0000_üÈ)_x0000_tÇÐÅ¤Â¤ÂìÓ Î__x0000_¹Ò_x0010_Ó
+_x0000__x0000_2848100873	_x0000__x0001_(_x0000_üÈ)_x0000_tÇÐÅ¤Â¤ÂìÓ Î_x0003__x0000__x0001__x0015_¼_x0018_Â Ì_x000C__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_ _x0000_µÑàÂ_x0010_Óä¹ÅÅ_x0008__x0000__x0000_20171228_x000C__x0000__x0000_031-763-2002_x000C__x0000__x0000_031-763-0400_x0005__x0000__x0000_12739_x000D__x0000__x0001_½¬0® _x0000__x0011_­üÈÜÂ _x0000_µÑø»\¸ _x0000_9_x0000_2_x0000__x000D__x0000__x0000_010-4085-9292_x0014__x0000__x0000_gysports@hanmail.net_x0008__x0000__x0000_20190725_x000E__x0000__x0000_37690004641137_x0006__x0000__x0000_D00528_x0007__x0000__x0001_2_x0000_0_x0000_8_x0000_0_x0000_Æ%±¤Â
+_x0000__x0000_8131601217_x0003__x0000__x0001_@®ÀÉÐÆ_x000C__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_ _x0000_¤ÂìÓ ÎXÇX¹_x000C__x0000__x0000_061-795-2088_x0008__x0000__x0001__x0004_È|·¨°Ä³ _x0000__x0011_­ÅÜÂ_x0005__x0000__x0000_57767_x0010__x0000__x0001__x0004_È¨° _x0000__x0011_­ÅÜÂ _x0000_ÀÉÙ³8® _x0000_3_x0000_0_x0000_-_x0000_3_x0000_5_x0000__x000D__x0000__x0000_010-9434-2223_x0013__x0000__x0000_3530162@hanmail.net_x0008__x0000__x0000_20190730_x000E__x0000__x0000_37690004643437_x0006__x0000__x0000_D00529	_x0000__x0001_°Æ¬¹¤ÂìÓ Î(_x0000__x0011_­üÈ)_x0000_
+_x0000__x0000_5212100399_x0003__x0000__x0001_$Æ_x0018_ÂÔÆ_x0008__x0000__x0000_20191030_x000C__x0000__x0000_062-434-8963_x0008__x0000__x0001__x0011_­üÈ_x0011_­íÅÜÂ _x0000_½l­_x0005__x0000__x0000_61185_x0018__x0000__x0001__x0011_­üÈ _x0000_½l­ _x0000_¨Ìè²ðÅàÂ\¸ _x0000_2_x0000_9_x0000_¼8® _x0000_1_x0000_5_x0000_ _x0000_ÀÉÁÀ1_x0000_5Î_x000D__x0000__x0001_½l­+ÈiÕ´Ì!Ç_x0000_­ _x0000_´Ì!Ç©ÆÔ_x0010_È_x000D__x0000__x0000_010-4614-9599_x000F__x0000__x0000_19qkqn@daum.net_x000B__x0000__x0000_01046149599_x000D__x0000__x0001_2_x0000_6_x0000_F_x0000_W_x0000_ _x0000_©ÆÔ_x0018_ÂüÈ _x0000_ø»8ÌìÅ_x0008__x0000__x0000_20190802_x000E__x0000__x0000_37690004642837_x0006__x0000__x0000_D00530_x000B__x0000__x0001_àÂàÂ´Ì!Ç¬À _x0000_2_x0000_1_x0000___x0000_¹Ò_x0010_Ó
+_x0000__x0000_1288148960_x000B__x0000__x0001_üÈÝÂÖ¬À _x0000_àÂàÂ´Ì!Ç2_x0000_1_x0000__x0003__x0000__x0001_iÖ¹Â8Ö_x0002__x0000__x0001__x001C_ÈpÈ_x0008__x0000__x0000_20000523
+_x0000__x0000_0319453376
+_x0000__x0000_0319450458_x0005__x0000__x0000_10844_x0013__x0000__x0001_½¬0® _x0000__x000C_ÓüÈÜÂ _x0000_ÔÆq¸tº _x0000_¬_x0014_¼_x0004_Ç8® _x0000_1_x0000_2_x0000_3_x0000__x0006__x0000__x0001_àÂàÂ´Ì!Ç$ÁD¾_x0014__x0000__x0000_sinsin5980@naver.com_x0008__x0000__x0000_20190823_x000E__x0000__x0000_37690004645737_x0006__x0000__x0000_D00534
+_x0000__x0001_2_x0000_0_x0000_1_x0000_9_x0000_ _x0000_TÏ¬¹DÅ$Æ_x0008_Õ
+_x0000__x0000_0000000000	_x0000__x0000_023352551_x0005__x0000__x0000_03964_x000E__x0000__x0001__x001C_Á¸Æ _x0000_È¹ìÓl­ _x0000_ìÓ@Ç\¸ _x0000_1_x0000_2_x0000_0_x0000__x0004__x0000__x0001_U³|ÇL¾)µ_x0008__x0000__x0000_20190918_x0006__x0000__x0000_D00538_x000E__x0000__x0001__x0000_³\Õ¤ÂìÓ Î°ÀÅÅ_x0011_ÖÙ³pÈiÕ__x0000_¹Ò_x0010_Ó
+_x0000__x0000_1168210643_x0003__x0000__x0001_üÈ_x0015_Ö8Ö	_x0000__x0001_´ÆÙ³©Æl­ _x0000__x000F_¼ _x0000_$ÁXÎ_x0008__x0000__x0000_19700319	_x0000__x0000_027867761	_x0000__x0000_027867764_x0005__x0000__x0000_07345_x000E__x0000__x0001__x001C_Á¸Æ _x0000__x0001_Æñ´ìÓl­ _x0000_6_x0000_3_x0000_\¸ _x0000_4_x0000_0_x0000__x0014__x0000__x0001_7_x0000_2_x0000_3_x0000_8Ö _x0000_(_x0000_ìÅXÇÄ³Ù³,_x0000_ _x0000_|·tÇ_x0004_Õ$Æ&lt;Õ¤ÂTÑ)_x0000__x0008__x0000__x0000_20190724_x000E__x0000__x0000_37690004646337_x0006__x0000__x0000_D00539_x000C__x0000__x0001_(_x0000_üÈ)_x0000__x0004_²¬¹ÐÅ¤ÂdÅÀÉ__x0000_¹Ò_x0010_Ó
+_x0000__x0000_2018609461	_x0000__x0001_(_x0000_üÈ)_x0000__x0004_²¬¹ÐÅ¤ÂdÅÀÉ_x0002__x0000__x0001_@®%Æ_x000C__x0000__x0000_031-527-8417_x0005__x0000__x0000_12245_x0015__x0000__x0001_½¬0® _x0000_¨°ÅüÈÜÂ _x0000_½¬_x0015_¬\¸2_x0000_9_x0000_4_x0000_¼8® _x0000_3_x0000_2_x0000_-_x0000_1_x0000__x0008__x0000__x0000_20190626_x000E__x0000__x0000_37690004648637_x0006__x0000__x0000_D00541_x0007__x0000__x0001_íÂtÇ_x0004_¬ÀÉ__x0000_¹Ò_x0010_Ó_x000C__x0000__x0001_¹Ò_x0010_Ó _x0000_p¬· Á _x0000_ÇÜÂ _x0000_ñ´]¸_x000D__x0000__x0000_010-2850-8962_x0003__x0000__x0001_Æ%±¤Â_x0008__x0000__x0000_20191014_x000E__x0000__x0000_37690004647037_x0006__x0000__x0000_D00543	_x0000__x0001_Á¨ºÇè²´Ìõ¼__x0000_¹Ò_x0010_Ó_x0004__x0000__x0001_Ù³¹ÂµÑÁÀ_x0008__x0000__x0000_20191016_x000E__x0000__x0000_37690004674237_x0006__x0000__x0000_D00546_x000B__x0000__x0001_8ÁÄÉ¤ÂìÓ Î)¼ü¬ÄÖ__x0000_¹Ò_x0010_Ó_x0005__x0000__x0000_06964_x000E__x0000__x0001__x001C_Á¸Æ _x0000_Ù³Çl­ _x0000_ÁÀÄ³\¸ _x0000_2_x0000_4_x0000_2_x0000__x0008__x0000__x0000_20191023_x000E__x0000__x0000_37690004649237_x0006__x0000__x0000_D00549	_x0000__x0001_)¼ü¬ÄÖà¬Ç_x0008_Í__x0000_¹Ò_x0010_Ó
+_x0000__x0000_1318303677_x0008__x0000__x0001_xÇÌà¬Ç_x0008_Íñ´YÕP­_x0003__x0000__x0001_@®_x001C_Âl×_x000C__x0000__x0000_032-433-0464	_x0000__x0001_xÇÌ_x0011_­íÅÜÂ _x0000_¨°Ù³l­_x0005__x0000__x0000_21685_x0014__x0000__x0001_xÇÌ _x0000_¨°Ù³l­ _x0000_DÅTÅ_x0000_³\¸1_x0000_5_x0000_0_x0000_3_x0000_¼8® _x0000_4_x0000_8_x0000__x000F__x0000__x0000_gojan@ice.go.kr_x0008__x0000__x0000_20191028_x0006__x0000__x0000_D00550
+_x0000__x0001_TÏ¬¹DÅü»4Ñ¬À·__x0000_¹Ò_x0010_Ó_x0008__x0000__x0000_20191108_x000E__x0000__x0000_37690004650237_x0006__x0000__x0000_D00554	_x0000__x0001_üÈýÅ_x0008_Íñ´YÕP­__x0000_¹Ò_x0010_Ó
+_x0000__x0000_1288302804_x0003__x0000__x0001__x0015_¼	½ Á_x000B__x0000__x0000_0319120031 _x0005__x0000__x0000_10385_x0012__x0000__x0001_½¬0® _x0000_à¬ÅÜÂ _x0000_|Ç°À_x001C_Ál­ _x0000__x0015_¬ Á\¸ _x0000_2_x0000_9_x0000__x0006__x0000__x0001_üÈýÅ_x0008_Íñ´YÕP­_x0008__x0000__x0000_20191118_x0006__x0000__x0000_D00557_x000B__x0000__x0001_üÈÝÂÖ¬À _x0000_tÎxÇÜ´ÉÅtÐÉ
+_x0000__x0000_7318601539_x0003__x0000__x0001_¥Ç¬Ç_x0001_Ö_x0008__x0000__x0000_20191210_x000D__x0000__x0000_010-2600-1460_x0005__x0000__x0000_06065_x000E__x0000__x0001__x001C_Á¸Æ _x0000__x0015_¬¨°l­ _x0000_ Á¹\¸ _x0000_7_x0000_2_x0000_0_x0000__x000E__x0000__x0001_ Ç_x0000_­L¾)µ _x0000_ÀÉXÕ1_x0000_5Î _x0000_ô¼Ü´|·xÇ_x0013__x0000__x0000_paul777@hanmail.net_x0008__x0000__x0000_20200914_x0006__x0000__x0000_D00560	_x0000__x0001_üÈÝÂÖ¬À _x0000__x0014_µÀÉ8ÑÄÉ
+_x0000__x0000_6418600391_x0003__x0000__x0001__x0015_¼¼ Á_x0019__x0000__x0001_ôÎèÔ0Ñ _x0000__x000F_¼ _x0000_üÈÀ¼0®0®,_x0000_ _x0000_´ÆÙ³ _x0000__x000F_¼ _x0000_½¬0®©ÆÔ _x0000_Ä³ä¹ _x0000__x0008__x0000__x0000_20160401_x000B__x0000__x0000_02-707-3326	_x0000__x0000_027038437	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_©Æ°Àl­_x0005__x0000__x0000_04366_x0011__x0000__x0001__x001C_Á¸ÆÜÂ _x0000_Ù³Çl­ _x0000__x0000_³)¼Ù³1_x0000_5_x0000_8® _x0000_3_x0000_0_x0000__x000D__x0000__x0000_010-4722-8308_x0014__x0000__x0000_jin@digitaljin.co.kr_x0005__x0000__x0000_24016_x0003__x0000__x0001_8»=Ì_x0018_Â_x0008__x0000__x0000_20191220_x000E__x0000__x0000_37690004655437_x0017__x0000__x0001_0_x0000_1_x0000_0_x0000_-_x0000_7_x0000_4_x0000_1_x0000_4_x0000_-_x0000_1_x0000_6_x0000_7_x0000_8_x0000_ _x0000_$Ç1ÁÜ­ _x0000_(_x0000_A_x0000_/_x0000_S_x0000_)_x0000__x0006__x0000__x0000_D00563	_x0000__x0001__x0001_ÆÅÅ3_x0000__x0000_Ó0®ÀÐ__x0000_¹Ò_x0010_Ó	_x0000__x0000_023332568_x0008__x0000__x0000_20200101_x0006__x0000__x0000_D00564_x0008__x0000__x0001_ü»4Ñ¤ÂìÓ Î__x0000_¹Ò_x0010_Ó_x0005__x0000__x0001__x001C_¬xÇ¬ÀÅÅÇ
+_x0000__x0000_1013095995_x0005__x0000__x0001_ü»4Ñ¤ÂìÓ Î_x0003__x0000__x0001_à¬_x0015_È%Æ_x0008__x0000__x0000_00000000_x0008__x0000__x0001__x0004_È|·½Ä³ _x0000_à¬=Ìp­_x0005__x0000__x0000_56430_x0012__x0000__x0001__x0004_È½ _x0000_à¬=Ìp­ _x0000_à¬=ÌMÇ _x0000_ÔÆá¬5_x0000_8® _x0000_1_x0000_1_x0000__x0008__x0000__x0000_20200103_x000E__x0000__x0000_37690004654837_x0006__x0000__x0000_D00568_x0007__x0000__x0001_\Õ¤ÂìÓ Î__x0000_¹Ò_x0010_Ó
+_x0000__x0000_3031277167_x0004__x0000__x0001_\Õ¤ÂìÓ Î_x0003__x0000__x0001_iÖ+ÈôÅ_x000D__x0000__x0000_010-5103-6696_x0005__x0000__x0000_27357_x0010__x0000__x0001_©Í½ _x0000_©ÍüÈÜÂ _x0000_Ä¬+º_x0000_³\¸ _x0000_9_x0000_1_x0000_-_x0000_1_x0000__x0005__x0000__x0001_(_x0000_P­_x0004_ÖÙ³)_x0000__x0016__x0000__x0000_archihjy@hometax.go.kr_x0008__x0000__x0000_20200203_x000E__x0000__x0000_37690004658337_x0006__x0000__x0000_D00574_x0006__x0000__x0001_¤Âä¹ñÂ¤ÂìÓ Î
+_x0000__x0000_1238638685_x0003__x0000__x0001_tÇ Ìl×_x0008__x0000__x0001_Ä³Áä¹,_x0000_ _x0000__x001C_ÈpÈÅÅ_x000C__x0000__x0001__x0004_ÈÇÁÀp¬·,_x0000_ _x0000_¤ÂìÓ Î©ÆÔ_x0008__x0000__x0000_20130615
+_x0000__x0000_0314271787_x000B__x0000__x0000_05054271788_x0005__x0000__x0000_15850_x000E__x0000__x0001_½¬0® _x0000_p­ìÓÜÂ _x0000_à¬°À\¸ _x0000_1_x0000_6_x0000_6_x0000__x000F__x0000__x0001_S_x0000_K_x0000_¤¼ðÒÀÆ _x0000_1_x0000_0_x0000_4_x0000_Ù³ _x0000_5_x0000_0_x0000_6_x0000_8Ö_x000D__x0000__x0000_010-3690-1786_x0011__x0000__x0000_4271787@naver.com_x000B__x0000__x0000_07046403943_x0005__x0000__x0000_19022_x0003__x0000__x0001_àÂÙ³ÐÆ_x0008__x0000__x0000_20200220_x000E__x0000__x0000_37690004666837_x0006__x0000__x0000_D00576_x0008__x0000__x0001_1¼È¹¤ÂìÓ Î__x0000_¹Ò_x0010_Ó_x0008__x0000__x0000_20200302_x000E__x0000__x0000_37690004667437_x0006__x0000__x0000_D00578_x0008__x0000__x0001_MÖ1ÁÆ%±¤Â__x0000_¹Ò_x0010_Ó_x0006__x0000__x0001_MÖ1Á _x0000_Æ%±¤Â_x0008__x0000__x0000_20200316_x0005__x0000__x0000_32223_x0016__x0000__x0001_©Í¨° _x0000_MÖ1Áp­ _x0000_MÖ1ÁMÇ _x0000_pÈÅ\¸1_x0000_0_x0000_3_x0000_¼8® _x0000_3_x0000_5_x0000__x000E__x0000__x0000_17-2 17-5 17-6_x000E__x0000__x0000_37690004669737_x0006__x0000__x0000_D00580_x0008__x0000__x0001__x0008_®_x0001_Æ¤ÂìÓ Î__x0000_¹Ò_x0010_Ó_x0005__x0000__x0000_04005_x0010__x0000__x0001__x001C_Á¸Æ _x0000_È¹ìÓl­ _x0000_Ù³P­\¸3_x0000_8® _x0000_1_x0000_2_x0000_5_x0000__x0003__x0000__x0000_205_x0008__x0000__x0000_20200324_x000E__x0000__x0000_37690004671337_x0006__x0000__x0000_D00585_x0008__x0000__x0001_Tº_x0014_µ¬ÀtÇ¸Å__x0000_¹Ò_x0010_Ó
+_x0000__x0000_2102438564_x0005__x0000__x0001_Tº_x0014_µ¬ÀtÇ¸Å_x0003__x0000__x0001__x0015_¼ÌÕÝÂ_x000D__x0000__x0001__x001C_ÁD¾¤Â,_x0000_ _x0000_Ä³ä¹ _x0000__x000F_¼ _x0000_Áä¹ÅÅ_x0010__x0000__x0001_$ÁXÎ_x000F_¼ ÇÀÉô¼_x0018_Â,_x0000_ _x0000_8»l­,_x0000_ _x0000_0®P±Ô_x000B__x0000__x0000_01088813256	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_1ÁÙ³l­_x0005__x0000__x0000_04750_x000F__x0000__x0001__x001C_Á¸Æ _x0000_1ÁÙ³l­ _x0000_à¬°ÀÇ\¸ _x0000_2_x0000_8_x0000_4_x0000__x0018__x0000__x0001_3_x0000_5Î _x0000_3_x0000_0_x0000_1_x0000_8Ö _x0000_6_x0000_1_x0000_äÂ _x0000_(_x0000_Õù²Ù³,_x0000_ _x0000_1ÁÙ³äÀt¹Ý¹)_x0000__x0015__x0000__x0000_eg6753256@hanmail.net_x0008__x0000__x0000_20200525_x000E__x0000__x0000_37690004672037_x0006__x0000__x0000_D00587_x000B__x0000__x0001_üÈÝÂÖ¬À _x0000_°tÇ¤Â(Ó_x0000_¼¬¹
+_x0000__x0000_3658101754_x0003__x0000__x0001__x0015_¼=Ìü»_x000B__x0000__x0001_¤ÂìÓ Î _x0000_©ÆÔ _x0000_Ä³Áä¹ÅÅ_x0008__x0000__x0000_20200407_x000C__x0000__x0000_031-341-8677_x000D__x0000__x0000_031-8068-5999_x0007__x0000__x0001_½¬0®Ä³ _x0000_XÇUÆÜÂ_x0005__x0000__x0000_16011_x000C__x0000__x0001_½¬0® _x0000_XÇUÆÜÂ _x0000_­ÌÄ¬\¸ _x0000_2_x0000__x000D__x0000__x0000_010-7417-4040_x0011__x0000__x0000_cmin401@naver.com_x0008__x0000__x0000_20200602_x000E__x0000__x0000_37690004673637_x0006__x0000__x0000_D00600	_x0000__x0001_Ä³á¬_x0008_Íñ´YÕP­__x0000_¹Ò_x0010_Ó_x0003__x0000__x0001_$Çø»l×_x0003__x0000__x0001_½Ù³°À_x0002__x0000__x0001_Ç_x0000_³	_x0000__x0000_025804577_x0005__x0000__x0000_06205_x0010__x0000__x0001__x001C_Á¸Æ _x0000__x0015_¬¨°l­ _x0000_ Á¹\¸6_x0000_4_x0000_8® _x0000_3_x0000_3_x0000__x0008__x0000__x0001__x001C_Á¸ÆÄ³á¬_x0008_Íñ´YÕP­_x0008__x0000__x0000_20201015_x0006__x0000__x0000_D00602_x000C__x0000__x0001__x001C_Á¸ÆÜÂ0¼Ü´ü»4Ñ_x0011_ÖÖ__x0000_¹Ò_x0010_Ó
+_x0000__x0000_2048204832	_x0000__x0001__x001C_Á¸ÆÜÂ0¼Ü´ü»4Ñ_x0011_ÖÖ_x0003__x0000__x0001__x0015_¼¬ÇXÖ_x000D__x0000__x0000_010-4359-4949_x0004__x0000__x0001_5_x0000_0_x0000_2_x0000_8Ö_x0008__x0000__x0000_20201102_x000E__x0000__x0000_37690004675937_x0006__x0000__x0000_D00605_x000B__x0000__x0001_ÌHÅàÂHÅ_x0008_Íñ´YÕP­__x0000_¹Ò_x0010_Ó
+_x0000__x0000_3128300473_x0003__x0000__x0001_@®_x0015_È`Å_x0008__x0000__x0000_622-7063_x0005__x0000__x0000_31125_x0013__x0000__x0001_©Í¨° _x0000_ÌHÅÜÂ _x0000_Ù³¨°l­ _x0000_ÐÆ1Á2_x0000_5_x0000_8® _x0000_2_x0000_1_x0000__x0008__x0000__x0001_ÌHÅàÂHÅ_x0008_Íñ´YÕP­_x0008__x0000__x0000_20201116_x0006__x0000__x0000_D00608_x000E__x0000__x0001_(_x0000_üÈ)_x0000_ _x0000__x0018_±¼ÐÆ¤ÂìÓ Î(_x0000_T_x0000_S_x0000_)_x0000__x0008__x0000__x0000_20210107_x0005__x0000__x0000_38661_x000E__x0000__x0001_½¬½ _x0000_½¬°ÀÜÂ _x0000_½¬°À\¸ _x0000_2_x0000_4_x0000_3_x0000__x000B__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_2_x0000_4_x0000__x000E__x0000__x0000_37690004676537_x0006__x0000__x0000_D00609	_x0000__x0001__x0008_®_x0001_Æ¤ÂìÓ Î(_x0000_T_x0000_S_x0000_)_x0000_$_x0000__x0001_2_x0000_4_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_4_x0000_0_x0000_ _x0000_/_x0000__x0001_ÆÅÅ¬ÀÐÆ _x0000_Æ­Ì(_x0000_¥Ç0® _x0000_ø»p¬·,_x0000_ _x0000__x0018_Â_x0008_® _x0000_½tÇÕ)_x0000__x000E__x0000__x0000_37690004677137_x0006__x0000__x0000_D00610	_x0000__x0001_XÕD¾¤ÂìÓ Î(_x0000_T_x0000_S_x0000_)_x0000__x0016__x0000__x0000_daegu-daejin@naver.com_x000F__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_4_x0000_0_x0000_+_x0000_5_x0000_0_x0000__x000E__x0000__x0000_37690004678837_x0006__x0000__x0000_D00611	_x0000__x0001_1¼È¹¤ÂìÓ Î(_x0000_T_x0000_S_x0000_)_x0000__x0005__x0000__x0000_04011_x000F__x0000__x0001__x001C_Á¸Æ _x0000_È¹ìÓl­ _x0000_Ù³P­\¸9_x0000_8® _x0000_9_x0000_5_x0000__x0010__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_7_x0000_0_x0000_+_x0000_1_x0000_8_x0000_5_x0000__x000E__x0000__x0000_37690004679437_x0006__x0000__x0000_D00612_x000D__x0000__x0001_¼À1Á¤ÂìÓ Î(_x0000_8»½¬)_x0000_(_x0000_T_x0000_S_x0000_)_x0000__x0005__x0000__x0000_36956_x000E__x0000__x0001_½¬½ _x0000_8»½¬ÜÂ _x0000_¨º_x0004_È\¸ _x0000_1_x0000_4_x0000_6_x0000_V_x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_0_x0000_+_x0000_6_x0000_ _x0000_/_x0000_ _x0000_2_x0000_5_x0000_S_x0000_S_x0000_ _x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_0_x0000_ _x0000_/_x0000_ _x0000_ _x0000_2_x0000_4_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_5_x0000_ _x0000_/_x0000_ _x0000_2_x0000_4_x0000_S_x0000_S_x0000__x0018_ÂüÈìÅàÂ _x0000_5_x0000_ _x0000_/_x0000_ _x0000_2_x0000_3_x0000_F_x0000_W_x0000_ _x0000__x0018_ÂüÈ _x0000_ìÅàÂ _x0000_1_x0000_0_x0000_ _x0000_/_x0000_ _x0000_2_x0000_3_x0000_S_x0000_S_x0000_ _x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_0_x0000__x000E__x0000__x0000_37690004680437_x0006__x0000__x0000_D00614_x0008__x0000__x0001__x0001_ÆÅÅ4_x0000__x0000_ÓÇXÇä¹¥Ç_x000B__x0000__x0000_02-335-2551_x0008__x0000__x0000_20210115_x0006__x0000__x0000_D00616_x0005__x0000__x0001_8Á_x0001_Æ¤ÂìÓ Î
+_x0000__x0000_8055100483_x0005__x0000__x0001_¤ÂìÓ ÎXÇX¹_x0008__x0000__x0000_20210125_x000D__x0000__x0000_070-8808-8799_x0017__x0000__x0000_yonexsejinspo@naver.com_x000E__x0000__x0000_37690004683337_x0006__x0000__x0000_D00620_x000D__x0000__x0001_üÈÝÂÖ¬À _x0000_8ÁÄÉ¤ÂìÓ Î__x0000_è²Å³
+_x0000__x0001_X_x0000_7_x0000_ _x0000_è²Å³¨ºx³ _x0000_TÏÜ´_x0008__x0000__x0000_20210226_x000E__x0000__x0000_37690004684037_x0006__x0000__x0000_D00621_x000E__x0000__x0001_¬À$Á´Ì!Ç_x0000_­(_x0000__x000C_Õ_x0008_¸tÇ(Æ)_x0000___x0000_¹Ò_x0010_Ó
+_x0000__x0000_7820601928_x0004__x0000__x0001__x000C_Õ_x0008_¸tÇ(Æ_x0003__x0000__x0001_\ÍÑ¼ÅÆ_x0008__x0000__x0001_0¼Ü´ü»4ÑtÐý·´Æ_x0001_Æ_x0008__x0000__x0000_20210305_x000D__x0000__x0000_010-4343-5610_x0005__x0000__x0000_31234_x0017__x0000__x0001_©Í¨° _x0000_ÌHÅÜÂ _x0000_Ù³¨°l­ _x0000_©ºÌMÇ _x0000_1Á¨°\¸ _x0000_3_x0000_9_x0000_-_x0000_1_x0000__x0010__x0000__x0000_cbw007@naver.com_x000E__x0000__x0000_37690004685637_x0006__x0000__x0000_D00626_x000B__x0000__x0001__x0018_ÂÐÆ¥ÇHÅà¬ñ´YÕP­__x0000_¹Ò_x0010_Ó
+_x0000__x0000_1358302549_x0006__x0000__x0001_¥ÇHÅà¬ñ´YÕP­_x0003__x0000__x0001_ ÇtÕ·_x0004__x0000__x0001_½Ù³°ÀÅÅ_x0008__x0000__x0000_20210324_x000C__x0000__x0000_031-250-2901_x0007__x0000__x0001_½¬0®Ä³ _x0000__x0018_ÂÐÆÜÂ_x0005__x0000__x0000_16316_x0015__x0000__x0001_½¬0® _x0000__x0018_ÂÐÆÜÂ _x0000_¥ÇHÅl­ _x0000__x0000_³ÉÓ\¸5_x0000_2_x0000_¼8® _x0000_1_x0000_2_x0000__x0013__x0000__x0000_jangan5955@korea.kr_x000E__x0000__x0000_37690004686237_x0006__x0000__x0000_D00628_x0007__x0000__x0001_Æ%±¤Â _x0000__x0018_ÂÐÆ_x0010_È
+_x0000__x0000_4401101673_x0003__x0000__x0001__x0015_¼°_x0004_Ö_x000B__x0000__x0001_¤ÂìÓ Î©Æ _x0000_XÇX¹,_x0000_ _x0000_©ÆÔ_x0008__x0000__x0000_20210407_x000C__x0000__x0000_031-216-4009_x0005__x0000__x0000_16540_x0010__x0000__x0001_½¬0® _x0000__x0018_ÂÐÆÜÂ _x0000__x0001_ÆµÑl­ _x0000_ä¹ÐÆ\¸ _x0000_3_x0000__x000D__x0000__x0000_010-2888-3600_x0011__x0000__x0000_yonexsw@naver.com_x000E__x0000__x0000_37690004687937_x0006__x0000__x0000_D00631_x000C__x0000__x0001__x0011_É·l­0¼Ü´ü»4Ñ_x0011_ÖÖ__x0000_¹Ò_x0010_Ó_x0008__x0000__x0000_20210510_x0006__x0000__x0000_D00632_x0008__x0000__x0001_©ÆÔ¬ÀÅÅ½ _x0000_A_x0000_S_x0000__x0003__x0000__x0001_@® ÌÅÆ_x000B__x0000__x0000_02-335-8077_x0008__x0000__x0000_20210601_x0006__x0000__x0000_D00638_x000D__x0000__x0001_p¬1Á¤ÂìÓ Î(_x0000_HÅÙ³)_x0000_(_x0000_T_x0000_S_x0000_)_x0000__x0008__x0000__x0000_20210622_x000F__x0000__x0001_½¬½ _x0000_HÅÙ³ÜÂ _x0000_½¬½_x0000_³\¸ _x0000_4_x0000_1_x0000_8_x0000__x0018__x0000__x0001_(_x0000_%ÆÙ³,_x0000_ _x0000_LÑÈ¹_x0004_Õ|·Ç)_x0000_Æ%±¤Â _x0000_p¬1Á¤ÂìÓ Î(_x0000_HÅÙ³)_x0000__x0012__x0000__x0000_klcjjh@lycos.co.kr_x000E__x0000__x0000_37690004688537_x0006__x0000__x0000_D00640_x0005__x0000__x0001__x0014_¼x¹¤ÂìÓ Î
+_x0000__x0000_1313599978_x0006__x0000__x0001__x0014_¼x¹ _x0000_¤ÂìÓ Î_x0003__x0000__x0001_tÇ¬Ç_x0001_Æ_x0007__x0000__x0001_Áä¹ÅÅ,_x0000_Ä³ä¹ÅÅ_x0008__x0000__x0000_20210715_x000C__x0000__x0000_032-466-1365_x0005__x0000__x0000_21543_x000E__x0000__x0001_xÇÌ _x0000_¨°Ù³l­ _x0000_1¼¼\¸ _x0000_1_x0000_3_x0000_9_x0000_
+_x0000__x0001_Æ%±¤Â _x0000__x0014_¼x¹ _x0000_¤ÂìÓ Î_x000D__x0000__x0000_010-8872-9764_x0017__x0000__x0000_hangang6528@hanmail.net_x000E__x0000__x0000_37690004689137_x0006__x0000__x0000_D00641_x0004__x0000__x0001_$±¼·Ü´
+_x0000__x0000_1292781688_x0003__x0000__x0001_@®e×-Á_x0013__x0000__x0001__x0004_ÈÇÁÀp¬·ÅÅ,_x0000_ _x0000_¤ÂìÓ Î©ÆÔ,_x0000_ _x0000_ìÕ¤Â©ÆÔ_x0008__x0000__x0000_20210730_x000C__x0000__x0000_031-742-4404_x0005__x0000__x0000_13134_x0013__x0000__x0001_½¬0® _x0000_1Á¨°ÜÂ _x0000__x0018_Â_x0015_Èl­ _x0000_°À1Á_x0000_³\¸ _x0000_5_x0000_8_x0000_5_x0000__x000D__x0000__x0000_010-9034-0945_x0014__x0000__x0000_samulnori4@naver.com_x000E__x0000__x0000_37690004690137_x0006__x0000__x0000_D00643_x000E__x0000__x0001_Æ%±¤Â _x0000_ÐÆüÈ_x0010_È(_x0000_J_x0000_S_x0000_¤ÂìÓ Î)_x0000_
+_x0000__x0000_3181501656_x0003__x0000__x0001_@®¬Ç1Á_x0012__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000__x0004_ÈÇÁÀp¬·(_x0000_¤ÂìÓ Î©ÆÔ)_x0000__x0008__x0000__x0000_20210810_x000C__x0000__x0000_033-764-1409_x0007__x0000__x0001__x0015_¬ÐÆÄ³ _x0000_ÐÆüÈÜÂ_x0005__x0000__x0000_26431_x000F__x0000__x0001__x0015_¬ÐÆ _x0000_ÐÆüÈÜÂ _x0000_ÐÆ|Ç\¸ _x0000_5_x0000_5_x0000_-_x0000_1_x0000__x0006__x0000__x0001_1_x0000_5Î(_x0000_ÐÆÙ³)_x0000__x000D__x0000__x0000_010-9799-0020_x0015__x0000__x0000_yonex_wonju@naver.com_x000E__x0000__x0000_37690004691837_x0006__x0000__x0000_D00649
+_x0000__x0001_(_x0000_üÈ)_x0000_È¹_x000C_ÕTÏ|Ó_x0008_¸tÇXÁ
+_x0000__x0000_1058813322_x0003__x0000__x0001__x0015_¼_x001C_Ö$Ç_x0011__x0000__x0001__x001C_ÈpÈ,_x0000_ _x0000_Ä³Áä¹,_x0000_ _x0000_Ä³ä¹ _x0000__x000F_¼ _x0000_Áä¹ÅÅ	_x0000__x0001_,Á Ç_x0004_Õ°¹¸Ò,_x0000_ _x0000_XÇX¹_x0008__x0000__x0000_20210901_x000D__x0000__x0000_010-4811-6484	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x0008_®Ìl­_x0005__x0000__x0000_08589_x0014__x0000__x0001__x001C_Á¸Æ _x0000__x0008_®Ìl­ _x0000__x0000_¬°À_x0014_µÀÉ8Ñ1_x0000_\¸ _x0000_7_x0000_5_x0000_-_x0000_2_x0000_4_x0000__x000B__x0000__x0001_1_x0000_0_x0000_5Î,_x0000_1_x0000_1_x0000_5Î,_x0000_1_x0000_2_x0000_5Î_x0013__x0000__x0000_account@marpple.com_x0006__x0000__x0000_D00654_x0007__x0000__x0001__x0004_Ö¥Ç_x0010_Óä¹__x0000_©ºìÓ_x0008__x0000__x0000_20211103_x0006__x0000__x0000_D00657_x0008__x0000__x0001_(_x0000_üÈ)_x0000_ìÎÐÌ×´Å\¸
+_x0000__x0000_1448135400
+_x0000__x0001_üÈÝÂÖ¬À _x0000_ìÎÐÌ×´Å\¸_x0003__x0000__x0001_Å_x0000_ÉÜ­_x0016__x0000__x0001__x0015_Èô¼_x001C_ÁD¾¤Â,_x0000_ _x0000_Ä³ä¹ _x0000__x000F_¼ _x0000_Áä¹ÅÅ,_x0000_ _x0000__x0015_Èô¼µÑàÂÅÅ!_x0000__x0001__x0004_ÈÇÁÀp¬·ÅÅ,_x0000_ _x0000__x0015_Èô¼Ì¬¹ÜÂ¤Â\Ñ,_x0000_ _x0000__x0015_Èô¼_x001C_ÁD¾¤ÂÅÅ,_x0000_ _x0000_(Æ|·xÇ_x0015_Èô¼_x001C_Èõ¬ÅÅ_x000D__x0000__x0000_010-4848-6263_x0005__x0000__x0000_13487_x0016__x0000__x0001_½¬0® _x0000_1Á¨°ÜÂ _x0000_½ù²l­ _x0000__x0010_ÓP­\¸2_x0000_2_x0000_8_x0000_¼8® _x0000_1_x0000_5_x0000__x000C__x0000__x0001_3_x0000_Ù³ _x0000_1_x0000_0_x0000_5Î _x0000_1_x0000_0_x0000_0_x0000_1_x0000_8Ö_x0017__x0000__x0000_contact@culturehero.net_x0011__x0000__x0000_YONEX-2021-009852_x0008__x0000__x0000_20211119_x000E__x0000__x0000_37690004694737_x0006__x0000__x0000_D00658_x0007__x0000__x0001_Æ%±¤Â _x0000__x0015_¬¨°_x0010_È
+_x0000__x0000_2440202373_x0003__x0000__x0001_tÇ@ÇüÈ_x0018__x0000__x0001_´ÆÙ³ _x0000__x000F_¼ _x0000_½¬0®©ÆÔ _x0000_Áä¹ÅÅ,_x0000_ _x0000__x0004_ÈÇÁÀp¬· _x0000_Áä¹ÅÅ_x0008__x0000__x0000_20211201_x000C__x0000__x0000_02-6498-9300_x0005__x0000__x0000_06777_x000D__x0000__x0001__x001C_Á¸Æ _x0000__x001C_Á_x0008_Íl­ _x0000_¸Å¨°8® _x0000_4_x0000_5_x0000__x000D__x0000__x0000_010-2416-3327_x0016__x0000__x0000_kidsrun005@hanmail.net_x000E__x0000__x0000_37690004695337_x0006__x0000__x0000_D00664	_x0000__x0001_o¸p³_x000C_¸ÈÐ_x0018_»ø»__x0000_¹Ò_x0010_Ó
+_x0000__x0000_2148779183_x0008__x0000__x0001_o¸p³_x000C_¸ÈÐ _x0000_(_x0000_üÈ)_x0000__x0003__x0000__x0001_@®_x0004_Ö_x0018_Â_x0007__x0000__x0001__x001C_ÁD¾¤Â,_x0000_ _x0000_Áä¹_x0018__x0000__x0001__x0015_Èô¼µÑàÂ0®0®_x000F_¼¥ÇD¾_x000C_¸ÈÐ,_x0000_ _x0000__x0010_Óä¹,_x0000_ _x0000_ ÇÀÉô¼_x0018_Â_x001C_ÁD¾¤Â_x0008__x0000__x0000_20220128_x000D__x0000__x0000_010-3085-5465_x0005__x0000__x0000_14042_x0011__x0000__x0001_½¬0® _x0000_HÅÅÜÂ _x0000_Ù³HÅl­ _x0000__x0004_È_x000C_Ó\¸ _x0000_8_x0000_8_x0000__x0002__x0000__x0001_8_x0000_5Î_x0016__x0000__x0000_ahnhyeokbeom@lotte.net_x0011__x0000__x0000_YONEX-2022-000914_x000E__x0000__x0000_37690004697637_x0017__x0000__x0001_ô²ô¼_x0008_®aÅ _x0000_ø»$Á_x0015_È,_x0000_ _x0000_uÇÔÆ _x0000_1_x0000_0_x0000_0_x0000_%_x0000_ _x0000__x0018_Â_x0008_® _x0000_ÄÉÕ_x0006__x0000__x0000_D00670_x000C__x0000__x0001_(_x0000_üÈ)_x0000_DÅüÈ_x0008_¸ìÓ Î(_x0000_T_x0000_S_x0000_)_x0000__x0008__x0000__x0000_20220317_x0015__x0000__x0000_luckright@hanmail.net_x000E__x0000__x0000_37690004698237_x0006__x0000__x0000_D00672_x000F__x0000__x0001_2_x0000_0_x0000_2_x0000_2_x0000_ _x0000_TÏ¬¹DÅ$Æ_x0008_Õ&amp;_x0000_È¹¤Â0ÑÉ_x0008__x0000__x0000_20220322_x0006__x0000__x0000_D00676_x0007__x0000__x0001__x0004_Ö¥Ç_x0010_Óä¹__x0000__x0000_³_x0004_È_x0008__x0000__x0000_20220509_x0008__x0000__x0001__x0000_³_x0004_È_x0011_­íÅÜÂ _x0000__x0011_Él­_x0006__x0000__x0000_D00677_x000C__x0000__x0001_1Á½l­0¼Ü´ü»4Ñ_x0011_ÖÖ__x0000_¹Ò_x0010_Ó_x0008__x0000__x0000_20220518_x0006__x0000__x0000_D00679_x0007__x0000__x0001__x0004_Ö¥Ç_x0010_Óä¹__x0000_¸Æ°À_x0008__x0000__x0000_20220524_x0006__x0000__x0000_D00680_x0007__x0000__x0001__x0004_Ö¥Ç_x0010_Óä¹__x0000__x001C_Á¸Æ_x0008__x0000__x0000_20220622_x0011__x0000__x0000_YONEX-2022-005692_x0006__x0000__x0000_D00685
+_x0000__x0001_üÈÝÂÖ¬À _x0000_(Æ¬¹¤ÂìÓ Î
+_x0000__x0000_7448101466_x0008__x0000__x0001_üÈÝÂÖ¬À _x0000_ôÎ_x0014_¼xÇ_x0007__x0000__x0001_@®ÁÀ¼,_x0000_8»_x001C_Á_x0004_Ö_x0008__x0000__x0001__x001C_ÁD¾¤ÂÅÅ,_x0000__x001C_ÈpÈÅÅ	_x0000__x0001_¤ÂìÓ ÎXÇX¹,_x0000_0®P±Ô_x0008__x0000__x0000_20220823</v>
           </cell>
           <cell r="C37" t="str">
-            <v>주식회사 에스엠</v>
+            <v>052-251-4982</v>
           </cell>
           <cell r="D37" t="str">
             <v>사용가능</v>
@@ -4507,13 +5233,13 @@
             <v>일반사업자</v>
           </cell>
           <cell r="F37" t="str">
-            <v>1318674023</v>
+            <v>울산광역시 북구</v>
           </cell>
           <cell r="G37" t="str">
-            <v>주식회사 에스엠</v>
+            <v>052-251-4982</v>
           </cell>
           <cell r="H37" t="str">
-            <v>손현호</v>
+            <v>44215</v>
           </cell>
           <cell r="I37" t="str">
             <v>도소매</v>
@@ -4522,34 +5248,187 @@
             <v>스포츠용품</v>
           </cell>
           <cell r="K37" t="str">
-            <v>20120330</v>
+            <v>울산 북구 약수4길 20</v>
           </cell>
           <cell r="L37" t="str">
             <v/>
           </cell>
           <cell r="M37" t="str">
-            <v>051-202-3541</v>
-          </cell>
-          <cell r="N37" t="str">
-            <v>0512013541</v>
+            <v>온리스포츠 배드민턴센터</v>
+          </cell>
+          <cell r="N37" t="e">
+            <v>#N/A</v>
           </cell>
           <cell r="O37" t="str">
-            <v>부산광역시 강서구</v>
+            <v>780778_x0005__x0000__x0000_04563_x001E__x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x0011_Él­ _x0000_­ÌÄ¬Ì\¸ _x0000_2_x0000_4_x0000_6_x0000_ _x0000_ _x0000_(_x0000_)¼°ÀÙ³,_x0000_ _x0000_ÉÓTÖÜÂ¥Ç)_x0000__x0016__x0000__x0001_1_x0000_,_x0000_2_x0000_,_x0000_3_x0000_5Î _x0000_ä²-_x0000_1_x0000_0_x0000_2_x0000_(_x0000_)¼°ÀÙ³,_x0000_ÉÓTÖÜÂ¥Ç)_x0000__x000D__x0000__x0000_010-3284-7383_x0019__x0000__x0000_victorysports@hanmail.net_x000E__x0000__x0000_37690004488937_x0006__x0000__x0000_D00101_x0005__x0000__x0001_DÅ°À¤ÂìÓ Î
+_x0000__x0000_3122872982_x0003__x0000__x0001_\Í+È¼¹_x000C__x0000__x0001_Ä³ä¹_x000F_¼ÁÀÔ_x0011_É_x001C_¬ÅÅ,_x0000_Áä¹ÅÅ_x0008__x0000__x0000_20110701_x000C__x0000__x0000_041-532-8381
+_x0000__x0000_0415328382_x0008__x0000__x0001_©Í­Ì¨°Ä³ _x0000_DÅ°ÀÜÂ_x0006__x0000__x0000_336050_x0010__x0000__x0001_©Í­Ì¨°Ä³ _x0000_DÅ°ÀÜÂ _x0000_ÜÂü»\¸ _x0000_2_x0000_5_x0000_1_x0000__x000D__x0000__x0000_010-4946-8385_x0013__x0000__x0000_judocjl@hanmail.net_x000E__x0000__x0000_37690004490537_x0006__x0000__x0000_D00109_x0008__x0000__x0001__x0001_Æ¤ÂìÓ Î(_x0000_¨°ÐÆ)_x0000_
+_x0000__x0000_1095289131_x0003__x0000__x0001_tÇ_x0015_ÈÌ_x0008__x0000__x0000_20071119_x000C__x0000__x0000_063-632-4154
+_x0000__x0000_0636324156_x0005__x0000__x0000_55703_x0015__x0000__x0001__x0004_È|·½Ä³ _x0000_¨°ÐÆÜÂ _x0000_¬Àä¹tº _x0000__x0000_³¬À\¸ _x0000_1_x0000_2_x0000_8_x0000_3_x0000__x0004__x0000__x0001__x0001_Æ¤ÂìÓ Î_x000D__x0000__x0000_010-4594-0634_x0013__x0000__x0000_jclee8734@naver.com_x000E__x0000__x0000_37690004497037_x0006__x0000__x0000_D00110_x0007__x0000__x0001_Æ%±¤Â _x0000_TÖ_x001C_Â_x0010_È
+_x0000__x0000_4080577085_x0003__x0000__x0001__x0004_È+º_x0019_Â_x0008__x0000__x0000_20071102_x000C__x0000__x0000_061-375-6647_x0008__x0000__x0001__x0004_È|·¨°Ä³ _x0000_TÖ_x001C_Âp­_x0006__x0000__x0000_519809_x0014__x0000__x0001__x0004_È|·¨°Ä³ _x0000_TÖ_x001C_Âp­ _x0000__x0011_­U³\¸ _x0000_1_x0000_4_x0000_0_x0000_ _x0000_ _x0000_1_x0000_5Î_x000D__x0000__x0000_010-6632-5893_x0012__x0000__x0000_ms-jon@hanmeil.net_x000E__x0000__x0000_37690004498637_x0006__x0000__x0000_D00111_x000C__x0000__x0001_,Æ¼¹=Õ+ÈiÕ¤ÂìÓ Î(_x0000_©ºìÓ)_x0000_
+_x0000__x0000_4111469486_x0003__x0000__x0001_@®=Ì©Æ_x000C__x0000__x0001_´ÆÙ³©ÆÔ,_x0000_ñ´°Àl­,_x0000_0®P±Ô_x0008__x0000__x0000_20070320_x000C__x0000__x0000_061-242-1032
+_x0000__x0000_0612443032_x0008__x0000__x0001__x0004_È|·¨°Ä³ _x0000_©ºìÓÜÂ_x0005__x0000__x0000_58726_x0010__x0000__x0001__x0004_È¨° _x0000_©ºìÓÜÂ _x0000_(Ì¼_x001D_Á8® _x0000_4_x0000_1_x0000_-_x0000_1_x0000__x0002__x0000__x0001_1_x0000_5Î_x000D__x0000__x0000_010-9243-4285_x0010__x0000__x0000_eyebono@daum.net_x000E__x0000__x0000_37690004499237_x0006__x0000__x0000_D00116_x000F__x0000__x0001_Æ%±¤ÂÈ¹°À_x0000_³¬¹_x0010_È(_x0000_ü»4Ñ¤ÂìÓ Î)_x0000_
+_x0000__x0000_6080288027_x0003__x0000__x0001_ Ç_x0001_Æ_x0019_Â_x0008__x0000__x0001_¤ÂìÓ Î©ÆÔ_x000F_¼XÇX¹_x000C__x0000__x0000_055-222-5431
+_x0000__x0000_0552225432_x0008__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_=ÌÐÆÜÂ_x0006__x0000__x0000_631852_x0018__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_=ÌÐÆÜÂ _x0000_È¹°ÀiÕìÓl­ _x0000_©ÆÈ¹\¸ _x0000_7_x0000_6_x0000_ _x0000_üÈÝÐ_x000D__x0000__x0000_010-3707-6245_x0016__x0000__x0000_dudtjs6245@hanmail.net_x000E__x0000__x0000_37690004504337_x0006__x0000__x0000_D00120_x0006__x0000__x0001_Æ%±¤Â­ÌüÈ_x0010_È
+_x0000__x0000_3170385854_x0003__x0000__x0001_\Í°Æ1Á_x000B__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_XÇX¹,_x0000__x0018_Ât¬_x0008__x0000__x0000_20110729_x000C__x0000__x0000_043-222-3040
+_x0000__x0000_0432245050_x0008__x0000__x0001_©Í­Ì½Ä³ _x0000_­ÌüÈÜÂ_x0006__x0000__x0000_361842_x0012__x0000__x0001_©Í½ _x0000_­ÌüÈÜÂ _x0000_ÁÀù²l­ _x0000_8Öø»\¸ _x0000_2_x0000_0_x0000_6_x0000__x0005__x0000__x0001_1_x0000_5Î _x0000_È!Î_x000D__x0000__x0000_010-5468-3319_x0015__x0000__x0000_wsung3525@hanmail.net_x0008__x0000__x0000_20080429_x000E__x0000__x0000_37690004507237_x0006__x0000__x0000_D00121_x000D__x0000__x0001_Æ%±¤ÂìÓmÕ_x0010_È(_x0000_XÕtÇlÐ¬¹´Å)_x0000_
+_x0000__x0000_5061736246_x0003__x0000__x0001__x0015_È@Ç_x0001_Æ_x0008__x0000__x0000_20090227_x000C__x0000__x0000_054-283-5234
+_x0000__x0000_0542835231_x0008__x0000__x0001_½¬ÁÀ½Ä³ _x0000_ìÓmÕÜÂ_x0006__x0000__x0000_790822_x0012__x0000__x0001_½¬½ _x0000_ìÓmÕÜÂ _x0000_¨°l­ _x0000__x0000_³Ä³Ù³ _x0000_8_x0000_6_x0000_-_x0000_2_x0000__x000D__x0000__x0000_010-4133-7770_x0014__x0000__x0000_minton1125@naver.com_x0008__x0000__x0000_20081105_x000E__x0000__x0000_37690004508937_x0006__x0000__x0000_D00122_x0005__x0000__x0001_°Æ¬¹¤ÂìÓ Î
+_x0000__x0000_4172105493_x0003__x0000__x0001__x0015_¼_x0018_ÂÄÉ_x0008__x0000__x0000_20180101_x000C__x0000__x0000_051-632-2681
+_x0000__x0000_0516322681_x0008__x0000__x0001_½°À_x0011_­íÅÜÂ _x0000_¨°l­_x0006__x0000__x0000_608827_x0011__x0000__x0001_½°À_x0011_­íÅÜÂ _x0000_¨°l­ _x0000_Ç ÇÉÓTÖ\¸ _x0000_4_x0000_9_x0000__x000D__x0000__x0000_010-2594-2682_x0015__x0000__x0000_moxie2000@hanmail.net_x000E__x0000__x0000_37690004509537_x0006__x0000__x0000_D00123_x0005__x0000__x0001_°Æ1Á¤ÂìÓ Î
+_x0000__x0000_2077003708_x0003__x0000__x0001_@®DÆÝÂ_x0008__x0000__x0000_20071009_x000B__x0000__x0000_02-465-1297	_x0000__x0000_024651197	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x0011_­ÄÉl­_x0006__x0000__x0000_143961_x0010__x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x0011_­ÄÉl­ _x0000_l­XÇ\¸ _x0000_6_x0000_6_x0000__x0014__x0000__x0001_1_x0000_5Î _x0000_(_x0000_l­XÇÙ³ _x0000_2_x0000_2_x0000_7_x0000_-_x0000_6_x0000_)_x0000_ _x0000_°Æ1Á¤ÂìÓ Î_x000D__x0000__x0000_010-3418-1230_x000F__x0000__x0000_ws418@naver.com_x000E__x0000__x0000_37690004510537_x0006__x0000__x0000_D00126_x0005__x0000__x0001_ÐÆÙ³´Ì!Ç¬À
+_x0000__x0000_3060363748_x0003__x0000__x0001_ü»Ñ¼ÁÉ_x0004__x0000__x0001_´ÆÙ³0®l­_x0008__x0000__x0000_20050705_x000C__x0000__x0000_042-531-4004
+_x0000__x0000_0425328899_x0008__x0000__x0001__x0000_³_x0004_È_x0011_­íÅÜÂ _x0000_Ù³l­_x0005__x0000__x0000_34630_x000D__x0000__x0001__x0000_³_x0004_È _x0000_Ù³l­ _x0000__x0000_³_x0004_È\¸ _x0000_7_x0000_6_x0000_5_x0000__x000D__x0000__x0000_010-5453-9536_x0012__x0000__x0000_wonspo@hanmail.net_x0008__x0000__x0000_20080214_x000E__x0000__x0000_37690004511137_x0006__x0000__x0000_D00127_x0008__x0000__x0001_ÐÆ¤ÂìÓ Î(_x0000__x001C_ÈüÈ)_x0000_
+_x0000__x0000_6160962051_x0003__x0000__x0001_@®ø»½¬_x000C__x0000__x0000_064-752-4422
+_x0000__x0000_0647232992_x000C__x0000__x0001__x001C_ÈüÈ¹ÒÄ¼ÇXÎÄ³ _x0000__x001C_ÁÀ­ìÓÜÂ_x0006__x0000__x0000_690161_x0013__x0000__x0001__x001C_ÈüÈ¹ÒÄ¼ÇXÎÄ³ _x0000__x001C_ÈüÈÜÂ _x0000_$Æ|·\¸ _x0000_1_x0000_3_x0000_4_x0000__x000D__x0000__x0000_010-4416-4412_x0015__x0000__x0000_crony0104@hanmail.net_x000E__x0000__x0000_37690004512837_x0006__x0000__x0000_D00132_x0005__x0000__x0001__x0004_ÈüÈÆ%±¤Â
+_x0000__x0000_4020887887_x0003__x0000__x0001_tÇ_x001C_Â+È_x000C__x0000__x0000_063-274-9337
+_x0000__x0000_0632789337_x0008__x0000__x0001__x0004_È|·½Ä³ _x0000__x0004_ÈüÈÜÂ_x0006__x0000__x0000_560080_x0013__x0000__x0001__x0004_È|·½Ä³ _x0000__x0004_ÈüÈÜÂ _x0000_DÆ°Àl­ _x0000_õ¬½\¸ _x0000_2_x0000_0_x0000__x000D__x0000__x0000_010-9224-8391_x0010__x0000__x0000_jyonex@naver.com_x000E__x0000__x0000_37690004516337_x0006__x0000__x0000_D00136_x0005__x0000__x0001__x001C_È|Ç¤ÂìÓ Î
+_x0000__x0000_4040533542_x000B__x0000__x0001__x001C_È|Ç_x0008_¸_x0000_È¤ÂìÓ Î(_x0000__x0015_ÈMÇ)_x0000__x0003__x0000__x0001_@®_x0011_­õ¼	_x0000__x0001_´ÆÙ³0®l­_x000F_¼´ÆÙ³õ¼xÆ_x000C__x0000__x0000_063-535-9146
+_x0000__x0000_0635332093_x0008__x0000__x0001__x0004_È|·½Ä³ _x0000__x0015_ÈMÇÜÂ_x0006__x0000__x0000_580804_x000F__x0000__x0001__x0004_È|·½Ä³ _x0000__x0015_ÈMÇÜÂ _x0000__x0011_ÉYÅ\¸ _x0000_8_x0000_3_x0000__x000D__x0000__x0000_010-9579-7800_x0016__x0000__x0000_sports9146@hanmaIl.net_x000E__x0000__x0000_37690004520237_x0006__x0000__x0000_D00137_x000B__x0000__x0001_üÈÝÂÖ¬À _x0000_0¼Ü´ü»4ÑÈ¹¸Ò
+_x0000__x0000_1108193203_x0003__x0000__x0001__x0015_ÈtÇ@±_x000B__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000__x0004_ÈÇÁÀp¬·_x0008__x0000__x0000_20130723_x000C__x0000__x0000_031-964-3530	_x0000__x0000_023829555_x0007__x0000__x0001_½¬0®Ä³ _x0000_à¬ÅÜÂ_x0005__x0000__x0000_10564_x0011__x0000__x0001_½¬0® _x0000_à¬ÅÜÂ _x0000_U³Ål­ _x0000_¼À¡Á\¸ _x0000_1_x0000_2_x0000__x0007__x0000__x0001_4_x0000_5Î _x0000_4_x0000_1_x0000_8_x0000_8Ö_x000D__x0000__x0000_010-7152-7538_x0014__x0000__x0000_mintonmart@naver.com_x000E__x0000__x0000_37690004521937_x0006__x0000__x0000_D00138	_x0000__x0001_üÈÝÂÖ¬ÀÙ³°Æ¤ÂìÓ Î
+_x0000__x0000_1108180426_x0003__x0000__x0001_¡Á_x0015_È|Ç_x000B__x0000__x0000_02-382-3598	_x0000__x0000_023553586	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_@ÇÉÓl­_x0006__x0000__x0000_122903_x0018__x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_@ÇÉÓl­ _x0000_ðÅ_x001C_Á\¸ _x0000_2_x0000_9_x0000_-_x0000_1_x0000_ _x0000_Ù³°Æ¤ÂìÓ Î_x000D__x0000__x0000_010-2018-3598_x0012__x0000__x0000_dvip1233@naver.com_x000B__x0000__x0000_01074353598
+_x0000__x0001__x0018_Â_x0008_® _x0000_½qÈ&lt;Ç\¸ _x0000_µÑ_x001C_È_x000E__x0000__x0000_37690004522537_x0006__x0000__x0000_D00141	_x0000__x0001__x0011_ÉYÅ¤ÂìÓ Î(_x0000_½¬üÈ)_x0000_
+_x0000__x0000_3226600323_x0003__x0000__x0001_iÖ_x0001_ÆäÂ_x0008__x0000__x0000_20081210_x000C__x0000__x0000_054-741-5177_x0008__x0000__x0001_½¬ÁÀ½Ä³ _x0000_½¬üÈÜÂ_x0006__x0000__x0000_780943_x0012__x0000__x0001_½¬ÁÀ½Ä³ _x0000_½¬üÈÜÂ _x0000__x0008_®1Á\¸ _x0000_2_x0000_9_x0000_4_x0000_-_x0000_1_x0000__x000D__x0000__x0000_010-7579-5177_x0014__x0000__x0000_jasp6304@hanmail.net_x0008__x0000__x0000_20081211_x000E__x0000__x0000_37690004525437_x0006__x0000__x0000_D00145_x0005__x0000__x0001_­Ìá¸¤ÂìÓ Î
+_x0000__x0000_6150796307_x0003__x0000__x0001_pÈø»_x0019_Â_x0008__x0000__x0000_20101004_x000C__x0000__x0000_055-312-9559
+_x0000__x0000_0553129560_x0008__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_@®tÕÜÂ_x0006__x0000__x0000_621833_x0012__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_@®tÕÜÂ _x0000_¥Ç Ç\¸ _x0000_2_x0000_9_x0000_7_x0000_-_x0000_5_x0000__x000D__x0000__x0000_010-9513-9559_x0016__x0000__x0000_jms3129559@hanmail.net_x0008__x0000__x0000_20101019_x000E__x0000__x0000_37690004530037_x0006__x0000__x0000_D00148_x0007__x0000__x0001__x0000_ÏtÇdÅD¾¤ÂìÓ Î
+_x0000__x0000_1232481068_x0003__x0000__x0001__x0015_¼+ºÇ_x000C__x0000__x0000_031-457-8706
+_x0000__x0000_0314578707_x0007__x0000__x0001_½¬0®Ä³ _x0000_HÅÅÜÂ_x0006__x0000__x0000_431837_x0012__x0000__x0001_½¬0®Ä³ _x0000_HÅÅÜÂ _x0000_Ù³HÅl­ _x0000_À­xÇ\¸ _x0000_8_x0000_9_x0000__x000D__x0000__x0000_010-7338-7375_x0016__x0000__x0000_jamjali200@hanmail.net_x000E__x0000__x0000_37690004532237_x0006__x0000__x0000_D00149	_x0000__x0001_TÏ¬¹DÅ$Æ_x0008_Õ(_x0000_@®Ì)_x0000_
+_x0000__x0000_5100147324_x0003__x0000__x0001__x0015_¼ Á_x0001_Æ_x0008__x0000__x0000_20070423_x000C__x0000__x0000_054-430-7007
+_x0000__x0000_0544307007_x0008__x0000__x0001_½¬ÁÀ½Ä³ _x0000_@®ÌÜÂ_x0005__x0000__x0000_39626_x000E__x0000__x0001_½¬½ _x0000_@®ÌÜÂ _x0000_¡Á$Á\¸ _x0000_1_x0000_6_x0000_4_x0000__x000D__x0000__x0000_010-4115-6306_x0013__x0000__x0000_jj10654@hanmail.net_x000E__x0000__x0000_37690004533937_x0006__x0000__x0000_D00150_x0005__x0000__x0001__x0014_Ól­¤ÂìÓ Î
+_x0000__x0000_5020153204_x0003__x0000__x0001_àÂÁÀÜ­_x0008__x0000__x0000_20080331_x000C__x0000__x0000_053-957-8989
+_x0000__x0000_0539432345_x0008__x0000__x0001__x0000_³l­_x0011_­íÅÜÂ _x0000_Ù³l­_x0005__x0000__x0000_41193_x000F__x0000__x0001__x0000_³l­ _x0000_Ù³l­ _x0000_DÅÅ\¸1_x0000_1_x0000_8® _x0000_8_x0000_1_x0000__x0008__x0000__x0001_1_x0000_5Î _x0000__x0014_Ól­¤ÂìÓ Î_x000D__x0000__x0000_010-8854-8989_x0012__x0000__x0000_89sports@naver.com_x000E__x0000__x0000_37690004534537_x0006__x0000__x0000_D00159_x0005__x0000__x0001__x001C_Ö1Á¤ÂìÓ Î
+_x0000__x0000_1300531089_x0003__x0000__x0001_tÇXÇ Á_x000D__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000__x0000_¬_x0004_È_x001C_ÈÔ,_x0000_¡ÇTÖ_x0008__x0000__x0000_20070529_x000C__x0000__x0000_032-654-2133
+_x0000__x0000_0326542132_x0007__x0000__x0001_½¬0®Ä³ _x0000_½ÌÜÂ_x0006__x0000__x0000_422819 _x0000__x0001_½¬0®Ä³ _x0000_½ÌÜÂ _x0000_Á¬Àl­ _x0000_½¬xÇ\¸1_x0000_2_x0000_0_x0000_¼8® _x0000_2_x0000_8_x0000_ _x0000_ _x0000_1_x0000_5Î_x0010_ÈìÓ _x0000_1_x0000_xÎ_x000D__x0000__x0000_010-7578-7740_x0015__x0000__x0000_hs7167741@hanmail.net_x000E__x0000__x0000_37690004541337_x0006__x0000__x0000_D00160_x0005__x0000__x0001_8ÖÙ³¤ÂìÓ Î
+_x0000__x0000_1243919047_x0003__x0000__x0001_@®8ÖÙ³_x0008__x0000__x0000_20100113_x000C__x0000__x0000_031-375-0331
+_x0000__x0000_0313750331_x0007__x0000__x0001_½¬0®Ä³ _x0000_$Æ°ÀÜÂ_x0006__x0000__x0000_447802_x001A__x0000__x0001_½¬0®Ä³ _x0000_$Æ°ÀÜÂ _x0000_1Á8Ö_x0000_³\¸ _x0000_2_x0000_5_x0000_ _x0000_´Æ°ÀL¾)µ _x0000_ _x0000_1_x0000_5Î _x0000_4_x0000__x000D__x0000__x0000_010-5295-8278_x0013__x0000__x0000_khd9982@hanmail.net_x000E__x0000__x0000_37690004542037_x0006__x0000__x0000_D00161_x0005__x0000__x0001_MÖ1ÁÆ%±¤Â
+_x0000__x0000_3100640518_x0003__x0000__x0001_@®_x0004_Ö_x0015_È_x0008__x0000__x0000_20090616_x000C__x0000__x0000_041-634-7327_x0008__x0000__x0001_©Í­Ì¨°Ä³ _x0000_MÖ1Áp­_x0005__x0000__x0000_32263_x0012__x0000__x0001_©Í¨° _x0000_MÖ1Áp­ _x0000_MÖ½MÇ _x0000_©Í¨°_x0000_³\¸ _x0000_3_x0000_6_x0000__x0015__x0000__x0001__x001C_È _x0000_1_x0000_5Î _x0000__x001C_È _x0000_1_x0000_0_x0000_1_x0000_8Ö(_x0000_L¾dÅT³¤Â$Æ&lt;Õ¤ÂTÑ)_x0000__x000D__x0000__x0000_010-8626-9825_x0010__x0000__x0000_hji923@naver.com_x000E__x0000__x0000_37690004543637_x0006__x0000__x0000_D00166_x000C__x0000__x0001_(_x0000_üÈ)_x0000_ðÒ_x001C_ÈtÇ_x0014_µ¤Â¸Ò¬¹ð½XÁ
+_x0000__x0000_2118732516_x0003__x0000__x0001_¡ÁÁÀÐÆ_x0006__x0000__x0001_Ä³Áä¹ _x0000_Ä³ä¹_x0008__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_4»íÅ_x0008__x0000__x0000_20120911_x000B__x0000__x0000_02-511-5114	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x0015_¬¨°l­_x0006__x0000__x0000_135010_x000B__x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ_x0015_¬¨°l­|±_x0004_ÖÙ³_x000E__x0000__x0001__x0008_®@ÇL¾)µ _x0000_1_x0000_5Î _x0000_ ¼¤Â¸Ò¤Â Ñ´Å_x000D__x0000__x0000_010-8784-1651_x0015__x0000__x0000_bestextreme@naver.com_x0007__x0000__x0001_B_x0000_ñ´	®(_x0000_T_x0000_S_x0000_)_x0000__x0005__x0000__x0000_14049_x0003__x0000__x0001__x0015_¼_x0004_ÖÄÉ_x0008__x0000__x0000_20190917_x0006__x0000__x0000_D00167_x0008__x0000__x0001_üÈÝÂÖ¬À _x0000_ÐÆÐÅÇ
+_x0000__x0000_1268800066_x0003__x0000__x0001_@®DÕ¹Â_x0006__x0000__x0001_Ä³Áä¹ÅÅ _x0000_xÆ_x0007__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_xÆ_x000C__x0000__x0000_02-1644-1662	_x0000__x0001_½°À_x0011_­íÅÜÂ _x0000__x0018_Â_x0001_Æl­_x0006__x0000__x0000_613815_x0013__x0000__x0001_½°À_x0011_­íÅÜÂ _x0000__x0018_Â_x0001_Æl­ _x0000__x0011_­¨°\¸ _x0000_6_x0000_3_x0000_ _x0000_B_x0000_Ù³_x0004__x0000__x0001_4_x0000_5Î|Ç½_x000D__x0000__x0000_010-8882-4137_x0014__x0000__x0000_oneeight@hanmail.net_x0006__x0000__x0000_D00173_x0005__x0000__x0001__x0008_®_x0001_Æ¤ÂìÓ Î
+_x0000__x0000_1052087391_x0003__x0000__x0001_°ÆÀÉÐÆ_x0008__x0000__x0000_20140217_x000D__x0000__x0000_010-6208-8112_x0006__x0000__x0000_121889_x0013__x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_È¹ìÓl­ _x0000_Ù³P­\¸3_x0000_8® _x0000_1_x0000_2_x0000_5_x0000__x0013__x0000__x0000_yonex0901@naver.com_x0008__x0000__x0000_20150122_x000E__x0000__x0000_37690004557937_x0006__x0000__x0000_D00181_x0004__x0000__x0001__x0000_É¤ÂìÓ Î
+_x0000__x0000_1410240836_x0003__x0000__x0001__x0015_¼½¬·_x0008__x0000__x0000_20140825_x000C__x0000__x0000_031-945-2007_x0007__x0000__x0001_½¬0®Ä³ _x0000__x000C_ÓüÈÜÂ_x0006__x0000__x0000_413819$_x0000__x0001_½¬0®Ä³ _x0000__x000C_ÓüÈÜÂ _x0000_DÅ¬¹·\¸ _x0000_5_x0000_5_x0000_ _x0000_-_x0000_8_x0000_1_x0000_ _x0000_(_x0000__x0008_®_x000C_ÍÙ³,_x0000_ _x0000__x000C_ÓüÈ_x0008_®_x000C_ÍXÕ_x0018_ÂÌ¬¹¥Ç)_x0000__x000C__x0000__x0001__x000C_ÓüÈÜÂ _x0000_0¼Ü´ü»4Ñ_x0004_È©Æl­¥Ç_x000D__x0000__x0000_010-9129-1126_x0017__x0000__x0000_leesjun1024@hanmail.net_x000E__x0000__x0000_37690004547137_x0006__x0000__x0000_D00183_x0003__x0000__x0001_T³_x001C_È|Ç
+_x0000__x0000_1171558537_x0003__x0000__x0001_iÖÐÆ Á_x000B__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_XÇX¹,_x0000_¡ÇTÖ_x0008__x0000__x0000_20141027_x000D__x0000__x0000_010-6333-2457	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_ÅÌl­_x0005__x0000__x0000_08078 _x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_ÅÌl­ _x0000_àÂ_x0015_È\¸ _x0000_2_x0000_7_x0000_5_x0000_ _x0000_ _x0000_(_x0000_àÂ_x0015_ÈÙ³,_x0000_ _x0000_àÂ¸Ò¬¹DÅ_x000C_Ó¸Ò)_x0000__x0010__x0000__x0001_ÁÀ_x0000_¬Ù³ _x0000_1_x0000_5Î _x0000_1_x0000_0_x0000_4_x0000_,_x0000_ _x0000_1_x0000_0_x0000_5_x0000_8Ö_x0011__x0000__x0000_thejeil@naver.com_x000D__x0000__x0000_010-9668-2210_x000E__x0000__x0000_37690004550437_x0006__x0000__x0000_D00184_x0005__x0000__x0001_$Æ¨°¤ÂìÓ Î
+_x0000__x0000_1322489384_x0003__x0000__x0001_Å+È¨º_x000D__x0000__x0001_´ÆÙ³0®l­©ÆÔ _x0000_aÅ8Á_x001C_Á¬¹ _x0000_xÆ_x0008__x0000__x0000_20141028
+_x0000__x0000_0315756464
+_x0000__x0000_0315755600_x0008__x0000__x0001_½¬0®Ä³ _x0000_¨°ÅüÈÜÂ_x0006__x0000__x0000_472881_x0016__x0000__x0001_½¬0®Ä³ _x0000_¨°ÅüÈÜÂ _x0000_ÄÉt¬$Æ¨°\¸ _x0000_8_x0000_0_x0000_6_x0000_ _x0000_-_x0000_1_x0000_4_x0000__x000D__x0000__x0000_010-9289-9637_x0012__x0000__x0000_jongmo83@naver.com_x000E__x0000__x0000_37690004552737_x0006__x0000__x0000_D00186_x0005__x0000__x0001_ä¹XÎìÓxÇ¸Ò
+_x0000__x0000_6091853217_x0003__x0000__x0001_iÖ­ÝÂ_x0008__x0000__x0000_20141202_x000C__x0000__x0000_055-298-7330_x0005__x0000__x0000_51378_x0011__x0000__x0001_½¬¨° _x0000_=ÌÐÆÜÂ _x0000_XÇ=Ìl­ _x0000__x0018_¼Ä¬\¸ _x0000_6_x0000_3_x0000__x000D__x0000__x0000_010-3561-0209_x000E__x0000__x0000_o2bbi@nate.com_x0008__x0000__x0000_20141212_x000E__x0000__x0000_37690004554037_x0006__x0000__x0000_D00190_x0005__x0000__x0001_p­°À¤ÂìÓ Î
+_x0000__x0000_4010657765_x0003__x0000__x0001__x0015_¼_x001C_Âl×	_x0000__x0001_¤ÂìÓ ÎXÇX¹,_x0000_ _x0000_©ÆÔ_x0008__x0000__x0000_20150406_x000D__x0000__x0000_010-9977-7141_x0008__x0000__x0001__x0004_È|·½Ä³ _x0000_p­°ÀÜÂ_x0005__x0000__x0000_54102_x000F__x0000__x0001__x0004_È½ _x0000_p­°ÀÜÂ _x0000_¨°_x0018_Â¡Á5_x0000_8® _x0000_4_x0000_2_x0000__x000F__x0000__x0001_1_x0000_0_x0000_1_x0000_8Ö(_x0000__x0018_Â¡ÁÙ³,_x0000_ _x0000_(Ì$Æ¹L¾)_x0000__x0013__x0000__x0000_shp7141@hanmaiL.net_x000E__x0000__x0000_37690004558537_x0006__x0000__x0000_D00192
+_x0000__x0001__x0001_Æ8»¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1222039517_x0005__x0000__x0001__x0001_Æ8»¤ÂìÓ Î_x0003__x0000__x0001_@®_x0001_Æ8»_x0008__x0000__x0000_20150608_x000C__x0000__x0000_032-523-1406_x000C__x0000__x0000_032-517-8009	_x0000__x0001_xÇÌ_x0011_­íÅÜÂ _x0000_½ÉÓl­_x0005__x0000__x0000_21337_x000D__x0000__x0000_010-4320-1406_x0012__x0000__x0000_YM1406@hanmail.net_x0007__x0000__x0001_A_x0000_ñ´	®(_x0000_T_x0000_S_x0000_)_x0000__x0005__x0000__x0000_13042_x0003__x0000__x0001_@®Ù³½¬_x000E__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_+_x0000_3_x0000_0_x0000__x000E__x0000__x0000_37690004561837_x0006__x0000__x0000_D00193_x000B__x0000__x0001_ÑÐ¤Â@Õ¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1320972497_x0006__x0000__x0001_ÑÐ¤Â@Õ¤ÂìÓ Î_x0003__x0000__x0001__x0015_¼_x0004_Ö=Ì_x0006__x0000__x0001_´ÆÙ³_x0004_È8»©ÆÔ_x0008__x0000__x0000_20150610_x000D__x0000__x0000_010-3706-2477_x0007__x0000__x0001_½¬0®Ä³ _x0000_l­¬¹ÜÂ_x0005__x0000__x0000_11907_x000F__x0000__x0001_½¬0® _x0000_l­¬¹ÜÂ _x0000_UÆ_x0019_ÂÌ\¸ _x0000_5_x0000_0_x0000_7_x0000_	_x0000__x0001_3_x0000_5Î _x0000_ÑÐ¤Â@Õ¤ÂìÓ Î_x000F__x0000__x0000_pspin@naver.com_x0005__x0000__x0000_22022_x0003__x0000__x0001_HÅ°ÆÄÉ_x000C__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_7_x0000_._x0000_5_x0000__x000E__x0000__x0000_37690004560137_x0006__x0000__x0000_D00195
+_x0000__x0001_¤ÂìÓ ÎLÑlÐ(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_6172249744_x0005__x0000__x0001_¤ÂìÓ ÎLÑlÐ_x0003__x0000__x0001_tÇÝÐ0®_x0006__x0000__x0001__x001C_ÈpÈÅÅ _x0000_Áä¹_x000C__x0000__x0001_õ¬_x0008_Æ _x0000_¤ÂìÓ Î©ÆÔ,_x0000_ _x0000_¡ÇTÖ_x000B__x0000__x0000_051-7564800_x000C__x0000__x0000_051-756-4801_x0005__x0000__x0000_48222_x0017__x0000__x0001_½°À_x0011_­íÅÜÂ _x0000_Ù³·l­ _x0000_+ÈiÕ´ÆÙ³¥Ç\¸ _x0000_4_x0000_0_x0000_¼8® _x0000_8_x0000_'_x0000__x0001_1_x0000_0_x0000_3_x0000_Ù³ _x0000_1_x0000_0_x0000_5_x0000_8Ö,_x0000_1_x0000_0_x0000_6_x0000_8Ö(_x0000_¬ÀÁÉÙ³,_x0000_½°À _x0000_DÅÜÂDÅÜ´ _x0000_TÏ$Æq¸ _x0000_XÕ²DÌ _x0000_DÅ_x000C_Ó¸Ò)_x0000__x000D__x0000__x0000_010-5578-1988_x0015__x0000__x0000_ltktennis@hanmail.net_x000B__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_8_x0000__x0008__x0000__x0000_20150611_x000E__x0000__x0000_37690004562437_x0006__x0000__x0000_D00196	_x0000__x0001__x0015_¬¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_5041920932_x0004__x0000__x0001__x0015_¬¤ÂìÓ Î_x0003__x0000__x0001__x0015_¬@Çl­_x000D__x0000__x0001_LÑÈ²¤Â©ÆÔ,_x0000_ _x0000_XÇX¹,_x0000_ _x0000_àÂ_x001C_¼_x000C__x0000__x0000_053-314-9090_x0005__x0000__x0000_41433_x000D__x0000__x0000_010-3828-0474_x0013__x0000__x0000_keg0417@hanmail.net_x000D__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_6_x0000_+_x0000_1_x0000_5_x0000__x0008__x0000__x0000_20150612_x000E__x0000__x0000_37690004565337_x0006__x0000__x0000_D00199
+_x0000__x0001_P´¬¹¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1283008985_x0003__x0000__x0001_@®_x0001_Æ Á_x000B__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_¤ÂìÓ ÎXÇX¹_x0008__x0000__x0000_20150703_x000C__x0000__x0000_031-911-4191_x000C__x0000__x0000_031-913-0067_x0006__x0000__x0000_410829_x000F__x0000__x0001_½¬0®Ä³à¬ÅÜÂ _x0000_|Ç°ÀÙ³l­_x0015_È_x001C_¼°ÀÙ³_x000E__x0000__x0001_1_x0000_1_x0000_4_x0000_8_x0000_-_x0000_1_x0000_3_x0000_ _x0000_1_x0000_5Î2_x0000_,_x0000_3_x0000_8Ö_x000D__x0000__x0000_010-4288-3563_x0012__x0000__x0000_usop2n@hanmail.net_x000D__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_6_x0000_+_x0000_2_x0000_3_x0000__x000E__x0000__x0000_37690004568237_x0006__x0000__x0000_D00201_x000E__x0000__x0001_(_x0000_üÈ)_x0000_¤ÂtÎtÇ¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_6278102573_x000B__x0000__x0001_¤ÂtÎtÇ¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000__x0003__x0000__x0001_@®1ÁÐÆ_x0006__x0000__x0001_Áä¹ÅÅ _x0000_Ä³ä¹_x0008__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_ä¹_x0010_È_x000C__x0000__x0000_041-566-1879_x000C__x0000__x0000_041-554-2732_x0005__x0000__x0000_31157"_x0000__x0001_©Í­Ì¨°Ä³ _x0000_ÌHÅÜÂ _x0000__x001C_Á½l­ _x0000_1¼_x001D_Á3_x0000_\¸ _x0000_2_x0000_9_x0000_ _x0000_ _x0000_(_x0000_1¼_x001D_ÁÙ³,_x0000_ _x0000_½¶É¹_x0008_Ã%¼)_x0000__x000D__x0000__x0000_010-4513-1879_x0011__x0000__x0000_kimsw000@nate.com_x000E__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_4_x0000_0_x0000_+_x0000_2_x0000_0_x0000__x0008__x0000__x0000_20150804_x000E__x0000__x0000_37690004570937_x0006__x0000__x0000_D00202_x0008__x0000__x0001_¤ÂìÓå²(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_3052275067_x0003__x0000__x0001_HÅü­¹Â_x000C__x0000__x0000_042-522-9566_x000C__x0000__x0000_042-271-4786_x0006__x0000__x0000_300810_x0017__x0000__x0001__x0000_³_x0004_È_x0011_­íÅÜÂ _x0000__x0011_Él­ _x0000_Ù³_x001C_Á_x0000_³\¸ _x0000_1_x0000_2_x0000_0_x0000_1_x0000_(_x0000_ÜÐÉÓÙ³)_x0000__x0007__x0000__x0001_¤ÂìÓå² _x0000_ÜÐÉÓ_x0010_È_x000B__x0000__x0000_01062224787_x0010__x0000__x0000_spodaq@naver.com_x000D__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_5_x0000_+_x0000_3_x0000_3_x0000__x0008__x0000__x0000_20150805_x000E__x0000__x0000_37690004571537_x0006__x0000__x0000_D00203	_x0000__x0001_ðÅTÏ¬¹DÅ(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_2041477980_x0004__x0000__x0001_ðÅTÏ¬¹DÅ_x0003__x0000__x0001_@®ÁÀ0®_x0006__x0000__x0001_Ä³Áä¹ _x0000_t¬$Á_x000D__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_´Ì!ÇÜÂ_x001C_Á&lt;»$ÁXÎ_x0008__x0000__x0000_20150806_x000C__x0000__x0000_02-3390-4345_x000C__x0000__x0000_02-3390-4344
+_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_Ù³_x0000_³8»l­_x0005__x0000__x0000_02496_x0011__x0000__x0001__x001C_Á¸Æ _x0000_Ù³_x0000_³8»l­ _x0000_Ý¹°Æ\¸1_x0000_2_x0000_8® _x0000_1_x0000_9_x0000__x000B__x0000__x0001_1_x0000_5Î _x0000_XÕtÇÐÆ¤ÂìÓ Î°ÀÅÅ_x000D__x0000__x0000_010-9089-5363_x0017__x0000__x0000_01090895363@hanmail.net_x000B__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_2_x0000_0_x0000__x000E__x0000__x0000_37690004572137_x0006__x0000__x0000_D00205_x0005__x0000__x0001_ÁLÑ¤ÂìÓ Î
+_x0000__x0000_1971301851_x0003__x0000__x0001_@®_x0001_Æ_x0018_Â_x0008__x0000__x0001_Ä³Áä¹ÅÅ _x0000_Ä³ä¹ÅÅ	_x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_4»íÅÅÅ_x000B__x0000__x0000_01063388568_x0008__x0000__x0001_½¬0®Ä³ _x0000_XÇ_x0015_È½ÜÂ_x0005__x0000__x0000_11806!_x0000__x0001_½¬0®Ä³ _x0000_XÇ_x0015_È½ÜÂ _x0000_$Æ©º\¸ _x0000_1_x0000_7_x0000_0_x0000_ _x0000_°Àä´È¹DÇ _x0000_DÅ_x000C_Ó¸Ò _x0000_4_x0000_1_x0000_2_x0000_-_x0000_7_x0000_0_x0000_6_x0000__x000D__x0000__x0000_010-6338-8568_x0011__x0000__x0000_3388568@naver.com_x0005__x0000__x0000_26002_x0003__x0000__x0001__x0015_¬ÜÐ8Ö_x0008__x0000__x0000_20220901_x000E__x0000__x0000_37690004700437_x0006__x0000__x0000_D00209_x0018__x0000__x0001_¤ÂìÓ Î_x000C_Õì·¤Â(_x0000_S_x0000_p_x0000_o_x0000_r_x0000_t_x0000_s_x0000_ _x0000_P_x0000_l_x0000_u_x0000_s_x0000_)_x0000_(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1192167071_x0003__x0000__x0001__x0015_¬ÜÂ¨º_x0006__x0000__x0001_Ä³Áä¹ _x0000_LÇÝÂ_x0008__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_\ÕÝÂ_x000B__x0000__x0000_02-871-5513	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x0000_­EÅl­_x0005__x0000__x0000_08750_x000F__x0000__x0001__x001C_Á¸Æ _x0000__x0000_­EÅl­ _x0000_àÂ¼¹\¸3_x0000_8® _x0000_4_x0000_0_x0000__x0005__x0000__x0001_ÀÉXÕ _x0000_1_x0000_5Î_x000D__x0000__x0000_010-7703-5353_x001A__x0000__x0000_tennisplus0122@esero.go.krX_x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_ _x0000_/_x0000_ _x0000_2_x0000_5_x0000_S_x0000_S_x0000_ _x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_ _x0000_/_x0000_ _x0000_2_x0000_4_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_9_x0000_._x0000_6_x0000_ _x0000_/_x0000_ _x0000_2_x0000_4_x0000_S_x0000_S_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_ _x0000_/_x0000_ _x0000_2_x0000_3_x0000_F_x0000_W_x0000_ _x0000__x0018_ÂüÈ _x0000_ìÅàÂ _x0000_ _x0000_1_x0000_2_x0000_ _x0000_(_x0000_ô²ù²Ç _x0000_Æ­Ì&lt;Ç\¸ _x0000_6_x0000_ _x0000__x0018_¼_x0001_Æ)_x0000__x0008__x0000__x0000_20160114_x000E__x0000__x0000_37690004577337_x0006__x0000__x0000_D00210_x0011__x0000__x0001_(_x0000_üÈ)_x0000_ÐÅtÇ_x001C_ÈtÇxÇ0Ñ´°TÁ °(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1268641398_x000C__x0000__x0000_031-761-8980_x000C__x0000__x0000_031-761-2140_x0005__x0000__x0000_12769_x000D__x0000__x0000_010-4552-3318	_x0000__x0000_1800-6142_x000E__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_4_x0000_0_x0000_+_x0000_2_x0000_5_x0000__x0008__x0000__x0000_20160121_x000E__x0000__x0000_37690004578037_x0006__x0000__x0000_D00256	_x0000__x0001_p¬1Á¤ÂìÓ Î(_x0000_Å°À)_x0000_
+_x0000__x0000_6210808090_x0003__x0000__x0001__x0015_È+È_x0015_¬_x0006__x0000__x0001_Ä³Áä¹ _x0000__x001C_ÈpÈ_x000B__x0000__x0001_ìÕ¤Â0®l­,_x0000_ _x0000_¤ÂìÓ Î©ÆÔ_x0008__x0000__x0000_20160412_x000C__x0000__x0000_055-387-3613_x000C__x0000__x0000_055-387-3615_x0008__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_Å°ÀÜÂ_x0005__x0000__x0000_50621 _x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_Å°ÀÜÂ _x0000__x001C_Á|ÇÙ³\¸ _x0000_2_x0000_5_x0000_ _x0000_ _x0000_(_x0000__x0011_É½Ù³,_x0000_ _x0000_$Ç ÁÝÀ_x0001_Æ´ÅP­äÂ)_x0000__x000D__x0000__x0000_010-2390-2994_x0013__x0000__x0000_dhrhr68@hanmail.netH_x0000__x0001_2_x0000_4_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_3_x0000_5_x0000_ _x0000_/_x0000_2_x0000_4_x0000_S_x0000_S_x0000__x0018_ÂüÈìÅàÂ _x0000_3_x0000_5_x0000_ _x0000_/_x0000_ _x0000_2_x0000_3_x0000_F_x0000_W_x0000_ _x0000__x0018_ÂüÈ _x0000_ìÅàÂ _x0000_3_x0000_5_x0000_ _x0000_/_x0000_ _x0000_2_x0000_3_x0000_S_x0000_S_x0000_ _x0000__x0018_ÂüÈ _x0000_ìÅàÂ _x0000_3_x0000_5_x0000_(_x0000_|·_x0013_Ï+_x0000_È¹D¾¤Â _x0000_9_x0000_4_x0000_3_x0000_,_x0000_2_x0000_5_x0000_0_x0000_)_x0000__x0008__x0000__x0000_20160407_x000E__x0000__x0000_37690004581237_x0006__x0000__x0000_D00267_x0006__x0000__x0001__x001C_ÈtÇD¾¤ÂìÓ Î
+_x0000__x0000_6664100083_x0003__x0000__x0001_Ç_x0015_È\Õ_x000D__x0000__x0001_Ä³ä¹ _x0000__x000F_¼ _x0000_Áä¹ÅÅ,_x0000_ _x0000__x001C_ÁD¾¤Â_x000C__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_ _x0000__x0011_­à¬_x0000_³ÕÅÅ_x0008__x0000__x0000_20160610_x000C__x0000__x0000_062-523-7451_x000C__x0000__x0000_062-523-7455_x0005__x0000__x0000_62023_x000D__x0000__x0001__x0011_­üÈ _x0000__x001C_Ál­ _x0000_´ÆÌ\¸ _x0000_1_x0000_2_x0000_2_x0000__x0005__x0000__x0001_(_x0000__x000D_Ã_x000C_ÍÙ³)_x0000__x000D__x0000__x0000_010-4606-4538_x0015__x0000__x0000_jhrim1226@hanmail.net_x0008__x0000__x0000_20160601_x000E__x0000__x0000_37690004584137_x0006__x0000__x0000_D00280_x0005__x0000__x0001_Ä³ô²¤ÂìÓ Î
+_x0000__x0000_3071042161_x0003__x0000__x0001_$ÇÙ³ÝÂ_x000B__x0000__x0001_Ä³ä¹_x000F_¼ _x0000_Áä¹ÅÅ _x0000_Áä¹ÅÅ_x0010__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_Ç_x0004_Èp¬ _x0000__x0010_Óä¹,_x0000_ _x0000__x0000_³ìÅ_x0008__x0000__x0000_20160825_x000C__x0000__x0000_044-863-8908_x000C__x0000__x0000_044-863-8970_x000F__x0000__x0001_8Á+È¹ÒÄ¼ÇXÎÜÂ _x0000_8Á+È¹ÒÄ¼ÇXÎÜÂ_x0005__x0000__x0000_30102_x001E__x0000__x0001_8Á+È¹ÒÄ¼ÇXÎÜÂ _x0000__x0008_È¬Ç\¸ _x0000_1_x0000_7_x0000_2_x0000_ _x0000_(_x0000_´ÅÄÉÙ³,_x0000_ _x0000_ÜÐ\Õ_x0004_Õ_x0008_¸¤Â&lt;Á0Ñ)_x0000__x0004__x0000__x0001_1_x0000_0_x0000_1_x0000_8Ö_x000D__x0000__x0000_010-7185-8008_x0015__x0000__x0000_dodamsports@naver.com_x000E__x0000__x0000_37690004586437_x0006__x0000__x0000_D00282_x0005__x0000__x0001__x0004_²¬¹¤ÂìÓ Î
+_x0000__x0000_1082124505_x0003__x0000__x0001_@®l×_x0015_È_x0006__x0000__x0001_Áä¹ _x0000_Ä³Áä¹_x000C__x0000__x0001__x0004_ÈÇÁÀp¬·ÅÅ _x0000_0¼Ü´ü»4Ñ _x0000__x000B__x0000__x0000_02-848-6291_x000B__x0000__x0000_02-848-7556
+_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x0001_Æñ´ìÓl­_x0005__x0000__x0000_07375_x000E__x0000__x0001__x001C_Á¸Æ _x0000__x0001_Æñ´ìÓl­ _x0000_Ä³àÂ\¸ _x0000_5_x0000_1_x0000__x000D__x0000__x0001_1_x0000_5Î _x0000_1_x0000_0_x0000_5_x0000_8Ö(_x0000_¡ÁU³L¾)µ)_x0000__x000D__x0000__x0000_010-8393-6291_x0013__x0000__x0000_hee00jung@naver.com_x0008__x0000__x0000_20160905_x000E__x0000__x0000_37690004588737_x0006__x0000__x0000_D00286_x0007__x0000__x0001_Æ%±¤Â _x0000_1Á¨°_x0010_È
+_x0000__x0000_2603001743_x0003__x0000__x0001_MÖ¥Ç8Ö_x0008__x0000__x0001_Ä³ä¹ _x0000__x000F_¼ _x0000_Áä¹ÅÅ_x0008__x0000__x0000_20151218_x000C__x0000__x0000_031-755-7257_x0007__x0000__x0001_½¬0®Ä³ _x0000_1Á¨°ÜÂ_x0005__x0000__x0000_13110_x001E__x0000__x0001_½¬0®Ä³ _x0000_1Á¨°ÜÂ _x0000__x0018_Â_x0015_Èl­ _x0000_1Á¨°_x0000_³\¸ _x0000_1_x0000_2_x0000_6_x0000_7_x0000_ _x0000_-_x0000_1_x0000_ _x0000_(_x0000_ÜÐÉÓÙ³)_x0000__x000D__x0000__x0000_010-7191-7257_x0012__x0000__x0000_nero1016@naver.com_x0002__x0000__x0001_¨°¸Ó_x0008__x0000__x0000_20161109_x000E__x0000__x0000_37690004591037_x0006__x0000__x0000_D00287_x0005__x0000__x0001_¤ÐtÎ¤ÂìÓ Î
+_x0000__x0000_6103752918_x0003__x0000__x0001_@®ÜÐÇ_x0008__x0000__x0000_20161125_x000C__x0000__x0000_052-268-6086_x000C__x0000__x0000_052-272-5908_x0008__x0000__x0001_¸Æ°À_x0011_­íÅÜÂ _x0000_¨°l­_x0005__x0000__x0000_44692_x0016__x0000__x0001_¸Æ°À_x0011_­íÅÜÂ _x0000_¨°l­ _x0000_Ë³ÈÉ\¸ _x0000_1_x0000_2_x0000_4_x0000_ _x0000_ _x0000_(_x0000_ì²Ù³)_x0000__x0003__x0000__x0000_3/2_x000D__x0000__x0000_010-9568-6086_x0014__x0000__x0000_kika5908@hanmail.net_x000E__x0000__x0000_37690004592637_x0006__x0000__x0000_D00292_x0008__x0000__x0001_Æ%±¤Â _x0000_¤ÂìÓÐÆ_x0010_È
+_x0000__x0000_6977800050_x0003__x0000__x0001_\ÕÀ­_x0001_Æ_x0008__x0000__x0000_20170102_x000C__x0000__x0000_051-517-3862_x000C__x0000__x0000_051-583-1023	_x0000__x0001_½°À_x0011_­íÅÜÂ _x0000__x0008_®_x0015_Èl­_x0005__x0000__x0000_46207&amp;_x0000__x0001_½°À_x0011_­íÅÜÂ _x0000__x0008_®_x0015_Èl­ _x0000_´Ì!Çõ¬ÐÆ\¸3_x0000_9_x0000_9_x0000_¼8® _x0000_3_x0000_2_x0000_4_x0000_ _x0000_ _x0000_(_x0000_P´l­Ù³,_x0000_ _x0000_¤ÂìÓÐÆ_x000C_ÓlÐ)_x0000__x0010__x0000__x0001_ÀÉXÕ1_x0000_5Î(_x0000_P´l­Ù³,_x0000_ _x0000_äÂ´°´Ì!Ç_x0000_­)_x0000__x000D__x0000__x0000_010-5505-3862_x0013__x0000__x0000_hgy4285@hanmail.net_x000E__x0000__x0000_37690004595537_x0006__x0000__x0000_D00306_x0007__x0000__x0001_Æ%±¤Â _x0000_ÁÀ4»_x0010_È
+_x0000__x0000_8042300420_x0003__x0000__x0001_@®_x0004_Ö+È_x000D__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_´ÆÙ³©ÆÔ _x0000_¡ÇTÖ_x0008__x0000__x0000_20170119_x000D__x0000__x0000_010-6886-7065_x000C__x0000__x0000_062-374-5410_x0005__x0000__x0000_61970_x0013__x0000__x0001__x0011_­üÈ _x0000__x001C_Ál­ _x0000_ÁÀ4»ü»üÈ\¸3_x0000_2_x0000_¼8® _x0000_3_x0000_-_x0000_5_x0000__x0013__x0000__x0000_sskim-j@hanmail.net_x000E__x0000__x0000_37690004597837_x0006__x0000__x0000_D00308_x0005__x0000__x0001_C_x0000_S_x0000_¤ÂìÓ Î
+_x0000__x0000_2270838785_x0007__x0000__x0001_iÖ_x001C_ÂU³xÆ _x0000_1_x0000_+º_x000C__x0000__x0000_031-385-1222_x000C__x0000__x0000_031-388-3477_x0005__x0000__x0000_13958_x0016__x0000__x0001_½¬0® _x0000_HÅÅÜÂ _x0000_Ì¹HÅl­ _x0000__x0008_Æ Âõ¬ÐÆ\¸5_x0000_2_x0000_¼8® _x0000_2_x0000__x000D__x0000__x0000_010-3176-9037_x0013__x0000__x0000_bill@cssports.co.kr_x000D__x0000_</v>
           </cell>
           <cell r="P37" t="str">
-            <v>618814</v>
-          </cell>
-          <cell r="Q37" t="str">
-            <v>부산광역시 강서구 명지오션시티13로 12-22  홍진빌딩 106호</v>
+            <v>ⴰ㜲㜲㈭ㄷ༸Ā25FW수주여신 15+3.5_x000E_㌀㘷〹〰㔴㠹㌴ط_x0000_い㌰ㄱ
+吁곏䒹꓅⃓⣎_xDC00_旂⧗਀_x0000_〳㜴〰㌱㘳_x0006_吁곏䒹꓅⃓ώĀ최영숙_x0012_ꐁ⃓꧎裆Ⳕက৓㳍ⲻ砀쓇㳁ⲻ　삮꧐裆ු_x0000_㄰ⴰ㘲㠱㔭ㄵస_x0000_㌰ⴱㄳⴲ㤸㈸_x0007_봁ガ쒮₳_xDC00_旂_xDCD7_ׂ_x0000_㐱㈹༲Ā경기 시흥시 은계번영길 27_x000F_㌁　㌀㠀⣖䀀觇_xD9D5_ⲳ _xDC00_೒泓⧐ᔀ_x0000_畱敥浮㕴ㄵ䀸慮敶⹲潣౭_x0000_㌰ⴱ〴ⴴㄶㄲ_x0008_㈀㄰〷㈲ะ_x0000_㜳㤶〰㐰〶㘰㜳_x0006_䐀〰ㄳาĀ요넥스(YONEX) 이천점
+㄀㔰㘲ㄴ㔵̳Ā윤유진_x000C_　ㄳ㘭ㄳ㈭ㄲܰĀ경기도 이천시_x0005_㄀㌷㈶_x0017_봁ガ쒮₳琀鳇_xDCCC_⃂怀⣅ᖸ峈₸㄀㐀㈀  ⠀㴀ӌ_xD9C8_⦳ഀ_x0000_㄰ⴰ㐳㤵ㄭㄳဳ_x0000_楪㝮〶䀱慤浵渮瑥_x0003_封ᗍ㢬ࣖ_x0000_〲㜱㈰ㄲ_x000E_㌀㘷〹〰㘴㄰㌲ط_x0000_い㌰㐲_x0006_ఁ룓࣒꒱⃓૎_x0000_㈱㈷㜴㌱㠶_x0003_䀁ꦮ惆೅_x0000_㌰ⴱ㤳ⴸ㤸㌵_x000C_　ㄳ㌭㠹㠭㔹ܴĀ경기도 군포시_x0005_㄀㠵㌳_x0016_봁ガ쒮₳瀀_xDCD3_⃂␀ࣆ岮₸㄀㔀　  ⠀ࠀᖮ_xD9C8_⦳ऀĀ102호(금정동)_x000D_　〱㐭㔸ⴴ㤸㌵_x0010_欀慹㜵㜶湀瑡⹥潣࡭_x0000_〲㜱㌰〲_x000E_㌀㘷〹〰㘴㌰㌵ط_x0000_い㌰㠲_x0006_쐁ﳉト_xDCBC_ﲴ㒻૑_x0000_ㄶㄳ㠰㜲㤲_x0003_ᔁꃈಬ_x0000_㔰ⴵ㐷ⴷㄲ㄰_x0008_봁솬ꣀ쒰₳쐀ﳉ_xDCC8_ׂ_x0000_㈵〸ᤶĀ경상남도 진주시 솔밭로75번길 8  (상평동)_x000D_　〱㤭ㄶⴲㄲ㠸_x0011_樀杣ㄲ㠸湀癡牥.com_x000B__x0000__x0000_01095082188_x0008__x0000__x0000_20170324_x000E__x0000__x0000_37690004604137_x0006__x0000__x0000_D00338
+_x0000__x0001_Æ%±¤Â=ÌÐÆ_x0010_È(_x0000_øÂtÎ)_x0000_
+_x0000__x0000_6092352584_x0003__x0000__x0001_HÅ¬Çü­_x0010__x0000__x0001_¤ÂìÓ Î _x0000_XÇX¹ _x0000__x000F_¼ _x0000_©ÆÔ _x0000_È¹lÐ_x001C_ÈÇ_x0008__x0000__x0000_20170411_x000C__x0000__x0000_055-261-0123_x0005__x0000__x0000_51420_x0019__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_=ÌÐÆÜÂ _x0000_1Á°Àl­ _x0000__x0018_¼ÀÉ\¸ _x0000_8_x0000_ _x0000_ _x0000_(_x0000__x0018_¼ÀÉÙ³)_x0000__x0005__x0000__x0001_(_x0000__x0018_¼ÀÉÙ³)_x0000__x000D__x0000__x0000_010-9796-1346_x0011__x0000__x0000_cwssaka@naver.com
+_x0000__x0000_0552610123_x000E__x0000__x0000_37690004606437_x0006__x0000__x0000_D00382_x0004__x0000__x0001_$Æ¤ÂìÓ Î
+_x0000__x0000_2860500614_x0003__x0000__x0001__x0015_¼Á|·_x000C__x0000__x0001__x0004_ÈÇÁÀp¬·(_x0000_¤ÂìÓ Î©ÆÔ)_x0000__x000C__x0000__x0000_063-231-0360_x0005__x0000__x0000_54947_x0015__x0000__x0001__x0004_È½ _x0000__x0004_ÈüÈÜÂ _x0000_DÆ°Àl­ _x0000__x0004_È|·_x0010_¬_x0001_Æ\¸ _x0000_4_x0000_0_x0000_-_x0000_1_x0000__x000B__x0000__x0000_01076785147_x0014__x0000__x0000_sora1976kr@naver.com_x0003__x0000__x0001__x0015_¼Ñ¼%ÆQ_x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_+_x0000_1_x0000_0_x0000_0_x0000_ _x0000_/_x0000_ _x0000_2_x0000_5_x0000_S_x0000_S_x0000_ _x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_ _x0000_+_x0000_ _x0000_1_x0000_0_x0000_0_x0000_ _x0000_/_x0000_ _x0000_ _x0000_2_x0000_4_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_ _x0000_/_x0000_ _x0000_2_x0000_4_x0000_S_x0000_S_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_ _x0000_/_x0000_ _x0000_2_x0000_3_x0000_F_x0000_W_x0000_ _x0000__x0018_ÂüÈ _x0000_ìÅàÂ _x0000_1_x0000_2_x0000__x0008__x0000__x0000_20170710_x000E__x0000__x0000_37690004610337_x0006__x0000__x0000_D00392_x0007__x0000__x0001_¨Ö1Á+ÈiÕ¤ÂìÓ Î
+_x0000__x0000_7521600607_x0002__x0000__x0001_@®_x0004_½_x0008__x0000__x0000_20170812_x000C__x0000__x0000_064-733-2992_x0005__x0000__x0000_63591_x0013__x0000__x0001__x001C_ÈüÈ¹ÒÄ¼ÇXÎÄ³ _x0000__x001C_ÁÀ­ìÓÜÂ _x0000_Ù³8»\¸ _x0000_3_x0000_0_x0000__x000B__x0000__x0000_01090156265_x0010__x0000__x0000_ddadon@naver.com_x000B__x0000__x0000_01036928845_x0008__x0000__x0000_20170821_x000E__x0000__x0000_37690004611037_x0006__x0000__x0000_D00396_x000E__x0000__x0001_Æ%±¤Â _x0000_Å°À_x0010_È(_x0000_TÖ·¤ÂìÓ Î)_x0000_
+_x0000__x0000_6211383962_x0003__x0000__x0001_\ÍiÖðÅ_x0008__x0000__x0000_20170813_x000C__x0000__x0000_055-382-6688_x000C__x0000__x0000_055-366-6648_x0005__x0000__x0000_50548_x000F__x0000__x0001_½¬¨° _x0000_Å°ÀÜÂ _x0000_ÅÆÁÀ_x0000_³\¸ _x0000_9_x0000_6_x0000_1_x0000__x0007__x0000__x0001_Æ%±¤Â _x0000_Å°À_x0010_È_x000D__x0000__x0000_010-9323-8281_x0016__x0000__x0000_eegmom0808@hanmail.net_x0008__x0000__x0000_20170915_x000E__x0000__x0000_37690004612637_x0006__x0000__x0000_D00408_x0005__x0000__x0001_l­¬¹TÏ¸Ò\¸
+_x0000__x0000_1321920436_x0003__x0000__x0001_àÂ_x0001_Æ8Ö_x0008__x0000__x0000_20060509_x000C__x0000__x0000_031-562-3307_x0005__x0000__x0000_11942_x0012__x0000__x0001_½¬0®Ä³ _x0000_¨°ÅüÈÜÂ _x0000__x0000_¬´Æ\¸2_x0000_8® _x0000_1_x0000_1_x0000_4_x0000__x000D__x0000__x0001_ø»1Á_x0004_Õ|·Ç _x0000_1_x0000_5Î _x0000_1_x0000_0_x0000_3_x0000_8Ö_x000D__x0000__x0000_010-3909-6608_x0015__x0000__x0000_sjs940421@hanmail.net_x000B__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_2_x0000_6_x0000__x0008__x0000__x0000_20171226_x000E__x0000__x0000_37690004615537_x0006__x0000__x0000_D00409_x0007__x0000__x0001_Æ%±¤Â _x0000_¤ÂìÓ Î
+_x0000__x0000_8624500277_x0003__x0000__x0001_tÇU³©Æ_x0008__x0000__x0000_20170905_x000C__x0000__x0000_041-357-1617_x0008__x0000__x0001_©Í­Ì¨°Ä³ _x0000_ù²ÄÉÜÂ_x0005__x0000__x0000_31777_x000E__x0000__x0001_©Í¨° _x0000_ù²ÄÉÜÂ _x0000_P­Ù³8® _x0000_1_x0000_2_x0000_4_x0000__x000D__x0000__x0000_010-3116-9915_x0013__x0000__x0000_ljy161617@naver.com_x0008__x0000__x0000_20171221_x000E__x0000__x0000_37690004616137_x0006__x0000__x0000_D00416_x0005__x0000__x0001__x001C_ÁÄÉ¤ÂìÓ Î
+_x0000__x0000_5920100957_x0003__x0000__x0001_@®ÉÓÜÐ_x000D__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_ _x0000__x0004_ÈÇÁÀp¬·ÅÅ_x0008__x0000__x0000_20180301_x000C__x0000__x0000_031-236-4936_x000C__x0000__x0000_031-216-4936_x0007__x0000__x0001_½¬0®Ä³ _x0000_©ÆxÇÜÂ_x0005__x0000__x0000_16833_x0013__x0000__x0001_½¬0® _x0000_©ÆxÇÜÂ _x0000__x0018_ÂÀÉl­ _x0000_ìÓ@Ç_x0000_³\¸ _x0000_4_x0000_6_x0000_7_x0000__x0016__x0000__x0001__x0018_ÂÀÉxÔt¹ÀÉ$ÆÔÆÜ´È¹lÐÁÀ_x0000_¬ _x0000_1_x0000_0_x0000_3_x0000_Ù³ _x0000_1_x0000_2_x0000_3_x0000_8Ö_x000D__x0000__x0000_010-4679-5630_x0013__x0000__x0000_ren7303@hanmail.net_x000E__x0000__x0000_37690004618437_x0006__x0000__x0000_D00431_x0006__x0000__x0001_¤ÂìÓ Îä¹È²DÅ
+_x0000__x0000_2701201033_x0003__x0000__x0001_8»¹ÂÄÉ_x0008__x0000__x0000_20180615_x000C__x0000__x0000_042-545-8511	_x0000__x0001__x0000_³_x0004_È_x0011_­íÅÜÂ _x0000_ Ç1Ál­_x0005__x0000__x0000_34210_x0016__x0000__x0001__x0000_³_x0004_È _x0000_ Ç1Ál­ _x0000_YÕXÕ_x0011_ÉYÅ\¸1_x0000_2_x0000_8_x0000_¼8® _x0000_2_x0000_3_x0000_-_x0000_8_x0000__x000B__x0000__x0001_1_x0000_0_x0000_2_x0000_8Ö _x0000_¤ÂìÓ Îä¹È²DÅ_x000D__x0000__x0000_010-6683-2114_x0013__x0000__x0000_capmoon39@naver.com_x0008__x0000__x0000_20180427_x000E__x0000__x0000_37690004623037_x0006__x0000__x0000_D00433_x000D__x0000__x0001__x0015_È_x0018_Â¤ÂìÓ Î _x0000_Æ%±¤Â _x0000__x0001_ÆüÈ_x0010_È
+_x0000__x0000_5293300343_x0003__x0000__x0001_@®Ù³ðÅ	_x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_ _x0000_XÇX¹_x0008__x0000__x0000_20170407_x000B__x0000__x0000_01048177736
+_x0000__x0000_0546367233_x0008__x0000__x0001_½¬ÁÀ½Ä³ _x0000__x0001_ÆüÈÜÂ_x0005__x0000__x0000_36138_x0013__x0000__x0001_½¬½ _x0000__x0001_ÆüÈÜÂ _x0000__x0000_³YÕ\¸2_x0000_0_x0000_1_x0000_¼8® _x0000_8_x0000_-_x0000_6_x0000__x0007__x0000__x0001_iÖ_x0008_®L¾)µ _x0000_1_x0000_5Î_x000D__x0000__x0000_010-4817-7736_x0013__x0000__x0000_kdy9249@hanmail.net_x0008__x0000__x0000_20180518_x000E__x0000__x0000_37690004624637_x0006__x0000__x0000_D00471_x000B__x0000__x0001_(_x0000_üÈ)_x0000_DÅüÈ_x0008_¸ìÓ Î__x0000_¹Ò_x0010_Ó_x000B__x0000__x0001_(_x0000_üÈ)_x0000_DÅüÈ_x0008_¸ìÓ Î-_x0000_¹Ò_x0010_Ó_x0008__x0000__x0000_20181026_x000B__x0000__x0000_02-489-1992_x000E__x0000__x0001_½¬0® _x0000__x0011_­üÈÜÂ _x0000_à¬½\¸ _x0000_3_x0000_4_x0000_0_x0000__x000D__x0000__x0000_070-4741-9644_x000E__x0000__x0000_37690004626937_x0006__x0000__x0000_D00490	_x0000__x0001_à¬ÅÜÂ0¼Ü´ü»4Ñ_x0011_ÖÖ
+_x0000__x0000_1288284226_x0003__x0000__x0001_tÇ8ÖÄÉ_x0008__x0000__x0000_20190315_x000B__x0000__x0000_01027161641_x0005__x0000__x0000_10223_x0014__x0000__x0001_½¬0® _x0000_à¬ÅÜÂ _x0000_|Ç°À_x001C_Ál­ _x0000__x0011_ÉYÅ\¸ _x0000_1_x0000_6_x0000_0_x0000_1_x0000__x001D__x0000__x0001_,_x0000_ _x0000_1_x0000_5Î(_x0000__x0000_³TÖÙ³,_x0000_ _x0000_à¬ÅÜÂ+ÈiÕ´ÆÙ³¥Ç _x0000_ÀÉXÕ1_x0000_5Î _x0000_C_x0000_-_x0000_0_x0000_8_x0000_)_x0000__x000D__x0000__x0000_010-2716-1641_x0012__x0000__x0000_76melany@gmail.com_x0005__x0000__x0000_19003_x0003__x0000__x0001_HÅ¬Ç°Æ_x000E__x0000__x0000_37690004628137_x0006__x0000__x0000_D00503_x0005__x0000__x0001_°tÇ¤Âü»4Ñ
+_x0000__x0000_6161951553_x0003__x0000__x0001_à¬ðÅüÈ
+_x0000__x0001_¤ÂìÓ Î©ÆÔ_x000F_¼0®ÀÐ©ÆÔ_x0008__x0000__x0000_20100913_x000C__x0000__x0000_064-712-4524_x000C__x0000__x0000_064-711-4524_x000B__x0000__x0001__x001C_ÈüÈ¹ÒÄ¼ÇXÎÄ³ _x0000__x001C_ÈüÈÜÂ_x0005__x0000__x0000_63087_x0013__x0000__x0001__x001C_ÈüÈ¹ÒÄ¼ÇXÎÄ³ _x0000__x001C_ÈüÈÜÂ _x0000_ÄÉp­8® _x0000_1_x0000_-_x0000_6_x0000__x000D__x0000__x0000_010-3639-7899_x0011__x0000__x0000_ktf1974@naver.com_x0003__x0000__x0001_@®1Át¬_x000B__x0000__x0000_01036397899_x0008__x0000__x0000_20190424_x000E__x0000__x0000_37690004630837_x0006__x0000__x0000_D00504_x0008__x0000__x0001_¤ÂÀÐ¤ÂìÓ Î__x0000_¹Ò_x0010_Ó
+_x0000__x0000_3031310445	_x0000__x0001_¤ÂÀÐ¤ÂìÓ Î(_x0000_©ÍüÈ)_x0000__x0003__x0000__x0001_LÇ_x0011_­l×_x0008__x0000__x0000_20070607_x000C__x0000__x0000_043-855-7688_x000C__x0000__x0000_043-848-3727_x0008__x0000__x0001_©Í­Ì½Ä³ _x0000_©ÍüÈÜÂ_x0005__x0000__x0000_27393_x000E__x0000__x0001_©Í½ _x0000_©ÍüÈÜÂ _x0000__x0015_Ö$Á\¸ _x0000_1_x0000_5_x0000_9_x0000__x0005__x0000__x0001_¤ÂÀÐ¤ÂìÓ Î_x000D__x0000__x0000_010-5303-1397_x0013__x0000__x0000_ekh3083@hanmail.net_x0006__x0000__x0000_D00513	_x0000__x0001__x001C_Á¸ÆÜÂ´Ì!ÇÖ__x0000_¹Ò_x0010_Ó
+_x0000__x0000_6078287556_x0006__x0000__x0001__x001C_Á¸ÆÜÂ´Ì!ÇÖ_x0003__x0000__x0001__x0015_¼ÐÆ_x001C_Â_x0003__x0000__x0001__x001C_ÁD¾¤Â_x0004__x0000__x0001_LÑÈ²¤Â¥Ç_x0008__x0000__x0000_20190614_x0001__x0000__x0000_0	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x0011_É·l­_x0005__x0000__x0000_02119_x000E__x0000__x0001__x001C_Á¸Æ _x0000__x0011_É·l­ _x0000_Ý¹°Æ\¸ _x0000_1_x0000_8_x0000_2_x0000__x0008__x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ´Ì!ÇÖ_x0008__x0000__x0000_20190617_x000E__x0000__x0000_37690004638937_x0006__x0000__x0000_D00515_x0004__x0000__x0001__x0001_Æ4»S_x0000_P_x0000_
+_x0000__x0000_4081497216_x0004__x0000__x0001__x0001_Æ4»s_x0000_p_x0000__x0003__x0000__x0001_@®U³	½_x0007__x0000__x0001_Ä³Áä¹,_x0000_ _x0000__x001C_ÈpÈ_x0011__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_ _x0000_±tÇ0®l­,_x0000_ _x0000_ìÕ¤Â0®l­_x0008__x0000__x0000_20070824_x000D__x0000__x0000_010-3622-7289_x000C__x0000__x0000_062-651-9942_x0008__x0000__x0001__x0011_­üÈ_x0011_­íÅÜÂ _x0000_¨°l­_x0005__x0000__x0000_61655_x000E__x0000__x0001__x0011_­üÈ _x0000_¨°l­ _x0000__x0000_³¨°_x0000_³\¸ _x0000_2_x0000_5_x0000_2_x0000_	_x0000__x0001_1¼´ÆÙ³,_x0000_ _x0000__x0001_Æ4»S_x0000_P_x0000__x0013__x0000__x0000_6519944@hanmail.net_x000D__x0000__x0000_(062)653-4141$_x0000__x0001_2_x0000_4_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_3_x0000_5_x0000_ _x0000_/_x0000_2_x0000_4_x0000_S_x0000_S_x0000__x0018_ÂüÈìÅàÂ _x0000_3_x0000_5_x0000_ _x0000_/_x0000_ _x0000__x0018_Â_x0008_®½qÈ _x0000_2_x0000_ÔÆµÑ_x001C_È_x0008__x0000__x0000_20190531_x000E__x0000__x0000_37690004634337_x0006__x0000__x0000_D00517_x000B__x0000__x0001_O_x0000_K_x0000_ _x0000_¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1293177008_x0003__x0000__x0001_tÇ_x0001_Æ±Æ
+_x0000__x0001_Ä³Áä¹,_x0000_Ä³ä¹,_x0000__x001C_ÁD¾¤Â_x0011__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_l­ä¹_x0000_³Õ,_x0000_t¬&lt;»­ÌÁ©ÆíÅ_x0008__x0000__x0000_20071108_x000C__x0000__x0000_031-708-3066
+_x0000__x0000_0317083067_x0005__x0000__x0000_13504_x0017__x0000__x0001_½¬0® _x0000_1Á¨°ÜÂ _x0000_½ù²l­ _x0000_¥Çø»\¸1_x0000_2_x0000_2_x0000_¼8® _x0000_3_x0000_-_x0000_1_x0000__x0005__x0000__x0001_(_x0000_|ÅÑÐÙ³)_x0000__x000D__x0000__x0000_010-8714-3324_x0014__x0000__x0000_75winwin@hanmail.net_x000B__x0000__x0000_01087143324_x000E__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_5_x0000_+_x0000_2_x0000_2_x0000__x0008__x0000__x0000_20190621_x000E__x0000__x0000_37690004635037_x0006__x0000__x0000_D00519_x0005__x0000__x0001__x0004_Ç_x0008_±¤ÂìÓ Î
+_x0000__x0000_3160449978_x0003__x0000__x0001_\Í_x0004_ÖÄÉ_x0008__x0000__x0000_20140927_x000D__x0000__x0000_010-6482-0228_x000C__x0000__x0000_041-665-1857_x0008__x0000__x0001_©Í­Ì¨°Ä³ _x0000__x001C_Á°ÀÜÂ_x0005__x0000__x0000_31993_x000F__x0000__x0001_©Í¨° _x0000__x001C_Á°ÀÜÂ _x0000_(ÇÀÉ1_x0000_6_x0000_\¸ _x0000_2_x0000_2_x0000__x0008__x0000__x0001_C_x0000_Ù³ _x0000_(_x0000_Ù³8»Ù³)_x0000__x0011__x0000__x0000_chj1981@naver.com_x000D__x0000__x0000_010-9112-9996_x0008__x0000__x0001_6_x0000_ÔÆ _x0000_üÈ8»µÑ_x001C_È/_x0000__x0008__x0000__x0000_20190620_x000E__x0000__x0000_37690004636637_x0006__x0000__x0000_D00524
+_x0000__x0001_üÈÝÂÖ¬À _x0000_©ÆxÇÆ%±¤Â
+_x0000__x0000_7968702997_x0003__x0000__x0001_@®ÄÉ©Æ_x0008__x0000__x0000_20150409_x000D__x0000__x0000_010-8881-0413_x0005__x0000__x0000_16967_x0014__x0000__x0001_½¬0® _x0000_©ÆxÇÜÂ _x0000_0®e×l­ _x0000_àÂ_x0008_¬\¸5_x0000_7_x0000_¼8® _x0000_7_x0000_
+_x0000__x0001_(_x0000_àÂ_x0008_¬Ù³,_x0000_ÐÅ¤Â_x001C_ÈtÇ)_x0000__x0013__x0000__x0000_goodester@naver.com_x0007__x0000__x0001_2_x0000_ÔÆ _x0000__x0018_Â_x0008_®µÑ_x001C_È_x0008__x0000__x0000_20190711_x000E__x0000__x0000_37690004640537_x0006__x0000__x0000_D00526_x0006__x0000__x0001_ìÅ_x0018_Â _x0000_Æ%±¤Â
+_x0000__x0000_6765400493_x0003__x0000__x0001_@® ÁU³_x0008__x0000__x0000_20190701_x000D__x0000__x0000_010-2066-5376_x0008__x0000__x0001__x0004_È|·¨°Ä³ _x0000_ìÅ_x0018_ÂÜÂ_x0005__x0000__x0000_59685_x000D__x0000__x0001__x0004_È¨° _x0000_ìÅ_x0018_ÂÜÂ _x0000_ÈÀ0Ñ\¸ _x0000_2_x0000_5_x0000__x0005__x0000__x0001_(_x0000_àÂ0®Ù³)_x0000__x0014__x0000__x0000_junsoo5376@naver.com_x0003__x0000__x0001_@®_x0000_É_x0018_Â_x0002__x0000__x0001__x0000_¬qÈ_x000E__x0000__x0000_37690004621737_x0006__x0000__x0000_D00527_x000C__x0000__x0001_(_x0000_üÈ)_x0000_tÇÐÅ¤Â¤ÂìÓ Î__x0000_¹Ò_x0010_Ó
+_x0000__x0000_2848100873	_x0000__x0001_(_x0000_üÈ)_x0000_tÇÐÅ¤Â¤ÂìÓ Î_x0003__x0000__x0001__x0015_¼_x0018_Â Ì_x000C__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_ _x0000_µÑàÂ_x0010_Óä¹ÅÅ_x0008__x0000__x0000_20171228_x000C__x0000__x0000_031-763-2002_x000C__x0000__x0000_031-763-0400_x0005__x0000__x0000_12739_x000D__x0000__x0001_½¬0® _x0000__x0011_­üÈÜÂ _x0000_µÑø»\¸ _x0000_9_x0000_2_x0000__x000D__x0000__x0000_010-4085-9292_x0014__x0000__x0000_gysports@hanmail.net_x0008__x0000__x0000_20190725_x000E__x0000__x0000_37690004641137_x0006__x0000__x0000_D00528_x0007__x0000__x0001_2_x0000_0_x0000_8_x0000_0_x0000_Æ%±¤Â
+_x0000__x0000_8131601217_x0003__x0000__x0001_@®ÀÉÐÆ_x000C__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_ _x0000_¤ÂìÓ ÎXÇX¹_x000C__x0000__x0000_061-795-2088_x0008__x0000__x0001__x0004_È|·¨°Ä³ _x0000__x0011_­ÅÜÂ_x0005__x0000__x0000_57767_x0010__x0000__x0001__x0004_È¨° _x0000__x0011_­ÅÜÂ _x0000_ÀÉÙ³8® _x0000_3_x0000_0_x0000_-_x0000_3_x0000_5_x0000__x000D__x0000__x0000_010-9434-2223_x0013__x0000__x0000_3530162@hanmail.net_x0008__x0000__x0000_20190730_x000E__x0000__x0000_37690004643437_x0006__x0000__x0000_D00529	_x0000__x0001_°Æ¬¹¤ÂìÓ Î(_x0000__x0011_­üÈ)_x0000_
+_x0000__x0000_5212100399_x0003__x0000__x0001_$Æ_x0018_ÂÔÆ_x0008__x0000__x0000_20191030_x000C__x0000__x0000_062-434-8963_x0008__x0000__x0001__x0011_­üÈ_x0011_­íÅÜÂ _x0000_½l­_x0005__x0000__x0000_61185_x0018__x0000__x0001__x0011_­üÈ _x0000_½l­ _x0000_¨Ìè²ðÅàÂ\¸ _x0000_2_x0000_9_x0000_¼8® _x0000_1_x0000_5_x0000_ _x0000_ÀÉÁÀ1_x0000_5Î_x000D__x0000__x0001_½l­+ÈiÕ´Ì!Ç_x0000_­ _x0000_´Ì!Ç©ÆÔ_x0010_È_x000D__x0000__x0000_010-4614-9599_x000F__x0000__x0000_19qkqn@daum.net_x000B__x0000__x0000_01046149599_x000D__x0000__x0001_2_x0000_6_x0000_F_x0000_W_x0000_ _x0000_©ÆÔ_x0018_ÂüÈ _x0000_ø»8ÌìÅ_x0008__x0000__x0000_20190802_x000E__x0000__x0000_37690004642837_x0006__x0000__x0000_D00530_x000B__x0000__x0001_àÂàÂ´Ì!Ç¬À _x0000_2_x0000_1_x0000___x0000_¹Ò_x0010_Ó
+_x0000__x0000_1288148960_x000B__x0000__x0001_üÈÝÂÖ¬À _x0000_àÂàÂ´Ì!Ç2_x0000_1_x0000__x0003__x0000__x0001_iÖ¹Â8Ö_x0002__x0000__x0001__x001C_ÈpÈ_x0008__x0000__x0000_20000523
+_x0000__x0000_0319453376
+_x0000__x0000_0319450458_x0005__x0000__x0000_10844_x0013__x0000__x0001_½¬0® _x0000__x000C_ÓüÈÜÂ _x0000_ÔÆq¸tº _x0000_¬_x0014_¼_x0004_Ç8® _x0000_1_x0000_2_x0000_3_x0000__x0006__x0000__x0001_àÂàÂ´Ì!Ç$ÁD¾_x0014__x0000__x0000_sinsin5980@naver.com_x0008__x0000__x0000_20190823_x000E__x0000__x0000_37690004645737_x0006__x0000__x0000_D00534
+_x0000__x0001_2_x0000_0_x0000_1_x0000_9_x0000_ _x0000_TÏ¬¹DÅ$Æ_x0008_Õ
+_x0000__x0000_0000000000	_x0000__x0000_023352551_x0005__x0000__x0000_03964_x000E__x0000__x0001__x001C_Á¸Æ _x0000_È¹ìÓl­ _x0000_ìÓ@Ç\¸ _x0000_1_x0000_2_x0000_0_x0000__x0004__x0000__x0001_U³|ÇL¾)µ_x0008__x0000__x0000_20190918_x0006__x0000__x0000_D00538_x000E__x0000__x0001__x0000_³\Õ¤ÂìÓ Î°ÀÅÅ_x0011_ÖÙ³pÈiÕ__x0000_¹Ò_x0010_Ó
+_x0000__x0000_1168210643_x0003__x0000__x0001_üÈ_x0015_Ö8Ö	_x0000__x0001_´ÆÙ³©Æl­ _x0000__x000F_¼ _x0000_$ÁXÎ_x0008__x0000__x0000_19700319	_x0000__x0000_027867761	_x0000__x0000_027867764_x0005__x0000__x0000_07345_x000E__x0000__x0001__x001C_Á¸Æ _x0000__x0001_Æñ´ìÓl­ _x0000_6_x0000_3_x0000_\¸ _x0000_4_x0000_0_x0000__x0014__x0000__x0001_7_x0000_2_x0000_3_x0000_8Ö _x0000_(_x0000_ìÅXÇÄ³Ù³,_x0000_ _x0000_|·tÇ_x0004_Õ$Æ&lt;Õ¤ÂTÑ)_x0000__x0008__x0000__x0000_20190724_x000E__x0000__x0000_37690004646337_x0006__x0000__x0000_D00539_x000C__x0000__x0001_(_x0000_üÈ)_x0000__x0004_²¬¹ÐÅ¤ÂdÅÀÉ__x0000_¹Ò_x0010_Ó
+_x0000__x0000_2018609461	_x0000__x0001_(_x0000_üÈ)_x0000__x0004_²¬¹ÐÅ¤ÂdÅÀÉ_x0002__x0000__x0001_@®%Æ_x000C__x0000__x0000_031-527-8417_x0005__x0000__x0000_12245_x0015__x0000__x0001_½¬0® _x0000_¨°ÅüÈÜÂ _x0000_½¬_x0015_¬\¸2_x0000_9_x0000_4_x0000_¼8® _x0000_3_x0000_2_x0000_-_x0000_1_x0000__x0008__x0000__x0000_20190626_x000E__x0000__x0000_37690004648637_x0006__x0000__x0000_D00541_x0007__x0000__x0001_íÂtÇ_x0004_¬ÀÉ__x0000_¹Ò_x0010_Ó_x000C__x0000__x0001_¹Ò_x0010_Ó _x0000_p¬· Á _x0000_ÇÜÂ _x0000_ñ´]¸_x000D__x0000__x0000_010-2850-8962_x0003__x0000__x0001_Æ%±¤Â_x0008__x0000__x0000_20191014_x000E__x0000__x0000_37690004647037_x0006__x0000__x0000_D00543	_x0000__x0001_Á¨ºÇè²´Ìõ¼__x0000_¹Ò_x0010_Ó_x0004__x0000__x0001_Ù³¹ÂµÑÁÀ_x0008__x0000__x0000_20191016_x000E__x0000__x0000_37690004674237_x0006__x0000__x0000_D00546_x000B__x0000__x0001_8ÁÄÉ¤ÂìÓ Î)¼ü¬ÄÖ__x0000_¹Ò_x0010_Ó_x0005__x0000__x0000_06964_x000E__x0000__x0001__x001C_Á¸Æ _x0000_Ù³Çl­ _x0000_ÁÀÄ³\¸ _x0000_2_x0000_4_x0000_2_x0000__x0008__x0000__x0000_20191023_x000E__x0000__x0000_37690004649237_x0006__x0000__x0000_D00549	_x0000__x0001_)¼ü¬ÄÖà¬Ç_x0008_Í__x0000_¹Ò_x0010_Ó
+_x0000__x0000_1318303677_x0008__x0000__x0001_xÇÌà¬Ç_x0008_Íñ´YÕP­_x0003__x0000__x0001_@®_x001C_Âl×_x000C__x0000__x0000_032-433-0464	_x0000__x0001_xÇÌ_x0011_­íÅÜÂ _x0000_¨°Ù³l­_x0005__x0000__x0000_21685_x0014__x0000__x0001_xÇÌ _x0000_¨°Ù³l­ _x0000_DÅTÅ_x0000_³\¸1_x0000_5_x0000_0_x0000_3_x0000_¼8® _x0000_4_x0000_8_x0000__x000F__x0000__x0000_gojan@ice.go.kr_x0008__x0000__x0000_20191028_x0006__x0000__x0000_D00550
+_x0000__x0001_TÏ¬¹DÅü»4Ñ¬À·__x0000_¹Ò_x0010_Ó_x0008__x0000__x0000_20191108_x000E__x0000__x0000_37690004650237_x0006__x0000__x0000_D00554	_x0000__x0001_üÈýÅ_x0008_Íñ´YÕP­__x0000_¹Ò_x0010_Ó
+_x0000__x0000_1288302804_x0003__x0000__x0001__x0015_¼	½ Á_x000B__x0000__x0000_0319120031 _x0005__x0000__x0000_10385_x0012__x0000__x0001_½¬0® _x0000_à¬ÅÜÂ _x0000_|Ç°À_x001C_Ál­ _x0000__x0015_¬ Á\¸ _x0000_2_x0000_9_x0000__x0006__x0000__x0001_üÈýÅ_x0008_Íñ´YÕP­_x0008__x0000__x0000_20191118_x0006__x0000__x0000_D00557_x000B__x0000__x0001_üÈÝÂÖ¬À _x0000_tÎxÇÜ´ÉÅtÐÉ
+_x0000__x0000_7318601539_x0003__x0000__x0001_¥Ç¬Ç_x0001_Ö_x0008__x0000__x0000_20191210_x000D__x0000__x0000_010-2600-1460_x0005__x0000__x0000_06065_x000E__x0000__x0001__x001C_Á¸Æ _x0000__x0015_¬¨°l­ _x0000_ Á¹\¸ _x0000_7_x0000_2_x0000_0_x0000__x000E__x0000__x0001_ Ç_x0000_­L¾)µ _x0000_ÀÉXÕ1_x0000_5Î _x0000_ô¼Ü´|·xÇ_x0013__x0000__x0000_paul777@hanmail.net_x0008__x0000__x0000_20200914_x0006__x0000__x0000_D00560	_x0000__x0001_üÈÝÂÖ¬À _x0000__x0014_µÀÉ8ÑÄÉ
+_x0000__x0000_6418600391_x0003__x0000__x0001__x0015_¼¼ Á_x0019__x0000__x0001_ôÎèÔ0Ñ _x0000__x000F_¼ _x0000_üÈÀ¼0®0®,_x0000_ _x0000_´ÆÙ³ _x0000__x000F_¼ _x0000_½¬0®©ÆÔ _x0000_Ä³ä¹ _x0000__x0008__x0000__x0000_20160401_x000B__x0000__x0000_02-707-3326	_x0000__x0000_027038437	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_©Æ°Àl­_x0005__x0000__x0000_04366_x0011__x0000__x0001__x001C_Á¸ÆÜÂ _x0000_Ù³Çl­ _x0000__x0000_³)¼Ù³1_x0000_5_x0000_8® _x0000_3_x0000_0_x0000__x000D__x0000__x0000_010-4722-8308_x0014__x0000__x0000_jin@digitaljin.co.kr_x0005__x0000__x0000_24016_x0003__x0000__x0001_8»=Ì_x0018_Â_x0008__x0000__x0000_20191220_x000E__x0000__x0000_37690004655437_x0017__x0000__x0001_0_x0000_1_x0000_0_x0000_-_x0000_7_x0000_4_x0000_1_x0000_4_x0000_-_x0000_1_x0000_6_x0000_7_x0000_8_x0000_ _x0000_$Ç1ÁÜ­ _x0000_(_x0000_A_x0000_/_x0000_S_x0000_)_x0000__x0006__x0000__x0000_D00563	_x0000__x0001__x0001_ÆÅÅ3_x0000__x0000_Ó0®ÀÐ__x0000_¹Ò_x0010_Ó	_x0000__x0000_023332568_x0008__x0000__x0000_20200101_x0006__x0000__x0000_D00564_x0008__x0000__x0001_ü»4Ñ¤ÂìÓ Î__x0000_¹Ò_x0010_Ó_x0005__x0000__x0001__x001C_¬xÇ¬ÀÅÅÇ
+_x0000__x0000_1013095995_x0005__x0000__x0001_ü»4Ñ¤ÂìÓ Î_x0003__x0000__x0001_à¬_x0015_È%Æ_x0008__x0000__x0000_00000000_x0008__x0000__x0001__x0004_È|·½Ä³ _x0000_à¬=Ìp­_x0005__x0000__x0000_56430_x0012__x0000__x0001__x0004_È½ _x0000_à¬=Ìp­ _x0000_à¬=ÌMÇ _x0000_ÔÆá¬5_x0000_8® _x0000_1_x0000_1_x0000__x0008__x0000__x0000_20200103_x000E__x0000__x0000_37690004654837_x0006__x0000__x0000_D00568_x0007__x0000__x0001_\Õ¤ÂìÓ Î__x0000_¹Ò_x0010_Ó
+_x0000__x0000_3031277167_x0004__x0000__x0001_\Õ¤ÂìÓ Î_x0003__x0000__x0001_iÖ+ÈôÅ_x000D__x0000__x0000_010-5103-6696_x0005__x0000__x0000_27357_x0010__x0000__x0001_©Í½ _x0000_©ÍüÈÜÂ _x0000_Ä¬+º_x0000_³\¸ _x0000_9_x0000_1_x0000_-_x0000_1_x0000__x0005__x0000__x0001_(_x0000_P­_x0004_ÖÙ³)_x0000__x0016__x0000__x0000_archihjy@hometax.go.kr_x0008__x0000__x0000_20200203_x000E__x0000__x0000_37690004658337_x0006__x0000__x0000_D00574_x0006__x0000__x0001_¤Âä¹ñÂ¤ÂìÓ Î
+_x0000__x0000_1238638685_x0003__x0000__x0001_tÇ Ìl×_x0008__x0000__x0001_Ä³Áä¹,_x0000_ _x0000__x001C_ÈpÈÅÅ_x000C__x0000__x0001__x0004_ÈÇÁÀp¬·,_x0000_ _x0000_¤ÂìÓ Î©ÆÔ_x0008__x0000__x0000_20130615
+_x0000__x0000_0314271787_x000B__x0000__x0000_05054271788_x0005__x0000__x0000_15850_x000E__x0000__x0001_½¬0® _x0000_p­ìÓÜÂ _x0000_à¬°À\¸ _x0000_1_x0000_6_x0000_6_x0000__x000F__x0000__x0001_S_x0000_K_x0000_¤¼ðÒÀÆ _x0000_1_x0000_0_x0000_4_x0000_Ù³ _x0000_5_x0000_0_x0000_6_x0000_8Ö_x000D__x0000__x0000_010-3690-1786_x0011__x0000__x0000_4271787@naver.com_x000B__x0000__x0000_07046403943_x0005__x0000__x0000_19022_x0003__x0000__x0001_àÂÙ³ÐÆ_x0008__x0000__x0000_20200220_x000E__x0000__x0000_37690004666837_x0006__x0000__x0000_D00576_x0008__x0000__x0001_1¼È¹¤ÂìÓ Î__x0000_¹Ò_x0010_Ó_x0008__x0000__x0000_20200302_x000E__x0000__x0000_37690004667437_x0006__x0000__x0000_D00578_x0008__x0000__x0001_MÖ1ÁÆ%±¤Â__x0000_¹Ò_x0010_Ó_x0006__x0000__x0001_MÖ1Á _x0000_Æ%±¤Â_x0008__x0000__x0000_20200316_x0005__x0000__x0000_32223_x0016__x0000__x0001_©Í¨° _x0000_MÖ1Áp­ _x0000_MÖ1ÁMÇ _x0000_pÈÅ\¸1_x0000_0_x0000_3_x0000_¼8® _x0000_3_x0000_5_x0000__x000E__x0000__x0000_17-2 17-5 17-6_x000E__x0000__x0000_37690004669737_x0006__x0000__x0000_D00580_x0008__x0000__x0001__x0008_®_x0001_Æ¤ÂìÓ Î__x0000_¹Ò_x0010_Ó_x0005__x0000__x0000_04005_x0010__x0000__x0001__x001C_Á¸Æ _x0000_È¹ìÓl­ _x0000_Ù³P­\¸3_x0000_8® _x0000_1_x0000_2_x0000_5_x0000__x0003__x0000__x0000_205_x0008__x0000__x0000_20200324_x000E__x0000__x0000_37690004671337_x0006__x0000__x0000_D00585_x0008__x0000__x0001_Tº_x0014_µ¬ÀtÇ¸Å__x0000_¹Ò_x0010_Ó
+_x0000__x0000_2102438564_x0005__x0000__x0001_Tº_x0014_µ¬ÀtÇ¸Å_x0003__x0000__x0001__x0015_¼ÌÕÝÂ_x000D__x0000__x0001__x001C_ÁD¾¤Â,_x0000_ _x0000_Ä³ä¹ _x0000__x000F_¼ _x0000_Áä¹ÅÅ_x0010__x0000__x0001_$ÁXÎ_x000F_¼ ÇÀÉô¼_x0018_Â,_x0000_ _x0000_8»l­,_x0000_ _x0000_0®P±Ô_x000B__x0000__x0000_01088813256	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_1ÁÙ³l­_x0005__x0000__x0000_04750_x000F__x0000__x0001__x001C_Á¸Æ _x0000_1ÁÙ³l­ _x0000_à¬°ÀÇ\¸ _x0000_2_x0000_8_x0000_4_x0000__x0018__x0000__x0001_3_x0000_5Î _x0000_3_x0000_0_x0000_1_x0000_8Ö _x0000_6_x0000_1_x0000_äÂ _x0000_(_x0000_Õù²Ù³,_x0000_ _x0000_1ÁÙ³äÀt¹Ý¹)_x0000__x0015__x0000__x0000_eg6753256@hanmail.net_x0008__x0000__x0000_20200525_x000E__x0000__x0000_37690004672037_x0006__x0000__x0000_D00587_x000B__x0000__x0001_üÈÝÂÖ¬À _x0000_°tÇ¤Â(Ó_x0000_¼¬¹
+_x0000__x0000_3658101754_x0003__x0000__x0001__x0015_¼=Ìü»_x000B__x0000__x0001_¤ÂìÓ Î _x0000_©ÆÔ _x0000_Ä³Áä¹ÅÅ_x0008__x0000__x0000_20200407_x000C__x0000__x0000_031-341-8677_x000D__x0000__x0000_031-8068-5999_x0007__x0000__x0001_½¬0®Ä³ _x0000_XÇUÆÜÂ_x0005__x0000__x0000_16011_x000C__x0000__x0001_½¬0® _x0000_XÇUÆÜÂ _x0000_­ÌÄ¬\¸ _x0000_2_x0000__x000D__x0000__x0000_010-7417-4040_x0011__x0000__x0000_cmin401@naver.com_x0008__x0000__x0000_20200602_x000E__x0000__x0000_37690004673637_x0006__x0000__x0000_D00600	_x0000__x0001_Ä³á¬_x0008_Íñ´YÕP­__x0000_¹Ò_x0010_Ó_x0003__x0000__x0001_$Çø»l×_x0003__x0000__x0001_½Ù³°À_x0002__x0000__x0001_Ç_x0000_³	_x0000__x0000_025804577_x0005__x0000__x0000_06205_x0010__x0000__x0001__x001C_Á¸Æ _x0000__x0015_¬¨°l­ _x0000_ Á¹\¸6_x0000_4_x0000_8® _x0000_3_x0000_3_x0000__x0008__x0000__x0001__x001C_Á¸ÆÄ³á¬_x0008_Íñ´YÕP­_x0008__x0000__x0000_20201015_x0006__x0000__x0000_D00602_x000C__x0000__x0001__x001C_Á¸ÆÜÂ0¼Ü´ü»4Ñ_x0011_ÖÖ__x0000_¹Ò_x0010_Ó
+_x0000__x0000_2048204832	_x0000__x0001__x001C_Á¸ÆÜÂ0¼Ü´ü»4Ñ_x0011_ÖÖ_x0003__x0000__x0001__x0015_¼¬ÇXÖ_x000D__x0000__x0000_010-4359-4949_x0004__x0000__x0001_5_x0000_0_x0000_2_x0000_8Ö_x0008__x0000__x0000_20201102_x000E__x0000__x0000_37690004675937_x0006__x0000__x0000_D00605_x000B__x0000__x0001_ÌHÅàÂHÅ_x0008_Íñ´YÕP­__x0000_¹Ò_x0010_Ó
+_x0000__x0000_3128300473_x0003__x0000__x0001_@®_x0015_È`Å_x0008__x0000__x0000_622-7063_x0005__x0000__x0000_31125_x0013__x0000__x0001_©Í¨° _x0000_ÌHÅÜÂ _x0000_Ù³¨°l­ _x0000_ÐÆ1Á2_x0000_5_x0000_8® _x0000_2_x0000_1_x0000__x0008__x0000__x0001_ÌHÅàÂHÅ_x0008_Íñ´YÕP­_x0008__x0000__x0000_20201116_x0006__x0000__x0000_D00608_x000E__x0000__x0001_(_x0000_üÈ)_x0000_ _x0000__x0018_±¼ÐÆ¤ÂìÓ Î(_x0000_T_x0000_S_x0000_)_x0000__x0008__x0000__x0000_20210107_x0005__x0000__x0000_38661_x000E__x0000__x0001_½¬½ _x0000_½¬°ÀÜÂ _x0000_½¬°À\¸ _x0000_2_x0000_4_x0000_3_x0000__x000B__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_2_x0000_4_x0000__x000E__x0000__x0000_37690004676537_x0006__x0000__x0000_D00609	_x0000__x0001__x0008_®_x0001_Æ¤ÂìÓ Î(_x0000_T_x0000_S_x0000_)_x0000_$_x0000__x0001_2_x0000_4_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_4_x0000_0_x0000_ _x0000_/_x0000__x0001_ÆÅÅ¬ÀÐÆ _x0000_Æ­Ì(_x0000_¥Ç0® _x0000_ø»p¬·,_x0000_ _x0000__x0018_Â_x0008_® _x0000_½tÇÕ)_x0000__x000E__x0000__x0000_37690004677137_x0006__x0000__x0000_D00610	_x0000__x0001_XÕD¾¤ÂìÓ Î(_x0000_T_x0000_S_x0000_)_x0000__x0016__x0000__x0000_daegu-daejin@naver.com_x000F__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_4_x0000_0_x0000_+_x0000_5_x0000_0_x0000__x000E__x0000__x0000_37690004678837_x0006__x0000__x0000_D00611	_x0000__x0001_1¼È¹¤ÂìÓ Î(_x0000_T_x0000_S_x0000_)_x0000__x0005__x0000__x0000_04011_x000F__x0000__x0001__x001C_Á¸Æ _x0000_È¹ìÓl­ _x0000_Ù³P­\¸9_x0000_8® _x0000_9_x0000_5_x0000__x0010__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_7_x0000_0_x0000_+_x0000_1_x0000_8_x0000_5_x0000__x000E__x0000__x0000_37690004679437_x0006__x0000__x0000_D00612_x000D__x0000__x0001_¼À1Á¤ÂìÓ Î(_x0000_8»½¬)_x0000_(_x0000_T_x0000_S_x0000_)_x0000__x0005__x0000__x0000_36956_x000E__x0000__x0001_½¬½ _x0000_8»½¬ÜÂ _x0000_¨º_x0004_È\¸ _x0000_1_x0000_4_x0000_6_x0000_V_x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_0_x0000_+_x0000_6_x0000_ _x0000_/_x0000_ _x0000_2_x0000_5_x0000_S_x0000_S_x0000_ _x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_0_x0000_ _x0000_/_x0000_ _x0000_ _x0000_2_x0000_4_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_5_x0000_ _x0000_/_x0000_ _x0000_2_x0000_4_x0000_S_x0000_S_x0000__x0018_ÂüÈìÅàÂ _x0000_5_x0000_ _x0000_/_x0000_ _x0000_2_x0000_3_x0000_F_x0000_W_x0000_ _x0000__x0018_ÂüÈ _x0000_ìÅàÂ _x0000_1_x0000_0_x0000_ _x0000_/_x0000_ _x0000_2_x0000_3_x0000_S_x0000_S_x0000_ _x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_0_x0000__x000E__x0000__x0000_37690004680437_x0006__x0000__x0000_D00614_x0008__x0000__x0001__x0001_ÆÅÅ4_x0000__x0000_ÓÇXÇä¹¥Ç_x000B__x0000__x0000_02-335-2551_x0008__x0000__x0000_20210115_x0006__x0000__x0000_D00616_x0005__x0000__x0001_8Á_x0001_Æ¤ÂìÓ Î
+_x0000__x0000_8055100483_x0005__x0000__x0001_¤ÂìÓ ÎXÇX¹_x0008__x0000__x0000_20210125_x000D__x0000__x0000_070-8808-8799_x0017__x0000__x0000_yonexsejinspo@naver.com_x000E__x0000__x0000_37690004683337_x0006__x0000__x0000_D00620_x000D__x0000__x0001_üÈÝÂÖ¬À _x0000_8ÁÄÉ¤ÂìÓ Î__x0000_è²Å³
+_x0000__x0001_X_x0000_7_x0000_ _x0000_è²Å³¨ºx³ _x0000_TÏÜ´_x0008__x0000__x0000_20210226_x000E__x0000__x0000_37690004684037_x0006__x0000__x0000_D00621_x000E__x0000__x0001_¬À$Á´Ì!Ç_x0000_­(_x0000__x000C_Õ_x0008_¸tÇ(Æ)_x0000___x0000_¹Ò_x0010_Ó
+_x0000__x0000_7820601928_x0004__x0000__x0001__x000C_Õ_x0008_¸tÇ(Æ_x0003__x0000__x0001_\ÍÑ¼ÅÆ_x0008__x0000__x0001_0¼Ü´ü»4ÑtÐý·´Æ_x0001_Æ_x0008__x0000__x0000_20210305_x000D__x0000__x0000_010-4343-5610_x0005__x0000__x0000_31234_x0017__x0000__x0001_©Í¨° _x0000_ÌHÅÜÂ _x0000_Ù³¨°l­ _x0000_©ºÌMÇ _x0000_1Á¨°\¸ _x0000_3_x0000_9_x0000_-_x0000_1_x0000__x0010__x0000__x0000_cbw007@naver.com_x000E__x0000__x0000_37690004685637_x0006__x0000__x0000_D00626_x000B__x0000__x0001__x0018_ÂÐÆ¥ÇHÅà¬ñ´YÕP­__x0000_¹Ò_x0010_Ó
+_x0000__x0000_1358302549_x0006__x0000__x0001_¥ÇHÅà¬ñ´YÕP­_x0003__x0000__x0001_ ÇtÕ·_x0004__x0000__x0001_½Ù³°ÀÅÅ_x0008__x0000__x0000_20210324_x000C__x0000__x0000_031-250-2901_x0007__x0000__x0001_½¬0®Ä³ _x0000__x0018_ÂÐÆÜÂ_x0005__x0000__x0000_16316_x0015__x0000__x0001_½¬0® _x0000__x0018_ÂÐÆÜÂ _x0000_¥ÇHÅl­ _x0000__x0000_³ÉÓ\¸5_x0000_2_x0000_¼8® _x0000_1_x0000_2_x0000__x0013__x0000__x0000_jangan5955@korea.kr_x000E__x0000__x0000_37690004686237_x0006__x0000__x0000_D00628_x0007__x0000__x0001_Æ%±¤Â _x0000__x0018_ÂÐÆ_x0010_È
+_x0000__x0000_4401101673_x0003__x0000__x0001__x0015_¼°_x0004_Ö_x000B__x0000__x0001_¤ÂìÓ Î©Æ _x0000_XÇX¹,_x0000_ _x0000_©ÆÔ_x0008__x0000__x0000_20210407_x000C__x0000__x0000_031-216-4009_x0005__x0000__x0000_16540_x0010__x0000__x0001_½¬0® _x0000__x0018_ÂÐÆÜÂ _x0000__x0001_ÆµÑl­ _x0000_ä¹ÐÆ\¸ _x0000_3_x0000__x000D__x0000__x0000_010-2888-3600_x0011__x0000__x0000_yonexsw@naver.com_x000E__x0000__x0000_37690004687937_x0006__x0000__x0000_D00631_x000C__x0000__x0001__x0011_É·l­0¼Ü´ü»4Ñ_x0011_ÖÖ__x0000_¹Ò_x0010_Ó_x0008__x0000__x0000_20210510_x0006__x0000__x0000_D00632_x0008__x0000__x0001_©ÆÔ¬ÀÅÅ½ _x0000_A_x0000_S_x0000__x0003__x0000__x0001_@® ÌÅÆ_x000B__x0000__x0000_02-335-8077_x0008__x0000__x0000_20210601_x0006__x0000__x0000_D00638_x000D__x0000__x0001_p¬1Á¤ÂìÓ Î(_x0000_HÅÙ³)_x0000_(_x0000_T_x0000_S_x0000_)_x0000__x0008__x0000__x0000_20210622_x000F__x0000__x0001_½¬½ _x0000_HÅÙ³ÜÂ _x0000_½¬½_x0000_³\¸ _x0000_4_x0000_1_x0000_8_x0000__x0018__x0000__x0001_(_x0000_%ÆÙ³,_x0000_ _x0000_LÑÈ¹_x0004_Õ|·Ç)_x0000_Æ%±¤Â _x0000_p¬1Á¤ÂìÓ Î(_x0000_HÅÙ³)_x0000__x0012__x0000__x0000_klcjjh@lycos.co.kr_x000E__x0000__x0000_37690004688537_x0006__x0000__x0000_D00640_x0005__x0000__x0001__x0014_¼x¹¤ÂìÓ Î
+_x0000__x0000_1313599978_x0006__x0000__x0001__x0014_¼x¹ _x0000_¤ÂìÓ Î_x0003__x0000__x0001_tÇ¬Ç_x0001_Æ_x0007__x0000__x0001_Áä¹ÅÅ,_x0000_Ä³ä¹ÅÅ_x0008__x0000__x0000_20210715_x000C__x0000__x0000_032-466-1365_x0005__x0000__x0000_21543_x000E__x0000__x0001_xÇÌ _x0000_¨°Ù³l­ _x0000_1¼¼\¸ _x0000_1_x0000_3_x0000_9_x0000_
+_x0000__x0001_Æ%±¤Â _x0000__x0014_¼x¹ _x0000_¤ÂìÓ Î_x000D__x0000__x0000_010-8872-9764_x0017__x0000__x0000_hangang6528@hanmail.net_x000E__x0000__x0000_37690004689137_x0006__x0000__x0000_D00641_x0004__x0000__x0001_$±¼·Ü´
+_x0000__x0000_1292781688_x0003__x0000__x0001_@®e×-Á_x0013__x0000__x0001__x0004_ÈÇÁÀp¬·ÅÅ,_x0000_ _x0000_¤ÂìÓ Î©ÆÔ,_x0000_ _x0000_ìÕ¤Â©ÆÔ_x0008__x0000__x0000_20210730_x000C__x0000__x0000_031-742-4404_x0005__x0000__x0000_13134_x0013__x0000__x0001_½¬0® _x0000_1Á¨°ÜÂ _x0000__x0018_Â_x0015_Èl­ _x0000_°À1Á_x0000_³\¸ _x0000_5_x0000_</v>
+          </cell>
+          <cell r="Q37" t="e">
+            <v>#N/A</v>
           </cell>
           <cell r="R37" t="str">
             <v/>
           </cell>
-          <cell r="S37" t="str">
-            <v>010-4733-3541</v>
-          </cell>
-          <cell r="T37" t="str">
-            <v>coolcomy1982@naver.com</v>
+          <cell r="S37" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="T37" t="e">
+            <v>#N/A</v>
           </cell>
           <cell r="U37" t="str">
             <v/>
@@ -4567,7 +5446,7 @@
             <v/>
           </cell>
           <cell r="Z37" t="str">
-            <v>051-202-3541</v>
+            <v>온리스포츠 배드민턴센터</v>
           </cell>
           <cell r="AA37" t="str">
             <v>N</v>
@@ -4586,11 +5465,91 @@
           </cell>
         </row>
         <row r="38">
-          <cell r="B38" t="str">
-            <v>D00087</v>
+          <cell r="B38" t="e">
+            <v>#N/A</v>
           </cell>
           <cell r="C38" t="str">
-            <v>주식회사 세진스포츠</v>
+            <v>8385_x0013__x0000__x0000_judocjl@hanmail.net_x000E__x0000__x0000_37690004490537_x0006__x0000__x0000_D00109_x0008__x0000__x0001__x0001_Æ¤ÂìÓ Î(_x0000_¨°ÐÆ)_x0000_
+_x0000__x0000_1095289131_x0003__x0000__x0001_tÇ_x0015_ÈÌ_x0008__x0000__x0000_20071119_x000C__x0000__x0000_063-632-4154
+_x0000__x0000_0636324156_x0005__x0000__x0000_55703_x0015__x0000__x0001__x0004_È|·½Ä³ _x0000_¨°ÐÆÜÂ _x0000_¬Àä¹tº _x0000__x0000_³¬À\¸ _x0000_1_x0000_2_x0000_8_x0000_3_x0000__x0004__x0000__x0001__x0001_Æ¤ÂìÓ Î_x000D__x0000__x0000_010-4594-0634_x0013__x0000__x0000_jclee8734@naver.com_x000E__x0000__x0000_37690004497037_x0006__x0000__x0000_D00110_x0007__x0000__x0001_Æ%±¤Â _x0000_TÖ_x001C_Â_x0010_È
+_x0000__x0000_4080577085_x0003__x0000__x0001__x0004_È+º_x0019_Â_x0008__x0000__x0000_20071102_x000C__x0000__x0000_061-375-6647_x0008__x0000__x0001__x0004_È|·¨°Ä³ _x0000_TÖ_x001C_Âp­_x0006__x0000__x0000_519809_x0014__x0000__x0001__x0004_È|·¨°Ä³ _x0000_TÖ_x001C_Âp­ _x0000__x0011_­U³\¸ _x0000_1_x0000_4_x0000_0_x0000_ _x0000_ _x0000_1_x0000_5Î_x000D__x0000__x0000_010-6632-5893_x0012__x0000__x0000_ms-jon@hanmeil.net_x000E__x0000__x0000_37690004498637_x0006__x0000__x0000_D00111_x000C__x0000__x0001_,Æ¼¹=Õ+ÈiÕ¤ÂìÓ Î(_x0000_©ºìÓ)_x0000_
+_x0000__x0000_4111469486_x0003__x0000__x0001_@®=Ì©Æ_x000C__x0000__x0001_´ÆÙ³©ÆÔ,_x0000_ñ´°Àl­,_x0000_0®P±Ô_x0008__x0000__x0000_20070320_x000C__x0000__x0000_061-242-1032
+_x0000__x0000_0612443032_x0008__x0000__x0001__x0004_È|·¨°Ä³ _x0000_©ºìÓÜÂ_x0005__x0000__x0000_58726_x0010__x0000__x0001__x0004_È¨° _x0000_©ºìÓÜÂ _x0000_(Ì¼_x001D_Á8® _x0000_4_x0000_1_x0000_-_x0000_1_x0000__x0002__x0000__x0001_1_x0000_5Î_x000D__x0000__x0000_010-9243-4285_x0010__x0000__x0000_eyebono@daum.net_x000E__x0000__x0000_37690004499237_x0006__x0000__x0000_D00116_x000F__x0000__x0001_Æ%±¤ÂÈ¹°À_x0000_³¬¹_x0010_È(_x0000_ü»4Ñ¤ÂìÓ Î)_x0000_
+_x0000__x0000_6080288027_x0003__x0000__x0001_ Ç_x0001_Æ_x0019_Â_x0008__x0000__x0001_¤ÂìÓ Î©ÆÔ_x000F_¼XÇX¹_x000C__x0000__x0000_055-222-5431
+_x0000__x0000_0552225432_x0008__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_=ÌÐÆÜÂ_x0006__x0000__x0000_631852_x0018__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_=ÌÐÆÜÂ _x0000_È¹°ÀiÕìÓl­ _x0000_©ÆÈ¹\¸ _x0000_7_x0000_6_x0000_ _x0000_üÈÝÐ_x000D__x0000__x0000_010-3707-6245_x0016__x0000__x0000_dudtjs6245@hanmail.net_x000E__x0000__x0000_37690004504337_x0006__x0000__x0000_D00120_x0006__x0000__x0001_Æ%±¤Â­ÌüÈ_x0010_È
+_x0000__x0000_3170385854_x0003__x0000__x0001_\Í°Æ1Á_x000B__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_XÇX¹,_x0000__x0018_Ât¬_x0008__x0000__x0000_20110729_x000C__x0000__x0000_043-222-3040
+_x0000__x0000_0432245050_x0008__x0000__x0001_©Í­Ì½Ä³ _x0000_­ÌüÈÜÂ_x0006__x0000__x0000_361842_x0012__x0000__x0001_©Í½ _x0000_­ÌüÈÜÂ _x0000_ÁÀù²l­ _x0000_8Öø»\¸ _x0000_2_x0000_0_x0000_6_x0000__x0005__x0000__x0001_1_x0000_5Î _x0000_È!Î_x000D__x0000__x0000_010-5468-3319_x0015__x0000__x0000_wsung3525@hanmail.net_x0008__x0000__x0000_20080429_x000E__x0000__x0000_37690004507237_x0006__x0000__x0000_D00121_x000D__x0000__x0001_Æ%±¤ÂìÓmÕ_x0010_È(_x0000_XÕtÇlÐ¬¹´Å)_x0000_
+_x0000__x0000_5061736246_x0003__x0000__x0001__x0015_È@Ç_x0001_Æ_x0008__x0000__x0000_20090227_x000C__x0000__x0000_054-283-5234
+_x0000__x0000_0542835231_x0008__x0000__x0001_½¬ÁÀ½Ä³ _x0000_ìÓmÕÜÂ_x0006__x0000__x0000_790822_x0012__x0000__x0001_½¬½ _x0000_ìÓmÕÜÂ _x0000_¨°l­ _x0000__x0000_³Ä³Ù³ _x0000_8_x0000_6_x0000_-_x0000_2_x0000__x000D__x0000__x0000_010-4133-7770_x0014__x0000__x0000_minton1125@naver.com_x0008__x0000__x0000_20081105_x000E__x0000__x0000_37690004508937_x0006__x0000__x0000_D00122_x0005__x0000__x0001_°Æ¬¹¤ÂìÓ Î
+_x0000__x0000_4172105493_x0003__x0000__x0001__x0015_¼_x0018_ÂÄÉ_x0008__x0000__x0000_20180101_x000C__x0000__x0000_051-632-2681
+_x0000__x0000_0516322681_x0008__x0000__x0001_½°À_x0011_­íÅÜÂ _x0000_¨°l­_x0006__x0000__x0000_608827_x0011__x0000__x0001_½°À_x0011_­íÅÜÂ _x0000_¨°l­ _x0000_Ç ÇÉÓTÖ\¸ _x0000_4_x0000_9_x0000__x000D__x0000__x0000_010-2594-2682_x0015__x0000__x0000_moxie2000@hanmail.net_x000E__x0000__x0000_37690004509537_x0006__x0000__x0000_D00123_x0005__x0000__x0001_°Æ1Á¤ÂìÓ Î
+_x0000__x0000_2077003708_x0003__x0000__x0001_@®DÆÝÂ_x0008__x0000__x0000_20071009_x000B__x0000__x0000_02-465-1297	_x0000__x0000_024651197	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x0011_­ÄÉl­_x0006__x0000__x0000_143961_x0010__x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x0011_­ÄÉl­ _x0000_l­XÇ\¸ _x0000_6_x0000_6_x0000__x0014__x0000__x0001_1_x0000_5Î _x0000_(_x0000_l­XÇÙ³ _x0000_2_x0000_2_x0000_7_x0000_-_x0000_6_x0000_)_x0000_ _x0000_°Æ1Á¤ÂìÓ Î_x000D__x0000__x0000_010-3418-1230_x000F__x0000__x0000_ws418@naver.com_x000E__x0000__x0000_37690004510537_x0006__x0000__x0000_D00126_x0005__x0000__x0001_ÐÆÙ³´Ì!Ç¬À
+_x0000__x0000_3060363748_x0003__x0000__x0001_ü»Ñ¼ÁÉ_x0004__x0000__x0001_´ÆÙ³0®l­_x0008__x0000__x0000_20050705_x000C__x0000__x0000_042-531-4004
+_x0000__x0000_0425328899_x0008__x0000__x0001__x0000_³_x0004_È_x0011_­íÅÜÂ _x0000_Ù³l­_x0005__x0000__x0000_34630_x000D__x0000__x0001__x0000_³_x0004_È _x0000_Ù³l­ _x0000__x0000_³_x0004_È\¸ _x0000_7_x0000_6_x0000_5_x0000__x000D__x0000__x0000_010-5453-9536_x0012__x0000__x0000_wonspo@hanmail.net_x0008__x0000__x0000_20080214_x000E__x0000__x0000_37690004511137_x0006__x0000__x0000_D00127_x0008__x0000__x0001_ÐÆ¤ÂìÓ Î(_x0000__x001C_ÈüÈ)_x0000_
+_x0000__x0000_6160962051_x0003__x0000__x0001_@®ø»½¬_x000C__x0000__x0000_064-752-4422
+_x0000__x0000_0647232992_x000C__x0000__x0001__x001C_ÈüÈ¹ÒÄ¼ÇXÎÄ³ _x0000__x001C_ÁÀ­ìÓÜÂ_x0006__x0000__x0000_690161_x0013__x0000__x0001__x001C_ÈüÈ¹ÒÄ¼ÇXÎÄ³ _x0000__x001C_ÈüÈÜÂ _x0000_$Æ|·\¸ _x0000_1_x0000_3_x0000_4_x0000__x000D__x0000__x0000_010-4416-4412_x0015__x0000__x0000_crony0104@hanmail.net_x000E__x0000__x0000_37690004512837_x0006__x0000__x0000_D00132_x0005__x0000__x0001__x0004_ÈüÈÆ%±¤Â
+_x0000__x0000_4020887887_x0003__x0000__x0001_tÇ_x001C_Â+È_x000C__x0000__x0000_063-274-9337
+_x0000__x0000_0632789337_x0008__x0000__x0001__x0004_È|·½Ä³ _x0000__x0004_ÈüÈÜÂ_x0006__x0000__x0000_560080_x0013__x0000__x0001__x0004_È|·½Ä³ _x0000__x0004_ÈüÈÜÂ _x0000_DÆ°Àl­ _x0000_õ¬½\¸ _x0000_2_x0000_0_x0000__x000D__x0000__x0000_010-9224-8391_x0010__x0000__x0000_jyonex@naver.com_x000E__x0000__x0000_37690004516337_x0006__x0000__x0000_D00136_x0005__x0000__x0001__x001C_È|Ç¤ÂìÓ Î
+_x0000__x0000_4040533542_x000B__x0000__x0001__x001C_È|Ç_x0008_¸_x0000_È¤ÂìÓ Î(_x0000__x0015_ÈMÇ)_x0000__x0003__x0000__x0001_@®_x0011_­õ¼	_x0000__x0001_´ÆÙ³0®l­_x000F_¼´ÆÙ³õ¼xÆ_x000C__x0000__x0000_063-535-9146
+_x0000__x0000_0635332093_x0008__x0000__x0001__x0004_È|·½Ä³ _x0000__x0015_ÈMÇÜÂ_x0006__x0000__x0000_580804_x000F__x0000__x0001__x0004_È|·½Ä³ _x0000__x0015_ÈMÇÜÂ _x0000__x0011_ÉYÅ\¸ _x0000_8_x0000_3_x0000__x000D__x0000__x0000_010-9579-7800_x0016__x0000__x0000_sports9146@hanmaIl.net_x000E__x0000__x0000_37690004520237_x0006__x0000__x0000_D00137_x000B__x0000__x0001_üÈÝÂÖ¬À _x0000_0¼Ü´ü»4ÑÈ¹¸Ò
+_x0000__x0000_1108193203_x0003__x0000__x0001__x0015_ÈtÇ@±_x000B__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000__x0004_ÈÇÁÀp¬·_x0008__x0000__x0000_20130723_x000C__x0000__x0000_031-964-3530	_x0000__x0000_023829555_x0007__x0000__x0001_½¬0®Ä³ _x0000_à¬ÅÜÂ_x0005__x0000__x0000_10564_x0011__x0000__x0001_½¬0® _x0000_à¬ÅÜÂ _x0000_U³Ål­ _x0000_¼À¡Á\¸ _x0000_1_x0000_2_x0000__x0007__x0000__x0001_4_x0000_5Î _x0000_4_x0000_1_x0000_8_x0000_8Ö_x000D__x0000__x0000_010-7152-7538_x0014__x0000__x0000_mintonmart@naver.com_x000E__x0000__x0000_37690004521937_x0006__x0000__x0000_D00138	_x0000__x0001_üÈÝÂÖ¬ÀÙ³°Æ¤ÂìÓ Î
+_x0000__x0000_1108180426_x0003__x0000__x0001_¡Á_x0015_È|Ç_x000B__x0000__x0000_02-382-3598	_x0000__x0000_023553586	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_@ÇÉÓl­_x0006__x0000__x0000_122903_x0018__x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_@ÇÉÓl­ _x0000_ðÅ_x001C_Á\¸ _x0000_2_x0000_9_x0000_-_x0000_1_x0000_ _x0000_Ù³°Æ¤ÂìÓ Î_x000D__x0000__x0000_010-2018-3598_x0012__x0000__x0000_dvip1233@naver.com_x000B__x0000__x0000_01074353598
+_x0000__x0001__x0018_Â_x0008_® _x0000_½qÈ&lt;Ç\¸ _x0000_µÑ_x001C_È_x000E__x0000__x0000_37690004522537_x0006__x0000__x0000_D00141	_x0000__x0001__x0011_ÉYÅ¤ÂìÓ Î(_x0000_½¬üÈ)_x0000_
+_x0000__x0000_3226600323_x0003__x0000__x0001_iÖ_x0001_ÆäÂ_x0008__x0000__x0000_20081210_x000C__x0000__x0000_054-741-5177_x0008__x0000__x0001_½¬ÁÀ½Ä³ _x0000_½¬üÈÜÂ_x0006__x0000__x0000_780943_x0012__x0000__x0001_½¬ÁÀ½Ä³ _x0000_½¬üÈÜÂ _x0000__x0008_®1Á\¸ _x0000_2_x0000_9_x0000_4_x0000_-_x0000_1_x0000__x000D__x0000__x0000_010-7579-5177_x0014__x0000__x0000_jasp6304@hanmail.net_x0008__x0000__x0000_20081211_x000E__x0000__x0000_37690004525437_x0006__x0000__x0000_D00145_x0005__x0000__x0001_­Ìá¸¤ÂìÓ Î
+_x0000__x0000_6150796307_x0003__x0000__x0001_pÈø»_x0019_Â_x0008__x0000__x0000_20101004_x000C__x0000__x0000_055-312-9559
+_x0000__x0000_0553129560_x0008__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_@®tÕÜÂ_x0006__x0000__x0000_621833_x0012__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_@®tÕÜÂ _x0000_¥Ç Ç\¸ _x0000_2_x0000_9_x0000_7_x0000_-_x0000_5_x0000__x000D__x0000__x0000_010-9513-9559_x0016__x0000__x0000_jms3129559@hanmail.net_x0008__x0000__x0000_20101019_x000E__x0000__x0000_37690004530037_x0006__x0000__x0000_D00148_x0007__x0000__x0001__x0000_ÏtÇdÅD¾¤ÂìÓ Î
+_x0000__x0000_1232481068_x0003__x0000__x0001__x0015_¼+ºÇ_x000C__x0000__x0000_031-457-8706
+_x0000__x0000_0314578707_x0007__x0000__x0001_½¬0®Ä³ _x0000_HÅÅÜÂ_x0006__x0000__x0000_431837_x0012__x0000__x0001_½¬0®Ä³ _x0000_HÅÅÜÂ _x0000_Ù³HÅl­ _x0000_À­xÇ\¸ _x0000_8_x0000_9_x0000__x000D__x0000__x0000_010-7338-7375_x0016__x0000__x0000_jamjali200@hanmail.net_x000E__x0000__x0000_37690004532237_x0006__x0000__x0000_D00149	_x0000__x0001_TÏ¬¹DÅ$Æ_x0008_Õ(_x0000_@®Ì)_x0000_
+_x0000__x0000_5100147324_x0003__x0000__x0001__x0015_¼ Á_x0001_Æ_x0008__x0000__x0000_20070423_x000C__x0000__x0000_054-430-7007
+_x0000__x0000_0544307007_x0008__x0000__x0001_½¬ÁÀ½Ä³ _x0000_@®ÌÜÂ_x0005__x0000__x0000_39626_x000E__x0000__x0001_½¬½ _x0000_@®ÌÜÂ _x0000_¡Á$Á\¸ _x0000_1_x0000_6_x0000_4_x0000__x000D__x0000__x0000_010-4115-6306_x0013__x0000__x0000_jj10654@hanmail.net_x000E__x0000__x0000_37690004533937_x0006__x0000__x0000_D00150_x0005__x0000__x0001__x0014_Ól­¤ÂìÓ Î
+_x0000__x0000_5020153204_x0003__x0000__x0001_àÂÁÀÜ­_x0008__x0000__x0000_20080331_x000C__x0000__x0000_053-957-8989
+_x0000__x0000_0539432345_x0008__x0000__x0001__x0000_³l­_x0011_­íÅÜÂ _x0000_Ù³l­_x0005__x0000__x0000_41193_x000F__x0000__x0001__x0000_³l­ _x0000_Ù³l­ _x0000_DÅÅ\¸1_x0000_1_x0000_8® _x0000_8_x0000_1_x0000__x0008__x0000__x0001_1_x0000_5Î _x0000__x0014_Ól­¤ÂìÓ Î_x000D__x0000__x0000_010-8854-8989_x0012__x0000__x0000_89sports@naver.com_x000E__x0000__x0000_37690004534537_x0006__x0000__x0000_D00159_x0005__x0000__x0001__x001C_Ö1Á¤ÂìÓ Î
+_x0000__x0000_1300531089_x0003__x0000__x0001_tÇXÇ Á_x000D__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000__x0000_¬_x0004_È_x001C_ÈÔ,_x0000_¡ÇTÖ_x0008__x0000__x0000_20070529_x000C__x0000__x0000_032-654-2133
+_x0000__x0000_0326542132_x0007__x0000__x0001_½¬0®Ä³ _x0000_½ÌÜÂ_x0006__x0000__x0000_422819 _x0000__x0001_½¬0®Ä³ _x0000_½ÌÜÂ _x0000_Á¬Àl­ _x0000_½¬xÇ\¸1_x0000_2_x0000_0_x0000_¼8® _x0000_2_x0000_8_x0000_ _x0000_ _x0000_1_x0000_5Î_x0010_ÈìÓ _x0000_1_x0000_xÎ_x000D__x0000__x0000_010-7578-7740_x0015__x0000__x0000_hs7167741@hanmail.net_x000E__x0000__x0000_37690004541337_x0006__x0000__x0000_D00160_x0005__x0000__x0001_8ÖÙ³¤ÂìÓ Î
+_x0000__x0000_1243919047_x0003__x0000__x0001_@®8ÖÙ³_x0008__x0000__x0000_20100113_x000C__x0000__x0000_031-375-0331
+_x0000__x0000_0313750331_x0007__x0000__x0001_½¬0®Ä³ _x0000_$Æ°ÀÜÂ_x0006__x0000__x0000_447802_x001A__x0000__x0001_½¬0®Ä³ _x0000_$Æ°ÀÜÂ _x0000_1Á8Ö_x0000_³\¸ _x0000_2_x0000_5_x0000_ _x0000_´Æ°ÀL¾)µ _x0000_ _x0000_1_x0000_5Î _x0000_4_x0000__x000D__x0000__x0000_010-5295-8278_x0013__x0000__x0000_khd9982@hanmail.net_x000E__x0000__x0000_37690004542037_x0006__x0000__x0000_D00161_x0005__x0000__x0001_MÖ1ÁÆ%±¤Â
+_x0000__x0000_3100640518_x0003__x0000__x0001_@®_x0004_Ö_x0015_È_x0008__x0000__x0000_20090616_x000C__x0000__x0000_041-634-7327_x0008__x0000__x0001_©Í­Ì¨°Ä³ _x0000_MÖ1Áp­_x0005__x0000__x0000_32263_x0012__x0000__x0001_©Í¨° _x0000_MÖ1Áp­ _x0000_MÖ½MÇ _x0000_©Í¨°_x0000_³\¸ _x0000_3_x0000_6_x0000__x0015__x0000__x0001__x001C_È _x0000_1_x0000_5Î _x0000__x001C_È _x0000_1_x0000_0_x0000_1_x0000_8Ö(_x0000_L¾dÅT³¤Â$Æ&lt;Õ¤ÂTÑ)_x0000__x000D__x0000__x0000_010-8626-9825_x0010__x0000__x0000_hji923@naver.com_x000E__x0000__x0000_37690004543637_x0006__x0000__x0000_D00166_x000C__x0000__x0001_(_x0000_üÈ)_x0000_ðÒ_x001C_ÈtÇ_x0014_µ¤Â¸Ò¬¹ð½XÁ
+_x0000__x0000_2118732516_x0003__x0000__x0001_¡ÁÁÀÐÆ_x0006__x0000__x0001_Ä³Áä¹ _x0000_Ä³ä¹_x0008__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_4»íÅ_x0008__x0000__x0000_20120911_x000B__x0000__x0000_02-511-5114	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x0015_¬¨°l­_x0006__x0000__x0000_135010_x000B__x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ_x0015_¬¨°l­|±_x0004_ÖÙ³_x000E__x0000__x0001__x0008_®@ÇL¾)µ _x0000_1_x0000_5Î _x0000_ ¼¤Â¸Ò¤Â Ñ´Å_x000D__x0000__x0000_010-8784-1651_x0015__x0000__x0000_bestextreme@naver.com_x0007__x0000__x0001_B_x0000_ñ´	®(_x0000_T_x0000_S_x0000_)_x0000__x0005__x0000__x0000_14049_x0003__x0000__x0001__x0015_¼_x0004_ÖÄÉ_x0008__x0000__x0000_20190917_x0006__x0000__x0000_D00167_x0008__x0000__x0001_üÈÝÂÖ¬À _x0000_ÐÆÐÅÇ
+_x0000__x0000_1268800066_x0003__x0000__x0001_@®DÕ¹Â_x0006__x0000__x0001_Ä³Áä¹ÅÅ _x0000_xÆ_x0007__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_xÆ_x000C__x0000__x0000_02-1644-1662	_x0000__x0001_½°À_x0011_­íÅÜÂ _x0000__x0018_Â_x0001_Æl­_x0006__x0000__x0000_613815_x0013__x0000__x0001_½°À_x0011_­íÅÜÂ _x0000__x0018_Â_x0001_Æl­ _x0000__x0011_­¨°\¸ _x0000_6_x0000_3_x0000_ _x0000_B_x0000_Ù³_x0004__x0000__x0001_4_x0000_5Î|Ç½_x000D__x0000__x0000_010-8882-4137_x0014__x0000__x0000_oneeight@hanmail.net_x0006__x0000__x0000_D00173_x0005__x0000__x0001__x0008_®_x0001_Æ¤ÂìÓ Î
+_x0000__x0000_1052087391_x0003__x0000__x0001_°ÆÀÉÐÆ_x0008__x0000__x0000_20140217_x000D__x0000__x0000_010-6208-8112_x0006__x0000__x0000_121889_x0013__x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_È¹ìÓl­ _x0000_Ù³P­\¸3_x0000_8® _x0000_1_x0000_2_x0000_5_x0000__x0013__x0000__x0000_yonex0901@naver.com_x0008__x0000__x0000_20150122_x000E__x0000__x0000_37690004557937_x0006__x0000__x0000_D00181_x0004__x0000__x0001__x0000_É¤ÂìÓ Î
+_x0000__x0000_1410240836_x0003__x0000__x0001__x0015_¼½¬·_x0008__x0000__x0000_20140825_x000C__x0000__x0000_031-945-2007_x0007__x0000__x0001_½¬0®Ä³ _x0000__x000C_ÓüÈÜÂ_x0006__x0000__x0000_413819$_x0000__x0001_½¬0®Ä³ _x0000__x000C_ÓüÈÜÂ _x0000_DÅ¬¹·\¸ _x0000_5_x0000_5_x0000_ _x0000_-_x0000_8_x0000_1_x0000_ _x0000_(_x0000__x0008_®_x000C_ÍÙ³,_x0000_ _x0000__x000C_ÓüÈ_x0008_®_x000C_ÍXÕ_x0018_ÂÌ¬¹¥Ç)_x0000__x000C__x0000__x0001__x000C_ÓüÈÜÂ _x0000_0¼Ü´ü»4Ñ_x0004_È©Æl­¥Ç_x000D__x0000__x0000_010-9129-1126_x0017__x0000__x0000_leesjun1024@hanmail.net_x000E__x0000__x0000_37690004547137_x0006__x0000__x0000_D00183_x0003__x0000__x0001_T³_x001C_È|Ç
+_x0000__x0000_1171558537_x0003__x0000__x0001_iÖÐÆ Á_x000B__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_XÇX¹,_x0000_¡ÇTÖ_x0008__x0000__x0000_20141027_x000D__x0000__x0000_010-6333-2457	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_ÅÌl­_x0005__x0000__x0000_08078 _x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_ÅÌl­ _x0000_àÂ_x0015_È\¸ _x0000_2_x0000_7_x0000_5_x0000_ _x0000_ _x0000_(_x0000_àÂ_x0015_ÈÙ³,_x0000_ _x0000_àÂ¸Ò¬¹DÅ_x000C_Ó¸Ò)_x0000__x0010__x0000__x0001_ÁÀ_x0000_¬Ù³ _x0000_1_x0000_5Î _x0000_1_x0000_0_x0000_4_x0000_,_x0000_ _x0000_1_x0000_0_x0000_5_x0000_8Ö_x0011__x0000__x0000_thejeil@naver.com_x000D__x0000__x0000_010-9668-2210_x000E__x0000__x0000_37690004550437_x0006__x0000__x0000_D00184_x0005__x0000__x0001_$Æ¨°¤ÂìÓ Î
+_x0000__x0000_1322489384_x0003__x0000__x0001_Å+È¨º_x000D__x0000__x0001_´ÆÙ³0®l­©ÆÔ _x0000_aÅ8Á_x001C_Á¬¹ _x0000_xÆ_x0008__x0000__x0000_20141028
+_x0000__x0000_0315756464
+_x0000__x0000_0315755600_x0008__x0000__x0001_½¬0®Ä³ _x0000_¨°ÅüÈÜÂ_x0006__x0000__x0000_472881_x0016__x0000__x0001_½¬0®Ä³ _x0000_¨°ÅüÈÜÂ _x0000_ÄÉt¬$Æ¨°\¸ _x0000_8_x0000_0_x0000_6_x0000_ _x0000_-_x0000_1_x0000_4_x0000__x000D__x0000__x0000_010-9289-9637_x0012__x0000__x0000_jongmo83@naver.com_x000E__x0000__x0000_37690004552737_x0006__x0000__x0000_D00186_x0005__x0000__x0001_ä¹XÎìÓxÇ¸Ò
+_x0000__x0000_6091853217_x0003__x0000__x0001_iÖ­ÝÂ_x0008__x0000__x0000_20141202_x000C__x0000__x0000_055-298-7330_x0005__x0000__x0000_51378_x0011__x0000__x0001_½¬¨° _x0000_=ÌÐÆÜÂ _x0000_XÇ=Ìl­ _x0000__x0018_¼Ä¬\¸ _x0000_6_x0000_3_x0000__x000D__x0000__x0000_010-3561-0209_x000E__x0000__x0000_o2bbi@nate.com_x0008__x0000__x0000_20141212_x000E__x0000__x0000_37690004554037_x0006__x0000__x0000_D00190_x0005__x0000__x0001_p­°À¤ÂìÓ Î
+_x0000__x0000_4010657765_x0003__x0000__x0001__x0015_¼_x001C_Âl×	_x0000__x0001_¤ÂìÓ ÎXÇX¹,_x0000_ _x0000_©ÆÔ_x0008__x0000__x0000_20150406_x000D__x0000__x0000_010-9977-7141_x0008__x0000__x0001__x0004_È|·½Ä³ _x0000_p­°ÀÜÂ_x0005__x0000__x0000_54102_x000F__x0000__x0001__x0004_È½ _x0000_p­°ÀÜÂ _x0000_¨°_x0018_Â¡Á5_x0000_8® _x0000_4_x0000_2_x0000__x000F__x0000__x0001_1_x0000_0_x0000_1_x0000_8Ö(_x0000__x0018_Â¡ÁÙ³,_x0000_ _x0000_(Ì$Æ¹L¾)_x0000__x0013__x0000__x0000_shp7141@hanmaiL.net_x000E__x0000__x0000_37690004558537_x0006__x0000__x0000_D00192
+_x0000__x0001__x0001_Æ8»¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1222039517_x0005__x0000__x0001__x0001_Æ8»¤ÂìÓ Î_x0003__x0000__x0001_@®_x0001_Æ8»_x0008__x0000__x0000_20150608_x000C__x0000__x0000_032-523-1406_x000C__x0000__x0000_032-517-8009	_x0000__x0001_xÇÌ_x0011_­íÅÜÂ _x0000_½ÉÓl­_x0005__x0000__x0000_21337_x000D__x0000__x0000_010-4320-1406_x0012__x0000__x0000_YM1406@hanmail.net_x0007__x0000__x0001_A_x0000_ñ´	®(_x0000_T_x0000_S_x0000_)_x0000__x0005__x0000__x0000_13042_x0003__x0000__x0001_@®Ù³½¬_x000E__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_+_x0000_3_x0000_0_x0000__x000E__x0000__x0000_37690004561837_x0006__x0000__x0000_D00193_x000B__x0000__x0001_ÑÐ¤Â@Õ¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1320972497_x0006__x0000__x0001_ÑÐ¤Â@Õ¤ÂìÓ Î_x0003__x0000__x0001__x0015_¼_x0004_Ö=Ì_x0006__x0000__x0001_´ÆÙ³_x0004_È8»©ÆÔ_x0008__x0000__x0000_20150610_x000D__x0000__x0000_010-3706-2477_x0007__x0000__x0001_½¬0®Ä³ _x0000_l­¬¹ÜÂ_x0005__x0000__x0000_11907_x000F__x0000__x0001_½¬0® _x0000_l­¬¹ÜÂ _x0000_UÆ_x0019_ÂÌ\¸ _x0000_5_x0000_0_x0000_7_x0000_	_x0000__x0001_3_x0000_5Î _x0000_ÑÐ¤Â@Õ¤ÂìÓ Î_x000F__x0000__x0000_pspin@naver.com_x0005__x0000__x0000_22022_x0003__x0000__x0001_HÅ°ÆÄÉ_x000C__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_7_x0000_._x0000_5_x0000__x000E__x0000__x0000_37690004560137_x0006__x0000__x0000_D00195
+_x0000__x0001_¤ÂìÓ ÎLÑlÐ(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_6172249744_x0005__x0000__x0001_¤ÂìÓ ÎLÑlÐ_x0003__x0000__x0001_tÇÝÐ0®_x0006__x0000__x0001__x001C_ÈpÈÅÅ _x0000_Áä¹_x000C__x0000__x0001_õ¬_x0008_Æ _x0000_¤ÂìÓ Î©ÆÔ,_x0000_ _x0000_¡ÇTÖ_x000B__x0000__x0000_051-7564800_x000C__x0000__x0000_051-756-4801_x0005__x0000__x0000_48222_x0017__x0000__x0001_½°À_x0011_­íÅÜÂ _x0000_Ù³·l­ _x0000_+ÈiÕ´ÆÙ³¥Ç\¸ _x0000_4_x0000_0_x0000_¼8® _x0000_8_x0000_'_x0000__x0001_1_x0000_0_x0000_3_x0000_Ù³ _x0000_1_x0000_0_x0000_5_x0000_8Ö,_x0000_1_x0000_0_x0000_6_x0000_8Ö(_x0000_¬ÀÁÉÙ³,_x0000_½°À _x0000_DÅÜÂDÅÜ´ _x0000_TÏ$Æq¸ _x0000_XÕ²DÌ _x0000_DÅ_x000C_Ó¸Ò)_x0000__x000D__x0000__x0000_010-5578-1988_x0015__x0000__x0000_ltktennis@hanmail.net_x000B__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_8_x0000__x0008__x0000__x0000_20150611_x000E__x0000__x0000_37690004562437_x0006__x0000__x0000_D00196	_x0000__x0001__x0015_¬¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_5041920932_x0004__x0000__x0001__x0015_¬¤ÂìÓ Î_x0003__x0000__x0001__x0015_¬@Çl­_x000D__x0000__x0001_LÑÈ²¤Â©ÆÔ,_x0000_ _x0000_XÇX¹,_x0000_ _x0000_àÂ_x001C_¼_x000C__x0000__x0000_053-314-9090_x0005__x0000__x0000_41433_x000D__x0000__x0000_010-3828-0474_x0013__x0000__x0000_keg0417@hanmail.net_x000D__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_6_x0000_+_x0000_1_x0000_5_x0000__x0008__x0000__x0000_20150612_x000E__x0000__x0000_37690004565337_x0006__x0000__x0000_D00199
+_x0000__x0001_P´¬¹¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1283008985_x0003__x0000__x0001_@®_x0001_Æ Á_x000B__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_¤ÂìÓ ÎXÇX¹_x0008__x0000__x0000_20150703_x000C__x0000__x0000_031-911-4191_x000C__x0000__x0000_031-913-0067_x0006__x0000__x0000_410829_x000F__x0000__x0001_½¬0®Ä³à¬ÅÜÂ _x0000_|Ç°ÀÙ³l­_x0015_È_x001C_¼°ÀÙ³_x000E__x0000__x0001_1_x0000_1_x0000_4_x0000_8_x0000_-_x0000_1_x0000_3_x0000_ _x0000_1_x0000_5Î2_x0000_,_x0000_3_x0000_8Ö_x000D__x0000__x0000_010-4288-3563_x0012__x0000__x0000_usop2n@hanmail.net_x000D__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_6_x0000_+_x0000_2_x0000_3_x0000__x000E__x0000__x0000_37690004568237_x0006__x0000__x0000_D00201_x000E__x0000__x0001_(_x0000_üÈ)_x0000_¤ÂtÎtÇ¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_6278102573_x000B__x0000__x0001_¤ÂtÎtÇ¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000__x0003__x0000__x0001_@®1ÁÐÆ_x0006__x0000__x0001_Áä¹ÅÅ _x0000_Ä³ä¹_x0008__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_ä¹_x0010_È_x000C__x0000__x0000_041-566-1879_x000C__x0000__x0000_041-554-2732_x0005__x0000__x0000_31157"_x0000__x0001_©Í­Ì¨°Ä³ _x0000_ÌHÅÜÂ _x0000__x001C_Á½l­ _x0000_1¼_x001D_Á3_x0000_\¸ _x0000_2_x0000_9_x0000_ _x0000_ _x0000_(_x0000_1¼_x001D_ÁÙ³,_x0000_ _x0000_½¶É¹_x0008_Ã%¼)_x0000__x000D__x0000__x0000_010-4513-1879_x0011__x0000__x0000_kimsw000@nate.com_x000E__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_4_x0000_0_x0000_+_x0000_2_x0000_0_x0000__x0008__x0000__x0000_20150804_x000E__x0000__x0000_37690004570937_x0006__x0000__x0000_D00202_x0008__x0000__x0001_¤ÂìÓå²(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_3052275067_x0003__x0000__x0001_HÅü­¹Â_x000C__x0000__x0000_042-522-9566_x000C__x0000__x0000_042-271-4786_x0006__x0000__x0000_300810_x0017__x0000__x0001__x0000_³_x0004_È_x0011_­íÅÜÂ _x0000__x0011_Él­ _x0000_Ù³_x001C_Á_x0000_³\¸ _x0000_1_x0000_2_x0000_0_x0000_1_x0000_(_x0000_ÜÐÉÓÙ³)_x0000__x0007__x0000__x0001_¤ÂìÓå² _x0000_ÜÐÉÓ_x0010_È_x000B__x0000__x0000_01062224787_x0010__x0000__x0000_spodaq@naver.com_x000D__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_5_x0000_+_x0000_3_x0000_3_x0000__x0008__x0000__x0000_20150805_x000E__x0000__x0000_37690004571537_x0006__x0000__x0000_D00203	_x0000__x0001_ðÅTÏ¬¹DÅ(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_2041477980_x0004__x0000__x0001_ðÅTÏ¬¹DÅ_x0003__x0000__x0001_@®ÁÀ0®_x0006__x0000__x0001_Ä³Áä¹ _x0000_t¬$Á_x000D__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_´Ì!ÇÜÂ_x001C_Á&lt;»$ÁXÎ_x0008__x0000__x0000_20150806_x000C__x0000__x0000_02-3390-4345_x000C__x0000__x0000_02-3390-4344
+_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_Ù³_x0000_³8»l­_x0005__x0000__x0000_02496_x0011__x0000__x0001__x001C_Á¸Æ _x0000_Ù³_x0000_³8»l­ _x0000_Ý¹°Æ\¸1_x0000_2_x0000_8® _x0000_1_x0000_9_x0000__x000B__x0000__x0001_1_x0000_5Î _x0000_XÕtÇÐÆ¤ÂìÓ Î°ÀÅÅ_x000D__x0000__x0000_010-9089-5363_x0017__x0000__x0000_01090895363@hanmail.net_x000B__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_2_x0000_0_x0000__x000E__x0000__x0000_37690004572137_x0006__x0000__x0000_D00205_x0005__x0000__x0001_ÁLÑ¤ÂìÓ Î
+_x0000__x0000_1971301851_x0003__x0000__x0001_@®_x0001_Æ_x0018_Â_x0008__x0000__x0001_Ä³Áä¹ÅÅ _x0000_Ä³ä¹ÅÅ	_x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_4»íÅÅÅ_x000B__x0000__x0000_01063388568_x0008__x0000__x0001_½¬0®Ä³ _x0000_XÇ_x0015_È½ÜÂ_x0005__x0000__x0000_11806!_x0000__x0001_½¬0®Ä³ _x0000_XÇ_x0015_È½ÜÂ _x0000_$Æ©º\¸ _x0000_1_x0000_7_x0000_0_x0000_ _x0000_°Àä´È¹DÇ _x0000_DÅ_x000C_Ó¸Ò _x0000_4_x0000_1_x0000_2_x0000_-_x0000_7_x0000_0_x0000_6_x0000__x000D__x0000__x0000_010-6338-8568_x0011__x0000__x0000_3388568@naver.com_x0005__x0000__x0000_26002_x0003__x0000__x0001__x0015_¬ÜÐ8Ö_x0008__x0000__x0000_20220901_x000E__x0000__x0000_37690004700437_x0006__x0000__x0000_D00209_x0018__x0000__x0001_¤ÂìÓ Î_x000C_Õì·¤Â(_x0000_S_x0000_p_x0000_o_x0000_r_x0000_t_x0000_s_x0000_ _x0000_P_x0000_l_x0000_u_x0000_s_x0000_)_x0000_(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1192167071_x0003__x0000__x0001__x0015_¬ÜÂ¨º_x0006__x0000__x0001_Ä³Áä¹ _x0000_LÇÝÂ_x0008__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_\ÕÝÂ_x000B__x0000__x0000_02-871-5513	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x0000_­EÅl­_x0005__x0000__x0000_08750_x000F__x0000__x0001__x001C_Á¸Æ _x0000__x0000_­EÅl­ _x0000_àÂ¼¹\¸3_x0000_8® _x0000_4_x0000_0_x0000__x0005__x0000__x0001_ÀÉXÕ _x0000_1_x0000_5Î_x000D__x0000__x0000_010-7703-5353_x001A__x0000__x0000_tennisplus0122@esero.go.krX_x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_ _x0000_/_x0000_ _x0000_2_x0000_5_x0000_S_x0000_S_x0000_ _x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_ _x0000_/_x0000_ _x0000_2_x0000_4_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_9_x0000_._x0000_6_x0000_ _x0000_/_x0000_ _x0000_2_x0000_4_x0000_S_x0000_S_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_ _x0000_/_x0000_ _x0000_2_x0000_3_x0000_F_x0000_W_x0000_ _x0000__x0018_ÂüÈ _x0000_ìÅàÂ _x0000_ _x0000_1_x0000_2_x0000_ _x0000_(_x0000_ô²ù²Ç _x0000_Æ­Ì&lt;Ç\¸ _x0000_6_x0000_ _x0000__x0018_¼_x0001_Æ)_x0000__x0008__x0000__x0000_20160114_x000E__x0000__x0000_37690004577337_x0006__x0000__x0000_D00210_x0011__x0000__x0001_(_x0000_üÈ)_x0000_ÐÅtÇ_x001C_ÈtÇxÇ0Ñ´°TÁ °(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1268641398_x000C__x0000__x0000_031-761-8980_x000C__x0000__x0000_031-761-2140_x0005__x0000__x0000_12769_x000D__x0000__x0000_010-4552-3318	_x0000__x0000_1800-6142_x000E__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_4_x0000_0_x0000_+_x0000_2_x0000_5_x0000__x0008__x0000__x0000_20160121_x000E__x0000__x0000_37690004578037_x0006__x0000__x0000_D00256	_x0000__x0001_p¬1Á¤ÂìÓ Î(_x0000_Å°À)_x0000_
+_x0000__x0000_6210808090_x0003__x0000__x0001__x0015_È+È_x0015_¬_x0006__x0000__x0001_Ä³Áä¹ _x0000__x001C_ÈpÈ_x000B__x0000__x0001_ìÕ¤Â0®l­,_x0000_ _x0000_¤ÂìÓ Î©ÆÔ_x0008__x0000__x0000_20160412_x000C__x0000__x0000_055-387-3613_x000C__x0000__x0000_055-387-3615_x0008__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_Å°ÀÜÂ_x0005__x0000__x0000_50621 _x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_Å°ÀÜÂ _x0000__x001C_Á|ÇÙ³\¸ _x0000_2_x0000_5_x0000_ _x0000_ _x0000_(_x0000__x0011_É½Ù³,_x0000_ _x0000_$Ç ÁÝÀ_x0001_Æ´ÅP­äÂ)_x0000__x000D__x0000__x0000_010-2390-2994_x0013__x0000__x0000_dhrhr68@hanmail.netH_x0000__x0001_2_x0000_4_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_3_x0000_5_x0000_ _x0000_/_x0000_2_x0000_4_x0000_S_x0000_S_x0000__x0018_ÂüÈìÅàÂ _x0000_3_x0000_5_x0000_ _x0000_/_x0000_ _x0000_2_x0000_3_x0000_F_x0000_W_x0000_ _x0000__x0018_ÂüÈ _x0000_ìÅàÂ _x0000_3_x0000_5_x0000_ _x0000_/_x0000_ _x0000_2_x0000_3_x0000_S_x0000_S_x0000_ _x0000__x0018_ÂüÈ _x0000_ìÅàÂ _x0000_3_x0000_5_x0000_(_x0000_|·_x0013_Ï+_x0000_È¹D¾¤Â _x0000_9_x0000_4_x0000_3_x0000_,_x0000_2_x0000_5_x0000_0_x0000_)_x0000__x0008__x0000__x0000_20160407_x000E__x0000__x0000_37690004581237_x0006__x0000__x0000_D00267_x0006__x0000__x0001__x001C_ÈtÇD¾¤ÂìÓ Î
+_x0000__x0000_6664100083_x0003__x0000__x0001_Ç_x0015_È\Õ_x000D__x0000__x0001_Ä³ä¹ _x0000__x000F_¼ _x0000_Áä¹ÅÅ,_x0000_ _x0000__x001C_ÁD¾¤Â_x000C__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_ _x0000__x0011_­à¬_x0000_³ÕÅÅ_x0008__x0000__x0000_20160610_x000C__x0000__x0000_062-523-7451_x000C__x0000__x0000_062-523-7455_x0005__x0000__x0000_62023_x000D__x0000__x0001__x0011_­üÈ _x0000__x001C_Ál­ _x0000_´ÆÌ\¸ _x0000_1_x0000_2_x0000_2_x0000__x0005__x0000__x0001_(_x0000__x000D_Ã_x000C_ÍÙ³)_x0000__x000D__x0000__x0000_010-4606-4538_x0015__x0000__x0000_jhrim1226@hanmail.net_x0008__x0000__x0000_20160601_x000E__x0000__x0000_37690004584137_x0006__x0000__x0000_D00280_x0005__x0000__x0001_Ä³ô²¤ÂìÓ Î
+_x0000__x0000_3071042161_x0003__x0000__x0001_$ÇÙ³ÝÂ_x000B__x0000__x0001_Ä³ä¹_x000F_¼ _x0000_Áä¹ÅÅ _x0000_Áä¹ÅÅ_x0010__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_Ç_x0004_Èp¬ _x0000__x0010_Óä¹,_x0000_ _x0000__x0000_³ìÅ_x0008__x0000__x0000_20160825_x000C__x0000__x0000_044-863-8908_x000C__x0000__x0000_044-863-8970_x000F__x0000__x0001_8Á+È¹ÒÄ¼ÇXÎÜÂ _x0000_8Á+È¹ÒÄ¼ÇXÎÜÂ_x0005__x0000__x0000_30102_x001E__x0000__x0001_8Á+È¹ÒÄ¼ÇXÎÜÂ _x0000__x0008_È¬Ç\¸ _x0000_1_x0000_7_x0000_2_x0000_ _x0000_(_x0000_´ÅÄÉÙ³,_x0000_ _x0000_ÜÐ\Õ_x0004_Õ_x0008_¸¤Â&lt;Á0Ñ)_x0000__x0004__x0000__x0001_1_x0000_0_x0000_1_x0000_8Ö_x000D__x0000__x0000_010-7185-8008_x0015__x0000__x0000_dodamsports@naver.com_x000E__x0000__x0000_37690004586437_x0006__x0000__x0000_D00282_x0005__x0000__x0001__x0004_²¬¹¤ÂìÓ Î
+_x0000__x0000_1082124505_x0003__x0000__x0001_@®l×_x0015_È_x0006__x0000__x0001_Áä¹ _x0000_Ä³Áä¹_x000C__x0000__x0001__x0004_ÈÇÁÀp¬·ÅÅ _x0000_0¼Ü´ü»4Ñ _x0000__x000B__x0000__x0000_02-848-6291_x000B__x0000__x0000_02-848-7556
+_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x0001_Æñ´ìÓl­_x0005__x0000__x0000_07375_x000E__x0000__x0001__x001C_Á¸Æ _x0000__x0001_Æñ´ìÓl­ _x0000_Ä³àÂ\¸ _x0000_5_x0000_1_x0000__x000D__x0000__x0001_1_x0000_5Î _x0000_1_x0000_0_x0000_5_x0000_8Ö(_x0000_¡ÁU³L¾)µ)_x0000__x000D__x0000__x0000_010-8393-6291_x0013__x0000__x0000_hee00jung@naver.com_x0008__x0000__x0000_20160905_x000E__x0000__x0000_37690004588737_x0006__x0000__x0000_D00286_x0007__x0000__x0001_Æ%±¤Â _x0000_1Á¨°_x0010_È
+_x0000__x0000_2603001743_x0003__x0000__x0001_MÖ¥Ç8Ö_x0008__x0000__x0001_Ä³ä¹ _x0000__x000F_¼ _x0000_Áä¹ÅÅ_x0008__x0000__x0000_20151218_x000C__x0000__x0000_031-755-7257_x0007__x0000__x0001_½¬0®Ä³ _x0000_1Á¨°ÜÂ_x0005__x0000__x0000_13110_x001E__x0000__x0001_½¬0®Ä³ _x0000_1Á¨°ÜÂ _x0000__x0018_Â_x0015_Èl­ _x0000_1Á¨°_x0000_³\¸ _x0000_1_x0000_2_x0000_6_x0000_7_x0000_ _x0000_-_x0000_1_x0000_ _x0000_(_x0000_ÜÐÉÓÙ³)_x0000__x000D__x0000__x0000_010-7191-7257_x0012__x0000__x0000_nero1016@naver.com_x0002__x0000__x0001_¨°¸Ó_x0008__x0000__x0000_2016110</v>
           </cell>
           <cell r="D38" t="str">
             <v>사용가능</v>
@@ -4598,50 +5557,281 @@
           <cell r="E38" t="str">
             <v>일반사업자</v>
           </cell>
-          <cell r="F38" t="str">
-            <v>3298701221</v>
+          <cell r="F38" t="e">
+            <v>#N/A</v>
           </cell>
           <cell r="G38" t="str">
-            <v>주식회사 세진스포츠</v>
-          </cell>
-          <cell r="H38" t="str">
-            <v>박순삼</v>
-          </cell>
-          <cell r="I38" t="str">
-            <v>도매 및 소매</v>
+            <v>8385_x0013__x0000__x0000_judocjl@hanmail.net_x000E__x0000__x0000_37690004490537_x0006__x0000__x0000_D00109_x0008__x0000__x0001__x0001_Æ¤ÂìÓ Î(_x0000_¨°ÐÆ)_x0000_
+_x0000__x0000_1095289131_x0003__x0000__x0001_tÇ_x0015_ÈÌ_x0008__x0000__x0000_20071119_x000C__x0000__x0000_063-632-4154
+_x0000__x0000_0636324156_x0005__x0000__x0000_55703_x0015__x0000__x0001__x0004_È|·½Ä³ _x0000_¨°ÐÆÜÂ _x0000_¬Àä¹tº _x0000__x0000_³¬À\¸ _x0000_1_x0000_2_x0000_8_x0000_3_x0000__x0004__x0000__x0001__x0001_Æ¤ÂìÓ Î_x000D__x0000__x0000_010-4594-0634_x0013__x0000__x0000_jclee8734@naver.com_x000E__x0000__x0000_37690004497037_x0006__x0000__x0000_D00110_x0007__x0000__x0001_Æ%±¤Â _x0000_TÖ_x001C_Â_x0010_È
+_x0000__x0000_4080577085_x0003__x0000__x0001__x0004_È+º_x0019_Â_x0008__x0000__x0000_20071102_x000C__x0000__x0000_061-375-6647_x0008__x0000__x0001__x0004_È|·¨°Ä³ _x0000_TÖ_x001C_Âp­_x0006__x0000__x0000_519809_x0014__x0000__x0001__x0004_È|·¨°Ä³ _x0000_TÖ_x001C_Âp­ _x0000__x0011_­U³\¸ _x0000_1_x0000_4_x0000_0_x0000_ _x0000_ _x0000_1_x0000_5Î_x000D__x0000__x0000_010-6632-5893_x0012__x0000__x0000_ms-jon@hanmeil.net_x000E__x0000__x0000_37690004498637_x0006__x0000__x0000_D00111_x000C__x0000__x0001_,Æ¼¹=Õ+ÈiÕ¤ÂìÓ Î(_x0000_©ºìÓ)_x0000_
+_x0000__x0000_4111469486_x0003__x0000__x0001_@®=Ì©Æ_x000C__x0000__x0001_´ÆÙ³©ÆÔ,_x0000_ñ´°Àl­,_x0000_0®P±Ô_x0008__x0000__x0000_20070320_x000C__x0000__x0000_061-242-1032
+_x0000__x0000_0612443032_x0008__x0000__x0001__x0004_È|·¨°Ä³ _x0000_©ºìÓÜÂ_x0005__x0000__x0000_58726_x0010__x0000__x0001__x0004_È¨° _x0000_©ºìÓÜÂ _x0000_(Ì¼_x001D_Á8® _x0000_4_x0000_1_x0000_-_x0000_1_x0000__x0002__x0000__x0001_1_x0000_5Î_x000D__x0000__x0000_010-9243-4285_x0010__x0000__x0000_eyebono@daum.net_x000E__x0000__x0000_37690004499237_x0006__x0000__x0000_D00116_x000F__x0000__x0001_Æ%±¤ÂÈ¹°À_x0000_³¬¹_x0010_È(_x0000_ü»4Ñ¤ÂìÓ Î)_x0000_
+_x0000__x0000_6080288027_x0003__x0000__x0001_ Ç_x0001_Æ_x0019_Â_x0008__x0000__x0001_¤ÂìÓ Î©ÆÔ_x000F_¼XÇX¹_x000C__x0000__x0000_055-222-5431
+_x0000__x0000_0552225432_x0008__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_=ÌÐÆÜÂ_x0006__x0000__x0000_631852_x0018__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_=ÌÐÆÜÂ _x0000_È¹°ÀiÕìÓl­ _x0000_©ÆÈ¹\¸ _x0000_7_x0000_6_x0000_ _x0000_üÈÝÐ_x000D__x0000__x0000_010-3707-6245_x0016__x0000__x0000_dudtjs6245@hanmail.net_x000E__x0000__x0000_37690004504337_x0006__x0000__x0000_D00120_x0006__x0000__x0001_Æ%±¤Â­ÌüÈ_x0010_È
+_x0000__x0000_3170385854_x0003__x0000__x0001_\Í°Æ1Á_x000B__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_XÇX¹,_x0000__x0018_Ât¬_x0008__x0000__x0000_20110729_x000C__x0000__x0000_043-222-3040
+_x0000__x0000_0432245050_x0008__x0000__x0001_©Í­Ì½Ä³ _x0000_­ÌüÈÜÂ_x0006__x0000__x0000_361842_x0012__x0000__x0001_©Í½ _x0000_­ÌüÈÜÂ _x0000_ÁÀù²l­ _x0000_8Öø»\¸ _x0000_2_x0000_0_x0000_6_x0000__x0005__x0000__x0001_1_x0000_5Î _x0000_È!Î_x000D__x0000__x0000_010-5468-3319_x0015__x0000__x0000_wsung3525@hanmail.net_x0008__x0000__x0000_20080429_x000E__x0000__x0000_37690004507237_x0006__x0000__x0000_D00121_x000D__x0000__x0001_Æ%±¤ÂìÓmÕ_x0010_È(_x0000_XÕtÇlÐ¬¹´Å)_x0000_
+_x0000__x0000_5061736246_x0003__x0000__x0001__x0015_È@Ç_x0001_Æ_x0008__x0000__x0000_20090227_x000C__x0000__x0000_054-283-5234
+_x0000__x0000_0542835231_x0008__x0000__x0001_½¬ÁÀ½Ä³ _x0000_ìÓmÕÜÂ_x0006__x0000__x0000_790822_x0012__x0000__x0001_½¬½ _x0000_ìÓmÕÜÂ _x0000_¨°l­ _x0000__x0000_³Ä³Ù³ _x0000_8_x0000_6_x0000_-_x0000_2_x0000__x000D__x0000__x0000_010-4133-7770_x0014__x0000__x0000_minton1125@naver.com_x0008__x0000__x0000_20081105_x000E__x0000__x0000_37690004508937_x0006__x0000__x0000_D00122_x0005__x0000__x0001_°Æ¬¹¤ÂìÓ Î
+_x0000__x0000_4172105493_x0003__x0000__x0001__x0015_¼_x0018_ÂÄÉ_x0008__x0000__x0000_20180101_x000C__x0000__x0000_051-632-2681
+_x0000__x0000_0516322681_x0008__x0000__x0001_½°À_x0011_­íÅÜÂ _x0000_¨°l­_x0006__x0000__x0000_608827_x0011__x0000__x0001_½°À_x0011_­íÅÜÂ _x0000_¨°l­ _x0000_Ç ÇÉÓTÖ\¸ _x0000_4_x0000_9_x0000__x000D__x0000__x0000_010-2594-2682_x0015__x0000__x0000_moxie2000@hanmail.net_x000E__x0000__x0000_37690004509537_x0006__x0000__x0000_D00123_x0005__x0000__x0001_°Æ1Á¤ÂìÓ Î
+_x0000__x0000_2077003708_x0003__x0000__x0001_@®DÆÝÂ_x0008__x0000__x0000_20071009_x000B__x0000__x0000_02-465-1297	_x0000__x0000_024651197	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x0011_­ÄÉl­_x0006__x0000__x0000_143961_x0010__x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x0011_­ÄÉl­ _x0000_l­XÇ\¸ _x0000_6_x0000_6_x0000__x0014__x0000__x0001_1_x0000_5Î _x0000_(_x0000_l­XÇÙ³ _x0000_2_x0000_2_x0000_7_x0000_-_x0000_6_x0000_)_x0000_ _x0000_°Æ1Á¤ÂìÓ Î_x000D__x0000__x0000_010-3418-1230_x000F__x0000__x0000_ws418@naver.com_x000E__x0000__x0000_37690004510537_x0006__x0000__x0000_D00126_x0005__x0000__x0001_ÐÆÙ³´Ì!Ç¬À
+_x0000__x0000_3060363748_x0003__x0000__x0001_ü»Ñ¼ÁÉ_x0004__x0000__x0001_´ÆÙ³0®l­_x0008__x0000__x0000_20050705_x000C__x0000__x0000_042-531-4004
+_x0000__x0000_0425328899_x0008__x0000__x0001__x0000_³_x0004_È_x0011_­íÅÜÂ _x0000_Ù³l­_x0005__x0000__x0000_34630_x000D__x0000__x0001__x0000_³_x0004_È _x0000_Ù³l­ _x0000__x0000_³_x0004_È\¸ _x0000_7_x0000_6_x0000_5_x0000__x000D__x0000__x0000_010-5453-9536_x0012__x0000__x0000_wonspo@hanmail.net_x0008__x0000__x0000_20080214_x000E__x0000__x0000_37690004511137_x0006__x0000__x0000_D00127_x0008__x0000__x0001_ÐÆ¤ÂìÓ Î(_x0000__x001C_ÈüÈ)_x0000_
+_x0000__x0000_6160962051_x0003__x0000__x0001_@®ø»½¬_x000C__x0000__x0000_064-752-4422
+_x0000__x0000_0647232992_x000C__x0000__x0001__x001C_ÈüÈ¹ÒÄ¼ÇXÎÄ³ _x0000__x001C_ÁÀ­ìÓÜÂ_x0006__x0000__x0000_690161_x0013__x0000__x0001__x001C_ÈüÈ¹ÒÄ¼ÇXÎÄ³ _x0000__x001C_ÈüÈÜÂ _x0000_$Æ|·\¸ _x0000_1_x0000_3_x0000_4_x0000__x000D__x0000__x0000_010-4416-4412_x0015__x0000__x0000_crony0104@hanmail.net_x000E__x0000__x0000_37690004512837_x0006__x0000__x0000_D00132_x0005__x0000__x0001__x0004_ÈüÈÆ%±¤Â
+_x0000__x0000_4020887887_x0003__x0000__x0001_tÇ_x001C_Â+È_x000C__x0000__x0000_063-274-9337
+_x0000__x0000_0632789337_x0008__x0000__x0001__x0004_È|·½Ä³ _x0000__x0004_ÈüÈÜÂ_x0006__x0000__x0000_560080_x0013__x0000__x0001__x0004_È|·½Ä³ _x0000__x0004_ÈüÈÜÂ _x0000_DÆ°Àl­ _x0000_õ¬½\¸ _x0000_2_x0000_0_x0000__x000D__x0000__x0000_010-9224-8391_x0010__x0000__x0000_jyonex@naver.com_x000E__x0000__x0000_37690004516337_x0006__x0000__x0000_D00136_x0005__x0000__x0001__x001C_È|Ç¤ÂìÓ Î
+_x0000__x0000_4040533542_x000B__x0000__x0001__x001C_È|Ç_x0008_¸_x0000_È¤ÂìÓ Î(_x0000__x0015_ÈMÇ)_x0000__x0003__x0000__x0001_@®_x0011_­õ¼	_x0000__x0001_´ÆÙ³0®l­_x000F_¼´ÆÙ³õ¼xÆ_x000C__x0000__x0000_063-535-9146
+_x0000__x0000_0635332093_x0008__x0000__x0001__x0004_È|·½Ä³ _x0000__x0015_ÈMÇÜÂ_x0006__x0000__x0000_580804_x000F__x0000__x0001__x0004_È|·½Ä³ _x0000__x0015_ÈMÇÜÂ _x0000__x0011_ÉYÅ\¸ _x0000_8_x0000_3_x0000__x000D__x0000__x0000_010-9579-7800_x0016__x0000__x0000_sports9146@hanmaIl.net_x000E__x0000__x0000_37690004520237_x0006__x0000__x0000_D00137_x000B__x0000__x0001_üÈÝÂÖ¬À _x0000_0¼Ü´ü»4ÑÈ¹¸Ò
+_x0000__x0000_1108193203_x0003__x0000__x0001__x0015_ÈtÇ@±_x000B__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000__x0004_ÈÇÁÀp¬·_x0008__x0000__x0000_20130723_x000C__x0000__x0000_031-964-3530	_x0000__x0000_023829555_x0007__x0000__x0001_½¬0®Ä³ _x0000_à¬ÅÜÂ_x0005__x0000__x0000_10564_x0011__x0000__x0001_½¬0® _x0000_à¬ÅÜÂ _x0000_U³Ål­ _x0000_¼À¡Á\¸ _x0000_1_x0000_2_x0000__x0007__x0000__x0001_4_x0000_5Î _x0000_4_x0000_1_x0000_8_x0000_8Ö_x000D__x0000__x0000_010-7152-7538_x0014__x0000__x0000_mintonmart@naver.com_x000E__x0000__x0000_37690004521937_x0006__x0000__x0000_D00138	_x0000__x0001_üÈÝÂÖ¬ÀÙ³°Æ¤ÂìÓ Î
+_x0000__x0000_1108180426_x0003__x0000__x0001_¡Á_x0015_È|Ç_x000B__x0000__x0000_02-382-3598	_x0000__x0000_023553586	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_@ÇÉÓl­_x0006__x0000__x0000_122903_x0018__x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_@ÇÉÓl­ _x0000_ðÅ_x001C_Á\¸ _x0000_2_x0000_9_x0000_-_x0000_1_x0000_ _x0000_Ù³°Æ¤ÂìÓ Î_x000D__x0000__x0000_010-2018-3598_x0012__x0000__x0000_dvip1233@naver.com_x000B__x0000__x0000_01074353598
+_x0000__x0001__x0018_Â_x0008_® _x0000_½qÈ&lt;Ç\¸ _x0000_µÑ_x001C_È_x000E__x0000__x0000_37690004522537_x0006__x0000__x0000_D00141	_x0000__x0001__x0011_ÉYÅ¤ÂìÓ Î(_x0000_½¬üÈ)_x0000_
+_x0000__x0000_3226600323_x0003__x0000__x0001_iÖ_x0001_ÆäÂ_x0008__x0000__x0000_20081210_x000C__x0000__x0000_054-741-5177_x0008__x0000__x0001_½¬ÁÀ½Ä³ _x0000_½¬üÈÜÂ_x0006__x0000__x0000_780943_x0012__x0000__x0001_½¬ÁÀ½Ä³ _x0000_½¬üÈÜÂ _x0000__x0008_®1Á\¸ _x0000_2_x0000_9_x0000_4_x0000_-_x0000_1_x0000__x000D__x0000__x0000_010-7579-5177_x0014__x0000__x0000_jasp6304@hanmail.net_x0008__x0000__x0000_20081211_x000E__x0000__x0000_37690004525437_x0006__x0000__x0000_D00145_x0005__x0000__x0001_­Ìá¸¤ÂìÓ Î
+_x0000__x0000_6150796307_x0003__x0000__x0001_pÈø»_x0019_Â_x0008__x0000__x0000_20101004_x000C__x0000__x0000_055-312-9559
+_x0000__x0000_0553129560_x0008__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_@®tÕÜÂ_x0006__x0000__x0000_621833_x0012__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_@®tÕÜÂ _x0000_¥Ç Ç\¸ _x0000_2_x0000_9_x0000_7_x0000_-_x0000_5_x0000__x000D__x0000__x0000_010-9513-9559_x0016__x0000__x0000_jms3129559@hanmail.net_x0008__x0000__x0000_20101019_x000E__x0000__x0000_37690004530037_x0006__x0000__x0000_D00148_x0007__x0000__x0001__x0000_ÏtÇdÅD¾¤ÂìÓ Î
+_x0000__x0000_1232481068_x0003__x0000__x0001__x0015_¼+ºÇ_x000C__x0000__x0000_031-457-8706
+_x0000__x0000_0314578707_x0007__x0000__x0001_½¬0®Ä³ _x0000_HÅÅÜÂ_x0006__x0000__x0000_431837_x0012__x0000__x0001_½¬0®Ä³ _x0000_HÅÅÜÂ _x0000_Ù³HÅl­ _x0000_À­xÇ\¸ _x0000_8_x0000_9_x0000__x000D__x0000__x0000_010-7338-7375_x0016__x0000__x0000_jamjali200@hanmail.net_x000E__x0000__x0000_37690004532237_x0006__x0000__x0000_D00149	_x0000__x0001_TÏ¬¹DÅ$Æ_x0008_Õ(_x0000_@®Ì)_x0000_
+_x0000__x0000_5100147324_x0003__x0000__x0001__x0015_¼ Á_x0001_Æ_x0008__x0000__x0000_20070423_x000C__x0000__x0000_054-430-7007
+_x0000__x0000_0544307007_x0008__x0000__x0001_½¬ÁÀ½Ä³ _x0000_@®ÌÜÂ_x0005__x0000__x0000_39626_x000E__x0000__x0001_½¬½ _x0000_@®ÌÜÂ _x0000_¡Á$Á\¸ _x0000_1_x0000_6_x0000_4_x0000__x000D__x0000__x0000_010-4115-6306_x0013__x0000__x0000_jj10654@hanmail.net_x000E__x0000__x0000_37690004533937_x0006__x0000__x0000_D00150_x0005__x0000__x0001__x0014_Ól­¤ÂìÓ Î
+_x0000__x0000_5020153204_x0003__x0000__x0001_àÂÁÀÜ­_x0008__x0000__x0000_20080331_x000C__x0000__x0000_053-957-8989
+_x0000__x0000_0539432345_x0008__x0000__x0001__x0000_³l­_x0011_­íÅÜÂ _x0000_Ù³l­_x0005__x0000__x0000_41193_x000F__x0000__x0001__x0000_³l­ _x0000_Ù³l­ _x0000_DÅÅ\¸1_x0000_1_x0000_8® _x0000_8_x0000_1_x0000__x0008__x0000__x0001_1_x0000_5Î _x0000__x0014_Ól­¤ÂìÓ Î_x000D__x0000__x0000_010-8854-8989_x0012__x0000__x0000_89sports@naver.com_x000E__x0000__x0000_37690004534537_x0006__x0000__x0000_D00159_x0005__x0000__x0001__x001C_Ö1Á¤ÂìÓ Î
+_x0000__x0000_1300531089_x0003__x0000__x0001_tÇXÇ Á_x000D__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000__x0000_¬_x0004_È_x001C_ÈÔ,_x0000_¡ÇTÖ_x0008__x0000__x0000_20070529_x000C__x0000__x0000_032-654-2133
+_x0000__x0000_0326542132_x0007__x0000__x0001_½¬0®Ä³ _x0000_½ÌÜÂ_x0006__x0000__x0000_422819 _x0000__x0001_½¬0®Ä³ _x0000_½ÌÜÂ _x0000_Á¬Àl­ _x0000_½¬xÇ\¸1_x0000_2_x0000_0_x0000_¼8® _x0000_2_x0000_8_x0000_ _x0000_ _x0000_1_x0000_5Î_x0010_ÈìÓ _x0000_1_x0000_xÎ_x000D__x0000__x0000_010-7578-7740_x0015__x0000__x0000_hs7167741@hanmail.net_x000E__x0000__x0000_37690004541337_x0006__x0000__x0000_D00160_x0005__x0000__x0001_8ÖÙ³¤ÂìÓ Î
+_x0000__x0000_1243919047_x0003__x0000__x0001_@®8ÖÙ³_x0008__x0000__x0000_20100113_x000C__x0000__x0000_031-375-0331
+_x0000__x0000_0313750331_x0007__x0000__x0001_½¬0®Ä³ _x0000_$Æ°ÀÜÂ_x0006__x0000__x0000_447802_x001A__x0000__x0001_½¬0®Ä³ _x0000_$Æ°ÀÜÂ _x0000_1Á8Ö_x0000_³\¸ _x0000_2_x0000_5_x0000_ _x0000_´Æ°ÀL¾)µ _x0000_ _x0000_1_x0000_5Î _x0000_4_x0000__x000D__x0000__x0000_010-5295-8278_x0013__x0000__x0000_khd9982@hanmail.net_x000E__x0000__x0000_37690004542037_x0006__x0000__x0000_D00161_x0005__x0000__x0001_MÖ1ÁÆ%±¤Â
+_x0000__x0000_3100640518_x0003__x0000__x0001_@®_x0004_Ö_x0015_È_x0008__x0000__x0000_20090616_x000C__x0000__x0000_041-634-7327_x0008__x0000__x0001_©Í­Ì¨°Ä³ _x0000_MÖ1Áp­_x0005__x0000__x0000_32263_x0012__x0000__x0001_©Í¨° _x0000_MÖ1Áp­ _x0000_MÖ½MÇ _x0000_©Í¨°_x0000_³\¸ _x0000_3_x0000_6_x0000__x0015__x0000__x0001__x001C_È _x0000_1_x0000_5Î _x0000__x001C_È _x0000_1_x0000_0_x0000_1_x0000_8Ö(_x0000_L¾dÅT³¤Â$Æ&lt;Õ¤ÂTÑ)_x0000__x000D__x0000__x0000_010-8626-9825_x0010__x0000__x0000_hji923@naver.com_x000E__x0000__x0000_37690004543637_x0006__x0000__x0000_D00166_x000C__x0000__x0001_(_x0000_üÈ)_x0000_ðÒ_x001C_ÈtÇ_x0014_µ¤Â¸Ò¬¹ð½XÁ
+_x0000__x0000_2118732516_x0003__x0000__x0001_¡ÁÁÀÐÆ_x0006__x0000__x0001_Ä³Áä¹ _x0000_Ä³ä¹_x0008__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_4»íÅ_x0008__x0000__x0000_20120911_x000B__x0000__x0000_02-511-5114	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x0015_¬¨°l­_x0006__x0000__x0000_135010_x000B__x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ_x0015_¬¨°l­|±_x0004_ÖÙ³_x000E__x0000__x0001__x0008_®@ÇL¾)µ _x0000_1_x0000_5Î _x0000_ ¼¤Â¸Ò¤Â Ñ´Å_x000D__x0000__x0000_010-8784-1651_x0015__x0000__x0000_bestextreme@naver.com_x0007__x0000__x0001_B_x0000_ñ´	®(_x0000_T_x0000_S_x0000_)_x0000__x0005__x0000__x0000_14049_x0003__x0000__x0001__x0015_¼_x0004_ÖÄÉ_x0008__x0000__x0000_20190917_x0006__x0000__x0000_D00167_x0008__x0000__x0001_üÈÝÂÖ¬À _x0000_ÐÆÐÅÇ
+_x0000__x0000_1268800066_x0003__x0000__x0001_@®DÕ¹Â_x0006__x0000__x0001_Ä³Áä¹ÅÅ _x0000_xÆ_x0007__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_xÆ_x000C__x0000__x0000_02-1644-1662	_x0000__x0001_½°À_x0011_­íÅÜÂ _x0000__x0018_Â_x0001_Æl­_x0006__x0000__x0000_613815_x0013__x0000__x0001_½°À_x0011_­íÅÜÂ _x0000__x0018_Â_x0001_Æl­ _x0000__x0011_­¨°\¸ _x0000_6_x0000_3_x0000_ _x0000_B_x0000_Ù³_x0004__x0000__x0001_4_x0000_5Î|Ç½_x000D__x0000__x0000_010-8882-4137_x0014__x0000__x0000_oneeight@hanmail.net_x0006__x0000__x0000_D00173_x0005__x0000__x0001__x0008_®_x0001_Æ¤ÂìÓ Î
+_x0000__x0000_1052087391_x0003__x0000__x0001_°ÆÀÉÐÆ_x0008__x0000__x0000_20140217_x000D__x0000__x0000_010-6208-8112_x0006__x0000__x0000_121889_x0013__x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_È¹ìÓl­ _x0000_Ù³P­\¸3_x0000_8® _x0000_1_x0000_2_x0000_5_x0000__x0013__x0000__x0000_yonex0901@naver.com_x0008__x0000__x0000_20150122_x000E__x0000__x0000_37690004557937_x0006__x0000__x0000_D00181_x0004__x0000__x0001__x0000_É¤ÂìÓ Î
+_x0000__x0000_1410240836_x0003__x0000__x0001__x0015_¼½¬·_x0008__x0000__x0000_20140825_x000C__x0000__x0000_031-945-2007_x0007__x0000__x0001_½¬0®Ä³ _x0000__x000C_ÓüÈÜÂ_x0006__x0000__x0000_413819$_x0000__x0001_½¬0®Ä³ _x0000__x000C_ÓüÈÜÂ _x0000_DÅ¬¹·\¸ _x0000_5_x0000_5_x0000_ _x0000_-_x0000_8_x0000_1_x0000_ _x0000_(_x0000__x0008_®_x000C_ÍÙ³,_x0000_ _x0000__x000C_ÓüÈ_x0008_®_x000C_ÍXÕ_x0018_ÂÌ¬¹¥Ç)_x0000__x000C__x0000__x0001__x000C_ÓüÈÜÂ _x0000_0¼Ü´ü»4Ñ_x0004_È©Æl­¥Ç_x000D__x0000__x0000_010-9129-1126_x0017__x0000__x0000_leesjun1024@hanmail.net_x000E__x0000__x0000_37690004547137_x0006__x0000__x0000_D00183_x0003__x0000__x0001_T³_x001C_È|Ç
+_x0000__x0000_1171558537_x0003__x0000__x0001_iÖÐÆ Á_x000B__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_XÇX¹,_x0000_¡ÇTÖ_x0008__x0000__x0000_20141027_x000D__x0000__x0000_010-6333-2457	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_ÅÌl­_x0005__x0000__x0000_08078 _x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_ÅÌl­ _x0000_àÂ_x0015_È\¸ _x0000_2_x0000_7_x0000_5_x0000_ _x0000_ _x0000_(_x0000_àÂ_x0015_ÈÙ³,_x0000_ _x0000_àÂ¸Ò¬¹DÅ_x000C_Ó¸Ò)_x0000__x0010__x0000__x0001_ÁÀ_x0000_¬Ù³ _x0000_1_x0000_5Î _x0000_1_x0000_0_x0000_4_x0000_,_x0000_ _x0000_1_x0000_0_x0000_5_x0000_8Ö_x0011__x0000__x0000_thejeil@naver.com_x000D__x0000__x0000_010-9668-2210_x000E__x0000__x0000_37690004550437_x0006__x0000__x0000_D00184_x0005__x0000__x0001_$Æ¨°¤ÂìÓ Î
+_x0000__x0000_1322489384_x0003__x0000__x0001_Å+È¨º_x000D__x0000__x0001_´ÆÙ³0®l­©ÆÔ _x0000_aÅ8Á_x001C_Á¬¹ _x0000_xÆ_x0008__x0000__x0000_20141028
+_x0000__x0000_0315756464
+_x0000__x0000_0315755600_x0008__x0000__x0001_½¬0®Ä³ _x0000_¨°ÅüÈÜÂ_x0006__x0000__x0000_472881_x0016__x0000__x0001_½¬0®Ä³ _x0000_¨°ÅüÈÜÂ _x0000_ÄÉt¬$Æ¨°\¸ _x0000_8_x0000_0_x0000_6_x0000_ _x0000_-_x0000_1_x0000_4_x0000__x000D__x0000__x0000_010-9289-9637_x0012__x0000__x0000_jongmo83@naver.com_x000E__x0000__x0000_37690004552737_x0006__x0000__x0000_D00186_x0005__x0000__x0001_ä¹XÎìÓxÇ¸Ò
+_x0000__x0000_6091853217_x0003__x0000__x0001_iÖ­ÝÂ_x0008__x0000__x0000_20141202_x000C__x0000__x0000_055-298-7330_x0005__x0000__x0000_51378_x0011__x0000__x0001_½¬¨° _x0000_=ÌÐÆÜÂ _x0000_XÇ=Ìl­ _x0000__x0018_¼Ä¬\¸ _x0000_6_x0000_3_x0000__x000D__x0000__x0000_010-3561-0209_x000E__x0000__x0000_o2bbi@nate.com_x0008__x0000__x0000_20141212_x000E__x0000__x0000_37690004554037_x0006__x0000__x0000_D00190_x0005__x0000__x0001_p­°À¤ÂìÓ Î
+_x0000__x0000_4010657765_x0003__x0000__x0001__x0015_¼_x001C_Âl×	_x0000__x0001_¤ÂìÓ ÎXÇX¹,_x0000_ _x0000_©ÆÔ_x0008__x0000__x0000_20150406_x000D__x0000__x0000_010-9977-7141_x0008__x0000__x0001__x0004_È|·½Ä³ _x0000_p­°ÀÜÂ_x0005__x0000__x0000_54102_x000F__x0000__x0001__x0004_È½ _x0000_p­°ÀÜÂ _x0000_¨°_x0018_Â¡Á5_x0000_8® _x0000_4_x0000_2_x0000__x000F__x0000__x0001_1_x0000_0_x0000_1_x0000_8Ö(_x0000__x0018_Â¡ÁÙ³,_x0000_ _x0000_(Ì$Æ¹L¾)_x0000__x0013__x0000__x0000_shp7141@hanmaiL.net_x000E__x0000__x0000_37690004558537_x0006__x0000__x0000_D00192
+_x0000__x0001__x0001_Æ8»¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1222039517_x0005__x0000__x0001__x0001_Æ8»¤ÂìÓ Î_x0003__x0000__x0001_@®_x0001_Æ8»_x0008__x0000__x0000_20150608_x000C__x0000__x0000_032-523-1406_x000C__x0000__x0000_032-517-8009	_x0000__x0001_xÇÌ_x0011_­íÅÜÂ _x0000_½ÉÓl­_x0005__x0000__x0000_21337_x000D__x0000__x0000_010-4320-1406_x0012__x0000__x0000_YM1406@hanmail.net_x0007__x0000__x0001_A_x0000_ñ´	®(_x0000_T_x0000_S_x0000_)_x0000__x0005__x0000__x0000_13042_x0003__x0000__x0001_@®Ù³½¬_x000E__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_+_x0000_3_x0000_0_x0000__x000E__x0000__x0000_37690004561837_x0006__x0000__x0000_D00193_x000B__x0000__x0001_ÑÐ¤Â@Õ¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1320972497_x0006__x0000__x0001_ÑÐ¤Â@Õ¤ÂìÓ Î_x0003__x0000__x0001__x0015_¼_x0004_Ö=Ì_x0006__x0000__x0001_´ÆÙ³_x0004_È8»©ÆÔ_x0008__x0000__x0000_20150610_x000D__x0000__x0000_010-3706-2477_x0007__x0000__x0001_½¬0®Ä³ _x0000_l­¬¹ÜÂ_x0005__x0000__x0000_11907_x000F__x0000__x0001_½¬0® _x0000_l­¬¹ÜÂ _x0000_UÆ_x0019_ÂÌ\¸ _x0000_5_x0000_0_x0000_7_x0000_	_x0000__x0001_3_x0000_5Î _x0000_ÑÐ¤Â@Õ¤ÂìÓ Î_x000F__x0000__x0000_pspin@naver.com_x0005__x0000__x0000_22022_x0003__x0000__x0001_HÅ°ÆÄÉ_x000C__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_7_x0000_._x0000_5_x0000__x000E__x0000__x0000_37690004560137_x0006__x0000__x0000_D00195
+_x0000__x0001_¤ÂìÓ ÎLÑlÐ(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_6172249744_x0005__x0000__x0001_¤ÂìÓ ÎLÑlÐ_x0003__x0000__x0001_tÇÝÐ0®_x0006__x0000__x0001__x001C_ÈpÈÅÅ _x0000_Áä¹_x000C__x0000__x0001_õ¬_x0008_Æ _x0000_¤ÂìÓ Î©ÆÔ,_x0000_ _x0000_¡ÇTÖ_x000B__x0000__x0000_051-7564800_x000C__x0000__x0000_051-756-4801_x0005__x0000__x0000_48222_x0017__x0000__x0001_½°À_x0011_­íÅÜÂ _x0000_Ù³·l­ _x0000_+ÈiÕ´ÆÙ³¥Ç\¸ _x0000_4_x0000_0_x0000_¼8® _x0000_8_x0000_'_x0000__x0001_1_x0000_0_x0000_3_x0000_Ù³ _x0000_1_x0000_0_x0000_5_x0000_8Ö,_x0000_1_x0000_0_x0000_6_x0000_8Ö(_x0000_¬ÀÁÉÙ³,_x0000_½°À _x0000_DÅÜÂDÅÜ´ _x0000_TÏ$Æq¸ _x0000_XÕ²DÌ _x0000_DÅ_x000C_Ó¸Ò)_x0000__x000D__x0000__x0000_010-5578-1988_x0015__x0000__x0000_ltktennis@hanmail.net_x000B__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_8_x0000__x0008__x0000__x0000_20150611_x000E__x0000__x0000_37690004562437_x0006__x0000__x0000_D00196	_x0000__x0001__x0015_¬¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_5041920932_x0004__x0000__x0001__x0015_¬¤ÂìÓ Î_x0003__x0000__x0001__x0015_¬@Çl­_x000D__x0000__x0001_LÑÈ²¤Â©ÆÔ,_x0000_ _x0000_XÇX¹,_x0000_ _x0000_àÂ_x001C_¼_x000C__x0000__x0000_053-314-9090_x0005__x0000__x0000_41433_x000D__x0000__x0000_010-3828-0474_x0013__x0000__x0000_keg0417@hanmail.net_x000D__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_6_x0000_+_x0000_1_x0000_5_x0000__x0008__x0000__x0000_20150612_x000E__x0000__x0000_37690004565337_x0006__x0000__x0000_D00199
+_x0000__x0001_P´¬¹¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1283008985_x0003__x0000__x0001_@®_x0001_Æ Á_x000B__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_¤ÂìÓ ÎXÇX¹_x0008__x0000__x0000_20150703_x000C__x0000__x0000_031-911-4191_x000C__x0000__x0000_031-913-0067_x0006__x0000__x0000_410829_x000F__x0000__x0001_½¬0®Ä³à¬ÅÜÂ _x0000_|Ç°ÀÙ³l­_x0015_È_x001C_¼°ÀÙ³_x000E__x0000__x0001_1_x0000_1_x0000_4_x0000_8_x0000_-_x0000_1_x0000_3_x0000_ _x0000_1_x0000_5Î2_x0000_,_x0000_3_x0000_8Ö_x000D__x0000__x0000_010-4288-3563_x0012__x0000__x0000_usop2n@hanmail.net_x000D__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_6_x0000_+_x0000_2_x0000_3_x0000__x000E__x0000__x0000_37690004568237_x0006__x0000__x0000_D00201_x000E__x0000__x0001_(_x0000_üÈ)_x0000_¤ÂtÎtÇ¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_6278102573_x000B__x0000__x0001_¤ÂtÎtÇ¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000__x0003__x0000__x0001_@®1ÁÐÆ_x0006__x0000__x0001_Áä¹ÅÅ _x0000_Ä³ä¹_x0008__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_ä¹_x0010_È_x000C__x0000__x0000_041-566-1879_x000C__x0000__x0000_041-554-2732_x0005__x0000__x0000_31157"_x0000__x0001_©Í­Ì¨°Ä³ _x0000_ÌHÅÜÂ _x0000__x001C_Á½l­ _x0000_1¼_x001D_Á3_x0000_\¸ _x0000_2_x0000_9_x0000_ _x0000_ _x0000_(_x0000_1¼_x001D_ÁÙ³,_x0000_ _x0000_½¶É¹_x0008_Ã%¼)_x0000__x000D__x0000__x0000_010-4513-1879_x0011__x0000__x0000_kimsw000@nate.com_x000E__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_4_x0000_0_x0000_+_x0000_2_x0000_0_x0000__x0008__x0000__x0000_20150804_x000E__x0000__x0000_37690004570937_x0006__x0000__x0000_D00202_x0008__x0000__x0001_¤ÂìÓå²(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_3052275067_x0003__x0000__x0001_HÅü­¹Â_x000C__x0000__x0000_042-522-9566_x000C__x0000__x0000_042-271-4786_x0006__x0000__x0000_300810_x0017__x0000__x0001__x0000_³_x0004_È_x0011_­íÅÜÂ _x0000__x0011_Él­ _x0000_Ù³_x001C_Á_x0000_³\¸ _x0000_1_x0000_2_x0000_0_x0000_1_x0000_(_x0000_ÜÐÉÓÙ³)_x0000__x0007__x0000__x0001_¤ÂìÓå² _x0000_ÜÐÉÓ_x0010_È_x000B__x0000__x0000_01062224787_x0010__x0000__x0000_spodaq@naver.com_x000D__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_5_x0000_+_x0000_3_x0000_3_x0000__x0008__x0000__x0000_20150805_x000E__x0000__x0000_37690004571537_x0006__x0000__x0000_D00203	_x0000__x0001_ðÅTÏ¬¹DÅ(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_2041477980_x0004__x0000__x0001_ðÅTÏ¬¹DÅ_x0003__x0000__x0001_@®ÁÀ0®_x0006__x0000__x0001_Ä³Áä¹ _x0000_t¬$Á_x000D__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_´Ì!ÇÜÂ_x001C_Á&lt;»$ÁXÎ_x0008__x0000__x0000_20150806_x000C__x0000__x0000_02-3390-4345_x000C__x0000__x0000_02-3390-4344
+_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_Ù³_x0000_³8»l­_x0005__x0000__x0000_02496_x0011__x0000__x0001__x001C_Á¸Æ _x0000_Ù³_x0000_³8»l­ _x0000_Ý¹°Æ\¸1_x0000_2_x0000_8® _x0000_1_x0000_9_x0000__x000B__x0000__x0001_1_x0000_5Î _x0000_XÕtÇÐÆ¤ÂìÓ Î°ÀÅÅ_x000D__x0000__x0000_010-9089-5363_x0017__x0000__x0000_01090895363@hanmail.net_x000B__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_2_x0000_0_x0000__x000E__x0000__x0000_37690004572137_x0006__x0000__x0000_D00205_x0005__x0000__x0001_ÁLÑ¤ÂìÓ Î
+_x0000__x0000_1971301851_x0003__x0000__x0001_@®_x0001_Æ_x0018_Â_x0008__x0000__x0001_Ä³Áä¹ÅÅ _x0000_Ä³ä¹ÅÅ	_x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_4»íÅÅÅ_x000B__x0000__x0000_01063388568_x0008__x0000__x0001_½¬0®Ä³ _x0000_XÇ_x0015_È½ÜÂ_x0005__x0000__x0000_11806!_x0000__x0001_½¬0®Ä³ _x0000_XÇ_x0015_È½ÜÂ _x0000_$Æ©º\¸ _x0000_1_x0000_7_x0000_0_x0000_ _x0000_°Àä´È¹DÇ _x0000_DÅ_x000C_Ó¸Ò _x0000_4_x0000_1_x0000_2_x0000_-_x0000_7_x0000_0_x0000_6_x0000__x000D__x0000__x0000_010-6338-8568_x0011__x0000__x0000_3388568@naver.com_x0005__x0000__x0000_26002_x0003__x0000__x0001__x0015_¬ÜÐ8Ö_x0008__x0000__x0000_20220901_x000E__x0000__x0000_37690004700437_x0006__x0000__x0000_D00209_x0018__x0000__x0001_¤ÂìÓ Î_x000C_Õì·¤Â(_x0000_S_x0000_p_x0000_o_x0000_r_x0000_t_x0000_s_x0000_ _x0000_P_x0000_l_x0000_u_x0000_s_x0000_)_x0000_(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1192167071_x0003__x0000__x0001__x0015_¬ÜÂ¨º_x0006__x0000__x0001_Ä³Áä¹ _x0000_LÇÝÂ_x0008__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_\ÕÝÂ_x000B__x0000__x0000_02-871-5513	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x0000_­EÅl­_x0005__x0000__x0000_08750_x000F__x0000__x0001__x001C_Á¸Æ _x0000__x0000_­EÅl­ _x0000_àÂ¼¹\¸3_x0000_8® _x0000_4_x0000_0_x0000__x0005__x0000__x0001_ÀÉXÕ _x0000_1_x0000_5Î_x000D__x0000__x0000_010-7703-5353_x001A__x0000__x0000_tennisplus0122@esero.go.krX_x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_ _x0000_/_x0000_ _x0000_2_x0000_5_x0000_S_x0000_S_x0000_ _x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_ _x0000_/_x0000_ _x0000_2_x0000_4_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_9_x0000_._x0000_6_x0000_ _x0000_/_x0000_ _x0000_2_x0000_4_x0000_S_x0000_S_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_ _x0000_/_x0000_ _x0000_2_x0000_3_x0000_F_x0000_W_x0000_ _x0000__x0018_ÂüÈ _x0000_ìÅàÂ _x0000_ _x0000_1_x0000_2_x0000_ _x0000_(_x0000_ô²ù²Ç _x0000_Æ­Ì&lt;Ç\¸ _x0000_6_x0000_ _x0000__x0018_¼_x0001_Æ)_x0000__x0008__x0000__x0000_20160114_x000E__x0000__x0000_37690004577337_x0006__x0000__x0000_D00210_x0011__x0000__x0001_(_x0000_üÈ)_x0000_ÐÅtÇ_x001C_ÈtÇxÇ0Ñ´°TÁ °(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1268641398_x000C__x0000__x0000_031-761-8980_x000C__x0000__x0000_031-761-2140_x0005__x0000__x0000_12769_x000D__x0000__x0000_010-4552-3318	_x0000__x0000_1800-6142_x000E__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_4_x0000_0_x0000_+_x0000_2_x0000_5_x0000__x0008__x0000__x0000_20160121_x000E__x0000__x0000_37690004578037_x0006__x0000__x0000_D00256	_x0000__x0001_p¬1Á¤ÂìÓ Î(_x0000_Å°À)_x0000_
+_x0000__x0000_6210808090_x0003__x0000__x0001__x0015_È+È_x0015_¬_x0006__x0000__x0001_Ä³Áä¹ _x0000__x001C_ÈpÈ_x000B__x0000__x0001_ìÕ¤Â0®l­,_x0000_ _x0000_¤ÂìÓ Î©ÆÔ_x0008__x0000__x0000_20160412_x000C__x0000__x0000_055-387-3613_x000C__x0000__x0000_055-387-3615_x0008__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_Å°ÀÜÂ_x0005__x0000__x0000_50621 _x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_Å°ÀÜÂ _x0000__x001C_Á|ÇÙ³\¸ _x0000_2_x0000_5_x0000_ _x0000_ _x0000_(_x0000__x0011_É½Ù³,_x0000_ _x0000_$Ç ÁÝÀ_x0001_Æ´ÅP­äÂ)_x0000__x000D__x0000__x0000_010-2390-2994_x0013__x0000__x0000_dhrhr68@hanmail.netH_x0000__x0001_2_x0000_4_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_3_x0000_5_x0000_ _x0000_/_x0000_2_x0000_4_x0000_S_x0000_S_x0000__x0018_ÂüÈìÅàÂ _x0000_3_x0000_5_x0000_ _x0000_/_x0000_ _x0000_2_x0000_3_x0000_F_x0000_W_x0000_ _x0000__x0018_ÂüÈ _x0000_ìÅàÂ _x0000_3_x0000_5_x0000_ _x0000_/_x0000_ _x0000_2_x0000_3_x0000_S_x0000_S_x0000_ _x0000__x0018_ÂüÈ _x0000_ìÅàÂ _x0000_3_x0000_5_x0000_(_x0000_|·_x0013_Ï+_x0000_È¹D¾¤Â _x0000_9_x0000_4_x0000_3_x0000_,_x0000_2_x0000_5_x0000_0_x0000_)_x0000__x0008__x0000__x0000_20160407_x000E__x0000__x0000_37690004581237_x0006__x0000__x0000_D00267_x0006__x0000__x0001__x001C_ÈtÇD¾¤ÂìÓ Î
+_x0000__x0000_6664100083_x0003__x0000__x0001_Ç_x0015_È\Õ_x000D__x0000__x0001_Ä³ä¹ _x0000__x000F_¼ _x0000_Áä¹ÅÅ,_x0000_ _x0000__x001C_ÁD¾¤Â_x000C__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_ _x0000__x0011_­à¬_x0000_³ÕÅÅ_x0008__x0000__x0000_20160610_x000C__x0000__x0000_062-523-7451_x000C__x0000__x0000_062-523-7455_x0005__x0000__x0000_62023_x000D__x0000__x0001__x0011_­üÈ _x0000__x001C_Ál­ _x0000_´ÆÌ\¸ _x0000_1_x0000_2_x0000_2_x0000__x0005__x0000__x0001_(_x0000__x000D_Ã_x000C_ÍÙ³)_x0000__x000D__x0000__x0000_010-4606-4538_x0015__x0000__x0000_jhrim1226@hanmail.net_x0008__x0000__x0000_20160601_x000E__x0000__x0000_37690004584137_x0006__x0000__x0000_D00280_x0005__x0000__x0001_Ä³ô²¤ÂìÓ Î
+_x0000__x0000_3071042161_x0003__x0000__x0001_$ÇÙ³ÝÂ_x000B__x0000__x0001_Ä³ä¹_x000F_¼ _x0000_Áä¹ÅÅ _x0000_Áä¹ÅÅ_x0010__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_Ç_x0004_Èp¬ _x0000__x0010_Óä¹,_x0000_ _x0000__x0000_³ìÅ_x0008__x0000__x0000_20160825_x000C__x0000__x0000_044-863-8908_x000C__x0000__x0000_044-863-8970_x000F__x0000__x0001_8Á+È¹ÒÄ¼ÇXÎÜÂ _x0000_8Á+È¹ÒÄ¼ÇXÎÜÂ_x0005__x0000__x0000_30102_x001E__x0000__x0001_8Á+È¹ÒÄ¼ÇXÎÜÂ _x0000__x0008_È¬Ç\¸ _x0000_1_x0000_7_x0000_2_x0000_ _x0000_(_x0000_´ÅÄÉÙ³,_x0000_ _x0000_ÜÐ\Õ_x0004_Õ_x0008_¸¤Â&lt;Á0Ñ)_x0000__x0004__x0000__x0001_1_x0000_0_x0000_1_x0000_8Ö_x000D__x0000__x0000_010-7185-8008_x0015__x0000__x0000_dodamsports@naver.com_x000E__x0000__x0000_37690004586437_x0006__x0000__x0000_D00282_x0005__x0000__x0001__x0004_²¬¹¤ÂìÓ Î
+_x0000__x0000_1082124505_x0003__x0000__x0001_@®l×_x0015_È_x0006__x0000__x0001_Áä¹ _x0000_Ä³Áä¹_x000C__x0000__x0001__x0004_ÈÇÁÀp¬·ÅÅ _x0000_0¼Ü´ü»4Ñ _x0000__x000B__x0000__x0000_02-848-6291_x000B__x0000__x0000_02-848-7556
+_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x0001_Æñ´ìÓl­_x0005__x0000__x0000_07375_x000E__x0000__x0001__x001C_Á¸Æ _x0000__x0001_Æñ´ìÓl­ _x0000_Ä³àÂ\¸ _x0000_5_x0000_1_x0000__x000D__x0000__x0001_1_x0000_5Î _x0000_1_x0000_0_x0000_5_x0000_8Ö(_x0000_¡ÁU³L¾)µ)_x0000__x000D__x0000__x0000_010-8393-6291_x0013__x0000__x0000_hee00jung@naver.com_x0008__x0000__x0000_20160905_x000E__x0000__x0000_37690004588737_x0006__x0000__x0000_D00286_x0007__x0000__x0001_Æ%±¤Â _x0000_1Á¨°_x0010_È
+_x0000__x0000_2603001743_x0003__x0000__x0001_MÖ¥Ç8Ö_x0008__x0000__x0001_Ä³ä¹ _x0000__x000F_¼ _x0000_Áä¹ÅÅ_x0008__x0000__x0000_20151218_x000C__x0000__x0000_031-755-7257_x0007__x0000__x0001_½¬0®Ä³ _x0000_1Á¨°ÜÂ_x0005__x0000__x0000_13110_x001E__x0000__x0001_½¬0®Ä³ _x0000_1Á¨°ÜÂ _x0000__x0018_Â_x0015_Èl­ _x0000_1Á¨°_x0000_³\¸ _x0000_1_x0000_2_x0000_6_x0000_7_x0000_ _x0000_-_x0000_1_x0000_ _x0000_(_x0000_ÜÐÉÓÙ³)_x0000__x000D__x0000__x0000_010-7191-7257_x0012__x0000__x0000_nero1016@naver.com_x0002__x0000__x0001_¨°¸Ó_x0008__x0000__x0000_2016110</v>
+          </cell>
+          <cell r="H38" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="I38" t="e">
+            <v>#N/A</v>
           </cell>
           <cell r="J38" t="str">
             <v>스포츠용품</v>
           </cell>
-          <cell r="K38" t="str">
-            <v>20070309</v>
+          <cell r="K38" t="e">
+            <v>#N/A</v>
           </cell>
           <cell r="L38" t="str">
             <v/>
           </cell>
-          <cell r="M38" t="str">
-            <v>02-824-8799</v>
-          </cell>
-          <cell r="N38" t="str">
-            <v>02-824-8799</v>
-          </cell>
-          <cell r="O38" t="str">
-            <v>서울특별시 동작구</v>
-          </cell>
-          <cell r="P38" t="str">
-            <v>06921</v>
+          <cell r="M38" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="N38" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="O38" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="P38" t="e">
+            <v>#N/A</v>
           </cell>
           <cell r="Q38" t="str">
-            <v>서울 동작구 만양로1길 3</v>
-          </cell>
-          <cell r="R38" t="str">
-            <v>지층 (상도동)</v>
-          </cell>
-          <cell r="S38" t="str">
-            <v>010-2942-3235</v>
-          </cell>
-          <cell r="T38" t="str">
-            <v>sejinsports2018@naver.com</v>
+            <v>om_x000E__x0000__x0000_37690004497037_x0006__x0000__x0000_D00110_x0007__x0000__x0001_Æ%±¤Â _x0000_TÖ_x001C_Â_x0010_È
+_x0000__x0000_4080577085_x0003__x0000__x0001__x0004_È+º_x0019_Â_x0008__x0000__x0000_20071102_x000C__x0000__x0000_061-375-6647_x0008__x0000__x0001__x0004_È|·¨°Ä³ _x0000_TÖ_x001C_Âp­_x0006__x0000__x0000_519809_x0014__x0000__x0001__x0004_È|·¨°Ä³ _x0000_TÖ_x001C_Âp­ _x0000__x0011_­U³\¸ _x0000_1_x0000_4_x0000_0_x0000_ _x0000_ _x0000_1_x0000_5Î_x000D__x0000__x0000_010-6632-5893_x0012__x0000__x0000_ms-jon@hanmeil.net_x000E__x0000__x0000_37690004498637_x0006__x0000__x0000_D00111_x000C__x0000__x0001_,Æ¼¹=Õ+ÈiÕ¤ÂìÓ Î(_x0000_©ºìÓ)_x0000_
+_x0000__x0000_4111469486_x0003__x0000__x0001_@®=Ì©Æ_x000C__x0000__x0001_´ÆÙ³©ÆÔ,_x0000_ñ´°Àl­,_x0000_0®P±Ô_x0008__x0000__x0000_20070320_x000C__x0000__x0000_061-242-1032
+_x0000__x0000_0612443032_x0008__x0000__x0001__x0004_È|·¨°Ä³ _x0000_©ºìÓÜÂ_x0005__x0000__x0000_58726_x0010__x0000__x0001__x0004_È¨° _x0000_©ºìÓÜÂ _x0000_(Ì¼_x001D_Á8® _x0000_4_x0000_1_x0000_-_x0000_1_x0000__x0002__x0000__x0001_1_x0000_5Î_x000D__x0000__x0000_010-9243-4285_x0010__x0000__x0000_eyebono@daum.net_x000E__x0000__x0000_37690004499237_x0006__x0000__x0000_D00116_x000F__x0000__x0001_Æ%±¤ÂÈ¹°À_x0000_³¬¹_x0010_È(_x0000_ü»4Ñ¤ÂìÓ Î)_x0000_
+_x0000__x0000_6080288027_x0003__x0000__x0001_ Ç_x0001_Æ_x0019_Â_x0008__x0000__x0001_¤ÂìÓ Î©ÆÔ_x000F_¼XÇX¹_x000C__x0000__x0000_055-222-5431
+_x0000__x0000_0552225432_x0008__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_=ÌÐÆÜÂ_x0006__x0000__x0000_631852_x0018__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_=ÌÐÆÜÂ _x0000_È¹°ÀiÕìÓl­ _x0000_©ÆÈ¹\¸ _x0000_7_x0000_6_x0000_ _x0000_üÈÝÐ_x000D__x0000__x0000_010-3707-6245_x0016__x0000__x0000_dudtjs6245@hanmail.net_x000E__x0000__x0000_37690004504337_x0006__x0000__x0000_D00120_x0006__x0000__x0001_Æ%±¤Â­ÌüÈ_x0010_È
+_x0000__x0000_3170385854_x0003__x0000__x0001_\Í°Æ1Á_x000B__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_XÇX¹,_x0000__x0018_Ât¬_x0008__x0000__x0000_20110729_x000C__x0000__x0000_043-222-3040
+_x0000__x0000_0432245050_x0008__x0000__x0001_©Í­Ì½Ä³ _x0000_­ÌüÈÜÂ_x0006__x0000__x0000_361842_x0012__x0000__x0001_©Í½ _x0000_­ÌüÈÜÂ _x0000_ÁÀù²l­ _x0000_8Öø»\¸ _x0000_2_x0000_0_x0000_6_x0000__x0005__x0000__x0001_1_x0000_5Î _x0000_È!Î_x000D__x0000__x0000_010-5468-3319_x0015__x0000__x0000_wsung3525@hanmail.net_x0008__x0000__x0000_20080429_x000E__x0000__x0000_37690004507237_x0006__x0000__x0000_D00121_x000D__x0000__x0001_Æ%±¤ÂìÓmÕ_x0010_È(_x0000_XÕtÇlÐ¬¹´Å)_x0000_
+_x0000__x0000_5061736246_x0003__x0000__x0001__x0015_È@Ç_x0001_Æ_x0008__x0000__x0000_20090227_x000C__x0000__x0000_054-283-5234
+_x0000__x0000_0542835231_x0008__x0000__x0001_½¬ÁÀ½Ä³ _x0000_ìÓmÕÜÂ_x0006__x0000__x0000_790822_x0012__x0000__x0001_½¬½ _x0000_ìÓmÕÜÂ _x0000_¨°l­ _x0000__x0000_³Ä³Ù³ _x0000_8_x0000_6_x0000_-_x0000_2_x0000__x000D__x0000__x0000_010-4133-7770_x0014__x0000__x0000_minton1125@naver.com_x0008__x0000__x0000_20081105_x000E__x0000__x0000_37690004508937_x0006__x0000__x0000_D00122_x0005__x0000__x0001_°Æ¬¹¤ÂìÓ Î
+_x0000__x0000_4172105493_x0003__x0000__x0001__x0015_¼_x0018_ÂÄÉ_x0008__x0000__x0000_20180101_x000C__x0000__x0000_051-632-2681
+_x0000__x0000_0516322681_x0008__x0000__x0001_½°À_x0011_­íÅÜÂ _x0000_¨°l­_x0006__x0000__x0000_608827_x0011__x0000__x0001_½°À_x0011_­íÅÜÂ _x0000_¨°l­ _x0000_Ç ÇÉÓTÖ\¸ _x0000_4_x0000_9_x0000__x000D__x0000__x0000_010-2594-2682_x0015__x0000__x0000_moxie2000@hanmail.net_x000E__x0000__x0000_37690004509537_x0006__x0000__x0000_D00123_x0005__x0000__x0001_°Æ1Á¤ÂìÓ Î
+_x0000__x0000_2077003708_x0003__x0000__x0001_@®DÆÝÂ_x0008__x0000__x0000_20071009_x000B__x0000__x0000_02-465-1297	_x0000__x0000_024651197	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x0011_­ÄÉl­_x0006__x0000__x0000_143961_x0010__x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x0011_­ÄÉl­ _x0000_l­XÇ\¸ _x0000_6_x0000_6_x0000__x0014__x0000__x0001_1_x0000_5Î _x0000_(_x0000_l­XÇÙ³ _x0000_2_x0000_2_x0000_7_x0000_-_x0000_6_x0000_)_x0000_ _x0000_°Æ1Á¤ÂìÓ Î_x000D__x0000__x0000_010-3418-1230_x000F__x0000__x0000_ws418@naver.com_x000E__x0000__x0000_37690004510537_x0006__x0000__x0000_D00126_x0005__x0000__x0001_ÐÆÙ³´Ì!Ç¬À
+_x0000__x0000_3060363748_x0003__x0000__x0001_ü»Ñ¼ÁÉ_x0004__x0000__x0001_´ÆÙ³0®l­_x0008__x0000__x0000_20050705_x000C__x0000__x0000_042-531-4004
+_x0000__x0000_0425328899_x0008__x0000__x0001__x0000_³_x0004_È_x0011_­íÅÜÂ _x0000_Ù³l­_x0005__x0000__x0000_34630_x000D__x0000__x0001__x0000_³_x0004_È _x0000_Ù³l­ _x0000__x0000_³_x0004_È\¸ _x0000_7_x0000_6_x0000_5_x0000__x000D__x0000__x0000_010-5453-9536_x0012__x0000__x0000_wonspo@hanmail.net_x0008__x0000__x0000_20080214_x000E__x0000__x0000_37690004511137_x0006__x0000__x0000_D00127_x0008__x0000__x0001_ÐÆ¤ÂìÓ Î(_x0000__x001C_ÈüÈ)_x0000_
+_x0000__x0000_6160962051_x0003__x0000__x0001_@®ø»½¬_x000C__x0000__x0000_064-752-4422
+_x0000__x0000_0647232992_x000C__x0000__x0001__x001C_ÈüÈ¹ÒÄ¼ÇXÎÄ³ _x0000__x001C_ÁÀ­ìÓÜÂ_x0006__x0000__x0000_690161_x0013__x0000__x0001__x001C_ÈüÈ¹ÒÄ¼ÇXÎÄ³ _x0000__x001C_ÈüÈÜÂ _x0000_$Æ|·\¸ _x0000_1_x0000_3_x0000_4_x0000__x000D__x0000__x0000_010-4416-4412_x0015__x0000__x0000_crony0104@hanmail.net_x000E__x0000__x0000_37690004512837_x0006__x0000__x0000_D00132_x0005__x0000__x0001__x0004_ÈüÈÆ%±¤Â
+_x0000__x0000_4020887887_x0003__x0000__x0001_tÇ_x001C_Â+È_x000C__x0000__x0000_063-274-9337
+_x0000__x0000_0632789337_x0008__x0000__x0001__x0004_È|·½Ä³ _x0000__x0004_ÈüÈÜÂ_x0006__x0000__x0000_560080_x0013__x0000__x0001__x0004_È|·½Ä³ _x0000__x0004_ÈüÈÜÂ _x0000_DÆ°Àl­ _x0000_õ¬½\¸ _x0000_2_x0000_0_x0000__x000D__x0000__x0000_010-9224-8391_x0010__x0000__x0000_jyonex@naver.com_x000E__x0000__x0000_37690004516337_x0006__x0000__x0000_D00136_x0005__x0000__x0001__x001C_È|Ç¤ÂìÓ Î
+_x0000__x0000_4040533542_x000B__x0000__x0001__x001C_È|Ç_x0008_¸_x0000_È¤ÂìÓ Î(_x0000__x0015_ÈMÇ)_x0000__x0003__x0000__x0001_@®_x0011_­õ¼	_x0000__x0001_´ÆÙ³0®l­_x000F_¼´ÆÙ³õ¼xÆ_x000C__x0000__x0000_063-535-9146
+_x0000__x0000_0635332093_x0008__x0000__x0001__x0004_È|·½Ä³ _x0000__x0015_ÈMÇÜÂ_x0006__x0000__x0000_580804_x000F__x0000__x0001__x0004_È|·½Ä³ _x0000__x0015_ÈMÇÜÂ _x0000__x0011_ÉYÅ\¸ _x0000_8_x0000_3_x0000__x000D__x0000__x0000_010-9579-7800_x0016__x0000__x0000_sports9146@hanmaIl.net_x000E__x0000__x0000_37690004520237_x0006__x0000__x0000_D00137_x000B__x0000__x0001_üÈÝÂÖ¬À _x0000_0¼Ü´ü»4ÑÈ¹¸Ò
+_x0000__x0000_1108193203_x0003__x0000__x0001__x0015_ÈtÇ@±_x000B__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000__x0004_ÈÇÁÀp¬·_x0008__x0000__x0000_20130723_x000C__x0000__x0000_031-964-3530	_x0000__x0000_023829555_x0007__x0000__x0001_½¬0®Ä³ _x0000_à¬ÅÜÂ_x0005__x0000__x0000_10564_x0011__x0000__x0001_½¬0® _x0000_à¬ÅÜÂ _x0000_U³Ål­ _x0000_¼À¡Á\¸ _x0000_1_x0000_2_x0000__x0007__x0000__x0001_4_x0000_5Î _x0000_4_x0000_1_x0000_8_x0000_8Ö_x000D__x0000__x0000_010-7152-7538_x0014__x0000__x0000_mintonmart@naver.com_x000E__x0000__x0000_37690004521937_x0006__x0000__x0000_D00138	_x0000__x0001_üÈÝÂÖ¬ÀÙ³°Æ¤ÂìÓ Î
+_x0000__x0000_1108180426_x0003__x0000__x0001_¡Á_x0015_È|Ç_x000B__x0000__x0000_02-382-3598	_x0000__x0000_023553586	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_@ÇÉÓl­_x0006__x0000__x0000_122903_x0018__x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_@ÇÉÓl­ _x0000_ðÅ_x001C_Á\¸ _x0000_2_x0000_9_x0000_-_x0000_1_x0000_ _x0000_Ù³°Æ¤ÂìÓ Î_x000D__x0000__x0000_010-2018-3598_x0012__x0000__x0000_dvip1233@naver.com_x000B__x0000__x0000_01074353598
+_x0000__x0001__x0018_Â_x0008_® _x0000_½qÈ&lt;Ç\¸ _x0000_µÑ_x001C_È_x000E__x0000__x0000_37690004522537_x0006__x0000__x0000_D00141	_x0000__x0001__x0011_ÉYÅ¤ÂìÓ Î(_x0000_½¬üÈ)_x0000_
+_x0000__x0000_3226600323_x0003__x0000__x0001_iÖ_x0001_ÆäÂ_x0008__x0000__x0000_20081210_x000C__x0000__x0000_054-741-5177_x0008__x0000__x0001_½¬ÁÀ½Ä³ _x0000_½¬üÈÜÂ_x0006__x0000__x0000_780943_x0012__x0000__x0001_½¬ÁÀ½Ä³ _x0000_½¬üÈÜÂ _x0000__x0008_®1Á\¸ _x0000_2_x0000_9_x0000_4_x0000_-_x0000_1_x0000__x000D__x0000__x0000_010-7579-5177_x0014__x0000__x0000_jasp6304@hanmail.net_x0008__x0000__x0000_20081211_x000E__x0000__x0000_37690004525437_x0006__x0000__x0000_D00145_x0005__x0000__x0001_­Ìá¸¤ÂìÓ Î
+_x0000__x0000_6150796307_x0003__x0000__x0001_pÈø»_x0019_Â_x0008__x0000__x0000_20101004_x000C__x0000__x0000_055-312-9559
+_x0000__x0000_0553129560_x0008__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_@®tÕÜÂ_x0006__x0000__x0000_621833_x0012__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_@®tÕÜÂ _x0000_¥Ç Ç\¸ _x0000_2_x0000_9_x0000_7_x0000_-_x0000_5_x0000__x000D__x0000__x0000_010-9513-9559_x0016__x0000__x0000_jms3129559@hanmail.net_x0008__x0000__x0000_20101019_x000E__x0000__x0000_37690004530037_x0006__x0000__x0000_D00148_x0007__x0000__x0001__x0000_ÏtÇdÅD¾¤ÂìÓ Î
+_x0000__x0000_1232481068_x0003__x0000__x0001__x0015_¼+ºÇ_x000C__x0000__x0000_031-457-8706
+_x0000__x0000_0314578707_x0007__x0000__x0001_½¬0®Ä³ _x0000_HÅÅÜÂ_x0006__x0000__x0000_431837_x0012__x0000__x0001_½¬0®Ä³ _x0000_HÅÅÜÂ _x0000_Ù³HÅl­ _x0000_À­xÇ\¸ _x0000_8_x0000_9_x0000__x000D__x0000__x0000_010-7338-7375_x0016__x0000__x0000_jamjali200@hanmail.net_x000E__x0000__x0000_37690004532237_x0006__x0000__x0000_D00149	_x0000__x0001_TÏ¬¹DÅ$Æ_x0008_Õ(_x0000_@®Ì)_x0000_
+_x0000__x0000_5100147324_x0003__x0000__x0001__x0015_¼ Á_x0001_Æ_x0008__x0000__x0000_20070423_x000C__x0000__x0000_054-430-7007
+_x0000__x0000_0544307007_x0008__x0000__x0001_½¬ÁÀ½Ä³ _x0000_@®ÌÜÂ_x0005__x0000__x0000_39626_x000E__x0000__x0001_½¬½ _x0000_@®ÌÜÂ _x0000_¡Á$Á\¸ _x0000_1_x0000_6_x0000_4_x0000__x000D__x0000__x0000_010-4115-6306_x0013__x0000__x0000_jj10654@hanmail.net_x000E__x0000__x0000_37690004533937_x0006__x0000__x0000_D00150_x0005__x0000__x0001__x0014_Ól­¤ÂìÓ Î
+_x0000__x0000_5020153204_x0003__x0000__x0001_àÂÁÀÜ­_x0008__x0000__x0000_20080331_x000C__x0000__x0000_053-957-8989
+_x0000__x0000_0539432345_x0008__x0000__x0001__x0000_³l­_x0011_­íÅÜÂ _x0000_Ù³l­_x0005__x0000__x0000_41193_x000F__x0000__x0001__x0000_³l­ _x0000_Ù³l­ _x0000_DÅÅ\¸1_x0000_1_x0000_8® _x0000_8_x0000_1_x0000__x0008__x0000__x0001_1_x0000_5Î _x0000__x0014_Ól­¤ÂìÓ Î_x000D__x0000__x0000_010-8854-8989_x0012__x0000__x0000_89sports@naver.com_x000E__x0000__x0000_37690004534537_x0006__x0000__x0000_D00159_x0005__x0000__x0001__x001C_Ö1Á¤ÂìÓ Î
+_x0000__x0000_1300531089_x0003__x0000__x0001_tÇXÇ Á_x000D__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000__x0000_¬_x0004_È_x001C_ÈÔ,_x0000_¡ÇTÖ_x0008__x0000__x0000_20070529_x000C__x0000__x0000_032-654-2133
+_x0000__x0000_0326542132_x0007__x0000__x0001_½¬0®Ä³ _x0000_½ÌÜÂ_x0006__x0000__x0000_422819 _x0000__x0001_½¬0®Ä³ _x0000_½ÌÜÂ _x0000_Á¬Àl­ _x0000_½¬xÇ\¸1_x0000_2_x0000_0_x0000_¼8® _x0000_2_x0000_8_x0000_ _x0000_ _x0000_1_x0000_5Î_x0010_ÈìÓ _x0000_1_x0000_xÎ_x000D__x0000__x0000_010-7578-7740_x0015__x0000__x0000_hs7167741@hanmail.net_x000E__x0000__x0000_37690004541337_x0006__x0000__x0000_D00160_x0005__x0000__x0001_8ÖÙ³¤ÂìÓ Î
+_x0000__x0000_1243919047_x0003__x0000__x0001_@®8ÖÙ³_x0008__x0000__x0000_20100113_x000C__x0000__x0000_031-375-0331
+_x0000__x0000_0313750331_x0007__x0000__x0001_½¬0®Ä³ _x0000_$Æ°ÀÜÂ_x0006__x0000__x0000_447802_x001A__x0000__x0001_½¬0®Ä³ _x0000_$Æ°ÀÜÂ _x0000_1Á8Ö_x0000_³\¸ _x0000_2_x0000_5_x0000_ _x0000_´Æ°ÀL¾)µ _x0000_ _x0000_1_x0000_5Î _x0000_4_x0000__x000D__x0000__x0000_010-5295-8278_x0013__x0000__x0000_khd9982@hanmail.net_x000E__x0000__x0000_37690004542037_x0006__x0000__x0000_D00161_x0005__x0000__x0001_MÖ1ÁÆ%±¤Â
+_x0000__x0000_3100640518_x0003__x0000__x0001_@®_x0004_Ö_x0015_È_x0008__x0000__x0000_20090616_x000C__x0000__x0000_041-634-7327_x0008__x0000__x0001_©Í­Ì¨°Ä³ _x0000_MÖ1Áp­_x0005__x0000__x0000_32263_x0012__x0000__x0001_©Í¨° _x0000_MÖ1Áp­ _x0000_MÖ½MÇ _x0000_©Í¨°_x0000_³\¸ _x0000_3_x0000_6_x0000__x0015__x0000__x0001__x001C_È _x0000_1_x0000_5Î _x0000__x001C_È _x0000_1_x0000_0_x0000_1_x0000_8Ö(_x0000_L¾dÅT³¤Â$Æ&lt;Õ¤ÂTÑ)_x0000__x000D__x0000__x0000_010-8626-9825_x0010__x0000__x0000_hji923@naver.com_x000E__x0000__x0000_37690004543637_x0006__x0000__x0000_D00166_x000C__x0000__x0001_(_x0000_üÈ)_x0000_ðÒ_x001C_ÈtÇ_x0014_µ¤Â¸Ò¬¹ð½XÁ
+_x0000__x0000_2118732516_x0003__x0000__x0001_¡ÁÁÀÐÆ_x0006__x0000__x0001_Ä³Áä¹ _x0000_Ä³ä¹_x0008__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_4»íÅ_x0008__x0000__x0000_20120911_x000B__x0000__x0000_02-511-5114	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x0015_¬¨°l­_x0006__x0000__x0000_135010_x000B__x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ_x0015_¬¨°l­|±_x0004_ÖÙ³_x000E__x0000__x0001__x0008_®@ÇL¾)µ _x0000_1_x0000_5Î _x0000_ ¼¤Â¸Ò¤Â Ñ´Å_x000D__x0000__x0000_010-8784-1651_x0015__x0000__x0000_bestextreme@naver.com_x0007__x0000__x0001_B_x0000_ñ´	®(_x0000_T_x0000_S_x0000_)_x0000__x0005__x0000__x0000_14049_x0003__x0000__x0001__x0015_¼_x0004_ÖÄÉ_x0008__x0000__x0000_20190917_x0006__x0000__x0000_D00167_x0008__x0000__x0001_üÈÝÂÖ¬À _x0000_ÐÆÐÅÇ
+_x0000__x0000_1268800066_x0003__x0000__x0001_@®DÕ¹Â_x0006__x0000__x0001_Ä³Áä¹ÅÅ _x0000_xÆ_x0007__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_xÆ_x000C__x0000__x0000_02-1644-1662	_x0000__x0001_½°À_x0011_­íÅÜÂ _x0000__x0018_Â_x0001_Æl­_x0006__x0000__x0000_613815_x0013__x0000__x0001_½°À_x0011_­íÅÜÂ _x0000__x0018_Â_x0001_Æl­ _x0000__x0011_­¨°\¸ _x0000_6_x0000_3_x0000_ _x0000_B_x0000_Ù³_x0004__x0000__x0001_4_x0000_5Î|Ç½_x000D__x0000__x0000_010-8882-4137_x0014__x0000__x0000_oneeight@hanmail.net_x0006__x0000__x0000_D00173_x0005__x0000__x0001__x0008_®_x0001_Æ¤ÂìÓ Î
+_x0000__x0000_1052087391_x0003__x0000__x0001_°ÆÀÉÐÆ_x0008__x0000__x0000_20140217_x000D__x0000__x0000_010-6208-8112_x0006__x0000__x0000_121889_x0013__x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_È¹ìÓl­ _x0000_Ù³P­\¸3_x0000_8® _x0000_1_x0000_2_x0000_5_x0000__x0013__x0000__x0000_yonex0901@naver.com_x0008__x0000__x0000_20150122_x000E__x0000__x0000_37690004557937_x0006__x0000__x0000_D00181_x0004__x0000__x0001__x0000_É¤ÂìÓ Î
+_x0000__x0000_1410240836_x0003__x0000__x0001__x0015_¼½¬·_x0008__x0000__x0000_20140825_x000C__x0000__x0000_031-945-2007_x0007__x0000__x0001_½¬0®Ä³ _x0000__x000C_ÓüÈÜÂ_x0006__x0000__x0000_413819$_x0000__x0001_½¬0®Ä³ _x0000__x000C_ÓüÈÜÂ _x0000_DÅ¬¹·\¸ _x0000_5_x0000_5_x0000_ _x0000_-_x0000_8_x0000_1_x0000_ _x0000_(_x0000__x0008_®_x000C_ÍÙ³,_x0000_ _x0000__x000C_ÓüÈ_x0008_®_x000C_ÍXÕ_x0018_ÂÌ¬¹¥Ç)_x0000__x000C__x0000__x0001__x000C_ÓüÈÜÂ _x0000_0¼Ü´ü»4Ñ_x0004_È©Æl­¥Ç_x000D__x0000__x0000_010-9129-1126_x0017__x0000__x0000_leesjun1024@hanmail.net_x000E__x0000__x0000_37690004547137_x0006__x0000__x0000_D00183_x0003__x0000__x0001_T³_x001C_È|Ç
+_x0000__x0000_1171558537_x0003__x0000__x0001_iÖÐÆ Á_x000B__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_XÇX¹,_x0000_¡ÇTÖ_x0008__x0000__x0000_20141027_x000D__x0000__x0000_010-6333-2457	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_ÅÌl­_x0005__x0000__x0000_08078 _x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_ÅÌl­ _x0000_àÂ_x0015_È\¸ _x0000_2_x0000_7_x0000_5_x0000_ _x0000_ _x0000_(_x0000_àÂ_x0015_ÈÙ³,_x0000_ _x0000_àÂ¸Ò¬¹DÅ_x000C_Ó¸Ò)_x0000__x0010__x0000__x0001_ÁÀ_x0000_¬Ù³ _x0000_1_x0000_5Î _x0000_1_x0000_0_x0000_4_x0000_,_x0000_ _x0000_1_x0000_0_x0000_5_x0000_8Ö_x0011__x0000__x0000_thejeil@naver.com_x000D__x0000__x0000_010-9668-2210_x000E__x0000__x0000_37690004550437_x0006__x0000__x0000_D00184_x0005__x0000__x0001_$Æ¨°¤ÂìÓ Î
+_x0000__x0000_1322489384_x0003__x0000__x0001_Å+È¨º_x000D__x0000__x0001_´ÆÙ³0®l­©ÆÔ _x0000_aÅ8Á_x001C_Á¬¹ _x0000_xÆ_x0008__x0000__x0000_20141028
+_x0000__x0000_0315756464
+_x0000__x0000_0315755600_x0008__x0000__x0001_½¬0®Ä³ _x0000_¨°ÅüÈÜÂ_x0006__x0000__x0000_472881_x0016__x0000__x0001_½¬0®Ä³ _x0000_¨°ÅüÈÜÂ _x0000_ÄÉt¬$Æ¨°\¸ _x0000_8_x0000_0_x0000_6_x0000_ _x0000_-_x0000_1_x0000_4_x0000__x000D__x0000__x0000_010-9289-9637_x0012__x0000__x0000_jongmo83@naver.com_x000E__x0000__x0000_37690004552737_x0006__x0000__x0000_D00186_x0005__x0000__x0001_ä¹XÎìÓxÇ¸Ò
+_x0000__x0000_6091853217_x0003__x0000__x0001_iÖ­ÝÂ_x0008__x0000__x0000_20141202_x000C__x0000__x0000_055-298-7330_x0005__x0000__x0000_51378_x0011__x0000__x0001_½¬¨° _x0000_=ÌÐÆÜÂ _x0000_XÇ=Ìl­ _x0000__x0018_¼Ä¬\¸ _x0000_6_x0000_3_x0000__x000D__x0000__x0000_010-3561-0209_x000E__x0000__x0000_o2bbi@nate.com_x0008__x0000__x0000_20141212_x000E__x0000__x0000_37690004554037_x0006__x0000__x0000_D00190_x0005__x0000__x0001_p­°À¤ÂìÓ Î
+_x0000__x0000_4010657765_x0003__x0000__x0001__x0015_¼_x001C_Âl×	_x0000__x0001_¤ÂìÓ ÎXÇX¹,_x0000_ _x0000_©ÆÔ_x0008__x0000__x0000_20150406_x000D__x0000__x0000_010-9977-7141_x0008__x0000__x0001__x0004_È|·½Ä³ _x0000_p­°ÀÜÂ_x0005__x0000__x0000_54102_x000F__x0000__x0001__x0004_È½ _x0000_p­°ÀÜÂ _x0000_¨°_x0018_Â¡Á5_x0000_8® _x0000_4_x0000_2_x0000__x000F__x0000__x0001_1_x0000_0_x0000_1_x0000_8Ö(_x0000__x0018_Â¡ÁÙ³,_x0000_ _x0000_(Ì$Æ¹L¾)_x0000__x0013__x0000__x0000_shp7141@hanmaiL.net_x000E__x0000__x0000_37690004558537_x0006__x0000__x0000_D00192
+_x0000__x0001__x0001_Æ8»¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1222039517_x0005__x0000__x0001__x0001_Æ8»¤ÂìÓ Î_x0003__x0000__x0001_@®_x0001_Æ8»_x0008__x0000__x0000_20150608_x000C__x0000__x0000_032-523-1406_x000C__x0000__x0000_032-517-8009	_x0000__x0001_xÇÌ_x0011_­íÅÜÂ _x0000_½ÉÓl­_x0005__x0000__x0000_21337_x000D__x0000__x0000_010-4320-1406_x0012__x0000__x0000_YM1406@hanmail.net_x0007__x0000__x0001_A_x0000_ñ´	®(_x0000_T_x0000_S_x0000_)_x0000__x0005__x0000__x0000_13042_x0003__x0000__x0001_@®Ù³½¬_x000E__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_+_x0000_3_x0000_0_x0000__x000E__x0000__x0000_37690004561837_x0006__x0000__x0000_D00193_x000B__x0000__x0001_ÑÐ¤Â@Õ¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1320972497_x0006__x0000__x0001_ÑÐ¤Â@Õ¤ÂìÓ Î_x0003__x0000__x0001__x0015_¼_x0004_Ö=Ì_x0006__x0000__x0001_´ÆÙ³_x0004_È8»©ÆÔ_x0008__x0000__x0000_20150610_x000D__x0000__x0000_010-3706-2477_x0007__x0000__x0001_½¬0®Ä³ _x0000_l­¬¹ÜÂ_x0005__x0000__x0000_11907_x000F__x0000__x0001_½¬0® _x0000_l­¬¹ÜÂ _x0000_UÆ_x0019_ÂÌ\¸ _x0000_5_x0000_0_x0000_7_x0000_	_x0000__x0001_3_x0000_5Î _x0000_ÑÐ¤Â@Õ¤ÂìÓ Î_x000F__x0000__x0000_pspin@naver.com_x0005__x0000__x0000_22022_x0003__x0000__x0001_HÅ°ÆÄÉ_x000C__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_7_x0000_._x0000_5_x0000__x000E__x0000__x0000_37690004560137_x0006__x0000__x0000_D00195
+_x0000__x0001_¤ÂìÓ ÎLÑlÐ(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_6172249744_x0005__x0000__x0001_¤ÂìÓ ÎLÑlÐ_x0003__x0000__x0001_tÇÝÐ0®_x0006__x0000__x0001__x001C_ÈpÈÅÅ _x0000_Áä¹_x000C__x0000__x0001_õ¬_x0008_Æ _x0000_¤ÂìÓ Î©ÆÔ,_x0000_ _x0000_¡ÇTÖ_x000B__x0000__x0000_051-7564800_x000C__x0000__x0000_051-756-4801_x0005__x0000__x0000_48222_x0017__x0000__x0001_½°À_x0011_­íÅÜÂ _x0000_Ù³·l­ _x0000_+ÈiÕ´ÆÙ³¥Ç\¸ _x0000_4_x0000_0_x0000_¼8® _x0000_8_x0000_'_x0000__x0001_1_x0000_0_x0000_3_x0000_Ù³ _x0000_1_x0000_0_x0000_5_x0000_8Ö,_x0000_1_x0000_0_x0000_6_x0000_8Ö(_x0000_¬ÀÁÉÙ³,_x0000_½°À _x0000_DÅÜÂDÅÜ´ _x0000_TÏ$Æq¸ _x0000_XÕ²DÌ _x0000_DÅ_x000C_Ó¸Ò)_x0000__x000D__x0000__x0000_010-5578-1988_x0015__x0000__x0000_ltktennis@hanmail.net_x000B__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_8_x0000__x0008__x0000__x0000_20150611_x000E__x0000__x0000_37690004562437_x0006__x0000__x0000_D00196	_x0000__x0001__x0015_¬¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_5041920932_x0004__x0000__x0001__x0015_¬¤ÂìÓ Î_x0003__x0000__x0001__x0015_¬@Çl­_x000D__x0000__x0001_LÑÈ²¤Â©ÆÔ,_x0000_ _x0000_XÇX¹,_x0000_ _x0000_àÂ_x001C_¼_x000C__x0000__x0000_053-314-9090_x0005__x0000__x0000_41433_x000D__x0000__x0000_010-3828-0474_x0013__x0000__x0000_keg0417@hanmail.net_x000D__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_6_x0000_+_x0000_1_x0000_5_x0000__x0008__x0000__x0000_20150612_x000E__x0000__x0000_37690004565337_x0006__x0000__x0000_D00199
+_x0000__x0001_P´¬¹¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1283008985_x0003__x0000__x0001_@®_x0001_Æ Á_x000B__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_¤ÂìÓ ÎXÇX¹_x0008__x0000__x0000_20150703_x000C__x0000__x0000_031-911-4191_x000C__x0000__x0000_031-913-0067_x0006__x0000__x0000_410829_x000F__x0000__x0001_½¬0®Ä³à¬ÅÜÂ _x0000_|Ç°ÀÙ³l­_x0015_È_x001C_¼°ÀÙ³_x000E__x0000__x0001_1_x0000_1_x0000_4_x0000_8_x0000_-_x0000_1_x0000_3_x0000_ _x0000_1_x0000_5Î2_x0000_,_x0000_3_x0000_8Ö_x000D__x0000__x0000_010-4288-3563_x0012__x0000__x0000_usop2n@hanmail.net_x000D__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_6_x0000_+_x0000_2_x0000_3_x0000__x000E__x0000__x0000_37690004568237_x0006__x0000__x0000_D00201_x000E__x0000__x0001_(_x0000_üÈ)_x0000_¤ÂtÎtÇ¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_6278102573_x000B__x0000__x0001_¤ÂtÎtÇ¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000__x0003__x0000__x0001_@®1ÁÐÆ_x0006__x0000__x0001_Áä¹ÅÅ _x0000_Ä³ä¹_x0008__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_ä¹_x0010_È_x000C__x0000__x0000_041-566-1879_x000C__x0000__x0000_041-554-2732_x0005__x0000__x0000_31157"_x0000__x0001_©Í­Ì¨°Ä³ _x0000_ÌHÅÜÂ _x0000__x001C_Á½l­ _x0000_1¼_x001D_Á3_x0000_\¸ _x0000_2_x0000_9_x0000_ _x0000_ _x0000_(_x0000_1¼_x001D_ÁÙ³,_x0000_ _x0000_½¶É¹_x0008_Ã%¼)_x0000__x000D__x0000__x0000_010-4513-1879_x0011__x0000__x0000_kimsw000@nate.com_x000E__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_4_x0000_0_x0000_+_x0000_2_x0000_0_x0000__x0008__x0000__x0000_20150804_x000E__x0000__x0000_37690004570937_x0006__x0000__x0000_D00202_x0008__x0000__x0001_¤ÂìÓå²(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_3052275067_x0003__x0000__x0001_HÅü­¹Â_x000C__x0000__x0000_042-522-9566_x000C__x0000__x0000_042-271-4786_x0006__x0000__x0000_300810_x0017__x0000__x0001__x0000_³_x0004_È_x0011_­íÅÜÂ _x0000__x0011_Él­ _x0000_Ù³_x001C_Á_x0000_³\¸ _x0000_1_x0000_2_x0000_0_x0000_1_x0000_(_x0000_ÜÐÉÓÙ³)_x0000__x0007__x0000__x0001_¤ÂìÓå² _x0000_ÜÐÉÓ_x0010_È_x000B__x0000__x0000_01062224787_x0010__x0000__x0000_spodaq@naver.com_x000D__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_5_x0000_+_x0000_3_x0000_3_x0000__x0008__x0000__x0000_20150805_x000E__x0000__x0000_37690004571537_x0006__x0000__x0000_D00203	_x0000__x0001_ðÅTÏ¬¹DÅ(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_2041477980_x0004__x0000__x0001_ðÅTÏ¬¹DÅ_x0003__x0000__x0001_@®ÁÀ0®_x0006__x0000__x0001_Ä³Áä¹ _x0000_t¬$Á_x000D__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_´Ì!ÇÜÂ_x001C_Á&lt;»$ÁXÎ_x0008__x0000__x0000_20150806_x000C__x0000__x0000_02-3390-4345_x000C__x0000__x0000_02-3390-4344
+_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_Ù³_x0000_³8»l­_x0005__x0000__x0000_02496_x0011__x0000__x0001__x001C_Á¸Æ _x0000_Ù³_x0000_³8»l­ _x0000_Ý¹°Æ\¸1_x0000_2_x0000_8® _x0000_1_x0000_9_x0000__x000B__x0000__x0001_1_x0000_5Î _x0000_XÕtÇÐÆ¤ÂìÓ Î°ÀÅÅ_x000D__x0000__x0000_010-9089-5363_x0017__x0000__x0000_01090895363@hanmail.net_x000B__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_2_x0000_0_x0000__x000E__x0000__x0000_37690004572137_x0006__x0000__x0000_D00205_x0005__x0000__x0001_ÁLÑ¤ÂìÓ Î
+_x0000__x0000_1971301851_x0003__x0000__x0001_@®_x0001_Æ_x0018_Â_x0008__x0000__x0001_Ä³Áä¹ÅÅ _x0000_Ä³ä¹ÅÅ	_x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_4»íÅÅÅ_x000B__x0000__x0000_01063388568_x0008__x0000__x0001_½¬0®Ä³ _x0000_XÇ_x0015_È½ÜÂ_x0005__x0000__x0000_11806!_x0000__x0001_½¬0®Ä³ _x0000_XÇ_x0015_È½ÜÂ _x0000_$Æ©º\¸ _x0000_1_x0000_7_x0000_0_x0000_ _x0000_°Àä´È¹DÇ _x0000_DÅ_x000C_Ó¸Ò _x0000_4_x0000_1_x0000_2_x0000_-_x0000_7_x0000_0_x0000_6_x0000__x000D__x0000__x0000_010-6338-8568_x0011__x0000__x0000_3388568@naver.com_x0005__x0000__x0000_26002_x0003__x0000__x0001__x0015_¬ÜÐ8Ö_x0008__x0000__x0000_20220901_x000E__x0000__x0000_37690004700437_x0006__x0000__x0000_D00209_x0018__x0000__x0001_¤ÂìÓ Î_x000C_Õì·¤Â(_x0000_S_x0000_p_x0000_o_x0000_r_x0000_t_x0000_s_x0000_ _x0000_P_x0000_l_x0000_u_x0000_s_x0000_)_x0000_(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1192167071_x0003__x0000__x0001__x0015_¬ÜÂ¨º_x0006__x0000__x0001_Ä³Áä¹ _x0000_LÇÝÂ_x0008__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_\ÕÝÂ_x000B__x0000__x0000_02-871-5513	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x0000_­EÅl­_x0005__x0000__x0000_08750_x000F__x0000__x0001__x001C_Á¸Æ _x0000__x0000_­EÅl­ _x0000_àÂ¼¹\¸3_x0000_8® _x0000_4_x0000_0_x0000__x0005__x0000__x0001_ÀÉXÕ _x0000_1_x0000_5Î_x000D__x0000__x0000_010-7703-5353_x001A__x0000__x0000_tennisplus0122@esero.go.krX_x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_ _x0000_/_x0000_ _x0000_2_x0000_5_x0000_S_x0000_S_x0000_ _x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_ _x0000_/_x0000_ _x0000_2_x0000_4_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_9_x0000_._x0000_6_x0000_ _x0000_/_x0000_ _x0000_2_x0000_4_x0000_S_x0000_S_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_ _x0000_/_x0000_ _x0000_2_x0000_3_x0000_F_x0000_W_x0000_ _x0000__x0018_ÂüÈ _x0000_ìÅàÂ _x0000_ _x0000_1_x0000_2_x0000_ _x0000_(_x0000_ô²ù²Ç _x0000_Æ­Ì&lt;Ç\¸ _x0000_6_x0000_ _x0000__x0018_¼_x0001_Æ)_x0000__x0008__x0000__x0000_20160114_x000E__x0000__x0000_37690004577337_x0006__x0000__x0000_D00210_x0011__x0000__x0001_(_x0000_üÈ)_x0000_ÐÅtÇ_x001C_ÈtÇxÇ0Ñ´°TÁ °(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1268641398_x000C__x0000__x0000_031-761-8980_x000C__x0000__x0000_031-761-2140_x0005__x0000__x0000_12769_x000D__x0000__x0000_010-4552-3318	_x0000__x0000_1800-6142_x000E__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_4_x0000_0_x0000_+_x0000_2_x0000_5_x0000__x0008__x0000__x0000_20160121_x000E__x0000__x0000_37690004578037_x0006__x0000__x0000_D00256	_x0000__x0001_p¬1Á¤ÂìÓ Î(_x0000_Å°À)_x0000_
+_x0000__x0000_6210808090_x0003__x0000__x0001__x0015_È+È_x0015_¬_x0006__x0000__x0001_Ä³Áä¹ _x0000__x001C_ÈpÈ_x000B__x0000__x0001_ìÕ¤Â0®l­,_x0000_ _x0000_¤ÂìÓ Î©ÆÔ_x0008__x0000__x0000_20160412_x000C__x0000__x0000_055-387-3613_x000C__x0000__x0000_055-387-3615_x0008__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_Å°ÀÜÂ_x0005__x0000__x0000_50621 _x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_Å°ÀÜÂ _x0000__x001C_Á|ÇÙ³\¸ _x0000_2_x0000_5_x0000_ _x0000_ _x0000_(_x0000__x0011_É½Ù³,_x0000_ _x0000_$Ç ÁÝÀ_x0001_Æ´ÅP­äÂ)_x0000__x000D__x0000__x0000_010-2390-2994_x0013__x0000__x0000_dhrhr68@hanmail.netH_x0000__x0001_2_x0000_4_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_3_x0000_5_x0000_ _x0000_/_x0000_2_x0000_4_x0000_S_x0000_S_x0000__x0018_ÂüÈìÅàÂ _x0000_3_x0000_5_x0000_ _x0000_/_x0000_ _x0000_2_x0000_3_x0000_F_x0000_W_x0000_ _x0000__x0018_ÂüÈ _x0000_ìÅàÂ _x0000_3_x0000_5_x0000_ _x0000_/_x0000_ _x0000_2_x0000_3_x0000_S_x0000_S_x0000_ _x0000__x0018_ÂüÈ _x0000_ìÅàÂ _x0000_3_x0000_5_x0000_(_x0000_|·_x0013_Ï+_x0000_È¹D¾¤Â _x0000_9_x0000_4_x0000_3_x0000_,_x0000_2_x0000_5_x0000_0_x0000_)_x0000__x0008__x0000__x0000_20160407_x000E__x0000__x0000_37690004581237_x0006__x0000__x0000_D00267_x0006__x0000__x0001__x001C_ÈtÇD¾¤ÂìÓ Î
+_x0000__x0000_6664100083_x0003__x0000__x0001_Ç_x0015_È\Õ_x000D__x0000__x0001_Ä³ä¹ _x0000__x000F_¼ _x0000_Áä¹ÅÅ,_x0000_ _x0000__x001C_ÁD¾¤Â_x000C__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_ _x0000__x0011_­à¬_x0000_³ÕÅÅ_x0008__x0000__x0000_20160610_x000C__x0000__x0000_062-523-7451_x000C__x0000__x0000_062-523-7455_x0005__x0000__x0000_62023_x000D__x0000__x0001__x0011_­üÈ _x0000__x001C_Ál­ _x0000_´ÆÌ\¸ _x0000_1_x0000_2_x0000_2_x0000__x0005__x0000__x0001_(_x0000__x000D_Ã_x000C_ÍÙ³)_x0000__x000D__x0000__x0000_010-4606-4538_x0015__x0000__x0000_jhrim1226@hanmail.net_x0008__x0000__x0000_20160601_x000E__x0000__x0000_37690004584137_x0006__x0000__x0000_D00280_x0005__x0000__x0001_Ä³ô²¤ÂìÓ Î
+_x0000__x0000_3071042161_x0003__x0000__x0001_$ÇÙ³ÝÂ_x000B__x0000__x0001_Ä³ä¹_x000F_¼ _x0000_Áä¹ÅÅ _x0000_Áä¹ÅÅ_x0010__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_Ç_x0004_Èp¬ _x0000__x0010_Óä¹,_x0000_ _x0000__x0000_³ìÅ_x0008__x0000__x0000_20160825_x000C__x0000__x0000_044-863-8908_x000C__x0000__x0000_044-863-8970_x000F__x0000__x0001_8Á+È¹ÒÄ¼ÇXÎÜÂ _x0000_8Á+È¹ÒÄ¼ÇXÎÜÂ_x0005__x0000__x0000_30102_x001E__x0000__x0001_8Á+È¹ÒÄ¼ÇXÎÜÂ _x0000__x0008_È¬Ç\¸ _x0000_1_x0000_7_x0000_2_x0000_ _x0000_(_x0000_´ÅÄÉÙ³,_x0000_ _x0000_ÜÐ\Õ_x0004_Õ_x0008_¸¤Â&lt;Á0Ñ)_x0000__x0004__x0000__x0001_1_x0000_0_x0000_1_x0000_8Ö_x000D__x0000__x0000_010-7185-8008_x0015__x0000__x0000_dodamsports@naver.com_x000E__x0000__x0000_37690004586437_x0006__x0000__x0000_D00282_x0005__x0000__x0001__x0004_²¬¹¤ÂìÓ Î
+_x0000__x0000_1082124505_x0003__x0000__x0001_@®l×_x0015_È_x0006__x0000__x0001_Áä¹ _x0000_Ä³Áä¹_x000C__x0000__x0001__x0004_ÈÇÁÀp¬·ÅÅ _x0000_0¼Ü´ü»4Ñ _x0000__x000B__x0000__x0000_02-848-6291_x000B__x0000__x0000_02-848-7556
+_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x0001_Æñ´ìÓl­_x0005__x0000__x0000_07375_x000E__x0000__x0001__x001C_Á¸Æ _x0000__x0001_Æñ´ìÓl­ _x0000_Ä³àÂ\¸ _x0000_5_x0000_1_x0000__x000D__x0000__x0001_1_x0000_5Î _x0000_1_x0000_0_x0000_5_x0000_8Ö(_x0000_¡ÁU³L¾)µ)_x0000__x000D__x0000__x0000_010-8393-6291_x0013__x0000__x0000_hee00jung@naver.com_x0008__x0000__x0000_20160905_x000E__x0000__x0000_37690004588737_x0006__x0000__x0000_D00286_x0007__x0000__x0001_Æ%±¤Â _x0000_1Á¨°_x0010_È
+_x0000__x0000_2603001743_x0003__x0000__x0001_MÖ¥Ç8Ö_x0008__x0000__x0001_Ä³ä¹ _x0000__x000F_¼ _x0000_Áä¹ÅÅ_x0008__x0000__x0000_20151218_x000C__x0000__x0000_031-755-7257_x0007__x0000__x0001_½¬0®Ä³ _x0000_1Á¨°ÜÂ_x0005__x0000__x0000_13110_x001E__x0000__x0001_½¬0®Ä³ _x0000_1Á¨°ÜÂ _x0000__x0018_Â_x0015_Èl­ _x0000_1Á¨°_x0000_³\¸ _x0000_1_x0000_2_x0000_6_x0000_7_x0000_ _x0000_-_x0000_1_x0000_ _x0000_(_x0000_ÜÐÉÓÙ³)_x0000__x000D__x0000__x0000_010-7191-7257_x0012__x0000__x0000_nero1016@naver.com_x0002__x0000__x0001_¨°¸Ó_x0008__x0000__x0000_20161109_x000E__x0000__x0000_37690004591037_x0006__x0000__x0000_D00287_x0005__x0000__x0001_¤ÐtÎ¤ÂìÓ Î
+_x0000__x0000_6103752918_x0003__x0000__x0001_@®ÜÐÇ_x0008__x0000__x0000_20161125_x000C__x0000__x0000_052-268-6086_x000C__x0000__x0000_052-272-5908_x0008__x0000__x0001_¸Æ°À_x0011_­íÅÜÂ _x0000_¨°l­_x0005__x0000__x0000_44692_x0016__x0000__x0001_¸Æ°À_x0011_­íÅÜÂ _x0000_¨°l­ _x0000_Ë³ÈÉ\¸ _x0000_1_x0000_2_x0000_4_x0000_ _x0000_ _x0000_(_x0000_ì²Ù³)_x0000__x0003__x0000__x0000_3/2_x000D__x0000__x0000_010-9568-6086_x0014__x0000__x0000_kika5908@hanmail.net_x000E__x0000__x0000_37690004592637_x0006__x0000__x0000_D00292_x0008__x0000__x0001_Æ%±¤Â _x0000_¤ÂìÓÐÆ_x0010_È
+_x0000__x0000_6977800050_x0003__x0000__x0001_\ÕÀ­_x0001_Æ_x0008__x0000__x0000_20170102_x000C__x0000__x0000_051-517-3862_x000C__x0000__x0000_051-583-1023	_x0000__x0001_½°À_x0011_­íÅÜÂ _x0000__x0008_®_x0015_Èl­_x0005__x0000__x0000_46207&amp;_x0000__x0001_½°À_x0011_­íÅÜÂ _x0000__x0008_®_x0015_Èl­ _x0000_´Ì!Çõ¬ÐÆ\¸3_x0000_9_x0000_9_x0000_¼8® _x0000_3_x0000_2_x0000_4_x0000_ _x0000_ _x0000_(_x0000_P´l­Ù³,_x0000_ _x0000_¤ÂìÓÐÆ_x000C_ÓlÐ)_x0000__x0010__x0000__x0001_ÀÉXÕ1_x0000_5Î(_x0000_P´l­Ù³,_x0000_ _x0000_äÂ´°´Ì!Ç_x0000_­)_x0000__x000D__x0000__x0000_010-5505-3862_x0013__x0000__x0000_hgy4285@hanmail.net_x000E__x0000__x0000_37690004595537_x0006__x0000__x0000_D00306_x0007__x0000__x0001_Æ%±¤Â _x0000_ÁÀ4»_x0010_È
+_x0000__x0000_8042300420_x0003__x0000__x0001_@®_x0004_Ö+È_x000D__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_´ÆÙ³©ÆÔ _x0000_¡ÇTÖ_x0008__x0000__x0000_20170119_x000D__x0000__x0000_010-6886-7065_x000C__x0000__x0000_062-374-5410_x0005__x0000__x0000_61970_x0013__x0000__x0001__x0011_­üÈ _x0000__x001C_Ál­ _x0000_ÁÀ4»ü»üÈ\¸3_x0000_2_x0000_¼8® _x0000_3_x0000_-_x0000_5_x0000__x0013__x0000__x0000_sskim-j@hanmail.net_x000E__x0000__x0000_37690004597837_x0006__x0000__x0000_D00308_x0005__x0000__x0001_C_x0000_S_x0000_¤ÂìÓ Î
+_x0000__x0000_2270838785_x0007__x0000__x0001_iÖ_x001C_ÂU³xÆ _x0000_1_x0000_+º_x000C__x0000__x0000_031-385-1222_x000C__x0000__x0000_031-388-3477_x0005__x0000__x0000_13958_x0016__x0000__x0001_½¬0® _x0000_HÅÅÜÂ _x0000_Ì¹HÅl­ _x0000__x0008_Æ Âõ¬ÐÆ\¸5_x0000_2_x0000_¼8® _x0000_2_x0000__x000D__x0000__x0000_010-3176-9037_x0013__x0000__x0000_bill@cssports.co.kr_x000D__x0000__x0000_010-2727-2718_x000F__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_5_x0000_+_x0000_3_x0000_._x0000_5_x0000__x000E__x0000__x0000_37690004598437_x0006__x0000__x0000_D00311
+_x0000__x0001_TÏ¬¹DÅ¤ÂìÓ Î(_x0000_ÜÂe×)_x0000_
+_x0000__x0000_3047001336_x0006__x0000__x0001_TÏ¬¹DÅ¤ÂìÓ Î_x0003__x0000__x0001_\Í_x0001_Æ_x0019_Â_x0012__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000__x0010_Ó	Í&lt;»,_x0000_xÇÄÁ&lt;»,_x0000_0®ÀÐ©ÆÔ_x000D__x0000__x0000_010-2618-5518_x000C__x0000__x0000_031-312-8982_x0007__x0000__x0001_½¬0®Ä³ _x0000_ÜÂe×ÜÂ_x0005__x0000__x0000_14922_x000F__x0000__x0001_½¬0® _x0000_ÜÂe×ÜÂ _x0000_@ÇÄ¬¼_x0001_Æ8® _x0000_2_x0000_7_x0000__x000F__x0000__x0001_3_x0000_0_x0000_3_x0000_8Ö(_x0000_@ÇÕÙ³,_x0000_ _x0000_ÜÂðÒ_x000C_ÓlÐ)_x0000__x0015__x0000__x0000_queenmt5518@naver.com_x000C__x0000__x0000_031-404-6121_x0008__x0000__x0000_20170220_x000E__x0000__x0000_37690004600637_x0006__x0000__x0000_D00312_x000E__x0000__x0001_Æ%±¤Â(_x0000_Y_x0000_O_x0000_N_x0000_E_x0000_X_x0000_)_x0000_ _x0000_tÇÌ_x0010_È
+_x0000__x0000_1052641553_x0003__x0000__x0001_$Ç ÇÄÉ_x000C__x0000__x0000_031-631-2210_x0007__x0000__x0001_½¬0®Ä³ _x0000_tÇÌÜÂ_x0005__x0000__x0000_17362_x0017__x0000__x0001_½¬0®Ä³ _x0000_tÇÌÜÂ _x0000_`Å(¸_x0015_È\¸ _x0000_1_x0000_4_x0000_2_x0000_ _x0000_ _x0000_(_x0000_=Ì_x0004_ÈÙ³)_x0000__x000D__x0000__x0000_010-3459-1313_x0010__x0000__x0000_jin7601@daum.net_x0003__x0000__x0001_\Í_x0015_¬8Ö_x0008__x0000__x0000_20170221_x000E__x0000__x0000_37690004601237_x0006__x0000__x0000_D00324_x0006__x0000__x0001__x000C_Ó¸Ò_x0008_±¤ÂìÓ Î
+_x0000__x0000_1272471368_x0003__x0000__x0001_@®©Æ`Å_x000C__x0000__x0000_031-398-8953_x000C__x0000__x0000_031-398-8954_x0007__x0000__x0001_½¬0®Ä³ _x0000_p­ìÓÜÂ_x0005__x0000__x0000_15833_x0016__x0000__x0001_½¬0®Ä³ _x0000_p­ìÓÜÂ _x0000_$Æ_x0008_®\¸ _x0000_1_x0000_5_x0000_0_x0000_ _x0000_ _x0000_(_x0000__x0008_®_x0015_ÈÙ³)_x0000_	_x0000__x0001_1_x0000_0_x0000_2_x0000_8Ö(_x0000__x0008_®_x0015_ÈÙ³)_x0000__x000D__x0000__x0000_010-4854-8953_x0010__x0000__x0000_kya5767@nate.com_x0008__x0000__x0000_20170320_x000E__x0000__x0000_37690004603537_x0006__x0000__x0000_D00328_x0006__x0000__x0001_ÄÉüÈ0¼Ü´ü»4Ñ
+_x0000__x0000_6131082729_x0003__x0000__x0001__x0015_È Ìä¬_x000C__x0000__x0000_055-747-2101_x0008__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_ÄÉüÈÜÂ_x0005__x0000__x0000_52806_x0019__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_ÄÉüÈÜÂ _x0000_Á-¼\¸7_x0000_5_x0000_¼8® _x0000_8_x0000_ _x0000_ _x0000_(_x0000_ÁÀÉÓÙ³)_x0000__x000D__x0000__x0000_010-9612-2188_x0011__x0000__x0000_jcg2188@naver.com_x000B__x0000__x0000_01095082188_x0008__x0000__x0000_20170324_x000E__x0000__x0000_37690004604137_x0006__x0000__x0000_D00338
+_x0000__x0001_Æ%±¤Â=ÌÐÆ_x0010_È(_x0000_øÂtÎ)_x0000_
+_x0000__x0000_6092352584_x0003__x0000__x0001_HÅ¬Çü­_x0010__x0000__x0001_¤ÂìÓ Î _x0000_XÇX¹ _x0000__x000F_¼ _x0000_©ÆÔ _x0000_È¹lÐ_x001C_ÈÇ_x0008__x0000__x0000_20170411_x000C__x0000__x0000_055-261-0123_x0005__x0000__x0000_51420_x0019__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_=ÌÐÆÜÂ _x0000_1Á°Àl­ _x0000__x0018_¼ÀÉ\¸ _x0000_8_x0000_ _x0000_ _x0000_(_x0000__x0018_¼ÀÉÙ³)_x0000__x0005__x0000__x0001_(_x0000__x0018_¼ÀÉÙ³)_x0000__x000D__x0000__x0000_010-9796-1346_x0011__x0000__x0000_cwssaka@naver.com
+_x0000__x0000_0552610123_x000E__x0000__x0000_37690004606437_x0006__x0000__x0000_D00382_x0004__x0000__x0001_$Æ¤ÂìÓ Î
+_x0000__x0000_2860500614_x0003__x0000__x0001__x0015_¼Á|·_x000C__x0000__x0001__x0004_ÈÇÁÀp¬·(_x0000_¤ÂìÓ Î©ÆÔ)_x0000__x000C__x0000__x0000_063-231-0360_x0005__x0000__x0000_54947_x0015__x0000__x0001__x0004_È½ _x0000__x0004_ÈüÈÜÂ _x0000_DÆ°Àl­ _x0000__x0004_È|·_x0010_¬_x0001_Æ\¸ _x0000_4_x0000_0_x0000_-_x0000_1_x0000__x000B__x0000__x0000_01076785147_x0014__x0000__x0000_sora1976kr@naver.com_x0003__x0000__x0001__x0015_¼Ñ¼%ÆQ_x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_+_x0000_1_x0000_0_x0000_0_x0000_ _x0000_/_x0000_ _x0000_2_x0000_5_x0000_S_x0000_S_x0000_ _x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_ _x0000_+_x0000_ _x0000_1_x0000_0_x0000_0_x0000_ _x0000_/_x0000_ _x0000_ _x0000_2_x0000_4_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_ _x0000_/_x0000_ _x0000_2_x0000_4_x0000_S_x0000_S_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_ _x0000_/_x0000_ _x0000_2_x0000_3_x0000_F_x0000_W_x0000_ _x0000__x0018_ÂüÈ _x0000_ìÅàÂ _x0000_1_x0000_2_x0000__x0008__x0000__x0000_20170710_x000E__x0000__x0000_37690004610337_x0006__x0000__x0000_D00392_x0007__x0000__x0001_¨Ö1Á+ÈiÕ¤ÂìÓ Î
+_x0000__x0000_7521600607_x0002__x0000__x0001_@®_x0004_½_x0008__x0000__x0000_20170812_x000C__x0000__x0000_064-733-2992_x0005__x0000__x0000_63591_x0013__x0000__x0001__x001C_ÈüÈ¹ÒÄ¼ÇXÎÄ³ _x0000__x001C_ÁÀ­ìÓÜÂ _x0000_Ù³8»\¸ _x0000_3_x0000_0_x0000__x000B__x0000__x0000_01090156265_x0010__x0000__x0000_ddadon@naver.com_x000B__x0000__x0000_01036928845_x0008__x0000__x0000_20170821_x000E__x0000__x0000_37690004611037_x0006__x0000__x0000_D00396_x000E__x0000__x0001_Æ%±¤Â _x0000_Å°À_x0010_È(_x0000_TÖ·¤ÂìÓ Î)_x0000_
+_x0000__x0000_6211383962_x0003__x0000__x0001_\ÍiÖðÅ_x0008__x0000__x0000_20170813_x000C__x0000__x0000_055-382-6688_x000C__x0000__x0000_055-366-6648_x0005__x0000__x0000_50548_x000F__x0000__x0001_½¬¨° _x0000_Å°ÀÜÂ _x0000_ÅÆÁÀ_x0000_³\¸ _x0000_9_x0000_6_x0000_1_x0000__x0007__x0000__x0001_Æ%±¤Â _x0000_Å°À_x0010_È_x000D__x0000__x0000_010-9323-8281_x0016__x0000__x0000_eegmom0808@hanmail.net_x0008__x0000__x0000_20170915_x000E__x0000__x0000_37690004612637_x0006__x0000__x0000_D00408_x0005__x0000__x0001_l­¬¹TÏ¸Ò\¸
+_x0000__x0000_1321920436_x0003__x0000__x0001_àÂ_x0001_Æ8Ö_x0008__x0000__x0000_20060509_x000C__x0000__x0000_031-562-3307_x0005__x0000__x0000_11942_x0012__x0000__x0001_½¬0®Ä³ _x0000_¨°ÅüÈÜÂ _x0000__x0000_¬´Æ\¸2_x0000_8® _x0000_1_x0000_1_x0000_4_x0000__x000D__x0000__x0001_ø»1Á_x0004_Õ|·Ç _x0000_1_x0000_5Î _x0000_1_x0000_0_x0000_3_x0000_8Ö_x000D__x0000__x0000_010-3909-6608_x0015__x0000__x0000_sjs940421@hanmail.net_x000B__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_2_x0000_6_x0000__x0008__x0000__x0000_20171226_x000E__x0000__x0000_37690004615537_x0006__x0000__x0000_D00409_x0007__x0000__x0001_Æ%±¤Â _x0000_¤ÂìÓ Î
+_x0000__x0000_8624500277_x0003__x0000__x0001_tÇU³©Æ_x0008__x0000__x0000_20170905_x000C__x0000__x0000_041-357-1617_x0008__x0000__x0001_©Í­Ì¨°Ä³ _x0000_ù²ÄÉÜÂ_x0005__x0000__x0000_31777_x000E__x0000__x0001_©Í¨° _x0000_ù²ÄÉÜÂ _x0000_P­Ù³8® _x0000_1_x0000_2_x0000_4_x0000__x000D__x0000__x0000_010-3116-9915_x0013__x0000__x0000_ljy161617@naver.com_x0008__x0000__x0000_20171221_x000E__x0000__x0000_37690004616137_x0006__x0000__x0000_D00416_x0005__x0000__x0001__x001C_ÁÄÉ¤ÂìÓ Î
+_x0000__x0000_5920100957_x0003__x0000__x0001_@®ÉÓÜÐ_x000D__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_ _x0000__x0004_ÈÇÁÀp¬·ÅÅ_x0008__x0000__x0000_20180301_x000C__x0000__x0000_031-236-4936_x000C__x0000__x0000_031-216-4936_x0007__x0000__x0001_½¬0®Ä³ _x0000_©ÆxÇÜÂ_x0005__x0000__x0000_16833_x0013__x0000__x0001_½¬0® _x0000_©ÆxÇÜÂ _x0000__x0018_ÂÀÉl­ _x0000_ìÓ@Ç_x0000_³\¸ _x0000_4_x0000_6_x0000_7_x0000__x0016__x0000__x0001__x0018_ÂÀÉxÔt¹ÀÉ$ÆÔÆÜ´È¹lÐÁÀ_x0000_¬ _x0000_1_x0000_0_x0000_3_x0000_Ù³ _x0000_1_x0000_2_x0000_3_x0000_8Ö_x000D__x0000__x0000_010-4679-5630_x0013__x0000__x0000_ren7303@hanmail.net_x000E__x0000__x0000_37690004618437_x0006__x0000__x0000_D00431_x0006__x0000__x0001_¤ÂìÓ Îä¹È²DÅ
+_x0000__x0000_2701201033_x0003__x0000__x0001_8»¹ÂÄÉ_x0008__x0000__x0000_20180615_x000C__x0000__x0000_042-545-8511	_x0000__x0001__x0000_³_x0004_È_x0011_­íÅÜÂ _x0000_ Ç1Ál­_x0005__x0000__x0000_34210_x0016__x0000__x0001__x0000_³_x0004_È _x0000_ Ç1Ál­ _x0000_YÕXÕ_x0011_ÉYÅ\¸1_x0000_2_x0000_8_x0000_¼8® _x0000_2_x0000_3_x0000_-_x0000_8_x0000__x000B__x0000__x0001_1_x0000_0_x0000_2_x0000_8Ö _x0000_¤ÂìÓ Îä¹È²DÅ_x000D__x0000__x0000_010-6683-2114_x0013__x0000__x0000_capmoon39@naver.com_x0008__x0000__x0000_20180427_x000E__x0000__x0000_37690004623037_x0006__x0000__x0000_D00433_x000D__x0000__x0001__x0015_È_x0018_Â¤ÂìÓ Î _x0000_Æ%±¤Â _x0000__x0001_ÆüÈ_x0010_È
+_x0000__x0000_5293300343_x0003__x0000__x0001_@®Ù³ðÅ	_x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_ _x0000_XÇX¹_x0008__x0000__x0000_20170407_x000B__x0000__x0000_01048177736
+_x0000__x0000_0546367233_x0008__x0000__x0001_½¬ÁÀ½Ä³ _x0000__x0001_ÆüÈÜÂ_x0005__x0000__x0000_36138_x0013__x0000__x0001_½¬½ _x0000__x0001_ÆüÈÜÂ _x0000__x0000_³YÕ\¸2_x0000_0_x0000_1_x0000_¼8® _x0000_8_x0000_-_x0000_6_x0000__x0007__x0000__x0001_iÖ_x0008_®L¾)µ _x0000_1_x0000_5Î_x000D__x0000__x0000_010-4817-7736_x0013__x0000__x0000_kdy9249@hanmail.net_x0008__x0000__x0000_20180518_x000E__x0000__x0000_37690004624637_x0006__x0000__x0000_D00471_x000B__x0000__x0001_(_x0000_üÈ)_x0000_DÅüÈ_x0008_¸ìÓ Î__x0000_¹Ò_x0010_Ó_x000B__x0000__x0001_(_x0000_üÈ)_x0000_DÅüÈ_x0008_¸ìÓ Î-_x0000_¹Ò_x0010_Ó_x0008__x0000__x0000_20181026_x000B__x0000__x0000_02-489-1992_x000E__x0000__x0001_½¬0® _x0000__x0011_­üÈÜÂ _x0000_à¬½\¸ _x0000_3_x0000_4_x0000_0_x0000__x000D__x0000__x0000_070-4741-9644_x000E__x0000__x0000_37690004626937_x0006__x0000__x0000_D00490	_x0000__x0001_à¬ÅÜÂ0¼Ü´ü»4Ñ_x0011_ÖÖ
+_x0000__x0000_1288284226_x0003__x0000__x0001_tÇ8ÖÄÉ_x0008__x0000__x0000_20190315_x000B__x0000__x0000_01027161641_x0005__x0000__x0000_10223_x0014__x0000__x0001_½¬0® _x0000_à¬ÅÜÂ _x0000_|Ç°À_x001C_Ál­ _x0000__x0011_ÉYÅ\¸ _x0000_1_x0000_6_x0000_0_x0000_1_x0000__x001D__x0000__x0001_,_x0000_ _x0000_1_x0000_5Î(_x0000__x0000_³TÖÙ³,_x0000_ _x0000_à¬ÅÜÂ+ÈiÕ´ÆÙ³¥Ç _x0000_ÀÉXÕ1_x0000_5Î _x0000_C_x0000_-_x0000_0_x0000_8_x0000_)_x0000__x000D__x0000__x0000_010-2716-1641_x0012__x0000__x0000_76melany@gmail.com_x0005__x0000__x0000_19003_x0003__x0000__x0001_HÅ¬Ç°Æ_x000E__x0000__x0000_37690004628137_x0006__x0000__x0000_D00503_x0005__x0000__x0001_°tÇ¤Âü»4Ñ
+_x0000__x0000_6161951553_x0003__x0000__x0001_à¬ðÅüÈ
+_x0000__x0001_¤ÂìÓ Î©ÆÔ_x000F_¼0®ÀÐ©ÆÔ_x0008__x0000__x0000_20100913_x000C__x0000__x0000_064-712-4524_x000C__x0000__x0000_064-711-4524_x000B__x0000__x0001__x001C_ÈüÈ¹ÒÄ¼ÇXÎÄ³ _x0000__x001C_ÈüÈÜÂ_x0005__x0000__x0000_63087_x0013__x0000__x0001__x001C_ÈüÈ¹ÒÄ¼ÇXÎÄ³ _x0000__x001C_ÈüÈÜÂ _x0000_ÄÉp­8® _x0000_1_x0000_-_x0000_6_x0000__x000D__x0000__x0000_010-3639-7899_x0011__x0000__x0000_ktf1974@naver.com_x0003__x0000__x0001_@®1Át¬_x000B__x0000__x0000_01036397899_x0008__x0000__x0000_20190424_x000E__x0000__x0000_37690004630837_x0006__x0000__x0000_D00504_x0008__x0000__x0001_¤ÂÀÐ¤ÂìÓ Î__x0000_¹Ò_x0010_Ó
+_x0000__x0000_3031310445	_x0000__x0001_¤ÂÀÐ¤ÂìÓ Î(_x0000_©ÍüÈ)_x0000__x0003__x0000__x0001_LÇ_x0011_­l×_x0008__x0000__x0000_20070607_x000C__x0000__x0000_043-855-7688_x000C__x0000__x0000_043-848-3727_x0008__x0000__x0001_©Í­Ì½Ä³ _x0000_©ÍüÈÜÂ_x0005__x0000__x0000_27393_x000E__x0000__x0001_©Í½ _x0000_©ÍüÈÜÂ _x0000__x0015_Ö$Á\¸ _x0000_1_x0000_5_x0000_9_x0000__x0005__x0000__x0001_¤ÂÀÐ¤ÂìÓ Î_x000D__x0000__x0000_010-5303-1397_x0013__x0000__x0000_ekh3083@hanmail.net_x0006__x0000__x0000_D00513	_x0000__x0001__x001C_Á¸ÆÜÂ´Ì!ÇÖ__x0000_¹Ò_x0010_Ó
+_x0000__x0000_6078287556_x0006__x0000__x0001__x001C_Á¸ÆÜÂ´Ì!ÇÖ_x0003__x0000__x0001__x0015_¼ÐÆ_x001C_Â_x0003__x0000__x0001__x001C_ÁD¾¤Â_x0004__x0000__x0001_LÑÈ²¤Â¥Ç_x0008__x0000__x0000_20190614_x0001__x0000__x0000_0	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x0011_É·l­_x0005__x0000__x0000_02119_x000E__x0000__x0001__x001C_Á¸Æ _x0000__x0011_É·l­ _x0000_Ý¹°Æ\¸ _x0000_1_x0000_8_x0000_2_x0000__x0008__x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ´Ì!ÇÖ_x0008__x0000__x0000_20190617_x000E__x0000__x0000_37690004638937_x0006__x0000__x0000_D00515_x0004__x0000__x0001__x0001_Æ4»S_x0000_P_x0000_
+_x0000__x0000_4081497216_x0004__x0000__x0001__x0001_Æ4»s_x0000_p_x0000__x0003__x0000__x0001_@®U³	½_x0007__x0000__x0001_Ä³Áä¹,_x0000_ _x0000__x001C_ÈpÈ_x0011__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_ _x0000_±tÇ0®l­,_x0000_ _x0000_ìÕ¤Â0®l­_x0008__x0000__x0000_20070824_x000D__x0000__x0000_010-3622-7289_x000C__x0000__x0000_062-651-9942_x0008__x0000__x0001__x0011_­üÈ_x0011_­íÅÜÂ _x0000_¨°l­_x0005__x0000__x0000_61655_x000E__x0000__x0001__x0011_­üÈ _x0000_¨°l­ _x0000__x0000_³¨°_x0000_³\¸ _x0000_2_x0000_5_x0000_2_x0000_	_x0000__x0001_1¼´ÆÙ³,_x0000_ _x0000__x0001_Æ4»S_x0000_P_x0000__x0013__x0000__x0000_6519944@hanmail.net_x000D__x0000__x0000_(062)653-4141$_x0000__x0001_2_x0000_4_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_3_x0000_5_x0000_ _x0000_/_x0000_2_x0000_4_x0000_S_x0000_S_x0000__x0018_ÂüÈìÅàÂ _x0000_3_x0000_5_x0000_ _x0000_/_x0000_ _x0000__x0018_Â_x0008_®½qÈ _x0000_2_x0000_ÔÆµÑ_x001C_È_x0008__x0000__x0000_20190531_x000E__x0000__x0000_37690004634337_x0006__x0000__x0000_D00517_x000B__x0000__x0001_O_x0000_K_x0000_ _x0000_¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1293177008_x0003__x0000__x0001_tÇ_x0001_Æ±Æ
+_x0000__x0001_Ä³Áä¹,_x0000_Ä³ä¹,_x0000__x001C_ÁD¾¤Â_x0011__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_l­ä¹_x0000_³Õ,_x0000_t¬&lt;»­ÌÁ©ÆíÅ_x0008__x0000__x0000_20071108_x000C__x0000__x0000_031-708-3066
+_x0000__x0000_0317083067_x0005__x0000__x0000_13504_x0017__x0000__x0001_½¬0® _x0000_1Á¨°ÜÂ _x0000_½ù²l­ _x0000_¥Çø»\¸1_x0000_2_x0000_2_x0000_¼8® _x0000_3_x0000_-_x0000_1_x0000__x0005__x0000__x0001_(_x0000_|ÅÑÐÙ³)_x0000__x000D__x0000__x0000_010-8714-3324_x0014__x0000__x0000_75winwin@hanmail.net_x000B__x0000__x0000_01087143324_x000E__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_5_x0000_+_x0000_2_x0000_2_x0000__x0008__x0000__x0000_20190621_x000E__x0000__x0000_37690004635037_x0006__x0000__x0000_D00519_x0005__x0000__x0001__x0004_Ç_x0008_±¤ÂìÓ Î
+_x0000__x0000_3160449978_x0003__x0000__x0001_\Í_x0004_ÖÄÉ_x0008__x0000__x0000_20140927_x000D__x0000__x0000_010-6482-0228_x000C__x0000__x0000_041-665-1857_x0008__x0000__x0001_©Í­Ì¨°Ä³ _x0000__x001C_Á°ÀÜÂ_x0005__x0000__x0000_31993_x000F__x0000__x0001_©Í¨° _x0000__x001C_Á°ÀÜÂ _x0000_(ÇÀÉ1_x0000_6_x0000_\¸ _x0000_2_x0000_2_x0000__x0008__x0000__x0001_C_x0000_Ù³ _x0000_(_x0000_Ù³8»Ù³)_x0000__x0011__x0000__x0000_chj1981@naver.com_x000D__x0000__x0000_010-9112-9996_x0008__x0000__x0001_6_x0000_ÔÆ _x0000_üÈ8»µÑ_x001C_È/_x0000__x0008__x0000__x0000_20190620_x000E__x0000__x0000_37690004636637_x0006__x0000__x0000_D00524
+_x0000__x0001_üÈÝÂÖ¬À _x0000_©ÆxÇÆ%±¤Â
+_x0000__x0000_7968702997_x0003__x0000__x0001_@®ÄÉ©Æ_x0008__x0000__x0000_20150409_x000D__x0000__x0000_010-8881-0413_x0005__x0000__x0000_16967_x0014__x0000__x0001_½¬0® _x0000_©ÆxÇÜÂ _x0000_0®e×l­ _x0000_àÂ_x0008_¬\¸5_x0000_7_x0000_¼8® _x0000_7_x0000_
+_x0000__x0001_(_x0000_àÂ_x0008_¬Ù³,_x0000_ÐÅ¤Â_x001C_ÈtÇ)_x0000__x0013__x0000__x0000_goodester@naver.com_x0007__x0000__x0001_2_x0000_ÔÆ _x0000__x0018_Â_x0008_®µÑ_x001C_È_x0008__x0000__x0000_20190711_x000E__x0000__x0000_37690004640537_x0006__x0000__x0000_D00526_x0006__x0000__x0001_ìÅ_x0018_Â _x0000_Æ%±¤Â
+_x0000__x0000_6765400493_x0003__x0000__x0001_@® ÁU³_x0008__x0000__x0000_20190701_x000D__x0000__x0000_010-2066-5376_x0008__x0000__x0001__x0004_È|·¨°Ä³ _x0000_ìÅ_x0018_ÂÜÂ_x0005__x0000__x0000_59685_x000D__x0000__x0001__x0004_È¨° _x0000_ìÅ_x0018_ÂÜÂ _x0000_ÈÀ0Ñ\¸ _x0000_2_x0000_5_x0000__x0005__x0000__x0001_(_x0000_àÂ0®Ù³)_x0000__x0014__x0000__x0000_junsoo5376@naver.com_x0003__x0000__x0001_@®_x0000_É_x0018_Â_x0002__x0000__x0001__x0000_¬qÈ_x000E__x0000__x0000_37690004621737_x0006__x0000__x0000_D00527_x000C__x0000__x0001_(_x0000_üÈ)_x0000_tÇÐÅ¤Â¤ÂìÓ Î__x0000_¹Ò_x0010_Ó
+_x0000__x0000_2848100873	_x0000__x0001_(_x0000_üÈ)_x0000_tÇÐÅ¤Â¤ÂìÓ Î_x0003__x0000__x0001__x0015_¼_x0018_Â Ì_x000C__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_ _x0000_µÑàÂ_x0010_Óä¹ÅÅ_x0008__x0000__x0000_20171228_x000C__x0000__x0000_031-763-2002_x000C__x0000__x0000_031-763-0400_x0005__x0000__x0000_12739_x000D__x0000__x0001_½¬0® _x0000__x0011_­üÈÜÂ _x0000_µÑø»\¸ _x0000_9_x0000_2_x0000__x000D__x0000__x0000_010-4085-9292_x0014__x0000__x0000_gysports@hanmail.net_x0008__x0000__x0000_20190725_x000E__x0000__x0000_37690004641137_x0006__x0000__x0000_D00528_x0007__x0000__x0001_2_x0000_0_x0000_8_x0000_0_x0000_Æ%±¤Â
+_x0000__x0000_8131601217_x0003__x0000__x0001_@®ÀÉÐÆ_x000C__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_ _x0000_¤ÂìÓ ÎXÇX¹_x000C__x0000__x0000_061-795-2088_x0008__x0000__x0001__x0004_È|·¨°Ä³ _x0000__x0011_­ÅÜÂ_x0005__x0000__x0000_57767_x0010__x0000__x0001__x0004_È¨° _x0000__x0011_­ÅÜÂ _x0000_ÀÉÙ³8® _x0000_3_x0000_0_x0000_-_x0000_3_x0000_5_x0000__x000D__x0000__x0000_010-9434-2223_x0013__x0000__x0000_3530162@hanmail.net_x0008__x0000__x0000_20190730_x000E__x0000__x0000_37690004643437_x0006__x0000__x0000_D00529	_x0000__x0001_°Æ¬¹¤ÂìÓ Î(_x0000__x0011_­üÈ)_x0000_
+_x0000__x0000_5212100399_x0003__x0000__x0001_$Æ_x0018_ÂÔÆ_x0008__x0000__x0000_20191030_x000C__x0000__x0000_062-434-8963_x0008__x0000__x0001__x0011_­üÈ_x0011_­íÅÜÂ _x0000_½l­_x0005__x0000__x0000_61185_x0018__x0000__x0001__x0011_­üÈ _x0000_½l­ _x0000_¨Ìè²ðÅàÂ\¸ _x0000_2_x0000_9_x0000_¼8® _x0000_1_x0000_5_x0000_ _x0000_ÀÉÁÀ1_x0000_5Î_x000D__x0000__x0001_½l­+ÈiÕ´Ì!Ç_x0000_­ _x0000_´Ì!Ç©ÆÔ_x0010_È_x000D__x0000__x0000_010-4614-9599_x000F__x0000__x0000_19qkqn@daum.net_x000B__x0000__x0000_01046149599_x000D__x0000__x0001_2_x0000_6_x0000_F_x0000_W_x0000_ _x0000_©ÆÔ_x0018_ÂüÈ _x0000_ø»8ÌìÅ_x0008__x0000__x0000_20190802_x000E__x0000__x0000_37690004642837_x0006__x0000__x0000_D00530_x000B__x0000__x0001_àÂàÂ´Ì!Ç¬À _x0000_2_x0000_1_x0000___x0000_¹Ò_x0010_Ó
+_x0000__x0000_1288148960_x000B__x0000__x0001_üÈÝÂÖ¬À _x0000_àÂàÂ´Ì!Ç2_x0000_1_x0000__x0003__x0000__x0001_iÖ¹Â8Ö_x0002__x0000__x0001__x001C_ÈpÈ_x0008__x0000__x0000_20000523
+_x0000__x0000_0319453376
+_x0000__x0000_0319450458_x0005__x0000__x0000_10844_x0013__x0000__x0001_½¬0® _x0000__x000C_ÓüÈÜÂ _x0000_ÔÆq¸tº _x0000_¬_x0014_¼_x0004_Ç8® _x0000_1_x0000_2_x0000_3_x0000__x0006__x0000__x0001_àÂàÂ´Ì!Ç$ÁD¾_x0014__x0000__x0000_sinsin5980@naver.com_x0008__x0000__x0000_20190823_x000E__x0000__x0000_37690004645737_x0006__x0000__x0000_D00534
+_x0000__x0001_2_x0000_0_x0000_1_x0000_9_x0000_ _x0000_TÏ¬¹DÅ$Æ_x0008_Õ
+_x0000__x0000_0000000000	_x0000__x0000_023352551_x0005__x0000__x0000_03964_x000E__x0000__x0001__x001C_Á¸Æ _x0000_È¹ìÓl­ _x0000_ìÓ@Ç\¸ _x0000_1_x0000_2_x0000_0_x0000__x0004__x0000__x0001_U³|ÇL¾)µ_x0008__x0000__x0000_20190918_x0006__x0000__x0000_D00538_x000E__x0000__x0001__x0000_³\Õ¤ÂìÓ Î°ÀÅÅ_x0011_ÖÙ³pÈiÕ__x0000_¹Ò_x0010_Ó
+_x0000__x0000_1168210643_x0003__x0000__x0001_üÈ_x0015_Ö8Ö	_x0000__x0001_´ÆÙ³©Æl­ _x0000__x000F_¼ _x0000_$ÁXÎ_x0008__x0000__x0000_19700319	_x0000__x0000_027867761	_x0000__x0000_027867764_x0005__x0000__x0000_07345_x000E__x0000__x0001__x001C_Á¸Æ _x0000__x0001_Æñ´ìÓl­ _x0000_6_x0000_3_x0000_\¸ _x0000_4_x0000_0_x0000__x0014__x0000__x0001_7_x0000_2_x0000_3_x0000_8Ö _x0000_(_x0000_ìÅXÇÄ³Ù³,_x0000_ _x0000_|·tÇ_x0004_Õ$Æ&lt;Õ¤ÂTÑ)_x0000__x0008__x0000__x0000_20190724_x000E__x0000__x0000_37690004646337_x0006__x0000__x0000_D00539_x000C__x0000__x0001_(_x0000_üÈ)_x0000__x0004_²¬¹ÐÅ¤ÂdÅÀÉ__x0000_¹Ò_x0010_Ó
+_x0000__x0000_2018609461	_x0000__x0001_(_x0000_üÈ)_x0000__x0004_²¬¹ÐÅ¤ÂdÅÀÉ_x0002__x0000__x0001_@®%Æ_x000C__x0000__x0000_031-527-8417_x0005__x0000__x0000_12245_x0015__x0000__x0001_½¬0® _x0000_¨°ÅüÈÜÂ _x0000_½¬_x0015_¬\¸2_x0000_9_x0000_4_x0000_¼8® _x0000_3_x0000_2_x0000_-_x0000_1_x0000__x0008__x0000__x0000_20190626_x000E__x0000__x0000_37690004648637_x0006__x0000__x0000_D00541_x0007__x0000__x0001_íÂtÇ_x0004_¬ÀÉ__x0000_¹Ò_x0010_Ó_x000C__x0000__x0001_¹Ò_x0010_Ó _x0000_p¬· Á _x0000_ÇÜÂ _x0000_ñ´]¸_x000D__x0000__x0000_010-2850-8962_x0003__x0000__x0001_Æ%±¤Â_x0008__x0000__x0000_20191014_x000E__x0000__x0000_37690004647037_x0006__x0000__x0000_D00543	_x0000__x0001_Á¨ºÇè²´Ìõ¼__x0000_¹Ò_x0010_Ó_x0004__x0000__x0001_Ù³¹ÂµÑÁÀ_x0008__x0000__x0000_20191016_x000E__x0000__x0000_37690004674237_x0006__x0000__x0000_D00546_x000B__x0000__x0001_8ÁÄÉ¤ÂìÓ Î)¼ü¬ÄÖ__x0000_¹Ò_x0010_Ó_x0005__x0000__x0000_06964_x000E__x0000__x0001__x001C_Á¸Æ _x0000_Ù³Çl­ _x0000_ÁÀÄ³\¸ _x0000_2_x0000_4_x0000_2_x0000__x0008__x0000__x0000_20191023_x000E__x0000__x0000_37690004649237_x0006__x0000__x0000_D00549	_x0000__x0001_)¼ü¬ÄÖà¬Ç_x0008_Í__x0000_¹Ò_x0010_Ó
+_x0000__x0000_1318303677_x0008__x0000__x0001_xÇÌà¬Ç_x0008_Íñ´YÕP­_x0003__x0000__x0001_@®_x001C_Âl×_x000C__x0000__x0000_032-433-0464	_x0000__x0001_xÇÌ_x0011_­íÅÜÂ _x0000_¨°Ù³l­_x0005__x0000__x0000_21685_x0014__x0000__x0001_xÇÌ _x0000_¨°Ù³l­ _x0000_DÅTÅ_x0000_³\¸1_x0000_5_x0000_0_x0000_3_x0000_¼8® _x0000_4_x0000_8_x0000__x000F__x0000__x0000_gojan@ice.go.kr_x0008__x0000__x0000_20191028_x0006__x0000__x0000_D00550
+_x0000__x0001_TÏ¬¹DÅü»4Ñ¬À·__x0000_¹Ò_x0010_Ó_x0008__x0000__x0000_20191108_x000E__x0000__x0000_37690004650237_x0006__x0000__x0000_D00554	_x0000__x0001_üÈýÅ_x0008_Íñ´YÕP­__x0000_¹Ò_x0010_Ó
+_x0000__x0000_1288302804_x0003__x0000__x0001__x0015_¼	½ Á_x000B__x0000__x0000_0319120031 _x0005__x0000__x0000_10385_x0012__x0000__x0001_½¬0® _x0000_à¬ÅÜÂ _x0000_|Ç°À_x001C_Ál­ _x0000__x0015_¬ Á\¸ _x0000_2_x0000_9_x0000__x0006__x0000__x0001_üÈýÅ_x0008_Íñ´YÕP­_x0008__x0000__x0000_20191118_x0006__x0000__x0000_D00557_x000B__x0000__x0001_üÈÝÂÖ¬À _x0000_tÎxÇÜ´ÉÅtÐÉ
+_x0000__x0000_7318601539_x0003__x0000__x0001_¥Ç¬Ç_x0001_Ö_x0008__x0000__x0000_20191210_x000D__x0000__x0000_010-2600-1460_x0005__x0000__x0000_06065_x000E__x0000__x0001__x001C_Á¸Æ _x0000__x0015_¬¨°l­ _x0000_ Á¹\¸ _x0000_7_x0000_2_x0000_0_x0000__x000E__x0000__x0001_ Ç_x0000_­L¾)µ _x0000_ÀÉXÕ1_x0000_5Î _x0000_ô¼Ü´|·xÇ_x0013__x0000__x0000_paul777@hanmail.net_x0008__x0000__x0000_20200914_x0006__x0000__x0000_D00560	_x0000__x0001_üÈÝÂÖ¬À _x0000__x0014_µÀÉ8ÑÄÉ
+_x0000__x0000_6418600391_x0003__x0000__x0001__x0015_¼¼ Á_x0019__x0000__x0001_ôÎèÔ0Ñ _x0000__x000F_¼ _x0000_üÈÀ¼0®0®,_x0000_ _x0000_´ÆÙ³ _x0000__x000F_¼ _x0000_½¬0®©ÆÔ _x0000_Ä³ä¹ _x0000__x0008__x0000__x0000_20160401_x000B__x0000__x0000_02-707-3326	_x0000__x0000_027038437	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_©Æ°Àl­_x0005__x0000__x0000_04366_x0011__x0000__x0001__x001C_Á¸ÆÜÂ _x0000_Ù³Çl­ _x0000__x0000_³)¼Ù³1_x0000_5_x0000_8® _x0000_3_x0000_0_x0000__x000D__x0000__x0000_010-4722-8308_x0014__x0000__x0000_jin@digitaljin.co.kr_x0005__x0000__x0000_24016_x0003__x0000__x0001_8»=Ì_x0018_Â_x0008__x0000__x0000_20191220_x000E__x0000__x0000_37690004655437_x0017__x0000__x0001_0_x0000_1_x0000_0_x0000_-_x0000_7_x0000_4_x0000_1_x0000_4_x0000_-_x0000_1_x0000_6_x0000_7_x0000_8_x0000_ _x0000_$Ç1ÁÜ­ _x0000_(_x0000_A_x0000_/_x0000_S_x0000_)_x0000__x0006__x0000__x0000_D00563	_x0000__x0001__x0001_ÆÅÅ3_x0000__x0000_Ó0®ÀÐ__x0000_¹Ò_x0010_Ó	_x0000__x0000_023332568_x0008__x0000__x0000_20200101_x0006__x0000__x0000_D00564_x0008__x0000__x0001_ü»4Ñ¤ÂìÓ Î__x0000_¹Ò_x0010_Ó_x0005__x0000__x0001__x001C_¬xÇ¬ÀÅÅÇ
+_x0000__x0000_1013095995_x0005__x0000__x0001_ü»4Ñ¤ÂìÓ Î_x0003__x0000__x0001_à¬_x0015_È%Æ_x0008__x0000__x0000_00000000_x0008__x0000__x0001__x0004_È|·½Ä³ _x0000_à¬=Ìp­_x0005__x0000__x0000_56430_x0012__x0000__x0001__x0004_È½ _x0000_à¬=Ìp­ _x0000_à¬=ÌMÇ _x0000_ÔÆá¬5_x0000_8® _x0000_1_x0000_1_x0000__x0008__x0000__x0000_20200103_x000E__x0000__x0000_37690004654837_x0006__x0000__x0000_D00568_x0007__x0000__x0001_\Õ¤ÂìÓ Î__x0000_¹Ò_x0010_Ó
+_x0000__x0000_3031277167_x0004__x0000__x0001_\Õ¤ÂìÓ Î_x0003__x0000__x0001_iÖ+ÈôÅ_x000D__x0000__x0000_010-5103-6696_x0005__x0000__x0000_27357_x0010__x0000__x0001_©Í½ _x0000_©ÍüÈÜÂ _x0000_Ä¬+º_x0000_³\¸ _x0000_9_x0000_1_x0000_-_x0000_1_x0000__x0005__x0000__x0001_(_x0000_P­_x0004_ÖÙ³)_x0000__x0016__x0000__x0000_archihjy@hometax.go.kr_x0008__x0000__x0000_20200203_x000E__x0000__x0000_37690004658337_x0006__x0000__x0000_D00574_x0006__x0000__x0001_¤Âä¹ñÂ¤ÂìÓ Î
+_x0000__x0000_1238638685_x0003__x0000__x0001_tÇ Ìl×_x0008__x0000__x0001_Ä³Áä¹,_x0000_ _x0000__x001C_ÈpÈÅÅ_x000C__x0000__x0001__x0004_ÈÇÁÀp¬·,_x0000_ _x0000_¤ÂìÓ Î©ÆÔ_x0008__x0000__x0000_20130615
+_x0000__x0000_0314271787_x000B__x0000__x0000_05054271788_x0005__x0000__x0000_15850_x000E__x0000__x0001_½¬0® _x0000_p­ìÓÜÂ _x0000_à¬°À\¸ _x0000_1_x0000_6_x0000_6_x0000__x000F__x0000__x0001_S_x0000_K_x0000_¤¼ðÒÀÆ _x0000_1_x0000_0_x0000_4_x0000_Ù³ _x0000_5_x0000_0_x0000_6_x0000_8Ö_x000D__x0000__x0000_010-3690-1786_x0011__x0000__x0000_4271787@naver.com_x000B__x0000__x0000_07046403943_x0005__x0000__x0000_19022_x0003__x0000__x0001_àÂÙ³ÐÆ_x0008__x0000__x0000_20200220_x000E__x0000__x0000_37690004666837_x0006__x0000__x0000_D00576_x0008__x0000__x0001_1¼È¹¤ÂìÓ Î__x0000_¹Ò_x0010_Ó_x0008__x0000__x0000_20200302_x000E__x0000__x0000_37690004667437_x0006__x0000__x0000_D00578_x0008__x0000__x0001_MÖ1ÁÆ%±¤Â__x0000_¹Ò_x0010_Ó_x0006__x0000__x0001_MÖ1Á _x0000_Æ%±¤Â_x0008__x0000__x0000_20200316_x0005__x0000__x0000_32223_x0016__x0000__x0001_©Í¨° _x0000_MÖ1Áp­ _x0000_MÖ1ÁMÇ _x0000_pÈÅ\¸1_x0000_0_x0000_3_x0000_¼8® _x0000_3_x0000_5_x0000__x000E__x0000__x0000_17-2 17-5 17-6_x000E__x0000__x0000_37690004669737_x0006__x0000__x0000_D00580_x0008__x0000__x0001__x0008_®_x0001_Æ¤ÂìÓ Î__x0000_¹Ò_x0010_Ó_x0005__x0000__x0000_04005_x0010__x0000__x0001__x001C_Á¸Æ _x0000_È¹ìÓl­ _x0000_Ù³P­\¸3_x0000_8® _x0000_1_x0000_2_x0000_5_x0000__x0003__x0000__x0000_205_x0008__x0000__x0000_20200324_x000E__x0000__x0000_37690004671337_x0006__x0000__x0000_D00585_x0008__x0000__x0001_Tº_x0014_µ¬ÀtÇ¸Å__x0000_¹Ò_x0010_Ó
+_x0000__x0000_2102438564_x0005__x0000__x0001_Tº_x0014_µ¬ÀtÇ¸Å_x0003__x0000__x0001__x0015_¼ÌÕÝÂ_x000D__x0000__x0001__x001C_ÁD¾¤Â,_x0000_ _x0000_Ä³ä¹ _x0000__x000F_¼ _x0000_Áä¹ÅÅ_x0010__x0000__x0001_$ÁXÎ_x000F_¼ ÇÀÉô¼_x0018_Â,_x0000_ _x0000_8»l­,_x0000_ _x0000_0®P±Ô_x000B__x0000__x0000_01088813256	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_1ÁÙ³l­_x0005__x0000__x0000_04750_x000F__x0000__x0001__x001C_Á¸Æ _x0000_1ÁÙ³l­ _x0000_à¬°ÀÇ\¸ _x0000_2_x0000_8_x0000_4_x0000__x0018__x0000__x0001_3_x0000_5Î _x0000_3_x0000_0_x0000_1_x0000_8Ö _x0000_6_x0000_1_x0000_äÂ _x0000_(_x0000_Õù²Ù³,_x0000_ _x0000_1ÁÙ³äÀt¹Ý¹)_x0000__x0015__x0000__x0000_eg6753256@hanmail.net_x0008__x0000__x0000_20200525_x000E__x0000__x0000_37690004672037_x0006__x0000__x0000_D00587_x000B__x0000__x0001_üÈÝÂÖ¬À _x0000_°tÇ¤Â(Ó_x0000_¼¬¹
+_x0000__x0000_3658101754_x0003__x0000__x0001__x0015_¼=Ìü»_x000B__x0000__x0001_¤ÂìÓ Î _x0000_©ÆÔ _x0000_Ä³Áä¹ÅÅ_x0008__x0000__x0000_20200407_x000C__x0000__x0000_031-341-8677_x000D__x0000__x0000_031-8068-5999_x0007__x0000__x0001_½¬0®Ä³ _x0000_XÇUÆÜÂ_x0005__x0000__x0000_16011_x000C__x0000__x0001_½¬0® _x0000_XÇUÆÜÂ _x0000_­ÌÄ¬\¸ _x0000_2_x0000__x000D__x0000__x0000_010-7417-4040_x0011__x0000__x0000_cmin401@naver.com_x0008__x0000__x0000_20200602_x000E__x0000__x0000_37690004673637_x0006__x0000__x0000_D00600	_x0000__x0001_Ä³á¬_x0008_Íñ´YÕP­__x0000_¹Ò_x0010_Ó_x0003__x0000__x0001_$Çø»l×_x0003__x0000__x0001_½Ù³°À_x0002__x0000__x0001_Ç_x0000_³	_x0000__x0000_025804577_x0005__x0000__x0000_06205_x0010__x0000__x0001__x001C_Á¸Æ _x0000__x0015_¬¨°l­ _x0000_ Á¹\¸6_x0000_4_x0000_8® _x0000_3_x0000_3_x0000__x0008__x0000__x0001__x001C_Á¸ÆÄ³á¬_x0008_Íñ´YÕP­_x0008__x0000__x0000_20201015_x0006__x0000__x0000_D00602_x000C__x0000__x0001__x001C_Á¸ÆÜÂ0¼Ü´ü»4Ñ_x0011_ÖÖ__x0000_¹Ò_x0010_Ó
+_x0000__x0000_2048204832	_x0000__x0001__x001C_Á¸ÆÜÂ0¼Ü´ü»4Ñ_x0011_ÖÖ_x0003__x0000__x0001__x0015_¼¬ÇXÖ_x000D__x0000__x0000_010-4359-4949_x0004__x0000__x0001_5_x0000_0_x0000_2_x0000_8Ö_x0008__x0000__x0000_20201102_x000E__x0000__x0000_37690004675937_x0006__x0000__x0000_D00605_x000B__x0000__x0001_ÌHÅàÂHÅ_x0008_Íñ´YÕP­__x0000_¹Ò_x0010_Ó
+_x0000__x0000_3128300473_x0003__x0000__x0001_@®_x0015_È`Å_x0008__x0000__x0000_622-7063_x0005__x0000__x0000_31125_x0013__x0000__x0001_©Í¨° _x0000_ÌHÅÜÂ _x0000_Ù³¨°l­ _x0000_ÐÆ1Á2_x0000_5_x0000_8® _x0000_2_x0000_1_x0000__x0008__x0000__x0001_ÌHÅàÂHÅ_x0008_Íñ´YÕP­_x0008__x0000__x0000_20201116_x0006__x0000__x0000_D00608_x000E__x0000__x0001_(_x0000_üÈ)_x0000_ _x0000__x0018_±¼ÐÆ¤ÂìÓ Î(_x0000_T_x0000_S_x0000_)_x0000__x0008__x0000__x0000_20210107_x0005__x0000__x0000_38661_x000E__x0000__x0001_½¬½ _x0000_½¬°ÀÜÂ _x0000_½¬°À\¸ _x0000_2_x0000_4_x0000_3_x0000__x000B__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_2_x0000_4_x0000__x000E__x0000__x0000_37690004676537_x0006__x0000__x0000_D00609	_x0000__x0001__x0008_®_x0001_Æ¤ÂìÓ Î(_x0000_T_x0000_S_x0000_)_x0000_$_x0000__x0001_2_x0000_4_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_4_x0000_0_x0000_ _x0000_/_x0000__x0001_ÆÅÅ¬ÀÐÆ _x0000_Æ­Ì(_x0000_¥Ç0® _x0000_ø»p¬·,_x0000_ _x0000__x0018_Â_x0008_® _x0000_½tÇÕ)_x0000__x000E__x0000__x0000_37690004677137_x0006__x0000__x0000_D00610	_x0000__x0001_XÕD¾¤ÂìÓ Î(_x0000_T_x0000_S_x0000_)_x0000__x0016__x0000__x0000_daegu-daejin@naver.com_x000F__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_4_x0000_0_x0000_+_x0000_5_x0000_0_x0000__x000E__x0000__x0000_37690004678837_x0006__x0000__x0000_D00611	_x0000__x0001_1¼È¹¤ÂìÓ Î(_x0000_T_x0000_S_x0000_)_x0000__x0005__x0000__x0000_04011_x000F__x0000__x0001__x001C_Á¸Æ _x0000_È¹ìÓl­ _x0000_Ù³P­\¸9_x0000_8® _x0000_9_x0000_5_x0000__x0010__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_7_x0000_0_x0000_+_x0000_1_x0000_8_x0000_5_x0000__x000E__x0000__x0000_37690004679437_x0006__x0000__x0000_D00612_x000D__x0000__x0001_¼À1Á¤ÂìÓ Î(_x0000_8»½¬)_x0000_(_x0000_T_x0000_S_x0000_)_x0000__x0005__x0000__x0000_36956_x000E__x0000__x0001_½¬½ _x0000_8»½¬ÜÂ _x0000_¨º_x0004_È\¸ _x0000_1_x0000_4_x0000_6_x0000_V_x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_0_x0000_+_x0000_6_x0000_ _x0000_/_x0000_ _x0000_2_x0000_5_x0000_S_x0000_S_x0000_ _x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_0_x0000_ _x0000_/_x0000_ _x0000_ _x0000_2_x0000_4_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_5_x0000_ _x0000_/_x0000_ _x0000_2_x0000_4_x0000_S_x0000_S_x0000__x0018_ÂüÈìÅàÂ _x0000_5_x0000_ _x0000_/_x0000_ _x0000_2_x0000_3_x0000_F_x0000_W_x0000_ _x0000__x0018_ÂüÈ _x0000_ìÅàÂ _x0000_1_x0000_0_x0000_ _x0000_/_x0000_ _x0000_2_x0000_3_x0000_S_x0000_S_x0000_ _x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_0_x0000__x000E__x0000__x0000_37690004680437_x0006__x0000__x0000_D00614_x0008__x0000__x0001__x0001_ÆÅÅ4_x0000__x0000_ÓÇXÇä¹¥Ç_x000B__x0000__x0000_02-335-2551_x0008__x0000__x0000_20210115_x0006__x0000__x0000_D00616_x0005__x0000__x0001_8Á_x0001_Æ¤ÂìÓ Î
+_x0000__x0000_8055100483_x0005__x0000__x0001_¤ÂìÓ ÎXÇX¹_x0008__x0000__x0000_20210125_x000D__x0000__x0000_070-8808-8799_x0017__x0000__x0000_yonexsejinspo@naver.com_x000E__x0000__x0000_37690004683337_x0006__x0000__x0000_D00620_x000D__x0000__x0001_üÈÝÂÖ¬À _x0000_8ÁÄÉ¤ÂìÓ Î__x0000_è²Å³
+_x0000__x0001_X_x0000_7_x0000_ _x0000_è²Å³¨ºx³ _x0000_TÏÜ´_x0008__x0000__x0000_20210226_x000E__x0000__x0000_37690004684037_x0006__x0000__x0000_D00621_x000E__x0000__x0001_¬À$Á´Ì!Ç_x0000_­(_x0000__x000C_Õ_x0008_¸tÇ(Æ)_x0000___x0000_¹Ò_x0010_Ó
+_x0000__x0000_7820601928_x0004__x0000__x0001__x000C_Õ_x0008_¸tÇ(Æ_x0003__x0000__x0001_\ÍÑ¼ÅÆ_x0008__x0000__x0001_0¼Ü´ü»4ÑtÐý·´Æ_x0001_Æ_x0008__x0000__x0000_20210305_x000D__x0000__x0000_010-4343-5610_x0005__x0000__x0000_31234_x0017__x0000__x0001_©Í¨° _x0000_ÌHÅÜÂ _x0000_Ù³¨°l­ _x0000_©ºÌMÇ _x0000_1Á¨°\¸ _x0000_3_x0000_9_x0000_-_x0000_1_x0000__x0010__x0000__x0000_cbw007@naver.com_x000E__x0000__x0000_37690004685637_x0006__x0000__x0000_D00626_x000B__x0000__x0001__x0018_ÂÐÆ¥ÇHÅà¬ñ´YÕP­__x0000_¹Ò_x0010_Ó
+_x0000__x0000_1358302549_x0006__x0000__x0001_¥ÇHÅà¬ñ´YÕP­_x0003__x0000__x0001_ ÇtÕ·_x0004__x0000__x0001_½Ù³°ÀÅÅ_x0008__x0000__x0000_20210324_x000C__x0000__x0000_031-250-2901_x0007__x0000__x0001_½¬0®Ä³ _x0000__x0018_ÂÐÆÜÂ_x0005__x0000__x0000_16316_x0015__x0000__x0001_½¬0® _x0000__x0018_ÂÐÆÜÂ _x0000_¥ÇHÅl­ _x0000__x0000_³ÉÓ\¸5_x0000_2_x0000_¼8® _x0000_1_x0000_2_x0000__x0013__x0000__x0000_jangan5955@korea.kr_x000E__x0000__x0000_37690004686237_x0006__x0000__x0000_D00628_x0007__x0000__x0001_Æ%±¤Â _x0000__x0018_ÂÐÆ_x0010_È
+_x0000__x0000_4401101673_x0003__x0000__x0001__x0015_¼°_x0004_Ö_x000B__x0000__x0001_¤ÂìÓ Î©Æ _x0000_XÇX¹,_x0000_ _x0000_©ÆÔ_x0008__x0000__x0000_20210407_x000C__x0000__x0000_031-216-4009_x0005__x0000__x0000_16540_x0010__x0000__x0001_½¬0® _x0000__x0018_ÂÐÆÜÂ _x0000__x0001_ÆµÑl­ _x0000_ä¹ÐÆ\¸ _x0000_3_x0000__x000D__x0000__x0000_010-2888-3600_x0011__x0000__x0000_yonexsw@naver.com_x000E__x0000__x0000_37690004687937_x0006__x0000__x0000_D00631_x000C__x0000__x0001__x0011_É·l­0¼Ü´ü»4Ñ_x0011_ÖÖ__x0000_¹Ò_x0010_Ó_x0008__x0000__x0000_20210510_x0006__x0000__x0000_D00632_x0008__x0000__x0001_©ÆÔ¬ÀÅÅ½ _x0000_A_x0000_S_x0000__x0003__x0000__x0001_@® ÌÅÆ_x000B__x0000__x0000_02-335-8077_x0008__x0000__x0000_20210601_x0006__x0000__x0000_D00638_x000D__x0000__x0001_p¬1Á¤ÂìÓ Î(_x0000_HÅÙ³)_x0000_(_x0000_T_x0000_S_x0000_)_x0000__x0008__x0000__x0000_20210622_x000F__x0000__x0001_½¬½ _x0000_HÅÙ³ÜÂ _x0000_½¬½_x0000_³\¸ _x0000_4_x0000_1_x0000_8_x0000__x0018__x0000__x0001_(_x0000_%ÆÙ³,_x0000_ _x0000_LÑÈ¹_x0004_Õ|·Ç)_x0000_Æ%±¤Â _x0000_p¬1Á¤ÂìÓ Î(_x0000_HÅÙ³)_x0000__x0012__x0000__x0000_klcjjh@lycos.co.kr_x000E__x0000__x0000_37690004688537_x0006__x0000__x0000_D00640_x0005__x0000__x0001__x0014_¼x¹¤ÂìÓ Î
+_x0000__x0000_1313599978_x0006__x0000__x0001__x0014_¼x¹ _x0000_¤ÂìÓ Î_x0003__x0000__x0001_tÇ¬Ç_x0001_Æ_x0007__x0000__x0001_Áä¹ÅÅ,_x0000_Ä³ä¹ÅÅ_x0008__x0000__x0000_20210715_x000C__x0000__x0000_032-466-1365_x0005__x0000__x0000_21543_x000E__x0000__x0001_xÇÌ _x0000_¨°Ù³l­ _x0000_1¼¼\¸ _x0000_1_x0000_3_x0000_9_x0000_
+_x0000__x0001_Æ%±¤Â _x0000__x0014_¼x¹ _x0000_¤ÂìÓ Î_x000D__x0000__x0000_010-8872-9764_x0017__x0000__x0000_hangang6528@hanmail.net_x000E__x0000__x0000_37690004689137_x0006__x0000__x0000_D00641_x0004__x0000__x0001_$±¼·Ü´
+_x0000__x0000_1292781688_x0003__x0000__x0001_@®e×-Á_x0013__x0000__x0001__x0004_ÈÇÁÀp¬·ÅÅ,_x0000_ _x0000_¤Âì</v>
+          </cell>
+          <cell r="R38" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="S38" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="T38" t="e">
+            <v>#N/A</v>
           </cell>
           <cell r="U38" t="str">
             <v/>
@@ -4658,8 +5848,8 @@
           <cell r="Y38" t="str">
             <v/>
           </cell>
-          <cell r="Z38" t="str">
-            <v>02-824-8799</v>
+          <cell r="Z38" t="e">
+            <v>#N/A</v>
           </cell>
           <cell r="AA38" t="str">
             <v>Y</v>
@@ -4678,11 +5868,91 @@
           </cell>
         </row>
         <row r="39">
-          <cell r="B39" t="str">
-            <v>D00089</v>
+          <cell r="B39" t="e">
+            <v>#N/A</v>
           </cell>
           <cell r="C39" t="str">
-            <v>속초배드민턴</v>
+            <v xml:space="preserve">7690004499237_x0006__x0000__x0000_D00116_x000F__x0000__x0001_Æ%±¤ÂÈ¹°À_x0000_³¬¹_x0010_È(_x0000_ü»4Ñ¤ÂìÓ Î)_x0000_
+_x0000__x0000_6080288027_x0003__x0000__x0001_ Ç_x0001_Æ_x0019_Â_x0008__x0000__x0001_¤ÂìÓ Î©ÆÔ_x000F_¼XÇX¹_x000C__x0000__x0000_055-222-5431
+_x0000__x0000_0552225432_x0008__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_=ÌÐÆÜÂ_x0006__x0000__x0000_631852_x0018__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_=ÌÐÆÜÂ _x0000_È¹°ÀiÕìÓl­ _x0000_©ÆÈ¹\¸ _x0000_7_x0000_6_x0000_ _x0000_üÈÝÐ_x000D__x0000__x0000_010-3707-6245_x0016__x0000__x0000_dudtjs6245@hanmail.net_x000E__x0000__x0000_37690004504337_x0006__x0000__x0000_D00120_x0006__x0000__x0001_Æ%±¤Â­ÌüÈ_x0010_È
+_x0000__x0000_3170385854_x0003__x0000__x0001_\Í°Æ1Á_x000B__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_XÇX¹,_x0000__x0018_Ât¬_x0008__x0000__x0000_20110729_x000C__x0000__x0000_043-222-3040
+_x0000__x0000_0432245050_x0008__x0000__x0001_©Í­Ì½Ä³ _x0000_­ÌüÈÜÂ_x0006__x0000__x0000_361842_x0012__x0000__x0001_©Í½ _x0000_­ÌüÈÜÂ _x0000_ÁÀù²l­ _x0000_8Öø»\¸ _x0000_2_x0000_0_x0000_6_x0000__x0005__x0000__x0001_1_x0000_5Î _x0000_È!Î_x000D__x0000__x0000_010-5468-3319_x0015__x0000__x0000_wsung3525@hanmail.net_x0008__x0000__x0000_20080429_x000E__x0000__x0000_37690004507237_x0006__x0000__x0000_D00121_x000D__x0000__x0001_Æ%±¤ÂìÓmÕ_x0010_È(_x0000_XÕtÇlÐ¬¹´Å)_x0000_
+_x0000__x0000_5061736246_x0003__x0000__x0001__x0015_È@Ç_x0001_Æ_x0008__x0000__x0000_20090227_x000C__x0000__x0000_054-283-5234
+_x0000__x0000_0542835231_x0008__x0000__x0001_½¬ÁÀ½Ä³ _x0000_ìÓmÕÜÂ_x0006__x0000__x0000_790822_x0012__x0000__x0001_½¬½ _x0000_ìÓmÕÜÂ _x0000_¨°l­ _x0000__x0000_³Ä³Ù³ _x0000_8_x0000_6_x0000_-_x0000_2_x0000__x000D__x0000__x0000_010-4133-7770_x0014__x0000__x0000_minton1125@naver.com_x0008__x0000__x0000_20081105_x000E__x0000__x0000_37690004508937_x0006__x0000__x0000_D00122_x0005__x0000__x0001_°Æ¬¹¤ÂìÓ Î
+_x0000__x0000_4172105493_x0003__x0000__x0001__x0015_¼_x0018_ÂÄÉ_x0008__x0000__x0000_20180101_x000C__x0000__x0000_051-632-2681
+_x0000__x0000_0516322681_x0008__x0000__x0001_½°À_x0011_­íÅÜÂ _x0000_¨°l­_x0006__x0000__x0000_608827_x0011__x0000__x0001_½°À_x0011_­íÅÜÂ _x0000_¨°l­ _x0000_Ç ÇÉÓTÖ\¸ _x0000_4_x0000_9_x0000__x000D__x0000__x0000_010-2594-2682_x0015__x0000__x0000_moxie2000@hanmail.net_x000E__x0000__x0000_37690004509537_x0006__x0000__x0000_D00123_x0005__x0000__x0001_°Æ1Á¤ÂìÓ Î
+_x0000__x0000_2077003708_x0003__x0000__x0001_@®DÆÝÂ_x0008__x0000__x0000_20071009_x000B__x0000__x0000_02-465-1297	_x0000__x0000_024651197	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x0011_­ÄÉl­_x0006__x0000__x0000_143961_x0010__x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x0011_­ÄÉl­ _x0000_l­XÇ\¸ _x0000_6_x0000_6_x0000__x0014__x0000__x0001_1_x0000_5Î _x0000_(_x0000_l­XÇÙ³ _x0000_2_x0000_2_x0000_7_x0000_-_x0000_6_x0000_)_x0000_ _x0000_°Æ1Á¤ÂìÓ Î_x000D__x0000__x0000_010-3418-1230_x000F__x0000__x0000_ws418@naver.com_x000E__x0000__x0000_37690004510537_x0006__x0000__x0000_D00126_x0005__x0000__x0001_ÐÆÙ³´Ì!Ç¬À
+_x0000__x0000_3060363748_x0003__x0000__x0001_ü»Ñ¼ÁÉ_x0004__x0000__x0001_´ÆÙ³0®l­_x0008__x0000__x0000_20050705_x000C__x0000__x0000_042-531-4004
+_x0000__x0000_0425328899_x0008__x0000__x0001__x0000_³_x0004_È_x0011_­íÅÜÂ _x0000_Ù³l­_x0005__x0000__x0000_34630_x000D__x0000__x0001__x0000_³_x0004_È _x0000_Ù³l­ _x0000__x0000_³_x0004_È\¸ _x0000_7_x0000_6_x0000_5_x0000__x000D__x0000__x0000_010-5453-9536_x0012__x0000__x0000_wonspo@hanmail.net_x0008__x0000__x0000_20080214_x000E__x0000__x0000_37690004511137_x0006__x0000__x0000_D00127_x0008__x0000__x0001_ÐÆ¤ÂìÓ Î(_x0000__x001C_ÈüÈ)_x0000_
+_x0000__x0000_6160962051_x0003__x0000__x0001_@®ø»½¬_x000C__x0000__x0000_064-752-4422
+_x0000__x0000_0647232992_x000C__x0000__x0001__x001C_ÈüÈ¹ÒÄ¼ÇXÎÄ³ _x0000__x001C_ÁÀ­ìÓÜÂ_x0006__x0000__x0000_690161_x0013__x0000__x0001__x001C_ÈüÈ¹ÒÄ¼ÇXÎÄ³ _x0000__x001C_ÈüÈÜÂ _x0000_$Æ|·\¸ _x0000_1_x0000_3_x0000_4_x0000__x000D__x0000__x0000_010-4416-4412_x0015__x0000__x0000_crony0104@hanmail.net_x000E__x0000__x0000_37690004512837_x0006__x0000__x0000_D00132_x0005__x0000__x0001__x0004_ÈüÈÆ%±¤Â
+_x0000__x0000_4020887887_x0003__x0000__x0001_tÇ_x001C_Â+È_x000C__x0000__x0000_063-274-9337
+_x0000__x0000_0632789337_x0008__x0000__x0001__x0004_È|·½Ä³ _x0000__x0004_ÈüÈÜÂ_x0006__x0000__x0000_560080_x0013__x0000__x0001__x0004_È|·½Ä³ _x0000__x0004_ÈüÈÜÂ _x0000_DÆ°Àl­ _x0000_õ¬½\¸ _x0000_2_x0000_0_x0000__x000D__x0000__x0000_010-9224-8391_x0010__x0000__x0000_jyonex@naver.com_x000E__x0000__x0000_37690004516337_x0006__x0000__x0000_D00136_x0005__x0000__x0001__x001C_È|Ç¤ÂìÓ Î
+_x0000__x0000_4040533542_x000B__x0000__x0001__x001C_È|Ç_x0008_¸_x0000_È¤ÂìÓ Î(_x0000__x0015_ÈMÇ)_x0000__x0003__x0000__x0001_@®_x0011_­õ¼	_x0000__x0001_´ÆÙ³0®l­_x000F_¼´ÆÙ³õ¼xÆ_x000C__x0000__x0000_063-535-9146
+_x0000__x0000_0635332093_x0008__x0000__x0001__x0004_È|·½Ä³ _x0000__x0015_ÈMÇÜÂ_x0006__x0000__x0000_580804_x000F__x0000__x0001__x0004_È|·½Ä³ _x0000__x0015_ÈMÇÜÂ _x0000__x0011_ÉYÅ\¸ _x0000_8_x0000_3_x0000__x000D__x0000__x0000_010-9579-7800_x0016__x0000__x0000_sports9146@hanmaIl.net_x000E__x0000__x0000_37690004520237_x0006__x0000__x0000_D00137_x000B__x0000__x0001_üÈÝÂÖ¬À _x0000_0¼Ü´ü»4ÑÈ¹¸Ò
+_x0000__x0000_1108193203_x0003__x0000__x0001__x0015_ÈtÇ@±_x000B__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000__x0004_ÈÇÁÀp¬·_x0008__x0000__x0000_20130723_x000C__x0000__x0000_031-964-3530	_x0000__x0000_023829555_x0007__x0000__x0001_½¬0®Ä³ _x0000_à¬ÅÜÂ_x0005__x0000__x0000_10564_x0011__x0000__x0001_½¬0® _x0000_à¬ÅÜÂ _x0000_U³Ål­ _x0000_¼À¡Á\¸ _x0000_1_x0000_2_x0000__x0007__x0000__x0001_4_x0000_5Î _x0000_4_x0000_1_x0000_8_x0000_8Ö_x000D__x0000__x0000_010-7152-7538_x0014__x0000__x0000_mintonmart@naver.com_x000E__x0000__x0000_37690004521937_x0006__x0000__x0000_D00138	_x0000__x0001_üÈÝÂÖ¬ÀÙ³°Æ¤ÂìÓ Î
+_x0000__x0000_1108180426_x0003__x0000__x0001_¡Á_x0015_È|Ç_x000B__x0000__x0000_02-382-3598	_x0000__x0000_023553586	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_@ÇÉÓl­_x0006__x0000__x0000_122903_x0018__x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_@ÇÉÓl­ _x0000_ðÅ_x001C_Á\¸ _x0000_2_x0000_9_x0000_-_x0000_1_x0000_ _x0000_Ù³°Æ¤ÂìÓ Î_x000D__x0000__x0000_010-2018-3598_x0012__x0000__x0000_dvip1233@naver.com_x000B__x0000__x0000_01074353598
+_x0000__x0001__x0018_Â_x0008_® _x0000_½qÈ&lt;Ç\¸ _x0000_µÑ_x001C_È_x000E__x0000__x0000_37690004522537_x0006__x0000__x0000_D00141	_x0000__x0001__x0011_ÉYÅ¤ÂìÓ Î(_x0000_½¬üÈ)_x0000_
+_x0000__x0000_3226600323_x0003__x0000__x0001_iÖ_x0001_ÆäÂ_x0008__x0000__x0000_20081210_x000C__x0000__x0000_054-741-5177_x0008__x0000__x0001_½¬ÁÀ½Ä³ _x0000_½¬üÈÜÂ_x0006__x0000__x0000_780943_x0012__x0000__x0001_½¬ÁÀ½Ä³ _x0000_½¬üÈÜÂ _x0000__x0008_®1Á\¸ _x0000_2_x0000_9_x0000_4_x0000_-_x0000_1_x0000__x000D__x0000__x0000_010-7579-5177_x0014__x0000__x0000_jasp6304@hanmail.net_x0008__x0000__x0000_20081211_x000E__x0000__x0000_37690004525437_x0006__x0000__x0000_D00145_x0005__x0000__x0001_­Ìá¸¤ÂìÓ Î
+_x0000__x0000_6150796307_x0003__x0000__x0001_pÈø»_x0019_Â_x0008__x0000__x0000_20101004_x000C__x0000__x0000_055-312-9559
+_x0000__x0000_0553129560_x0008__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_@®tÕÜÂ_x0006__x0000__x0000_621833_x0012__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_@®tÕÜÂ _x0000_¥Ç Ç\¸ _x0000_2_x0000_9_x0000_7_x0000_-_x0000_5_x0000__x000D__x0000__x0000_010-9513-9559_x0016__x0000__x0000_jms3129559@hanmail.net_x0008__x0000__x0000_20101019_x000E__x0000__x0000_37690004530037_x0006__x0000__x0000_D00148_x0007__x0000__x0001__x0000_ÏtÇdÅD¾¤ÂìÓ Î
+_x0000__x0000_1232481068_x0003__x0000__x0001__x0015_¼+ºÇ_x000C__x0000__x0000_031-457-8706
+_x0000__x0000_0314578707_x0007__x0000__x0001_½¬0®Ä³ _x0000_HÅÅÜÂ_x0006__x0000__x0000_431837_x0012__x0000__x0001_½¬0®Ä³ _x0000_HÅÅÜÂ _x0000_Ù³HÅl­ _x0000_À­xÇ\¸ _x0000_8_x0000_9_x0000__x000D__x0000__x0000_010-7338-7375_x0016__x0000__x0000_jamjali200@hanmail.net_x000E__x0000__x0000_37690004532237_x0006__x0000__x0000_D00149	_x0000__x0001_TÏ¬¹DÅ$Æ_x0008_Õ(_x0000_@®Ì)_x0000_
+_x0000__x0000_5100147324_x0003__x0000__x0001__x0015_¼ Á_x0001_Æ_x0008__x0000__x0000_20070423_x000C__x0000__x0000_054-430-7007
+_x0000__x0000_0544307007_x0008__x0000__x0001_½¬ÁÀ½Ä³ _x0000_@®ÌÜÂ_x0005__x0000__x0000_39626_x000E__x0000__x0001_½¬½ _x0000_@®ÌÜÂ _x0000_¡Á$Á\¸ _x0000_1_x0000_6_x0000_4_x0000__x000D__x0000__x0000_010-4115-6306_x0013__x0000__x0000_jj10654@hanmail.net_x000E__x0000__x0000_37690004533937_x0006__x0000__x0000_D00150_x0005__x0000__x0001__x0014_Ól­¤ÂìÓ Î
+_x0000__x0000_5020153204_x0003__x0000__x0001_àÂÁÀÜ­_x0008__x0000__x0000_20080331_x000C__x0000__x0000_053-957-8989
+_x0000__x0000_0539432345_x0008__x0000__x0001__x0000_³l­_x0011_­íÅÜÂ _x0000_Ù³l­_x0005__x0000__x0000_41193_x000F__x0000__x0001__x0000_³l­ _x0000_Ù³l­ _x0000_DÅÅ\¸1_x0000_1_x0000_8® _x0000_8_x0000_1_x0000__x0008__x0000__x0001_1_x0000_5Î _x0000__x0014_Ól­¤ÂìÓ Î_x000D__x0000__x0000_010-8854-8989_x0012__x0000__x0000_89sports@naver.com_x000E__x0000__x0000_37690004534537_x0006__x0000__x0000_D00159_x0005__x0000__x0001__x001C_Ö1Á¤ÂìÓ Î
+_x0000__x0000_1300531089_x0003__x0000__x0001_tÇXÇ Á_x000D__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000__x0000_¬_x0004_È_x001C_ÈÔ,_x0000_¡ÇTÖ_x0008__x0000__x0000_20070529_x000C__x0000__x0000_032-654-2133
+_x0000__x0000_0326542132_x0007__x0000__x0001_½¬0®Ä³ _x0000_½ÌÜÂ_x0006__x0000__x0000_422819 _x0000__x0001_½¬0®Ä³ _x0000_½ÌÜÂ _x0000_Á¬Àl­ _x0000_½¬xÇ\¸1_x0000_2_x0000_0_x0000_¼8® _x0000_2_x0000_8_x0000_ _x0000_ _x0000_1_x0000_5Î_x0010_ÈìÓ _x0000_1_x0000_xÎ_x000D__x0000__x0000_010-7578-7740_x0015__x0000__x0000_hs7167741@hanmail.net_x000E__x0000__x0000_37690004541337_x0006__x0000__x0000_D00160_x0005__x0000__x0001_8ÖÙ³¤ÂìÓ Î
+_x0000__x0000_1243919047_x0003__x0000__x0001_@®8ÖÙ³_x0008__x0000__x0000_20100113_x000C__x0000__x0000_031-375-0331
+_x0000__x0000_0313750331_x0007__x0000__x0001_½¬0®Ä³ _x0000_$Æ°ÀÜÂ_x0006__x0000__x0000_447802_x001A__x0000__x0001_½¬0®Ä³ _x0000_$Æ°ÀÜÂ _x0000_1Á8Ö_x0000_³\¸ _x0000_2_x0000_5_x0000_ _x0000_´Æ°ÀL¾)µ _x0000_ _x0000_1_x0000_5Î _x0000_4_x0000__x000D__x0000__x0000_010-5295-8278_x0013__x0000__x0000_khd9982@hanmail.net_x000E__x0000__x0000_37690004542037_x0006__x0000__x0000_D00161_x0005__x0000__x0001_MÖ1ÁÆ%±¤Â
+_x0000__x0000_3100640518_x0003__x0000__x0001_@®_x0004_Ö_x0015_È_x0008__x0000__x0000_20090616_x000C__x0000__x0000_041-634-7327_x0008__x0000__x0001_©Í­Ì¨°Ä³ _x0000_MÖ1Áp­_x0005__x0000__x0000_32263_x0012__x0000__x0001_©Í¨° _x0000_MÖ1Áp­ _x0000_MÖ½MÇ _x0000_©Í¨°_x0000_³\¸ _x0000_3_x0000_6_x0000__x0015__x0000__x0001__x001C_È _x0000_1_x0000_5Î _x0000__x001C_È _x0000_1_x0000_0_x0000_1_x0000_8Ö(_x0000_L¾dÅT³¤Â$Æ&lt;Õ¤ÂTÑ)_x0000__x000D__x0000__x0000_010-8626-9825_x0010__x0000__x0000_hji923@naver.com_x000E__x0000__x0000_37690004543637_x0006__x0000__x0000_D00166_x000C__x0000__x0001_(_x0000_üÈ)_x0000_ðÒ_x001C_ÈtÇ_x0014_µ¤Â¸Ò¬¹ð½XÁ
+_x0000__x0000_2118732516_x0003__x0000__x0001_¡ÁÁÀÐÆ_x0006__x0000__x0001_Ä³Áä¹ _x0000_Ä³ä¹_x0008__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_4»íÅ_x0008__x0000__x0000_20120911_x000B__x0000__x0000_02-511-5114	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x0015_¬¨°l­_x0006__x0000__x0000_135010_x000B__x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ_x0015_¬¨°l­|±_x0004_ÖÙ³_x000E__x0000__x0001__x0008_®@ÇL¾)µ _x0000_1_x0000_5Î _x0000_ ¼¤Â¸Ò¤Â Ñ´Å_x000D__x0000__x0000_010-8784-1651_x0015__x0000__x0000_bestextreme@naver.com_x0007__x0000__x0001_B_x0000_ñ´	®(_x0000_T_x0000_S_x0000_)_x0000__x0005__x0000__x0000_14049_x0003__x0000__x0001__x0015_¼_x0004_ÖÄÉ_x0008__x0000__x0000_20190917_x0006__x0000__x0000_D00167_x0008__x0000__x0001_üÈÝÂÖ¬À _x0000_ÐÆÐÅÇ
+_x0000__x0000_1268800066_x0003__x0000__x0001_@®DÕ¹Â_x0006__x0000__x0001_Ä³Áä¹ÅÅ _x0000_xÆ_x0007__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_xÆ_x000C__x0000__x0000_02-1644-1662	_x0000__x0001_½°À_x0011_­íÅÜÂ _x0000__x0018_Â_x0001_Æl­_x0006__x0000__x0000_613815_x0013__x0000__x0001_½°À_x0011_­íÅÜÂ _x0000__x0018_Â_x0001_Æl­ _x0000__x0011_­¨°\¸ _x0000_6_x0000_3_x0000_ _x0000_B_x0000_Ù³_x0004__x0000__x0001_4_x0000_5Î|Ç½_x000D__x0000__x0000_010-8882-4137_x0014__x0000__x0000_oneeight@hanmail.net_x0006__x0000__x0000_D00173_x0005__x0000__x0001__x0008_®_x0001_Æ¤ÂìÓ Î
+_x0000__x0000_1052087391_x0003__x0000__x0001_°ÆÀÉÐÆ_x0008__x0000__x0000_20140217_x000D__x0000__x0000_010-6208-8112_x0006__x0000__x0000_121889_x0013__x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_È¹ìÓl­ _x0000_Ù³P­\¸3_x0000_8® _x0000_1_x0000_2_x0000_5_x0000__x0013__x0000__x0000_yonex0901@naver.com_x0008__x0000__x0000_20150122_x000E__x0000__x0000_37690004557937_x0006__x0000__x0000_D00181_x0004__x0000__x0001__x0000_É¤ÂìÓ Î
+_x0000__x0000_1410240836_x0003__x0000__x0001__x0015_¼½¬·_x0008__x0000__x0000_20140825_x000C__x0000__x0000_031-945-2007_x0007__x0000__x0001_½¬0®Ä³ _x0000__x000C_ÓüÈÜÂ_x0006__x0000__x0000_413819$_x0000__x0001_½¬0®Ä³ _x0000__x000C_ÓüÈÜÂ _x0000_DÅ¬¹·\¸ _x0000_5_x0000_5_x0000_ _x0000_-_x0000_8_x0000_1_x0000_ _x0000_(_x0000__x0008_®_x000C_ÍÙ³,_x0000_ _x0000__x000C_ÓüÈ_x0008_®_x000C_ÍXÕ_x0018_ÂÌ¬¹¥Ç)_x0000__x000C__x0000__x0001__x000C_ÓüÈÜÂ _x0000_0¼Ü´ü»4Ñ_x0004_È©Æl­¥Ç_x000D__x0000__x0000_010-9129-1126_x0017__x0000__x0000_leesjun1024@hanmail.net_x000E__x0000__x0000_37690004547137_x0006__x0000__x0000_D00183_x0003__x0000__x0001_T³_x001C_È|Ç
+_x0000__x0000_1171558537_x0003__x0000__x0001_iÖÐÆ Á_x000B__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_XÇX¹,_x0000_¡ÇTÖ_x0008__x0000__x0000_20141027_x000D__x0000__x0000_010-6333-2457	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_ÅÌl­_x0005__x0000__x0000_08078 _x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_ÅÌl­ _x0000_àÂ_x0015_È\¸ _x0000_2_x0000_7_x0000_5_x0000_ _x0000_ _x0000_(_x0000_àÂ_x0015_ÈÙ³,_x0000_ _x0000_àÂ¸Ò¬¹DÅ_x000C_Ó¸Ò)_x0000__x0010__x0000__x0001_ÁÀ_x0000_¬Ù³ _x0000_1_x0000_5Î _x0000_1_x0000_0_x0000_4_x0000_,_x0000_ _x0000_1_x0000_0_x0000_5_x0000_8Ö_x0011__x0000__x0000_thejeil@naver.com_x000D__x0000__x0000_010-9668-2210_x000E__x0000__x0000_37690004550437_x0006__x0000__x0000_D00184_x0005__x0000__x0001_$Æ¨°¤ÂìÓ Î
+_x0000__x0000_1322489384_x0003__x0000__x0001_Å+È¨º_x000D__x0000__x0001_´ÆÙ³0®l­©ÆÔ _x0000_aÅ8Á_x001C_Á¬¹ _x0000_xÆ_x0008__x0000__x0000_20141028
+_x0000__x0000_0315756464
+_x0000__x0000_0315755600_x0008__x0000__x0001_½¬0®Ä³ _x0000_¨°ÅüÈÜÂ_x0006__x0000__x0000_472881_x0016__x0000__x0001_½¬0®Ä³ _x0000_¨°ÅüÈÜÂ _x0000_ÄÉt¬$Æ¨°\¸ _x0000_8_x0000_0_x0000_6_x0000_ _x0000_-_x0000_1_x0000_4_x0000__x000D__x0000__x0000_010-9289-9637_x0012__x0000__x0000_jongmo83@naver.com_x000E__x0000__x0000_37690004552737_x0006__x0000__x0000_D00186_x0005__x0000__x0001_ä¹XÎìÓxÇ¸Ò
+_x0000__x0000_6091853217_x0003__x0000__x0001_iÖ­ÝÂ_x0008__x0000__x0000_20141202_x000C__x0000__x0000_055-298-7330_x0005__x0000__x0000_51378_x0011__x0000__x0001_½¬¨° _x0000_=ÌÐÆÜÂ _x0000_XÇ=Ìl­ _x0000__x0018_¼Ä¬\¸ _x0000_6_x0000_3_x0000__x000D__x0000__x0000_010-3561-0209_x000E__x0000__x0000_o2bbi@nate.com_x0008__x0000__x0000_20141212_x000E__x0000__x0000_37690004554037_x0006__x0000__x0000_D00190_x0005__x0000__x0001_p­°À¤ÂìÓ Î
+_x0000__x0000_4010657765_x0003__x0000__x0001__x0015_¼_x001C_Âl×	_x0000__x0001_¤ÂìÓ ÎXÇX¹,_x0000_ _x0000_©ÆÔ_x0008__x0000__x0000_20150406_x000D__x0000__x0000_010-9977-7141_x0008__x0000__x0001__x0004_È|·½Ä³ _x0000_p­°ÀÜÂ_x0005__x0000__x0000_54102_x000F__x0000__x0001__x0004_È½ _x0000_p­°ÀÜÂ _x0000_¨°_x0018_Â¡Á5_x0000_8® _x0000_4_x0000_2_x0000__x000F__x0000__x0001_1_x0000_0_x0000_1_x0000_8Ö(_x0000__x0018_Â¡ÁÙ³,_x0000_ _x0000_(Ì$Æ¹L¾)_x0000__x0013__x0000__x0000_shp7141@hanmaiL.net_x000E__x0000__x0000_37690004558537_x0006__x0000__x0000_D00192
+_x0000__x0001__x0001_Æ8»¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1222039517_x0005__x0000__x0001__x0001_Æ8»¤ÂìÓ Î_x0003__x0000__x0001_@®_x0001_Æ8»_x0008__x0000__x0000_20150608_x000C__x0000__x0000_032-523-1406_x000C__x0000__x0000_032-517-8009	_x0000__x0001_xÇÌ_x0011_­íÅÜÂ _x0000_½ÉÓl­_x0005__x0000__x0000_21337_x000D__x0000__x0000_010-4320-1406_x0012__x0000__x0000_YM1406@hanmail.net_x0007__x0000__x0001_A_x0000_ñ´	®(_x0000_T_x0000_S_x0000_)_x0000__x0005__x0000__x0000_13042_x0003__x0000__x0001_@®Ù³½¬_x000E__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_+_x0000_3_x0000_0_x0000__x000E__x0000__x0000_37690004561837_x0006__x0000__x0000_D00193_x000B__x0000__x0001_ÑÐ¤Â@Õ¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1320972497_x0006__x0000__x0001_ÑÐ¤Â@Õ¤ÂìÓ Î_x0003__x0000__x0001__x0015_¼_x0004_Ö=Ì_x0006__x0000__x0001_´ÆÙ³_x0004_È8»©ÆÔ_x0008__x0000__x0000_20150610_x000D__x0000__x0000_010-3706-2477_x0007__x0000__x0001_½¬0®Ä³ _x0000_l­¬¹ÜÂ_x0005__x0000__x0000_11907_x000F__x0000__x0001_½¬0® _x0000_l­¬¹ÜÂ _x0000_UÆ_x0019_ÂÌ\¸ _x0000_5_x0000_0_x0000_7_x0000_	_x0000__x0001_3_x0000_5Î _x0000_ÑÐ¤Â@Õ¤ÂìÓ Î_x000F__x0000__x0000_pspin@naver.com_x0005__x0000__x0000_22022_x0003__x0000__x0001_HÅ°ÆÄÉ_x000C__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_7_x0000_._x0000_5_x0000__x000E__x0000__x0000_37690004560137_x0006__x0000__x0000_D00195
+_x0000__x0001_¤ÂìÓ ÎLÑlÐ(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_6172249744_x0005__x0000__x0001_¤ÂìÓ ÎLÑlÐ_x0003__x0000__x0001_tÇÝÐ0®_x0006__x0000__x0001__x001C_ÈpÈÅÅ _x0000_Áä¹_x000C__x0000__x0001_õ¬_x0008_Æ _x0000_¤ÂìÓ Î©ÆÔ,_x0000_ _x0000_¡ÇTÖ_x000B__x0000__x0000_051-7564800_x000C__x0000__x0000_051-756-4801_x0005__x0000__x0000_48222_x0017__x0000__x0001_½°À_x0011_­íÅÜÂ _x0000_Ù³·l­ _x0000_+ÈiÕ´ÆÙ³¥Ç\¸ _x0000_4_x0000_0_x0000_¼8® _x0000_8_x0000_'_x0000__x0001_1_x0000_0_x0000_3_x0000_Ù³ _x0000_1_x0000_0_x0000_5_x0000_8Ö,_x0000_1_x0000_0_x0000_6_x0000_8Ö(_x0000_¬ÀÁÉÙ³,_x0000_½°À _x0000_DÅÜÂDÅÜ´ _x0000_TÏ$Æq¸ _x0000_XÕ²DÌ _x0000_DÅ_x000C_Ó¸Ò)_x0000__x000D__x0000__x0000_010-5578-1988_x0015__x0000__x0000_ltktennis@hanmail.net_x000B__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_8_x0000__x0008__x0000__x0000_20150611_x000E__x0000__x0000_37690004562437_x0006__x0000__x0000_D00196	_x0000__x0001__x0015_¬¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_5041920932_x0004__x0000__x0001__x0015_¬¤ÂìÓ Î_x0003__x0000__x0001__x0015_¬@Çl­_x000D__x0000__x0001_LÑÈ²¤Â©ÆÔ,_x0000_ _x0000_XÇX¹,_x0000_ _x0000_àÂ_x001C_¼_x000C__x0000__x0000_053-314-9090_x0005__x0000__x0000_41433_x000D__x0000__x0000_010-3828-0474_x0013__x0000__x0000_keg0417@hanmail.net_x000D__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_6_x0000_+_x0000_1_x0000_5_x0000__x0008__x0000__x0000_20150612_x000E__x0000__x0000_37690004565337_x0006__x0000__x0000_D00199
+_x0000__x0001_P´¬¹¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1283008985_x0003__x0000__x0001_@®_x0001_Æ Á_x000B__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_¤ÂìÓ ÎXÇX¹_x0008__x0000__x0000_20150703_x000C__x0000__x0000_031-911-4191_x000C__x0000__x0000_031-913-0067_x0006__x0000__x0000_410829_x000F__x0000__x0001_½¬0®Ä³à¬ÅÜÂ _x0000_|Ç°ÀÙ³l­_x0015_È_x001C_¼°ÀÙ³_x000E__x0000__x0001_1_x0000_1_x0000_4_x0000_8_x0000_-_x0000_1_x0000_3_x0000_ _x0000_1_x0000_5Î2_x0000_,_x0000_3_x0000_8Ö_x000D__x0000__x0000_010-4288-3563_x0012__x0000__x0000_usop2n@hanmail.net_x000D__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_6_x0000_+_x0000_2_x0000_3_x0000__x000E__x0000__x0000_37690004568237_x0006__x0000__x0000_D00201_x000E__x0000__x0001_(_x0000_üÈ)_x0000_¤ÂtÎtÇ¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_6278102573_x000B__x0000__x0001_¤ÂtÎtÇ¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000__x0003__x0000__x0001_@®1ÁÐÆ_x0006__x0000__x0001_Áä¹ÅÅ _x0000_Ä³ä¹_x0008__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_ä¹_x0010_È_x000C__x0000__x0000_041-566-1879_x000C__x0000__x0000_041-554-2732_x0005__x0000__x0000_31157"_x0000__x0001_©Í­Ì¨°Ä³ _x0000_ÌHÅÜÂ _x0000__x001C_Á½l­ _x0000_1¼_x001D_Á3_x0000_\¸ _x0000_2_x0000_9_x0000_ _x0000_ _x0000_(_x0000_1¼_x001D_ÁÙ³,_x0000_ _x0000_½¶É¹_x0008_Ã%¼)_x0000__x000D__x0000__x0000_010-4513-1879_x0011__x0000__x0000_kimsw000@nate.com_x000E__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_4_x0000_0_x0000_+_x0000_2_x0000_0_x0000__x0008__x0000__x0000_20150804_x000E__x0000__x0000_37690004570937_x0006__x0000__x0000_D00202_x0008__x0000__x0001_¤ÂìÓå²(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_3052275067_x0003__x0000__x0001_HÅü­¹Â_x000C__x0000__x0000_042-522-9566_x000C__x0000__x0000_042-271-4786_x0006__x0000__x0000_300810_x0017__x0000__x0001__x0000_³_x0004_È_x0011_­íÅÜÂ _x0000__x0011_Él­ _x0000_Ù³_x001C_Á_x0000_³\¸ _x0000_1_x0000_2_x0000_0_x0000_1_x0000_(_x0000_ÜÐÉÓÙ³)_x0000__x0007__x0000__x0001_¤ÂìÓå² _x0000_ÜÐÉÓ_x0010_È_x000B__x0000__x0000_01062224787_x0010__x0000__x0000_spodaq@naver.com_x000D__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_5_x0000_+_x0000_3_x0000_3_x0000__x0008__x0000__x0000_20150805_x000E__x0000__x0000_37690004571537_x0006__x0000__x0000_D00203	_x0000__x0001_ðÅTÏ¬¹DÅ(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_2041477980_x0004__x0000__x0001_ðÅTÏ¬¹DÅ_x0003__x0000__x0001_@®ÁÀ0®_x0006__x0000__x0001_Ä³Áä¹ _x0000_t¬$Á_x000D__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_´Ì!ÇÜÂ_x001C_Á&lt;»$ÁXÎ_x0008__x0000__x0000_20150806_x000C__x0000__x0000_02-3390-4345_x000C__x0000__x0000_02-3390-4344
+_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_Ù³_x0000_³8»l­_x0005__x0000__x0000_02496_x0011__x0000__x0001__x001C_Á¸Æ _x0000_Ù³_x0000_³8»l­ _x0000_Ý¹°Æ\¸1_x0000_2_x0000_8® _x0000_1_x0000_9_x0000__x000B__x0000__x0001_1_x0000_5Î _x0000_XÕtÇÐÆ¤ÂìÓ Î°ÀÅÅ_x000D__x0000__x0000_010-9089-5363_x0017__x0000__x0000_01090895363@hanmail.net_x000B__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_2_x0000_0_x0000__x000E__x0000__x0000_37690004572137_x0006__x0000__x0000_D00205_x0005__x0000__x0001_ÁLÑ¤ÂìÓ Î
+_x0000__x0000_1971301851_x0003__x0000__x0001_@®_x0001_Æ_x0018_Â_x0008__x0000__x0001_Ä³Áä¹ÅÅ _x0000_Ä³ä¹ÅÅ	_x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_4»íÅÅÅ_x000B__x0000__x0000_01063388568_x0008__x0000__x0001_½¬0®Ä³ _x0000_XÇ_x0015_È½ÜÂ_x0005__x0000__x0000_11806!_x0000__x0001_½¬0®Ä³ _x0000_XÇ_x0015_È½ÜÂ _x0000_$Æ©º\¸ _x0000_1_x0000_7_x0000_0_x0000_ _x0000_°Àä´È¹DÇ _x0000_DÅ_x000C_Ó¸Ò _x0000_4_x0000_1_x0000_2_x0000_-_x0000_7_x0000_0_x0000_6_x0000__x000D__x0000__x0000_010-6338-8568_x0011__x0000__x0000_3388568@naver.com_x0005__x0000__x0000_26002_x0003__x0000__x0001__x0015_¬ÜÐ8Ö_x0008__x0000__x0000_20220901_x000E__x0000__x0000_37690004700437_x0006__x0000__x0000_D00209_x0018__x0000__x0001_¤ÂìÓ Î_x000C_Õì·¤Â(_x0000_S_x0000_p_x0000_o_x0000_r_x0000_t_x0000_s_x0000_ _x0000_P_x0000_l_x0000_u_x0000_s_x0000_)_x0000_(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1192167071_x0003__x0000__x0001__x0015_¬ÜÂ¨º_x0006__x0000__x0001_Ä³Áä¹ _x0000_LÇÝÂ_x0008__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_\ÕÝÂ_x000B__x0000__x0000_02-871-5513	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x0000_­EÅl­_x0005__x0000__x0000_08750_x000F__x0000__x0001__x001C_Á¸Æ _x0000__x0000_­EÅl­ _x0000_àÂ¼¹\¸3_x0000_8® _x0000_4_x0000_0_x0000__x0005__x0000__x0001_ÀÉXÕ _x0000_1_x0000_5Î_x000D__x0000__x0000_010-7703-5353_x001A__x0000__x0000_tennisplus0122@esero.go.krX_x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_ _x0000_/_x0000_ _x0000_2_x0000_5_x0000_S_x0000_S_x0000_ _x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_ _x0000_/_x0000_ _x0000_2_x0000_4_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_9_x0000_._x0000_6_x0000_ _x0000_/_x0000_ _x0000_2_x0000_4_x0000_S_x0000_S_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_ _x0000_/_x0000_ _x0000_2_x0000_3_x0000_F_x0000_W_x0000_ _x0000__x0018_ÂüÈ _x0000_ìÅàÂ _x0000_ _x0000_1_x0000_2_x0000_ _x0000_(_x0000_ô²ù²Ç _x0000_Æ­Ì&lt;Ç\¸ _x0000_6_x0000_ _x0000__x0018_¼_x0001_Æ)_x0000__x0008__x0000__x0000_20160114_x000E__x0000__x0000_37690004577337_x0006__x0000__x0000_D00210_x0011__x0000__x0001_(_x0000_üÈ)_x0000_ÐÅtÇ_x001C_ÈtÇxÇ0Ñ´°TÁ °(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1268641398_x000C__x0000__x0000_031-761-8980_x000C__x0000__x0000_031-761-2140_x0005__x0000__x0000_12769_x000D__x0000__x0000_010-4552-3318	_x0000__x0000_1800-6142_x000E__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_4_x0000_0_x0000_+_x0000_2_x0000_5_x0000__x0008__x0000__x0000_20160121_x000E__x0000__x0000_37690004578037_x0006__x0000__x0000_D00256	_x0000__x0001_p¬1Á¤ÂìÓ Î(_x0000_Å°À)_x0000_
+_x0000__x0000_6210808090_x0003__x0000__x0001__x0015_È+È_x0015_¬_x0006__x0000__x0001_Ä³Áä¹ _x0000__x001C_ÈpÈ_x000B__x0000__x0001_ìÕ¤Â0®l­,_x0000_ _x0000_¤ÂìÓ Î©ÆÔ_x0008__x0000__x0000_20160412_x000C__x0000__x0000_055-387-3613_x000C__x0000__x0000_055-387-3615_x0008__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_Å°ÀÜÂ_x0005__x0000__x0000_50621 _x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_Å°ÀÜÂ _x0000__x001C_Á|ÇÙ³\¸ _x0000_2_x0000_5_x0000_ _x0000_ _x0000_(_x0000__x0011_É½Ù³,_x0000_ _x0000_$Ç ÁÝÀ_x0001_Æ´ÅP­äÂ)_x0000__x000D__x0000__x0000_010-2390-2994_x0013__x0000__x0000_dhrhr68@hanmail.netH_x0000__x0001_2_x0000_4_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_3_x0000_5_x0000_ _x0000_/_x0000_2_x0000_4_x0000_S_x0000_S_x0000__x0018_ÂüÈìÅàÂ _x0000_3_x0000_5_x0000_ _x0000_/_x0000_ _x0000_2_x0000_3_x0000_F_x0000_W_x0000_ _x0000__x0018_ÂüÈ _x0000_ìÅàÂ _x0000_3_x0000_5_x0000_ _x0000_/_x0000_ _x0000_2_x0000_3_x0000_S_x0000_S_x0000_ _x0000__x0018_ÂüÈ _x0000_ìÅàÂ _x0000_3_x0000_5_x0000_(_x0000_|·_x0013_Ï+_x0000_È¹D¾¤Â _x0000_9_x0000_4_x0000_3_x0000_,_x0000_2_x0000_5_x0000_0_x0000_)_x0000__x0008__x0000__x0000_20160407_x000E__x0000__x0000_37690004581237_x0006__x0000__x0000_D00267_x0006__x0000__x0001__x001C_ÈtÇD¾¤ÂìÓ Î
+_x0000__x0000_6664100083_x0003__x0000__x0001_Ç_x0015_È\Õ_x000D__x0000__x0001_Ä³ä¹ _x0000__x000F_¼ _x0000_Áä¹ÅÅ,_x0000_ _x0000__x001C_ÁD¾¤Â_x000C__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_ _x0000__x0011_­à¬_x0000_³ÕÅÅ_x0008__x0000__x0000_20160610_x000C__x0000__x0000_062-523-7451_x000C__x0000__x0000_062-523-7455_x0005__x0000__x0000_62023_x000D__x0000__x0001__x0011_­üÈ _x0000__x001C_Ál­ _x0000_´ÆÌ\¸ _x0000_1_x0000_2_x0000_2_x0000__x0005__x0000__x0001_(_x0000__x000D_Ã_x000C_ÍÙ³)_x0000__x000D__x0000__x0000_010-4606-4538_x0015__x0000__x0000_jhrim1226@hanmail.net_x0008__x0000__x0000_20160601_x000E__x0000__x0000_37690004584137_x0006__x0000__x0000_D00280_x0005__x0000__x0001_Ä³ô²¤ÂìÓ Î
+_x0000__x0000_3071042161_x0003__x0000__x0001_$ÇÙ³ÝÂ_x000B__x0000__x0001_Ä³ä¹_x000F_¼ _x0000_Áä¹ÅÅ _x0000_Áä¹ÅÅ_x0010__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_Ç_x0004_Èp¬ _x0000__x0010_Óä¹,_x0000_ _x0000__x0000_³ìÅ_x0008__x0000__x0000_20160825_x000C__x0000__x0000_044-863-8908_x000C__x0000__x0000_044-863-8970_x000F__x0000__x0001_8Á+È¹ÒÄ¼ÇXÎÜÂ _x0000_8Á+È¹ÒÄ¼ÇXÎÜÂ_x0005__x0000__x0000_30102_x001E__x0000__x0001_8Á+È¹ÒÄ¼ÇXÎÜÂ _x0000__x0008_È¬Ç\¸ _x0000_1_x0000_7_x0000_2_x0000_ _x0000_(_x0000_´ÅÄÉÙ³,_x0000_ _x0000_ÜÐ\Õ_x0004_Õ_x0008_¸¤Â&lt;Á0Ñ)_x0000__x0004__x0000__x0001_1_x0000_0_x0000_1_x0000_8Ö_x000D__x0000__x0000_010-7185-8008_x0015__x0000__x0000_dodamsports@naver.com_x000E__x0000__x0000_37690004586437_x0006__x0000__x0000_D00282_x0005__x0000__x0001__x0004_²¬¹¤ÂìÓ Î
+_x0000__x0000_1082124505_x0003__x0000__x0001_@®l×_x0015_È_x0006__x0000__x0001_Áä¹ _x0000_Ä³Áä¹_x000C__x0000__x0001__x0004_ÈÇÁÀp¬·ÅÅ _x0000_0¼Ü´ü»4Ñ _x0000__x000B__x0000__x0000_02-848-6291_x000B__x0000__x0000_02-848-7556
+_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x0001_Æñ´ìÓl­_x0005__x0000__x0000_07375_x000E__x0000__x0001__x001C_Á¸Æ _x0000__x0001_Æñ´ìÓl­ _x0000_Ä³àÂ\¸ _x0000_5_x0000_1_x0000__x000D__x0000__x0001_1_x0000_5Î _x0000_1_x0000_0_x0000_5_x0000_8Ö(_x0000_¡ÁU³L¾)µ)_x0000__x000D__x0000__x0000_010-8393-6291_x0013__x0000__x0000_hee00jung@naver.com_x0008__x0000__x0000_20160905_x000E__x0000__x0000_37690004588737_x0006__x0000__x0000_D00286_x0007__x0000__x0001_Æ%±¤Â _x0000_1Á¨°_x0010_È
+_x0000__x0000_2603001743_x0003__x0000__x0001_MÖ¥Ç8Ö_x0008__x0000__x0001_Ä³ä¹ _x0000__x000F_¼ _x0000_Áä¹ÅÅ_x0008__x0000__x0000_20151218_x000C__x0000__x0000_031-755-7257_x0007__x0000__x0001_½¬0®Ä³ _x0000_1Á¨°ÜÂ_x0005__x0000__x0000_13110_x001E__x0000__x0001_½¬0®Ä³ _x0000_1Á¨°ÜÂ _x0000__x0018_Â_x0015_Èl­ _x0000_1Á¨°_x0000_³\¸ _x0000_1_x0000_2_x0000_6_x0000_7_x0000_ _x0000_-_x0000_1_x0000_ _x0000_(_x0000_ÜÐÉÓÙ³)_x0000__x000D__x0000__x0000_010-7191-7257_x0012__x0000__x0000_nero1016@naver.com_x0002__x0000__x0001_¨°¸Ó_x0008__x0000__x0000_20161109_x000E__x0000__x0000_37690004591037_x0006__x0000__x0000_D00287_x0005__x0000__x0001_¤ÐtÎ¤ÂìÓ Î
+_x0000__x0000_6103752918_x0003__x0000__x0001_@®ÜÐÇ_x0008__x0000__x0000_20161125_x000C__x0000__x0000_052-268-6086_x000C__x0000__x0000_052-272-5908_x0008__x0000__x0001_¸Æ°À_x0011_­íÅÜÂ _x0000_¨°l­_x0005__x0000__x0000_44692_x0016__x0000__x0001_¸Æ°À_x0011_­íÅÜÂ _x0000_¨°l­ _x0000_Ë³ÈÉ\¸ _x0000_1_x0000_2_x0000_4_x0000_ _x0000_ _x0000_(_x0000_ì²Ù³)_x0000__x0003__x0000__x0000_3/2_x000D__x0000__x0000_010-9568-6086_x0014__x0000__x0000_kika5908@hanmail.net_x000E__x0000__x0000_37690004592637_x0006__x0000__x0000_D00292_x0008__x0000__x0001_Æ%±¤Â _x0000_¤ÂìÓÐÆ_x0010_È
+_x0000__x0000_6977800050_x0003__x0000__x0001_\ÕÀ­_x0001_Æ_x0008__x0000__x0000_20170102_x000C__x0000__x0000_051-517-3862_x000C__x0000__x0000_051-583-1023	_x0000__x0001_½°À_x0011_­íÅÜÂ _x0000__x0008_®_x0015_Èl­_x0005__x0000__x0000_46207&amp;_x0000__x0001_½°À_x0011_­íÅÜÂ _x0000__x0008_®_x0015_Èl­ _x0000_´Ì!Çõ¬ÐÆ\¸3_x0000_9_x0000_9_x0000_¼8® _x0000_3_x0000_2_x0000_4_x0000_ _x0000_ _x0000_(_x0000_P´l­Ù³,_x0000_ _x0000_¤ÂìÓÐÆ_x000C_ÓlÐ)_x0000__x0010__x0000__x0001_ÀÉXÕ1_x0000_5Î(_x0000_P´l­Ù³,_x0000_ _x0000_äÂ´°´Ì!Ç_x0000_­)_x0000__x000D__x0000__x0000_010-5505-3862_x0013__x0000__x0000_hgy4285@hanmail.net_x000E__x0000__x0000_37690004595537_x0006__x0000__x0000_D00306_x0007__x0000__x0001_Æ%±¤Â _x0000_ÁÀ4»_x0010_È
+_x0000__x0000_8042300420_x0003__x0000__x0001_@®_x0004_Ö+È_x000D__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_´ÆÙ³©ÆÔ _x0000_¡ÇTÖ_x0008__x0000__x0000_20170119_x000D__x0000__x0000_010-6886-7065_x000C__x0000__x0000_062-374-5410_x0005__x0000__x0000_61970_x0013__x0000__x0001__x0011_­üÈ _x0000__x001C_Ál­ _x0000_ÁÀ4»ü»üÈ\¸3_x0000_2_x0000_¼8® _x0000_3_x0000_-_x0000_5_x0000__x0013__x0000__x0000_sskim-j@hanmail.net_x000E__x0000__x0000_37690004597837_x0006__x0000__x0000_D00308_x0005__x0000__x0001_C_x0000_S_x0000_¤ÂìÓ Î
+_x0000__x0000_2270838785_x0007__x0000__x0001_iÖ_x001C_ÂU³xÆ _x0000_1_x0000_+º_x000C__x0000__x0000_031-385-1222_x000C__x0000__x0000_031-388-3477_x0005__x0000__x0000_13958_x0016__x0000__x0001_½¬0® _x0000_HÅÅÜÂ _x0000_Ì¹HÅl­ _x0000__x0008_Æ Âõ¬ÐÆ\¸5_x0000_2_x0000_¼8® _x0000_2_x0000__x000D__x0000__x0000_010-3176-9037_x0013__x0000__x0000_bill@cssports.co.kr_x000D__x0000__x0000_010-2727-2718_x000F__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_5_x0000_+_x0000_3_x0000_._x0000_5_x0000__x000E__x0000__x0000_37690004598437_x0006__x0000__x0000_D00311
+_x0000__x0001_TÏ¬¹DÅ¤ÂìÓ </v>
           </cell>
           <cell r="D39" t="str">
             <v>사용가능</v>
@@ -4690,14 +5960,94 @@
           <cell r="E39" t="str">
             <v>일반사업자</v>
           </cell>
-          <cell r="F39" t="str">
-            <v>2270299081</v>
+          <cell r="F39" t="e">
+            <v>#N/A</v>
           </cell>
           <cell r="G39" t="str">
-            <v>속초배드민턴</v>
-          </cell>
-          <cell r="H39" t="str">
-            <v>정재훈</v>
+            <v xml:space="preserve">7690004499237_x0006__x0000__x0000_D00116_x000F__x0000__x0001_Æ%±¤ÂÈ¹°À_x0000_³¬¹_x0010_È(_x0000_ü»4Ñ¤ÂìÓ Î)_x0000_
+_x0000__x0000_6080288027_x0003__x0000__x0001_ Ç_x0001_Æ_x0019_Â_x0008__x0000__x0001_¤ÂìÓ Î©ÆÔ_x000F_¼XÇX¹_x000C__x0000__x0000_055-222-5431
+_x0000__x0000_0552225432_x0008__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_=ÌÐÆÜÂ_x0006__x0000__x0000_631852_x0018__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_=ÌÐÆÜÂ _x0000_È¹°ÀiÕìÓl­ _x0000_©ÆÈ¹\¸ _x0000_7_x0000_6_x0000_ _x0000_üÈÝÐ_x000D__x0000__x0000_010-3707-6245_x0016__x0000__x0000_dudtjs6245@hanmail.net_x000E__x0000__x0000_37690004504337_x0006__x0000__x0000_D00120_x0006__x0000__x0001_Æ%±¤Â­ÌüÈ_x0010_È
+_x0000__x0000_3170385854_x0003__x0000__x0001_\Í°Æ1Á_x000B__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_XÇX¹,_x0000__x0018_Ât¬_x0008__x0000__x0000_20110729_x000C__x0000__x0000_043-222-3040
+_x0000__x0000_0432245050_x0008__x0000__x0001_©Í­Ì½Ä³ _x0000_­ÌüÈÜÂ_x0006__x0000__x0000_361842_x0012__x0000__x0001_©Í½ _x0000_­ÌüÈÜÂ _x0000_ÁÀù²l­ _x0000_8Öø»\¸ _x0000_2_x0000_0_x0000_6_x0000__x0005__x0000__x0001_1_x0000_5Î _x0000_È!Î_x000D__x0000__x0000_010-5468-3319_x0015__x0000__x0000_wsung3525@hanmail.net_x0008__x0000__x0000_20080429_x000E__x0000__x0000_37690004507237_x0006__x0000__x0000_D00121_x000D__x0000__x0001_Æ%±¤ÂìÓmÕ_x0010_È(_x0000_XÕtÇlÐ¬¹´Å)_x0000_
+_x0000__x0000_5061736246_x0003__x0000__x0001__x0015_È@Ç_x0001_Æ_x0008__x0000__x0000_20090227_x000C__x0000__x0000_054-283-5234
+_x0000__x0000_0542835231_x0008__x0000__x0001_½¬ÁÀ½Ä³ _x0000_ìÓmÕÜÂ_x0006__x0000__x0000_790822_x0012__x0000__x0001_½¬½ _x0000_ìÓmÕÜÂ _x0000_¨°l­ _x0000__x0000_³Ä³Ù³ _x0000_8_x0000_6_x0000_-_x0000_2_x0000__x000D__x0000__x0000_010-4133-7770_x0014__x0000__x0000_minton1125@naver.com_x0008__x0000__x0000_20081105_x000E__x0000__x0000_37690004508937_x0006__x0000__x0000_D00122_x0005__x0000__x0001_°Æ¬¹¤ÂìÓ Î
+_x0000__x0000_4172105493_x0003__x0000__x0001__x0015_¼_x0018_ÂÄÉ_x0008__x0000__x0000_20180101_x000C__x0000__x0000_051-632-2681
+_x0000__x0000_0516322681_x0008__x0000__x0001_½°À_x0011_­íÅÜÂ _x0000_¨°l­_x0006__x0000__x0000_608827_x0011__x0000__x0001_½°À_x0011_­íÅÜÂ _x0000_¨°l­ _x0000_Ç ÇÉÓTÖ\¸ _x0000_4_x0000_9_x0000__x000D__x0000__x0000_010-2594-2682_x0015__x0000__x0000_moxie2000@hanmail.net_x000E__x0000__x0000_37690004509537_x0006__x0000__x0000_D00123_x0005__x0000__x0001_°Æ1Á¤ÂìÓ Î
+_x0000__x0000_2077003708_x0003__x0000__x0001_@®DÆÝÂ_x0008__x0000__x0000_20071009_x000B__x0000__x0000_02-465-1297	_x0000__x0000_024651197	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x0011_­ÄÉl­_x0006__x0000__x0000_143961_x0010__x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x0011_­ÄÉl­ _x0000_l­XÇ\¸ _x0000_6_x0000_6_x0000__x0014__x0000__x0001_1_x0000_5Î _x0000_(_x0000_l­XÇÙ³ _x0000_2_x0000_2_x0000_7_x0000_-_x0000_6_x0000_)_x0000_ _x0000_°Æ1Á¤ÂìÓ Î_x000D__x0000__x0000_010-3418-1230_x000F__x0000__x0000_ws418@naver.com_x000E__x0000__x0000_37690004510537_x0006__x0000__x0000_D00126_x0005__x0000__x0001_ÐÆÙ³´Ì!Ç¬À
+_x0000__x0000_3060363748_x0003__x0000__x0001_ü»Ñ¼ÁÉ_x0004__x0000__x0001_´ÆÙ³0®l­_x0008__x0000__x0000_20050705_x000C__x0000__x0000_042-531-4004
+_x0000__x0000_0425328899_x0008__x0000__x0001__x0000_³_x0004_È_x0011_­íÅÜÂ _x0000_Ù³l­_x0005__x0000__x0000_34630_x000D__x0000__x0001__x0000_³_x0004_È _x0000_Ù³l­ _x0000__x0000_³_x0004_È\¸ _x0000_7_x0000_6_x0000_5_x0000__x000D__x0000__x0000_010-5453-9536_x0012__x0000__x0000_wonspo@hanmail.net_x0008__x0000__x0000_20080214_x000E__x0000__x0000_37690004511137_x0006__x0000__x0000_D00127_x0008__x0000__x0001_ÐÆ¤ÂìÓ Î(_x0000__x001C_ÈüÈ)_x0000_
+_x0000__x0000_6160962051_x0003__x0000__x0001_@®ø»½¬_x000C__x0000__x0000_064-752-4422
+_x0000__x0000_0647232992_x000C__x0000__x0001__x001C_ÈüÈ¹ÒÄ¼ÇXÎÄ³ _x0000__x001C_ÁÀ­ìÓÜÂ_x0006__x0000__x0000_690161_x0013__x0000__x0001__x001C_ÈüÈ¹ÒÄ¼ÇXÎÄ³ _x0000__x001C_ÈüÈÜÂ _x0000_$Æ|·\¸ _x0000_1_x0000_3_x0000_4_x0000__x000D__x0000__x0000_010-4416-4412_x0015__x0000__x0000_crony0104@hanmail.net_x000E__x0000__x0000_37690004512837_x0006__x0000__x0000_D00132_x0005__x0000__x0001__x0004_ÈüÈÆ%±¤Â
+_x0000__x0000_4020887887_x0003__x0000__x0001_tÇ_x001C_Â+È_x000C__x0000__x0000_063-274-9337
+_x0000__x0000_0632789337_x0008__x0000__x0001__x0004_È|·½Ä³ _x0000__x0004_ÈüÈÜÂ_x0006__x0000__x0000_560080_x0013__x0000__x0001__x0004_È|·½Ä³ _x0000__x0004_ÈüÈÜÂ _x0000_DÆ°Àl­ _x0000_õ¬½\¸ _x0000_2_x0000_0_x0000__x000D__x0000__x0000_010-9224-8391_x0010__x0000__x0000_jyonex@naver.com_x000E__x0000__x0000_37690004516337_x0006__x0000__x0000_D00136_x0005__x0000__x0001__x001C_È|Ç¤ÂìÓ Î
+_x0000__x0000_4040533542_x000B__x0000__x0001__x001C_È|Ç_x0008_¸_x0000_È¤ÂìÓ Î(_x0000__x0015_ÈMÇ)_x0000__x0003__x0000__x0001_@®_x0011_­õ¼	_x0000__x0001_´ÆÙ³0®l­_x000F_¼´ÆÙ³õ¼xÆ_x000C__x0000__x0000_063-535-9146
+_x0000__x0000_0635332093_x0008__x0000__x0001__x0004_È|·½Ä³ _x0000__x0015_ÈMÇÜÂ_x0006__x0000__x0000_580804_x000F__x0000__x0001__x0004_È|·½Ä³ _x0000__x0015_ÈMÇÜÂ _x0000__x0011_ÉYÅ\¸ _x0000_8_x0000_3_x0000__x000D__x0000__x0000_010-9579-7800_x0016__x0000__x0000_sports9146@hanmaIl.net_x000E__x0000__x0000_37690004520237_x0006__x0000__x0000_D00137_x000B__x0000__x0001_üÈÝÂÖ¬À _x0000_0¼Ü´ü»4ÑÈ¹¸Ò
+_x0000__x0000_1108193203_x0003__x0000__x0001__x0015_ÈtÇ@±_x000B__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000__x0004_ÈÇÁÀp¬·_x0008__x0000__x0000_20130723_x000C__x0000__x0000_031-964-3530	_x0000__x0000_023829555_x0007__x0000__x0001_½¬0®Ä³ _x0000_à¬ÅÜÂ_x0005__x0000__x0000_10564_x0011__x0000__x0001_½¬0® _x0000_à¬ÅÜÂ _x0000_U³Ål­ _x0000_¼À¡Á\¸ _x0000_1_x0000_2_x0000__x0007__x0000__x0001_4_x0000_5Î _x0000_4_x0000_1_x0000_8_x0000_8Ö_x000D__x0000__x0000_010-7152-7538_x0014__x0000__x0000_mintonmart@naver.com_x000E__x0000__x0000_37690004521937_x0006__x0000__x0000_D00138	_x0000__x0001_üÈÝÂÖ¬ÀÙ³°Æ¤ÂìÓ Î
+_x0000__x0000_1108180426_x0003__x0000__x0001_¡Á_x0015_È|Ç_x000B__x0000__x0000_02-382-3598	_x0000__x0000_023553586	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_@ÇÉÓl­_x0006__x0000__x0000_122903_x0018__x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_@ÇÉÓl­ _x0000_ðÅ_x001C_Á\¸ _x0000_2_x0000_9_x0000_-_x0000_1_x0000_ _x0000_Ù³°Æ¤ÂìÓ Î_x000D__x0000__x0000_010-2018-3598_x0012__x0000__x0000_dvip1233@naver.com_x000B__x0000__x0000_01074353598
+_x0000__x0001__x0018_Â_x0008_® _x0000_½qÈ&lt;Ç\¸ _x0000_µÑ_x001C_È_x000E__x0000__x0000_37690004522537_x0006__x0000__x0000_D00141	_x0000__x0001__x0011_ÉYÅ¤ÂìÓ Î(_x0000_½¬üÈ)_x0000_
+_x0000__x0000_3226600323_x0003__x0000__x0001_iÖ_x0001_ÆäÂ_x0008__x0000__x0000_20081210_x000C__x0000__x0000_054-741-5177_x0008__x0000__x0001_½¬ÁÀ½Ä³ _x0000_½¬üÈÜÂ_x0006__x0000__x0000_780943_x0012__x0000__x0001_½¬ÁÀ½Ä³ _x0000_½¬üÈÜÂ _x0000__x0008_®1Á\¸ _x0000_2_x0000_9_x0000_4_x0000_-_x0000_1_x0000__x000D__x0000__x0000_010-7579-5177_x0014__x0000__x0000_jasp6304@hanmail.net_x0008__x0000__x0000_20081211_x000E__x0000__x0000_37690004525437_x0006__x0000__x0000_D00145_x0005__x0000__x0001_­Ìá¸¤ÂìÓ Î
+_x0000__x0000_6150796307_x0003__x0000__x0001_pÈø»_x0019_Â_x0008__x0000__x0000_20101004_x000C__x0000__x0000_055-312-9559
+_x0000__x0000_0553129560_x0008__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_@®tÕÜÂ_x0006__x0000__x0000_621833_x0012__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_@®tÕÜÂ _x0000_¥Ç Ç\¸ _x0000_2_x0000_9_x0000_7_x0000_-_x0000_5_x0000__x000D__x0000__x0000_010-9513-9559_x0016__x0000__x0000_jms3129559@hanmail.net_x0008__x0000__x0000_20101019_x000E__x0000__x0000_37690004530037_x0006__x0000__x0000_D00148_x0007__x0000__x0001__x0000_ÏtÇdÅD¾¤ÂìÓ Î
+_x0000__x0000_1232481068_x0003__x0000__x0001__x0015_¼+ºÇ_x000C__x0000__x0000_031-457-8706
+_x0000__x0000_0314578707_x0007__x0000__x0001_½¬0®Ä³ _x0000_HÅÅÜÂ_x0006__x0000__x0000_431837_x0012__x0000__x0001_½¬0®Ä³ _x0000_HÅÅÜÂ _x0000_Ù³HÅl­ _x0000_À­xÇ\¸ _x0000_8_x0000_9_x0000__x000D__x0000__x0000_010-7338-7375_x0016__x0000__x0000_jamjali200@hanmail.net_x000E__x0000__x0000_37690004532237_x0006__x0000__x0000_D00149	_x0000__x0001_TÏ¬¹DÅ$Æ_x0008_Õ(_x0000_@®Ì)_x0000_
+_x0000__x0000_5100147324_x0003__x0000__x0001__x0015_¼ Á_x0001_Æ_x0008__x0000__x0000_20070423_x000C__x0000__x0000_054-430-7007
+_x0000__x0000_0544307007_x0008__x0000__x0001_½¬ÁÀ½Ä³ _x0000_@®ÌÜÂ_x0005__x0000__x0000_39626_x000E__x0000__x0001_½¬½ _x0000_@®ÌÜÂ _x0000_¡Á$Á\¸ _x0000_1_x0000_6_x0000_4_x0000__x000D__x0000__x0000_010-4115-6306_x0013__x0000__x0000_jj10654@hanmail.net_x000E__x0000__x0000_37690004533937_x0006__x0000__x0000_D00150_x0005__x0000__x0001__x0014_Ól­¤ÂìÓ Î
+_x0000__x0000_5020153204_x0003__x0000__x0001_àÂÁÀÜ­_x0008__x0000__x0000_20080331_x000C__x0000__x0000_053-957-8989
+_x0000__x0000_0539432345_x0008__x0000__x0001__x0000_³l­_x0011_­íÅÜÂ _x0000_Ù³l­_x0005__x0000__x0000_41193_x000F__x0000__x0001__x0000_³l­ _x0000_Ù³l­ _x0000_DÅÅ\¸1_x0000_1_x0000_8® _x0000_8_x0000_1_x0000__x0008__x0000__x0001_1_x0000_5Î _x0000__x0014_Ól­¤ÂìÓ Î_x000D__x0000__x0000_010-8854-8989_x0012__x0000__x0000_89sports@naver.com_x000E__x0000__x0000_37690004534537_x0006__x0000__x0000_D00159_x0005__x0000__x0001__x001C_Ö1Á¤ÂìÓ Î
+_x0000__x0000_1300531089_x0003__x0000__x0001_tÇXÇ Á_x000D__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000__x0000_¬_x0004_È_x001C_ÈÔ,_x0000_¡ÇTÖ_x0008__x0000__x0000_20070529_x000C__x0000__x0000_032-654-2133
+_x0000__x0000_0326542132_x0007__x0000__x0001_½¬0®Ä³ _x0000_½ÌÜÂ_x0006__x0000__x0000_422819 _x0000__x0001_½¬0®Ä³ _x0000_½ÌÜÂ _x0000_Á¬Àl­ _x0000_½¬xÇ\¸1_x0000_2_x0000_0_x0000_¼8® _x0000_2_x0000_8_x0000_ _x0000_ _x0000_1_x0000_5Î_x0010_ÈìÓ _x0000_1_x0000_xÎ_x000D__x0000__x0000_010-7578-7740_x0015__x0000__x0000_hs7167741@hanmail.net_x000E__x0000__x0000_37690004541337_x0006__x0000__x0000_D00160_x0005__x0000__x0001_8ÖÙ³¤ÂìÓ Î
+_x0000__x0000_1243919047_x0003__x0000__x0001_@®8ÖÙ³_x0008__x0000__x0000_20100113_x000C__x0000__x0000_031-375-0331
+_x0000__x0000_0313750331_x0007__x0000__x0001_½¬0®Ä³ _x0000_$Æ°ÀÜÂ_x0006__x0000__x0000_447802_x001A__x0000__x0001_½¬0®Ä³ _x0000_$Æ°ÀÜÂ _x0000_1Á8Ö_x0000_³\¸ _x0000_2_x0000_5_x0000_ _x0000_´Æ°ÀL¾)µ _x0000_ _x0000_1_x0000_5Î _x0000_4_x0000__x000D__x0000__x0000_010-5295-8278_x0013__x0000__x0000_khd9982@hanmail.net_x000E__x0000__x0000_37690004542037_x0006__x0000__x0000_D00161_x0005__x0000__x0001_MÖ1ÁÆ%±¤Â
+_x0000__x0000_3100640518_x0003__x0000__x0001_@®_x0004_Ö_x0015_È_x0008__x0000__x0000_20090616_x000C__x0000__x0000_041-634-7327_x0008__x0000__x0001_©Í­Ì¨°Ä³ _x0000_MÖ1Áp­_x0005__x0000__x0000_32263_x0012__x0000__x0001_©Í¨° _x0000_MÖ1Áp­ _x0000_MÖ½MÇ _x0000_©Í¨°_x0000_³\¸ _x0000_3_x0000_6_x0000__x0015__x0000__x0001__x001C_È _x0000_1_x0000_5Î _x0000__x001C_È _x0000_1_x0000_0_x0000_1_x0000_8Ö(_x0000_L¾dÅT³¤Â$Æ&lt;Õ¤ÂTÑ)_x0000__x000D__x0000__x0000_010-8626-9825_x0010__x0000__x0000_hji923@naver.com_x000E__x0000__x0000_37690004543637_x0006__x0000__x0000_D00166_x000C__x0000__x0001_(_x0000_üÈ)_x0000_ðÒ_x001C_ÈtÇ_x0014_µ¤Â¸Ò¬¹ð½XÁ
+_x0000__x0000_2118732516_x0003__x0000__x0001_¡ÁÁÀÐÆ_x0006__x0000__x0001_Ä³Áä¹ _x0000_Ä³ä¹_x0008__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_4»íÅ_x0008__x0000__x0000_20120911_x000B__x0000__x0000_02-511-5114	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x0015_¬¨°l­_x0006__x0000__x0000_135010_x000B__x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ_x0015_¬¨°l­|±_x0004_ÖÙ³_x000E__x0000__x0001__x0008_®@ÇL¾)µ _x0000_1_x0000_5Î _x0000_ ¼¤Â¸Ò¤Â Ñ´Å_x000D__x0000__x0000_010-8784-1651_x0015__x0000__x0000_bestextreme@naver.com_x0007__x0000__x0001_B_x0000_ñ´	®(_x0000_T_x0000_S_x0000_)_x0000__x0005__x0000__x0000_14049_x0003__x0000__x0001__x0015_¼_x0004_ÖÄÉ_x0008__x0000__x0000_20190917_x0006__x0000__x0000_D00167_x0008__x0000__x0001_üÈÝÂÖ¬À _x0000_ÐÆÐÅÇ
+_x0000__x0000_1268800066_x0003__x0000__x0001_@®DÕ¹Â_x0006__x0000__x0001_Ä³Áä¹ÅÅ _x0000_xÆ_x0007__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_xÆ_x000C__x0000__x0000_02-1644-1662	_x0000__x0001_½°À_x0011_­íÅÜÂ _x0000__x0018_Â_x0001_Æl­_x0006__x0000__x0000_613815_x0013__x0000__x0001_½°À_x0011_­íÅÜÂ _x0000__x0018_Â_x0001_Æl­ _x0000__x0011_­¨°\¸ _x0000_6_x0000_3_x0000_ _x0000_B_x0000_Ù³_x0004__x0000__x0001_4_x0000_5Î|Ç½_x000D__x0000__x0000_010-8882-4137_x0014__x0000__x0000_oneeight@hanmail.net_x0006__x0000__x0000_D00173_x0005__x0000__x0001__x0008_®_x0001_Æ¤ÂìÓ Î
+_x0000__x0000_1052087391_x0003__x0000__x0001_°ÆÀÉÐÆ_x0008__x0000__x0000_20140217_x000D__x0000__x0000_010-6208-8112_x0006__x0000__x0000_121889_x0013__x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_È¹ìÓl­ _x0000_Ù³P­\¸3_x0000_8® _x0000_1_x0000_2_x0000_5_x0000__x0013__x0000__x0000_yonex0901@naver.com_x0008__x0000__x0000_20150122_x000E__x0000__x0000_37690004557937_x0006__x0000__x0000_D00181_x0004__x0000__x0001__x0000_É¤ÂìÓ Î
+_x0000__x0000_1410240836_x0003__x0000__x0001__x0015_¼½¬·_x0008__x0000__x0000_20140825_x000C__x0000__x0000_031-945-2007_x0007__x0000__x0001_½¬0®Ä³ _x0000__x000C_ÓüÈÜÂ_x0006__x0000__x0000_413819$_x0000__x0001_½¬0®Ä³ _x0000__x000C_ÓüÈÜÂ _x0000_DÅ¬¹·\¸ _x0000_5_x0000_5_x0000_ _x0000_-_x0000_8_x0000_1_x0000_ _x0000_(_x0000__x0008_®_x000C_ÍÙ³,_x0000_ _x0000__x000C_ÓüÈ_x0008_®_x000C_ÍXÕ_x0018_ÂÌ¬¹¥Ç)_x0000__x000C__x0000__x0001__x000C_ÓüÈÜÂ _x0000_0¼Ü´ü»4Ñ_x0004_È©Æl­¥Ç_x000D__x0000__x0000_010-9129-1126_x0017__x0000__x0000_leesjun1024@hanmail.net_x000E__x0000__x0000_37690004547137_x0006__x0000__x0000_D00183_x0003__x0000__x0001_T³_x001C_È|Ç
+_x0000__x0000_1171558537_x0003__x0000__x0001_iÖÐÆ Á_x000B__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_XÇX¹,_x0000_¡ÇTÖ_x0008__x0000__x0000_20141027_x000D__x0000__x0000_010-6333-2457	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_ÅÌl­_x0005__x0000__x0000_08078 _x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_ÅÌl­ _x0000_àÂ_x0015_È\¸ _x0000_2_x0000_7_x0000_5_x0000_ _x0000_ _x0000_(_x0000_àÂ_x0015_ÈÙ³,_x0000_ _x0000_àÂ¸Ò¬¹DÅ_x000C_Ó¸Ò)_x0000__x0010__x0000__x0001_ÁÀ_x0000_¬Ù³ _x0000_1_x0000_5Î _x0000_1_x0000_0_x0000_4_x0000_,_x0000_ _x0000_1_x0000_0_x0000_5_x0000_8Ö_x0011__x0000__x0000_thejeil@naver.com_x000D__x0000__x0000_010-9668-2210_x000E__x0000__x0000_37690004550437_x0006__x0000__x0000_D00184_x0005__x0000__x0001_$Æ¨°¤ÂìÓ Î
+_x0000__x0000_1322489384_x0003__x0000__x0001_Å+È¨º_x000D__x0000__x0001_´ÆÙ³0®l­©ÆÔ _x0000_aÅ8Á_x001C_Á¬¹ _x0000_xÆ_x0008__x0000__x0000_20141028
+_x0000__x0000_0315756464
+_x0000__x0000_0315755600_x0008__x0000__x0001_½¬0®Ä³ _x0000_¨°ÅüÈÜÂ_x0006__x0000__x0000_472881_x0016__x0000__x0001_½¬0®Ä³ _x0000_¨°ÅüÈÜÂ _x0000_ÄÉt¬$Æ¨°\¸ _x0000_8_x0000_0_x0000_6_x0000_ _x0000_-_x0000_1_x0000_4_x0000__x000D__x0000__x0000_010-9289-9637_x0012__x0000__x0000_jongmo83@naver.com_x000E__x0000__x0000_37690004552737_x0006__x0000__x0000_D00186_x0005__x0000__x0001_ä¹XÎìÓxÇ¸Ò
+_x0000__x0000_6091853217_x0003__x0000__x0001_iÖ­ÝÂ_x0008__x0000__x0000_20141202_x000C__x0000__x0000_055-298-7330_x0005__x0000__x0000_51378_x0011__x0000__x0001_½¬¨° _x0000_=ÌÐÆÜÂ _x0000_XÇ=Ìl­ _x0000__x0018_¼Ä¬\¸ _x0000_6_x0000_3_x0000__x000D__x0000__x0000_010-3561-0209_x000E__x0000__x0000_o2bbi@nate.com_x0008__x0000__x0000_20141212_x000E__x0000__x0000_37690004554037_x0006__x0000__x0000_D00190_x0005__x0000__x0001_p­°À¤ÂìÓ Î
+_x0000__x0000_4010657765_x0003__x0000__x0001__x0015_¼_x001C_Âl×	_x0000__x0001_¤ÂìÓ ÎXÇX¹,_x0000_ _x0000_©ÆÔ_x0008__x0000__x0000_20150406_x000D__x0000__x0000_010-9977-7141_x0008__x0000__x0001__x0004_È|·½Ä³ _x0000_p­°ÀÜÂ_x0005__x0000__x0000_54102_x000F__x0000__x0001__x0004_È½ _x0000_p­°ÀÜÂ _x0000_¨°_x0018_Â¡Á5_x0000_8® _x0000_4_x0000_2_x0000__x000F__x0000__x0001_1_x0000_0_x0000_1_x0000_8Ö(_x0000__x0018_Â¡ÁÙ³,_x0000_ _x0000_(Ì$Æ¹L¾)_x0000__x0013__x0000__x0000_shp7141@hanmaiL.net_x000E__x0000__x0000_37690004558537_x0006__x0000__x0000_D00192
+_x0000__x0001__x0001_Æ8»¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1222039517_x0005__x0000__x0001__x0001_Æ8»¤ÂìÓ Î_x0003__x0000__x0001_@®_x0001_Æ8»_x0008__x0000__x0000_20150608_x000C__x0000__x0000_032-523-1406_x000C__x0000__x0000_032-517-8009	_x0000__x0001_xÇÌ_x0011_­íÅÜÂ _x0000_½ÉÓl­_x0005__x0000__x0000_21337_x000D__x0000__x0000_010-4320-1406_x0012__x0000__x0000_YM1406@hanmail.net_x0007__x0000__x0001_A_x0000_ñ´	®(_x0000_T_x0000_S_x0000_)_x0000__x0005__x0000__x0000_13042_x0003__x0000__x0001_@®Ù³½¬_x000E__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_+_x0000_3_x0000_0_x0000__x000E__x0000__x0000_37690004561837_x0006__x0000__x0000_D00193_x000B__x0000__x0001_ÑÐ¤Â@Õ¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1320972497_x0006__x0000__x0001_ÑÐ¤Â@Õ¤ÂìÓ Î_x0003__x0000__x0001__x0015_¼_x0004_Ö=Ì_x0006__x0000__x0001_´ÆÙ³_x0004_È8»©ÆÔ_x0008__x0000__x0000_20150610_x000D__x0000__x0000_010-3706-2477_x0007__x0000__x0001_½¬0®Ä³ _x0000_l­¬¹ÜÂ_x0005__x0000__x0000_11907_x000F__x0000__x0001_½¬0® _x0000_l­¬¹ÜÂ _x0000_UÆ_x0019_ÂÌ\¸ _x0000_5_x0000_0_x0000_7_x0000_	_x0000__x0001_3_x0000_5Î _x0000_ÑÐ¤Â@Õ¤ÂìÓ Î_x000F__x0000__x0000_pspin@naver.com_x0005__x0000__x0000_22022_x0003__x0000__x0001_HÅ°ÆÄÉ_x000C__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_7_x0000_._x0000_5_x0000__x000E__x0000__x0000_37690004560137_x0006__x0000__x0000_D00195
+_x0000__x0001_¤ÂìÓ ÎLÑlÐ(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_6172249744_x0005__x0000__x0001_¤ÂìÓ ÎLÑlÐ_x0003__x0000__x0001_tÇÝÐ0®_x0006__x0000__x0001__x001C_ÈpÈÅÅ _x0000_Áä¹_x000C__x0000__x0001_õ¬_x0008_Æ _x0000_¤ÂìÓ Î©ÆÔ,_x0000_ _x0000_¡ÇTÖ_x000B__x0000__x0000_051-7564800_x000C__x0000__x0000_051-756-4801_x0005__x0000__x0000_48222_x0017__x0000__x0001_½°À_x0011_­íÅÜÂ _x0000_Ù³·l­ _x0000_+ÈiÕ´ÆÙ³¥Ç\¸ _x0000_4_x0000_0_x0000_¼8® _x0000_8_x0000_'_x0000__x0001_1_x0000_0_x0000_3_x0000_Ù³ _x0000_1_x0000_0_x0000_5_x0000_8Ö,_x0000_1_x0000_0_x0000_6_x0000_8Ö(_x0000_¬ÀÁÉÙ³,_x0000_½°À _x0000_DÅÜÂDÅÜ´ _x0000_TÏ$Æq¸ _x0000_XÕ²DÌ _x0000_DÅ_x000C_Ó¸Ò)_x0000__x000D__x0000__x0000_010-5578-1988_x0015__x0000__x0000_ltktennis@hanmail.net_x000B__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_8_x0000__x0008__x0000__x0000_20150611_x000E__x0000__x0000_37690004562437_x0006__x0000__x0000_D00196	_x0000__x0001__x0015_¬¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_5041920932_x0004__x0000__x0001__x0015_¬¤ÂìÓ Î_x0003__x0000__x0001__x0015_¬@Çl­_x000D__x0000__x0001_LÑÈ²¤Â©ÆÔ,_x0000_ _x0000_XÇX¹,_x0000_ _x0000_àÂ_x001C_¼_x000C__x0000__x0000_053-314-9090_x0005__x0000__x0000_41433_x000D__x0000__x0000_010-3828-0474_x0013__x0000__x0000_keg0417@hanmail.net_x000D__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_6_x0000_+_x0000_1_x0000_5_x0000__x0008__x0000__x0000_20150612_x000E__x0000__x0000_37690004565337_x0006__x0000__x0000_D00199
+_x0000__x0001_P´¬¹¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1283008985_x0003__x0000__x0001_@®_x0001_Æ Á_x000B__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_¤ÂìÓ ÎXÇX¹_x0008__x0000__x0000_20150703_x000C__x0000__x0000_031-911-4191_x000C__x0000__x0000_031-913-0067_x0006__x0000__x0000_410829_x000F__x0000__x0001_½¬0®Ä³à¬ÅÜÂ _x0000_|Ç°ÀÙ³l­_x0015_È_x001C_¼°ÀÙ³_x000E__x0000__x0001_1_x0000_1_x0000_4_x0000_8_x0000_-_x0000_1_x0000_3_x0000_ _x0000_1_x0000_5Î2_x0000_,_x0000_3_x0000_8Ö_x000D__x0000__x0000_010-4288-3563_x0012__x0000__x0000_usop2n@hanmail.net_x000D__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_6_x0000_+_x0000_2_x0000_3_x0000__x000E__x0000__x0000_37690004568237_x0006__x0000__x0000_D00201_x000E__x0000__x0001_(_x0000_üÈ)_x0000_¤ÂtÎtÇ¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_6278102573_x000B__x0000__x0001_¤ÂtÎtÇ¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000__x0003__x0000__x0001_@®1ÁÐÆ_x0006__x0000__x0001_Áä¹ÅÅ _x0000_Ä³ä¹_x0008__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_ä¹_x0010_È_x000C__x0000__x0000_041-566-1879_x000C__x0000__x0000_041-554-2732_x0005__x0000__x0000_31157"_x0000__x0001_©Í­Ì¨°Ä³ _x0000_ÌHÅÜÂ _x0000__x001C_Á½l­ _x0000_1¼_x001D_Á3_x0000_\¸ _x0000_2_x0000_9_x0000_ _x0000_ _x0000_(_x0000_1¼_x001D_ÁÙ³,_x0000_ _x0000_½¶É¹_x0008_Ã%¼)_x0000__x000D__x0000__x0000_010-4513-1879_x0011__x0000__x0000_kimsw000@nate.com_x000E__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_4_x0000_0_x0000_+_x0000_2_x0000_0_x0000__x0008__x0000__x0000_20150804_x000E__x0000__x0000_37690004570937_x0006__x0000__x0000_D00202_x0008__x0000__x0001_¤ÂìÓå²(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_3052275067_x0003__x0000__x0001_HÅü­¹Â_x000C__x0000__x0000_042-522-9566_x000C__x0000__x0000_042-271-4786_x0006__x0000__x0000_300810_x0017__x0000__x0001__x0000_³_x0004_È_x0011_­íÅÜÂ _x0000__x0011_Él­ _x0000_Ù³_x001C_Á_x0000_³\¸ _x0000_1_x0000_2_x0000_0_x0000_1_x0000_(_x0000_ÜÐÉÓÙ³)_x0000__x0007__x0000__x0001_¤ÂìÓå² _x0000_ÜÐÉÓ_x0010_È_x000B__x0000__x0000_01062224787_x0010__x0000__x0000_spodaq@naver.com_x000D__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_5_x0000_+_x0000_3_x0000_3_x0000__x0008__x0000__x0000_20150805_x000E__x0000__x0000_37690004571537_x0006__x0000__x0000_D00203	_x0000__x0001_ðÅTÏ¬¹DÅ(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_2041477980_x0004__x0000__x0001_ðÅTÏ¬¹DÅ_x0003__x0000__x0001_@®ÁÀ0®_x0006__x0000__x0001_Ä³Áä¹ _x0000_t¬$Á_x000D__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_´Ì!ÇÜÂ_x001C_Á&lt;»$ÁXÎ_x0008__x0000__x0000_20150806_x000C__x0000__x0000_02-3390-4345_x000C__x0000__x0000_02-3390-4344
+_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_Ù³_x0000_³8»l­_x0005__x0000__x0000_02496_x0011__x0000__x0001__x001C_Á¸Æ _x0000_Ù³_x0000_³8»l­ _x0000_Ý¹°Æ\¸1_x0000_2_x0000_8® _x0000_1_x0000_9_x0000__x000B__x0000__x0001_1_x0000_5Î _x0000_XÕtÇÐÆ¤ÂìÓ Î°ÀÅÅ_x000D__x0000__x0000_010-9089-5363_x0017__x0000__x0000_01090895363@hanmail.net_x000B__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_2_x0000_0_x0000__x000E__x0000__x0000_37690004572137_x0006__x0000__x0000_D00205_x0005__x0000__x0001_ÁLÑ¤ÂìÓ Î
+_x0000__x0000_1971301851_x0003__x0000__x0001_@®_x0001_Æ_x0018_Â_x0008__x0000__x0001_Ä³Áä¹ÅÅ _x0000_Ä³ä¹ÅÅ	_x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_4»íÅÅÅ_x000B__x0000__x0000_01063388568_x0008__x0000__x0001_½¬0®Ä³ _x0000_XÇ_x0015_È½ÜÂ_x0005__x0000__x0000_11806!_x0000__x0001_½¬0®Ä³ _x0000_XÇ_x0015_È½ÜÂ _x0000_$Æ©º\¸ _x0000_1_x0000_7_x0000_0_x0000_ _x0000_°Àä´È¹DÇ _x0000_DÅ_x000C_Ó¸Ò _x0000_4_x0000_1_x0000_2_x0000_-_x0000_7_x0000_0_x0000_6_x0000__x000D__x0000__x0000_010-6338-8568_x0011__x0000__x0000_3388568@naver.com_x0005__x0000__x0000_26002_x0003__x0000__x0001__x0015_¬ÜÐ8Ö_x0008__x0000__x0000_20220901_x000E__x0000__x0000_37690004700437_x0006__x0000__x0000_D00209_x0018__x0000__x0001_¤ÂìÓ Î_x000C_Õì·¤Â(_x0000_S_x0000_p_x0000_o_x0000_r_x0000_t_x0000_s_x0000_ _x0000_P_x0000_l_x0000_u_x0000_s_x0000_)_x0000_(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1192167071_x0003__x0000__x0001__x0015_¬ÜÂ¨º_x0006__x0000__x0001_Ä³Áä¹ _x0000_LÇÝÂ_x0008__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_\ÕÝÂ_x000B__x0000__x0000_02-871-5513	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x0000_­EÅl­_x0005__x0000__x0000_08750_x000F__x0000__x0001__x001C_Á¸Æ _x0000__x0000_­EÅl­ _x0000_àÂ¼¹\¸3_x0000_8® _x0000_4_x0000_0_x0000__x0005__x0000__x0001_ÀÉXÕ _x0000_1_x0000_5Î_x000D__x0000__x0000_010-7703-5353_x001A__x0000__x0000_tennisplus0122@esero.go.krX_x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_ _x0000_/_x0000_ _x0000_2_x0000_5_x0000_S_x0000_S_x0000_ _x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_ _x0000_/_x0000_ _x0000_2_x0000_4_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_9_x0000_._x0000_6_x0000_ _x0000_/_x0000_ _x0000_2_x0000_4_x0000_S_x0000_S_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_ _x0000_/_x0000_ _x0000_2_x0000_3_x0000_F_x0000_W_x0000_ _x0000__x0018_ÂüÈ _x0000_ìÅàÂ _x0000_ _x0000_1_x0000_2_x0000_ _x0000_(_x0000_ô²ù²Ç _x0000_Æ­Ì&lt;Ç\¸ _x0000_6_x0000_ _x0000__x0018_¼_x0001_Æ)_x0000__x0008__x0000__x0000_20160114_x000E__x0000__x0000_37690004577337_x0006__x0000__x0000_D00210_x0011__x0000__x0001_(_x0000_üÈ)_x0000_ÐÅtÇ_x001C_ÈtÇxÇ0Ñ´°TÁ °(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1268641398_x000C__x0000__x0000_031-761-8980_x000C__x0000__x0000_031-761-2140_x0005__x0000__x0000_12769_x000D__x0000__x0000_010-4552-3318	_x0000__x0000_1800-6142_x000E__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_4_x0000_0_x0000_+_x0000_2_x0000_5_x0000__x0008__x0000__x0000_20160121_x000E__x0000__x0000_37690004578037_x0006__x0000__x0000_D00256	_x0000__x0001_p¬1Á¤ÂìÓ Î(_x0000_Å°À)_x0000_
+_x0000__x0000_6210808090_x0003__x0000__x0001__x0015_È+È_x0015_¬_x0006__x0000__x0001_Ä³Áä¹ _x0000__x001C_ÈpÈ_x000B__x0000__x0001_ìÕ¤Â0®l­,_x0000_ _x0000_¤ÂìÓ Î©ÆÔ_x0008__x0000__x0000_20160412_x000C__x0000__x0000_055-387-3613_x000C__x0000__x0000_055-387-3615_x0008__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_Å°ÀÜÂ_x0005__x0000__x0000_50621 _x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_Å°ÀÜÂ _x0000__x001C_Á|ÇÙ³\¸ _x0000_2_x0000_5_x0000_ _x0000_ _x0000_(_x0000__x0011_É½Ù³,_x0000_ _x0000_$Ç ÁÝÀ_x0001_Æ´ÅP­äÂ)_x0000__x000D__x0000__x0000_010-2390-2994_x0013__x0000__x0000_dhrhr68@hanmail.netH_x0000__x0001_2_x0000_4_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_3_x0000_5_x0000_ _x0000_/_x0000_2_x0000_4_x0000_S_x0000_S_x0000__x0018_ÂüÈìÅàÂ _x0000_3_x0000_5_x0000_ _x0000_/_x0000_ _x0000_2_x0000_3_x0000_F_x0000_W_x0000_ _x0000__x0018_ÂüÈ _x0000_ìÅàÂ _x0000_3_x0000_5_x0000_ _x0000_/_x0000_ _x0000_2_x0000_3_x0000_S_x0000_S_x0000_ _x0000__x0018_ÂüÈ _x0000_ìÅàÂ _x0000_3_x0000_5_x0000_(_x0000_|·_x0013_Ï+_x0000_È¹D¾¤Â _x0000_9_x0000_4_x0000_3_x0000_,_x0000_2_x0000_5_x0000_0_x0000_)_x0000__x0008__x0000__x0000_20160407_x000E__x0000__x0000_37690004581237_x0006__x0000__x0000_D00267_x0006__x0000__x0001__x001C_ÈtÇD¾¤ÂìÓ Î
+_x0000__x0000_6664100083_x0003__x0000__x0001_Ç_x0015_È\Õ_x000D__x0000__x0001_Ä³ä¹ _x0000__x000F_¼ _x0000_Áä¹ÅÅ,_x0000_ _x0000__x001C_ÁD¾¤Â_x000C__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_ _x0000__x0011_­à¬_x0000_³ÕÅÅ_x0008__x0000__x0000_20160610_x000C__x0000__x0000_062-523-7451_x000C__x0000__x0000_062-523-7455_x0005__x0000__x0000_62023_x000D__x0000__x0001__x0011_­üÈ _x0000__x001C_Ál­ _x0000_´ÆÌ\¸ _x0000_1_x0000_2_x0000_2_x0000__x0005__x0000__x0001_(_x0000__x000D_Ã_x000C_ÍÙ³)_x0000__x000D__x0000__x0000_010-4606-4538_x0015__x0000__x0000_jhrim1226@hanmail.net_x0008__x0000__x0000_20160601_x000E__x0000__x0000_37690004584137_x0006__x0000__x0000_D00280_x0005__x0000__x0001_Ä³ô²¤ÂìÓ Î
+_x0000__x0000_3071042161_x0003__x0000__x0001_$ÇÙ³ÝÂ_x000B__x0000__x0001_Ä³ä¹_x000F_¼ _x0000_Áä¹ÅÅ _x0000_Áä¹ÅÅ_x0010__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_Ç_x0004_Èp¬ _x0000__x0010_Óä¹,_x0000_ _x0000__x0000_³ìÅ_x0008__x0000__x0000_20160825_x000C__x0000__x0000_044-863-8908_x000C__x0000__x0000_044-863-8970_x000F__x0000__x0001_8Á+È¹ÒÄ¼ÇXÎÜÂ _x0000_8Á+È¹ÒÄ¼ÇXÎÜÂ_x0005__x0000__x0000_30102_x001E__x0000__x0001_8Á+È¹ÒÄ¼ÇXÎÜÂ _x0000__x0008_È¬Ç\¸ _x0000_1_x0000_7_x0000_2_x0000_ _x0000_(_x0000_´ÅÄÉÙ³,_x0000_ _x0000_ÜÐ\Õ_x0004_Õ_x0008_¸¤Â&lt;Á0Ñ)_x0000__x0004__x0000__x0001_1_x0000_0_x0000_1_x0000_8Ö_x000D__x0000__x0000_010-7185-8008_x0015__x0000__x0000_dodamsports@naver.com_x000E__x0000__x0000_37690004586437_x0006__x0000__x0000_D00282_x0005__x0000__x0001__x0004_²¬¹¤ÂìÓ Î
+_x0000__x0000_1082124505_x0003__x0000__x0001_@®l×_x0015_È_x0006__x0000__x0001_Áä¹ _x0000_Ä³Áä¹_x000C__x0000__x0001__x0004_ÈÇÁÀp¬·ÅÅ _x0000_0¼Ü´ü»4Ñ _x0000__x000B__x0000__x0000_02-848-6291_x000B__x0000__x0000_02-848-7556
+_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x0001_Æñ´ìÓl­_x0005__x0000__x0000_07375_x000E__x0000__x0001__x001C_Á¸Æ _x0000__x0001_Æñ´ìÓl­ _x0000_Ä³àÂ\¸ _x0000_5_x0000_1_x0000__x000D__x0000__x0001_1_x0000_5Î _x0000_1_x0000_0_x0000_5_x0000_8Ö(_x0000_¡ÁU³L¾)µ)_x0000__x000D__x0000__x0000_010-8393-6291_x0013__x0000__x0000_hee00jung@naver.com_x0008__x0000__x0000_20160905_x000E__x0000__x0000_37690004588737_x0006__x0000__x0000_D00286_x0007__x0000__x0001_Æ%±¤Â _x0000_1Á¨°_x0010_È
+_x0000__x0000_2603001743_x0003__x0000__x0001_MÖ¥Ç8Ö_x0008__x0000__x0001_Ä³ä¹ _x0000__x000F_¼ _x0000_Áä¹ÅÅ_x0008__x0000__x0000_20151218_x000C__x0000__x0000_031-755-7257_x0007__x0000__x0001_½¬0®Ä³ _x0000_1Á¨°ÜÂ_x0005__x0000__x0000_13110_x001E__x0000__x0001_½¬0®Ä³ _x0000_1Á¨°ÜÂ _x0000__x0018_Â_x0015_Èl­ _x0000_1Á¨°_x0000_³\¸ _x0000_1_x0000_2_x0000_6_x0000_7_x0000_ _x0000_-_x0000_1_x0000_ _x0000_(_x0000_ÜÐÉÓÙ³)_x0000__x000D__x0000__x0000_010-7191-7257_x0012__x0000__x0000_nero1016@naver.com_x0002__x0000__x0001_¨°¸Ó_x0008__x0000__x0000_20161109_x000E__x0000__x0000_37690004591037_x0006__x0000__x0000_D00287_x0005__x0000__x0001_¤ÐtÎ¤ÂìÓ Î
+_x0000__x0000_6103752918_x0003__x0000__x0001_@®ÜÐÇ_x0008__x0000__x0000_20161125_x000C__x0000__x0000_052-268-6086_x000C__x0000__x0000_052-272-5908_x0008__x0000__x0001_¸Æ°À_x0011_­íÅÜÂ _x0000_¨°l­_x0005__x0000__x0000_44692_x0016__x0000__x0001_¸Æ°À_x0011_­íÅÜÂ _x0000_¨°l­ _x0000_Ë³ÈÉ\¸ _x0000_1_x0000_2_x0000_4_x0000_ _x0000_ _x0000_(_x0000_ì²Ù³)_x0000__x0003__x0000__x0000_3/2_x000D__x0000__x0000_010-9568-6086_x0014__x0000__x0000_kika5908@hanmail.net_x000E__x0000__x0000_37690004592637_x0006__x0000__x0000_D00292_x0008__x0000__x0001_Æ%±¤Â _x0000_¤ÂìÓÐÆ_x0010_È
+_x0000__x0000_6977800050_x0003__x0000__x0001_\ÕÀ­_x0001_Æ_x0008__x0000__x0000_20170102_x000C__x0000__x0000_051-517-3862_x000C__x0000__x0000_051-583-1023	_x0000__x0001_½°À_x0011_­íÅÜÂ _x0000__x0008_®_x0015_Èl­_x0005__x0000__x0000_46207&amp;_x0000__x0001_½°À_x0011_­íÅÜÂ _x0000__x0008_®_x0015_Èl­ _x0000_´Ì!Çõ¬ÐÆ\¸3_x0000_9_x0000_9_x0000_¼8® _x0000_3_x0000_2_x0000_4_x0000_ _x0000_ _x0000_(_x0000_P´l­Ù³,_x0000_ _x0000_¤ÂìÓÐÆ_x000C_ÓlÐ)_x0000__x0010__x0000__x0001_ÀÉXÕ1_x0000_5Î(_x0000_P´l­Ù³,_x0000_ _x0000_äÂ´°´Ì!Ç_x0000_­)_x0000__x000D__x0000__x0000_010-5505-3862_x0013__x0000__x0000_hgy4285@hanmail.net_x000E__x0000__x0000_37690004595537_x0006__x0000__x0000_D00306_x0007__x0000__x0001_Æ%±¤Â _x0000_ÁÀ4»_x0010_È
+_x0000__x0000_8042300420_x0003__x0000__x0001_@®_x0004_Ö+È_x000D__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_´ÆÙ³©ÆÔ _x0000_¡ÇTÖ_x0008__x0000__x0000_20170119_x000D__x0000__x0000_010-6886-7065_x000C__x0000__x0000_062-374-5410_x0005__x0000__x0000_61970_x0013__x0000__x0001__x0011_­üÈ _x0000__x001C_Ál­ _x0000_ÁÀ4»ü»üÈ\¸3_x0000_2_x0000_¼8® _x0000_3_x0000_-_x0000_5_x0000__x0013__x0000__x0000_sskim-j@hanmail.net_x000E__x0000__x0000_37690004597837_x0006__x0000__x0000_D00308_x0005__x0000__x0001_C_x0000_S_x0000_¤ÂìÓ Î
+_x0000__x0000_2270838785_x0007__x0000__x0001_iÖ_x001C_ÂU³xÆ _x0000_1_x0000_+º_x000C__x0000__x0000_031-385-1222_x000C__x0000__x0000_031-388-3477_x0005__x0000__x0000_13958_x0016__x0000__x0001_½¬0® _x0000_HÅÅÜÂ _x0000_Ì¹HÅl­ _x0000__x0008_Æ Âõ¬ÐÆ\¸5_x0000_2_x0000_¼8® _x0000_2_x0000__x000D__x0000__x0000_010-3176-9037_x0013__x0000__x0000_bill@cssports.co.kr_x000D__x0000__x0000_010-2727-2718_x000F__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_5_x0000_+_x0000_3_x0000_._x0000_5_x0000__x000E__x0000__x0000_37690004598437_x0006__x0000__x0000_D00311
+_x0000__x0001_TÏ¬¹DÅ¤ÂìÓ </v>
+          </cell>
+          <cell r="H39" t="e">
+            <v>#N/A</v>
           </cell>
           <cell r="I39" t="str">
             <v>소매</v>
@@ -4711,29 +6061,109 @@
           <cell r="L39" t="str">
             <v/>
           </cell>
-          <cell r="M39" t="str">
-            <v>033-638-0024</v>
-          </cell>
-          <cell r="N39" t="str">
-            <v>0336382400</v>
-          </cell>
-          <cell r="O39" t="str">
-            <v>강원도 속초시</v>
-          </cell>
-          <cell r="P39" t="str">
-            <v>217803</v>
-          </cell>
-          <cell r="Q39" t="str">
-            <v>강원도 속초시 교동로 39</v>
+          <cell r="M39" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="N39" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="O39" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="P39" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="Q39" t="e">
+            <v>#N/A</v>
           </cell>
           <cell r="R39" t="str">
             <v/>
           </cell>
           <cell r="S39" t="str">
-            <v>010-3297-3133</v>
-          </cell>
-          <cell r="T39" t="str">
-            <v>yubgijung1257@hanmail.net</v>
+            <v>㌱ᤳ_x0000_畹杢橩湵ㅧ㔲䀷慨浮楡⹬敮๴_x0000_㜳㤶〰㐰㠴㐱㜳_x0006_䐀〰㤰ରĀ주식회사 스매쉬스포츠
+㠀㔵㜸㌰㜲ضĀ스매쉬스포츠_x0003_␁_xDCC7_ࢻ_x0000_〲㜰㤰㜱_x000B_　〱㜸ㄵㄱ㤹_x0007_봁ガ쒮₳䠀냅_xDCC0_ׂ_x0000_㔱㤴ሷĀ경기 안산시 상록구 천문4길 17_x001A_㄁㔀㇎㔀㄀㤀ⴀ㄀㌀  ㄀㔀⃎ ꐀ油꓂⃓⃎㰀墻㲹チෑ_x0000_㄰ⴰ㐵ㄷ㌭㌳ጰ_x0000_浳獡⵨㈱䀳慮敶⹲潣୭_x0000_㄰㔰㜴㌱㌳ะ_x0000_㜳㤶〰㐰㠴㜳㜳_x0008_℁㇇Ⴡ⛈㄀　　─؀_x0000_い〰㘹_x0005_ꐁ⃓䗎沼ૐ_x0000_㈱㈷㤰ㄲㄶ_x0003_䀁쒮짉ӓĀ체육용품_x0008_㈀〰〷〵ళ_x0000_㌰ⴱ㌵ⴵ㈱㐴
+　ㄳ㌵㈵㐲ܵĀ경기도 포천시_x0006_㐀㜸㔰ᠰĀ경기도 포천시 군내면 호국로 1696. 2층_x000D_　〱㘭㔳ⴴ㐵ㄷ_x0011_欀灪ㄳ桀湡慭汩渮瑥_x000E_㌀㘷〹〰㐴㜸㌲ط_x0000_い〰㜹_x0005_뤁곂꒹⃓૎_x0000_〲ㄱ㠰㐱㌷_x0003_톬낼ࣆ_x0000_〲㜰㈱ㄲ_x000C_　ⴲ㈲㤷〭㜷ਹ_x0000_㈰㈲㠷㜰㠷_x0005_　㔴㌶_x001E_ᰁ룁맆쓒_xDCBC_⃂ᄀ泉₭관쓌鲬峌₸㈀㐀㘀  ⠀⤀낼_xD9C0_ⲳ 준哓_xDCD6_ꗂ⧇ᘀĀ1,2,3층 다-102(방산동,평화시장)_x000D_　〱㌭㠲ⴴ㌷㌸_x0019_瘀捩潴祲灳牯獴桀湡慭汩渮瑥_x000E_㌀㘷〹〰㐴㠸㌹ط_x0000_い㄰㄰_x0005_䐁냅꓀⃓૎_x0000_ㄳ㈲㜸㤲㈸_x0003_封藍볈ಹĀ도매및상품중개업,소매업_x0008_㈀㄰〱〷ఱ_x0000_㐰ⴱ㌵ⴲ㌸ㄸ
+　ㄴ㌵㠲㠳࠲Ā충청남도 아산시_x0006_㌀㘳㔰ူĀ충청남도 아산시 시민로 251_x000D_　〱㐭㐹ⴶ㌸㔸_x0013_樀摵捯汪桀湡慭汩渮瑥_x000E_㌀㘷〹〰㐴〹㌵ط_x0000_い㄰㤰_x0008_ā꓆⃓⣎ꠀ킰⧆਀_x0000_〱㔹㠲ㄹㄳ_x0003_琁ᗇ鳈࣌_x0000_〲㜰ㄱ㤱_x000C_　㌶㘭㈳㐭㔱਴_x0000_㘰㘳㈳ㄴ㘵_x0005_㔀㜵㌰_x0015_Ё糈膷쒽₳ꠀ킰_xDCC6_⃂가璹₺_x0000_겳峀₸㄀㈀㠀㌀ЀĀ영스포츠_x000D_　〱㐭㤵ⴴ㘰㐳_x0013_樀汣敥㜸㐳湀癡牥挮浯_x000E_㌀㘷〹〰㐴㜹㌰ط_x0000_い㄰〱_x0007_鐁◆꒱⃂吀᳖Ⴢૈ_x0000_〴〸㜵〷㔸_x0003_Ё藈ᦺࣂ_x0000_〲㜰ㄱ㈰_x000C_　ㄶ㌭㔷㘭㐶࠷Ā전라남도 화순군_x0006_㔀㤱〸ᐹĀ전라남도 화순군 광덕로 140  1층_x000D_　〱㘭㌶ⴲ㠵㌹_x0012_洀⵳潪䁮慨浮楥⹬敮๴_x0000_㜳㤶〰㐰㤴㘸㜳_x0006_䐀〰ㄱఱĀ올림픽종합스포츠(목포)
+㐀ㄱ㐱㤶㠴̶Ā김창용_x000C_됁_xD9C6_꦳裆Ⳕ내泀ⲭ　傮袱ࣔ_x0000_〲㜰㌰〲_x000C_　ㄶ㈭㈴ㄭ㌰ਲ_x0000_㘰㈱㐴〳㈳_x0008_Ё糈ꢷ쒰₳꤀_xDCD3_ׂ_x0000_㠵㈷ံĀ전남 목포시 차범석길 41-1_x0002_㄁㔀෎_x0000_㄰ⴰ㈹㌴㐭㠲ဵ_x0000_祥扥湯䁯慤浵渮瑥_x000E_㌀㘷〹〰㐴㤹㌲ط_x0000_い㄰㘱_x000F_鐁◆꒱죂낹À겳Ⴙ⣈ﰀ㒻ꓑ⃓⧎਀_x0000_〶〸㠲〸㜲_x0003_ ǇᧆࣂĀ스포츠용품및의류_x000C_　㔵㈭㈲㔭㌴਱_x0000_㔰㈵㈲㐵㈳_x0008_봁솬ꣀ쒰₳㴀탌_xDCC6_ۂ_x0000_㌶㠱㈵_x0018_봁솬ꣀ쒰₳㴀탌_xDCC6_⃂저낹槀泓₭꤀죆岹₸㜀㘀 ﰀ_xDDC8_ැ_x0000_㄰ⴰ㜳㜰㘭㐲ᘵ_x0000_畤瑤獪㈶㔴桀湡慭汩渮瑥_x000E_㌀㘷〹〰㔴㐰㌳ط_x0000_い㄰〲_x0006_鐁◆꒱귂ﳌ჈ૈ_x0000_ㄳ〷㠳㠵㐵_x0003_封냍㇆ுĀ스포츠용품,의류,수건_x0008_㈀㄰〱㈷హ_x0000_㐰ⴳ㈲ⴲ〳〴
+　㌴㈲㔴㔰࠰Ā충청북도 청주시_x0006_㌀ㄶ㐸ሲĀ충북 청주시 상당구 호미로 206_x0005_㄁㔀⃎谀⇈෎_x0000_㄰ⴰ㐵㠶㌭ㄳᔹ_x0000_獷湵㍧㈵䀵慨浮楡⹬敮ࡴ_x0000_〲㠰㐰㤲_x000E_㌀㘷〹〰㔴㜰㌲ط_x0000_い㄰ㄲ_x000D_鐁◆꒱淓ვ⣈堀瓕泇곐뒹⧅਀_x0000_〵ㄶ㌷㈶㘴_x0003_ᔁ䃈Ǉࣆ_x0000_〲㤰㈰㜲_x000C_　㐵㈭㌸㔭㌲਴_x0000_㔰㈴㌸㈵ㄳ_x0008_봁솬臀쒽₳淓_xDCD5_ۂ_x0000_㤷㠰㈲_x0012_봁膬₽淓_xDCD5_⃂ꠀ沰₭_x0000_쒳_xD9B3_₳㠀㘀ⴀ㈀ഀ_x0000_㄰ⴰㄴ㌳㜭㜷ᐰ_x0000_業瑮湯ㄱ㔲湀癡牥挮浯_x0008_㈀〰ㄸ〱ี_x0000_㜳㤶〰㐰〵㤸㜳_x0006_䐀〰㈱ԲĀ우리스포츠
+㐀㜱ㄲ㔰㤴̳Ā박수진_x0008_㈀㄰〸〱ఱ_x0000_㔰ⴱ㌶ⴲ㘲ㄸ
+　ㄵ㌶㈲㠶࠱Ā부산광역시 남구_x0006_㘀㠰㈸ᄷĀ부산광역시 남구 자유평화로 49_x000D_　〱㈭㤵ⴴ㘲㈸_x0015_洀硯敩〲〰桀湡慭汩渮瑥_x000E_㌀㘷〹〰㔴㤰㌵ط_x0000_い㄰㌲_x0005_뀁㇆꓁⃓૎_x0000_〲㜷〰㜳㠰_x0003_䀁䒮_xDDC6_ࣂ_x0000_〲㜰〱㤰_x000B_　ⴲ㘴ⴵ㈱㜹	　㐲㔶ㄱ㜹	ᰁ룁맆쓒_xDCBC_⃂ᄀ쒭泉ڭ_x0000_㐱㤳ㄶ_x0010_ᰁ룁맆쓒_xDCBC_⃂ᄀ쒭泉₭氀墭峇₸㘀㘀᐀Ā1층 (구의동 227-6) 우성스포츠_x000D_　〱㌭ㄴⴸ㈱〳_x000F_眀㑳㠱湀癡牥挮浯_x000E_㌀㘷〹〰㔴〱㌵ط_x0000_い㄰㘲_x0005_퀁_xD9C6_뒳⇌곇ી_x0000_〳〶㘳㜳㠴_x0003_ﰁ톻솼ӉĀ운동기구_x0008_㈀〰〵〷వ_x0000_㐰ⴲ㌵ⴱ〴㐰
+　㈴㌵㠲㤸࠹Ā대전광역시 동구_x0005_㌀㘴〳_x000D__x0001_ҳ⃈_xD900_河₭_x0000_ҳ峈₸㜀㘀㔀ഀ_x0000_㄰ⴰ㐵㌵㤭㌵ሶ_x0000_潷獮潰桀湡慭汩渮瑥_x0008_㈀〰〸ㄲิ_x0000_㜳㤶〰㐰ㄵㄱ㜳_x0006_䐀〰㈱࠷Ā원스포츠(제주)
+㘀㘱㤰㈶㔰̱Ā김미경_x000C_　㐶㜭㈵㐭㈴ਲ_x0000_㘰㜴㌲㤲㈹_x000C_ᰁﳈ마쓒邼壇쓎₳ᰀ상_xDCD3_ۂ_x0000_㤶㄰ㄶ_x0013_ᰁﳈ마쓒邼壇쓎₳ᰀﳈ_xDCC8_⃂␀糆岷₸㄀㌀㐀ഀ_x0000_㄰ⴰ㐴㘱㐭ㄴᔲ_x0000_牣湯べ〱䀴慨浮楡⹬敮๴_x0000_㜳㤶〰㐰ㄵ㠲㜳_x0006_䐀〰㌱ԲĀ전주요넥스
+㐀㈰㠰㜸㠸̷Ā이순종_x000C_　㌶㈭㐷㤭㌳਷_x0000_㘰㈳㠷㌹㜳_x0008_Ё糈膷쒽₳Ѐﳈ_xDCC8_ۂ_x0000_㘵〰〸_x0013_Ё糈膷쒽₳Ѐﳈ_xDCC8_⃂䐀냆泀₭膬岽₸㈀　ഀ_x0000_㄰ⴰ㈹㐲㠭㤳ေ_x0000_祪湯硥湀癡牥挮浯_x000E_㌀㘷〹〰㔴㘱㌳ط_x0000_い㄰㘳_x0005_ᰁ糈꓇⃓૎_x0000_〴〴㌵㔳㈴_x000B_ᰁ糈ࣇ¸꓈⃓⣎ᔀ䷈⧇̀Ā김광복	됁_xD9C6_コ沮ྭ뒼_xD9C6_碼ೆ_x0000_㘰ⴳ㌵ⴵㄹ㘴
+　㌶㌵㈳㤰࠳Ā전라북도 정읍시_x0006_㔀〸〸༴Ā전라북도 정읍시 중앙로 83_x000D_　〱㤭㜵ⴹ㠷〰_x0016_猀潰瑲㥳㐱䀶慨浮䥡⹬敮๴_x0000_㜳㤶〰㐰㈵㈰㜳_x0006_䐀〰㌱ଷĀ주식회사 배드민턴마트
+㄀〱ㄸ㌹〲̳Ā정이녀_x000B_ꐁ⃓꧎裆⃔Ѐ郈쇇烀颬ࢷ_x0000_〲㌱㜰㌲_x000C_　ㄳ㤭㐶㌭㌵र_x0000_㈰㠳㤲㔵ܵĀ경기도 고양시_x0005_㄀㔰㐶_x0011_봁ガ₮醬_xDCC5_⃂唀醳泅₭밀ꇀ峁₸㄀㈀܀Ā4층 418호_x000D_　〱㜭㔱ⴲ㔷㠳_x0014_洀湩潴浮牡䁴慮敶⹲潣๭_x0000_㜳㤶〰㐰㈵㤱㜳_x0006_䐀〰㌱सĀ주식회사동우스포츠
+㄀〱ㄸ〸㈴̶Ā송정일_x000B_　ⴲ㠳ⴲ㔳㠹	　㌲㔵㔳㘸	ᰁ룁맆쓒_xDCBC_⃂䀀짇泓ڭ_x0000_㈱㤲㌰_x0018_ᰁ룁맆쓒_xDCBC_⃂䀀짇泓₭᳅峁₸㈀㤀ⴀ㄀ _xD900_낳꓆⃓෎_x0000_㄰ⴰ〲㠱㌭㤵ሸ_x0000_癤灩㈱㌳湀癡牥挮浯_x000B_　〱㐷㔳㔳㠹
+᠁ࣂ₮耀熽㳈峇₸딀່᳑_x0000_㜳㤶〰㐰㈵㔲㜳_x0006_䐀〰㐱ऱĀ중앙스포츠(경주)
+㌀㈲㘶〰㈳̳Ā황영실_x0008_㈀〰ㄸㄲర_x0000_㔰ⴴ㐷ⴱㄵ㜷_x0008_봁솬臀쒽₳봀ﲬ_xDCC8_ۂ_x0000_㠷㤰㌴_x0012_봁솬臀쒽₳봀ﲬ_xDCC8_⃂ࠀㆮ峁₸㈀㤀㐀ⴀ㄀ഀ_x0000_㄰ⴰ㔷㤷㔭㜱ᐷ_x0000_慪灳㌶㐰桀湡慭汩渮瑥_x0008_㈀〰ㄸㄲั_x0000_㜳㤶〰㐰㈵㐵㜳_x0006_䐀〰㐱ԵĀ청룡스포츠
+㘀㔱㜰㘹〳̷Ā조미숙_x0008_㈀㄰㄰〰ఴ_x0000_㔰ⴵㄳⴲ㔹㤵
+　㔵ㄳ㤲㘵࠰Ā경상남도 김해시_x0006_㘀ㄲ㌸ሳĀ경상남도 김해시 장유로 297-5_x000D_　〱㤭ㄵⴳ㔹㤵_x0016_樀獭ㄳ㤲㔵䀹慨浮楡⹬敮ࡴ_x0000_〲〱〱㤱_x000E_㌀㘷〹〰㔴〳㌰ط_x0000_い㄰㠴_x0007__x0001_瓏擇䓅꒾⃓૎_x0000_㈱㈳㠴〱㠶_x0003_ᔁ薼邺ೇ_x0000_㌰ⴱ㔴ⴷ㜸㘰
+　ㄳ㔴㠷〷ܷĀ경기도 안양시_x0006_㐀ㄳ㌸ሷĀ경기도 안양시 동안구 귀인로 89_x000D_　〱㜭㌳ⴸ㌷㔷_x0016_樀浡慪楬〲䀰慨浮楡⹬敮๴_x0000_㜳㤶〰㐰㌵㈲㜳_x0006_䐀〰㐱हĀ코리아오픈(김천)
+㔀〱㄰㜴㈳̴Ā박선영_x0008_㈀〰〷㈴ళ_x0000_㔰ⴴ㌴ⴰ〷㜰
+　㐵㌴㜰〰࠷Ā경상북도 김천시_x0005_㌀㘹㘲_x000E_봁膬₽䀀鲮_xDCCC_⃂ꄀⓁ峁₸㄀㘀㐀ഀ_x0000_㄰ⴰㄴ㔱㘭〳ጶ_x0000_橪〱㔶䀴慨浮楡⹬敮๴_x0000_㜳㤶〰㐰㌵㤳㜳_x0006_䐀〰㔱԰Ā팔구스포츠
+㔀㈰㄰㌵〲̴Ā신상규_x0008_㈀〰〸㌳ఱ_x0000_㔰ⴳ㔹ⴷ㤸㤸
+　㌵㐹㈳㐳࠵Ā대구광역시 동구_x0005_㐀ㄱ㌹_x000F__x0001_河₭_xD900_河₭䐀釅峅ㆸ㄀㠀₮㠀㄀ࠀĀ1층 팔구스포츠_x000D_　〱㠭㔸ⴴ㤸㤸_x0012_㠀猹潰瑲䁳慮敶⹲潣๭_x0000_㜳㤶〰㐰㌵㔴㜳_x0006_䐀〰㔱ԹĀ혜성스포츠
+㄀〳㔰ㄳ㠰̹Ā이의선_x000D_ꐁ⃓꧎裆Ⳕ_x0000_Ҭ᳈裈Ⳕꄀ哇ࣖ_x0000_〲㜰㔰㤲_x000C_　㈳㘭㐵㈭㌱ਲ਼_x0000_㌰㘲㐵ㄲ㈳_x0007_봁ガ쒮₳耀鲽_xDCCC_ۂ_x0000_㈴㠲㤱 봁ガ쒮₳耀鲽_xDCCC_⃂谀곁泀₭봀碬峇ㆸ㈀　蠀㢼₮㈀㠀  ㄀㔀჎⃓㄀砀෎_x0000_㄰ⴰ㔷㠷㜭㐷ᔰ_x0000_獨ㄷ㜶㐷䀱慨浮楡⹬敮๴_x0000_㜳㤶〰㐰㐵㌱㜳_x0006_䐀〰㘱԰Ā호동스포츠
+㄀㐲㤳㤱㐰̷Ā김호동_x0008_㈀㄰〰ㄱళ_x0000_㌰ⴱ㜳ⴵ㌰ㄳ
+　ㄳ㜳〵㌳ܱĀ경기도 오산시_x0006_㐀㜴〸ᨲĀ경기도 오산시 성호대로 25 운산빌딩  1층 4_x000D_　〱㔭㤲ⴵ㈸㠷_x0013_欀摨㤹㈸桀湡慭汩渮瑥_x000E_㌀㘷〹〰㔴㈴㌰ط_x0000_い㄰ㄶ_x0005_䴁㇖铁◆꒱ૂ_x0000_ㄳ〰㐶㔰㠱_x0003_䀁Үᗖࣈ_x0000_〲㤰㘰㘱_x000C_　ㄴ㘭㐳㜭㈳࠷Ā충청남도 홍성군_x0005_㌀㈲㌶_x0012_꤁꣍₰䴀㇖烁₭䴀臖䶽⃇꤀꣍°岳₸㌀㘀ᔀĀ제 1층 제 101호(빌앤더스오피스텔)_x000D_　〱㠭㈶ⴶ㠹㔲_x0010_栀楪㈹䀳慮敶⹲潣๭_x0000_㜳㤶〰㐰㐵㘳㜳_x0006_䐀〰㘱శĀ(주)티제이디스트리뷰션
+㈀ㄱ㜸㈳ㄵ̶Ā송상원_x0006_쐁貳₹쐀ࢹĀ스포츠용품 무역_x0008_㈀㄰〲ㄹ଱_x0000_㈰㔭ㄱ㔭ㄱऴĀ서울특별시 강남구_x0006_㄀㔳㄰ରĀ서울특별시강남구논현동_x000E_ࠁ䂮䳇⦾₵㄀㔀⃎ꀀ꒼룂ꓒꃂ듑ළ_x0000_㄰ⴰ㜸㐸ㄭ㔶ᔱ_x0000_敢瑳硥牴浥䁥慮敶⹲潣m_x0007__x0000__x0001_B_x0000_ñ´	®(_x0000_T_x0000_S_x0000_)_x0000__x0005__x0000__x0000_14049_x0003__x0000__x0001__x0015_¼_x0004_ÖÄÉ_x0008__x0000__x0000_20190917_x0006__x0000__x0000_D00167_x0008__x0000__x0001_üÈÝÂÖ¬À _x0000_ÐÆÐÅÇ
+_x0000__x0000_1268800066_x0003__x0000__x0001_@®DÕ¹Â_x0006__x0000__x0001_Ä³Áä¹ÅÅ _x0000_xÆ_x0007__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_xÆ_x000C__x0000__x0000_02-1644-1662	_x0000__x0001_½°À_x0011_­íÅÜÂ _x0000__x0018_Â_x0001_Æl­_x0006__x0000__x0000_613815_x0013__x0000__x0001_½°À_x0011_­íÅÜÂ _x0000__x0018_Â_x0001_Æl­ _x0000__x0011_­¨°\¸ _x0000_6_x0000_3_x0000_ _x0000_B_x0000_Ù³_x0004__x0000__x0001_4_x0000_5Î|Ç½_x000D__x0000__x0000_010-8882-4137_x0014__x0000__x0000_oneeight@hanmail.net_x0006__x0000__x0000_D00173_x0005__x0000__x0001__x0008_®_x0001_Æ¤ÂìÓ Î
+_x0000__x0000_1052087391_x0003__x0000__x0001_°ÆÀÉÐÆ_x0008__x0000__x0000_20140217_x000D__x0000__x0000_010-6208-8112_x0006__x0000__x0000_121889_x0013__x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_È¹ìÓl­ _x0000_Ù³P­\¸3_x0000_8® _x0000_1_x0000_2_x0000_5_x0000__x0013__x0000__x0000_yonex0901@naver.com_x0008__x0000__x0000_20150122_x000E__x0000__x0000_37690004557937_x0006__x0000__x0000_D00181_x0004__x0000__x0001__x0000_É¤ÂìÓ Î
+_x0000__x0000_1410240836_x0003__x0000__x0001__x0015_¼½¬·_x0008__x0000__x0000_20140825_x000C__x0000__x0000_031-945-2007_x0007__x0000__x0001_½¬0®Ä³ _x0000__x000C_ÓüÈÜÂ_x0006__x0000__x0000_413819$_x0000__x0001_½¬0®Ä³ _x0000__x000C_ÓüÈÜÂ _x0000_DÅ¬¹·\¸ _x0000_5_x0000_5_x0000_ _x0000_-_x0000_8_x0000_1_x0000_ _x0000_(_x0000__x0008_®_x000C_ÍÙ³,_x0000_ _x0000__x000C_ÓüÈ_x0008_®_x000C_ÍXÕ_x0018_ÂÌ¬¹¥Ç)_x0000__x000C__x0000__x0001__x000C_ÓüÈÜÂ _x0000_0¼Ü´ü»4Ñ_x0004_È©Æl­¥Ç_x000D__x0000__x0000_010-9129-1126_x0017__x0000__x0000_leesjun1024@hanmail.net_x000E__x0000__x0000_37690004547137_x0006__x0000__x0000_D00183_x0003__x0000__x0001_T³_x001C_È|Ç
+_x0000__x0000_1171558537_x0003__x0000__x0001_iÖÐÆ Á_x000B__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_XÇX¹,_x0000_¡ÇTÖ_x0008__x0000__x0000_20141027_x000D__x0000__x0000_010-6333-2457	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_ÅÌl­_x0005__x0000__x0000_08078 _x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_ÅÌl­ _x0000_àÂ_x0015_È\¸ _x0000_2_x0000_7_x0000_5_x0000_ _x0000_ _x0000_(_x0000_àÂ_x0015_ÈÙ³,_x0000_ _x0000_àÂ¸Ò¬¹DÅ_x000C_Ó¸Ò)_x0000__x0010__x0000__x0001_ÁÀ_x0000_¬Ù³ _x0000_1_x0000_5Î _x0000_1_x0000_0_x0000_4_x0000_,_x0000_ _x0000_1_x0000_0_x0000_5_x0000_8Ö_x0011__x0000__x0000_thejeil@naver.com_x000D__x0000__x0000_010-9668-2210_x000E__x0000__x0000_37690004550437_x0006__x0000__x0000_D00184_x0005__x0000__x0001_$Æ¨°¤ÂìÓ Î
+_x0000__x0000_1322489384_x0003__x0000__x0001_Å+È¨º_x000D__x0000__x0001_´ÆÙ³0®l­©ÆÔ _x0000_aÅ8Á_x001C_Á¬¹ _x0000_xÆ_x0008__x0000__x0000_20141028
+_x0000__x0000_0315756464
+_x0000__x0000_0315755600_x0008__x0000__x0001_½¬0®Ä³ _x0000_¨°ÅüÈÜÂ_x0006__x0000__x0000_472881_x0016__x0000__x0001_½¬0®Ä³ _x0000_¨°ÅüÈÜÂ _x0000_ÄÉt¬$Æ¨°\¸ _x0000_8_x0000_0_x0000_6_x0000_ _x0000_-_x0000_1_x0000_4_x0000__x000D__x0000__x0000_010-9289-9637_x0012__x0000__x0000_jongmo83@naver.com_x000E__x0000__x0000_37690004552737_x0006__x0000__x0000_D00186_x0005__x0000__x0001_ä¹XÎìÓxÇ¸Ò
+_x0000__x0000_6091853217_x0003__x0000__x0001_iÖ­ÝÂ_x0008__x0000__x0000_20141202_x000C__x0000__x0000_055-298-7330_x0005__x0000__x0000_51378_x0011__x0000__x0001_½¬¨° _x0000_=ÌÐÆÜÂ _x0000_XÇ=Ìl­ _x0000__x0018_¼Ä¬\¸ _x0000_6_x0000_3_x0000__x000D__x0000__x0000_010-3561-0209_x000E__x0000__x0000_o2bbi@nate.com_x0008__x0000__x0000_20141212_x000E__x0000__x0000_37690004554037_x0006__x0000__x0000_D00190_x0005__x0000__x0001_p­°À¤ÂìÓ Î
+_x0000__x0000_4010657765_x0003__x0000__x0001__x0015_¼_x001C_Âl×	_x0000__x0001_¤ÂìÓ ÎXÇX¹,_x0000_ _x0000_©ÆÔ_x0008__x0000__x0000_20150406_x000D__x0000__x0000_010-9977-7141_x0008__x0000__x0001__x0004_È|·½Ä³ _x0000_p­°ÀÜÂ_x0005__x0000__x0000_54102_x000F__x0000__x0001__x0004_È½ _x0000_p­°ÀÜÂ _x0000_¨°_x0018_Â¡Á5_x0000_8® _x0000_4_x0000_2_x0000__x000F__x0000__x0001_1_x0000_0_x0000_1_x0000_8Ö(_x0000__x0018_Â¡ÁÙ³,_x0000_ _x0000_(Ì$Æ¹L¾)_x0000__x0013__x0000__x0000_shp7141@hanmaiL.net_x000E__x0000__x0000_37690004558537_x0006__x0000__x0000_D00192
+_x0000__x0001__x0001_Æ8»¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1222039517_x0005__x0000__x0001__x0001_Æ8»¤ÂìÓ Î_x0003__x0000__x0001_@®_x0001_Æ8»_x0008__x0000__x0000_20150608_x000C__x0000__x0000_032-523-1406_x000C__x0000__x0000_032-517-8009	_x0000__x0001_xÇÌ_x0011_­íÅÜÂ _x0000_½ÉÓl­_x0005__x0000__x0000_21337_x000D__x0000__x0000_010-4320-1406_x0012__x0000__x0000_YM1406@hanmail.net_x0007__x0000__x0001_A_x0000_ñ´	®(_x0000_T_x0000_S_x0000_)_x0000__x0005__x0000__x0000_13042_x0003__x0000__x0001_@®Ù³½¬_x000E__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_+_x0000_3_x0000_0_x0000__x000E__x0000__x0000_37690004561837_x0006__x0000__x0000_D00193_x000B__x0000__x0001_ÑÐ¤Â@Õ¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1320972497_x0006__x0000__x0001_ÑÐ¤Â@Õ¤ÂìÓ Î_x0003__x0000__x0001__x0015_¼_x0004_Ö=Ì_x0006__x0000__x0001_´ÆÙ³_x0004_È8»©ÆÔ_x0008__x0000__x0000_20150610_x000D__x0000__x0000_010-3706-2477_x0007__x0000__x0001_½¬0®Ä³ _x0000_l­¬¹ÜÂ_x0005__x0000__x0000_11907_x000F__x0000__x0001_½¬0® _x0000_l­¬¹ÜÂ _x0000_UÆ_x0019_ÂÌ\¸ _x0000_5_x0000_0_x0000_7_x0000_	_x0000__x0001_3_x0000_5Î _x0000_ÑÐ¤Â@Õ¤ÂìÓ Î_x000F__x0000__x0000_pspin@naver.com_x0005__x0000__x0000_22022_x0003__x0000__x0001_HÅ°ÆÄÉ_x000C__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_7_x0000_._x0000_5_x0000__x000E__x0000__x0000_37690004560137_x0006__x0000__x0000_D00195
+_x0000__x0001_¤ÂìÓ ÎLÑlÐ(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_6172249744_x0005__x0000__x0001_¤ÂìÓ ÎLÑlÐ_x0003__x0000__x0001_tÇÝÐ0®_x0006__x0000__x0001__x001C_ÈpÈÅÅ _x0000_Áä¹_x000C__x0000__x0001_õ¬_x0008_Æ _x0000_¤ÂìÓ Î©ÆÔ,_x0000_ _x0000_¡ÇTÖ_x000B__x0000__x0000_051-7564800_x000C__x0000__x0000_051-756-4801_x0005__x0000__x0000_48222_x0017__x0000__x0001_½°À_x0011_­íÅÜÂ _x0000_Ù³·l­ _x0000_+ÈiÕ´ÆÙ³¥Ç\¸ _x0000_4_x0000_0_x0000_¼8® _x0000_8_x0000_'_x0000__x0001_1_x0000_0_x0000_3_x0000_Ù³ _x0000_1_x0000_0_x0000_5_x0000_8Ö,_x0000_1_x0000_0_x0000_6_x0000_8Ö(_x0000_¬ÀÁÉÙ³,_x0000_½°À _x0000_DÅÜÂDÅÜ´ _x0000_TÏ$Æq¸ _x0000_XÕ²DÌ _x0000_DÅ_x000C_Ó¸Ò)_x0000__x000D__x0000__x0000_010-5578-1988_x0015__x0000__x0000_ltktennis@hanmail.net_x000B__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_8_x0000__x0008__x0000__x0000_20150611_x000E__x0000__x0000_37690004562437_x0006__x0000__x0000_D00196	_x0000__x0001__x0015_¬¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_5041920932_x0004__x0000__x0001__x0015_¬¤ÂìÓ Î_x0003__x0000__x0001__x0015_¬@Çl­_x000D__x0000__x0001_LÑÈ²¤Â©ÆÔ,_x0000_ _x0000_XÇX¹,_x0000_ _x0000_àÂ_x001C_¼_x000C__x0000__x0000_053-314-9090_x0005__x0000__x0000_41433_x000D__x0000__x0000_010-3828-0474_x0013__x0000__x0000_keg0417@hanmail.net_x000D__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_6_x0000_+_x0000_1_x0000_5_x0000__x0008__x0000__x0000_20150612_x000E__x0000__x0000_37690004565337_x0006__x0000__x0000_D00199
+_x0000__x0001_P´¬¹¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1283008985_x0003__x0000__x0001_@®_x0001_Æ Á_x000B__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_¤ÂìÓ ÎXÇX¹_x0008__x0000__x0000_20150703_x000C__x0000__x0000_031-911-4191_x000C__x0000__x0000_031-913-0067_x0006__x0000__x0000_410829_x000F__x0000__x0001_½¬0®Ä³à¬ÅÜÂ _x0000_|Ç°ÀÙ³l­_x0015_È_x001C_¼°ÀÙ³_x000E__x0000__x0001_1_x0000_1_x0000_4_x0000_8_x0000_-_x0000_1_x0000_3_x0000_ _x0000_1_x0000_5Î2_x0000_,_x0000_3_x0000_8Ö_x000D__x0000__x0000_010-4288-3563_x0012__x0000__x0000_usop2n@hanmail.net_x000D__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_6_x0000_+_x0000_2_x0000_3_x0000__x000E__x0000__x0000_37690004568237_x0006__x0000__x0000_D00201_x000E__x0000__x0001_(_x0000_üÈ)_x0000_¤ÂtÎtÇ¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_6278102573_x000B__x0000__x0001_¤ÂtÎtÇ¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000__x0003__x0000__x0001_@®1ÁÐÆ_x0006__x0000__x0001_Áä¹ÅÅ _x0000_Ä³ä¹_x0008__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_ä¹_x0010_È_x000C__x0000__x0000_041-566-1879_x000C__x0000__x0000_041-554-2732_x0005__x0000__x0000_31157"_x0000__x0001_©Í­Ì¨°Ä³ _x0000_ÌHÅÜÂ _x0000__x001C_Á½l­ _x0000_1¼_x001D_Á3_x0000_\¸ _x0000_2_x0000_9_x0000_ _x0000_ _x0000_(_x0000_1¼_x001D_ÁÙ³,_x0000_ _x0000_½¶É¹_x0008_Ã%¼)_x0000__x000D__x0000__x0000_010-4513-1879_x0011__x0000__x0000_kimsw000@nate.com_x000E__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_4_x0000_0_x0000_+_x0000_2_x0000_0_x0000__x0008__x0000__x0000_20150804_x000E__x0000__x0000_37690004570937_x0006__x0000__x0000_D00202_x0008__x0000__x0001_¤ÂìÓå²(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_3052275067_x0003__x0000__x0001_HÅü­¹Â_x000C__x0000__x0000_042-522-9566_x000C__x0000__x0000_042-271-4786_x0006__x0000__x0000_300810_x0017__x0000__x0001__x0000_³_x0004_È_x0011_­íÅÜÂ _x0000__x0011_Él­ _x0000_Ù³_x001C_Á_x0000_³\¸ _x0000_1_x0000_2_x0000_0_x0000_1_x0000_(_x0000_ÜÐÉÓÙ³)_x0000__x0007__x0000__x0001_¤ÂìÓå² _x0000_ÜÐÉÓ_x0010_È_x000B__x0000__x0000_01062224787_x0010__x0000__x0000_spodaq@naver.com_x000D__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_5_x0000_+_x0000_3_x0000_3_x0000__x0008__x0000__x0000_20150805_x000E__x0000__x0000_37690004571537_x0006__x0000__x0000_D00203	_x0000__x0001_ðÅTÏ¬¹DÅ(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_2041477980_x0004__x0000__x0001_ðÅTÏ¬¹DÅ_x0003__x0000__x0001_@®ÁÀ0®_x0006__x0000__x0001_Ä³Áä¹ _x0000_t¬$Á_x000D__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_´Ì!ÇÜÂ_x001C_Á&lt;»$ÁXÎ_x0008__x0000__x0000_20150806_x000C__x0000__x0000_02-3390-4345_x000C__x0000__x0000_02-3390-4344
+_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_Ù³_x0000_³8»l­_x0005__x0000__x0000_02496_x0011__x0000__x0001__x001C_Á¸Æ _x0000_Ù³_x0000_³8»l­ _x0000_Ý¹°Æ\¸1_x0000_2_x0000_8® _x0000_1_x0000_9_x0000__x000B__x0000__x0001_1_x0000_5Î _x0000_XÕtÇÐÆ¤ÂìÓ Î°ÀÅÅ_x000D__x0000__x0000_010-9089-5363_x0017__x0000__x0000_01090895363@hanmail.net_x000B__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_2_x0000_0_x0000__x000E__x0000__x0000_37690004572137_x0006__x0000__x0000_D00205_x0005__x0000__x0001_ÁLÑ¤ÂìÓ Î
+_x0000__x0000_1971301851_x0003__x0000__x0001_@®_x0001_Æ_x0018_Â_x0008__x0000__x0001_Ä³Áä¹ÅÅ _x0000_Ä³ä¹ÅÅ	_x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_4»íÅÅÅ_x000B__x0000__x0000_01063388568_x0008__x0000__x0001_½¬0®Ä³ _x0000_XÇ_x0015_È½ÜÂ_x0005__x0000__x0000_11806!_x0000__x0001_½¬0®Ä³ _x0000_XÇ_x0015_È½ÜÂ _x0000_$Æ©º\¸ _x0000_1_x0000_7_x0000_0_x0000_ _x0000_°Àä´È¹DÇ _x0000_DÅ_x000C_Ó¸Ò _x0000_4_x0000_1_x0000_2_x0000_-_x0000_7_x0000_0_x0000_6_x0000__x000D__x0000__x0000_010-6338-8568_x0011__x0000__x0000_3388568@naver.com_x0005__x0000__x0000_26002_x0003__x0000__x0001__x0015_¬ÜÐ8Ö_x0008__x0000__x0000_20220901_x000E__x0000__x0000_37690004700437_x0006__x0000__x0000_D00209_x0018__x0000__x0001_¤ÂìÓ Î_x000C_Õì·¤Â(_x0000_S_x0000_p_x0000_o_x0000_r_x0000_t_x0000_s_x0000_ _x0000_P_x0000_l_x0000_u_x0000_s_x0000_)_x0000_(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1192167071_x0003__x0000__x0001__x0015_¬ÜÂ¨º_x0006__x0000__x0001_Ä³Áä¹ _x0000_LÇÝÂ_x0008__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_\ÕÝÂ_x000B__x0000__x0000_02-871-5513	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x0000_­EÅl­_x0005__x0000__x0000_08750_x000F__x0000__x0001__x001C_Á¸Æ _x0000__x0000_­EÅl­ _x0000_àÂ¼¹\¸3_x0000_8® _x0000_4_x0000_0_x0000__x0005__x0000__x0001_ÀÉXÕ _x0000_1_x0000_5Î_x000D__x0000__x0000_010-7703-5353_x001A__x0000__x0000_tennisplus0122@esero.go.krX_x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_ _x0000_/_x0000_ _x0000_2_x0000_5_x0000_S_x0000_S_x0000_ _x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_ _x0000_/_x0000_ _x0000_2_x0000_4_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_9_x0000_._x0000_6_x0000_ _x0000_/_x0000_ _x0000_2_x0000_4_x0000_S_x0000_S_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_ _x0000_/_x0000_ _x0000_2_x0000_3_x0000_F_x0000_W_x0000_ _x0000__x0018_ÂüÈ _x0000_ìÅàÂ _x0000_ _x0000_1_x0000_2_x0000_ _x0000_(_x0000_ô²ù²Ç _x0000_Æ­Ì&lt;Ç\¸ _x0000_6_x0000_ _x0000__x0018_¼_x0001_Æ)_x0000__x0008__x0000__x0000_20160114_x000E__x0000__x0000_37690004577337_x0006__x0000__x0000_D00210_x0011__x0000__x0001_(_x0000_üÈ)_x0000_ÐÅtÇ_x001C_ÈtÇxÇ0Ñ´°TÁ °(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1268641398_x000C__x0000__x0000_031-761-8980_x000C__x0000__x0000_031-761-2140_x0005__x0000__x0000_12769_x000D__x0000__x0000_010-4552-3318	_x0000__x0000_1800-6142_x000E__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_4_x0000_0_x0000_+_x0000_2_x0000_5_x0000__x0008__x0000__x0000_20160121_x000E__x0000__x0000_37690004578037_x0006__x0000__x0000_D00256	_x0000__x0001_p¬1Á¤ÂìÓ Î(_x0000_Å°À)_x0000_
+_x0000__x0000_6210808090_x0003__x0000__x0001__x0015_È+È_x0015_¬_x0006__x0000__x0001_Ä³Áä¹ _x0000__x001C_ÈpÈ_x000B__x0000__x0001_ìÕ¤Â0®l­,_x0000_ _x0000_¤ÂìÓ Î©ÆÔ_x0008__x0000__x0000_20160412_x000C__x0000__x0000_055-387-3613_x000C__x0000__x0000_055-387-3615_x0008__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_Å°ÀÜÂ_x0005__x0000__x0000_50621 _x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_Å°ÀÜÂ _x0000__x001C_Á|ÇÙ³\¸ _x0000_2_x0000_5_x0000_ _x0000_ _x0000_(_x0000__x0011_É½Ù³,_x0000_ _x0000_$Ç ÁÝÀ_x0001_Æ´ÅP­äÂ)_x0000__x000D__x0000__x0000_010-2390-2994_x0013__x0000__x0000_dhrhr68@hanmail.netH_x0000__x0001_2_x0000_4_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_3_x0000_5_x0000_ _x0000_/_x0000_2_x0000_4_x0000_S_x0000_S_x0000__x0018_ÂüÈìÅàÂ _x0000_3_x0000_5_x0000_ _x0000_/_x0000_ _x0000_2_x0000_3_x0000_F_x0000_W_x0000_ _x0000__x0018_ÂüÈ _x0000_ìÅàÂ _x0000_3_x0000_5_x0000_ _x0000_/_x0000_ _x0000_2_x0000_3_x0000_S_x0000_S_x0000_ _x0000__x0018_ÂüÈ _x0000_ìÅàÂ _x0000_3_x0000_5_x0000_(_x0000_|·_x0013_Ï+_x0000_È¹D¾¤Â _x0000_9_x0000_4_x0000_3_x0000_,_x0000_2_x0000_5_x0000_0_x0000_)_x0000__x0008__x0000__x0000_20160407_x000E__x0000__x0000_37690004581237_x0006__x0000__x0000_D00267_x0006__x0000__x0001__x001C_ÈtÇD¾¤ÂìÓ Î
+_x0000__x0000_6664100083_x0003__x0000__x0001_Ç_x0015_È\Õ_x000D__x0000__x0001_Ä³ä¹ _x0000__x000F_¼ _x0000_Áä¹ÅÅ,_x0000_ _x0000__x001C_ÁD¾¤Â_x000C__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_ _x0000__x0011_­à¬_x0000_³ÕÅÅ_x0008__x0000__x0000_20160610_x000C__x0000__x0000_062-523-7451_x000C__x0000__x0000_062-523-7455_x0005__x0000__x0000_62023_x000D__x0000__x0001__x0011_­üÈ _x0000__x001C_Ál­ _x0000_´ÆÌ\¸ _x0000_1_x0000_2_x0000_2_x0000__x0005__x0000__x0001_(_x0000__x000D_Ã_x000C_ÍÙ³)_x0000__x000D__x0000__x0000_010-4606-4538_x0015__x0000__x0000_jhrim1226@hanmail.net_x0008__x0000__x0000_20160601_x000E__x0000__x0000_37690004584137_x0006__x0000__x0000_D00280_x0005__x0000__x0001_Ä³ô²¤ÂìÓ Î
+_x0000__x0000_3071042161_x0003__x0000__x0001_$ÇÙ³ÝÂ_x000B__x0000__x0001_Ä³ä¹_x000F_¼ _x0000_Áä¹ÅÅ _x0000_Áä¹ÅÅ_x0010__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_Ç_x0004_Èp¬ _x0000__x0010_Óä¹,_x0000_ _x0000__x0000_³ìÅ_x0008__x0000__x0000_20160825_x000C__x0000__x0000_044-863-8908_x000C__x0000__x0000_044-863-8970_x000F__x0000__x0001_8Á+È¹ÒÄ¼ÇXÎÜÂ _x0000_8Á+È¹ÒÄ¼ÇXÎÜÂ_x0005__x0000__x0000_30102_x001E__x0000__x0001_8Á+È¹ÒÄ¼ÇXÎÜÂ _x0000__x0008_È¬Ç\¸ _x0000_1_x0000_7_x0000_2_x0000_ _x0000_(_x0000_´ÅÄÉÙ³,_x0000_ _x0000_ÜÐ\Õ_x0004_Õ_x0008_¸¤Â&lt;Á0Ñ)_x0000__x0004__x0000__x0001_1_x0000_0_x0000_1_x0000_8Ö_x000D__x0000__x0000_010-7185-8008_x0015__x0000__x0000_dodamsports@naver.com_x000E__x0000__x0000_37690004586437_x0006__x0000__x0000_D00282_x0005__x0000__x0001__x0004_²¬¹¤ÂìÓ Î
+_x0000__x0000_1082124505_x0003__x0000__x0001_@®l×_x0015_È_x0006__x0000__x0001_Áä¹ _x0000_Ä³Áä¹_x000C__x0000__x0001__x0004_ÈÇÁÀp¬·ÅÅ _x0000_0¼Ü´ü»4Ñ _x0000__x000B__x0000__x0000_02-848-6291_x000B__x0000__x0000_02-848-7556
+_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x0001_Æñ´ìÓl­_x0005__x0000__x0000_07375_x000E__x0000__x0001__x001C_Á¸Æ _x0000__x0001_Æñ´ìÓl­ _x0000_Ä³àÂ\¸ _x0000_5_x0000_1_x0000__x000D__x0000__x0001_1_x0000_5Î _x0000_1_x0000_0_x0000_5_x0000_8Ö(_x0000_¡ÁU³L¾)µ)_x0000__x000D__x0000__x0000_010-8393-6291_x0013__x0000__x0000_hee00jung@naver.com_x0008__x0000__x0000_20160905_x000E__x0000__x0000_37690004588737_x0006__x0000__x0000_D00286_x0007__x0000__x0001_Æ%±¤Â _x0000_1Á¨°_x0010_È
+_x0000__x0000_2603001743_x0003__x0000__x0001_MÖ¥Ç8Ö_x0008__x0000__x0001_Ä³ä¹ _x0000__x000F_¼ _x0000_Áä¹ÅÅ_x0008__x0000__x0000_20151218_x000C__x0000__x0000_031-755-7257_x0007__x0000__x0001_½¬0®Ä³ _x0000_1Á¨°ÜÂ_x0005__x0000__x0000_13110_x001E__x0000__x0001_½¬0®Ä³ _x0000_1Á¨°ÜÂ _x0000__x0018_Â_x0015_Èl­ _x0000_1Á¨°_x0000_³\¸ _x0000_1_x0000_2_x0000_6_x0000_7_x0000_ _x0000_-_x0000_1_x0000_ _x0000_(_x0000_ÜÐÉÓÙ³)_x0000__x000D__x0000__x0000_010-7191-7257_x0012__x0000__x0000_nero1016@naver.com_x0002__x0000__x0001_¨°¸Ó_x0008__x0000__x0000_20161109_x000E__x0000__x0000_37690004591037_x0006__x0000__x0000_D00287_x0005__x0000__x0001_¤ÐtÎ¤ÂìÓ Î
+_x0000__x0000_6103752918_x0003__x0000__x0001_@®ÜÐÇ_x0008__x0000__x0000_20161125_x000C__x0000__x0000_052-268-6086_x000C__x0000__x0000_052-272-5908_x0008__x0000__x0001_¸Æ°À_x0011_­íÅÜÂ _x0000_¨°l­_x0005__x0000__x0000_44692_x0016__x0000__x0001_¸Æ°À_x0011_­íÅÜÂ _x0000_¨°l­ _x0000_Ë³ÈÉ\¸ _x0000_1_x0000_2_x0000_4_x0000_ _x0000_ _x0000_(_x0000_ì²Ù³)_x0000__x0003__x0000__x0000_3/2_x000D__x0000__x0000_010-9568-6086_x0014__x0000__x0000_kika5908@hanmail.net_x000E__x0000__x0000_37690004592637_x0006__x0000__x0000_D00292_x0008__x0000__x0001_Æ%±¤Â _x0000_¤ÂìÓÐÆ_x0010_È
+_x0000__x0000_6977800050_x0003__x0000__x0001_\ÕÀ­_x0001_Æ_x0008__x0000__x0000_20170102_x000C__x0000__x0000_051-517-3862_x000C__x0000__x0000_051-583-1023	_x0000__x0001_½°À_x0011_­íÅÜÂ _x0000__x0008_®_x0015_Èl­_x0005__x0000__x0000_46207&amp;_x0000__x0001_½°À_x0011_­íÅÜÂ _x0000__x0008_®_x0015_Èl­ _x0000_´Ì!Çõ¬ÐÆ\¸3_x0000_9_x0000_9_x0000_¼8® _x0000_3_x0000_2_x0000_4_x0000_ _x0000_ _x0000_(_x0000_P´l­Ù³,_x0000_ _x0000_¤ÂìÓÐÆ_x000C_ÓlÐ)_x0000__x0010__x0000__x0001_ÀÉXÕ1_x0000_5Î(_x0000_P´l­Ù³,_x0000_ _x0000_äÂ´°´Ì!Ç_x0000_­)_x0000__x000D__x0000__x0000_010-5505-3862_x0013__x0000__x0000_hgy4285@hanmail.net_x000E__x0000__x0000_37690004595537_x0006__x0000__x0000_D00306_x0007__x0000__x0001_Æ%±¤Â _x0000_ÁÀ4»_x0010_È
+_x0000__x0000_8042300420_x0003__x0000__x0001_@®_x0004_Ö+È_x000D__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_´ÆÙ³©ÆÔ _x0000_¡ÇTÖ_x0008__x0000__x0000_20170119_x000D__x0000__x0000_010-6886-7065_x000C__x0000__x0000_062-374-5410_x0005__x0000__x0000_61970_x0013__x0000__x0001__x0011_­üÈ _x0000__x001C_Ál­ _x0000_ÁÀ4»ü»üÈ\¸3_x0000_2_x0000_¼8® _x0000_3_x0000_-_x0000_5_x0000__x0013__x0000__x0000_sskim-j@hanmail.net_x000E__x0000__x0000_37690004597837_x0006__x0000__x0000_D00308_x0005__x0000__x0001_C_x0000_S_x0000_¤ÂìÓ Î
+_x0000__x0000_2270838785_x0007__x0000__x0001_iÖ_x001C_ÂU³xÆ _x0000_1_x0000_+º_x000C__x0000__x0000_031-385-1222_x000C__x0000__x0000_031-388-3477_x0005__x0000__x0000_13958_x0016__x0000__x0001_½¬0® _x0000_HÅÅÜÂ _x0000_Ì¹HÅl­ _x0000__x0008_Æ Âõ¬ÐÆ\¸5_x0000_2_x0000_¼8® _x0000_2_x0000__x000D__x0000__x0000_010-3176-9037_x0013__x0000__x0000_bill@cssports.co.kr_x000D__x0000__x0000_010-2727-2718_x000F__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_5_x0000_+_x0000_3_x0000_._x0000_5_x0000__x000E__x0000__x0000_37690004598437_x0006__x0000__x0000_D00311
+_x0000__x0001_TÏ¬¹DÅ¤ÂìÓ Î(_x0000_ÜÂe×)_x0000_
+_x0000__x0000_3047001336_x0006__x0000__x0001_TÏ¬¹DÅ¤ÂìÓ Î_x0003__x0000__x0001_\Í_x0001_Æ_x0019_Â_x0012__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000__x0010_Ó	Í&lt;»,_x0000_xÇÄÁ&lt;»,_x0000_0®ÀÐ©ÆÔ_x000D__x0000__x0000_010-2618-5518_x000C__x0000__x0000_031-312-8982_x0007__x0000__x0001_½¬0®Ä³ _x0000_ÜÂe×ÜÂ_x0005__x0000__x0000_14922_x000F__x0000__x0001_½¬0® _x0000_ÜÂe×ÜÂ _x0000_@ÇÄ¬¼_x0001_Æ8® _x0000_2_x0000_7_x0000__x000F__x0000__x0001_3_x0000_0_x0000_3_x0000_8Ö(_x0000_@ÇÕÙ³,_x0000_ _x0000_ÜÂðÒ_x000C_ÓlÐ)_x0000__x0015__x0000__x0000_queenmt5518@naver.com_x000C__x0000__x0000_031-404-6121_x0008__x0000__x0000_20170220_x000E__x0000__x0000_37690004600637_x0006__x0000__x0000_D00312_x000E__x0000__x0001_Æ%±¤Â(_x0000_Y_x0000_O_x0000_N_x0000_E_x0000_X_x0000_)_x0000_ _x0000_tÇÌ_x0010_È
+_x0000__x0000_1052641553_x0003__x0000__x0001_$Ç ÇÄÉ_x000C__x0000__x0000_031-631-2210_x0007__x0000__x0001_½¬0®Ä³ _x0000_tÇÌÜÂ_x0005__x0000__x0000_17362_x0017__x0000__x0001_½¬0®Ä³ _x0000_tÇÌÜÂ _x0000_`Å(¸_x0015_È\¸ _x0000_1_x0000_4_x0000_2_x0000_ _x0000_ _x0000_(_x0000_=Ì_x0004_ÈÙ³)_x0000__x000D__x0000__x0000_010-3459-1313_x0010__x0000__x0000_jin7601@daum.net_x0003__x0000__x0001_\Í_x0015_¬8Ö_x0008__x0000__x0000_20170221_x000E__x0000__x0000_37690004601237_x0006__x0000__x0000_D00324_x0006__x0000__x0001__x000C_Ó¸Ò_x0008_±¤ÂìÓ Î
+_x0000__x0000_1272471368_x0003__x0000__x0001_@®©Æ`Å_x000C__x0000__x0000_031-398-8953_x000C__x0000__x0000_031-398-8954_x0007__x0000__x0001_½¬0®Ä³ _x0000_p­ìÓÜÂ_x0005__x0000__x0000_15833_x0016__x0000__x0001_½¬0®Ä³ _x0000_p­ìÓÜÂ _x0000_$Æ_x0008_®\¸ _x0000_1_x0000_5_x0000_0_x0000_ _x0000_ _x0000_(_x0000__x0008_®_x0015_ÈÙ³)_x0000_	_x0000__x0001_1_x0000_0_x0000_2_x0000_8Ö(_x0000__x0008_®_x0015_ÈÙ³)_x0000__x000D__x0000__x0000_010-4854-8953_x0010__x0000__x0000_kya5767@nate.com_x0008__x0000__x0000_20170320_x000E__x0000__x0000_37690004603537_x0006__x0000__x0000_D00328_x0006__x0000__x0001_ÄÉüÈ0¼Ü´ü»4Ñ
+_x0000__x0000_6131082729_x0003__x0000__x0001__x0015_È Ìä¬_x000C__x0000__x0000_055-747-2101_x0008__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_ÄÉüÈÜÂ_x0005__x0000__x0000_52806_x0019__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_ÄÉüÈÜÂ _x0000_Á-¼\¸7_x0000_5_x0000_¼8® _x0000_8_x0000_ _x0000_ _x0000_(_x0000_ÁÀÉÓÙ³)_x0000__x000D__x0000__x0000_010-9612-2188_x0011__x0000__x0000_jcg2188@naver.com_x000B__x0000__x0000_01095082188_x0008__x0000__x0000_20170324_x000E__x0000__x0000_37690004604137_x0006__x0000__x0000_D00338
+_x0000__x0001_Æ%±¤Â=ÌÐÆ_x0010_È(_x0000_øÂtÎ)_x0000_
+_x0000__x0000_6092352584_x0003__x0000__x0001_HÅ¬Çü­_x0010__x0000__x0001_¤ÂìÓ Î _x0000_XÇX¹ _x0000__x000F_¼ _x0000_©ÆÔ _x0000_È¹lÐ_x001C_ÈÇ_x0008__x0000__x0000_20170411_x000C__x0000__x0000_055-261-0123_x0005__x0000__x0000_51420_x0019__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_=ÌÐÆÜÂ _x0000_1Á°Àl­ _x0000__x0018_¼ÀÉ\¸ _x0000_8_x0000_ _x0000_ _x0000_(_x0000__x0018_¼ÀÉÙ³)_x0000__x0005__x0000__x0001_(_x0000__x0018_¼ÀÉÙ³)_x0000__x000D__x0000__x0000_010-9796-1346_x0011__x0000__x0000_cwssaka@naver.com
+_x0000__x0000_0552610123_x000E__x0000__x0000_37690004606437_x0006__x0000__x0000_D00382_x0004__x0000__x0001_$Æ¤ÂìÓ Î
+_x0000__x0000_2860500614_x0003__x0000__x0001__x0015_¼Á|·_x000C__x0000__x0001__x0004_ÈÇÁÀp¬·(_x0000_¤ÂìÓ Î©ÆÔ)_x0000__x000C__x0000__x0000_063-231-0360_x0005__x0000__x0000_54947_x0015__x0000__x0001__x0004_È½ _x0000__x0004_ÈüÈÜÂ _x0000_DÆ°Àl­ _x0000__x0004_È|·_x0010_¬_x0001_Æ\¸ _x0000_4_x0000_0_x0000_-_x0000_1_x0000__x000B__x0000__x0000_01076785147_x0014__x0000__x0000_sora1976kr@naver.com_x0003__x0000__x0001__x0015_¼Ñ¼%ÆQ_x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_+_x0000_1_x0000_0_x0000_0_x0000_ _x0000_/_x0000_ _x0000_2_x0000_5_x0000_S_x0000_S_x0000_ _x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_ _x0000_+_x0000_ _x0000_1_x0000_0_x0000_0_x0000_ _x0000_/_x0000_ _x0000_ _x0000_2_x0000_4_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_ _x0000_/_x0000_ _x0000_2_x0000_4_x0000_S_x0000_S_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_ _x0000_/_x0000_ _x0000_2_x0000_3_x0000_F_x0000_W_x0000_ _x0000__x0018_ÂüÈ _x0000_ìÅàÂ _x0000_1_x0000_2_x0000__x0008__x0000__x0000_20170710_x000E__x0000__x0000_37690004610337_x0006__x0000__x0000_D00392_x0007__x0000__x0001_¨Ö1Á+ÈiÕ¤ÂìÓ Î
+_x0000__x0000_7521600607_x0002__x0000__x0001_@®_x0004_½_x0008__x0000__x0000_20170812_x000C__x0000__x0000_064-733-2992_x0005__x0000__x0000_63591_x0013__x0000__x0001__x001C_ÈüÈ¹ÒÄ¼ÇXÎÄ³ _x0000__x001C_ÁÀ­ìÓÜÂ _x0000_Ù³8»\¸ _x0000_3_x0000_0_x0000__x000B__x0000__x0000_01090156265_x0010__x0000__x0000_ddadon@naver.com_x000B__x0000__x0000_01036928845_x0008__x0000__x0000_20170821_x000E__x0000__x0000_37690004611037_x0006__x0000__x0000_D00396_x000E__x0000__x0001_Æ%±¤Â _x0000_Å°À_x0010_È(_x0000_TÖ·¤ÂìÓ Î)_x0000_
+_x0000__x0000_6211383962_x0003__x0000__x0001_\ÍiÖðÅ_x0008__x0000__x0000_20170813_x000C__x0000__x0000_055-382-6688_x000C__x0000__x0000_055-366-6648_x0005__x0000__x0000_5</v>
+          </cell>
+          <cell r="T39" t="e">
+            <v>#N/A</v>
           </cell>
           <cell r="U39" t="str">
             <v/>
@@ -4750,8 +6180,8 @@
           <cell r="Y39" t="str">
             <v/>
           </cell>
-          <cell r="Z39" t="str">
-            <v>033-638-0024</v>
+          <cell r="Z39" t="e">
+            <v>#N/A</v>
           </cell>
           <cell r="AA39" t="str">
             <v>N</v>
@@ -4770,11 +6200,11 @@
           </cell>
         </row>
         <row r="40">
-          <cell r="B40" t="str">
-            <v>D00090</v>
-          </cell>
-          <cell r="C40" t="str">
-            <v>주식회사 스매쉬스포츠</v>
+          <cell r="B40" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="C40" t="e">
+            <v>#N/A</v>
           </cell>
           <cell r="D40" t="str">
             <v>사용가능</v>
@@ -4782,14 +6212,14 @@
           <cell r="E40" t="str">
             <v>일반사업자</v>
           </cell>
-          <cell r="F40" t="str">
-            <v>8558703276</v>
-          </cell>
-          <cell r="G40" t="str">
-            <v>스매쉬스포츠</v>
-          </cell>
-          <cell r="H40" t="str">
-            <v>윤규미</v>
+          <cell r="F40" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="G40" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="H40" t="e">
+            <v>#N/A</v>
           </cell>
           <cell r="I40" t="str">
             <v>소매업</v>
@@ -4798,34 +6228,113 @@
             <v>배드민턴용품</v>
           </cell>
           <cell r="K40" t="str">
-            <v>20070917</v>
+            <v>_x000B_　〱㜸ㄵㄱ㤹_x0007_봁ガ쒮₳䠀냅_xDCC0_ׂ_x0000_㔱㤴ሷĀ경기 안산시 상록구 천문4길 17_x001A_㄁㔀㇎㔀㄀㤀ⴀ㄀㌀  ㄀㔀⃎ ꐀ油꓂⃓⃎㰀墻㲹チෑ_x0000_㄰ⴰ㐵ㄷ㌭㌳ጰ_x0000_浳獡⵨㈱䀳慮敶⹲潣୭_x0000_㄰㔰㜴㌱㌳ะ_x0000_㜳㤶〰㐰㠴㜳㜳_x0008_℁㇇Ⴡ⛈㄀　　─؀_x0000_い〰㘹_x0005_ꐁ⃓䗎沼ૐ_x0000_㈱㈷㤰ㄲㄶ_x0003_䀁쒮짉ӓĀ체육용품_x0008_㈀〰〷〵ళ_x0000_㌰ⴱ㌵ⴵ㈱㐴
+　ㄳ㌵㈵㐲ܵĀ경기도 포천시_x0006_㐀㜸㔰ᠰĀ경기도 포천시 군내면 호국로 1696. 2층_x000D_　〱㘭㔳ⴴ㐵ㄷ_x0011_欀灪ㄳ桀湡慭汩渮瑥_x000E_㌀㘷〹〰㐴㜸㌲ط_x0000_い〰㜹_x0005_뤁곂꒹⃓૎_x0000_〲ㄱ㠰㐱㌷_x0003_톬낼ࣆ_x0000_〲㜰㈱ㄲ_x000C_　ⴲ㈲㤷〭㜷ਹ_x0000_㈰㈲㠷㜰㠷_x0005_　㔴㌶_x001E_ᰁ룁맆쓒_xDCBC_⃂ᄀ泉₭관쓌鲬峌₸㈀㐀㘀  ⠀⤀낼_xD9C0_ⲳ 준哓_xDCD6_ꗂ⧇ᘀĀ1,2,3층 다-102(방산동,평화시장)_x000D_　〱㌭㠲ⴴ㌷㌸_x0019_瘀捩潴祲灳牯獴桀湡慭汩渮瑥_x000E_㌀㘷〹〰㐴㠸㌹ط_x0000_い㄰㄰_x0005_䐁냅꓀⃓૎_x0000_ㄳ㈲㜸㤲㈸_x0003_封藍볈ಹĀ도매및상품중개업,소매업_x0008_㈀㄰〱〷ఱ_x0000_㐰ⴱ㌵ⴲ㌸ㄸ
+　ㄴ㌵㠲㠳࠲Ā충청남도 아산시_x0006_㌀㘳㔰ူĀ충청남도 아산시 시민로 251_x000D_　〱㐭㐹ⴶ㌸㔸_x0013_樀摵捯汪桀湡慭汩渮瑥_x000E_㌀㘷〹〰㐴〹㌵ط_x0000_い㄰㤰_x0008_ā꓆⃓⣎ꠀ킰⧆਀_x0000_〱㔹㠲ㄹㄳ_x0003_琁ᗇ鳈࣌_x0000_〲㜰ㄱ㤱_x000C_　㌶㘭㈳㐭㔱਴_x0000_㘰㘳㈳ㄴ㘵_x0005_㔀㜵㌰_x0015_Ё糈膷쒽₳ꠀ킰_xDCC6_⃂가璹₺_x0000_겳峀₸㄀㈀㠀㌀ЀĀ영스포츠_x000D_　〱㐭㤵ⴴ㘰㐳_x0013_樀汣敥㜸㐳湀癡牥挮浯_x000E_㌀㘷〹〰㐴㜹㌰ط_x0000_い㄰〱_x0007_鐁◆꒱⃂吀᳖Ⴢૈ_x0000_〴〸㜵〷㔸_x0003_Ё藈ᦺࣂ_x0000_〲㜰ㄱ㈰_x000C_　ㄶ㌭㔷㘭㐶࠷Ā전라남도 화순군_x0006_㔀㤱〸ᐹĀ전라남도 화순군 광덕로 140  1층_x000D_　〱㘭㌶ⴲ㠵㌹_x0012_洀⵳潪䁮慨浮楥⹬敮๴_x0000_㜳㤶〰㐰㤴㘸㜳_x0006_䐀〰ㄱఱĀ올림픽종합스포츠(목포)
+㐀ㄱ㐱㤶㠴̶Ā김창용_x000C_됁_xD9C6_꦳裆Ⳕ내泀ⲭ　傮袱ࣔ_x0000_〲㜰㌰〲_x000C_　ㄶ㈭㈴ㄭ㌰ਲ_x0000_㘰㈱㐴〳㈳_x0008_Ё糈ꢷ쒰₳꤀_xDCD3_ׂ_x0000_㠵㈷ံĀ전남 목포시 차범석길 41-1_x0002_㄁㔀෎_x0000_㄰ⴰ㈹㌴㐭㠲ဵ_x0000_祥扥湯䁯慤浵渮瑥_x000E_㌀㘷〹〰㐴㤹㌲ط_x0000_い㄰㘱_x000F_鐁◆꒱죂낹À겳Ⴙ⣈ﰀ㒻ꓑ⃓⧎਀_x0000_〶〸㠲〸㜲_x0003_ ǇᧆࣂĀ스포츠용품및의류_x000C_　㔵㈭㈲㔭㌴਱_x0000_㔰㈵㈲㐵㈳_x0008_봁솬ꣀ쒰₳㴀탌_xDCC6_ۂ_x0000_㌶㠱㈵_x0018_봁솬ꣀ쒰₳㴀탌_xDCC6_⃂저낹槀泓₭꤀죆岹₸㜀㘀 ﰀ_xDDC8_ැ_x0000_㄰ⴰ㜳㜰㘭㐲ᘵ_x0000_畤瑤獪㈶㔴桀湡慭汩渮瑥_x000E_㌀㘷〹〰㔴㐰㌳ط_x0000_い㄰〲_x0006_鐁◆꒱귂ﳌ჈ૈ_x0000_ㄳ〷㠳㠵㐵_x0003_封냍㇆ுĀ스포츠용품,의류,수건_x0008_㈀㄰〱㈷హ_x0000_㐰ⴳ㈲ⴲ〳〴
+　㌴㈲㔴㔰࠰Ā충청북도 청주시_x0006_㌀ㄶ㐸ሲĀ충북 청주시 상당구 호미로 206_x0005_㄁㔀⃎谀⇈෎_x0000_㄰ⴰ㐵㠶㌭ㄳᔹ_x0000_獷湵㍧㈵䀵慨浮楡⹬敮ࡴ_x0000_〲㠰㐰㤲_x000E_㌀㘷〹〰㔴㜰㌲ط_x0000_い㄰ㄲ_x000D_鐁◆꒱淓ვ⣈堀瓕泇곐뒹⧅਀_x0000_〵ㄶ㌷㈶㘴_x0003_ᔁ䃈Ǉࣆ_x0000_〲㤰㈰㜲_x000C_　㐵㈭㌸㔭㌲਴_x0000_㔰㈴㌸㈵ㄳ_x0008_봁솬臀쒽₳淓_xDCD5_ۂ_x0000_㤷㠰㈲_x0012_봁膬₽淓_xDCD5_⃂ꠀ沰₭_x0000_쒳_xD9B3_₳㠀㘀ⴀ㈀ഀ_x0000_㄰ⴰㄴ㌳㜭㜷ᐰ_x0000_業瑮湯ㄱ㔲湀癡牥挮浯_x0008_㈀〰ㄸ〱ี_x0000_㜳㤶〰㐰〵㤸㜳_x0006_䐀〰㈱ԲĀ우리스포츠
+㐀㜱ㄲ㔰㤴̳Ā박수진_x0008_㈀㄰〸〱ఱ_x0000_㔰ⴱ㌶ⴲ㘲ㄸ
+　ㄵ㌶㈲㠶࠱Ā부산광역시 남구_x0006_㘀㠰㈸ᄷĀ부산광역시 남구 자유평화로 49_x000D_　〱㈭㤵ⴴ㘲㈸_x0015_洀硯敩〲〰桀湡慭汩渮瑥_x000E_㌀㘷〹〰㔴㤰㌵ط_x0000_い㄰㌲_x0005_뀁㇆꓁⃓૎_x0000_〲㜷〰㜳㠰_x0003_䀁䒮_xDDC6_ࣂ_x0000_〲㜰〱㤰_x000B_　ⴲ㘴ⴵ㈱㜹	　㐲㔶ㄱ㜹	ᰁ룁맆쓒_xDCBC_⃂ᄀ쒭泉ڭ_x0000_㐱㤳ㄶ_x0010_ᰁ룁맆쓒_xDCBC_⃂ᄀ쒭泉₭氀墭峇₸㘀㘀᐀Ā1층 (구의동 227-6) 우성스포츠_x000D_　〱㌭ㄴⴸ㈱〳_x000F_眀㑳㠱湀癡牥挮浯_x000E_㌀㘷〹〰㔴〱㌵ط_x0000_い㄰㘲_x0005_퀁_xD9C6_뒳⇌곇ી_x0000_〳〶㘳㜳㠴_x0003_ﰁ톻솼ӉĀ운동기구_x0008_㈀〰〵〷వ_x0000_㐰ⴲ㌵ⴱ〴㐰
+　㈴㌵㠲㤸࠹Ā대전광역시 동구_x0005_㌀㘴〳_x000D__x0001_ҳ⃈_xD900_河₭_x0000_ҳ峈₸㜀㘀㔀ഀ_x0000_㄰ⴰ㐵㌵㤭㌵ሶ_x0000_潷獮潰桀湡慭汩渮瑥_x0008_㈀〰〸ㄲิ_x0000_㜳㤶〰㐰ㄵㄱ㜳_x0006_䐀〰㈱࠷Ā원스포츠(제주)
+㘀㘱㤰㈶㔰̱Ā김미경_x000C_　㐶㜭㈵㐭㈴ਲ_x0000_㘰㜴㌲㤲㈹_x000C_ᰁﳈ마쓒邼壇쓎₳ᰀ상_xDCD3_ۂ_x0000_㤶㄰ㄶ_x0013_ᰁﳈ마쓒邼壇쓎₳ᰀﳈ_xDCC8_⃂␀糆岷₸㄀㌀㐀ഀ_x0000_㄰ⴰ㐴㘱㐭ㄴᔲ_x0000_牣湯べ〱䀴慨浮楡⹬敮๴_x0000_㜳㤶〰㐰ㄵ㠲㜳_x0006_䐀〰㌱ԲĀ전주요넥스
+㐀㈰㠰㜸㠸̷Ā이순종_x000C_　㌶㈭㐷㤭㌳਷_x0000_㘰㈳㠷㌹㜳_x0008_Ё糈膷쒽₳Ѐﳈ_xDCC8_ۂ_x0000_㘵〰〸_x0013_Ё糈膷쒽₳Ѐﳈ_xDCC8_⃂䐀냆泀₭膬岽₸㈀　ഀ_x0000_㄰ⴰ㈹㐲㠭㤳ေ_x0000_祪湯硥湀癡牥挮浯_x000E_㌀㘷〹〰㔴㘱㌳ط_x0000_い㄰㘳_x0005_ᰁ糈꓇⃓૎_x0000_〴〴㌵㔳㈴_x000B_ᰁ糈ࣇ¸꓈⃓⣎ᔀ䷈⧇̀Ā김광복	됁_xD9C6_コ沮ྭ뒼_xD9C6_碼ೆ_x0000_㘰ⴳ㌵ⴵㄹ㘴
+　㌶㌵㈳㤰࠳Ā전라북도 정읍시_x0006_㔀〸〸༴Ā전라북도 정읍시 중앙로 83_x000D_　〱㤭㜵ⴹ㠷〰_x0016_猀潰瑲㥳㐱䀶慨浮䥡⹬敮๴_x0000_㜳㤶〰㐰㈵㈰㜳_x0006_䐀〰㌱ଷĀ주식회사 배드민턴마트
+㄀〱ㄸ㌹〲̳Ā정이녀_x000B_ꐁ⃓꧎裆⃔Ѐ郈쇇烀颬ࢷ_x0000_〲㌱㜰㌲_x000C_　ㄳ㤭㐶㌭㌵र_x0000_㈰㠳㤲㔵ܵĀ경기도 고양시_x0005_㄀㔰㐶_x0011_봁ガ₮醬_xDCC5_⃂唀醳泅₭밀ꇀ峁₸㄀㈀܀Ā4층 418호_x000D_　〱㜭㔱ⴲ㔷㠳_x0014_洀湩潴浮牡䁴慮敶⹲潣๭_x0000_㜳㤶〰㐰㈵㤱㜳_x0006_䐀〰㌱सĀ주식회사동우스포츠
+㄀〱ㄸ〸㈴̶Ā송정일_x000B_　ⴲ㠳ⴲ㔳㠹	　㌲㔵㔳㘸	ᰁ룁맆쓒_xDCBC_⃂䀀짇泓ڭ_x0000_㈱㤲㌰_x0018_ᰁ룁맆쓒_xDCBC_⃂䀀짇泓₭᳅峁₸㈀㤀ⴀ㄀ _xD900_낳꓆⃓෎_x0000_㄰ⴰ〲㠱㌭㤵ሸ_x0000_癤灩㈱㌳湀癡牥挮浯_x000B_　〱㐷㔳㔳㠹
+᠁ࣂ₮耀熽㳈峇₸딀່᳑_x0000_㜳㤶〰㐰㈵㔲㜳_x0006_䐀〰㐱ऱĀ중앙스포츠(경주)
+㌀㈲㘶〰㈳̳Ā황영실_x0008_㈀〰ㄸㄲర_x0000_㔰ⴴ㐷ⴱㄵ㜷_x0008_봁솬臀쒽₳봀ﲬ_xDCC8_ۂ_x0000_㠷㤰㌴_x0012_봁솬臀쒽₳봀ﲬ_xDCC8_⃂ࠀㆮ峁₸㈀㤀㐀ⴀ㄀ഀ_x0000_㄰ⴰ㔷㤷㔭㜱ᐷ_x0000_慪灳㌶㐰桀湡慭汩渮瑥_x0008_㈀〰ㄸㄲั_x0000_㜳㤶〰㐰㈵㐵㜳_x0006_䐀〰㐱ԵĀ청룡스포츠
+㘀㔱㜰㘹〳̷Ā조미숙_x0008_㈀㄰㄰〰ఴ_x0000_㔰ⴵㄳⴲ㔹㤵
+　㔵ㄳ㤲㘵࠰Ā경상남도 김해시_x0006_㘀ㄲ㌸ሳĀ경상남도 김해시 장유로 297-5_x000D_　〱㤭ㄵⴳ㔹㤵_x0016_樀獭ㄳ㤲㔵䀹慨浮楡⹬敮ࡴ_x0000_〲〱〱㤱_x000E_㌀㘷〹〰㔴〳㌰ط_x0000_い㄰㠴_x0007__x0001_瓏擇䓅꒾⃓૎_x0000_㈱㈳㠴〱㠶_x0003_ᔁ薼邺ೇ_x0000_㌰ⴱ㔴ⴷ㜸㘰
+　ㄳ㔴㠷〷ܷĀ경기도 안양시_x0006_㐀ㄳ㌸ሷĀ경기도 안양시 동안구 귀인로 89_x000D_　〱㜭㌳ⴸ㌷㔷_x0016_樀浡慪楬〲䀰慨浮楡⹬敮๴_x0000_㜳㤶〰㐰㌵㈲㜳_x0006_䐀〰㐱हĀ코리아오픈(김천)
+㔀〱㄰㜴㈳̴Ā박선영_x0008_㈀〰〷㈴ళ_x0000_㔰ⴴ㌴ⴰ〷㜰
+　㐵㌴㜰〰࠷Ā경상북도 김천시_x0005_㌀㘹㘲_x000E_봁膬₽䀀鲮_xDCCC_⃂ꄀⓁ峁₸㄀㘀㐀ഀ_x0000_㄰ⴰㄴ㔱㘭〳ጶ_x0000_橪〱㔶䀴慨浮楡⹬敮๴_x0000_㜳㤶〰㐰㌵㤳㜳_x0006_䐀〰㔱԰Ā팔구스포츠
+㔀㈰㄰㌵〲̴Ā신상규_x0008_㈀〰〸㌳ఱ_x0000_㔰ⴳ㔹ⴷ㤸㤸
+　㌵㐹㈳㐳࠵Ā대구광역시 동구_x0005_㐀ㄱ㌹_x000F__x0001_河₭_xD900_河₭䐀釅峅ㆸ㄀㠀₮㠀㄀ࠀĀ1층 팔구스포츠_x000D_　〱㠭㔸ⴴ㤸㤸_x0012_㠀猹潰瑲䁳慮敶⹲潣๭_x0000_㜳㤶〰㐰㌵㔴㜳_x0006_䐀〰㔱ԹĀ혜성스포츠
+㄀〳㔰ㄳ㠰̹Ā이의선_x000D_ꐁ⃓꧎裆Ⳕ_x0000_Ҭ᳈裈Ⳕꄀ哇ࣖ_x0000_〲㜰㔰㤲_x000C_　㈳㘭㐵㈭㌱ਲ਼_x0000_㌰㘲㐵ㄲ㈳_x0007_봁ガ쒮₳耀鲽_xDCCC_ۂ_x0000_㈴㠲㤱 봁ガ쒮₳耀鲽_xDCCC_⃂谀곁泀₭봀碬峇ㆸ㈀　蠀㢼₮㈀㠀  ㄀㔀჎⃓㄀砀෎_x0000_㄰ⴰ㔷㠷㜭㐷ᔰ_x0000_獨ㄷ㜶㐷䀱慨浮楡⹬敮๴_x0000_㜳㤶〰㐰㐵㌱㜳_x0006_䐀〰㘱԰Ā호동스포츠
+㄀㐲㤳㤱㐰̷Ā김호동_x0008_㈀㄰〰ㄱళ_x0000_㌰ⴱ㜳ⴵ㌰ㄳ
+　ㄳ㜳〵㌳ܱĀ경기도 오산시_x0006_㐀㜴〸ᨲĀ경기도 오산시 성호대로 25 운산빌딩  1층 4_x000D_　〱㔭㤲ⴵ㈸㠷_x0013_欀摨㤹㈸桀湡慭汩渮瑥_x000E_㌀㘷〹〰㔴㈴㌰ط_x0000_い㄰ㄶ_x0005_䴁㇖铁◆꒱ૂ_x0000_ㄳ〰㐶㔰㠱_x0003_䀁Үᗖࣈ_x0000_〲㤰㘰㘱_x000C_　ㄴ㘭㐳㜭㈳࠷Ā충청남도 홍성군_x0005_㌀㈲㌶_x0012_꤁꣍₰䴀㇖烁₭䴀臖䶽⃇꤀꣍°岳₸㌀㘀ᔀĀ제 1층 제 101호(빌앤더스오피스텔)_x000D_　〱㠭㈶ⴶ㠹㔲_x0010_栀楪㈹䀳慮敶⹲潣๭_x0000_㜳㤶〰㐰㐵㘳㜳_x0006_䐀〰㘱శĀ(주)티제이디스트리뷰션
+㈀ㄱ㜸㈳ㄵ̶Ā송상원_x0006_쐁貳₹쐀ࢹĀ스포츠용품 무역_x0008_㈀㄰〲ㄹ଱_x0000_㈰㔭ㄱ㔭ㄱऴĀ서울특별시 강남구_x0006_㄀㔳㄰ରĀ서울특별시강남구논현동_x000E_ࠁ䂮䳇⦾₵㄀㔀⃎ꀀ꒼룂ꓒꃂ듑ළ_x0000_㄰ⴰ㜸㐸ㄭ㔶ᔱ_x0000_敢瑳硥牴浥䁥慮敶⹲潣m_x0007__x0000__x0001_B_x0000_ñ´	®(_x0000_T_x0000_S_x0000_)_x0000__x0005__x0000__x0000_14049_x0003__x0000__x0001__x0015_¼_x0004_ÖÄÉ_x0008__x0000__x0000_20190917_x0006__x0000__x0000_D00167_x0008__x0000__x0001_üÈÝÂÖ¬À _x0000_ÐÆÐÅÇ
+_x0000__x0000_1268800066_x0003__x0000__x0001_@®DÕ¹Â_x0006__x0000__x0001_Ä³Áä¹ÅÅ _x0000_xÆ_x0007__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_xÆ_x000C__x0000__x0000_02-1644-1662	_x0000__x0001_½°À_x0011_­íÅÜÂ _x0000__x0018_Â_x0001_Æl­_x0006__x0000__x0000_613815_x0013__x0000__x0001_½°À_x0011_­íÅÜÂ _x0000__x0018_Â_x0001_Æl­ _x0000__x0011_­¨°\¸ _x0000_6_x0000_3_x0000_ _x0000_B_x0000_Ù³_x0004__x0000__x0001_4_x0000_5Î|Ç½_x000D__x0000__x0000_010-8882-4137_x0014__x0000__x0000_oneeight@hanmail.net_x0006__x0000__x0000_D00173_x0005__x0000__x0001__x0008_®_x0001_Æ¤ÂìÓ Î
+_x0000__x0000_1052087391_x0003__x0000__x0001_°ÆÀÉÐÆ_x0008__x0000__x0000_20140217_x000D__x0000__x0000_010-6208-8112_x0006__x0000__x0000_121889_x0013__x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_È¹ìÓl­ _x0000_Ù³P­\¸3_x0000_8® _x0000_1_x0000_2_x0000_5_x0000__x0013__x0000__x0000_yonex0901@naver.com_x0008__x0000__x0000_20150122_x000E__x0000__x0000_37690004557937_x0006__x0000__x0000_D00181_x0004__x0000__x0001__x0000_É¤ÂìÓ Î
+_x0000__x0000_1410240836_x0003__x0000__x0001__x0015_¼½¬·_x0008__x0000__x0000_20140825_x000C__x0000__x0000_031-945-2007_x0007__x0000__x0001_½¬0®Ä³ _x0000__x000C_ÓüÈÜÂ_x0006__x0000__x0000_413819$_x0000__x0001_½¬0®Ä³ _x0000__x000C_ÓüÈÜÂ _x0000_DÅ¬¹·\¸ _x0000_5_x0000_5_x0000_ _x0000_-_x0000_8_x0000_1_x0000_ _x0000_(_x0000__x0008_®_x000C_ÍÙ³,_x0000_ _x0000__x000C_ÓüÈ_x0008_®_x000C_ÍXÕ_x0018_ÂÌ¬¹¥Ç)_x0000__x000C__x0000__x0001__x000C_ÓüÈÜÂ _x0000_0¼Ü´ü»4Ñ_x0004_È©Æl­¥Ç_x000D__x0000__x0000_010-9129-1126_x0017__x0000__x0000_leesjun1024@hanmail.net_x000E__x0000__x0000_37690004547137_x0006__x0000__x0000_D00183_x0003__x0000__x0001_T³_x001C_È|Ç
+_x0000__x0000_1171558537_x0003__x0000__x0001_iÖÐÆ Á_x000B__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_XÇX¹,_x0000_¡ÇTÖ_x0008__x0000__x0000_20141027_x000D__x0000__x0000_010-6333-2457	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_ÅÌl­_x0005__x0000__x0000_08078 _x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_ÅÌl­ _x0000_àÂ_x0015_È\¸ _x0000_2_x0000_7_x0000_5_x0000_ _x0000_ _x0000_(_x0000_àÂ_x0015_ÈÙ³,_x0000_ _x0000_àÂ¸Ò¬¹DÅ_x000C_Ó¸Ò)_x0000__x0010__x0000__x0001_ÁÀ_x0000_¬Ù³ _x0000_1_x0000_5Î _x0000_1_x0000_0_x0000_4_x0000_,_x0000_ _x0000_1_x0000_0_x0000_5_x0000_8Ö_x0011__x0000__x0000_thejeil@naver.com_x000D__x0000__x0000_010-9668-2210_x000E__x0000__x0000_37690004550437_x0006__x0000__x0000_D00184_x0005__x0000__x0001_$Æ¨°¤ÂìÓ Î
+_x0000__x0000_1322489384_x0003__x0000__x0001_Å+È¨º_x000D__x0000__x0001_´ÆÙ³0®l­©ÆÔ _x0000_aÅ8Á_x001C_Á¬¹ _x0000_xÆ_x0008__x0000__x0000_20141028
+_x0000__x0000_0315756464
+_x0000__x0000_0315755600_x0008__x0000__x0001_½¬0®Ä³ _x0000_¨°ÅüÈÜÂ_x0006__x0000__x0000_472881_x0016__x0000__x0001_½¬0®Ä³ _x0000_¨°ÅüÈÜÂ _x0000_ÄÉt¬$Æ¨°\¸ _x0000_8_x0000_0_x0000_6_x0000_ _x0000_-_x0000_1_x0000_4_x0000__x000D__x0000__x0000_010-9289-9637_x0012__x0000__x0000_jongmo83@naver.com_x000E__x0000__x0000_37690004552737_x0006__x0000__x0000_D00186_x0005__x0000__x0001_ä¹XÎìÓxÇ¸Ò
+_x0000__x0000_6091853217_x0003__x0000__x0001_iÖ­ÝÂ_x0008__x0000__x0000_20141202_x000C__x0000__x0000_055-298-7330_x0005__x0000__x0000_51378_x0011__x0000__x0001_½¬¨° _x0000_=ÌÐÆÜÂ _x0000_XÇ=Ìl­ _x0000__x0018_¼Ä¬\¸ _x0000_6_x0000_3_x0000__x000D__x0000__x0000_010-3561-0209_x000E__x0000__x0000_o2bbi@nate.com_x0008__x0000__x0000_20141212_x000E__x0000__x0000_37690004554037_x0006__x0000__x0000_D00190_x0005__x0000__x0001_p­°À¤ÂìÓ Î
+_x0000__x0000_4010657765_x0003__x0000__x0001__x0015_¼_x001C_Âl×	_x0000__x0001_¤ÂìÓ ÎXÇX¹,_x0000_ _x0000_©ÆÔ_x0008__x0000__x0000_20150406_x000D__x0000__x0000_010-9977-7141_x0008__x0000__x0001__x0004_È|·½Ä³ _x0000_p­°ÀÜÂ_x0005__x0000__x0000_54102_x000F__x0000__x0001__x0004_È½ _x0000_p­°ÀÜÂ _x0000_¨°_x0018_Â¡Á5_x0000_8® _x0000_4_x0000_2_x0000__x000F__x0000__x0001_1_x0000_0_x0000_1_x0000_8Ö(_x0000__x0018_Â¡ÁÙ³,_x0000_ _x0000_(Ì$Æ¹L¾)_x0000__x0013__x0000__x0000_shp7141@hanmaiL.net_x000E__x0000__x0000_37690004558537_x0006__x0000__x0000_D00192
+_x0000__x0001__x0001_Æ8»¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1222039517_x0005__x0000__x0001__x0001_Æ8»¤ÂìÓ Î_x0003__x0000__x0001_@®_x0001_Æ8»_x0008__x0000__x0000_20150608_x000C__x0000__x0000_032-523-1406_x000C__x0000__x0000_032-517-8009	_x0000__x0001_xÇÌ_x0011_­íÅÜÂ _x0000_½ÉÓl­_x0005__x0000__x0000_21337_x000D__x0000__x0000_010-4320-1406_x0012__x0000__x0000_YM1406@hanmail.net_x0007__x0000__x0001_A_x0000_ñ´	®(_x0000_T_x0000_S_x0000_)_x0000__x0005__x0000__x0000_13042_x0003__x0000__x0001_@®Ù³½¬_x000E__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_+_x0000_3_x0000_0_x0000__x000E__x0000__x0000_37690004561837_x0006__x0000__x0000_D00193_x000B__x0000__x0001_ÑÐ¤Â@Õ¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1320972497_x0006__x0000__x0001_ÑÐ¤Â@Õ¤ÂìÓ Î_x0003__x0000__x0001__x0015_¼_x0004_Ö=Ì_x0006__x0000__x0001_´ÆÙ³_x0004_È8»©ÆÔ_x0008__x0000__x0000_20150610_x000D__x0000__x0000_010-3706-2477_x0007__x0000__x0001_½¬0®Ä³ _x0000_l­¬¹ÜÂ_x0005__x0000__x0000_11907_x000F__x0000__x0001_½¬0® _x0000_l­¬¹ÜÂ _x0000_UÆ_x0019_ÂÌ\¸ _x0000_5_x0000_0_x0000_7_x0000_	_x0000__x0001_3_x0000_5Î _x0000_ÑÐ¤Â@Õ¤ÂìÓ Î_x000F__x0000__x0000_pspin@naver.com_x0005__x0000__x0000_22022_x0003__x0000__x0001_HÅ°ÆÄÉ_x000C__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_7_x0000_._x0000_5_x0000__x000E__x0000__x0000_37690004560137_x0006__x0000__x0000_D00195
+_x0000__x0001_¤ÂìÓ ÎLÑlÐ(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_6172249744_x0005__x0000__x0001_¤ÂìÓ ÎLÑlÐ_x0003__x0000__x0001_tÇÝÐ0®_x0006__x0000__x0001__x001C_ÈpÈÅÅ _x0000_Áä¹_x000C__x0000__x0001_õ¬_x0008_Æ _x0000_¤ÂìÓ Î©ÆÔ,_x0000_ _x0000_¡ÇTÖ_x000B__x0000__x0000_051-7564800_x000C__x0000__x0000_051-756-4801_x0005__x0000__x0000_48222_x0017__x0000__x0001_½°À_x0011_­íÅÜÂ _x0000_Ù³·l­ _x0000_+ÈiÕ´ÆÙ³¥Ç\¸ _x0000_4_x0000_0_x0000_¼8® _x0000_8_x0000_'_x0000__x0001_1_x0000_0_x0000_3_x0000_Ù³ _x0000_1_x0000_0_x0000_5_x0000_8Ö,_x0000_1_x0000_0_x0000_6_x0000_8Ö(_x0000_¬ÀÁÉÙ³,_x0000_½°À _x0000_DÅÜÂDÅÜ´ _x0000_TÏ$Æq¸ _x0000_XÕ²DÌ _x0000_DÅ_x000C_Ó¸Ò)_x0000__x000D__x0000__x0000_010-5578-1988_x0015__x0000__x0000_ltktennis@hanmail.net_x000B__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_8_x0000__x0008__x0000__x0000_20150611_x000E__x0000__x0000_37690004562437_x0006__x0000__x0000_D00196	_x0000__x0001__x0015_¬¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_5041920932_x0004__x0000__x0001__x0015_¬¤ÂìÓ Î_x0003__x0000__x0001__x0015_¬@Çl­_x000D__x0000__x0001_LÑÈ²¤Â©ÆÔ,_x0000_ _x0000_XÇX¹,_x0000_ _x0000_àÂ_x001C_¼_x000C__x0000__x0000_053-314-9090_x0005__x0000__x0000_41433_x000D__x0000__x0000_010-3828-0474_x0013__x0000__x0000_keg0417@hanmail.net_x000D__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_6_x0000_+_x0000_1_x0000_5_x0000__x0008__x0000__x0000_20150612_x000E__x0000__x0000_37690004565337_x0006__x0000__x0000_D00199
+_x0000__x0001_P´¬¹¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1283008985_x0003__x0000__x0001_@®_x0001_Æ Á_x000B__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_¤ÂìÓ ÎXÇX¹_x0008__x0000__x0000_20150703_x000C__x0000__x0000_031-911-4191_x000C__x0000__x0000_031-913-0067_x0006__x0000__x0000_410829_x000F__x0000__x0001_½¬0®Ä³à¬ÅÜÂ _x0000_|Ç°ÀÙ³l­_x0015_È_x001C_¼°ÀÙ³_x000E__x0000__x0001_1_x0000_1_x0000_4_x0000_8_x0000_-_x0000_1_x0000_3_x0000_ _x0000_1_x0000_5Î2_x0000_,_x0000_3_x0000_8Ö_x000D__x0000__x0000_010-4288-3563_x0012__x0000__x0000_usop2n@hanmail.net_x000D__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_6_x0000_+_x0000_2_x0000_3_x0000__x000E__x0000__x0000_37690004568237_x0006__x0000__x0000_D00201_x000E__x0000__x0001_(_x0000_üÈ)_x0000_¤ÂtÎtÇ¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_6278102573_x000B__x0000__x0001_¤ÂtÎtÇ¤ÂìÓ Î(_x0000_LÑÈ²¤Â)_x0000__x0003__x0000__x0001_@®1ÁÐÆ_x0006__x0000__x0001_Áä¹ÅÅ _x0000_Ä³ä¹_x0008__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_ä¹_x0010_È_x000C__x0000__x0000_041-566-1879_x000C__x0000__x0000_041-554-2732_x0005__x0000__x0000_31157"_x0000__x0001_©Í­Ì¨°Ä³ _x0000_ÌHÅÜÂ _x0000__x001C_Á½l­ _x0000_1¼_x001D_Á3_x0000_\¸ _x0000_2_x0000_9_x0000_ _x0000_ _x0000_(_x0000_1¼_x001D_ÁÙ³,_x0000_ _x0000_½¶É¹_x0008_Ã%¼)_x0000__x000D__x0000__x0000_010-4513-1879_x0011__x0000__x0000_kimsw000@nate.com_x000E__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_4_x0000_0_x0000_+_x0000_2_x0000_0_x0000__x0008__x0000__x0000_20150804_x000E__x0000__x0000_37690004570937_x0006__x0000__x0000_D00202_x0008__x0000__x0001_¤ÂìÓå²(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_3052275067_x0003__x0000__x0001_HÅü­¹Â_x000C__x0000__x0000_042-522-9566_x000C__x0000__x0000_042-271-4786_x0006__x0000__x0000_300810_x0017__x0000__x0001__x0000_³_x0004_È_x0011_­íÅÜÂ _x0000__x0011_Él­ _x0000_Ù³_x001C_Á_x0000_³\¸ _x0000_1_x0000_2_x0000_0_x0000_1_x0000_(_x0000_ÜÐÉÓÙ³)_x0000__x0007__x0000__x0001_¤ÂìÓå² _x0000_ÜÐÉÓ_x0010_È_x000B__x0000__x0000_01062224787_x0010__x0000__x0000_spodaq@naver.com_x000D__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_5_x0000_+_x0000_3_x0000_3_x0000__x0008__x0000__x0000_20150805_x000E__x0000__x0000_37690004571537_x0006__x0000__x0000_D00203	_x0000__x0001_ðÅTÏ¬¹DÅ(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_2041477980_x0004__x0000__x0001_ðÅTÏ¬¹DÅ_x0003__x0000__x0001_@®ÁÀ0®_x0006__x0000__x0001_Ä³Áä¹ _x0000_t¬$Á_x000D__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_´Ì!ÇÜÂ_x001C_Á&lt;»$ÁXÎ_x0008__x0000__x0000_20150806_x000C__x0000__x0000_02-3390-4345_x000C__x0000__x0000_02-3390-4344
+_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000_Ù³_x0000_³8»l­_x0005__x0000__x0000_02496_x0011__x0000__x0001__x001C_Á¸Æ _x0000_Ù³_x0000_³8»l­ _x0000_Ý¹°Æ\¸1_x0000_2_x0000_8® _x0000_1_x0000_9_x0000__x000B__x0000__x0001_1_x0000_5Î _x0000_XÕtÇÐÆ¤ÂìÓ Î°ÀÅÅ_x000D__x0000__x0000_010-9089-5363_x0017__x0000__x0000_01090895363@hanmail.net_x000B__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_2_x0000_0_x0000__x000E__x0000__x0000_37690004572137_x0006__x0000__x0000_D00205_x0005__x0000__x0001_ÁLÑ¤ÂìÓ Î
+_x0000__x0000_1971301851_x0003__x0000__x0001_@®_x0001_Æ_x0018_Â_x0008__x0000__x0001_Ä³Áä¹ÅÅ _x0000_Ä³ä¹ÅÅ	_x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_4»íÅÅÅ_x000B__x0000__x0000_01063388568_x0008__x0000__x0001_½¬0®Ä³ _x0000_XÇ_x0015_È½ÜÂ_x0005__x0000__x0000_11806!_x0000__x0001_½¬0®Ä³ _x0000_XÇ_x0015_È½ÜÂ _x0000_$Æ©º\¸ _x0000_1_x0000_7_x0000_0_x0000_ _x0000_°Àä´È¹DÇ _x0000_DÅ_x000C_Ó¸Ò _x0000_4_x0000_1_x0000_2_x0000_-_x0000_7_x0000_0_x0000_6_x0000__x000D__x0000__x0000_010-6338-8568_x0011__x0000__x0000_3388568@naver.com_x0005__x0000__x0000_26002_x0003__x0000__x0001__x0015_¬ÜÐ8Ö_x0008__x0000__x0000_20220901_x000E__x0000__x0000_37690004700437_x0006__x0000__x0000_D00209_x0018__x0000__x0001_¤ÂìÓ Î_x000C_Õì·¤Â(_x0000_S_x0000_p_x0000_o_x0000_r_x0000_t_x0000_s_x0000_ _x0000_P_x0000_l_x0000_u_x0000_s_x0000_)_x0000_(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1192167071_x0003__x0000__x0001__x0015_¬ÜÂ¨º_x0006__x0000__x0001_Ä³Áä¹ _x0000_LÇÝÂ_x0008__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_\ÕÝÂ_x000B__x0000__x0000_02-871-5513	_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x0000_­EÅl­_x0005__x0000__x0000_08750_x000F__x0000__x0001__x001C_Á¸Æ _x0000__x0000_­EÅl­ _x0000_àÂ¼¹\¸3_x0000_8® _x0000_4_x0000_0_x0000__x0005__x0000__x0001_ÀÉXÕ _x0000_1_x0000_5Î_x000D__x0000__x0000_010-7703-5353_x001A__x0000__x0000_tennisplus0122@esero.go.krX_x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_ _x0000_/_x0000_ _x0000_2_x0000_5_x0000_S_x0000_S_x0000_ _x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_ _x0000_/_x0000_ _x0000_2_x0000_4_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_9_x0000_._x0000_6_x0000_ _x0000_/_x0000_ _x0000_2_x0000_4_x0000_S_x0000_S_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_ _x0000_/_x0000_ _x0000_2_x0000_3_x0000_F_x0000_W_x0000_ _x0000__x0018_ÂüÈ _x0000_ìÅàÂ _x0000_ _x0000_1_x0000_2_x0000_ _x0000_(_x0000_ô²ù²Ç _x0000_Æ­Ì&lt;Ç\¸ _x0000_6_x0000_ _x0000__x0018_¼_x0001_Æ)_x0000__x0008__x0000__x0000_20160114_x000E__x0000__x0000_37690004577337_x0006__x0000__x0000_D00210_x0011__x0000__x0001_(_x0000_üÈ)_x0000_ÐÅtÇ_x001C_ÈtÇxÇ0Ñ´°TÁ °(_x0000_LÑÈ²¤Â)_x0000_
+_x0000__x0000_1268641398_x000C__x0000__x0000_031-761-8980_x000C__x0000__x0000_031-761-2140_x0005__x0000__x0000_12769_x000D__x0000__x0000_010-4552-3318	_x0000__x0000_1800-6142_x000E__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_4_x0000_0_x0000_+_x0000_2_x0000_5_x0000__x0008__x0000__x0000_20160121_x000E__x0000__x0000_37690004578037_x0006__x0000__x0000_D00256	_x0000__x0001_p¬1Á¤ÂìÓ Î(_x0000_Å°À)_x0000_
+_x0000__x0000_6210808090_x0003__x0000__x0001__x0015_È+È_x0015_¬_x0006__x0000__x0001_Ä³Áä¹ _x0000__x001C_ÈpÈ_x000B__x0000__x0001_ìÕ¤Â0®l­,_x0000_ _x0000_¤ÂìÓ Î©ÆÔ_x0008__x0000__x0000_20160412_x000C__x0000__x0000_055-387-3613_x000C__x0000__x0000_055-387-3615_x0008__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_Å°ÀÜÂ_x0005__x0000__x0000_50621 _x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_Å°ÀÜÂ _x0000__x001C_Á|ÇÙ³\¸ _x0000_2_x0000_5_x0000_ _x0000_ _x0000_(_x0000__x0011_É½Ù³,_x0000_ _x0000_$Ç ÁÝÀ_x0001_Æ´ÅP­äÂ)_x0000__x000D__x0000__x0000_010-2390-2994_x0013__x0000__x0000_dhrhr68@hanmail.netH_x0000__x0001_2_x0000_4_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_3_x0000_5_x0000_ _x0000_/_x0000_2_x0000_4_x0000_S_x0000_S_x0000__x0018_ÂüÈìÅàÂ _x0000_3_x0000_5_x0000_ _x0000_/_x0000_ _x0000_2_x0000_3_x0000_F_x0000_W_x0000_ _x0000__x0018_ÂüÈ _x0000_ìÅàÂ _x0000_3_x0000_5_x0000_ _x0000_/_x0000_ _x0000_2_x0000_3_x0000_S_x0000_S_x0000_ _x0000__x0018_ÂüÈ _x0000_ìÅàÂ _x0000_3_x0000_5_x0000_(_x0000_|·_x0013_Ï+_x0000_È¹D¾¤Â _x0000_9_x0000_4_x0000_3_x0000_,_x0000_2_x0000_5_x0000_0_x0000_)_x0000__x0008__x0000__x0000_20160407_x000E__x0000__x0000_37690004581237_x0006__x0000__x0000_D00267_x0006__x0000__x0001__x001C_ÈtÇD¾¤ÂìÓ Î
+_x0000__x0000_6664100083_x0003__x0000__x0001_Ç_x0015_È\Õ_x000D__x0000__x0001_Ä³ä¹ _x0000__x000F_¼ _x0000_Áä¹ÅÅ,_x0000_ _x0000__x001C_ÁD¾¤Â_x000C__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000_ _x0000__x0011_­à¬_x0000_³ÕÅÅ_x0008__x0000__x0000_20160610_x000C__x0000__x0000_062-523-7451_x000C__x0000__x0000_062-523-7455_x0005__x0000__x0000_62023_x000D__x0000__x0001__x0011_­üÈ _x0000__x001C_Ál­ _x0000_´ÆÌ\¸ _x0000_1_x0000_2_x0000_2_x0000__x0005__x0000__x0001_(_x0000__x000D_Ã_x000C_ÍÙ³)_x0000__x000D__x0000__x0000_010-4606-4538_x0015__x0000__x0000_jhrim1226@hanmail.net_x0008__x0000__x0000_20160601_x000E__x0000__x0000_37690004584137_x0006__x0000__x0000_D00280_x0005__x0000__x0001_Ä³ô²¤ÂìÓ Î
+_x0000__x0000_3071042161_x0003__x0000__x0001_$ÇÙ³ÝÂ_x000B__x0000__x0001_Ä³ä¹_x000F_¼ _x0000_Áä¹ÅÅ _x0000_Áä¹ÅÅ_x0010__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_Ç_x0004_Èp¬ _x0000__x0010_Óä¹,_x0000_ _x0000__x0000_³ìÅ_x0008__x0000__x0000_20160825_x000C__x0000__x0000_044-863-8908_x000C__x0000__x0000_044-863-8970_x000F__x0000__x0001_8Á+È¹ÒÄ¼ÇXÎÜÂ _x0000_8Á+È¹ÒÄ¼ÇXÎÜÂ_x0005__x0000__x0000_30102_x001E__x0000__x0001_8Á+È¹ÒÄ¼ÇXÎÜÂ _x0000__x0008_È¬Ç\¸ _x0000_1_x0000_7_x0000_2_x0000_ _x0000_(_x0000_´ÅÄÉÙ³,_x0000_ _x0000_ÜÐ\Õ_x0004_Õ_x0008_¸¤Â&lt;Á0Ñ)_x0000__x0004__x0000__x0001_1_x0000_0_x0000_1_x0000_8Ö_x000D__x0000__x0000_010-7185-8008_x0015__x0000__x0000_dodamsports@naver.com_x000E__x0000__x0000_37690004586437_x0006__x0000__x0000_D00282_x0005__x0000__x0001__x0004_²¬¹¤ÂìÓ Î
+_x0000__x0000_1082124505_x0003__x0000__x0001_@®l×_x0015_È_x0006__x0000__x0001_Áä¹ _x0000_Ä³Áä¹_x000C__x0000__x0001__x0004_ÈÇÁÀp¬·ÅÅ _x0000_0¼Ü´ü»4Ñ _x0000__x000B__x0000__x0000_02-848-6291_x000B__x0000__x0000_02-848-7556
+_x0000__x0001__x001C_Á¸Æ¹ÒÄ¼ÜÂ _x0000__x0001_Æñ´ìÓl­_x0005__x0000__x0000_07375_x000E__x0000__x0001__x001C_Á¸Æ _x0000__x0001_Æñ´ìÓl­ _x0000_Ä³àÂ\¸ _x0000_5_x0000_1_x0000__x000D__x0000__x0001_1_x0000_5Î _x0000_1_x0000_0_x0000_5_x0000_8Ö(_x0000_¡ÁU³L¾)µ)_x0000__x000D__x0000__x0000_010-8393-6291_x0013__x0000__x0000_hee00jung@naver.com_x0008__x0000__x0000_20160905_x000E__x0000__x0000_37690004588737_x0006__x0000__x0000_D00286_x0007__x0000__x0001_Æ%±¤Â _x0000_1Á¨°_x0010_È
+_x0000__x0000_2603001743_x0003__x0000__x0001_MÖ¥Ç8Ö_x0008__x0000__x0001_Ä³ä¹ _x0000__x000F_¼ _x0000_Áä¹ÅÅ_x0008__x0000__x0000_20151218_x000C__x0000__x0000_031-755-7257_x0007__x0000__x0001_½¬0®Ä³ _x0000_1Á¨°ÜÂ_x0005__x0000__x0000_13110_x001E__x0000__x0001_½¬0®Ä³ _x0000_1Á¨°ÜÂ _x0000__x0018_Â_x0015_Èl­ _x0000_1Á¨°_x0000_³\¸ _x0000_1_x0000_2_x0000_6_x0000_7_x0000_ _x0000_-_x0000_1_x0000_ _x0000_(_x0000_ÜÐÉÓÙ³)_x0000__x000D__x0000__x0000_010-7191-7257_x0012__x0000__x0000_nero1016@naver.com_x0002__x0000__x0001_¨°¸Ó_x0008__x0000__x0000_20161109_x000E__x0000__x0000_37690004591037_x0006__x0000__x0000_D00287_x0005__x0000__x0001_¤ÐtÎ¤ÂìÓ Î
+_x0000__x0000_6103752918_x0003__x0000__x0001_@®ÜÐÇ_x0008__x0000__x0000_20161125_x000C__x0000__x0000_052-268-6086_x000C__x0000__x0000_052-272-5908_x0008__x0000__x0001_¸Æ°À_x0011_­íÅÜÂ _x0000_¨°l­_x0005__x0000__x0000_44692_x0016__x0000__x0001_¸Æ°À_x0011_­íÅÜÂ _x0000_¨°l­ _x0000_Ë³ÈÉ\¸ _x0000_1_x0000_2_x0000_4_x0000_ _x0000_ _x0000_(_x0000_ì²Ù³)_x0000__x0003__x0000__x0000_3/2_x000D__x0000__x0000_010-9568-6086_x0014__x0000__x0000_kika5908@hanmail.net_x000E__x0000__x0000_37690004592637_x0006__x0000__x0000_D00292_x0008__x0000__x0001_Æ%±¤Â _x0000_¤ÂìÓÐÆ_x0010_È
+_x0000__x0000_6977800050_x0003__x0000__x0001_\ÕÀ­_x0001_Æ_x0008__x0000__x0000_20170102_x000C__x0000__x0000_051-517-3862_x000C__x0000__x0000_051-583-1023	_x0000__x0001_½°À_x0011_­íÅÜÂ _x0000__x0008_®_x0015_Èl­_x0005__x0000__x0000_46207&amp;_x0000__x0001_½°À_x0011_­íÅÜÂ _x0000__x0008_®_x0015_Èl­ _x0000_´Ì!Çõ¬ÐÆ\¸3_x0000_9_x0000_9_x0000_¼8® _x0000_3_x0000_2_x0000_4_x0000_ _x0000_ _x0000_(_x0000_P´l­Ù³,_x0000_ _x0000_¤ÂìÓÐÆ_x000C_ÓlÐ)_x0000__x0010__x0000__x0001_ÀÉXÕ1_x0000_5Î(_x0000_P´l­Ù³,_x0000_ _x0000_äÂ´°´Ì!Ç_x0000_­)_x0000__x000D__x0000__x0000_010-5505-3862_x0013__x0000__x0000_hgy4285@hanmail.net_x000E__x0000__x0000_37690004595537_x0006__x0000__x0000_D00306_x0007__x0000__x0001_Æ%±¤Â _x0000_ÁÀ4»_x0010_È
+_x0000__x0000_8042300420_x0003__x0000__x0001_@®_x0004_Ö+È_x000D__x0000__x0001_¤ÂìÓ Î©ÆÔ _x0000_´ÆÙ³©ÆÔ _x0000_¡ÇTÖ_x0008__x0000__x0000_20170119_x000D__x0000__x0000_010-6886-7065_x000C__x0000__x0000_062-374-5410_x0005__x0000__x0000_61970_x0013__x0000__x0001__x0011_­üÈ _x0000__x001C_Ál­ _x0000_ÁÀ4»ü»üÈ\¸3_x0000_2_x0000_¼8® _x0000_3_x0000_-_x0000_5_x0000__x0013__x0000__x0000_sskim-j@hanmail.net_x000E__x0000__x0000_37690004597837_x0006__x0000__x0000_D00308_x0005__x0000__x0001_C_x0000_S_x0000_¤ÂìÓ Î
+_x0000__x0000_2270838785_x0007__x0000__x0001_iÖ_x001C_ÂU³xÆ _x0000_1_x0000_+º_x000C__x0000__x0000_031-385-1222_x000C__x0000__x0000_031-388-3477_x0005__x0000__x0000_13958_x0016__x0000__x0001_½¬0® _x0000_HÅÅÜÂ _x0000_Ì¹HÅl­ _x0000__x0008_Æ Âõ¬ÐÆ\¸5_x0000_2_x0000_¼8® _x0000_2_x0000__x000D__x0000__x0000_010-3176-9037_x0013__x0000__x0000_bill@cssports.co.kr_x000D__x0000__x0000_010-2727-2718_x000F__x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_5_x0000_+_x0000_3_x0000_._x0000_5_x0000__x000E__x0000__x0000_37690004598437_x0006__x0000__x0000_D00311
+_x0000__x0001_TÏ¬¹DÅ¤ÂìÓ Î(_x0000_ÜÂe×)_x0000_
+_x0000__x0000_3047001336_x0006__x0000__x0001_TÏ¬¹DÅ¤ÂìÓ Î_x0003__x0000__x0001_\Í_x0001_Æ_x0019_Â_x0012__x0000__x0001_¤ÂìÓ Î©ÆÔ,_x0000__x0010_Ó	Í&lt;»,_x0000_xÇÄÁ&lt;»,_x0000_0®ÀÐ©ÆÔ_x000D__x0000__x0000_010-2618-5518_x000C__x0000__x0000_031-312-8982_x0007__x0000__x0001_½¬0®Ä³ _x0000_ÜÂe×ÜÂ_x0005__x0000__x0000_14922_x000F__x0000__x0001_½¬0® _x0000_ÜÂe×ÜÂ _x0000_@ÇÄ¬¼_x0001_Æ8® _x0000_2_x0000_7_x0000__x000F__x0000__x0001_3_x0000_0_x0000_3_x0000_8Ö(_x0000_@ÇÕÙ³,_x0000_ _x0000_ÜÂðÒ_x000C_ÓlÐ)_x0000__x0015__x0000__x0000_queenmt5518@naver.com_x000C__x0000__x0000_031-404-6121_x0008__x0000__x0000_20170220_x000E__x0000__x0000_37690004600637_x0006__x0000__x0000_D00312_x000E__x0000__x0001_Æ%±¤Â(_x0000_Y_x0000_O_x0000_N_x0000_E_x0000_X_x0000_)_x0000_ _x0000_tÇÌ_x0010_È
+_x0000__x0000_1052641553_x0003__x0000__x0001_$Ç ÇÄÉ_x000C__x0000__x0000_031-631-2210_x0007__x0000__x0001_½¬0®Ä³ _x0000_tÇÌÜÂ_x0005__x0000__x0000_17362_x0017__x0000__x0001_½¬0®Ä³ _x0000_tÇÌÜÂ _x0000_`Å(¸_x0015_È\¸ _x0000_1_x0000_4_x0000_2_x0000_ _x0000_ _x0000_(_x0000_=Ì_x0004_ÈÙ³)_x0000__x000D__x0000__x0000_010-3459-1313_x0010__x0000__x0000_jin7601@daum.net_x0003__x0000__x0001_\Í_x0015_¬8Ö_x0008__x0000__x0000_20170221_x000E__x0000__x0000_37690004601237_x0006__x0000__x0000_D00324_x0006__x0000__x0001__x000C_Ó¸Ò_x0008_±¤ÂìÓ Î
+_x0000__x0000_1272471368_x0003__x0000__x0001_@®©Æ`Å_x000C__x0000__x0000_031-398-8953_x000C__x0000__x0000_031-398-8954_x0007__x0000__x0001_½¬0®Ä³ _x0000_p­ìÓÜÂ_x0005__x0000__x0000_15833_x0016__x0000__x0001_½¬0®Ä³ _x0000_p­ìÓÜÂ _x0000_$Æ_x0008_®\¸ _x0000_1_x0000_5_x0000_0_x0000_ _x0000_ _x0000_(_x0000__x0008_®_x0015_ÈÙ³)_x0000_	_x0000__x0001_1_x0000_0_x0000_2_x0000_8Ö(_x0000__x0008_®_x0015_ÈÙ³)_x0000__x000D__x0000__x0000_010-4854-8953_x0010__x0000__x0000_kya5767@nate.com_x0008__x0000__x0000_20170320_x000E__x0000__x0000_37690004603537_x0006__x0000__x0000_D00328_x0006__x0000__x0001_ÄÉüÈ0¼Ü´ü»4Ñ
+_x0000__x0000_6131082729_x0003__x0000__x0001__x0015_È Ìä¬_x000C__x0000__x0000_055-747-2101_x0008__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_ÄÉüÈÜÂ_x0005__x0000__x0000_52806_x0019__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_ÄÉüÈÜÂ _x0000_Á-¼\¸7_x0000_5_x0000_¼8® _x0000_8_x0000_ _x0000_ _x0000_(_x0000_ÁÀÉÓÙ³)_x0000__x000D__x0000__x0000_010-9612-2188_x0011__x0000__x0000_jcg2188@naver.com_x000B__x0000__x0000_01095082188_x0008__x0000__x0000_20170324_x000E__x0000__x0000_37690004604137_x0006__x0000__x0000_D00338
+_x0000__x0001_Æ%±¤Â=ÌÐÆ_x0010_È(_x0000_øÂtÎ)_x0000_
+_x0000__x0000_6092352584_x0003__x0000__x0001_HÅ¬Çü­_x0010__x0000__x0001_¤ÂìÓ Î _x0000_XÇX¹ _x0000__x000F_¼ _x0000_©ÆÔ _x0000_È¹lÐ_x001C_ÈÇ_x0008__x0000__x0000_20170411_x000C__x0000__x0000_055-261-0123_x0005__x0000__x0000_51420_x0019__x0000__x0001_½¬ÁÀ¨°Ä³ _x0000_=ÌÐÆÜÂ _x0000_1Á°Àl­ _x0000__x0018_¼ÀÉ\¸ _x0000_8_x0000_ _x0000_ _x0000_(_x0000__x0018_¼ÀÉÙ³)_x0000__x0005__x0000__x0001_(_x0000__x0018_¼ÀÉÙ³)_x0000__x000D__x0000__x0000_010-9796-1346_x0011__x0000__x0000_cwssaka@naver.com
+_x0000__x0000_0552610123_x000E__x0000__x0000_37690004606437_x0006__x0000__x0000_D00382_x0004__x0000__x0001_$Æ¤ÂìÓ Î
+_x0000__x0000_2860500614_x0003__x0000__x0001__x0015_¼Á|·_x000C__x0000__x0001__x0004_ÈÇÁÀp¬·(_x0000_¤ÂìÓ Î©ÆÔ)_x0000__x000C__x0000__x0000_063-231-0360_x0005__x0000__x0000_54947_x0015__x0000__x0001__x0004_È½ _x0000__x0004_ÈüÈÜÂ _x0000_DÆ°Àl­ _x0000__x0004_È|·_x0010_¬_x0001_Æ\¸ _x0000_4_x0000_0_x0000_-_x0000_1_x0000__x000B__x0000__x0000_01076785147_x0014__x0000__x0000_sora1976kr@naver.com_x0003__x0000__x0001__x0015_¼Ñ¼%ÆQ_x0000__x0001_2_x0000_5_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_+_x0000_1_x0000_0_x0000_0_x0000_ _x0000_/_x0000_ _x0000_2_x0000_5_x0000_S_x0000_S_x0000_ _x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_ _x0000_+_x0000_ _x0000_1_x0000_0_x0000_0_x0000_ _x0000_/_x0000_ _x0000_ _x0000_2_x0000_4_x0000_F_x0000_W_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_ _x0000_/_x0000_ _x0000_2_x0000_4_x0000_S_x0000_S_x0000__x0018_ÂüÈìÅàÂ _x0000_1_x0000_2_x0000_ _x0000_/_x0000_ _x0000_2_x0000_3_x0000_F_x0000_W_x0000_ _x0000__x0018_ÂüÈ _x0000_ìÅàÂ _x0000_1_x0000_2_x0000__x0008__x0000__x0000_20170710_x000E__x0000__x0000_37690004610337_x0006__x0000__x0000_D00392_x0007__x0000__x0001_¨Ö1Á+ÈiÕ¤ÂìÓ Î
+_x0000__x0000_7521600607_x0002__x0000__x0001_@®_x0004_½_x0008__x0000__x0000_20170812_x000C__x0000__x0000_064-733-2992_x0005__x0000__x0000_63591_x0013__x0000__x0001__x001C_ÈüÈ¹ÒÄ¼ÇXÎÄ³ _x0000__x001C_ÁÀ­ìÓÜÂ _x0000_Ù³8»\¸ _x0000_3_x0000_0_x0000__x000B__x0000__x0000_01090156265_x0010__x0000__x0000_ddadon@naver.com_x000B__x0000__x0000_01036928845_x0008__x0000__x0000_20170821_x000E__x0000__x0000_37690004611037_x0006__x0000__x0000_D00396_x000E__x0000__x0001_Æ%±¤Â _x0000_Å°À_x0010_È(_x0000_TÖ·¤ÂìÓ Î)_x0000_
+_x0000__x0000_6211383962_x0003__x0000__x0001_\ÍiÖðÅ_x0008__x0000__x0000_20170813_x000C__x0000__x0000_055-382-6688_x000C__x0000__x0000_055-366-6648_x0005__x0000__x0000_50548_x000F__x0000__x0001_½¬¨° _x0000_Å°ÀÜÂ _x0000_ÅÆÁÀ_x0000_³\¸ _x0000_9_x0000_6_x0000_1_x0000__x0007__x0000__x0001_Æ%±¤Â _x0000_Å°À_x0010_È_x000D__x0000__x0000_010-932</v>
           </cell>
           <cell r="L40" t="str">
             <v/>
           </cell>
-          <cell r="M40" t="str">
-            <v>01087511199</v>
+          <cell r="M40" t="e">
+            <v>#N/A</v>
           </cell>
           <cell r="N40" t="str">
             <v/>
           </cell>
-          <cell r="O40" t="str">
-            <v>경기도 안산시</v>
-          </cell>
-          <cell r="P40" t="str">
-            <v>15497</v>
-          </cell>
-          <cell r="Q40" t="str">
-            <v>경기 안산시 상록구 천문4길 17</v>
-          </cell>
-          <cell r="R40" t="str">
-            <v>1층1519-13  1층  스매쉬스포츠 물류센터</v>
-          </cell>
-          <cell r="S40" t="str">
-            <v>010-5471-3330</v>
-          </cell>
-          <cell r="T40" t="str">
-            <v>smash-123@naver.com</v>
+          <cell r="O40" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="P40" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="Q40" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="R40" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="S40" t="e">
+            <v>#N/A</v>
+          </cell>
+          <cell r="T40" t="e">
+            <v>#N/A</v>
           </cell>
           <cell r="U40" t="str">
             <v/>
@@ -4843,7 +6352,7 @@
             <v/>
           </cell>
           <cell r="Z40" t="str">
-            <v>01054713330</v>
+            <v>부산광역시 남구 자유평화로 49</v>
           </cell>
           <cell r="AA40" t="str">
             <v>Y</v>
@@ -4862,96 +6371,36 @@
           </cell>
         </row>
         <row r="41">
-          <cell r="B41" t="str">
-            <v>D00096</v>
-          </cell>
-          <cell r="C41" t="str">
-            <v>스포츠뱅크</v>
-          </cell>
-          <cell r="D41" t="str">
-            <v>사용가능</v>
-          </cell>
-          <cell r="E41" t="str">
-            <v>일반사업자</v>
-          </cell>
-          <cell r="F41" t="str">
-            <v>1272092161</v>
-          </cell>
-          <cell r="G41" t="str">
-            <v>스포츠뱅크</v>
-          </cell>
-          <cell r="H41" t="str">
-            <v>김진평</v>
-          </cell>
-          <cell r="I41" t="str">
-            <v>소매</v>
-          </cell>
-          <cell r="J41" t="str">
-            <v>체육용품</v>
-          </cell>
-          <cell r="K41" t="str">
-            <v>20070503</v>
-          </cell>
-          <cell r="L41" t="str">
-            <v/>
-          </cell>
-          <cell r="M41" t="str">
-            <v>031-535-1244</v>
-          </cell>
-          <cell r="N41" t="str">
-            <v>0315352245</v>
-          </cell>
-          <cell r="O41" t="str">
-            <v>경기도 포천시</v>
-          </cell>
-          <cell r="P41" t="str">
-            <v>487050</v>
-          </cell>
-          <cell r="Q41" t="str">
-            <v>경기도 포천시 군내면 호국로 1696. 2층</v>
-          </cell>
-          <cell r="R41" t="str">
-            <v/>
-          </cell>
-          <cell r="S41" t="str">
-            <v>010-6354-5471</v>
-          </cell>
-          <cell r="T41" t="str">
-            <v>kjp31@hanmail.net</v>
-          </cell>
-          <cell r="U41" t="str">
-            <v/>
-          </cell>
-          <cell r="V41" t="str">
-            <v/>
-          </cell>
-          <cell r="W41" t="str">
-            <v/>
-          </cell>
-          <cell r="X41" t="str">
-            <v/>
-          </cell>
-          <cell r="Y41" t="str">
-            <v/>
-          </cell>
-          <cell r="Z41" t="str">
-            <v>031-535-1244</v>
-          </cell>
-          <cell r="AA41" t="str">
-            <v>N</v>
-          </cell>
-          <cell r="AB41" t="str">
-            <v>Y</v>
-          </cell>
-          <cell r="AC41" t="str">
-            <v>B등급</v>
-          </cell>
-          <cell r="AD41" t="str">
-            <v>24013</v>
-          </cell>
-          <cell r="AE41" t="str">
-            <v>김종윤</v>
-          </cell>
+          <cell r="B41"/>
+          <cell r="C41"/>
+          <cell r="D41"/>
+          <cell r="E41"/>
+          <cell r="F41"/>
+          <cell r="G41"/>
+          <cell r="H41"/>
+          <cell r="I41"/>
+          <cell r="J41"/>
+          <cell r="K41"/>
+          <cell r="L41"/>
+          <cell r="M41"/>
+          <cell r="N41"/>
+          <cell r="O41"/>
+          <cell r="P41"/>
+          <cell r="Q41"/>
+          <cell r="R41"/>
+          <cell r="S41"/>
+          <cell r="T41"/>
+          <cell r="U41"/>
+          <cell r="V41"/>
+          <cell r="W41"/>
+          <cell r="X41"/>
+          <cell r="Y41"/>
+          <cell r="Z41"/>
+          <cell r="AA41"/>
+          <cell r="AB41"/>
+          <cell r="AC41"/>
+          <cell r="AD41"/>
+          <cell r="AE41"/>
         </row>
         <row r="42">
           <cell r="B42" t="str">
@@ -19299,7 +20748,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet11"/>
-  <dimension ref="A1:N149"/>
+  <dimension ref="A1:N150"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.625" style="3" customWidth="1"/>
@@ -21973,17 +23422,17 @@
         <v>123</v>
       </c>
       <c r="B107" s="11" t="s">
-        <v>213</v>
+        <v>317</v>
       </c>
       <c r="C107" s="10" t="s">
-        <v>214</v>
+        <v>318</v>
       </c>
       <c r="D107" s="8" t="str">
         <f>VLOOKUP(B107,[1]export!$B$2:$AE$194,30,0)</f>
-        <v>유창림</v>
+        <v>손효동</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F107" s="2"/>
       <c r="G107" s="2"/>
@@ -21998,17 +23447,17 @@
         <v>124</v>
       </c>
       <c r="B108" s="11" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C108" s="10" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D108" s="8" t="str">
         <f>VLOOKUP(B108,[1]export!$B$2:$AE$194,30,0)</f>
-        <v>손효동</v>
+        <v>유창림</v>
       </c>
       <c r="E108" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F108" s="2"/>
       <c r="G108" s="2"/>
@@ -22023,17 +23472,17 @@
         <v>125</v>
       </c>
       <c r="B109" s="11" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C109" s="10" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D109" s="8" t="str">
         <f>VLOOKUP(B109,[1]export!$B$2:$AE$194,30,0)</f>
-        <v>안우진</v>
+        <v>손효동</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="F109" s="2"/>
       <c r="G109" s="2"/>
@@ -22048,17 +23497,17 @@
         <v>126</v>
       </c>
       <c r="B110" s="11" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C110" s="10" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D110" s="8" t="str">
         <f>VLOOKUP(B110,[1]export!$B$2:$AE$194,30,0)</f>
-        <v>설광배</v>
+        <v>안우진</v>
       </c>
       <c r="E110" s="10" t="s">
-        <v>311</v>
+        <v>300</v>
       </c>
       <c r="F110" s="2"/>
       <c r="G110" s="2"/>
@@ -22073,17 +23522,17 @@
         <v>127</v>
       </c>
       <c r="B111" s="11" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C111" s="10" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D111" s="8" t="str">
         <f>VLOOKUP(B111,[1]export!$B$2:$AE$194,30,0)</f>
         <v>설광배</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="F111" s="2"/>
       <c r="G111" s="2"/>
@@ -22098,17 +23547,17 @@
         <v>128</v>
       </c>
       <c r="B112" s="11" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C112" s="10" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D112" s="8" t="str">
         <f>VLOOKUP(B112,[1]export!$B$2:$AE$194,30,0)</f>
-        <v>최낙호</v>
+        <v>설광배</v>
       </c>
       <c r="E112" s="10" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F112" s="2"/>
       <c r="G112" s="2"/>
@@ -22123,17 +23572,17 @@
         <v>129</v>
       </c>
       <c r="B113" s="11" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C113" s="10" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D113" s="8" t="str">
         <f>VLOOKUP(B113,[1]export!$B$2:$AE$194,30,0)</f>
         <v>최낙호</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F113" s="2"/>
       <c r="G113" s="2"/>
@@ -22148,17 +23597,17 @@
         <v>130</v>
       </c>
       <c r="B114" s="11" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C114" s="10" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D114" s="8" t="str">
         <f>VLOOKUP(B114,[1]export!$B$2:$AE$194,30,0)</f>
-        <v>손효동</v>
+        <v>최낙호</v>
       </c>
       <c r="E114" s="10" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F114" s="2"/>
       <c r="G114" s="2"/>
@@ -22173,17 +23622,17 @@
         <v>131</v>
       </c>
       <c r="B115" s="11" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C115" s="10" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D115" s="8" t="str">
         <f>VLOOKUP(B115,[1]export!$B$2:$AE$194,30,0)</f>
-        <v>박현진</v>
+        <v>손효동</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="F115" s="2"/>
       <c r="G115" s="2"/>
@@ -22198,17 +23647,17 @@
         <v>132</v>
       </c>
       <c r="B116" s="11" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C116" s="10" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D116" s="8" t="str">
         <f>VLOOKUP(B116,[1]export!$B$2:$AE$194,30,0)</f>
-        <v>문창수</v>
+        <v>박현진</v>
       </c>
       <c r="E116" s="10" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="F116" s="2"/>
       <c r="G116" s="2"/>
@@ -22223,17 +23672,17 @@
         <v>133</v>
       </c>
       <c r="B117" s="11" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C117" s="10" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D117" s="8" t="str">
         <f>VLOOKUP(B117,[1]export!$B$2:$AE$194,30,0)</f>
-        <v>신동원</v>
+        <v>문창수</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F117" s="2"/>
       <c r="G117" s="2"/>
@@ -22248,17 +23697,17 @@
         <v>134</v>
       </c>
       <c r="B118" s="11" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C118" s="10" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D118" s="8" t="str">
         <f>VLOOKUP(B118,[1]export!$B$2:$AE$194,30,0)</f>
-        <v>김연준</v>
+        <v>신동원</v>
       </c>
       <c r="E118" s="10" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F118" s="2"/>
       <c r="G118" s="2"/>
@@ -22273,17 +23722,17 @@
         <v>135</v>
       </c>
       <c r="B119" s="11" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C119" s="10" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D119" s="8" t="str">
         <f>VLOOKUP(B119,[1]export!$B$2:$AE$194,30,0)</f>
-        <v>김동경</v>
+        <v>김연준</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="F119" s="2"/>
       <c r="G119" s="2"/>
@@ -22298,10 +23747,10 @@
         <v>136</v>
       </c>
       <c r="B120" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C120" s="10" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D120" s="8" t="str">
         <f>VLOOKUP(B120,[1]export!$B$2:$AE$194,30,0)</f>
@@ -22323,17 +23772,17 @@
         <v>137</v>
       </c>
       <c r="B121" s="11" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C121" s="10" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D121" s="8" t="str">
         <f>VLOOKUP(B121,[1]export!$B$2:$AE$194,30,0)</f>
         <v>김동경</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="F121" s="2"/>
       <c r="G121" s="2"/>
@@ -22348,17 +23797,17 @@
         <v>138</v>
       </c>
       <c r="B122" s="11" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C122" s="10" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D122" s="8" t="str">
         <f>VLOOKUP(B122,[1]export!$B$2:$AE$194,30,0)</f>
         <v>김동경</v>
       </c>
       <c r="E122" s="10" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="F122" s="2"/>
       <c r="G122" s="2"/>
@@ -22373,17 +23822,17 @@
         <v>139</v>
       </c>
       <c r="B123" s="11" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C123" s="10" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D123" s="8" t="str">
         <f>VLOOKUP(B123,[1]export!$B$2:$AE$194,30,0)</f>
         <v>김동경</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="F123" s="2"/>
       <c r="G123" s="2"/>
@@ -22398,17 +23847,17 @@
         <v>140</v>
       </c>
       <c r="B124" s="11" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C124" s="10" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D124" s="8" t="str">
         <f>VLOOKUP(B124,[1]export!$B$2:$AE$194,30,0)</f>
-        <v>신동원</v>
+        <v>김동경</v>
       </c>
       <c r="E124" s="10" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="F124" s="2"/>
       <c r="G124" s="2"/>
@@ -22423,17 +23872,17 @@
         <v>141</v>
       </c>
       <c r="B125" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C125" s="10" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D125" s="8" t="str">
         <f>VLOOKUP(B125,[1]export!$B$2:$AE$194,30,0)</f>
-        <v>손효동</v>
+        <v>신동원</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="F125" s="2"/>
       <c r="G125" s="2"/>
@@ -22448,17 +23897,17 @@
         <v>142</v>
       </c>
       <c r="B126" s="11" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C126" s="10" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D126" s="8" t="str">
         <f>VLOOKUP(B126,[1]export!$B$2:$AE$194,30,0)</f>
-        <v>강태호</v>
+        <v>손효동</v>
       </c>
       <c r="E126" s="10" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="F126" s="2"/>
       <c r="G126" s="2"/>
@@ -22473,17 +23922,17 @@
         <v>143</v>
       </c>
       <c r="B127" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C127" s="10" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D127" s="8" t="str">
         <f>VLOOKUP(B127,[1]export!$B$2:$AE$194,30,0)</f>
-        <v>최낙호</v>
+        <v>강태호</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="F127" s="2"/>
       <c r="G127" s="2"/>
@@ -22498,14 +23947,14 @@
         <v>144</v>
       </c>
       <c r="B128" s="11" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C128" s="10" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D128" s="8" t="str">
         <f>VLOOKUP(B128,[1]export!$B$2:$AE$194,30,0)</f>
-        <v>전재영</v>
+        <v>최낙호</v>
       </c>
       <c r="E128" s="10" t="s">
         <v>307</v>
@@ -22523,17 +23972,17 @@
         <v>145</v>
       </c>
       <c r="B129" s="11" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C129" s="10" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D129" s="8" t="str">
         <f>VLOOKUP(B129,[1]export!$B$2:$AE$194,30,0)</f>
-        <v>김종윤</v>
+        <v>전재영</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F129" s="2"/>
       <c r="G129" s="2"/>
@@ -22548,17 +23997,17 @@
         <v>146</v>
       </c>
       <c r="B130" s="11" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C130" s="10" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D130" s="8" t="str">
         <f>VLOOKUP(B130,[1]export!$B$2:$AE$194,30,0)</f>
-        <v>왕준하</v>
+        <v>김종윤</v>
       </c>
       <c r="E130" s="10" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="F130" s="2"/>
       <c r="G130" s="2"/>
@@ -22573,17 +24022,17 @@
         <v>147</v>
       </c>
       <c r="B131" s="11" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C131" s="10" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D131" s="8" t="str">
         <f>VLOOKUP(B131,[1]export!$B$2:$AE$194,30,0)</f>
-        <v>김동경</v>
+        <v>왕준하</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="F131" s="2"/>
       <c r="G131" s="2"/>
@@ -22598,17 +24047,17 @@
         <v>148</v>
       </c>
       <c r="B132" s="11" t="s">
-        <v>263</v>
-      </c>
-      <c r="C132" s="12" t="s">
-        <v>264</v>
+        <v>261</v>
+      </c>
+      <c r="C132" s="10" t="s">
+        <v>262</v>
       </c>
       <c r="D132" s="8" t="str">
         <f>VLOOKUP(B132,[1]export!$B$2:$AE$194,30,0)</f>
-        <v>전재영</v>
+        <v>김동경</v>
       </c>
       <c r="E132" s="10" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="F132" s="2"/>
       <c r="G132" s="2"/>
@@ -22623,17 +24072,17 @@
         <v>149</v>
       </c>
       <c r="B133" s="11" t="s">
-        <v>265</v>
-      </c>
-      <c r="C133" s="10" t="s">
-        <v>266</v>
+        <v>263</v>
+      </c>
+      <c r="C133" s="12" t="s">
+        <v>264</v>
       </c>
       <c r="D133" s="8" t="str">
         <f>VLOOKUP(B133,[1]export!$B$2:$AE$194,30,0)</f>
-        <v>김종윤</v>
+        <v>전재영</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="F133" s="2"/>
       <c r="G133" s="2"/>
@@ -22648,17 +24097,17 @@
         <v>150</v>
       </c>
       <c r="B134" s="11" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C134" s="10" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D134" s="8" t="str">
         <f>VLOOKUP(B134,[1]export!$B$2:$AE$194,30,0)</f>
-        <v>왕준하</v>
+        <v>김종윤</v>
       </c>
       <c r="E134" s="10" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="F134" s="2"/>
       <c r="G134" s="2"/>
@@ -22673,17 +24122,17 @@
         <v>151</v>
       </c>
       <c r="B135" s="11" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C135" s="10" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D135" s="8" t="str">
         <f>VLOOKUP(B135,[1]export!$B$2:$AE$194,30,0)</f>
-        <v>문창수</v>
+        <v>왕준하</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="F135" s="2"/>
       <c r="G135" s="2"/>
@@ -22698,17 +24147,17 @@
         <v>152</v>
       </c>
       <c r="B136" s="11" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C136" s="10" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D136" s="8" t="str">
         <f>VLOOKUP(B136,[1]export!$B$2:$AE$194,30,0)</f>
-        <v>전재영</v>
+        <v>문창수</v>
       </c>
       <c r="E136" s="10" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F136" s="2"/>
       <c r="G136" s="2"/>
@@ -22723,14 +24172,14 @@
         <v>153</v>
       </c>
       <c r="B137" s="11" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C137" s="10" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D137" s="8" t="str">
         <f>VLOOKUP(B137,[1]export!$B$2:$AE$194,30,0)</f>
-        <v>김연준</v>
+        <v>전재영</v>
       </c>
       <c r="E137" s="10" t="s">
         <v>307</v>
@@ -22748,17 +24197,17 @@
         <v>154</v>
       </c>
       <c r="B138" s="11" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C138" s="10" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D138" s="8" t="str">
         <f>VLOOKUP(B138,[1]export!$B$2:$AE$194,30,0)</f>
-        <v>손효동</v>
+        <v>김연준</v>
       </c>
       <c r="E138" s="10" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F138" s="2"/>
       <c r="G138" s="2"/>
@@ -22773,17 +24222,17 @@
         <v>155</v>
       </c>
       <c r="B139" s="11" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C139" s="10" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D139" s="8" t="str">
         <f>VLOOKUP(B139,[1]export!$B$2:$AE$194,30,0)</f>
-        <v>최낙호</v>
+        <v>손효동</v>
       </c>
       <c r="E139" s="10" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="F139" s="2"/>
       <c r="G139" s="2"/>
@@ -22798,17 +24247,17 @@
         <v>156</v>
       </c>
       <c r="B140" s="11" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C140" s="10" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D140" s="8" t="str">
         <f>VLOOKUP(B140,[1]export!$B$2:$AE$194,30,0)</f>
-        <v>박현진</v>
+        <v>최낙호</v>
       </c>
       <c r="E140" s="10" t="s">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="F140" s="2"/>
       <c r="G140" s="2"/>
@@ -22823,17 +24272,17 @@
         <v>157</v>
       </c>
       <c r="B141" s="11" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C141" s="10" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="D141" s="8" t="str">
         <f>VLOOKUP(B141,[1]export!$B$2:$AE$194,30,0)</f>
-        <v>김연준</v>
+        <v>박현진</v>
       </c>
       <c r="E141" s="10" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="F141" s="2"/>
       <c r="G141" s="2"/>
@@ -22848,17 +24297,17 @@
         <v>158</v>
       </c>
       <c r="B142" s="11" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C142" s="10" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D142" s="8" t="str">
         <f>VLOOKUP(B142,[1]export!$B$2:$AE$194,30,0)</f>
-        <v>안우진</v>
+        <v>김연준</v>
       </c>
       <c r="E142" s="10" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="F142" s="2"/>
       <c r="G142" s="2"/>
@@ -22873,17 +24322,17 @@
         <v>159</v>
       </c>
       <c r="B143" s="11" t="s">
-        <v>295</v>
-      </c>
-      <c r="C143" s="8" t="s">
-        <v>296</v>
+        <v>283</v>
+      </c>
+      <c r="C143" s="10" t="s">
+        <v>284</v>
       </c>
       <c r="D143" s="8" t="str">
         <f>VLOOKUP(B143,[1]export!$B$2:$AE$194,30,0)</f>
-        <v>강태호</v>
+        <v>안우진</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F143" s="2"/>
       <c r="G143" s="2"/>
@@ -22898,17 +24347,17 @@
         <v>160</v>
       </c>
       <c r="B144" s="11" t="s">
-        <v>285</v>
-      </c>
-      <c r="C144" s="10" t="s">
-        <v>286</v>
+        <v>295</v>
+      </c>
+      <c r="C144" s="8" t="s">
+        <v>296</v>
       </c>
       <c r="D144" s="8" t="str">
         <f>VLOOKUP(B144,[1]export!$B$2:$AE$194,30,0)</f>
-        <v>최낙호</v>
+        <v>강태호</v>
       </c>
       <c r="E144" s="10" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="F144" s="2"/>
       <c r="G144" s="2"/>
@@ -22923,17 +24372,17 @@
         <v>161</v>
       </c>
       <c r="B145" s="11" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C145" s="10" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D145" s="8" t="str">
         <f>VLOOKUP(B145,[1]export!$B$2:$AE$194,30,0)</f>
-        <v>김연준</v>
+        <v>최낙호</v>
       </c>
       <c r="E145" s="10" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="F145" s="2"/>
       <c r="G145" s="2"/>
@@ -22948,17 +24397,17 @@
         <v>162</v>
       </c>
       <c r="B146" s="11" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C146" s="10" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="D146" s="8" t="str">
         <f>VLOOKUP(B146,[1]export!$B$2:$AE$194,30,0)</f>
-        <v>전재영</v>
+        <v>김연준</v>
       </c>
       <c r="E146" s="10" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F146" s="2"/>
       <c r="G146" s="2"/>
@@ -22973,17 +24422,17 @@
         <v>163</v>
       </c>
       <c r="B147" s="11" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C147" s="10" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D147" s="8" t="str">
         <f>VLOOKUP(B147,[1]export!$B$2:$AE$194,30,0)</f>
-        <v>왕준하</v>
+        <v>전재영</v>
       </c>
       <c r="E147" s="10" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="F147" s="2"/>
       <c r="G147" s="2"/>
@@ -22998,17 +24447,17 @@
         <v>164</v>
       </c>
       <c r="B148" s="11" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C148" s="10" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D148" s="8" t="str">
         <f>VLOOKUP(B148,[1]export!$B$2:$AE$194,30,0)</f>
-        <v>설광배</v>
+        <v>왕준하</v>
       </c>
       <c r="E148" s="10" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F148" s="2"/>
       <c r="G148" s="2"/>
@@ -23019,25 +24468,50 @@
       <c r="N148" s="2"/>
     </row>
     <row r="149" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A149" s="9">
+      <c r="A149" s="6">
         <v>165</v>
       </c>
-      <c r="B149" s="9" t="s">
+      <c r="B149" s="11" t="s">
+        <v>293</v>
+      </c>
+      <c r="C149" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="D149" s="8" t="str">
+        <f>VLOOKUP(B149,[1]export!$B$2:$AE$194,30,0)</f>
+        <v>설광배</v>
+      </c>
+      <c r="E149" s="10" t="s">
+        <v>308</v>
+      </c>
+      <c r="F149" s="2"/>
+      <c r="G149" s="2"/>
+      <c r="H149" s="2"/>
+      <c r="I149" s="2"/>
+      <c r="J149" s="2"/>
+      <c r="M149" s="2"/>
+      <c r="N149" s="2"/>
+    </row>
+    <row r="150" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A150" s="6">
+        <v>166</v>
+      </c>
+      <c r="B150" s="9" t="s">
         <v>315</v>
       </c>
-      <c r="C149" s="10" t="s">
+      <c r="C150" s="10" t="s">
         <v>314</v>
       </c>
-      <c r="D149" s="10" t="s">
+      <c r="D150" s="10" t="s">
         <v>316</v>
       </c>
-      <c r="E149" s="10" t="s">
+      <c r="E150" s="10" t="s">
         <v>308</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="C150:E65505 C1:E1 C2:C148 C149:D149">
+  <conditionalFormatting sqref="C151:E65506 C1:E1 C2:C149 C150:D150">
     <cfRule type="duplicateValues" dxfId="0" priority="6" stopIfTrue="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
